--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="311">
   <si>
     <t>Year</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Chester Twp Auditor</t>
   </si>
   <si>
+    <t>Council Member City of Sunbury Sunbury City</t>
+  </si>
+  <si>
     <t>TYRE MACON</t>
   </si>
   <si>
@@ -47,9 +50,18 @@
     <t>AKESHA GAINER</t>
   </si>
   <si>
+    <t>DEM VICTORIA ROSANCRANS</t>
+  </si>
+  <si>
+    <t>REP ANDREW RAMOS</t>
+  </si>
+  <si>
     <t>Delaware County (Media + boroughs + townships)</t>
   </si>
   <si>
+    <t>Northumberland County (Sunbury + Shamokin + boroughs)</t>
+  </si>
+  <si>
     <t>DEM JUDGE OF THE COURT OF COMMON PLEAS</t>
   </si>
   <si>
@@ -921,9 +933,6 @@
   </si>
   <si>
     <t>Lehigh County (Allentown + boroughs + townships)</t>
-  </si>
-  <si>
-    <t>Northumberland County (Sunbury + Shamokin + boroughs)</t>
   </si>
   <si>
     <t>York County (city + boroughs + townships)</t>
@@ -1296,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1327,7 +1336,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>773</v>
@@ -1336,7 +1345,7 @@
         <v>33.97802197802198</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1347,7 +1356,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>757</v>
@@ -1356,7 +1365,7 @@
         <v>33.27472527472528</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1367,7 +1376,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>745</v>
@@ -1376,7 +1385,47 @@
         <v>32.74725274725274</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>752</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>2025</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>752</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1414,10 +1463,10 @@
         <v>2021</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D2">
         <v>3420</v>
@@ -1426,7 +1475,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1434,10 +1483,10 @@
         <v>2021</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D3">
         <v>2391</v>
@@ -1446,7 +1495,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1454,10 +1503,10 @@
         <v>2021</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D4">
         <v>2184</v>
@@ -1466,7 +1515,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1474,10 +1523,10 @@
         <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D6">
         <v>572</v>
@@ -1486,7 +1535,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F6" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1494,10 +1543,10 @@
         <v>2021</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D7">
         <v>380</v>
@@ -1506,7 +1555,7 @@
         <v>31.25</v>
       </c>
       <c r="F7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1514,10 +1563,10 @@
         <v>2021</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D8">
         <v>264</v>
@@ -1526,7 +1575,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1534,10 +1583,10 @@
         <v>2021</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D10">
         <v>177</v>
@@ -1546,7 +1595,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F10" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1554,10 +1603,10 @@
         <v>2021</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D11">
         <v>141</v>
@@ -1566,7 +1615,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1574,10 +1623,10 @@
         <v>2021</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D12">
         <v>81</v>
@@ -1586,7 +1635,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F12" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1594,10 +1643,10 @@
         <v>2021</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D13">
         <v>44</v>
@@ -1606,7 +1655,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F13" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1614,10 +1663,10 @@
         <v>2021</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D15">
         <v>1471</v>
@@ -1626,7 +1675,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F15" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1634,10 +1683,10 @@
         <v>2021</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D16">
         <v>1247</v>
@@ -1646,7 +1695,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F16" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1654,10 +1703,10 @@
         <v>2021</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D17">
         <v>616</v>
@@ -1666,7 +1715,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F17" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1674,10 +1723,10 @@
         <v>2021</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>1183</v>
@@ -1686,7 +1735,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F19" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1694,10 +1743,10 @@
         <v>2021</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D20">
         <v>1177</v>
@@ -1706,7 +1755,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F20" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1714,10 +1763,10 @@
         <v>2021</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D21">
         <v>373</v>
@@ -1726,7 +1775,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F21" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1734,10 +1783,10 @@
         <v>2021</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D22">
         <v>270</v>
@@ -1746,7 +1795,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F22" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1754,10 +1803,10 @@
         <v>2021</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D24">
         <v>2064</v>
@@ -1766,7 +1815,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F24" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1774,10 +1823,10 @@
         <v>2021</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D25">
         <v>1942</v>
@@ -1786,7 +1835,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F25" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1794,10 +1843,10 @@
         <v>2021</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D26">
         <v>1927</v>
@@ -1806,7 +1855,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F26" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1814,10 +1863,10 @@
         <v>2021</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D27">
         <v>1817</v>
@@ -1826,7 +1875,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F27" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1834,10 +1883,10 @@
         <v>2021</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D29">
         <v>167</v>
@@ -1846,7 +1895,7 @@
         <v>30.36363636363636</v>
       </c>
       <c r="F29" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1854,10 +1903,10 @@
         <v>2021</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D30">
         <v>163</v>
@@ -1866,7 +1915,7 @@
         <v>29.63636363636364</v>
       </c>
       <c r="F30" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1874,10 +1923,10 @@
         <v>2021</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D31">
         <v>130</v>
@@ -1886,7 +1935,7 @@
         <v>23.63636363636364</v>
       </c>
       <c r="F31" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1894,10 +1943,10 @@
         <v>2021</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D32">
         <v>90</v>
@@ -1906,7 +1955,7 @@
         <v>16.36363636363636</v>
       </c>
       <c r="F32" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1914,10 +1963,10 @@
         <v>2021</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D34">
         <v>522</v>
@@ -1926,7 +1975,7 @@
         <v>48.33333333333334</v>
       </c>
       <c r="F34" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1934,10 +1983,10 @@
         <v>2021</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D35">
         <v>331</v>
@@ -1946,7 +1995,7 @@
         <v>30.64814814814815</v>
       </c>
       <c r="F35" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1954,10 +2003,10 @@
         <v>2021</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D36">
         <v>227</v>
@@ -1966,7 +2015,7 @@
         <v>21.01851851851852</v>
       </c>
       <c r="F36" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1974,10 +2023,10 @@
         <v>2021</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D38">
         <v>4922</v>
@@ -1986,7 +2035,7 @@
         <v>41.68713475057169</v>
       </c>
       <c r="F38" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1994,10 +2043,10 @@
         <v>2021</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D39">
         <v>4820</v>
@@ -2006,7 +2055,7 @@
         <v>40.82324045058016</v>
       </c>
       <c r="F39" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2014,10 +2063,10 @@
         <v>2021</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D40">
         <v>2065</v>
@@ -2026,7 +2075,7 @@
         <v>17.48962479884814</v>
       </c>
       <c r="F40" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2034,10 +2083,10 @@
         <v>2021</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D42">
         <v>1779</v>
@@ -2046,7 +2095,7 @@
         <v>46.82811266122664</v>
       </c>
       <c r="F42" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2054,10 +2103,10 @@
         <v>2021</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D43">
         <v>1349</v>
@@ -2066,7 +2115,7 @@
         <v>35.50934456435904</v>
       </c>
       <c r="F43" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2074,10 +2123,10 @@
         <v>2021</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D44">
         <v>671</v>
@@ -2086,7 +2135,7 @@
         <v>17.66254277441432</v>
       </c>
       <c r="F44" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2094,10 +2143,10 @@
         <v>2021</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D46">
         <v>253</v>
@@ -2106,7 +2155,7 @@
         <v>37.09677419354838</v>
       </c>
       <c r="F46" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2114,10 +2163,10 @@
         <v>2021</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D47">
         <v>224</v>
@@ -2126,7 +2175,7 @@
         <v>32.84457478005865</v>
       </c>
       <c r="F47" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2134,10 +2183,10 @@
         <v>2021</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D48">
         <v>122</v>
@@ -2146,7 +2195,7 @@
         <v>17.88856304985337</v>
       </c>
       <c r="F48" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2154,10 +2203,10 @@
         <v>2021</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D49">
         <v>60</v>
@@ -2166,7 +2215,7 @@
         <v>8.797653958944283</v>
       </c>
       <c r="F49" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2174,10 +2223,10 @@
         <v>2021</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D50">
         <v>23</v>
@@ -2186,7 +2235,7 @@
         <v>3.372434017595308</v>
       </c>
       <c r="F50" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2194,10 +2243,10 @@
         <v>2021</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D52">
         <v>917</v>
@@ -2206,7 +2255,7 @@
         <v>36.31683168316832</v>
       </c>
       <c r="F52" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2214,10 +2263,10 @@
         <v>2021</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D53">
         <v>706</v>
@@ -2226,7 +2275,7 @@
         <v>27.96039603960396</v>
       </c>
       <c r="F53" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2234,10 +2283,10 @@
         <v>2021</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D54">
         <v>578</v>
@@ -2246,7 +2295,7 @@
         <v>22.89108910891089</v>
       </c>
       <c r="F54" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2254,10 +2303,10 @@
         <v>2021</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D55">
         <v>324</v>
@@ -2266,7 +2315,7 @@
         <v>12.83168316831683</v>
       </c>
       <c r="F55" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2274,10 +2323,10 @@
         <v>2021</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D57">
         <v>682</v>
@@ -2286,7 +2335,7 @@
         <v>41.89189189189189</v>
       </c>
       <c r="F57" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2294,10 +2343,10 @@
         <v>2021</v>
       </c>
       <c r="B58" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D58">
         <v>653</v>
@@ -2306,7 +2355,7 @@
         <v>40.11056511056511</v>
       </c>
       <c r="F58" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2314,10 +2363,10 @@
         <v>2021</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D59">
         <v>293</v>
@@ -2326,7 +2375,7 @@
         <v>17.997542997543</v>
       </c>
       <c r="F59" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2334,10 +2383,10 @@
         <v>2021</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D61">
         <v>301</v>
@@ -2346,7 +2395,7 @@
         <v>35.16355140186916</v>
       </c>
       <c r="F61" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2354,10 +2403,10 @@
         <v>2021</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D62">
         <v>292</v>
@@ -2366,7 +2415,7 @@
         <v>34.11214953271028</v>
       </c>
       <c r="F62" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2374,10 +2423,10 @@
         <v>2021</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D63">
         <v>132</v>
@@ -2386,7 +2435,7 @@
         <v>15.42056074766355</v>
       </c>
       <c r="F63" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2394,10 +2443,10 @@
         <v>2021</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D64">
         <v>131</v>
@@ -2406,7 +2455,7 @@
         <v>15.30373831775701</v>
       </c>
       <c r="F64" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2414,10 +2463,10 @@
         <v>2021</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D66">
         <v>235</v>
@@ -2426,7 +2475,7 @@
         <v>38.14935064935065</v>
       </c>
       <c r="F66" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2434,10 +2483,10 @@
         <v>2021</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C67" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D67">
         <v>173</v>
@@ -2446,7 +2495,7 @@
         <v>28.08441558441558</v>
       </c>
       <c r="F67" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2454,10 +2503,10 @@
         <v>2021</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D68">
         <v>154</v>
@@ -2466,7 +2515,7 @@
         <v>25</v>
       </c>
       <c r="F68" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2474,10 +2523,10 @@
         <v>2021</v>
       </c>
       <c r="B69" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D69">
         <v>54</v>
@@ -2486,7 +2535,7 @@
         <v>8.766233766233766</v>
       </c>
       <c r="F69" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2494,10 +2543,10 @@
         <v>2021</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C71" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D71">
         <v>179</v>
@@ -2506,7 +2555,7 @@
         <v>45.31645569620253</v>
       </c>
       <c r="F71" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2514,10 +2563,10 @@
         <v>2021</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D72">
         <v>110</v>
@@ -2526,7 +2575,7 @@
         <v>27.84810126582278</v>
       </c>
       <c r="F72" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2534,10 +2583,10 @@
         <v>2021</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D73">
         <v>106</v>
@@ -2546,7 +2595,7 @@
         <v>26.83544303797468</v>
       </c>
       <c r="F73" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2554,10 +2603,10 @@
         <v>2021</v>
       </c>
       <c r="B75" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C75" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D75">
         <v>276</v>
@@ -2566,7 +2615,7 @@
         <v>47.01873935264054</v>
       </c>
       <c r="F75" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2574,10 +2623,10 @@
         <v>2021</v>
       </c>
       <c r="B76" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C76" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D76">
         <v>226</v>
@@ -2586,7 +2635,7 @@
         <v>38.50085178875639</v>
       </c>
       <c r="F76" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2594,10 +2643,10 @@
         <v>2021</v>
       </c>
       <c r="B77" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D77">
         <v>85</v>
@@ -2606,7 +2655,7 @@
         <v>14.48040885860307</v>
       </c>
       <c r="F77" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2614,10 +2663,10 @@
         <v>2021</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D79">
         <v>636</v>
@@ -2626,7 +2675,7 @@
         <v>41.24513618677042</v>
       </c>
       <c r="F79" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2634,10 +2683,10 @@
         <v>2021</v>
       </c>
       <c r="B80" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D80">
         <v>544</v>
@@ -2646,7 +2695,7 @@
         <v>35.27885862516213</v>
       </c>
       <c r="F80" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2654,10 +2703,10 @@
         <v>2021</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C81" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D81">
         <v>362</v>
@@ -2666,7 +2715,7 @@
         <v>23.47600518806744</v>
       </c>
       <c r="F81" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2674,10 +2723,10 @@
         <v>2023</v>
       </c>
       <c r="B83" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D83">
         <v>113</v>
@@ -2686,7 +2735,7 @@
         <v>32.7536231884058</v>
       </c>
       <c r="F83" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2694,10 +2743,10 @@
         <v>2023</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C84" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D84">
         <v>13</v>
@@ -2706,7 +2755,7 @@
         <v>3.768115942028986</v>
       </c>
       <c r="F84" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2714,10 +2763,10 @@
         <v>2023</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C85" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D85">
         <v>5</v>
@@ -2726,7 +2775,7 @@
         <v>1.449275362318841</v>
       </c>
       <c r="F85" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2734,10 +2783,10 @@
         <v>2023</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -2746,7 +2795,7 @@
         <v>1.159420289855073</v>
       </c>
       <c r="F86" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2754,10 +2803,10 @@
         <v>2023</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D88">
         <v>156</v>
@@ -2766,7 +2815,7 @@
         <v>31.51515151515151</v>
       </c>
       <c r="F88" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2774,10 +2823,10 @@
         <v>2023</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D89">
         <v>153</v>
@@ -2786,7 +2835,7 @@
         <v>30.90909090909091</v>
       </c>
       <c r="F89" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2794,10 +2843,10 @@
         <v>2023</v>
       </c>
       <c r="B90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C90" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D90">
         <v>104</v>
@@ -2806,7 +2855,7 @@
         <v>21.01010101010101</v>
       </c>
       <c r="F90" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2814,10 +2863,10 @@
         <v>2023</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D91">
         <v>82</v>
@@ -2826,7 +2875,7 @@
         <v>16.56565656565657</v>
       </c>
       <c r="F91" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2834,10 +2883,10 @@
         <v>2023</v>
       </c>
       <c r="B93" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D93">
         <v>151</v>
@@ -2846,7 +2895,7 @@
         <v>29.78303747534517</v>
       </c>
       <c r="F93" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2854,10 +2903,10 @@
         <v>2023</v>
       </c>
       <c r="B94" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D94">
         <v>64</v>
@@ -2866,7 +2915,7 @@
         <v>12.6232741617357</v>
       </c>
       <c r="F94" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2874,10 +2923,10 @@
         <v>2023</v>
       </c>
       <c r="B95" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D95">
         <v>48</v>
@@ -2886,7 +2935,7 @@
         <v>9.467455621301776</v>
       </c>
       <c r="F95" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2894,10 +2943,10 @@
         <v>2023</v>
       </c>
       <c r="B96" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C96" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D96">
         <v>9</v>
@@ -2906,7 +2955,7 @@
         <v>1.775147928994083</v>
       </c>
       <c r="F96" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2914,10 +2963,10 @@
         <v>2023</v>
       </c>
       <c r="B98" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C98" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D98">
         <v>104</v>
@@ -2926,7 +2975,7 @@
         <v>38.95131086142322</v>
       </c>
       <c r="F98" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2934,10 +2983,10 @@
         <v>2023</v>
       </c>
       <c r="B99" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C99" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D99">
         <v>100</v>
@@ -2946,7 +2995,7 @@
         <v>37.45318352059925</v>
       </c>
       <c r="F99" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2954,10 +3003,10 @@
         <v>2023</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C100" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D100">
         <v>63</v>
@@ -2966,7 +3015,7 @@
         <v>23.59550561797753</v>
       </c>
       <c r="F100" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2974,10 +3023,10 @@
         <v>2023</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C102" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D102">
         <v>445</v>
@@ -2986,7 +3035,7 @@
         <v>43.28793774319066</v>
       </c>
       <c r="F102" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2994,10 +3043,10 @@
         <v>2023</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C103" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D103">
         <v>353</v>
@@ -3006,7 +3055,7 @@
         <v>34.33852140077821</v>
       </c>
       <c r="F103" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3014,10 +3063,10 @@
         <v>2023</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C104" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D104">
         <v>230</v>
@@ -3026,7 +3075,7 @@
         <v>22.37354085603113</v>
       </c>
       <c r="F104" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3034,10 +3083,10 @@
         <v>2023</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C106" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D106">
         <v>684</v>
@@ -3046,7 +3095,7 @@
         <v>46.94577899794098</v>
       </c>
       <c r="F106" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3054,10 +3103,10 @@
         <v>2023</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C107" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D107">
         <v>395</v>
@@ -3066,7 +3115,7 @@
         <v>27.1105010295127</v>
       </c>
       <c r="F107" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3074,10 +3123,10 @@
         <v>2023</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C108" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D108">
         <v>378</v>
@@ -3086,7 +3135,7 @@
         <v>25.94371997254633</v>
       </c>
       <c r="F108" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3094,10 +3143,10 @@
         <v>2023</v>
       </c>
       <c r="B110" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C110" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D110">
         <v>828</v>
@@ -3106,7 +3155,7 @@
         <v>36.71840354767184</v>
       </c>
       <c r="F110" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3114,10 +3163,10 @@
         <v>2023</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C111" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D111">
         <v>524</v>
@@ -3126,7 +3175,7 @@
         <v>23.23725055432372</v>
       </c>
       <c r="F111" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3134,10 +3183,10 @@
         <v>2023</v>
       </c>
       <c r="B112" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C112" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D112">
         <v>485</v>
@@ -3146,7 +3195,7 @@
         <v>21.50776053215078</v>
       </c>
       <c r="F112" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3154,10 +3203,10 @@
         <v>2023</v>
       </c>
       <c r="B113" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C113" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D113">
         <v>261</v>
@@ -3166,7 +3215,7 @@
         <v>11.57427937915743</v>
       </c>
       <c r="F113" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3174,10 +3223,10 @@
         <v>2023</v>
       </c>
       <c r="B114" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C114" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D114">
         <v>157</v>
@@ -3186,7 +3235,7 @@
         <v>6.962305986696231</v>
       </c>
       <c r="F114" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3194,10 +3243,10 @@
         <v>2023</v>
       </c>
       <c r="B116" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C116" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D116">
         <v>584</v>
@@ -3206,7 +3255,7 @@
         <v>43.90977443609022</v>
       </c>
       <c r="F116" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3214,10 +3263,10 @@
         <v>2023</v>
       </c>
       <c r="B117" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C117" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D117">
         <v>388</v>
@@ -3226,7 +3275,7 @@
         <v>29.17293233082707</v>
       </c>
       <c r="F117" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3234,10 +3283,10 @@
         <v>2023</v>
       </c>
       <c r="B118" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C118" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D118">
         <v>358</v>
@@ -3246,7 +3295,7 @@
         <v>26.91729323308271</v>
       </c>
       <c r="F118" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3254,10 +3303,10 @@
         <v>2023</v>
       </c>
       <c r="B120" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C120" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D120">
         <v>634</v>
@@ -3266,7 +3315,7 @@
         <v>45.67723342939482</v>
       </c>
       <c r="F120" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3274,10 +3323,10 @@
         <v>2023</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C121" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D121">
         <v>298</v>
@@ -3286,7 +3335,7 @@
         <v>21.46974063400576</v>
       </c>
       <c r="F121" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3294,10 +3343,10 @@
         <v>2023</v>
       </c>
       <c r="B122" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C122" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D122">
         <v>246</v>
@@ -3306,7 +3355,7 @@
         <v>17.72334293948127</v>
       </c>
       <c r="F122" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3314,10 +3363,10 @@
         <v>2023</v>
       </c>
       <c r="B123" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C123" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D123">
         <v>210</v>
@@ -3326,7 +3375,7 @@
         <v>15.12968299711815</v>
       </c>
       <c r="F123" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3334,10 +3383,10 @@
         <v>2023</v>
       </c>
       <c r="B125" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C125" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D125">
         <v>294</v>
@@ -3346,7 +3395,7 @@
         <v>38.33116036505867</v>
       </c>
       <c r="F125" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3354,10 +3403,10 @@
         <v>2023</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C126" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D126">
         <v>145</v>
@@ -3366,7 +3415,7 @@
         <v>18.90482398956975</v>
       </c>
       <c r="F126" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3374,10 +3423,10 @@
         <v>2023</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C127" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D127">
         <v>136</v>
@@ -3386,7 +3435,7 @@
         <v>17.73142112125163</v>
       </c>
       <c r="F127" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3394,10 +3443,10 @@
         <v>2023</v>
       </c>
       <c r="B128" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C128" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D128">
         <v>104</v>
@@ -3406,7 +3455,7 @@
         <v>13.5593220338983</v>
       </c>
       <c r="F128" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3414,10 +3463,10 @@
         <v>2023</v>
       </c>
       <c r="B129" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C129" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D129">
         <v>88</v>
@@ -3426,7 +3475,7 @@
         <v>11.47327249022164</v>
       </c>
       <c r="F129" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3434,10 +3483,10 @@
         <v>2023</v>
       </c>
       <c r="B131" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C131" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D131">
         <v>154</v>
@@ -3446,7 +3495,7 @@
         <v>41.06666666666667</v>
       </c>
       <c r="F131" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3454,10 +3503,10 @@
         <v>2023</v>
       </c>
       <c r="B133" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C133" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D133">
         <v>598</v>
@@ -3466,7 +3515,7 @@
         <v>31.24346917450366</v>
       </c>
       <c r="F133" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3474,10 +3523,10 @@
         <v>2023</v>
       </c>
       <c r="B134" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C134" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D134">
         <v>493</v>
@@ -3486,7 +3535,7 @@
         <v>25.75757575757576</v>
       </c>
       <c r="F134" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3494,10 +3543,10 @@
         <v>2023</v>
       </c>
       <c r="B135" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C135" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D135">
         <v>368</v>
@@ -3506,7 +3555,7 @@
         <v>19.22675026123302</v>
       </c>
       <c r="F135" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3514,10 +3563,10 @@
         <v>2023</v>
       </c>
       <c r="B136" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C136" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D136">
         <v>282</v>
@@ -3526,7 +3575,7 @@
         <v>14.73354231974922</v>
       </c>
       <c r="F136" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3534,10 +3583,10 @@
         <v>2023</v>
       </c>
       <c r="B137" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C137" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D137">
         <v>173</v>
@@ -3546,7 +3595,7 @@
         <v>9.03866248693835</v>
       </c>
       <c r="F137" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3554,10 +3603,10 @@
         <v>2023</v>
       </c>
       <c r="B139" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C139" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D139">
         <v>148</v>
@@ -3566,7 +3615,7 @@
         <v>29.83870967741936</v>
       </c>
       <c r="F139" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3574,10 +3623,10 @@
         <v>2023</v>
       </c>
       <c r="B140" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C140" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D140">
         <v>20</v>
@@ -3586,7 +3635,7 @@
         <v>4.032258064516129</v>
       </c>
       <c r="F140" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3594,10 +3643,10 @@
         <v>2023</v>
       </c>
       <c r="B141" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C141" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D141">
         <v>10</v>
@@ -3606,7 +3655,7 @@
         <v>2.016129032258065</v>
       </c>
       <c r="F141" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3614,10 +3663,10 @@
         <v>2023</v>
       </c>
       <c r="B142" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C142" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D142">
         <v>5</v>
@@ -3626,7 +3675,7 @@
         <v>1.008064516129032</v>
       </c>
       <c r="F142" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3634,10 +3683,10 @@
         <v>2023</v>
       </c>
       <c r="B143" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C143" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D143">
         <v>5</v>
@@ -3646,7 +3695,7 @@
         <v>1.008064516129032</v>
       </c>
       <c r="F143" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3654,10 +3703,10 @@
         <v>2023</v>
       </c>
       <c r="B145" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C145" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D145">
         <v>170</v>
@@ -3666,7 +3715,7 @@
         <v>46.19565217391305</v>
       </c>
       <c r="F145" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3674,10 +3723,10 @@
         <v>2023</v>
       </c>
       <c r="B146" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C146" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D146">
         <v>169</v>
@@ -3686,7 +3735,7 @@
         <v>45.92391304347826</v>
       </c>
       <c r="F146" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -3694,10 +3743,10 @@
         <v>2023</v>
       </c>
       <c r="B147" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C147" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D147">
         <v>29</v>
@@ -3706,7 +3755,7 @@
         <v>7.880434782608696</v>
       </c>
       <c r="F147" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3714,10 +3763,10 @@
         <v>2023</v>
       </c>
       <c r="B149" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C149" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D149">
         <v>110</v>
@@ -3726,7 +3775,7 @@
         <v>41.35338345864661</v>
       </c>
       <c r="F149" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3734,10 +3783,10 @@
         <v>2023</v>
       </c>
       <c r="B150" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C150" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D150">
         <v>79</v>
@@ -3746,7 +3795,7 @@
         <v>29.69924812030075</v>
       </c>
       <c r="F150" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -3754,10 +3803,10 @@
         <v>2023</v>
       </c>
       <c r="B151" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C151" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D151">
         <v>77</v>
@@ -3766,7 +3815,7 @@
         <v>28.94736842105263</v>
       </c>
       <c r="F151" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3774,10 +3823,10 @@
         <v>2023</v>
       </c>
       <c r="B153" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C153" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D153">
         <v>886</v>
@@ -3786,7 +3835,7 @@
         <v>48.86927744070601</v>
       </c>
       <c r="F153" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3794,10 +3843,10 @@
         <v>2023</v>
       </c>
       <c r="B154" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C154" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D154">
         <v>699</v>
@@ -3806,7 +3855,7 @@
         <v>38.55488141202427</v>
       </c>
       <c r="F154" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -3814,10 +3863,10 @@
         <v>2023</v>
       </c>
       <c r="B155" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C155" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D155">
         <v>228</v>
@@ -3826,7 +3875,7 @@
         <v>12.57584114726972</v>
       </c>
       <c r="F155" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -3834,10 +3883,10 @@
         <v>2023</v>
       </c>
       <c r="B157" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C157" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D157">
         <v>1630</v>
@@ -3846,7 +3895,7 @@
         <v>44.46262956901255</v>
       </c>
       <c r="F157" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -3854,10 +3903,10 @@
         <v>2023</v>
       </c>
       <c r="B158" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C158" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D158">
         <v>1039</v>
@@ -3866,7 +3915,7 @@
         <v>28.34151663938898</v>
       </c>
       <c r="F158" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -3874,10 +3923,10 @@
         <v>2023</v>
       </c>
       <c r="B159" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C159" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D159">
         <v>813</v>
@@ -3886,7 +3935,7 @@
         <v>22.17675941080196</v>
       </c>
       <c r="F159" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -3894,10 +3943,10 @@
         <v>2023</v>
       </c>
       <c r="B160" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C160" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D160">
         <v>184</v>
@@ -3906,7 +3955,7 @@
         <v>5.019094380796509</v>
       </c>
       <c r="F160" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -3914,10 +3963,10 @@
         <v>2023</v>
       </c>
       <c r="B162" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C162" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D162">
         <v>1334</v>
@@ -3926,7 +3975,7 @@
         <v>46.38386648122393</v>
       </c>
       <c r="F162" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -3934,10 +3983,10 @@
         <v>2023</v>
       </c>
       <c r="B163" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C163" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D163">
         <v>1278</v>
@@ -3946,7 +3995,7 @@
         <v>44.43671766342142</v>
       </c>
       <c r="F163" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -3954,10 +4003,10 @@
         <v>2023</v>
       </c>
       <c r="B164" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C164" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D164">
         <v>264</v>
@@ -3966,7 +4015,7 @@
         <v>9.179415855354661</v>
       </c>
       <c r="F164" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -3974,10 +4023,10 @@
         <v>2023</v>
       </c>
       <c r="B166" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C166" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D166">
         <v>1466</v>
@@ -3986,7 +4035,7 @@
         <v>43.1303324507208</v>
       </c>
       <c r="F166" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -3994,10 +4043,10 @@
         <v>2023</v>
       </c>
       <c r="B167" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C167" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D167">
         <v>893</v>
@@ -4006,7 +4055,7 @@
         <v>26.27243306854957</v>
       </c>
       <c r="F167" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -4014,10 +4063,10 @@
         <v>2023</v>
       </c>
       <c r="B168" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C168" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D168">
         <v>672</v>
@@ -4026,7 +4075,7 @@
         <v>19.77052074139453</v>
       </c>
       <c r="F168" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -4034,10 +4083,10 @@
         <v>2023</v>
       </c>
       <c r="B169" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C169" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D169">
         <v>245</v>
@@ -4046,7 +4095,7 @@
         <v>7.208002353633422</v>
       </c>
       <c r="F169" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -4054,10 +4103,10 @@
         <v>2023</v>
       </c>
       <c r="B170" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C170" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D170">
         <v>123</v>
@@ -4066,7 +4115,7 @@
         <v>3.618711385701677</v>
       </c>
       <c r="F170" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -4074,10 +4123,10 @@
         <v>2023</v>
       </c>
       <c r="B172" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C172" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D172">
         <v>1108</v>
@@ -4086,7 +4135,7 @@
         <v>46.4765100671141</v>
       </c>
       <c r="F172" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4094,10 +4143,10 @@
         <v>2023</v>
       </c>
       <c r="B173" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C173" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D173">
         <v>444</v>
@@ -4106,7 +4155,7 @@
         <v>18.6241610738255</v>
       </c>
       <c r="F173" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4114,10 +4163,10 @@
         <v>2023</v>
       </c>
       <c r="B174" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C174" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D174">
         <v>343</v>
@@ -4126,7 +4175,7 @@
         <v>14.38758389261745</v>
       </c>
       <c r="F174" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4134,10 +4183,10 @@
         <v>2023</v>
       </c>
       <c r="B175" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C175" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D175">
         <v>323</v>
@@ -4146,7 +4195,7 @@
         <v>13.5486577181208</v>
       </c>
       <c r="F175" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4154,10 +4203,10 @@
         <v>2023</v>
       </c>
       <c r="B176" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C176" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D176">
         <v>166</v>
@@ -4166,7 +4215,7 @@
         <v>6.963087248322148</v>
       </c>
       <c r="F176" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4174,10 +4223,10 @@
         <v>2023</v>
       </c>
       <c r="B178" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C178" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D178">
         <v>904</v>
@@ -4186,7 +4235,7 @@
         <v>42.60131950989632</v>
       </c>
       <c r="F178" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4194,10 +4243,10 @@
         <v>2023</v>
       </c>
       <c r="B179" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C179" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D179">
         <v>860</v>
@@ -4206,7 +4255,7 @@
         <v>40.52780395852969</v>
       </c>
       <c r="F179" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4214,10 +4263,10 @@
         <v>2023</v>
       </c>
       <c r="B180" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C180" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D180">
         <v>193</v>
@@ -4226,7 +4275,7 @@
         <v>9.095193213949104</v>
       </c>
       <c r="F180" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -4234,10 +4283,10 @@
         <v>2023</v>
       </c>
       <c r="B181" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C181" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D181">
         <v>165</v>
@@ -4246,7 +4295,7 @@
         <v>7.775683317624882</v>
       </c>
       <c r="F181" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -4254,10 +4303,10 @@
         <v>2023</v>
       </c>
       <c r="B183" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C183" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D183">
         <v>425</v>
@@ -4266,7 +4315,7 @@
         <v>25.11820330969267</v>
       </c>
       <c r="F183" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4274,10 +4323,10 @@
         <v>2023</v>
       </c>
       <c r="B184" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C184" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D184">
         <v>341</v>
@@ -4286,7 +4335,7 @@
         <v>20.15366430260048</v>
       </c>
       <c r="F184" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4294,10 +4343,10 @@
         <v>2023</v>
       </c>
       <c r="B185" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C185" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D185">
         <v>279</v>
@@ -4306,7 +4355,7 @@
         <v>16.48936170212766</v>
       </c>
       <c r="F185" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4314,10 +4363,10 @@
         <v>2023</v>
       </c>
       <c r="B186" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C186" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D186">
         <v>272</v>
@@ -4326,7 +4375,7 @@
         <v>16.07565011820331</v>
       </c>
       <c r="F186" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4334,10 +4383,10 @@
         <v>2023</v>
       </c>
       <c r="B187" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C187" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D187">
         <v>220</v>
@@ -4346,7 +4395,7 @@
         <v>13.00236406619385</v>
       </c>
       <c r="F187" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4354,10 +4403,10 @@
         <v>2023</v>
       </c>
       <c r="B188" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C188" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D188">
         <v>155</v>
@@ -4366,7 +4415,7 @@
         <v>9.160756501182032</v>
       </c>
       <c r="F188" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4374,10 +4423,10 @@
         <v>2023</v>
       </c>
       <c r="B190" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C190" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D190">
         <v>118</v>
@@ -4386,7 +4435,7 @@
         <v>44.3609022556391</v>
       </c>
       <c r="F190" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4394,10 +4443,10 @@
         <v>2023</v>
       </c>
       <c r="B191" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C191" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D191">
         <v>25</v>
@@ -4406,7 +4455,7 @@
         <v>9.398496240601503</v>
       </c>
       <c r="F191" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -4414,10 +4463,10 @@
         <v>2023</v>
       </c>
       <c r="B192" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C192" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D192">
         <v>10</v>
@@ -4426,7 +4475,7 @@
         <v>3.759398496240602</v>
       </c>
       <c r="F192" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4434,10 +4483,10 @@
         <v>2023</v>
       </c>
       <c r="B193" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C193" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D193">
         <v>8</v>
@@ -4446,7 +4495,7 @@
         <v>3.007518796992481</v>
       </c>
       <c r="F193" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4454,10 +4503,10 @@
         <v>2023</v>
       </c>
       <c r="B194" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C194" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D194">
         <v>6</v>
@@ -4466,7 +4515,7 @@
         <v>2.255639097744361</v>
       </c>
       <c r="F194" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4474,10 +4523,10 @@
         <v>2023</v>
       </c>
       <c r="B195" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C195" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D195">
         <v>5</v>
@@ -4486,7 +4535,7 @@
         <v>1.879699248120301</v>
       </c>
       <c r="F195" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -4494,10 +4543,10 @@
         <v>2023</v>
       </c>
       <c r="B196" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C196" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D196">
         <v>4</v>
@@ -4506,7 +4555,7 @@
         <v>1.503759398496241</v>
       </c>
       <c r="F196" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4514,10 +4563,10 @@
         <v>2023</v>
       </c>
       <c r="B197" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C197" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D197">
         <v>3</v>
@@ -4526,7 +4575,7 @@
         <v>1.12781954887218</v>
       </c>
       <c r="F197" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4534,10 +4583,10 @@
         <v>2023</v>
       </c>
       <c r="B198" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C198" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D198">
         <v>3</v>
@@ -4546,7 +4595,7 @@
         <v>1.12781954887218</v>
       </c>
       <c r="F198" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4554,10 +4603,10 @@
         <v>2023</v>
       </c>
       <c r="B199" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D199">
         <v>3</v>
@@ -4566,7 +4615,7 @@
         <v>1.12781954887218</v>
       </c>
       <c r="F199" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4574,10 +4623,10 @@
         <v>2023</v>
       </c>
       <c r="B201" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C201" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D201">
         <v>1002</v>
@@ -4586,7 +4635,7 @@
         <v>34.70730862487011</v>
       </c>
       <c r="F201" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4594,10 +4643,10 @@
         <v>2023</v>
       </c>
       <c r="B202" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C202" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D202">
         <v>878</v>
@@ -4606,7 +4655,7 @@
         <v>30.41219258746104</v>
       </c>
       <c r="F202" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4614,10 +4663,10 @@
         <v>2023</v>
       </c>
       <c r="B203" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C203" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D203">
         <v>439</v>
@@ -4626,7 +4675,7 @@
         <v>15.20609629373052</v>
       </c>
       <c r="F203" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4634,10 +4683,10 @@
         <v>2023</v>
       </c>
       <c r="B204" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C204" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D204">
         <v>329</v>
@@ -4646,7 +4695,7 @@
         <v>11.39591271215795</v>
       </c>
       <c r="F204" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4654,10 +4703,10 @@
         <v>2023</v>
       </c>
       <c r="B205" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C205" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D205">
         <v>239</v>
@@ -4666,7 +4715,7 @@
         <v>8.278489781780394</v>
       </c>
       <c r="F205" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4674,10 +4723,10 @@
         <v>2023</v>
       </c>
       <c r="B207" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C207" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D207">
         <v>286</v>
@@ -4686,7 +4735,7 @@
         <v>48.22934232715008</v>
       </c>
       <c r="F207" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4694,10 +4743,10 @@
         <v>2023</v>
       </c>
       <c r="B208" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C208" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D208">
         <v>212</v>
@@ -4706,7 +4755,7 @@
         <v>35.7504215851602</v>
       </c>
       <c r="F208" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4714,10 +4763,10 @@
         <v>2023</v>
       </c>
       <c r="B209" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C209" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D209">
         <v>95</v>
@@ -4726,7 +4775,7 @@
         <v>16.02023608768971</v>
       </c>
       <c r="F209" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4734,10 +4783,10 @@
         <v>2023</v>
       </c>
       <c r="B211" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C211" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D211">
         <v>431</v>
@@ -4746,7 +4795,7 @@
         <v>36.77474402730375</v>
       </c>
       <c r="F211" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -4754,10 +4803,10 @@
         <v>2023</v>
       </c>
       <c r="B212" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C212" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D212">
         <v>297</v>
@@ -4766,7 +4815,7 @@
         <v>25.34129692832764</v>
       </c>
       <c r="F212" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -4774,10 +4823,10 @@
         <v>2023</v>
       </c>
       <c r="B213" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C213" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D213">
         <v>285</v>
@@ -4786,7 +4835,7 @@
         <v>24.31740614334471</v>
       </c>
       <c r="F213" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -4794,10 +4843,10 @@
         <v>2023</v>
       </c>
       <c r="B214" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C214" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D214">
         <v>96</v>
@@ -4806,7 +4855,7 @@
         <v>8.191126279863481</v>
       </c>
       <c r="F214" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -4814,10 +4863,10 @@
         <v>2023</v>
       </c>
       <c r="B215" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C215" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D215">
         <v>63</v>
@@ -4826,7 +4875,7 @@
         <v>5.375426621160409</v>
       </c>
       <c r="F215" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -4834,10 +4883,10 @@
         <v>2023</v>
       </c>
       <c r="B217" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C217" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D217">
         <v>273</v>
@@ -4846,7 +4895,7 @@
         <v>45.4242928452579</v>
       </c>
       <c r="F217" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -4854,10 +4903,10 @@
         <v>2023</v>
       </c>
       <c r="B218" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C218" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D218">
         <v>234</v>
@@ -4866,7 +4915,7 @@
         <v>38.9351081530782</v>
       </c>
       <c r="F218" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -4874,10 +4923,10 @@
         <v>2023</v>
       </c>
       <c r="B219" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C219" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D219">
         <v>94</v>
@@ -4886,7 +4935,7 @@
         <v>15.64059900166389</v>
       </c>
       <c r="F219" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -4894,10 +4943,10 @@
         <v>2023</v>
       </c>
       <c r="B221" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C221" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D221">
         <v>124</v>
@@ -4906,7 +4955,7 @@
         <v>47.69230769230769</v>
       </c>
       <c r="F221" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -4914,10 +4963,10 @@
         <v>2023</v>
       </c>
       <c r="B222" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C222" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D222">
         <v>73</v>
@@ -4926,7 +4975,7 @@
         <v>28.07692307692308</v>
       </c>
       <c r="F222" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -4934,10 +4983,10 @@
         <v>2023</v>
       </c>
       <c r="B223" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C223" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D223">
         <v>63</v>
@@ -4946,7 +4995,7 @@
         <v>24.23076923076923</v>
       </c>
       <c r="F223" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -4954,10 +5003,10 @@
         <v>2023</v>
       </c>
       <c r="B225" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C225" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D225">
         <v>827</v>
@@ -4966,7 +5015,7 @@
         <v>47.88650839606254</v>
       </c>
       <c r="F225" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -4974,10 +5023,10 @@
         <v>2023</v>
       </c>
       <c r="B226" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C226" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D226">
         <v>284</v>
@@ -4986,7 +5035,7 @@
         <v>16.44470179502026</v>
       </c>
       <c r="F226" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -4994,10 +5043,10 @@
         <v>2023</v>
       </c>
       <c r="B227" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C227" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D227">
         <v>222</v>
@@ -5006,7 +5055,7 @@
         <v>12.85466126230457</v>
       </c>
       <c r="F227" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -5014,10 +5063,10 @@
         <v>2023</v>
       </c>
       <c r="B228" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C228" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D228">
         <v>211</v>
@@ -5026,7 +5075,7 @@
         <v>12.21771858714534</v>
       </c>
       <c r="F228" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -5034,10 +5083,10 @@
         <v>2023</v>
       </c>
       <c r="B229" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C229" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D229">
         <v>183</v>
@@ -5046,7 +5095,7 @@
         <v>10.59640995946728</v>
       </c>
       <c r="F229" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -5054,10 +5103,10 @@
         <v>2023</v>
       </c>
       <c r="B231" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C231" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D231">
         <v>605</v>
@@ -5066,7 +5115,7 @@
         <v>41.10054347826087</v>
       </c>
       <c r="F231" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -5074,10 +5123,10 @@
         <v>2023</v>
       </c>
       <c r="B232" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C232" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D232">
         <v>593</v>
@@ -5086,7 +5135,7 @@
         <v>40.28532608695652</v>
       </c>
       <c r="F232" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -5094,10 +5143,10 @@
         <v>2023</v>
       </c>
       <c r="B233" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C233" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D233">
         <v>274</v>
@@ -5106,7 +5155,7 @@
         <v>18.61413043478261</v>
       </c>
       <c r="F233" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5114,10 +5163,10 @@
         <v>2023</v>
       </c>
       <c r="B235" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C235" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D235">
         <v>347</v>
@@ -5126,7 +5175,7 @@
         <v>49.15014164305949</v>
       </c>
       <c r="F235" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -5134,10 +5183,10 @@
         <v>2023</v>
       </c>
       <c r="B236" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C236" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D236">
         <v>168</v>
@@ -5146,7 +5195,7 @@
         <v>23.79603399433428</v>
       </c>
       <c r="F236" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -5154,10 +5203,10 @@
         <v>2023</v>
       </c>
       <c r="B237" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C237" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D237">
         <v>103</v>
@@ -5166,7 +5215,7 @@
         <v>14.58923512747875</v>
       </c>
       <c r="F237" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5174,10 +5223,10 @@
         <v>2023</v>
       </c>
       <c r="B238" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C238" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D238">
         <v>88</v>
@@ -5186,7 +5235,7 @@
         <v>12.46458923512748</v>
       </c>
       <c r="F238" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -5194,10 +5243,10 @@
         <v>2024</v>
       </c>
       <c r="B240" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C240" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D240">
         <v>147</v>
@@ -5206,7 +5255,7 @@
         <v>44.68085106382978</v>
       </c>
       <c r="F240" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -5214,10 +5263,10 @@
         <v>2024</v>
       </c>
       <c r="B241" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C241" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D241">
         <v>102</v>
@@ -5226,7 +5275,7 @@
         <v>31.00303951367781</v>
       </c>
       <c r="F241" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -5234,10 +5283,10 @@
         <v>2024</v>
       </c>
       <c r="B242" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C242" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D242">
         <v>80</v>
@@ -5246,7 +5295,7 @@
         <v>24.3161094224924</v>
       </c>
       <c r="F242" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -5254,10 +5303,10 @@
         <v>2025</v>
       </c>
       <c r="B244" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C244" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D244">
         <v>977</v>
@@ -5266,7 +5315,7 @@
         <v>40.6575114440283</v>
       </c>
       <c r="F244" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -5274,10 +5323,10 @@
         <v>2025</v>
       </c>
       <c r="B245" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C245" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D245">
         <v>970</v>
@@ -5286,7 +5335,7 @@
         <v>40.36620890553475</v>
       </c>
       <c r="F245" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -5294,10 +5343,10 @@
         <v>2025</v>
       </c>
       <c r="B246" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C246" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D246">
         <v>456</v>
@@ -5306,7 +5355,7 @@
         <v>18.97627965043695</v>
       </c>
       <c r="F246" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -5314,10 +5363,10 @@
         <v>2025</v>
       </c>
       <c r="B248" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C248" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D248">
         <v>113</v>
@@ -5326,7 +5375,7 @@
         <v>21.56488549618321</v>
       </c>
       <c r="F248" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -5334,10 +5383,10 @@
         <v>2025</v>
       </c>
       <c r="B249" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C249" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D249">
         <v>42</v>
@@ -5346,7 +5395,7 @@
         <v>8.015267175572518</v>
       </c>
       <c r="F249" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -5354,10 +5403,10 @@
         <v>2025</v>
       </c>
       <c r="B250" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C250" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D250">
         <v>42</v>
@@ -5366,7 +5415,7 @@
         <v>8.015267175572518</v>
       </c>
       <c r="F250" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -5374,10 +5423,10 @@
         <v>2025</v>
       </c>
       <c r="B251" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C251" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D251">
         <v>8</v>
@@ -5386,7 +5435,7 @@
         <v>1.526717557251908</v>
       </c>
       <c r="F251" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -5394,10 +5443,10 @@
         <v>2025</v>
       </c>
       <c r="B252" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C252" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D252">
         <v>8</v>
@@ -5406,7 +5455,7 @@
         <v>1.526717557251908</v>
       </c>
       <c r="F252" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -5414,10 +5463,10 @@
         <v>2025</v>
       </c>
       <c r="B253" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C253" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D253">
         <v>7</v>
@@ -5426,7 +5475,7 @@
         <v>1.33587786259542</v>
       </c>
       <c r="F253" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -5434,10 +5483,10 @@
         <v>2025</v>
       </c>
       <c r="B254" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C254" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D254">
         <v>7</v>
@@ -5446,7 +5495,7 @@
         <v>1.33587786259542</v>
       </c>
       <c r="F254" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -5454,10 +5503,10 @@
         <v>2025</v>
       </c>
       <c r="B256" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C256" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D256">
         <v>252</v>
@@ -5466,7 +5515,7 @@
         <v>43.37349397590361</v>
       </c>
       <c r="F256" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -5474,10 +5523,10 @@
         <v>2025</v>
       </c>
       <c r="B257" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C257" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D257">
         <v>43</v>
@@ -5486,7 +5535,7 @@
         <v>7.401032702237521</v>
       </c>
       <c r="F257" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -5494,10 +5543,10 @@
         <v>2025</v>
       </c>
       <c r="B258" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C258" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D258">
         <v>12</v>
@@ -5506,7 +5555,7 @@
         <v>2.065404475043029</v>
       </c>
       <c r="F258" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -5514,10 +5563,10 @@
         <v>2025</v>
       </c>
       <c r="B259" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C259" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D259">
         <v>7</v>
@@ -5526,7 +5575,7 @@
         <v>1.204819277108434</v>
       </c>
       <c r="F259" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -5534,10 +5583,10 @@
         <v>2025</v>
       </c>
       <c r="B261" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C261" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D261">
         <v>366</v>
@@ -5546,7 +5595,7 @@
         <v>35.91756624141315</v>
       </c>
       <c r="F261" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -5554,10 +5603,10 @@
         <v>2025</v>
       </c>
       <c r="B262" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C262" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D262">
         <v>115</v>
@@ -5566,7 +5615,7 @@
         <v>11.2855740922473</v>
       </c>
       <c r="F262" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -5574,10 +5623,10 @@
         <v>2025</v>
       </c>
       <c r="B263" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C263" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D263">
         <v>94</v>
@@ -5586,7 +5635,7 @@
         <v>9.224730127576054</v>
       </c>
       <c r="F263" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -5594,10 +5643,10 @@
         <v>2025</v>
       </c>
       <c r="B264" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C264" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D264">
         <v>70</v>
@@ -5606,7 +5655,7 @@
         <v>6.869479882237488</v>
       </c>
       <c r="F264" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -5614,10 +5663,10 @@
         <v>2025</v>
       </c>
       <c r="B265" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C265" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D265">
         <v>25</v>
@@ -5626,7 +5675,7 @@
         <v>2.453385672227674</v>
       </c>
       <c r="F265" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -5634,10 +5683,10 @@
         <v>2025</v>
       </c>
       <c r="B267" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C267" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D267">
         <v>710</v>
@@ -5646,7 +5695,7 @@
         <v>46.64914586070959</v>
       </c>
       <c r="F267" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -5654,10 +5703,10 @@
         <v>2025</v>
       </c>
       <c r="B268" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C268" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D268">
         <v>617</v>
@@ -5666,7 +5715,7 @@
         <v>40.53876478318003</v>
       </c>
       <c r="F268" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -5674,10 +5723,10 @@
         <v>2025</v>
       </c>
       <c r="B269" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C269" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D269">
         <v>195</v>
@@ -5686,7 +5735,7 @@
         <v>12.81208935611038</v>
       </c>
       <c r="F269" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -5694,10 +5743,10 @@
         <v>2025</v>
       </c>
       <c r="B271" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C271" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D271">
         <v>193</v>
@@ -5706,7 +5755,7 @@
         <v>39.95859213250517</v>
       </c>
       <c r="F271" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -5714,10 +5763,10 @@
         <v>2025</v>
       </c>
       <c r="B272" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C272" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D272">
         <v>7</v>
@@ -5726,7 +5775,7 @@
         <v>1.449275362318841</v>
       </c>
       <c r="F272" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -5734,10 +5783,10 @@
         <v>2025</v>
       </c>
       <c r="B274" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C274" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D274">
         <v>336</v>
@@ -5746,7 +5795,7 @@
         <v>38.93395133256084</v>
       </c>
       <c r="F274" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -5754,10 +5803,10 @@
         <v>2025</v>
       </c>
       <c r="B275" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C275" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D275">
         <v>329</v>
@@ -5766,7 +5815,7 @@
         <v>38.12282734646581</v>
       </c>
       <c r="F275" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -5774,10 +5823,10 @@
         <v>2025</v>
       </c>
       <c r="B276" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C276" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D276">
         <v>198</v>
@@ -5786,7 +5835,7 @@
         <v>22.94322132097335</v>
       </c>
       <c r="F276" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -5794,10 +5843,10 @@
         <v>2025</v>
       </c>
       <c r="B278" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C278" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D278">
         <v>399</v>
@@ -5806,7 +5855,7 @@
         <v>47.10743801652892</v>
       </c>
       <c r="F278" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -5814,10 +5863,10 @@
         <v>2025</v>
       </c>
       <c r="B279" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C279" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D279">
         <v>279</v>
@@ -5826,7 +5875,7 @@
         <v>32.93978748524203</v>
       </c>
       <c r="F279" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -5834,10 +5883,10 @@
         <v>2025</v>
       </c>
       <c r="B280" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C280" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D280">
         <v>169</v>
@@ -5846,7 +5895,7 @@
         <v>19.95277449822904</v>
       </c>
       <c r="F280" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -5854,10 +5903,10 @@
         <v>2025</v>
       </c>
       <c r="B282" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C282" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D282">
         <v>241</v>
@@ -5866,7 +5915,7 @@
         <v>49.79338842975206</v>
       </c>
       <c r="F282" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -5874,10 +5923,10 @@
         <v>2025</v>
       </c>
       <c r="B283" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C283" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D283">
         <v>193</v>
@@ -5886,7 +5935,7 @@
         <v>39.87603305785124</v>
       </c>
       <c r="F283" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -5894,10 +5943,10 @@
         <v>2025</v>
       </c>
       <c r="B284" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C284" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D284">
         <v>49</v>
@@ -5906,7 +5955,7 @@
         <v>10.12396694214876</v>
       </c>
       <c r="F284" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -5914,10 +5963,10 @@
         <v>2025</v>
       </c>
       <c r="B286" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C286" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D286">
         <v>6552</v>
@@ -5926,7 +5975,7 @@
         <v>47.15704620699582</v>
       </c>
       <c r="F286" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -5934,10 +5983,10 @@
         <v>2025</v>
       </c>
       <c r="B287" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C287" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D287">
         <v>4724</v>
@@ -5946,7 +5995,7 @@
         <v>34.00028789405498</v>
       </c>
       <c r="F287" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -5954,10 +6003,10 @@
         <v>2025</v>
       </c>
       <c r="B288" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C288" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D288">
         <v>2618</v>
@@ -5966,7 +6015,7 @@
         <v>18.84266589894919</v>
       </c>
       <c r="F288" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -5974,10 +6023,10 @@
         <v>2025</v>
       </c>
       <c r="B290" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C290" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D290">
         <v>9318</v>
@@ -5986,7 +6035,7 @@
         <v>41.92764578833693</v>
       </c>
       <c r="F290" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -5994,10 +6043,10 @@
         <v>2025</v>
       </c>
       <c r="B291" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C291" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D291">
         <v>8700</v>
@@ -6006,7 +6055,7 @@
         <v>39.14686825053996</v>
       </c>
       <c r="F291" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -6014,10 +6063,10 @@
         <v>2025</v>
       </c>
       <c r="B292" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C292" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D292">
         <v>4206</v>
@@ -6026,7 +6075,7 @@
         <v>18.92548596112311</v>
       </c>
       <c r="F292" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -6034,10 +6083,10 @@
         <v>2025</v>
       </c>
       <c r="B294" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C294" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D294">
         <v>1473</v>
@@ -6046,7 +6095,7 @@
         <v>39.30096051227321</v>
       </c>
       <c r="F294" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -6054,10 +6103,10 @@
         <v>2025</v>
       </c>
       <c r="B295" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C295" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D295">
         <v>1297</v>
@@ -6066,7 +6115,7 @@
         <v>34.6051227321238</v>
       </c>
       <c r="F295" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -6074,10 +6123,10 @@
         <v>2025</v>
       </c>
       <c r="B296" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C296" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D296">
         <v>516</v>
@@ -6086,7 +6135,7 @@
         <v>13.76734258271078</v>
       </c>
       <c r="F296" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -6094,10 +6143,10 @@
         <v>2025</v>
       </c>
       <c r="B297" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C297" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D297">
         <v>305</v>
@@ -6106,7 +6155,7 @@
         <v>8.137673425827108</v>
       </c>
       <c r="F297" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -6114,10 +6163,10 @@
         <v>2025</v>
       </c>
       <c r="B298" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C298" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D298">
         <v>157</v>
@@ -6126,7 +6175,7 @@
         <v>4.188900747065102</v>
       </c>
       <c r="F298" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -6134,10 +6183,10 @@
         <v>2025</v>
       </c>
       <c r="B300" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C300" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D300">
         <v>232</v>
@@ -6146,7 +6195,7 @@
         <v>40.63047285464098</v>
       </c>
       <c r="F300" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -6154,10 +6203,10 @@
         <v>2025</v>
       </c>
       <c r="B301" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C301" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D301">
         <v>227</v>
@@ -6166,7 +6215,7 @@
         <v>39.75481611208406</v>
       </c>
       <c r="F301" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -6174,10 +6223,10 @@
         <v>2025</v>
       </c>
       <c r="B302" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C302" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D302">
         <v>112</v>
@@ -6186,7 +6235,7 @@
         <v>19.61471103327496</v>
       </c>
       <c r="F302" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -6194,10 +6243,10 @@
         <v>2025</v>
       </c>
       <c r="B304" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C304" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D304">
         <v>287</v>
@@ -6206,7 +6255,7 @@
         <v>47.83333333333334</v>
       </c>
       <c r="F304" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -6214,10 +6263,10 @@
         <v>2025</v>
       </c>
       <c r="B305" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C305" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D305">
         <v>175</v>
@@ -6226,7 +6275,7 @@
         <v>29.16666666666667</v>
       </c>
       <c r="F305" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -6234,10 +6283,10 @@
         <v>2025</v>
       </c>
       <c r="B306" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C306" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D306">
         <v>138</v>
@@ -6246,7 +6295,7 @@
         <v>23</v>
       </c>
       <c r="F306" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -6254,10 +6303,10 @@
         <v>2025</v>
       </c>
       <c r="B308" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C308" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D308">
         <v>660</v>
@@ -6266,7 +6315,7 @@
         <v>46.31578947368421</v>
       </c>
       <c r="F308" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -6274,10 +6323,10 @@
         <v>2025</v>
       </c>
       <c r="B309" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C309" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D309">
         <v>534</v>
@@ -6286,7 +6335,7 @@
         <v>37.47368421052632</v>
       </c>
       <c r="F309" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -6294,10 +6343,10 @@
         <v>2025</v>
       </c>
       <c r="B310" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C310" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D310">
         <v>221</v>
@@ -6306,7 +6355,7 @@
         <v>15.50877192982456</v>
       </c>
       <c r="F310" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -6314,10 +6363,10 @@
         <v>2025</v>
       </c>
       <c r="B312" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C312" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D312">
         <v>1465</v>
@@ -6326,7 +6375,7 @@
         <v>49.96589358799454</v>
       </c>
       <c r="F312" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -6334,10 +6383,10 @@
         <v>2025</v>
       </c>
       <c r="B313" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C313" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D313">
         <v>1457</v>
@@ -6346,7 +6395,7 @@
         <v>49.69304229195088</v>
       </c>
       <c r="F313" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -6354,10 +6403,10 @@
         <v>2025</v>
       </c>
       <c r="B315" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C315" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D315">
         <v>163</v>
@@ -6366,7 +6415,7 @@
         <v>38.71733966745843</v>
       </c>
       <c r="F315" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -6374,10 +6423,10 @@
         <v>2025</v>
       </c>
       <c r="B316" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C316" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D316">
         <v>160</v>
@@ -6386,7 +6435,7 @@
         <v>38.00475059382423</v>
       </c>
       <c r="F316" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -6394,10 +6443,10 @@
         <v>2025</v>
       </c>
       <c r="B317" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C317" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D317">
         <v>75</v>
@@ -6406,7 +6455,7 @@
         <v>17.81472684085511</v>
       </c>
       <c r="F317" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -6414,10 +6463,10 @@
         <v>2025</v>
       </c>
       <c r="B318" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C318" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D318">
         <v>23</v>
@@ -6426,7 +6475,7 @@
         <v>5.463182897862233</v>
       </c>
       <c r="F318" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -6434,10 +6483,10 @@
         <v>2025</v>
       </c>
       <c r="B320" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C320" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D320">
         <v>549</v>
@@ -6446,7 +6495,7 @@
         <v>42.99138606108065</v>
       </c>
       <c r="F320" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -6454,10 +6503,10 @@
         <v>2025</v>
       </c>
       <c r="B321" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C321" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D321">
         <v>445</v>
@@ -6466,7 +6515,7 @@
         <v>34.84729835552075</v>
       </c>
       <c r="F321" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -6474,10 +6523,10 @@
         <v>2025</v>
       </c>
       <c r="B322" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C322" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D322">
         <v>283</v>
@@ -6486,7 +6535,7 @@
         <v>22.16131558339859</v>
       </c>
       <c r="F322" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -6494,10 +6543,10 @@
         <v>2025</v>
       </c>
       <c r="B324" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C324" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D324">
         <v>123</v>
@@ -6506,7 +6555,7 @@
         <v>28.21100917431193</v>
       </c>
       <c r="F324" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -6514,10 +6563,10 @@
         <v>2025</v>
       </c>
       <c r="B325" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C325" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D325">
         <v>117</v>
@@ -6526,7 +6575,7 @@
         <v>26.8348623853211</v>
       </c>
       <c r="F325" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -6534,10 +6583,10 @@
         <v>2025</v>
       </c>
       <c r="B326" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C326" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D326">
         <v>106</v>
@@ -6546,7 +6595,7 @@
         <v>24.31192660550459</v>
       </c>
       <c r="F326" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -6554,10 +6603,10 @@
         <v>2025</v>
       </c>
       <c r="B327" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C327" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D327">
         <v>90</v>
@@ -6566,7 +6615,7 @@
         <v>20.64220183486239</v>
       </c>
       <c r="F327" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -6574,10 +6623,10 @@
         <v>2025</v>
       </c>
       <c r="B329" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C329" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D329">
         <v>195</v>
@@ -6586,7 +6635,7 @@
         <v>45.03464203233256</v>
       </c>
       <c r="F329" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -6594,10 +6643,10 @@
         <v>2025</v>
       </c>
       <c r="B330" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C330" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D330">
         <v>162</v>
@@ -6606,7 +6655,7 @@
         <v>37.41339491916859</v>
       </c>
       <c r="F330" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -6614,10 +6663,10 @@
         <v>2025</v>
       </c>
       <c r="B331" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C331" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D331">
         <v>76</v>
@@ -6626,7 +6675,7 @@
         <v>17.55196304849884</v>
       </c>
       <c r="F331" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -6634,10 +6683,10 @@
         <v>2025</v>
       </c>
       <c r="B333" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C333" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D333">
         <v>315</v>
@@ -6646,7 +6695,7 @@
         <v>43.09165526675787</v>
       </c>
       <c r="F333" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -6654,10 +6703,10 @@
         <v>2025</v>
       </c>
       <c r="B334" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C334" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D334">
         <v>247</v>
@@ -6666,7 +6715,7 @@
         <v>33.78932968536252</v>
       </c>
       <c r="F334" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -6674,10 +6723,10 @@
         <v>2025</v>
       </c>
       <c r="B335" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C335" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D335">
         <v>169</v>
@@ -6686,7 +6735,7 @@
         <v>23.11901504787962</v>
       </c>
       <c r="F335" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -6694,10 +6743,10 @@
         <v>2025</v>
       </c>
       <c r="B337" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C337" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D337">
         <v>1002</v>
@@ -6706,7 +6755,7 @@
         <v>49.80119284294234</v>
       </c>
       <c r="F337" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -6714,10 +6763,10 @@
         <v>2025</v>
       </c>
       <c r="B338" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C338" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D338">
         <v>984</v>
@@ -6726,7 +6775,7 @@
         <v>48.9065606361829</v>
       </c>
       <c r="F338" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="213">
   <si>
     <t>Year</t>
   </si>
@@ -92,12 +92,6 @@
     <t>REP Township Supervisor North Whitehall</t>
   </si>
   <si>
-    <t>DEM Clerk of Courts</t>
-  </si>
-  <si>
-    <t>DEM County Treasurer</t>
-  </si>
-  <si>
     <t>DEM Hazleton Area School District 2yr Hazleton Area School District</t>
   </si>
   <si>
@@ -119,12 +113,6 @@
     <t>DEM North Schuylkill School District 2yr North Schuylkill Area</t>
   </si>
   <si>
-    <t>DEM Register of Wills // Clerk of Orphans Court</t>
-  </si>
-  <si>
-    <t>DEM Sheriff</t>
-  </si>
-  <si>
     <t>REP Commissioner Bethlehem Twsp 1st Ward</t>
   </si>
   <si>
@@ -173,21 +161,9 @@
     <t>Committeeman, Aston Township Ward 7</t>
   </si>
   <si>
-    <t>DEM County Controller-DEM</t>
-  </si>
-  <si>
-    <t>DEM County Coroner-DEM</t>
-  </si>
-  <si>
-    <t>DEM District Attorney-DEM</t>
-  </si>
-  <si>
     <t>DEM MAGISTERIAL DISTRICT JUDGE 03-3-02</t>
   </si>
   <si>
-    <t>DEM Recorder of Deeds-DEM</t>
-  </si>
-  <si>
     <t>REP Codorus Township Supervisor-REP</t>
   </si>
   <si>
@@ -326,30 +302,6 @@
     <t>CHRISTOPHER MOAKLEY</t>
   </si>
   <si>
-    <t>DAN BYRNES</t>
-  </si>
-  <si>
-    <t>RYAN SUPLER</t>
-  </si>
-  <si>
-    <t>ADAM JONES</t>
-  </si>
-  <si>
-    <t>BRYAN TATE</t>
-  </si>
-  <si>
-    <t>BARBARA BAIR</t>
-  </si>
-  <si>
-    <t>ANDREW KROFT</t>
-  </si>
-  <si>
-    <t>JOE JEFCOAT</t>
-  </si>
-  <si>
-    <t>CHRISTOPHER SNYDER</t>
-  </si>
-  <si>
     <t>CAROL MAKUTA</t>
   </si>
   <si>
@@ -428,21 +380,6 @@
     <t>PHILIP RAPANT JR</t>
   </si>
   <si>
-    <t>RICHARD KEUERLEBER</t>
-  </si>
-  <si>
-    <t>SHANE BECKER</t>
-  </si>
-  <si>
-    <t>KEUERLEBER</t>
-  </si>
-  <si>
-    <t>HEATH CHESNEY</t>
-  </si>
-  <si>
-    <t>WILLIAM KING</t>
-  </si>
-  <si>
     <t>ARTHUR MURPHY</t>
   </si>
   <si>
@@ -569,57 +506,12 @@
     <t>JOSEPH DYCHALA</t>
   </si>
   <si>
-    <t>GREGORY BOWER</t>
-  </si>
-  <si>
-    <t>CLIFFORD ACKMAN</t>
-  </si>
-  <si>
-    <t>GREG BOWER</t>
-  </si>
-  <si>
-    <t>ISAAC RISTON</t>
-  </si>
-  <si>
-    <t>SEAN CAMPBELL</t>
-  </si>
-  <si>
-    <t>CLIFF ACKMAN</t>
-  </si>
-  <si>
-    <t>TANIA ZECH</t>
-  </si>
-  <si>
-    <t>PAM GAY</t>
-  </si>
-  <si>
-    <t>PAMELA GAY</t>
-  </si>
-  <si>
-    <t>TIM BARKER</t>
-  </si>
-  <si>
-    <t>JACK GRAYBILL</t>
-  </si>
-  <si>
-    <t>JACK GRAYBILL II</t>
-  </si>
-  <si>
-    <t>GRAYBILL</t>
-  </si>
-  <si>
-    <t>TIMOTHY BARKER</t>
-  </si>
-  <si>
     <t>ELLEN KINGSLEY</t>
   </si>
   <si>
     <t>ROBERT KEMMERER</t>
   </si>
   <si>
-    <t>LAURA SHUE</t>
-  </si>
-  <si>
     <t>JASON GROSS</t>
   </si>
   <si>
@@ -749,10 +641,10 @@
     <t>Northumberland County (Sunbury + Shamokin + boroughs)</t>
   </si>
   <si>
+    <t>Schuylkill County (Pottsville + boroughs + townships)</t>
+  </si>
+  <si>
     <t>York County (city + boroughs + townships)</t>
-  </si>
-  <si>
-    <t>Schuylkill County (Pottsville + boroughs + townships)</t>
   </si>
   <si>
     <t>Berks County (Reading + boroughs + townships)</t>
@@ -1209,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1240,7 +1132,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D2">
         <v>3420</v>
@@ -1249,7 +1141,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F2" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1260,7 +1152,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>2391</v>
@@ -1269,7 +1161,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F3" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1280,7 +1172,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D4">
         <v>2184</v>
@@ -1289,7 +1181,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F4" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1300,7 +1192,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>572</v>
@@ -1309,7 +1201,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F6" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1320,7 +1212,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D7">
         <v>380</v>
@@ -1329,7 +1221,7 @@
         <v>31.25</v>
       </c>
       <c r="F7" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1340,7 +1232,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D8">
         <v>264</v>
@@ -1349,7 +1241,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F8" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1360,7 +1252,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D10">
         <v>177</v>
@@ -1369,7 +1261,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F10" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1380,7 +1272,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D11">
         <v>141</v>
@@ -1389,7 +1281,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F11" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1400,7 +1292,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D12">
         <v>81</v>
@@ -1409,7 +1301,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F12" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1420,7 +1312,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D13">
         <v>44</v>
@@ -1429,7 +1321,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F13" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1440,7 +1332,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D15">
         <v>1471</v>
@@ -1449,7 +1341,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F15" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1460,7 +1352,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D16">
         <v>1247</v>
@@ -1469,7 +1361,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F16" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1480,7 +1372,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D17">
         <v>616</v>
@@ -1489,7 +1381,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F17" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1500,7 +1392,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D19">
         <v>1183</v>
@@ -1509,7 +1401,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F19" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1520,7 +1412,7 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D20">
         <v>1177</v>
@@ -1529,7 +1421,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F20" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1540,7 +1432,7 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D21">
         <v>373</v>
@@ -1549,7 +1441,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F21" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1560,7 +1452,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D22">
         <v>270</v>
@@ -1569,7 +1461,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F22" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1580,7 +1472,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D24">
         <v>2064</v>
@@ -1589,7 +1481,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F24" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1600,7 +1492,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D25">
         <v>1942</v>
@@ -1609,7 +1501,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F25" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1620,7 +1512,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D26">
         <v>1927</v>
@@ -1629,7 +1521,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F26" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1640,7 +1532,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D27">
         <v>1817</v>
@@ -1649,7 +1541,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F27" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1660,7 +1552,7 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D29">
         <v>522</v>
@@ -1669,7 +1561,7 @@
         <v>48.33333333333334</v>
       </c>
       <c r="F29" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1680,7 +1572,7 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D30">
         <v>331</v>
@@ -1689,7 +1581,7 @@
         <v>30.64814814814815</v>
       </c>
       <c r="F30" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1700,7 +1592,7 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D31">
         <v>227</v>
@@ -1709,7 +1601,7 @@
         <v>21.01851851851852</v>
       </c>
       <c r="F31" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1720,7 +1612,7 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D33">
         <v>4922</v>
@@ -1729,7 +1621,7 @@
         <v>41.68713475057169</v>
       </c>
       <c r="F33" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1740,7 +1632,7 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D34">
         <v>4820</v>
@@ -1749,7 +1641,7 @@
         <v>40.82324045058016</v>
       </c>
       <c r="F34" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1760,7 +1652,7 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D35">
         <v>2065</v>
@@ -1769,7 +1661,7 @@
         <v>17.48962479884814</v>
       </c>
       <c r="F35" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1780,7 +1672,7 @@
         <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D37">
         <v>1779</v>
@@ -1789,7 +1681,7 @@
         <v>46.82811266122664</v>
       </c>
       <c r="F37" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1800,7 +1692,7 @@
         <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D38">
         <v>1349</v>
@@ -1809,7 +1701,7 @@
         <v>35.50934456435904</v>
       </c>
       <c r="F38" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1820,7 +1712,7 @@
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D39">
         <v>671</v>
@@ -1829,7 +1721,7 @@
         <v>17.66254277441432</v>
       </c>
       <c r="F39" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1840,7 +1732,7 @@
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D41">
         <v>253</v>
@@ -1849,7 +1741,7 @@
         <v>37.09677419354838</v>
       </c>
       <c r="F41" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1860,7 +1752,7 @@
         <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D42">
         <v>224</v>
@@ -1869,7 +1761,7 @@
         <v>32.84457478005865</v>
       </c>
       <c r="F42" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1880,7 +1772,7 @@
         <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D43">
         <v>122</v>
@@ -1889,7 +1781,7 @@
         <v>17.88856304985337</v>
       </c>
       <c r="F43" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1900,7 +1792,7 @@
         <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D44">
         <v>60</v>
@@ -1909,7 +1801,7 @@
         <v>8.797653958944283</v>
       </c>
       <c r="F44" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1920,7 +1812,7 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D45">
         <v>23</v>
@@ -1929,7 +1821,7 @@
         <v>3.372434017595308</v>
       </c>
       <c r="F45" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1940,7 +1832,7 @@
         <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D47">
         <v>917</v>
@@ -1949,7 +1841,7 @@
         <v>36.31683168316832</v>
       </c>
       <c r="F47" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1960,7 +1852,7 @@
         <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D48">
         <v>706</v>
@@ -1969,7 +1861,7 @@
         <v>27.96039603960396</v>
       </c>
       <c r="F48" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1980,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D49">
         <v>578</v>
@@ -1989,7 +1881,7 @@
         <v>22.89108910891089</v>
       </c>
       <c r="F49" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2000,7 +1892,7 @@
         <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D50">
         <v>324</v>
@@ -2009,7 +1901,7 @@
         <v>12.83168316831683</v>
       </c>
       <c r="F50" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2020,7 +1912,7 @@
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D52">
         <v>179</v>
@@ -2029,7 +1921,7 @@
         <v>45.31645569620253</v>
       </c>
       <c r="F52" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2040,7 +1932,7 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D53">
         <v>110</v>
@@ -2049,7 +1941,7 @@
         <v>27.84810126582278</v>
       </c>
       <c r="F53" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2060,7 +1952,7 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D54">
         <v>106</v>
@@ -2069,7 +1961,7 @@
         <v>26.83544303797468</v>
       </c>
       <c r="F54" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2080,7 +1972,7 @@
         <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D56">
         <v>276</v>
@@ -2089,7 +1981,7 @@
         <v>47.01873935264054</v>
       </c>
       <c r="F56" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2100,7 +1992,7 @@
         <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D57">
         <v>226</v>
@@ -2109,7 +2001,7 @@
         <v>38.50085178875639</v>
       </c>
       <c r="F57" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2120,7 +2012,7 @@
         <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D58">
         <v>85</v>
@@ -2129,7 +2021,7 @@
         <v>14.48040885860307</v>
       </c>
       <c r="F58" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2140,7 +2032,7 @@
         <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D60">
         <v>636</v>
@@ -2149,7 +2041,7 @@
         <v>41.24513618677042</v>
       </c>
       <c r="F60" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2160,7 +2052,7 @@
         <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D61">
         <v>544</v>
@@ -2169,7 +2061,7 @@
         <v>35.27885862516213</v>
       </c>
       <c r="F61" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2180,7 +2072,7 @@
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D62">
         <v>362</v>
@@ -2189,7 +2081,7 @@
         <v>23.47600518806744</v>
       </c>
       <c r="F62" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2200,16 +2092,16 @@
         <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D64">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E64">
-        <v>32.7536231884058</v>
+        <v>38.95131086142322</v>
       </c>
       <c r="F64" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2220,16 +2112,16 @@
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D65">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="E65">
-        <v>3.768115942028986</v>
+        <v>37.45318352059925</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2240,36 +2132,36 @@
         <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="E66">
-        <v>1.449275362318841</v>
+        <v>23.59550561797753</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>2023</v>
-      </c>
-      <c r="B67" t="s">
-        <v>25</v>
-      </c>
-      <c r="C67" t="s">
-        <v>106</v>
-      </c>
-      <c r="D67">
-        <v>4</v>
-      </c>
-      <c r="E67">
-        <v>1.159420289855073</v>
-      </c>
-      <c r="F67" t="s">
-        <v>244</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>2023</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>98</v>
+      </c>
+      <c r="D68">
+        <v>445</v>
+      </c>
+      <c r="E68">
+        <v>43.28793774319066</v>
+      </c>
+      <c r="F68" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2280,16 +2172,16 @@
         <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D69">
-        <v>151</v>
+        <v>353</v>
       </c>
       <c r="E69">
-        <v>29.78303747534517</v>
+        <v>34.33852140077821</v>
       </c>
       <c r="F69" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2300,36 +2192,16 @@
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D70">
-        <v>64</v>
+        <v>230</v>
       </c>
       <c r="E70">
-        <v>12.6232741617357</v>
+        <v>22.37354085603113</v>
       </c>
       <c r="F70" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>2023</v>
-      </c>
-      <c r="B71" t="s">
-        <v>26</v>
-      </c>
-      <c r="C71" t="s">
-        <v>109</v>
-      </c>
-      <c r="D71">
-        <v>48</v>
-      </c>
-      <c r="E71">
-        <v>9.467455621301776</v>
-      </c>
-      <c r="F71" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2337,19 +2209,39 @@
         <v>2023</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D72">
-        <v>9</v>
+        <v>684</v>
       </c>
       <c r="E72">
-        <v>1.775147928994083</v>
+        <v>46.94577899794098</v>
       </c>
       <c r="F72" t="s">
-        <v>244</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>2023</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73">
+        <v>395</v>
+      </c>
+      <c r="E73">
+        <v>27.1105010295127</v>
+      </c>
+      <c r="F73" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2360,36 +2252,16 @@
         <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D74">
-        <v>104</v>
+        <v>378</v>
       </c>
       <c r="E74">
-        <v>38.95131086142322</v>
+        <v>25.94371997254633</v>
       </c>
       <c r="F74" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>2023</v>
-      </c>
-      <c r="B75" t="s">
-        <v>27</v>
-      </c>
-      <c r="C75" t="s">
-        <v>112</v>
-      </c>
-      <c r="D75">
-        <v>100</v>
-      </c>
-      <c r="E75">
-        <v>37.45318352059925</v>
-      </c>
-      <c r="F75" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2397,19 +2269,39 @@
         <v>2023</v>
       </c>
       <c r="B76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D76">
-        <v>63</v>
+        <v>828</v>
       </c>
       <c r="E76">
-        <v>23.59550561797753</v>
+        <v>36.71840354767184</v>
       </c>
       <c r="F76" t="s">
-        <v>245</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>2023</v>
+      </c>
+      <c r="B77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" t="s">
+        <v>105</v>
+      </c>
+      <c r="D77">
+        <v>524</v>
+      </c>
+      <c r="E77">
+        <v>23.23725055432372</v>
+      </c>
+      <c r="F77" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2420,16 +2312,16 @@
         <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D78">
-        <v>445</v>
+        <v>485</v>
       </c>
       <c r="E78">
-        <v>43.28793774319066</v>
+        <v>21.50776053215078</v>
       </c>
       <c r="F78" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2440,16 +2332,16 @@
         <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D79">
-        <v>353</v>
+        <v>261</v>
       </c>
       <c r="E79">
-        <v>34.33852140077821</v>
+        <v>11.57427937915743</v>
       </c>
       <c r="F79" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2460,16 +2352,16 @@
         <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D80">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E80">
-        <v>22.37354085603113</v>
+        <v>6.962305986696231</v>
       </c>
       <c r="F80" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2480,16 +2372,16 @@
         <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D82">
-        <v>684</v>
+        <v>584</v>
       </c>
       <c r="E82">
-        <v>46.94577899794098</v>
+        <v>43.90977443609022</v>
       </c>
       <c r="F82" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2500,16 +2392,16 @@
         <v>29</v>
       </c>
       <c r="C83" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D83">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="E83">
-        <v>27.1105010295127</v>
+        <v>29.17293233082707</v>
       </c>
       <c r="F83" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2520,16 +2412,16 @@
         <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D84">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="E84">
-        <v>25.94371997254633</v>
+        <v>26.91729323308271</v>
       </c>
       <c r="F84" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2540,16 +2432,16 @@
         <v>30</v>
       </c>
       <c r="C86" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D86">
-        <v>828</v>
+        <v>634</v>
       </c>
       <c r="E86">
-        <v>36.71840354767184</v>
+        <v>45.67723342939482</v>
       </c>
       <c r="F86" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2560,16 +2452,16 @@
         <v>30</v>
       </c>
       <c r="C87" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D87">
-        <v>524</v>
+        <v>298</v>
       </c>
       <c r="E87">
-        <v>23.23725055432372</v>
+        <v>21.46974063400576</v>
       </c>
       <c r="F87" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2580,16 +2472,16 @@
         <v>30</v>
       </c>
       <c r="C88" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D88">
-        <v>485</v>
+        <v>246</v>
       </c>
       <c r="E88">
-        <v>21.50776053215078</v>
+        <v>17.72334293948127</v>
       </c>
       <c r="F88" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2600,36 +2492,36 @@
         <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D89">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="E89">
-        <v>11.57427937915743</v>
+        <v>15.12968299711815</v>
       </c>
       <c r="F89" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>2023</v>
-      </c>
-      <c r="B90" t="s">
-        <v>30</v>
-      </c>
-      <c r="C90" t="s">
-        <v>124</v>
-      </c>
-      <c r="D90">
-        <v>157</v>
-      </c>
-      <c r="E90">
-        <v>6.962305986696231</v>
-      </c>
-      <c r="F90" t="s">
-        <v>240</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>2023</v>
+      </c>
+      <c r="B91" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" t="s">
+        <v>116</v>
+      </c>
+      <c r="D91">
+        <v>294</v>
+      </c>
+      <c r="E91">
+        <v>38.33116036505867</v>
+      </c>
+      <c r="F91" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2640,16 +2532,16 @@
         <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D92">
-        <v>584</v>
+        <v>145</v>
       </c>
       <c r="E92">
-        <v>43.90977443609022</v>
+        <v>18.90482398956975</v>
       </c>
       <c r="F92" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2660,16 +2552,16 @@
         <v>31</v>
       </c>
       <c r="C93" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D93">
-        <v>388</v>
+        <v>136</v>
       </c>
       <c r="E93">
-        <v>29.17293233082707</v>
+        <v>17.73142112125163</v>
       </c>
       <c r="F93" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2680,36 +2572,36 @@
         <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D94">
-        <v>358</v>
+        <v>104</v>
       </c>
       <c r="E94">
-        <v>26.91729323308271</v>
+        <v>13.5593220338983</v>
       </c>
       <c r="F94" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>2023</v>
-      </c>
-      <c r="B96" t="s">
-        <v>32</v>
-      </c>
-      <c r="C96" t="s">
-        <v>128</v>
-      </c>
-      <c r="D96">
-        <v>634</v>
-      </c>
-      <c r="E96">
-        <v>45.67723342939482</v>
-      </c>
-      <c r="F96" t="s">
-        <v>246</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>2023</v>
+      </c>
+      <c r="B95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" t="s">
+        <v>120</v>
+      </c>
+      <c r="D95">
+        <v>88</v>
+      </c>
+      <c r="E95">
+        <v>11.47327249022164</v>
+      </c>
+      <c r="F95" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2720,16 +2612,16 @@
         <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D97">
-        <v>298</v>
+        <v>170</v>
       </c>
       <c r="E97">
-        <v>21.46974063400576</v>
+        <v>46.19565217391305</v>
       </c>
       <c r="F97" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2740,16 +2632,16 @@
         <v>32</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D98">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="E98">
-        <v>17.72334293948127</v>
+        <v>45.92391304347826</v>
       </c>
       <c r="F98" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2760,16 +2652,16 @@
         <v>32</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D99">
-        <v>210</v>
+        <v>29</v>
       </c>
       <c r="E99">
-        <v>15.12968299711815</v>
+        <v>7.880434782608696</v>
       </c>
       <c r="F99" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -2780,16 +2672,16 @@
         <v>33</v>
       </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="D101">
-        <v>294</v>
+        <v>886</v>
       </c>
       <c r="E101">
-        <v>38.33116036505867</v>
+        <v>48.86927744070601</v>
       </c>
       <c r="F101" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2800,16 +2692,16 @@
         <v>33</v>
       </c>
       <c r="C102" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="D102">
-        <v>145</v>
+        <v>699</v>
       </c>
       <c r="E102">
-        <v>18.90482398956975</v>
+        <v>38.55488141202427</v>
       </c>
       <c r="F102" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2820,36 +2712,16 @@
         <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D103">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="E103">
-        <v>17.73142112125163</v>
+        <v>12.57584114726972</v>
       </c>
       <c r="F103" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>2023</v>
-      </c>
-      <c r="B104" t="s">
-        <v>33</v>
-      </c>
-      <c r="C104" t="s">
-        <v>135</v>
-      </c>
-      <c r="D104">
-        <v>104</v>
-      </c>
-      <c r="E104">
-        <v>13.5593220338983</v>
-      </c>
-      <c r="F104" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2857,19 +2729,39 @@
         <v>2023</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="D105">
-        <v>88</v>
+        <v>1630</v>
       </c>
       <c r="E105">
-        <v>11.47327249022164</v>
+        <v>44.46262956901255</v>
       </c>
       <c r="F105" t="s">
-        <v>245</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106">
+        <v>2023</v>
+      </c>
+      <c r="B106" t="s">
+        <v>34</v>
+      </c>
+      <c r="C106" t="s">
+        <v>103</v>
+      </c>
+      <c r="D106">
+        <v>1039</v>
+      </c>
+      <c r="E106">
+        <v>28.34151663938898</v>
+      </c>
+      <c r="F106" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -2880,36 +2772,36 @@
         <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D107">
-        <v>154</v>
+        <v>813</v>
       </c>
       <c r="E107">
-        <v>41.06666666666667</v>
+        <v>22.17675941080196</v>
       </c>
       <c r="F107" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>2023</v>
-      </c>
-      <c r="B109" t="s">
-        <v>35</v>
-      </c>
-      <c r="C109" t="s">
-        <v>137</v>
-      </c>
-      <c r="D109">
-        <v>148</v>
-      </c>
-      <c r="E109">
-        <v>29.83870967741936</v>
-      </c>
-      <c r="F109" t="s">
-        <v>244</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108">
+        <v>2023</v>
+      </c>
+      <c r="B108" t="s">
+        <v>34</v>
+      </c>
+      <c r="C108" t="s">
+        <v>124</v>
+      </c>
+      <c r="D108">
+        <v>184</v>
+      </c>
+      <c r="E108">
+        <v>5.019094380796509</v>
+      </c>
+      <c r="F108" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -2920,16 +2812,16 @@
         <v>35</v>
       </c>
       <c r="C110" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D110">
-        <v>20</v>
+        <v>1334</v>
       </c>
       <c r="E110">
-        <v>4.032258064516129</v>
+        <v>46.38386648122393</v>
       </c>
       <c r="F110" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -2940,16 +2832,16 @@
         <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D111">
-        <v>10</v>
+        <v>1278</v>
       </c>
       <c r="E111">
-        <v>2.016129032258065</v>
+        <v>44.43671766342142</v>
       </c>
       <c r="F111" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -2960,36 +2852,36 @@
         <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>264</v>
       </c>
       <c r="E112">
-        <v>1.008064516129032</v>
+        <v>9.179415855354661</v>
       </c>
       <c r="F112" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>2023</v>
-      </c>
-      <c r="B113" t="s">
-        <v>35</v>
-      </c>
-      <c r="C113" t="s">
-        <v>141</v>
-      </c>
-      <c r="D113">
-        <v>5</v>
-      </c>
-      <c r="E113">
-        <v>1.008064516129032</v>
-      </c>
-      <c r="F113" t="s">
-        <v>244</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114">
+        <v>2023</v>
+      </c>
+      <c r="B114" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" t="s">
+        <v>108</v>
+      </c>
+      <c r="D114">
+        <v>1466</v>
+      </c>
+      <c r="E114">
+        <v>43.1303324507208</v>
+      </c>
+      <c r="F114" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3000,16 +2892,16 @@
         <v>36</v>
       </c>
       <c r="C115" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="D115">
-        <v>170</v>
+        <v>893</v>
       </c>
       <c r="E115">
-        <v>46.19565217391305</v>
+        <v>26.27243306854957</v>
       </c>
       <c r="F115" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3020,16 +2912,16 @@
         <v>36</v>
       </c>
       <c r="C116" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="D116">
-        <v>169</v>
+        <v>672</v>
       </c>
       <c r="E116">
-        <v>45.92391304347826</v>
+        <v>19.77052074139453</v>
       </c>
       <c r="F116" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3040,36 +2932,36 @@
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="D117">
-        <v>29</v>
+        <v>245</v>
       </c>
       <c r="E117">
-        <v>7.880434782608696</v>
+        <v>7.208002353633422</v>
       </c>
       <c r="F117" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>2023</v>
-      </c>
-      <c r="B119" t="s">
-        <v>37</v>
-      </c>
-      <c r="C119" t="s">
-        <v>114</v>
-      </c>
-      <c r="D119">
-        <v>886</v>
-      </c>
-      <c r="E119">
-        <v>48.86927744070601</v>
-      </c>
-      <c r="F119" t="s">
-        <v>244</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118">
+        <v>2023</v>
+      </c>
+      <c r="B118" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" t="s">
+        <v>104</v>
+      </c>
+      <c r="D118">
+        <v>123</v>
+      </c>
+      <c r="E118">
+        <v>3.618711385701677</v>
+      </c>
+      <c r="F118" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3080,16 +2972,16 @@
         <v>37</v>
       </c>
       <c r="C120" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D120">
-        <v>699</v>
+        <v>1108</v>
       </c>
       <c r="E120">
-        <v>38.55488141202427</v>
+        <v>46.4765100671141</v>
       </c>
       <c r="F120" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3100,16 +2992,36 @@
         <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D121">
-        <v>228</v>
+        <v>444</v>
       </c>
       <c r="E121">
-        <v>12.57584114726972</v>
+        <v>18.6241610738255</v>
       </c>
       <c r="F121" t="s">
-        <v>244</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122">
+        <v>2023</v>
+      </c>
+      <c r="B122" t="s">
+        <v>37</v>
+      </c>
+      <c r="C122" t="s">
+        <v>128</v>
+      </c>
+      <c r="D122">
+        <v>343</v>
+      </c>
+      <c r="E122">
+        <v>14.38758389261745</v>
+      </c>
+      <c r="F122" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3117,19 +3029,19 @@
         <v>2023</v>
       </c>
       <c r="B123" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C123" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D123">
-        <v>1630</v>
+        <v>323</v>
       </c>
       <c r="E123">
-        <v>44.46262956901255</v>
+        <v>13.5486577181208</v>
       </c>
       <c r="F123" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3137,39 +3049,19 @@
         <v>2023</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C124" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D124">
-        <v>1039</v>
+        <v>166</v>
       </c>
       <c r="E124">
-        <v>28.34151663938898</v>
+        <v>6.963087248322148</v>
       </c>
       <c r="F124" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>2023</v>
-      </c>
-      <c r="B125" t="s">
-        <v>38</v>
-      </c>
-      <c r="C125" t="s">
-        <v>118</v>
-      </c>
-      <c r="D125">
-        <v>813</v>
-      </c>
-      <c r="E125">
-        <v>22.17675941080196</v>
-      </c>
-      <c r="F125" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3180,16 +3072,36 @@
         <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="D126">
-        <v>184</v>
+        <v>904</v>
       </c>
       <c r="E126">
-        <v>5.019094380796509</v>
+        <v>42.60131950989632</v>
       </c>
       <c r="F126" t="s">
-        <v>244</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127">
+        <v>2023</v>
+      </c>
+      <c r="B127" t="s">
+        <v>38</v>
+      </c>
+      <c r="C127" t="s">
+        <v>130</v>
+      </c>
+      <c r="D127">
+        <v>860</v>
+      </c>
+      <c r="E127">
+        <v>40.52780395852969</v>
+      </c>
+      <c r="F127" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3197,19 +3109,19 @@
         <v>2023</v>
       </c>
       <c r="B128" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C128" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D128">
-        <v>1334</v>
+        <v>193</v>
       </c>
       <c r="E128">
-        <v>46.38386648122393</v>
+        <v>9.095193213949104</v>
       </c>
       <c r="F128" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3217,39 +3129,39 @@
         <v>2023</v>
       </c>
       <c r="B129" t="s">
+        <v>38</v>
+      </c>
+      <c r="C129" t="s">
+        <v>132</v>
+      </c>
+      <c r="D129">
+        <v>165</v>
+      </c>
+      <c r="E129">
+        <v>7.775683317624882</v>
+      </c>
+      <c r="F129" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131">
+        <v>2023</v>
+      </c>
+      <c r="B131" t="s">
         <v>39</v>
       </c>
-      <c r="C129" t="s">
-        <v>147</v>
-      </c>
-      <c r="D129">
-        <v>1278</v>
-      </c>
-      <c r="E129">
-        <v>44.43671766342142</v>
-      </c>
-      <c r="F129" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>2023</v>
-      </c>
-      <c r="B130" t="s">
-        <v>39</v>
-      </c>
-      <c r="C130" t="s">
-        <v>148</v>
-      </c>
-      <c r="D130">
-        <v>264</v>
-      </c>
-      <c r="E130">
-        <v>9.179415855354661</v>
-      </c>
-      <c r="F130" t="s">
-        <v>247</v>
+      <c r="C131" t="s">
+        <v>117</v>
+      </c>
+      <c r="D131">
+        <v>425</v>
+      </c>
+      <c r="E131">
+        <v>25.11820330969267</v>
+      </c>
+      <c r="F131" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3257,19 +3169,19 @@
         <v>2023</v>
       </c>
       <c r="B132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D132">
-        <v>1466</v>
+        <v>341</v>
       </c>
       <c r="E132">
-        <v>43.1303324507208</v>
+        <v>20.15366430260048</v>
       </c>
       <c r="F132" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3277,19 +3189,19 @@
         <v>2023</v>
       </c>
       <c r="B133" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C133" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D133">
-        <v>893</v>
+        <v>279</v>
       </c>
       <c r="E133">
-        <v>26.27243306854957</v>
+        <v>16.48936170212766</v>
       </c>
       <c r="F133" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3297,19 +3209,19 @@
         <v>2023</v>
       </c>
       <c r="B134" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C134" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D134">
-        <v>672</v>
+        <v>272</v>
       </c>
       <c r="E134">
-        <v>19.77052074139453</v>
+        <v>16.07565011820331</v>
       </c>
       <c r="F134" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3317,19 +3229,19 @@
         <v>2023</v>
       </c>
       <c r="B135" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C135" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D135">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="E135">
-        <v>7.208002353633422</v>
+        <v>13.00236406619385</v>
       </c>
       <c r="F135" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3337,19 +3249,19 @@
         <v>2023</v>
       </c>
       <c r="B136" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C136" t="s">
         <v>120</v>
       </c>
       <c r="D136">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="E136">
-        <v>3.618711385701677</v>
+        <v>9.160756501182032</v>
       </c>
       <c r="F136" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3357,19 +3269,19 @@
         <v>2023</v>
       </c>
       <c r="B138" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C138" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D138">
-        <v>1108</v>
+        <v>286</v>
       </c>
       <c r="E138">
-        <v>46.4765100671141</v>
+        <v>48.22934232715008</v>
       </c>
       <c r="F138" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3377,19 +3289,19 @@
         <v>2023</v>
       </c>
       <c r="B139" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C139" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D139">
-        <v>444</v>
+        <v>212</v>
       </c>
       <c r="E139">
-        <v>18.6241610738255</v>
+        <v>35.7504215851602</v>
       </c>
       <c r="F139" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3397,39 +3309,19 @@
         <v>2023</v>
       </c>
       <c r="B140" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C140" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D140">
-        <v>343</v>
+        <v>95</v>
       </c>
       <c r="E140">
-        <v>14.38758389261745</v>
+        <v>16.02023608768971</v>
       </c>
       <c r="F140" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>2023</v>
-      </c>
-      <c r="B141" t="s">
-        <v>41</v>
-      </c>
-      <c r="C141" t="s">
-        <v>129</v>
-      </c>
-      <c r="D141">
-        <v>323</v>
-      </c>
-      <c r="E141">
-        <v>13.5486577181208</v>
-      </c>
-      <c r="F141" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3440,16 +3332,36 @@
         <v>41</v>
       </c>
       <c r="C142" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D142">
-        <v>166</v>
+        <v>431</v>
       </c>
       <c r="E142">
-        <v>6.963087248322148</v>
+        <v>36.77474402730375</v>
       </c>
       <c r="F142" t="s">
-        <v>246</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143">
+        <v>2023</v>
+      </c>
+      <c r="B143" t="s">
+        <v>41</v>
+      </c>
+      <c r="C143" t="s">
+        <v>138</v>
+      </c>
+      <c r="D143">
+        <v>297</v>
+      </c>
+      <c r="E143">
+        <v>25.34129692832764</v>
+      </c>
+      <c r="F143" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3457,19 +3369,19 @@
         <v>2023</v>
       </c>
       <c r="B144" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C144" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D144">
-        <v>904</v>
+        <v>285</v>
       </c>
       <c r="E144">
-        <v>42.60131950989632</v>
+        <v>24.31740614334471</v>
       </c>
       <c r="F144" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3477,19 +3389,19 @@
         <v>2023</v>
       </c>
       <c r="B145" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C145" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D145">
-        <v>860</v>
+        <v>96</v>
       </c>
       <c r="E145">
-        <v>40.52780395852969</v>
+        <v>8.191126279863481</v>
       </c>
       <c r="F145" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3497,39 +3409,39 @@
         <v>2023</v>
       </c>
       <c r="B146" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" t="s">
+        <v>141</v>
+      </c>
+      <c r="D146">
+        <v>63</v>
+      </c>
+      <c r="E146">
+        <v>5.375426621160409</v>
+      </c>
+      <c r="F146" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148">
+        <v>2023</v>
+      </c>
+      <c r="B148" t="s">
         <v>42</v>
       </c>
-      <c r="C146" t="s">
-        <v>152</v>
-      </c>
-      <c r="D146">
-        <v>193</v>
-      </c>
-      <c r="E146">
-        <v>9.095193213949104</v>
-      </c>
-      <c r="F146" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>2023</v>
-      </c>
-      <c r="B147" t="s">
-        <v>42</v>
-      </c>
-      <c r="C147" t="s">
-        <v>153</v>
-      </c>
-      <c r="D147">
-        <v>165</v>
-      </c>
-      <c r="E147">
-        <v>7.775683317624882</v>
-      </c>
-      <c r="F147" t="s">
-        <v>246</v>
+      <c r="C148" t="s">
+        <v>142</v>
+      </c>
+      <c r="D148">
+        <v>273</v>
+      </c>
+      <c r="E148">
+        <v>45.4242928452579</v>
+      </c>
+      <c r="F148" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3537,19 +3449,19 @@
         <v>2023</v>
       </c>
       <c r="B149" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C149" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D149">
-        <v>425</v>
+        <v>234</v>
       </c>
       <c r="E149">
-        <v>25.11820330969267</v>
+        <v>38.9351081530782</v>
       </c>
       <c r="F149" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3557,39 +3469,19 @@
         <v>2023</v>
       </c>
       <c r="B150" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C150" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D150">
-        <v>341</v>
+        <v>94</v>
       </c>
       <c r="E150">
-        <v>20.15366430260048</v>
+        <v>15.64059900166389</v>
       </c>
       <c r="F150" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>2023</v>
-      </c>
-      <c r="B151" t="s">
-        <v>43</v>
-      </c>
-      <c r="C151" t="s">
-        <v>134</v>
-      </c>
-      <c r="D151">
-        <v>279</v>
-      </c>
-      <c r="E151">
-        <v>16.48936170212766</v>
-      </c>
-      <c r="F151" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -3600,16 +3492,16 @@
         <v>43</v>
       </c>
       <c r="C152" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D152">
-        <v>272</v>
+        <v>124</v>
       </c>
       <c r="E152">
-        <v>16.07565011820331</v>
+        <v>47.69230769230769</v>
       </c>
       <c r="F152" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3620,16 +3512,16 @@
         <v>43</v>
       </c>
       <c r="C153" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D153">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="E153">
-        <v>13.00236406619385</v>
+        <v>28.07692307692308</v>
       </c>
       <c r="F153" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3640,16 +3532,16 @@
         <v>43</v>
       </c>
       <c r="C154" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="D154">
-        <v>155</v>
+        <v>63</v>
       </c>
       <c r="E154">
-        <v>9.160756501182032</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="F154" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3660,16 +3552,16 @@
         <v>44</v>
       </c>
       <c r="C156" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D156">
-        <v>286</v>
+        <v>827</v>
       </c>
       <c r="E156">
-        <v>48.22934232715008</v>
+        <v>47.88650839606254</v>
       </c>
       <c r="F156" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -3680,16 +3572,16 @@
         <v>44</v>
       </c>
       <c r="C157" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D157">
-        <v>212</v>
+        <v>284</v>
       </c>
       <c r="E157">
-        <v>35.7504215851602</v>
+        <v>16.44470179502026</v>
       </c>
       <c r="F157" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -3700,16 +3592,36 @@
         <v>44</v>
       </c>
       <c r="C158" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D158">
-        <v>95</v>
+        <v>222</v>
       </c>
       <c r="E158">
-        <v>16.02023608768971</v>
+        <v>12.85466126230457</v>
       </c>
       <c r="F158" t="s">
-        <v>241</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159">
+        <v>2023</v>
+      </c>
+      <c r="B159" t="s">
+        <v>44</v>
+      </c>
+      <c r="C159" t="s">
+        <v>151</v>
+      </c>
+      <c r="D159">
+        <v>211</v>
+      </c>
+      <c r="E159">
+        <v>12.21771858714534</v>
+      </c>
+      <c r="F159" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -3717,39 +3629,19 @@
         <v>2023</v>
       </c>
       <c r="B160" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C160" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D160">
-        <v>431</v>
+        <v>183</v>
       </c>
       <c r="E160">
-        <v>36.77474402730375</v>
+        <v>10.59640995946728</v>
       </c>
       <c r="F160" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>2023</v>
-      </c>
-      <c r="B161" t="s">
-        <v>45</v>
-      </c>
-      <c r="C161" t="s">
-        <v>159</v>
-      </c>
-      <c r="D161">
-        <v>297</v>
-      </c>
-      <c r="E161">
-        <v>25.34129692832764</v>
-      </c>
-      <c r="F161" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -3760,16 +3652,16 @@
         <v>45</v>
       </c>
       <c r="C162" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D162">
-        <v>285</v>
+        <v>605</v>
       </c>
       <c r="E162">
-        <v>24.31740614334471</v>
+        <v>41.10054347826087</v>
       </c>
       <c r="F162" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -3780,16 +3672,16 @@
         <v>45</v>
       </c>
       <c r="C163" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D163">
-        <v>96</v>
+        <v>593</v>
       </c>
       <c r="E163">
-        <v>8.191126279863481</v>
+        <v>40.28532608695652</v>
       </c>
       <c r="F163" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -3800,16 +3692,16 @@
         <v>45</v>
       </c>
       <c r="C164" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D164">
-        <v>63</v>
+        <v>274</v>
       </c>
       <c r="E164">
-        <v>5.375426621160409</v>
+        <v>18.61413043478261</v>
       </c>
       <c r="F164" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -3820,16 +3712,16 @@
         <v>46</v>
       </c>
       <c r="C166" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D166">
-        <v>273</v>
+        <v>347</v>
       </c>
       <c r="E166">
-        <v>45.4242928452579</v>
+        <v>49.15014164305949</v>
       </c>
       <c r="F166" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -3840,16 +3732,16 @@
         <v>46</v>
       </c>
       <c r="C167" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D167">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="E167">
-        <v>38.9351081530782</v>
+        <v>23.79603399433428</v>
       </c>
       <c r="F167" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -3860,376 +3752,376 @@
         <v>46</v>
       </c>
       <c r="C168" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D168">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E168">
-        <v>15.64059900166389</v>
+        <v>14.58923512747875</v>
       </c>
       <c r="F168" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170">
-        <v>2023</v>
-      </c>
-      <c r="B170" t="s">
-        <v>47</v>
-      </c>
-      <c r="C170" t="s">
-        <v>166</v>
-      </c>
-      <c r="D170">
-        <v>124</v>
-      </c>
-      <c r="E170">
-        <v>47.69230769230769</v>
-      </c>
-      <c r="F170" t="s">
-        <v>243</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169">
+        <v>2023</v>
+      </c>
+      <c r="B169" t="s">
+        <v>46</v>
+      </c>
+      <c r="C169" t="s">
+        <v>159</v>
+      </c>
+      <c r="D169">
+        <v>88</v>
+      </c>
+      <c r="E169">
+        <v>12.46458923512748</v>
+      </c>
+      <c r="F169" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B171" t="s">
         <v>47</v>
       </c>
       <c r="C171" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D171">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="E171">
-        <v>28.07692307692308</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="F171" t="s">
-        <v>243</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B172" t="s">
         <v>47</v>
       </c>
       <c r="C172" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D172">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="E172">
-        <v>24.23076923076923</v>
+        <v>31.00303951367781</v>
       </c>
       <c r="F172" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174">
-        <v>2023</v>
-      </c>
-      <c r="B174" t="s">
-        <v>48</v>
-      </c>
-      <c r="C174" t="s">
-        <v>169</v>
-      </c>
-      <c r="D174">
-        <v>827</v>
-      </c>
-      <c r="E174">
-        <v>47.88650839606254</v>
-      </c>
-      <c r="F174" t="s">
-        <v>246</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173">
+        <v>2024</v>
+      </c>
+      <c r="B173" t="s">
+        <v>47</v>
+      </c>
+      <c r="C173" t="s">
+        <v>162</v>
+      </c>
+      <c r="D173">
+        <v>80</v>
+      </c>
+      <c r="E173">
+        <v>24.3161094224924</v>
+      </c>
+      <c r="F173" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B175" t="s">
         <v>48</v>
       </c>
       <c r="C175" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D175">
-        <v>284</v>
+        <v>710</v>
       </c>
       <c r="E175">
-        <v>16.44470179502026</v>
+        <v>46.64914586070959</v>
       </c>
       <c r="F175" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B176" t="s">
         <v>48</v>
       </c>
       <c r="C176" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D176">
-        <v>222</v>
+        <v>617</v>
       </c>
       <c r="E176">
-        <v>12.85466126230457</v>
+        <v>40.53876478318003</v>
       </c>
       <c r="F176" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B177" t="s">
         <v>48</v>
       </c>
       <c r="C177" t="s">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="D177">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="E177">
-        <v>12.21771858714534</v>
+        <v>12.81208935611038</v>
       </c>
       <c r="F177" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178">
-        <v>2023</v>
-      </c>
-      <c r="B178" t="s">
-        <v>48</v>
-      </c>
-      <c r="C178" t="s">
-        <v>173</v>
-      </c>
-      <c r="D178">
-        <v>183</v>
-      </c>
-      <c r="E178">
-        <v>10.59640995946728</v>
-      </c>
-      <c r="F178" t="s">
-        <v>246</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179">
+        <v>2025</v>
+      </c>
+      <c r="B179" t="s">
+        <v>49</v>
+      </c>
+      <c r="C179" t="s">
+        <v>165</v>
+      </c>
+      <c r="D179">
+        <v>241</v>
+      </c>
+      <c r="E179">
+        <v>49.79338842975206</v>
+      </c>
+      <c r="F179" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B180" t="s">
         <v>49</v>
       </c>
       <c r="C180" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D180">
-        <v>605</v>
+        <v>193</v>
       </c>
       <c r="E180">
-        <v>41.10054347826087</v>
+        <v>39.87603305785124</v>
       </c>
       <c r="F180" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B181" t="s">
         <v>49</v>
       </c>
       <c r="C181" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D181">
-        <v>593</v>
+        <v>49</v>
       </c>
       <c r="E181">
-        <v>40.28532608695652</v>
+        <v>10.12396694214876</v>
       </c>
       <c r="F181" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182">
-        <v>2023</v>
-      </c>
-      <c r="B182" t="s">
-        <v>49</v>
-      </c>
-      <c r="C182" t="s">
-        <v>176</v>
-      </c>
-      <c r="D182">
-        <v>274</v>
-      </c>
-      <c r="E182">
-        <v>18.61413043478261</v>
-      </c>
-      <c r="F182" t="s">
-        <v>244</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183">
+        <v>2025</v>
+      </c>
+      <c r="B183" t="s">
+        <v>50</v>
+      </c>
+      <c r="C183" t="s">
+        <v>168</v>
+      </c>
+      <c r="D183">
+        <v>6552</v>
+      </c>
+      <c r="E183">
+        <v>47.15704620699582</v>
+      </c>
+      <c r="F183" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B184" t="s">
         <v>50</v>
       </c>
       <c r="C184" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D184">
-        <v>347</v>
+        <v>4724</v>
       </c>
       <c r="E184">
-        <v>49.15014164305949</v>
+        <v>34.00028789405498</v>
       </c>
       <c r="F184" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B185" t="s">
         <v>50</v>
       </c>
       <c r="C185" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D185">
-        <v>168</v>
+        <v>2618</v>
       </c>
       <c r="E185">
-        <v>23.79603399433428</v>
+        <v>18.84266589894919</v>
       </c>
       <c r="F185" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186">
-        <v>2023</v>
-      </c>
-      <c r="B186" t="s">
-        <v>50</v>
-      </c>
-      <c r="C186" t="s">
-        <v>179</v>
-      </c>
-      <c r="D186">
-        <v>103</v>
-      </c>
-      <c r="E186">
-        <v>14.58923512747875</v>
-      </c>
-      <c r="F186" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B187" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C187" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D187">
-        <v>88</v>
+        <v>9318</v>
       </c>
       <c r="E187">
-        <v>12.46458923512748</v>
+        <v>41.92764578833693</v>
       </c>
       <c r="F187" t="s">
-        <v>244</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188">
+        <v>2025</v>
+      </c>
+      <c r="B188" t="s">
+        <v>51</v>
+      </c>
+      <c r="C188" t="s">
+        <v>172</v>
+      </c>
+      <c r="D188">
+        <v>8700</v>
+      </c>
+      <c r="E188">
+        <v>39.14686825053996</v>
+      </c>
+      <c r="F188" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B189" t="s">
         <v>51</v>
       </c>
       <c r="C189" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D189">
-        <v>147</v>
+        <v>4206</v>
       </c>
       <c r="E189">
-        <v>44.68085106382978</v>
+        <v>18.92548596112311</v>
       </c>
       <c r="F189" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190">
-        <v>2024</v>
-      </c>
-      <c r="B190" t="s">
-        <v>51</v>
-      </c>
-      <c r="C190" t="s">
-        <v>182</v>
-      </c>
-      <c r="D190">
-        <v>102</v>
-      </c>
-      <c r="E190">
-        <v>31.00303951367781</v>
-      </c>
-      <c r="F190" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B191" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C191" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D191">
-        <v>80</v>
+        <v>1473</v>
       </c>
       <c r="E191">
-        <v>24.3161094224924</v>
+        <v>39.30096051227321</v>
       </c>
       <c r="F191" t="s">
-        <v>10</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192">
+        <v>2025</v>
+      </c>
+      <c r="B192" t="s">
+        <v>52</v>
+      </c>
+      <c r="C192" t="s">
+        <v>175</v>
+      </c>
+      <c r="D192">
+        <v>1297</v>
+      </c>
+      <c r="E192">
+        <v>34.6051227321238</v>
+      </c>
+      <c r="F192" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4240,16 +4132,16 @@
         <v>52</v>
       </c>
       <c r="C193" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D193">
-        <v>113</v>
+        <v>516</v>
       </c>
       <c r="E193">
-        <v>21.56488549618321</v>
+        <v>13.76734258271078</v>
       </c>
       <c r="F193" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4260,16 +4152,16 @@
         <v>52</v>
       </c>
       <c r="C194" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D194">
-        <v>42</v>
+        <v>305</v>
       </c>
       <c r="E194">
-        <v>8.015267175572518</v>
+        <v>8.137673425827108</v>
       </c>
       <c r="F194" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4280,36 +4172,16 @@
         <v>52</v>
       </c>
       <c r="C195" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D195">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="E195">
-        <v>8.015267175572518</v>
+        <v>4.188900747065102</v>
       </c>
       <c r="F195" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196">
-        <v>2025</v>
-      </c>
-      <c r="B196" t="s">
-        <v>52</v>
-      </c>
-      <c r="C196" t="s">
-        <v>187</v>
-      </c>
-      <c r="D196">
-        <v>8</v>
-      </c>
-      <c r="E196">
-        <v>1.526717557251908</v>
-      </c>
-      <c r="F196" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4317,19 +4189,19 @@
         <v>2025</v>
       </c>
       <c r="B197" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C197" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="D197">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="E197">
-        <v>1.526717557251908</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="F197" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4337,19 +4209,19 @@
         <v>2025</v>
       </c>
       <c r="B198" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C198" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D198">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="E198">
-        <v>1.33587786259542</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="F198" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4357,19 +4229,19 @@
         <v>2025</v>
       </c>
       <c r="B199" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C199" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D199">
-        <v>7</v>
+        <v>138</v>
       </c>
       <c r="E199">
-        <v>1.33587786259542</v>
+        <v>23</v>
       </c>
       <c r="F199" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4377,19 +4249,19 @@
         <v>2025</v>
       </c>
       <c r="B201" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C201" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D201">
-        <v>252</v>
+        <v>1465</v>
       </c>
       <c r="E201">
-        <v>43.37349397590361</v>
+        <v>49.96589358799454</v>
       </c>
       <c r="F201" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4397,39 +4269,19 @@
         <v>2025</v>
       </c>
       <c r="B202" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C202" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="D202">
-        <v>43</v>
+        <v>1457</v>
       </c>
       <c r="E202">
-        <v>7.401032702237521</v>
+        <v>49.69304229195088</v>
       </c>
       <c r="F202" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203">
-        <v>2025</v>
-      </c>
-      <c r="B203" t="s">
-        <v>53</v>
-      </c>
-      <c r="C203" t="s">
-        <v>192</v>
-      </c>
-      <c r="D203">
-        <v>12</v>
-      </c>
-      <c r="E203">
-        <v>2.065404475043029</v>
-      </c>
-      <c r="F203" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4437,19 +4289,39 @@
         <v>2025</v>
       </c>
       <c r="B204" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D204">
-        <v>7</v>
+        <v>163</v>
       </c>
       <c r="E204">
-        <v>1.204819277108434</v>
+        <v>38.71733966745843</v>
       </c>
       <c r="F204" t="s">
-        <v>244</v>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205">
+        <v>2025</v>
+      </c>
+      <c r="B205" t="s">
+        <v>55</v>
+      </c>
+      <c r="C205" t="s">
+        <v>184</v>
+      </c>
+      <c r="D205">
+        <v>160</v>
+      </c>
+      <c r="E205">
+        <v>38.00475059382423</v>
+      </c>
+      <c r="F205" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4457,19 +4329,19 @@
         <v>2025</v>
       </c>
       <c r="B206" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C206" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D206">
-        <v>366</v>
+        <v>75</v>
       </c>
       <c r="E206">
-        <v>35.91756624141315</v>
+        <v>17.81472684085511</v>
       </c>
       <c r="F206" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4477,39 +4349,19 @@
         <v>2025</v>
       </c>
       <c r="B207" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C207" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D207">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="E207">
-        <v>11.2855740922473</v>
+        <v>5.463182897862233</v>
       </c>
       <c r="F207" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208">
-        <v>2025</v>
-      </c>
-      <c r="B208" t="s">
-        <v>54</v>
-      </c>
-      <c r="C208" t="s">
-        <v>195</v>
-      </c>
-      <c r="D208">
-        <v>94</v>
-      </c>
-      <c r="E208">
-        <v>9.224730127576054</v>
-      </c>
-      <c r="F208" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4517,19 +4369,19 @@
         <v>2025</v>
       </c>
       <c r="B209" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C209" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D209">
-        <v>70</v>
+        <v>549</v>
       </c>
       <c r="E209">
-        <v>6.869479882237488</v>
+        <v>42.99138606108065</v>
       </c>
       <c r="F209" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -4537,39 +4389,39 @@
         <v>2025</v>
       </c>
       <c r="B210" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C210" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D210">
-        <v>25</v>
+        <v>445</v>
       </c>
       <c r="E210">
-        <v>2.453385672227674</v>
+        <v>34.84729835552075</v>
       </c>
       <c r="F210" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211">
         <v>2025</v>
       </c>
-      <c r="B212" t="s">
-        <v>55</v>
-      </c>
-      <c r="C212" t="s">
-        <v>198</v>
-      </c>
-      <c r="D212">
-        <v>710</v>
-      </c>
-      <c r="E212">
-        <v>46.64914586070959</v>
-      </c>
-      <c r="F212" t="s">
-        <v>241</v>
+      <c r="B211" t="s">
+        <v>56</v>
+      </c>
+      <c r="C211" t="s">
+        <v>189</v>
+      </c>
+      <c r="D211">
+        <v>283</v>
+      </c>
+      <c r="E211">
+        <v>22.16131558339859</v>
+      </c>
+      <c r="F211" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -4577,19 +4429,19 @@
         <v>2025</v>
       </c>
       <c r="B213" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C213" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D213">
-        <v>617</v>
+        <v>123</v>
       </c>
       <c r="E213">
-        <v>40.53876478318003</v>
+        <v>28.21100917431193</v>
       </c>
       <c r="F213" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -4597,19 +4449,39 @@
         <v>2025</v>
       </c>
       <c r="B214" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C214" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="D214">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="E214">
-        <v>12.81208935611038</v>
+        <v>26.8348623853211</v>
       </c>
       <c r="F214" t="s">
-        <v>241</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215">
+        <v>2025</v>
+      </c>
+      <c r="B215" t="s">
+        <v>57</v>
+      </c>
+      <c r="C215" t="s">
+        <v>192</v>
+      </c>
+      <c r="D215">
+        <v>106</v>
+      </c>
+      <c r="E215">
+        <v>24.31192660550459</v>
+      </c>
+      <c r="F215" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -4617,39 +4489,39 @@
         <v>2025</v>
       </c>
       <c r="B216" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C216" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D216">
-        <v>193</v>
+        <v>90</v>
       </c>
       <c r="E216">
-        <v>39.95859213250517</v>
+        <v>20.64220183486239</v>
       </c>
       <c r="F216" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218">
         <v>2025</v>
       </c>
-      <c r="B217" t="s">
-        <v>56</v>
-      </c>
-      <c r="C217" t="s">
-        <v>187</v>
-      </c>
-      <c r="D217">
-        <v>7</v>
-      </c>
-      <c r="E217">
-        <v>1.449275362318841</v>
-      </c>
-      <c r="F217" t="s">
-        <v>244</v>
+      <c r="B218" t="s">
+        <v>58</v>
+      </c>
+      <c r="C218" t="s">
+        <v>194</v>
+      </c>
+      <c r="D218">
+        <v>195</v>
+      </c>
+      <c r="E218">
+        <v>45.03464203233256</v>
+      </c>
+      <c r="F218" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -4657,19 +4529,19 @@
         <v>2025</v>
       </c>
       <c r="B219" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C219" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D219">
-        <v>241</v>
+        <v>162</v>
       </c>
       <c r="E219">
-        <v>49.79338842975206</v>
+        <v>37.41339491916859</v>
       </c>
       <c r="F219" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -4677,39 +4549,39 @@
         <v>2025</v>
       </c>
       <c r="B220" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C220" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D220">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="E220">
-        <v>39.87603305785124</v>
+        <v>17.55196304849884</v>
       </c>
       <c r="F220" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222">
         <v>2025</v>
       </c>
-      <c r="B221" t="s">
-        <v>57</v>
-      </c>
-      <c r="C221" t="s">
-        <v>203</v>
-      </c>
-      <c r="D221">
-        <v>49</v>
-      </c>
-      <c r="E221">
-        <v>10.12396694214876</v>
-      </c>
-      <c r="F221" t="s">
-        <v>244</v>
+      <c r="B222" t="s">
+        <v>59</v>
+      </c>
+      <c r="C222" t="s">
+        <v>197</v>
+      </c>
+      <c r="D222">
+        <v>315</v>
+      </c>
+      <c r="E222">
+        <v>43.09165526675787</v>
+      </c>
+      <c r="F222" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -4717,19 +4589,19 @@
         <v>2025</v>
       </c>
       <c r="B223" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C223" t="s">
+        <v>198</v>
+      </c>
+      <c r="D223">
+        <v>247</v>
+      </c>
+      <c r="E223">
+        <v>33.78932968536252</v>
+      </c>
+      <c r="F223" t="s">
         <v>204</v>
-      </c>
-      <c r="D223">
-        <v>6552</v>
-      </c>
-      <c r="E223">
-        <v>47.15704620699582</v>
-      </c>
-      <c r="F223" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -4737,39 +4609,39 @@
         <v>2025</v>
       </c>
       <c r="B224" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C224" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D224">
-        <v>4724</v>
+        <v>169</v>
       </c>
       <c r="E224">
-        <v>34.00028789405498</v>
+        <v>23.11901504787962</v>
       </c>
       <c r="F224" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
-      <c r="A225">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226">
         <v>2025</v>
       </c>
-      <c r="B225" t="s">
-        <v>58</v>
-      </c>
-      <c r="C225" t="s">
-        <v>206</v>
-      </c>
-      <c r="D225">
-        <v>2618</v>
-      </c>
-      <c r="E225">
-        <v>18.84266589894919</v>
-      </c>
-      <c r="F225" t="s">
-        <v>241</v>
+      <c r="B226" t="s">
+        <v>60</v>
+      </c>
+      <c r="C226" t="s">
+        <v>200</v>
+      </c>
+      <c r="D226">
+        <v>1002</v>
+      </c>
+      <c r="E226">
+        <v>49.80119284294234</v>
+      </c>
+      <c r="F226" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -4777,639 +4649,19 @@
         <v>2025</v>
       </c>
       <c r="B227" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C227" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D227">
-        <v>9318</v>
+        <v>984</v>
       </c>
       <c r="E227">
-        <v>41.92764578833693</v>
+        <v>48.9065606361829</v>
       </c>
       <c r="F227" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6">
-      <c r="A228">
-        <v>2025</v>
-      </c>
-      <c r="B228" t="s">
-        <v>59</v>
-      </c>
-      <c r="C228" t="s">
-        <v>208</v>
-      </c>
-      <c r="D228">
-        <v>8700</v>
-      </c>
-      <c r="E228">
-        <v>39.14686825053996</v>
-      </c>
-      <c r="F228" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6">
-      <c r="A229">
-        <v>2025</v>
-      </c>
-      <c r="B229" t="s">
-        <v>59</v>
-      </c>
-      <c r="C229" t="s">
         <v>209</v>
-      </c>
-      <c r="D229">
-        <v>4206</v>
-      </c>
-      <c r="E229">
-        <v>18.92548596112311</v>
-      </c>
-      <c r="F229" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6">
-      <c r="A231">
-        <v>2025</v>
-      </c>
-      <c r="B231" t="s">
-        <v>60</v>
-      </c>
-      <c r="C231" t="s">
-        <v>210</v>
-      </c>
-      <c r="D231">
-        <v>1473</v>
-      </c>
-      <c r="E231">
-        <v>39.30096051227321</v>
-      </c>
-      <c r="F231" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
-      <c r="A232">
-        <v>2025</v>
-      </c>
-      <c r="B232" t="s">
-        <v>60</v>
-      </c>
-      <c r="C232" t="s">
-        <v>211</v>
-      </c>
-      <c r="D232">
-        <v>1297</v>
-      </c>
-      <c r="E232">
-        <v>34.6051227321238</v>
-      </c>
-      <c r="F232" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
-      <c r="A233">
-        <v>2025</v>
-      </c>
-      <c r="B233" t="s">
-        <v>60</v>
-      </c>
-      <c r="C233" t="s">
-        <v>212</v>
-      </c>
-      <c r="D233">
-        <v>516</v>
-      </c>
-      <c r="E233">
-        <v>13.76734258271078</v>
-      </c>
-      <c r="F233" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
-      <c r="A234">
-        <v>2025</v>
-      </c>
-      <c r="B234" t="s">
-        <v>60</v>
-      </c>
-      <c r="C234" t="s">
-        <v>213</v>
-      </c>
-      <c r="D234">
-        <v>305</v>
-      </c>
-      <c r="E234">
-        <v>8.137673425827108</v>
-      </c>
-      <c r="F234" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
-      <c r="A235">
-        <v>2025</v>
-      </c>
-      <c r="B235" t="s">
-        <v>60</v>
-      </c>
-      <c r="C235" t="s">
-        <v>214</v>
-      </c>
-      <c r="D235">
-        <v>157</v>
-      </c>
-      <c r="E235">
-        <v>4.188900747065102</v>
-      </c>
-      <c r="F235" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
-      <c r="A237">
-        <v>2025</v>
-      </c>
-      <c r="B237" t="s">
-        <v>61</v>
-      </c>
-      <c r="C237" t="s">
-        <v>156</v>
-      </c>
-      <c r="D237">
-        <v>287</v>
-      </c>
-      <c r="E237">
-        <v>47.83333333333334</v>
-      </c>
-      <c r="F237" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6">
-      <c r="A238">
-        <v>2025</v>
-      </c>
-      <c r="B238" t="s">
-        <v>61</v>
-      </c>
-      <c r="C238" t="s">
-        <v>215</v>
-      </c>
-      <c r="D238">
-        <v>175</v>
-      </c>
-      <c r="E238">
-        <v>29.16666666666667</v>
-      </c>
-      <c r="F238" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6">
-      <c r="A239">
-        <v>2025</v>
-      </c>
-      <c r="B239" t="s">
-        <v>61</v>
-      </c>
-      <c r="C239" t="s">
-        <v>216</v>
-      </c>
-      <c r="D239">
-        <v>138</v>
-      </c>
-      <c r="E239">
-        <v>23</v>
-      </c>
-      <c r="F239" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
-      <c r="A241">
-        <v>2025</v>
-      </c>
-      <c r="B241" t="s">
-        <v>62</v>
-      </c>
-      <c r="C241" t="s">
-        <v>217</v>
-      </c>
-      <c r="D241">
-        <v>1465</v>
-      </c>
-      <c r="E241">
-        <v>49.96589358799454</v>
-      </c>
-      <c r="F241" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
-      <c r="A242">
-        <v>2025</v>
-      </c>
-      <c r="B242" t="s">
-        <v>62</v>
-      </c>
-      <c r="C242" t="s">
-        <v>218</v>
-      </c>
-      <c r="D242">
-        <v>1457</v>
-      </c>
-      <c r="E242">
-        <v>49.69304229195088</v>
-      </c>
-      <c r="F242" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6">
-      <c r="A244">
-        <v>2025</v>
-      </c>
-      <c r="B244" t="s">
-        <v>63</v>
-      </c>
-      <c r="C244" t="s">
-        <v>219</v>
-      </c>
-      <c r="D244">
-        <v>163</v>
-      </c>
-      <c r="E244">
-        <v>38.71733966745843</v>
-      </c>
-      <c r="F244" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
-      <c r="A245">
-        <v>2025</v>
-      </c>
-      <c r="B245" t="s">
-        <v>63</v>
-      </c>
-      <c r="C245" t="s">
-        <v>220</v>
-      </c>
-      <c r="D245">
-        <v>160</v>
-      </c>
-      <c r="E245">
-        <v>38.00475059382423</v>
-      </c>
-      <c r="F245" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246">
-        <v>2025</v>
-      </c>
-      <c r="B246" t="s">
-        <v>63</v>
-      </c>
-      <c r="C246" t="s">
-        <v>221</v>
-      </c>
-      <c r="D246">
-        <v>75</v>
-      </c>
-      <c r="E246">
-        <v>17.81472684085511</v>
-      </c>
-      <c r="F246" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
-      <c r="A247">
-        <v>2025</v>
-      </c>
-      <c r="B247" t="s">
-        <v>63</v>
-      </c>
-      <c r="C247" t="s">
-        <v>222</v>
-      </c>
-      <c r="D247">
-        <v>23</v>
-      </c>
-      <c r="E247">
-        <v>5.463182897862233</v>
-      </c>
-      <c r="F247" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
-      <c r="A249">
-        <v>2025</v>
-      </c>
-      <c r="B249" t="s">
-        <v>64</v>
-      </c>
-      <c r="C249" t="s">
-        <v>223</v>
-      </c>
-      <c r="D249">
-        <v>549</v>
-      </c>
-      <c r="E249">
-        <v>42.99138606108065</v>
-      </c>
-      <c r="F249" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250">
-        <v>2025</v>
-      </c>
-      <c r="B250" t="s">
-        <v>64</v>
-      </c>
-      <c r="C250" t="s">
-        <v>224</v>
-      </c>
-      <c r="D250">
-        <v>445</v>
-      </c>
-      <c r="E250">
-        <v>34.84729835552075</v>
-      </c>
-      <c r="F250" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
-      <c r="A251">
-        <v>2025</v>
-      </c>
-      <c r="B251" t="s">
-        <v>64</v>
-      </c>
-      <c r="C251" t="s">
-        <v>225</v>
-      </c>
-      <c r="D251">
-        <v>283</v>
-      </c>
-      <c r="E251">
-        <v>22.16131558339859</v>
-      </c>
-      <c r="F251" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
-      <c r="A253">
-        <v>2025</v>
-      </c>
-      <c r="B253" t="s">
-        <v>65</v>
-      </c>
-      <c r="C253" t="s">
-        <v>226</v>
-      </c>
-      <c r="D253">
-        <v>123</v>
-      </c>
-      <c r="E253">
-        <v>28.21100917431193</v>
-      </c>
-      <c r="F253" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6">
-      <c r="A254">
-        <v>2025</v>
-      </c>
-      <c r="B254" t="s">
-        <v>65</v>
-      </c>
-      <c r="C254" t="s">
-        <v>227</v>
-      </c>
-      <c r="D254">
-        <v>117</v>
-      </c>
-      <c r="E254">
-        <v>26.8348623853211</v>
-      </c>
-      <c r="F254" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
-      <c r="A255">
-        <v>2025</v>
-      </c>
-      <c r="B255" t="s">
-        <v>65</v>
-      </c>
-      <c r="C255" t="s">
-        <v>228</v>
-      </c>
-      <c r="D255">
-        <v>106</v>
-      </c>
-      <c r="E255">
-        <v>24.31192660550459</v>
-      </c>
-      <c r="F255" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
-      <c r="A256">
-        <v>2025</v>
-      </c>
-      <c r="B256" t="s">
-        <v>65</v>
-      </c>
-      <c r="C256" t="s">
-        <v>229</v>
-      </c>
-      <c r="D256">
-        <v>90</v>
-      </c>
-      <c r="E256">
-        <v>20.64220183486239</v>
-      </c>
-      <c r="F256" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
-      <c r="A258">
-        <v>2025</v>
-      </c>
-      <c r="B258" t="s">
-        <v>66</v>
-      </c>
-      <c r="C258" t="s">
-        <v>230</v>
-      </c>
-      <c r="D258">
-        <v>195</v>
-      </c>
-      <c r="E258">
-        <v>45.03464203233256</v>
-      </c>
-      <c r="F258" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
-      <c r="A259">
-        <v>2025</v>
-      </c>
-      <c r="B259" t="s">
-        <v>66</v>
-      </c>
-      <c r="C259" t="s">
-        <v>231</v>
-      </c>
-      <c r="D259">
-        <v>162</v>
-      </c>
-      <c r="E259">
-        <v>37.41339491916859</v>
-      </c>
-      <c r="F259" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
-      <c r="A260">
-        <v>2025</v>
-      </c>
-      <c r="B260" t="s">
-        <v>66</v>
-      </c>
-      <c r="C260" t="s">
-        <v>232</v>
-      </c>
-      <c r="D260">
-        <v>76</v>
-      </c>
-      <c r="E260">
-        <v>17.55196304849884</v>
-      </c>
-      <c r="F260" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
-      <c r="A262">
-        <v>2025</v>
-      </c>
-      <c r="B262" t="s">
-        <v>67</v>
-      </c>
-      <c r="C262" t="s">
-        <v>233</v>
-      </c>
-      <c r="D262">
-        <v>315</v>
-      </c>
-      <c r="E262">
-        <v>43.09165526675787</v>
-      </c>
-      <c r="F262" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
-      <c r="A263">
-        <v>2025</v>
-      </c>
-      <c r="B263" t="s">
-        <v>67</v>
-      </c>
-      <c r="C263" t="s">
-        <v>234</v>
-      </c>
-      <c r="D263">
-        <v>247</v>
-      </c>
-      <c r="E263">
-        <v>33.78932968536252</v>
-      </c>
-      <c r="F263" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="A264">
-        <v>2025</v>
-      </c>
-      <c r="B264" t="s">
-        <v>67</v>
-      </c>
-      <c r="C264" t="s">
-        <v>235</v>
-      </c>
-      <c r="D264">
-        <v>169</v>
-      </c>
-      <c r="E264">
-        <v>23.11901504787962</v>
-      </c>
-      <c r="F264" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
-      <c r="A266">
-        <v>2025</v>
-      </c>
-      <c r="B266" t="s">
-        <v>68</v>
-      </c>
-      <c r="C266" t="s">
-        <v>236</v>
-      </c>
-      <c r="D266">
-        <v>1002</v>
-      </c>
-      <c r="E266">
-        <v>49.80119284294234</v>
-      </c>
-      <c r="F266" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="A267">
-        <v>2025</v>
-      </c>
-      <c r="B267" t="s">
-        <v>68</v>
-      </c>
-      <c r="C267" t="s">
-        <v>237</v>
-      </c>
-      <c r="D267">
-        <v>984</v>
-      </c>
-      <c r="E267">
-        <v>48.9065606361829</v>
-      </c>
-      <c r="F267" t="s">
-        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="207">
   <si>
     <t>Year</t>
   </si>
@@ -179,9 +179,6 @@
     <t>REP SUPERVISOR 6YR Plainfield Twsp</t>
   </si>
   <si>
-    <t>REP Springettsbury Township Auditor-REP</t>
-  </si>
-  <si>
     <t>REP TAX COLLECTOR CENTER TOWNSHIP</t>
   </si>
   <si>
@@ -197,9 +194,6 @@
     <t>REP Township Supervisor West Caln Township</t>
   </si>
   <si>
-    <t>REP Windsor Township Supervisor-REP</t>
-  </si>
-  <si>
     <t>WILLIAM MCCONNELL JR</t>
   </si>
   <si>
@@ -560,12 +554,6 @@
     <t>KEN FAIRCHILD</t>
   </si>
   <si>
-    <t>JEFFREY GAY</t>
-  </si>
-  <si>
-    <t>JONATHAN STAYER</t>
-  </si>
-  <si>
     <t>BRENDA SMYERS DUFFY</t>
   </si>
   <si>
@@ -615,12 +603,6 @@
   </si>
   <si>
     <t>JOE HUTTON</t>
-  </si>
-  <si>
-    <t>KATHERINE KERCHNER</t>
-  </si>
-  <si>
-    <t>STANLEY SAYLOR</t>
   </si>
   <si>
     <t>Mercer County (Mercer + Sharon + Hermitage + townships)</t>
@@ -1101,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1132,7 +1114,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D2">
         <v>3420</v>
@@ -1141,7 +1123,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1152,7 +1134,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>2391</v>
@@ -1161,7 +1143,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1172,7 +1154,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D4">
         <v>2184</v>
@@ -1181,7 +1163,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1192,7 +1174,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>572</v>
@@ -1201,7 +1183,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1212,7 +1194,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>380</v>
@@ -1221,7 +1203,7 @@
         <v>31.25</v>
       </c>
       <c r="F7" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1232,7 +1214,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>264</v>
@@ -1241,7 +1223,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F8" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1252,7 +1234,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D10">
         <v>177</v>
@@ -1261,7 +1243,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1272,7 +1254,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D11">
         <v>141</v>
@@ -1281,7 +1263,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F11" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1292,7 +1274,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D12">
         <v>81</v>
@@ -1301,7 +1283,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F12" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1312,7 +1294,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13">
         <v>44</v>
@@ -1321,7 +1303,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F13" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1332,7 +1314,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D15">
         <v>1471</v>
@@ -1341,7 +1323,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F15" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1352,7 +1334,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16">
         <v>1247</v>
@@ -1361,7 +1343,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F16" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1372,7 +1354,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17">
         <v>616</v>
@@ -1381,7 +1363,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F17" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1392,7 +1374,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D19">
         <v>1183</v>
@@ -1401,7 +1383,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F19" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1412,7 +1394,7 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D20">
         <v>1177</v>
@@ -1421,7 +1403,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F20" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1432,7 +1414,7 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D21">
         <v>373</v>
@@ -1441,7 +1423,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F21" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1452,7 +1434,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22">
         <v>270</v>
@@ -1461,7 +1443,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F22" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1472,7 +1454,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D24">
         <v>2064</v>
@@ -1481,7 +1463,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F24" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1492,7 +1474,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D25">
         <v>1942</v>
@@ -1501,7 +1483,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F25" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1512,7 +1494,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D26">
         <v>1927</v>
@@ -1521,7 +1503,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F26" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1532,7 +1514,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D27">
         <v>1817</v>
@@ -1541,7 +1523,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F27" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1552,7 +1534,7 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D29">
         <v>522</v>
@@ -1561,7 +1543,7 @@
         <v>48.33333333333334</v>
       </c>
       <c r="F29" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1572,7 +1554,7 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D30">
         <v>331</v>
@@ -1581,7 +1563,7 @@
         <v>30.64814814814815</v>
       </c>
       <c r="F30" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1592,7 +1574,7 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D31">
         <v>227</v>
@@ -1601,7 +1583,7 @@
         <v>21.01851851851852</v>
       </c>
       <c r="F31" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1612,7 +1594,7 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D33">
         <v>4922</v>
@@ -1621,7 +1603,7 @@
         <v>41.68713475057169</v>
       </c>
       <c r="F33" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1632,7 +1614,7 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D34">
         <v>4820</v>
@@ -1641,7 +1623,7 @@
         <v>40.82324045058016</v>
       </c>
       <c r="F34" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1652,7 +1634,7 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D35">
         <v>2065</v>
@@ -1661,7 +1643,7 @@
         <v>17.48962479884814</v>
       </c>
       <c r="F35" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1672,7 +1654,7 @@
         <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D37">
         <v>1779</v>
@@ -1681,7 +1663,7 @@
         <v>46.82811266122664</v>
       </c>
       <c r="F37" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1692,7 +1674,7 @@
         <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D38">
         <v>1349</v>
@@ -1701,7 +1683,7 @@
         <v>35.50934456435904</v>
       </c>
       <c r="F38" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1712,7 +1694,7 @@
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D39">
         <v>671</v>
@@ -1721,7 +1703,7 @@
         <v>17.66254277441432</v>
       </c>
       <c r="F39" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1732,7 +1714,7 @@
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D41">
         <v>253</v>
@@ -1741,7 +1723,7 @@
         <v>37.09677419354838</v>
       </c>
       <c r="F41" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1752,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D42">
         <v>224</v>
@@ -1761,7 +1743,7 @@
         <v>32.84457478005865</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1772,7 +1754,7 @@
         <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D43">
         <v>122</v>
@@ -1781,7 +1763,7 @@
         <v>17.88856304985337</v>
       </c>
       <c r="F43" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1792,7 +1774,7 @@
         <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D44">
         <v>60</v>
@@ -1801,7 +1783,7 @@
         <v>8.797653958944283</v>
       </c>
       <c r="F44" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1812,7 +1794,7 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D45">
         <v>23</v>
@@ -1821,7 +1803,7 @@
         <v>3.372434017595308</v>
       </c>
       <c r="F45" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1832,7 +1814,7 @@
         <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D47">
         <v>917</v>
@@ -1841,7 +1823,7 @@
         <v>36.31683168316832</v>
       </c>
       <c r="F47" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1852,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D48">
         <v>706</v>
@@ -1861,7 +1843,7 @@
         <v>27.96039603960396</v>
       </c>
       <c r="F48" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1872,7 +1854,7 @@
         <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D49">
         <v>578</v>
@@ -1881,7 +1863,7 @@
         <v>22.89108910891089</v>
       </c>
       <c r="F49" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1892,7 +1874,7 @@
         <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D50">
         <v>324</v>
@@ -1901,7 +1883,7 @@
         <v>12.83168316831683</v>
       </c>
       <c r="F50" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1912,7 +1894,7 @@
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D52">
         <v>179</v>
@@ -1921,7 +1903,7 @@
         <v>45.31645569620253</v>
       </c>
       <c r="F52" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1932,7 +1914,7 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D53">
         <v>110</v>
@@ -1941,7 +1923,7 @@
         <v>27.84810126582278</v>
       </c>
       <c r="F53" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1952,7 +1934,7 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D54">
         <v>106</v>
@@ -1961,7 +1943,7 @@
         <v>26.83544303797468</v>
       </c>
       <c r="F54" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1972,7 +1954,7 @@
         <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D56">
         <v>276</v>
@@ -1981,7 +1963,7 @@
         <v>47.01873935264054</v>
       </c>
       <c r="F56" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1992,7 +1974,7 @@
         <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D57">
         <v>226</v>
@@ -2001,7 +1983,7 @@
         <v>38.50085178875639</v>
       </c>
       <c r="F57" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2012,7 +1994,7 @@
         <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D58">
         <v>85</v>
@@ -2021,7 +2003,7 @@
         <v>14.48040885860307</v>
       </c>
       <c r="F58" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2032,7 +2014,7 @@
         <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D60">
         <v>636</v>
@@ -2041,7 +2023,7 @@
         <v>41.24513618677042</v>
       </c>
       <c r="F60" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2052,7 +2034,7 @@
         <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D61">
         <v>544</v>
@@ -2061,7 +2043,7 @@
         <v>35.27885862516213</v>
       </c>
       <c r="F61" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2072,7 +2054,7 @@
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D62">
         <v>362</v>
@@ -2081,7 +2063,7 @@
         <v>23.47600518806744</v>
       </c>
       <c r="F62" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2092,7 +2074,7 @@
         <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D64">
         <v>104</v>
@@ -2101,7 +2083,7 @@
         <v>38.95131086142322</v>
       </c>
       <c r="F64" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2112,7 +2094,7 @@
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D65">
         <v>100</v>
@@ -2121,7 +2103,7 @@
         <v>37.45318352059925</v>
       </c>
       <c r="F65" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2132,7 +2114,7 @@
         <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D66">
         <v>63</v>
@@ -2141,7 +2123,7 @@
         <v>23.59550561797753</v>
       </c>
       <c r="F66" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2152,7 +2134,7 @@
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D68">
         <v>445</v>
@@ -2161,7 +2143,7 @@
         <v>43.28793774319066</v>
       </c>
       <c r="F68" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2172,7 +2154,7 @@
         <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D69">
         <v>353</v>
@@ -2181,7 +2163,7 @@
         <v>34.33852140077821</v>
       </c>
       <c r="F69" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2192,7 +2174,7 @@
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D70">
         <v>230</v>
@@ -2201,7 +2183,7 @@
         <v>22.37354085603113</v>
       </c>
       <c r="F70" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2212,7 +2194,7 @@
         <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D72">
         <v>684</v>
@@ -2221,7 +2203,7 @@
         <v>46.94577899794098</v>
       </c>
       <c r="F72" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2232,7 +2214,7 @@
         <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D73">
         <v>395</v>
@@ -2241,7 +2223,7 @@
         <v>27.1105010295127</v>
       </c>
       <c r="F73" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2252,7 +2234,7 @@
         <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D74">
         <v>378</v>
@@ -2261,7 +2243,7 @@
         <v>25.94371997254633</v>
       </c>
       <c r="F74" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2272,7 +2254,7 @@
         <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D76">
         <v>828</v>
@@ -2281,7 +2263,7 @@
         <v>36.71840354767184</v>
       </c>
       <c r="F76" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2292,7 +2274,7 @@
         <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D77">
         <v>524</v>
@@ -2301,7 +2283,7 @@
         <v>23.23725055432372</v>
       </c>
       <c r="F77" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2312,7 +2294,7 @@
         <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D78">
         <v>485</v>
@@ -2321,7 +2303,7 @@
         <v>21.50776053215078</v>
       </c>
       <c r="F78" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2332,7 +2314,7 @@
         <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D79">
         <v>261</v>
@@ -2341,7 +2323,7 @@
         <v>11.57427937915743</v>
       </c>
       <c r="F79" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2352,7 +2334,7 @@
         <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D80">
         <v>157</v>
@@ -2361,7 +2343,7 @@
         <v>6.962305986696231</v>
       </c>
       <c r="F80" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2372,7 +2354,7 @@
         <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D82">
         <v>584</v>
@@ -2381,7 +2363,7 @@
         <v>43.90977443609022</v>
       </c>
       <c r="F82" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2392,7 +2374,7 @@
         <v>29</v>
       </c>
       <c r="C83" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D83">
         <v>388</v>
@@ -2401,7 +2383,7 @@
         <v>29.17293233082707</v>
       </c>
       <c r="F83" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2412,7 +2394,7 @@
         <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D84">
         <v>358</v>
@@ -2421,7 +2403,7 @@
         <v>26.91729323308271</v>
       </c>
       <c r="F84" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2432,7 +2414,7 @@
         <v>30</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D86">
         <v>634</v>
@@ -2441,7 +2423,7 @@
         <v>45.67723342939482</v>
       </c>
       <c r="F86" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2452,7 +2434,7 @@
         <v>30</v>
       </c>
       <c r="C87" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D87">
         <v>298</v>
@@ -2461,7 +2443,7 @@
         <v>21.46974063400576</v>
       </c>
       <c r="F87" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2472,7 +2454,7 @@
         <v>30</v>
       </c>
       <c r="C88" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D88">
         <v>246</v>
@@ -2481,7 +2463,7 @@
         <v>17.72334293948127</v>
       </c>
       <c r="F88" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2492,7 +2474,7 @@
         <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D89">
         <v>210</v>
@@ -2501,7 +2483,7 @@
         <v>15.12968299711815</v>
       </c>
       <c r="F89" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2512,7 +2494,7 @@
         <v>31</v>
       </c>
       <c r="C91" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D91">
         <v>294</v>
@@ -2521,7 +2503,7 @@
         <v>38.33116036505867</v>
       </c>
       <c r="F91" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2532,7 +2514,7 @@
         <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D92">
         <v>145</v>
@@ -2541,7 +2523,7 @@
         <v>18.90482398956975</v>
       </c>
       <c r="F92" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2552,7 +2534,7 @@
         <v>31</v>
       </c>
       <c r="C93" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D93">
         <v>136</v>
@@ -2561,7 +2543,7 @@
         <v>17.73142112125163</v>
       </c>
       <c r="F93" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2572,7 +2554,7 @@
         <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D94">
         <v>104</v>
@@ -2581,7 +2563,7 @@
         <v>13.5593220338983</v>
       </c>
       <c r="F94" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2592,7 +2574,7 @@
         <v>31</v>
       </c>
       <c r="C95" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D95">
         <v>88</v>
@@ -2601,7 +2583,7 @@
         <v>11.47327249022164</v>
       </c>
       <c r="F95" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2612,7 +2594,7 @@
         <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D97">
         <v>170</v>
@@ -2621,7 +2603,7 @@
         <v>46.19565217391305</v>
       </c>
       <c r="F97" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2632,7 +2614,7 @@
         <v>32</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D98">
         <v>169</v>
@@ -2641,7 +2623,7 @@
         <v>45.92391304347826</v>
       </c>
       <c r="F98" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2652,7 +2634,7 @@
         <v>32</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D99">
         <v>29</v>
@@ -2661,7 +2643,7 @@
         <v>7.880434782608696</v>
       </c>
       <c r="F99" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -2672,7 +2654,7 @@
         <v>33</v>
       </c>
       <c r="C101" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D101">
         <v>886</v>
@@ -2681,7 +2663,7 @@
         <v>48.86927744070601</v>
       </c>
       <c r="F101" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2692,7 +2674,7 @@
         <v>33</v>
       </c>
       <c r="C102" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D102">
         <v>699</v>
@@ -2701,7 +2683,7 @@
         <v>38.55488141202427</v>
       </c>
       <c r="F102" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2712,7 +2694,7 @@
         <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D103">
         <v>228</v>
@@ -2721,7 +2703,7 @@
         <v>12.57584114726972</v>
       </c>
       <c r="F103" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2732,7 +2714,7 @@
         <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D105">
         <v>1630</v>
@@ -2741,7 +2723,7 @@
         <v>44.46262956901255</v>
       </c>
       <c r="F105" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -2752,7 +2734,7 @@
         <v>34</v>
       </c>
       <c r="C106" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D106">
         <v>1039</v>
@@ -2761,7 +2743,7 @@
         <v>28.34151663938898</v>
       </c>
       <c r="F106" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -2772,7 +2754,7 @@
         <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D107">
         <v>813</v>
@@ -2781,7 +2763,7 @@
         <v>22.17675941080196</v>
       </c>
       <c r="F107" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -2792,7 +2774,7 @@
         <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D108">
         <v>184</v>
@@ -2801,7 +2783,7 @@
         <v>5.019094380796509</v>
       </c>
       <c r="F108" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -2812,7 +2794,7 @@
         <v>35</v>
       </c>
       <c r="C110" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D110">
         <v>1334</v>
@@ -2821,7 +2803,7 @@
         <v>46.38386648122393</v>
       </c>
       <c r="F110" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -2832,7 +2814,7 @@
         <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D111">
         <v>1278</v>
@@ -2841,7 +2823,7 @@
         <v>44.43671766342142</v>
       </c>
       <c r="F111" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -2852,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D112">
         <v>264</v>
@@ -2861,7 +2843,7 @@
         <v>9.179415855354661</v>
       </c>
       <c r="F112" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -2872,7 +2854,7 @@
         <v>36</v>
       </c>
       <c r="C114" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D114">
         <v>1466</v>
@@ -2881,7 +2863,7 @@
         <v>43.1303324507208</v>
       </c>
       <c r="F114" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -2892,7 +2874,7 @@
         <v>36</v>
       </c>
       <c r="C115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D115">
         <v>893</v>
@@ -2901,7 +2883,7 @@
         <v>26.27243306854957</v>
       </c>
       <c r="F115" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -2912,7 +2894,7 @@
         <v>36</v>
       </c>
       <c r="C116" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D116">
         <v>672</v>
@@ -2921,7 +2903,7 @@
         <v>19.77052074139453</v>
       </c>
       <c r="F116" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -2932,7 +2914,7 @@
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D117">
         <v>245</v>
@@ -2941,7 +2923,7 @@
         <v>7.208002353633422</v>
       </c>
       <c r="F117" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -2952,7 +2934,7 @@
         <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D118">
         <v>123</v>
@@ -2961,7 +2943,7 @@
         <v>3.618711385701677</v>
       </c>
       <c r="F118" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -2972,7 +2954,7 @@
         <v>37</v>
       </c>
       <c r="C120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D120">
         <v>1108</v>
@@ -2981,7 +2963,7 @@
         <v>46.4765100671141</v>
       </c>
       <c r="F120" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -2992,7 +2974,7 @@
         <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D121">
         <v>444</v>
@@ -3001,7 +2983,7 @@
         <v>18.6241610738255</v>
       </c>
       <c r="F121" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3012,7 +2994,7 @@
         <v>37</v>
       </c>
       <c r="C122" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D122">
         <v>343</v>
@@ -3021,7 +3003,7 @@
         <v>14.38758389261745</v>
       </c>
       <c r="F122" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3032,7 +3014,7 @@
         <v>37</v>
       </c>
       <c r="C123" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D123">
         <v>323</v>
@@ -3041,7 +3023,7 @@
         <v>13.5486577181208</v>
       </c>
       <c r="F123" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3052,7 +3034,7 @@
         <v>37</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D124">
         <v>166</v>
@@ -3061,7 +3043,7 @@
         <v>6.963087248322148</v>
       </c>
       <c r="F124" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3072,7 +3054,7 @@
         <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D126">
         <v>904</v>
@@ -3081,7 +3063,7 @@
         <v>42.60131950989632</v>
       </c>
       <c r="F126" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3092,7 +3074,7 @@
         <v>38</v>
       </c>
       <c r="C127" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D127">
         <v>860</v>
@@ -3101,7 +3083,7 @@
         <v>40.52780395852969</v>
       </c>
       <c r="F127" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3112,7 +3094,7 @@
         <v>38</v>
       </c>
       <c r="C128" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D128">
         <v>193</v>
@@ -3121,7 +3103,7 @@
         <v>9.095193213949104</v>
       </c>
       <c r="F128" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3132,7 +3114,7 @@
         <v>38</v>
       </c>
       <c r="C129" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D129">
         <v>165</v>
@@ -3141,7 +3123,7 @@
         <v>7.775683317624882</v>
       </c>
       <c r="F129" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3152,7 +3134,7 @@
         <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D131">
         <v>425</v>
@@ -3161,7 +3143,7 @@
         <v>25.11820330969267</v>
       </c>
       <c r="F131" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3172,7 +3154,7 @@
         <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D132">
         <v>341</v>
@@ -3181,7 +3163,7 @@
         <v>20.15366430260048</v>
       </c>
       <c r="F132" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3192,7 +3174,7 @@
         <v>39</v>
       </c>
       <c r="C133" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D133">
         <v>279</v>
@@ -3201,7 +3183,7 @@
         <v>16.48936170212766</v>
       </c>
       <c r="F133" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3212,7 +3194,7 @@
         <v>39</v>
       </c>
       <c r="C134" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D134">
         <v>272</v>
@@ -3221,7 +3203,7 @@
         <v>16.07565011820331</v>
       </c>
       <c r="F134" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3232,7 +3214,7 @@
         <v>39</v>
       </c>
       <c r="C135" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D135">
         <v>220</v>
@@ -3241,7 +3223,7 @@
         <v>13.00236406619385</v>
       </c>
       <c r="F135" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3252,7 +3234,7 @@
         <v>39</v>
       </c>
       <c r="C136" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D136">
         <v>155</v>
@@ -3261,7 +3243,7 @@
         <v>9.160756501182032</v>
       </c>
       <c r="F136" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3272,7 +3254,7 @@
         <v>40</v>
       </c>
       <c r="C138" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D138">
         <v>286</v>
@@ -3281,7 +3263,7 @@
         <v>48.22934232715008</v>
       </c>
       <c r="F138" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3292,7 +3274,7 @@
         <v>40</v>
       </c>
       <c r="C139" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D139">
         <v>212</v>
@@ -3301,7 +3283,7 @@
         <v>35.7504215851602</v>
       </c>
       <c r="F139" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3312,7 +3294,7 @@
         <v>40</v>
       </c>
       <c r="C140" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D140">
         <v>95</v>
@@ -3321,7 +3303,7 @@
         <v>16.02023608768971</v>
       </c>
       <c r="F140" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3332,7 +3314,7 @@
         <v>41</v>
       </c>
       <c r="C142" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D142">
         <v>431</v>
@@ -3341,7 +3323,7 @@
         <v>36.77474402730375</v>
       </c>
       <c r="F142" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3352,7 +3334,7 @@
         <v>41</v>
       </c>
       <c r="C143" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D143">
         <v>297</v>
@@ -3361,7 +3343,7 @@
         <v>25.34129692832764</v>
       </c>
       <c r="F143" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3372,7 +3354,7 @@
         <v>41</v>
       </c>
       <c r="C144" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D144">
         <v>285</v>
@@ -3381,7 +3363,7 @@
         <v>24.31740614334471</v>
       </c>
       <c r="F144" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3392,7 +3374,7 @@
         <v>41</v>
       </c>
       <c r="C145" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D145">
         <v>96</v>
@@ -3401,7 +3383,7 @@
         <v>8.191126279863481</v>
       </c>
       <c r="F145" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3412,7 +3394,7 @@
         <v>41</v>
       </c>
       <c r="C146" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D146">
         <v>63</v>
@@ -3421,7 +3403,7 @@
         <v>5.375426621160409</v>
       </c>
       <c r="F146" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3432,7 +3414,7 @@
         <v>42</v>
       </c>
       <c r="C148" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D148">
         <v>273</v>
@@ -3441,7 +3423,7 @@
         <v>45.4242928452579</v>
       </c>
       <c r="F148" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3452,7 +3434,7 @@
         <v>42</v>
       </c>
       <c r="C149" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D149">
         <v>234</v>
@@ -3461,7 +3443,7 @@
         <v>38.9351081530782</v>
       </c>
       <c r="F149" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3472,7 +3454,7 @@
         <v>42</v>
       </c>
       <c r="C150" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D150">
         <v>94</v>
@@ -3481,7 +3463,7 @@
         <v>15.64059900166389</v>
       </c>
       <c r="F150" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -3492,7 +3474,7 @@
         <v>43</v>
       </c>
       <c r="C152" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D152">
         <v>124</v>
@@ -3501,7 +3483,7 @@
         <v>47.69230769230769</v>
       </c>
       <c r="F152" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3512,7 +3494,7 @@
         <v>43</v>
       </c>
       <c r="C153" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D153">
         <v>73</v>
@@ -3521,7 +3503,7 @@
         <v>28.07692307692308</v>
       </c>
       <c r="F153" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3532,7 +3514,7 @@
         <v>43</v>
       </c>
       <c r="C154" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D154">
         <v>63</v>
@@ -3541,7 +3523,7 @@
         <v>24.23076923076923</v>
       </c>
       <c r="F154" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3552,7 +3534,7 @@
         <v>44</v>
       </c>
       <c r="C156" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D156">
         <v>827</v>
@@ -3561,7 +3543,7 @@
         <v>47.88650839606254</v>
       </c>
       <c r="F156" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -3572,7 +3554,7 @@
         <v>44</v>
       </c>
       <c r="C157" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D157">
         <v>284</v>
@@ -3581,7 +3563,7 @@
         <v>16.44470179502026</v>
       </c>
       <c r="F157" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -3592,7 +3574,7 @@
         <v>44</v>
       </c>
       <c r="C158" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D158">
         <v>222</v>
@@ -3601,7 +3583,7 @@
         <v>12.85466126230457</v>
       </c>
       <c r="F158" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -3612,7 +3594,7 @@
         <v>44</v>
       </c>
       <c r="C159" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D159">
         <v>211</v>
@@ -3621,7 +3603,7 @@
         <v>12.21771858714534</v>
       </c>
       <c r="F159" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -3632,7 +3614,7 @@
         <v>44</v>
       </c>
       <c r="C160" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D160">
         <v>183</v>
@@ -3641,7 +3623,7 @@
         <v>10.59640995946728</v>
       </c>
       <c r="F160" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -3652,7 +3634,7 @@
         <v>45</v>
       </c>
       <c r="C162" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D162">
         <v>605</v>
@@ -3661,7 +3643,7 @@
         <v>41.10054347826087</v>
       </c>
       <c r="F162" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -3672,7 +3654,7 @@
         <v>45</v>
       </c>
       <c r="C163" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D163">
         <v>593</v>
@@ -3681,7 +3663,7 @@
         <v>40.28532608695652</v>
       </c>
       <c r="F163" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -3692,7 +3674,7 @@
         <v>45</v>
       </c>
       <c r="C164" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D164">
         <v>274</v>
@@ -3701,7 +3683,7 @@
         <v>18.61413043478261</v>
       </c>
       <c r="F164" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -3712,7 +3694,7 @@
         <v>46</v>
       </c>
       <c r="C166" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D166">
         <v>347</v>
@@ -3721,7 +3703,7 @@
         <v>49.15014164305949</v>
       </c>
       <c r="F166" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -3732,7 +3714,7 @@
         <v>46</v>
       </c>
       <c r="C167" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D167">
         <v>168</v>
@@ -3741,7 +3723,7 @@
         <v>23.79603399433428</v>
       </c>
       <c r="F167" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -3752,7 +3734,7 @@
         <v>46</v>
       </c>
       <c r="C168" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D168">
         <v>103</v>
@@ -3761,7 +3743,7 @@
         <v>14.58923512747875</v>
       </c>
       <c r="F168" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -3772,7 +3754,7 @@
         <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D169">
         <v>88</v>
@@ -3781,7 +3763,7 @@
         <v>12.46458923512748</v>
       </c>
       <c r="F169" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -3792,7 +3774,7 @@
         <v>47</v>
       </c>
       <c r="C171" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D171">
         <v>147</v>
@@ -3812,7 +3794,7 @@
         <v>47</v>
       </c>
       <c r="C172" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D172">
         <v>102</v>
@@ -3832,7 +3814,7 @@
         <v>47</v>
       </c>
       <c r="C173" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D173">
         <v>80</v>
@@ -3852,7 +3834,7 @@
         <v>48</v>
       </c>
       <c r="C175" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D175">
         <v>710</v>
@@ -3861,7 +3843,7 @@
         <v>46.64914586070959</v>
       </c>
       <c r="F175" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -3872,7 +3854,7 @@
         <v>48</v>
       </c>
       <c r="C176" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D176">
         <v>617</v>
@@ -3881,7 +3863,7 @@
         <v>40.53876478318003</v>
       </c>
       <c r="F176" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -3892,7 +3874,7 @@
         <v>48</v>
       </c>
       <c r="C177" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D177">
         <v>195</v>
@@ -3901,7 +3883,7 @@
         <v>12.81208935611038</v>
       </c>
       <c r="F177" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -3912,7 +3894,7 @@
         <v>49</v>
       </c>
       <c r="C179" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D179">
         <v>241</v>
@@ -3921,7 +3903,7 @@
         <v>49.79338842975206</v>
       </c>
       <c r="F179" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -3932,7 +3914,7 @@
         <v>49</v>
       </c>
       <c r="C180" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D180">
         <v>193</v>
@@ -3941,7 +3923,7 @@
         <v>39.87603305785124</v>
       </c>
       <c r="F180" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -3952,7 +3934,7 @@
         <v>49</v>
       </c>
       <c r="C181" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D181">
         <v>49</v>
@@ -3961,7 +3943,7 @@
         <v>10.12396694214876</v>
       </c>
       <c r="F181" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -3972,7 +3954,7 @@
         <v>50</v>
       </c>
       <c r="C183" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D183">
         <v>6552</v>
@@ -3981,7 +3963,7 @@
         <v>47.15704620699582</v>
       </c>
       <c r="F183" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -3992,7 +3974,7 @@
         <v>50</v>
       </c>
       <c r="C184" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D184">
         <v>4724</v>
@@ -4001,7 +3983,7 @@
         <v>34.00028789405498</v>
       </c>
       <c r="F184" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4012,7 +3994,7 @@
         <v>50</v>
       </c>
       <c r="C185" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D185">
         <v>2618</v>
@@ -4021,7 +4003,7 @@
         <v>18.84266589894919</v>
       </c>
       <c r="F185" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4032,7 +4014,7 @@
         <v>51</v>
       </c>
       <c r="C187" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D187">
         <v>9318</v>
@@ -4041,7 +4023,7 @@
         <v>41.92764578833693</v>
       </c>
       <c r="F187" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4052,7 +4034,7 @@
         <v>51</v>
       </c>
       <c r="C188" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D188">
         <v>8700</v>
@@ -4061,7 +4043,7 @@
         <v>39.14686825053996</v>
       </c>
       <c r="F188" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -4072,7 +4054,7 @@
         <v>51</v>
       </c>
       <c r="C189" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D189">
         <v>4206</v>
@@ -4081,7 +4063,7 @@
         <v>18.92548596112311</v>
       </c>
       <c r="F189" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4092,7 +4074,7 @@
         <v>52</v>
       </c>
       <c r="C191" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D191">
         <v>1473</v>
@@ -4101,7 +4083,7 @@
         <v>39.30096051227321</v>
       </c>
       <c r="F191" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -4112,7 +4094,7 @@
         <v>52</v>
       </c>
       <c r="C192" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D192">
         <v>1297</v>
@@ -4121,7 +4103,7 @@
         <v>34.6051227321238</v>
       </c>
       <c r="F192" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4132,7 +4114,7 @@
         <v>52</v>
       </c>
       <c r="C193" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D193">
         <v>516</v>
@@ -4141,7 +4123,7 @@
         <v>13.76734258271078</v>
       </c>
       <c r="F193" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4152,7 +4134,7 @@
         <v>52</v>
       </c>
       <c r="C194" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D194">
         <v>305</v>
@@ -4161,7 +4143,7 @@
         <v>8.137673425827108</v>
       </c>
       <c r="F194" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4172,7 +4154,7 @@
         <v>52</v>
       </c>
       <c r="C195" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D195">
         <v>157</v>
@@ -4181,7 +4163,7 @@
         <v>4.188900747065102</v>
       </c>
       <c r="F195" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4192,7 +4174,7 @@
         <v>53</v>
       </c>
       <c r="C197" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D197">
         <v>287</v>
@@ -4201,7 +4183,7 @@
         <v>47.83333333333334</v>
       </c>
       <c r="F197" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4212,7 +4194,7 @@
         <v>53</v>
       </c>
       <c r="C198" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D198">
         <v>175</v>
@@ -4221,7 +4203,7 @@
         <v>29.16666666666667</v>
       </c>
       <c r="F198" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4232,7 +4214,7 @@
         <v>53</v>
       </c>
       <c r="C199" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D199">
         <v>138</v>
@@ -4241,7 +4223,7 @@
         <v>23</v>
       </c>
       <c r="F199" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4252,16 +4234,16 @@
         <v>54</v>
       </c>
       <c r="C201" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D201">
-        <v>1465</v>
+        <v>163</v>
       </c>
       <c r="E201">
-        <v>49.96589358799454</v>
+        <v>38.71733966745843</v>
       </c>
       <c r="F201" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4272,16 +4254,36 @@
         <v>54</v>
       </c>
       <c r="C202" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D202">
-        <v>1457</v>
+        <v>160</v>
       </c>
       <c r="E202">
-        <v>49.69304229195088</v>
+        <v>38.00475059382423</v>
       </c>
       <c r="F202" t="s">
-        <v>209</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203">
+        <v>2025</v>
+      </c>
+      <c r="B203" t="s">
+        <v>54</v>
+      </c>
+      <c r="C203" t="s">
+        <v>181</v>
+      </c>
+      <c r="D203">
+        <v>75</v>
+      </c>
+      <c r="E203">
+        <v>17.81472684085511</v>
+      </c>
+      <c r="F203" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4289,39 +4291,19 @@
         <v>2025</v>
       </c>
       <c r="B204" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C204" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D204">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="E204">
-        <v>38.71733966745843</v>
+        <v>5.463182897862233</v>
       </c>
       <c r="F204" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205">
-        <v>2025</v>
-      </c>
-      <c r="B205" t="s">
-        <v>55</v>
-      </c>
-      <c r="C205" t="s">
-        <v>184</v>
-      </c>
-      <c r="D205">
-        <v>160</v>
-      </c>
-      <c r="E205">
-        <v>38.00475059382423</v>
-      </c>
-      <c r="F205" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4332,16 +4314,16 @@
         <v>55</v>
       </c>
       <c r="C206" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D206">
-        <v>75</v>
+        <v>549</v>
       </c>
       <c r="E206">
-        <v>17.81472684085511</v>
+        <v>42.99138606108065</v>
       </c>
       <c r="F206" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4352,36 +4334,36 @@
         <v>55</v>
       </c>
       <c r="C207" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D207">
-        <v>23</v>
+        <v>445</v>
       </c>
       <c r="E207">
-        <v>5.463182897862233</v>
+        <v>34.84729835552075</v>
       </c>
       <c r="F207" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208">
         <v>2025</v>
       </c>
-      <c r="B209" t="s">
-        <v>56</v>
-      </c>
-      <c r="C209" t="s">
-        <v>187</v>
-      </c>
-      <c r="D209">
-        <v>549</v>
-      </c>
-      <c r="E209">
-        <v>42.99138606108065</v>
-      </c>
-      <c r="F209" t="s">
-        <v>210</v>
+      <c r="B208" t="s">
+        <v>55</v>
+      </c>
+      <c r="C208" t="s">
+        <v>185</v>
+      </c>
+      <c r="D208">
+        <v>283</v>
+      </c>
+      <c r="E208">
+        <v>22.16131558339859</v>
+      </c>
+      <c r="F208" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -4392,16 +4374,16 @@
         <v>56</v>
       </c>
       <c r="C210" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D210">
-        <v>445</v>
+        <v>123</v>
       </c>
       <c r="E210">
-        <v>34.84729835552075</v>
+        <v>28.21100917431193</v>
       </c>
       <c r="F210" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4412,16 +4394,36 @@
         <v>56</v>
       </c>
       <c r="C211" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D211">
-        <v>283</v>
+        <v>117</v>
       </c>
       <c r="E211">
-        <v>22.16131558339859</v>
+        <v>26.8348623853211</v>
       </c>
       <c r="F211" t="s">
-        <v>210</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212">
+        <v>2025</v>
+      </c>
+      <c r="B212" t="s">
+        <v>56</v>
+      </c>
+      <c r="C212" t="s">
+        <v>188</v>
+      </c>
+      <c r="D212">
+        <v>106</v>
+      </c>
+      <c r="E212">
+        <v>24.31192660550459</v>
+      </c>
+      <c r="F212" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -4429,39 +4431,19 @@
         <v>2025</v>
       </c>
       <c r="B213" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C213" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D213">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="E213">
-        <v>28.21100917431193</v>
+        <v>20.64220183486239</v>
       </c>
       <c r="F213" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214">
-        <v>2025</v>
-      </c>
-      <c r="B214" t="s">
-        <v>57</v>
-      </c>
-      <c r="C214" t="s">
-        <v>191</v>
-      </c>
-      <c r="D214">
-        <v>117</v>
-      </c>
-      <c r="E214">
-        <v>26.8348623853211</v>
-      </c>
-      <c r="F214" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -4472,16 +4454,16 @@
         <v>57</v>
       </c>
       <c r="C215" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D215">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="E215">
-        <v>24.31192660550459</v>
+        <v>45.03464203233256</v>
       </c>
       <c r="F215" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -4492,36 +4474,36 @@
         <v>57</v>
       </c>
       <c r="C216" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D216">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="E216">
-        <v>20.64220183486239</v>
+        <v>37.41339491916859</v>
       </c>
       <c r="F216" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217">
         <v>2025</v>
       </c>
-      <c r="B218" t="s">
-        <v>58</v>
-      </c>
-      <c r="C218" t="s">
-        <v>194</v>
-      </c>
-      <c r="D218">
-        <v>195</v>
-      </c>
-      <c r="E218">
-        <v>45.03464203233256</v>
-      </c>
-      <c r="F218" t="s">
-        <v>210</v>
+      <c r="B217" t="s">
+        <v>57</v>
+      </c>
+      <c r="C217" t="s">
+        <v>192</v>
+      </c>
+      <c r="D217">
+        <v>76</v>
+      </c>
+      <c r="E217">
+        <v>17.55196304849884</v>
+      </c>
+      <c r="F217" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -4532,16 +4514,16 @@
         <v>58</v>
       </c>
       <c r="C219" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D219">
-        <v>162</v>
+        <v>315</v>
       </c>
       <c r="E219">
-        <v>37.41339491916859</v>
+        <v>43.09165526675787</v>
       </c>
       <c r="F219" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -4552,116 +4534,36 @@
         <v>58</v>
       </c>
       <c r="C220" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D220">
-        <v>76</v>
+        <v>247</v>
       </c>
       <c r="E220">
-        <v>17.55196304849884</v>
+        <v>33.78932968536252</v>
       </c>
       <c r="F220" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221">
         <v>2025</v>
       </c>
-      <c r="B222" t="s">
-        <v>59</v>
-      </c>
-      <c r="C222" t="s">
-        <v>197</v>
-      </c>
-      <c r="D222">
-        <v>315</v>
-      </c>
-      <c r="E222">
-        <v>43.09165526675787</v>
-      </c>
-      <c r="F222" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
-      <c r="A223">
-        <v>2025</v>
-      </c>
-      <c r="B223" t="s">
-        <v>59</v>
-      </c>
-      <c r="C223" t="s">
+      <c r="B221" t="s">
+        <v>58</v>
+      </c>
+      <c r="C221" t="s">
+        <v>195</v>
+      </c>
+      <c r="D221">
+        <v>169</v>
+      </c>
+      <c r="E221">
+        <v>23.11901504787962</v>
+      </c>
+      <c r="F221" t="s">
         <v>198</v>
-      </c>
-      <c r="D223">
-        <v>247</v>
-      </c>
-      <c r="E223">
-        <v>33.78932968536252</v>
-      </c>
-      <c r="F223" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
-      <c r="A224">
-        <v>2025</v>
-      </c>
-      <c r="B224" t="s">
-        <v>59</v>
-      </c>
-      <c r="C224" t="s">
-        <v>199</v>
-      </c>
-      <c r="D224">
-        <v>169</v>
-      </c>
-      <c r="E224">
-        <v>23.11901504787962</v>
-      </c>
-      <c r="F224" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
-      <c r="A226">
-        <v>2025</v>
-      </c>
-      <c r="B226" t="s">
-        <v>60</v>
-      </c>
-      <c r="C226" t="s">
-        <v>200</v>
-      </c>
-      <c r="D226">
-        <v>1002</v>
-      </c>
-      <c r="E226">
-        <v>49.80119284294234</v>
-      </c>
-      <c r="F226" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6">
-      <c r="A227">
-        <v>2025</v>
-      </c>
-      <c r="B227" t="s">
-        <v>60</v>
-      </c>
-      <c r="C227" t="s">
-        <v>201</v>
-      </c>
-      <c r="D227">
-        <v>984</v>
-      </c>
-      <c r="E227">
-        <v>48.9065606361829</v>
-      </c>
-      <c r="F227" t="s">
-        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="276">
   <si>
     <t>Year</t>
   </si>
@@ -68,12 +68,24 @@
     <t>DEM Mayor Allentown</t>
   </si>
   <si>
+    <t>DEM Mayor-Swoyersville Borough (4 Year Term)</t>
+  </si>
+  <si>
+    <t>REP CONSTABLE LIGONIER</t>
+  </si>
+  <si>
     <t>REP Constable Moore Twsp</t>
   </si>
   <si>
     <t>REP JUDGE OF THE COURT OF COMMON PLEAS</t>
   </si>
   <si>
+    <t>REP MAGISTERIAL DISTRICT JUDGE 10-2-01</t>
+  </si>
+  <si>
+    <t>REP MAGISTERIAL DISTRICT JUDGE 10-3-08</t>
+  </si>
+  <si>
     <t>REP MAGISTERIAL DISTRICT JUDGE 35-03-02</t>
   </si>
   <si>
@@ -83,6 +95,9 @@
     <t>REP Magisterial District Judge 03-2-09</t>
   </si>
   <si>
+    <t>REP SUPERVISOR COOK</t>
+  </si>
+  <si>
     <t>REP Supervisor Zerbe Township</t>
   </si>
   <si>
@@ -95,6 +110,9 @@
     <t>DEM Hazleton Area School District 2yr Hazleton Area School District</t>
   </si>
   <si>
+    <t>DEM MAGISTERIAL DISTRICT JUDGE 10-2-06</t>
+  </si>
+  <si>
     <t>DEM Magisterial District Judge 19-2-03</t>
   </si>
   <si>
@@ -116,6 +134,9 @@
     <t>REP Commissioner Bethlehem Twsp 1st Ward</t>
   </si>
   <si>
+    <t>REP MAGISTERIAL DISTRICT JUDGE 10-2-06</t>
+  </si>
+  <si>
     <t>REP Magisterial District Judge 19-2-03</t>
   </si>
   <si>
@@ -161,27 +182,51 @@
     <t>Committeeman, Aston Township Ward 7</t>
   </si>
   <si>
+    <t>DEM COUNTY COUNCIL - DISTRICT 4 - 4 YEAR TERM</t>
+  </si>
+  <si>
+    <t>DEM ERIE CITY CONTROLLER 4 YEAR TERM</t>
+  </si>
+  <si>
     <t>DEM MAGISTERIAL DISTRICT JUDGE 03-3-02</t>
   </si>
   <si>
     <t>REP Codorus Township Supervisor-REP</t>
   </si>
   <si>
+    <t>REP EAST HUNTINGDON TOWNSHIP Supervisor - 6 Year Term</t>
+  </si>
+  <si>
     <t>REP JUDGE OF THE COURT OF COMMON  PLEAS</t>
   </si>
   <si>
+    <t>REP JUDGE OF THE COURT OF COMMON PLEAS - 6TH JUDICIAL DISTRICT 10 YEAR TERM</t>
+  </si>
+  <si>
     <t>REP Judge of the Court of Common Pleas</t>
   </si>
   <si>
     <t>REP Magisterial District Judge 21-3-04</t>
   </si>
   <si>
+    <t>REP Magisterial District Judge Magisterial District 11-2-01 (2 Year Term)</t>
+  </si>
+  <si>
+    <t>REP NORTH HUNTINGDON TOWNSHIP Commissioner 6th Ward - 4</t>
+  </si>
+  <si>
+    <t>REP Register of Wills and Clerk of the Orphans' Court</t>
+  </si>
+  <si>
     <t>REP SUPERVISOR 6YR Plainfield Twsp</t>
   </si>
   <si>
     <t>REP TAX COLLECTOR CENTER TOWNSHIP</t>
   </si>
   <si>
+    <t>REP Township Supervisor (6 Year Term) Foster Twp</t>
+  </si>
+  <si>
     <t>REP Township Supervisor 2 Year Term Exeter Twp</t>
   </si>
   <si>
@@ -257,6 +302,30 @@
     <t>CE CE GERLACH</t>
   </si>
   <si>
+    <t>KATHLEEN BREZNAY</t>
+  </si>
+  <si>
+    <t>KELLEY CONNER</t>
+  </si>
+  <si>
+    <t>PAULA SCHNELLY</t>
+  </si>
+  <si>
+    <t>DEBORAH LAYAOU</t>
+  </si>
+  <si>
+    <t>ESPY WILLIAMS</t>
+  </si>
+  <si>
+    <t>SHAWN MILLER</t>
+  </si>
+  <si>
+    <t>ROBERT AMICONE</t>
+  </si>
+  <si>
+    <t>JOE RUSSELL</t>
+  </si>
+  <si>
     <t>RONALD DELBACCO</t>
   </si>
   <si>
@@ -266,9 +335,39 @@
     <t>JEFFREY KOCHER</t>
   </si>
   <si>
+    <t>SCOTT FANCHALSKY</t>
+  </si>
+  <si>
+    <t>DOUG WEIMER</t>
+  </si>
+  <si>
+    <t>IRVIN SHIPLEY</t>
+  </si>
+  <si>
+    <t>KELLY TUA HAMMERS</t>
+  </si>
+  <si>
+    <t>AMY ALTMAN MCCHESNEY</t>
+  </si>
+  <si>
+    <t>JANELLE HOOD</t>
+  </si>
+  <si>
     <t>SEAN MAGUIRE</t>
   </si>
   <si>
+    <t>LUKE GRIMM</t>
+  </si>
+  <si>
+    <t>COLTON LENHART</t>
+  </si>
+  <si>
+    <t>WILLY GROSS</t>
+  </si>
+  <si>
+    <t>RICHARD UMBAUGH</t>
+  </si>
+  <si>
     <t>DANIEL TUBBY BILLIG</t>
   </si>
   <si>
@@ -305,6 +404,18 @@
     <t>TAIRA FERRERAS</t>
   </si>
   <si>
+    <t>JOHN CHRISTNER</t>
+  </si>
+  <si>
+    <t>KAREN GELETY PATTERSON</t>
+  </si>
+  <si>
+    <t>CHRIS HUFFMAN</t>
+  </si>
+  <si>
+    <t>MICHAEL STANGROOM</t>
+  </si>
+  <si>
     <t>TOBIN ZECH</t>
   </si>
   <si>
@@ -500,6 +611,30 @@
     <t>JOSEPH DYCHALA</t>
   </si>
   <si>
+    <t>JIM WINARSKI</t>
+  </si>
+  <si>
+    <t>MICHAEL KEYS</t>
+  </si>
+  <si>
+    <t>MARCUS JACOBS</t>
+  </si>
+  <si>
+    <t>CARL ANDERSON III</t>
+  </si>
+  <si>
+    <t>KEVIN PASTEWKA</t>
+  </si>
+  <si>
+    <t>BROOKE SANFILIPPO</t>
+  </si>
+  <si>
+    <t>ED BRZEZINSKI</t>
+  </si>
+  <si>
+    <t>CHUCK NELSON</t>
+  </si>
+  <si>
     <t>ELLEN KINGSLEY</t>
   </si>
   <si>
@@ -515,6 +650,21 @@
     <t>CAROLYN BUPP</t>
   </si>
   <si>
+    <t>JUSTIN MORROW</t>
+  </si>
+  <si>
+    <t>TONY MOORE</t>
+  </si>
+  <si>
+    <t>JIM CARSON</t>
+  </si>
+  <si>
+    <t>LARRY ANSELL</t>
+  </si>
+  <si>
+    <t>MATTHEW ACCIPITER</t>
+  </si>
+  <si>
     <t>JAMES FULLER</t>
   </si>
   <si>
@@ -524,6 +674,15 @@
     <t>ROBERT EYER</t>
   </si>
   <si>
+    <t>JEREMY LIGHTNER</t>
+  </si>
+  <si>
+    <t>LEIGH ANN ORTON</t>
+  </si>
+  <si>
+    <t>EMILY MOSCO MERSKI</t>
+  </si>
+  <si>
     <t>KATHRYN LEHMAN</t>
   </si>
   <si>
@@ -548,6 +707,33 @@
     <t>GUY SMITH</t>
   </si>
   <si>
+    <t>LAURA DENNIS-BOVANI</t>
+  </si>
+  <si>
+    <t>MATTHEW CARMODY</t>
+  </si>
+  <si>
+    <t>ROBERT BOYER</t>
+  </si>
+  <si>
+    <t>LEAH MCGHEE</t>
+  </si>
+  <si>
+    <t>ANTONIO LIO</t>
+  </si>
+  <si>
+    <t>WILLIAM CUMMINGS</t>
+  </si>
+  <si>
+    <t>KATIE PECARCHIK</t>
+  </si>
+  <si>
+    <t>JON WIAN</t>
+  </si>
+  <si>
+    <t>KIMBERLY HORRELL</t>
+  </si>
+  <si>
     <t>JONATHAN FRANK ITTERLY</t>
   </si>
   <si>
@@ -566,6 +752,18 @@
     <t>JENNIFER SHAFFOR</t>
   </si>
   <si>
+    <t>JOHN PAVUK</t>
+  </si>
+  <si>
+    <t>ALICE LACHEWITZ</t>
+  </si>
+  <si>
+    <t>BENJAMIN EVANCHO</t>
+  </si>
+  <si>
+    <t>SCATTER</t>
+  </si>
+  <si>
     <t>LARRY DROGO</t>
   </si>
   <si>
@@ -620,6 +818,12 @@
     <t>Lehigh County (Allentown + boroughs + townships)</t>
   </si>
   <si>
+    <t>Luzerne County (Wilkes-Barre + boroughs + townships)</t>
+  </si>
+  <si>
+    <t>Westmoreland County (city + boroughs + townships)</t>
+  </si>
+  <si>
     <t>Northumberland County (Sunbury + Shamokin + boroughs)</t>
   </si>
   <si>
@@ -633,6 +837,9 @@
   </si>
   <si>
     <t>Lycoming County (Williamsport + boroughs + townships)</t>
+  </si>
+  <si>
+    <t>Erie County (city + boroughs + townships)</t>
   </si>
   <si>
     <t>Indiana County (Indiana + boroughs + townships)</t>
@@ -1083,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:F291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1114,7 +1321,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D2">
         <v>3420</v>
@@ -1123,7 +1330,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F2" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1134,7 +1341,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D3">
         <v>2391</v>
@@ -1143,7 +1350,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F3" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1154,7 +1361,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D4">
         <v>2184</v>
@@ -1163,7 +1370,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F4" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1174,7 +1381,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D6">
         <v>572</v>
@@ -1183,7 +1390,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F6" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1194,7 +1401,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D7">
         <v>380</v>
@@ -1203,7 +1410,7 @@
         <v>31.25</v>
       </c>
       <c r="F7" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1214,7 +1421,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D8">
         <v>264</v>
@@ -1223,7 +1430,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F8" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1234,7 +1441,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <v>177</v>
@@ -1243,7 +1450,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F10" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1254,7 +1461,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D11">
         <v>141</v>
@@ -1263,7 +1470,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F11" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1274,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D12">
         <v>81</v>
@@ -1283,7 +1490,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F12" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1294,7 +1501,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D13">
         <v>44</v>
@@ -1303,7 +1510,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F13" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1314,7 +1521,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D15">
         <v>1471</v>
@@ -1323,7 +1530,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F15" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1334,7 +1541,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D16">
         <v>1247</v>
@@ -1343,7 +1550,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F16" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1354,7 +1561,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D17">
         <v>616</v>
@@ -1363,7 +1570,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F17" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1374,7 +1581,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D19">
         <v>1183</v>
@@ -1383,7 +1590,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F19" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1394,7 +1601,7 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D20">
         <v>1177</v>
@@ -1403,7 +1610,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F20" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1414,7 +1621,7 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D21">
         <v>373</v>
@@ -1423,7 +1630,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F21" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1434,7 +1641,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D22">
         <v>270</v>
@@ -1443,7 +1650,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F22" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1454,7 +1661,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D24">
         <v>2064</v>
@@ -1463,7 +1670,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F24" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1474,7 +1681,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D25">
         <v>1942</v>
@@ -1483,7 +1690,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F25" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1494,7 +1701,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D26">
         <v>1927</v>
@@ -1503,7 +1710,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F26" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1514,7 +1721,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D27">
         <v>1817</v>
@@ -1523,7 +1730,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F27" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1534,16 +1741,16 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D29">
-        <v>522</v>
+        <v>237</v>
       </c>
       <c r="E29">
-        <v>48.33333333333334</v>
+        <v>32.20108695652174</v>
       </c>
       <c r="F29" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1554,16 +1761,16 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D30">
-        <v>331</v>
+        <v>234</v>
       </c>
       <c r="E30">
-        <v>30.64814814814815</v>
+        <v>31.79347826086957</v>
       </c>
       <c r="F30" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1574,16 +1781,36 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D31">
-        <v>227</v>
+        <v>148</v>
       </c>
       <c r="E31">
-        <v>21.01851851851852</v>
+        <v>20.10869565217391</v>
       </c>
       <c r="F31" t="s">
-        <v>199</v>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>2021</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32">
+        <v>90</v>
+      </c>
+      <c r="E32">
+        <v>12.22826086956522</v>
+      </c>
+      <c r="F32" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1591,39 +1818,19 @@
         <v>2021</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="D33">
-        <v>4922</v>
+        <v>27</v>
       </c>
       <c r="E33">
-        <v>41.68713475057169</v>
+        <v>3.668478260869565</v>
       </c>
       <c r="F33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>2021</v>
-      </c>
-      <c r="B34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34">
-        <v>4820</v>
-      </c>
-      <c r="E34">
-        <v>40.82324045058016</v>
-      </c>
-      <c r="F34" t="s">
-        <v>196</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1634,16 +1841,36 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D35">
-        <v>2065</v>
+        <v>588</v>
       </c>
       <c r="E35">
-        <v>17.48962479884814</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="F35" t="s">
-        <v>196</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>2021</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36">
+        <v>379</v>
+      </c>
+      <c r="E36">
+        <v>31.47840531561462</v>
+      </c>
+      <c r="F36" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1651,39 +1878,19 @@
         <v>2021</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="D37">
-        <v>1779</v>
+        <v>237</v>
       </c>
       <c r="E37">
-        <v>46.82811266122664</v>
+        <v>19.6843853820598</v>
       </c>
       <c r="F37" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>2021</v>
-      </c>
-      <c r="B38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" t="s">
-        <v>63</v>
-      </c>
-      <c r="D38">
-        <v>1349</v>
-      </c>
-      <c r="E38">
-        <v>35.50934456435904</v>
-      </c>
-      <c r="F38" t="s">
-        <v>196</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1694,16 +1901,36 @@
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D39">
-        <v>671</v>
+        <v>522</v>
       </c>
       <c r="E39">
-        <v>17.66254277441432</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="F39" t="s">
-        <v>196</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>2021</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40">
+        <v>331</v>
+      </c>
+      <c r="E40">
+        <v>30.64814814814815</v>
+      </c>
+      <c r="F40" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1711,39 +1938,19 @@
         <v>2021</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D41">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="E41">
-        <v>37.09677419354838</v>
+        <v>21.01851851851852</v>
       </c>
       <c r="F41" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>2021</v>
-      </c>
-      <c r="B42" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42">
-        <v>224</v>
-      </c>
-      <c r="E42">
-        <v>32.84457478005865</v>
-      </c>
-      <c r="F42" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1754,16 +1961,16 @@
         <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D43">
-        <v>122</v>
+        <v>4922</v>
       </c>
       <c r="E43">
-        <v>17.88856304985337</v>
+        <v>41.68713475057169</v>
       </c>
       <c r="F43" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1774,16 +1981,16 @@
         <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D44">
-        <v>60</v>
+        <v>4820</v>
       </c>
       <c r="E44">
-        <v>8.797653958944283</v>
+        <v>40.82324045058016</v>
       </c>
       <c r="F44" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1794,16 +2001,16 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D45">
-        <v>23</v>
+        <v>2065</v>
       </c>
       <c r="E45">
-        <v>3.372434017595308</v>
+        <v>17.48962479884814</v>
       </c>
       <c r="F45" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1814,16 +2021,16 @@
         <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D47">
-        <v>917</v>
+        <v>1281</v>
       </c>
       <c r="E47">
-        <v>36.31683168316832</v>
+        <v>43.88489208633094</v>
       </c>
       <c r="F47" t="s">
-        <v>199</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1834,16 +2041,16 @@
         <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="D48">
-        <v>706</v>
+        <v>924</v>
       </c>
       <c r="E48">
-        <v>27.96039603960396</v>
+        <v>31.6546762589928</v>
       </c>
       <c r="F48" t="s">
-        <v>199</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1854,36 +2061,36 @@
         <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="D49">
-        <v>578</v>
+        <v>714</v>
       </c>
       <c r="E49">
-        <v>22.89108910891089</v>
+        <v>24.46043165467626</v>
       </c>
       <c r="F49" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>2021</v>
-      </c>
-      <c r="B50" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" t="s">
-        <v>75</v>
-      </c>
-      <c r="D50">
-        <v>324</v>
-      </c>
-      <c r="E50">
-        <v>12.83168316831683</v>
-      </c>
-      <c r="F50" t="s">
-        <v>199</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>2021</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51">
+        <v>999</v>
+      </c>
+      <c r="E51">
+        <v>49.47994056463596</v>
+      </c>
+      <c r="F51" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1894,16 +2101,16 @@
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="D52">
-        <v>179</v>
+        <v>629</v>
       </c>
       <c r="E52">
-        <v>45.31645569620253</v>
+        <v>31.15403665180783</v>
       </c>
       <c r="F52" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1914,36 +2121,36 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="D53">
-        <v>110</v>
+        <v>391</v>
       </c>
       <c r="E53">
-        <v>27.84810126582278</v>
+        <v>19.36602278355622</v>
       </c>
       <c r="F53" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>2021</v>
-      </c>
-      <c r="B54" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" t="s">
-        <v>86</v>
-      </c>
-      <c r="D54">
-        <v>106</v>
-      </c>
-      <c r="E54">
-        <v>26.83544303797468</v>
-      </c>
-      <c r="F54" t="s">
-        <v>201</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>2021</v>
+      </c>
+      <c r="B55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C55" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55">
+        <v>1779</v>
+      </c>
+      <c r="E55">
+        <v>46.82811266122664</v>
+      </c>
+      <c r="F55" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1954,16 +2161,16 @@
         <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D56">
-        <v>276</v>
+        <v>1349</v>
       </c>
       <c r="E56">
-        <v>47.01873935264054</v>
+        <v>35.50934456435904</v>
       </c>
       <c r="F56" t="s">
-        <v>200</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1974,36 +2181,36 @@
         <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D57">
-        <v>226</v>
+        <v>671</v>
       </c>
       <c r="E57">
-        <v>38.50085178875639</v>
+        <v>17.66254277441432</v>
       </c>
       <c r="F57" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>2021</v>
-      </c>
-      <c r="B58" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58">
-        <v>85</v>
-      </c>
-      <c r="E58">
-        <v>14.48040885860307</v>
-      </c>
-      <c r="F58" t="s">
-        <v>200</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>2021</v>
+      </c>
+      <c r="B59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59">
+        <v>253</v>
+      </c>
+      <c r="E59">
+        <v>37.09677419354838</v>
+      </c>
+      <c r="F59" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2014,16 +2221,16 @@
         <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D60">
-        <v>636</v>
+        <v>224</v>
       </c>
       <c r="E60">
-        <v>41.24513618677042</v>
+        <v>32.84457478005865</v>
       </c>
       <c r="F60" t="s">
-        <v>200</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2034,16 +2241,16 @@
         <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D61">
-        <v>544</v>
+        <v>122</v>
       </c>
       <c r="E61">
-        <v>35.27885862516213</v>
+        <v>17.88856304985337</v>
       </c>
       <c r="F61" t="s">
-        <v>200</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2054,376 +2261,376 @@
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D62">
-        <v>362</v>
+        <v>60</v>
       </c>
       <c r="E62">
-        <v>23.47600518806744</v>
+        <v>8.797653958944283</v>
       </c>
       <c r="F62" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>2023</v>
-      </c>
-      <c r="B64" t="s">
-        <v>25</v>
-      </c>
-      <c r="C64" t="s">
-        <v>93</v>
-      </c>
-      <c r="D64">
-        <v>104</v>
-      </c>
-      <c r="E64">
-        <v>38.95131086142322</v>
-      </c>
-      <c r="F64" t="s">
-        <v>202</v>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>2021</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63">
+        <v>23</v>
+      </c>
+      <c r="E63">
+        <v>3.372434017595308</v>
+      </c>
+      <c r="F63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B65" t="s">
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D65">
-        <v>100</v>
+        <v>917</v>
       </c>
       <c r="E65">
-        <v>37.45318352059925</v>
+        <v>36.31683168316832</v>
       </c>
       <c r="F65" t="s">
-        <v>202</v>
+        <v>265</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B66" t="s">
         <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D66">
-        <v>63</v>
+        <v>706</v>
       </c>
       <c r="E66">
-        <v>23.59550561797753</v>
+        <v>27.96039603960396</v>
       </c>
       <c r="F66" t="s">
-        <v>202</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>2021</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" t="s">
+        <v>87</v>
+      </c>
+      <c r="D67">
+        <v>578</v>
+      </c>
+      <c r="E67">
+        <v>22.89108910891089</v>
+      </c>
+      <c r="F67" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D68">
-        <v>445</v>
+        <v>324</v>
       </c>
       <c r="E68">
-        <v>43.28793774319066</v>
+        <v>12.83168316831683</v>
       </c>
       <c r="F68" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>2023</v>
-      </c>
-      <c r="B69" t="s">
-        <v>26</v>
-      </c>
-      <c r="C69" t="s">
-        <v>97</v>
-      </c>
-      <c r="D69">
-        <v>353</v>
-      </c>
-      <c r="E69">
-        <v>34.33852140077821</v>
-      </c>
-      <c r="F69" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B70" t="s">
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D70">
-        <v>230</v>
+        <v>149</v>
       </c>
       <c r="E70">
-        <v>22.37354085603113</v>
+        <v>41.38888888888889</v>
       </c>
       <c r="F70" t="s">
-        <v>203</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>2021</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71">
+        <v>113</v>
+      </c>
+      <c r="E71">
+        <v>31.38888888888889</v>
+      </c>
+      <c r="F71" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D72">
-        <v>684</v>
+        <v>59</v>
       </c>
       <c r="E72">
-        <v>46.94577899794098</v>
+        <v>16.38888888888889</v>
       </c>
       <c r="F72" t="s">
-        <v>203</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73">
+        <v>39</v>
+      </c>
+      <c r="E73">
+        <v>10.83333333333333</v>
+      </c>
+      <c r="F73" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>2021</v>
+      </c>
+      <c r="B75" t="s">
         <v>27</v>
       </c>
-      <c r="C73" t="s">
-        <v>100</v>
-      </c>
-      <c r="D73">
-        <v>395</v>
-      </c>
-      <c r="E73">
-        <v>27.1105010295127</v>
-      </c>
-      <c r="F73" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>2023</v>
-      </c>
-      <c r="B74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" t="s">
-        <v>101</v>
-      </c>
-      <c r="D74">
-        <v>378</v>
-      </c>
-      <c r="E74">
-        <v>25.94371997254633</v>
-      </c>
-      <c r="F74" t="s">
-        <v>203</v>
+      <c r="C75" t="s">
+        <v>117</v>
+      </c>
+      <c r="D75">
+        <v>179</v>
+      </c>
+      <c r="E75">
+        <v>45.31645569620253</v>
+      </c>
+      <c r="F75" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D76">
-        <v>828</v>
+        <v>110</v>
       </c>
       <c r="E76">
-        <v>36.71840354767184</v>
+        <v>27.84810126582278</v>
       </c>
       <c r="F76" t="s">
-        <v>198</v>
+        <v>269</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D77">
-        <v>524</v>
+        <v>106</v>
       </c>
       <c r="E77">
-        <v>23.23725055432372</v>
+        <v>26.83544303797468</v>
       </c>
       <c r="F77" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>2023</v>
-      </c>
-      <c r="B78" t="s">
-        <v>28</v>
-      </c>
-      <c r="C78" t="s">
-        <v>104</v>
-      </c>
-      <c r="D78">
-        <v>485</v>
-      </c>
-      <c r="E78">
-        <v>21.50776053215078</v>
-      </c>
-      <c r="F78" t="s">
-        <v>198</v>
+        <v>269</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B79" t="s">
         <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="D79">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="E79">
-        <v>11.57427937915743</v>
+        <v>47.01873935264054</v>
       </c>
       <c r="F79" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B80" t="s">
         <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D80">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="E80">
-        <v>6.962305986696231</v>
+        <v>38.50085178875639</v>
       </c>
       <c r="F80" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>2023</v>
-      </c>
-      <c r="B82" t="s">
-        <v>29</v>
-      </c>
-      <c r="C82" t="s">
-        <v>107</v>
-      </c>
-      <c r="D82">
-        <v>584</v>
-      </c>
-      <c r="E82">
-        <v>43.90977443609022</v>
-      </c>
-      <c r="F82" t="s">
-        <v>204</v>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>2021</v>
+      </c>
+      <c r="B81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" t="s">
+        <v>122</v>
+      </c>
+      <c r="D81">
+        <v>85</v>
+      </c>
+      <c r="E81">
+        <v>14.48040885860307</v>
+      </c>
+      <c r="F81" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B83" t="s">
         <v>29</v>
       </c>
       <c r="C83" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D83">
-        <v>388</v>
+        <v>636</v>
       </c>
       <c r="E83">
-        <v>29.17293233082707</v>
+        <v>41.24513618677042</v>
       </c>
       <c r="F83" t="s">
-        <v>204</v>
+        <v>266</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B84" t="s">
         <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D84">
-        <v>358</v>
+        <v>544</v>
       </c>
       <c r="E84">
-        <v>26.91729323308271</v>
+        <v>35.27885862516213</v>
       </c>
       <c r="F84" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>2023</v>
-      </c>
-      <c r="B86" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86" t="s">
-        <v>110</v>
-      </c>
-      <c r="D86">
-        <v>634</v>
-      </c>
-      <c r="E86">
-        <v>45.67723342939482</v>
-      </c>
-      <c r="F86" t="s">
-        <v>204</v>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>2021</v>
+      </c>
+      <c r="B85" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" t="s">
+        <v>125</v>
+      </c>
+      <c r="D85">
+        <v>362</v>
+      </c>
+      <c r="E85">
+        <v>23.47600518806744</v>
+      </c>
+      <c r="F85" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2434,16 +2641,16 @@
         <v>30</v>
       </c>
       <c r="C87" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D87">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="E87">
-        <v>21.46974063400576</v>
+        <v>38.95131086142322</v>
       </c>
       <c r="F87" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2454,16 +2661,16 @@
         <v>30</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D88">
-        <v>246</v>
+        <v>100</v>
       </c>
       <c r="E88">
-        <v>17.72334293948127</v>
+        <v>37.45318352059925</v>
       </c>
       <c r="F88" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2474,16 +2681,16 @@
         <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="D89">
-        <v>210</v>
+        <v>63</v>
       </c>
       <c r="E89">
-        <v>15.12968299711815</v>
+        <v>23.59550561797753</v>
       </c>
       <c r="F89" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2494,16 +2701,16 @@
         <v>31</v>
       </c>
       <c r="C91" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D91">
-        <v>294</v>
+        <v>882</v>
       </c>
       <c r="E91">
-        <v>38.33116036505867</v>
+        <v>45.60496380558428</v>
       </c>
       <c r="F91" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2514,16 +2721,16 @@
         <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D92">
-        <v>145</v>
+        <v>502</v>
       </c>
       <c r="E92">
-        <v>18.90482398956975</v>
+        <v>25.95656670113754</v>
       </c>
       <c r="F92" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2534,16 +2741,16 @@
         <v>31</v>
       </c>
       <c r="C93" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D93">
-        <v>136</v>
+        <v>399</v>
       </c>
       <c r="E93">
-        <v>17.73142112125163</v>
+        <v>20.63081695966908</v>
       </c>
       <c r="F93" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2554,36 +2761,36 @@
         <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D94">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="E94">
-        <v>13.5593220338983</v>
+        <v>7.807652533609101</v>
       </c>
       <c r="F94" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>2023</v>
-      </c>
-      <c r="B95" t="s">
-        <v>31</v>
-      </c>
-      <c r="C95" t="s">
-        <v>118</v>
-      </c>
-      <c r="D95">
-        <v>88</v>
-      </c>
-      <c r="E95">
-        <v>11.47327249022164</v>
-      </c>
-      <c r="F95" t="s">
-        <v>202</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>2023</v>
+      </c>
+      <c r="B96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" t="s">
+        <v>133</v>
+      </c>
+      <c r="D96">
+        <v>445</v>
+      </c>
+      <c r="E96">
+        <v>43.28793774319066</v>
+      </c>
+      <c r="F96" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2594,16 +2801,16 @@
         <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="D97">
-        <v>170</v>
+        <v>353</v>
       </c>
       <c r="E97">
-        <v>46.19565217391305</v>
+        <v>34.33852140077821</v>
       </c>
       <c r="F97" t="s">
-        <v>199</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2614,36 +2821,36 @@
         <v>32</v>
       </c>
       <c r="C98" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D98">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="E98">
-        <v>45.92391304347826</v>
+        <v>22.37354085603113</v>
       </c>
       <c r="F98" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>2023</v>
-      </c>
-      <c r="B99" t="s">
-        <v>32</v>
-      </c>
-      <c r="C99" t="s">
-        <v>121</v>
-      </c>
-      <c r="D99">
-        <v>29</v>
-      </c>
-      <c r="E99">
-        <v>7.880434782608696</v>
-      </c>
-      <c r="F99" t="s">
-        <v>199</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>2023</v>
+      </c>
+      <c r="B100" t="s">
+        <v>33</v>
+      </c>
+      <c r="C100" t="s">
+        <v>136</v>
+      </c>
+      <c r="D100">
+        <v>684</v>
+      </c>
+      <c r="E100">
+        <v>46.94577899794098</v>
+      </c>
+      <c r="F100" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -2654,16 +2861,16 @@
         <v>33</v>
       </c>
       <c r="C101" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="D101">
-        <v>886</v>
+        <v>395</v>
       </c>
       <c r="E101">
-        <v>48.86927744070601</v>
+        <v>27.1105010295127</v>
       </c>
       <c r="F101" t="s">
-        <v>203</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2674,36 +2881,36 @@
         <v>33</v>
       </c>
       <c r="C102" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="D102">
-        <v>699</v>
+        <v>378</v>
       </c>
       <c r="E102">
-        <v>38.55488141202427</v>
+        <v>25.94371997254633</v>
       </c>
       <c r="F102" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>2023</v>
-      </c>
-      <c r="B103" t="s">
-        <v>33</v>
-      </c>
-      <c r="C103" t="s">
-        <v>98</v>
-      </c>
-      <c r="D103">
-        <v>228</v>
-      </c>
-      <c r="E103">
-        <v>12.57584114726972</v>
-      </c>
-      <c r="F103" t="s">
-        <v>203</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104">
+        <v>2023</v>
+      </c>
+      <c r="B104" t="s">
+        <v>34</v>
+      </c>
+      <c r="C104" t="s">
+        <v>139</v>
+      </c>
+      <c r="D104">
+        <v>828</v>
+      </c>
+      <c r="E104">
+        <v>36.71840354767184</v>
+      </c>
+      <c r="F104" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2714,16 +2921,16 @@
         <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="D105">
-        <v>1630</v>
+        <v>524</v>
       </c>
       <c r="E105">
-        <v>44.46262956901255</v>
+        <v>23.23725055432372</v>
       </c>
       <c r="F105" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -2734,16 +2941,16 @@
         <v>34</v>
       </c>
       <c r="C106" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="D106">
-        <v>1039</v>
+        <v>485</v>
       </c>
       <c r="E106">
-        <v>28.34151663938898</v>
+        <v>21.50776053215078</v>
       </c>
       <c r="F106" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -2754,16 +2961,16 @@
         <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="D107">
-        <v>813</v>
+        <v>261</v>
       </c>
       <c r="E107">
-        <v>22.17675941080196</v>
+        <v>11.57427937915743</v>
       </c>
       <c r="F107" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -2774,16 +2981,16 @@
         <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D108">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="E108">
-        <v>5.019094380796509</v>
+        <v>6.962305986696231</v>
       </c>
       <c r="F108" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -2794,16 +3001,16 @@
         <v>35</v>
       </c>
       <c r="C110" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D110">
-        <v>1334</v>
+        <v>584</v>
       </c>
       <c r="E110">
-        <v>46.38386648122393</v>
+        <v>43.90977443609022</v>
       </c>
       <c r="F110" t="s">
-        <v>205</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -2814,16 +3021,16 @@
         <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D111">
-        <v>1278</v>
+        <v>388</v>
       </c>
       <c r="E111">
-        <v>44.43671766342142</v>
+        <v>29.17293233082707</v>
       </c>
       <c r="F111" t="s">
-        <v>205</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -2834,16 +3041,16 @@
         <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="D112">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="E112">
-        <v>9.179415855354661</v>
+        <v>26.91729323308271</v>
       </c>
       <c r="F112" t="s">
-        <v>205</v>
+        <v>272</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -2854,16 +3061,16 @@
         <v>36</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="D114">
-        <v>1466</v>
+        <v>634</v>
       </c>
       <c r="E114">
-        <v>43.1303324507208</v>
+        <v>45.67723342939482</v>
       </c>
       <c r="F114" t="s">
-        <v>198</v>
+        <v>272</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -2874,16 +3081,16 @@
         <v>36</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="D115">
-        <v>893</v>
+        <v>298</v>
       </c>
       <c r="E115">
-        <v>26.27243306854957</v>
+        <v>21.46974063400576</v>
       </c>
       <c r="F115" t="s">
-        <v>198</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -2894,16 +3101,16 @@
         <v>36</v>
       </c>
       <c r="C116" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="D116">
-        <v>672</v>
+        <v>246</v>
       </c>
       <c r="E116">
-        <v>19.77052074139453</v>
+        <v>17.72334293948127</v>
       </c>
       <c r="F116" t="s">
-        <v>198</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -2914,36 +3121,36 @@
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="D117">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="E117">
-        <v>7.208002353633422</v>
+        <v>15.12968299711815</v>
       </c>
       <c r="F117" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>2023</v>
-      </c>
-      <c r="B118" t="s">
-        <v>36</v>
-      </c>
-      <c r="C118" t="s">
-        <v>102</v>
-      </c>
-      <c r="D118">
-        <v>123</v>
-      </c>
-      <c r="E118">
-        <v>3.618711385701677</v>
-      </c>
-      <c r="F118" t="s">
-        <v>198</v>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119">
+        <v>2023</v>
+      </c>
+      <c r="B119" t="s">
+        <v>37</v>
+      </c>
+      <c r="C119" t="s">
+        <v>151</v>
+      </c>
+      <c r="D119">
+        <v>294</v>
+      </c>
+      <c r="E119">
+        <v>38.33116036505867</v>
+      </c>
+      <c r="F119" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -2954,16 +3161,16 @@
         <v>37</v>
       </c>
       <c r="C120" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="D120">
-        <v>1108</v>
+        <v>145</v>
       </c>
       <c r="E120">
-        <v>46.4765100671141</v>
+        <v>18.90482398956975</v>
       </c>
       <c r="F120" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -2974,16 +3181,16 @@
         <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="D121">
-        <v>444</v>
+        <v>136</v>
       </c>
       <c r="E121">
-        <v>18.6241610738255</v>
+        <v>17.73142112125163</v>
       </c>
       <c r="F121" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -2994,16 +3201,16 @@
         <v>37</v>
       </c>
       <c r="C122" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="D122">
-        <v>343</v>
+        <v>104</v>
       </c>
       <c r="E122">
-        <v>14.38758389261745</v>
+        <v>13.5593220338983</v>
       </c>
       <c r="F122" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3014,36 +3221,36 @@
         <v>37</v>
       </c>
       <c r="C123" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="D123">
-        <v>323</v>
+        <v>88</v>
       </c>
       <c r="E123">
-        <v>13.5486577181208</v>
+        <v>11.47327249022164</v>
       </c>
       <c r="F123" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>2023</v>
-      </c>
-      <c r="B124" t="s">
-        <v>37</v>
-      </c>
-      <c r="C124" t="s">
-        <v>112</v>
-      </c>
-      <c r="D124">
-        <v>166</v>
-      </c>
-      <c r="E124">
-        <v>6.963087248322148</v>
-      </c>
-      <c r="F124" t="s">
-        <v>204</v>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125">
+        <v>2023</v>
+      </c>
+      <c r="B125" t="s">
+        <v>38</v>
+      </c>
+      <c r="C125" t="s">
+        <v>156</v>
+      </c>
+      <c r="D125">
+        <v>170</v>
+      </c>
+      <c r="E125">
+        <v>46.19565217391305</v>
+      </c>
+      <c r="F125" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3054,16 +3261,16 @@
         <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="D126">
-        <v>904</v>
+        <v>169</v>
       </c>
       <c r="E126">
-        <v>42.60131950989632</v>
+        <v>45.92391304347826</v>
       </c>
       <c r="F126" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3074,36 +3281,16 @@
         <v>38</v>
       </c>
       <c r="C127" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="D127">
-        <v>860</v>
+        <v>29</v>
       </c>
       <c r="E127">
-        <v>40.52780395852969</v>
+        <v>7.880434782608696</v>
       </c>
       <c r="F127" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>2023</v>
-      </c>
-      <c r="B128" t="s">
-        <v>38</v>
-      </c>
-      <c r="C128" t="s">
-        <v>129</v>
-      </c>
-      <c r="D128">
-        <v>193</v>
-      </c>
-      <c r="E128">
-        <v>9.095193213949104</v>
-      </c>
-      <c r="F128" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3111,19 +3298,39 @@
         <v>2023</v>
       </c>
       <c r="B129" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D129">
-        <v>165</v>
+        <v>1114</v>
       </c>
       <c r="E129">
-        <v>7.775683317624882</v>
+        <v>47.79064779064779</v>
       </c>
       <c r="F129" t="s">
-        <v>204</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130">
+        <v>2023</v>
+      </c>
+      <c r="B130" t="s">
+        <v>39</v>
+      </c>
+      <c r="C130" t="s">
+        <v>131</v>
+      </c>
+      <c r="D130">
+        <v>647</v>
+      </c>
+      <c r="E130">
+        <v>27.75632775632776</v>
+      </c>
+      <c r="F130" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3134,16 +3341,16 @@
         <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D131">
-        <v>425</v>
+        <v>369</v>
       </c>
       <c r="E131">
-        <v>25.11820330969267</v>
+        <v>15.83011583011583</v>
       </c>
       <c r="F131" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3154,36 +3361,16 @@
         <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D132">
-        <v>341</v>
+        <v>201</v>
       </c>
       <c r="E132">
-        <v>20.15366430260048</v>
+        <v>8.622908622908623</v>
       </c>
       <c r="F132" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>2023</v>
-      </c>
-      <c r="B133" t="s">
-        <v>39</v>
-      </c>
-      <c r="C133" t="s">
-        <v>116</v>
-      </c>
-      <c r="D133">
-        <v>279</v>
-      </c>
-      <c r="E133">
-        <v>16.48936170212766</v>
-      </c>
-      <c r="F133" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3191,19 +3378,19 @@
         <v>2023</v>
       </c>
       <c r="B134" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C134" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="D134">
-        <v>272</v>
+        <v>886</v>
       </c>
       <c r="E134">
-        <v>16.07565011820331</v>
+        <v>48.86927744070601</v>
       </c>
       <c r="F134" t="s">
-        <v>202</v>
+        <v>271</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3211,19 +3398,19 @@
         <v>2023</v>
       </c>
       <c r="B135" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C135" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D135">
-        <v>220</v>
+        <v>699</v>
       </c>
       <c r="E135">
-        <v>13.00236406619385</v>
+        <v>38.55488141202427</v>
       </c>
       <c r="F135" t="s">
-        <v>202</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3231,19 +3418,19 @@
         <v>2023</v>
       </c>
       <c r="B136" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C136" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D136">
-        <v>155</v>
+        <v>228</v>
       </c>
       <c r="E136">
-        <v>9.160756501182032</v>
+        <v>12.57584114726972</v>
       </c>
       <c r="F136" t="s">
-        <v>202</v>
+        <v>271</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3251,19 +3438,19 @@
         <v>2023</v>
       </c>
       <c r="B138" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C138" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D138">
-        <v>286</v>
+        <v>1630</v>
       </c>
       <c r="E138">
-        <v>48.22934232715008</v>
+        <v>44.46262956901255</v>
       </c>
       <c r="F138" t="s">
-        <v>199</v>
+        <v>271</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3271,19 +3458,19 @@
         <v>2023</v>
       </c>
       <c r="B139" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D139">
-        <v>212</v>
+        <v>1039</v>
       </c>
       <c r="E139">
-        <v>35.7504215851602</v>
+        <v>28.34151663938898</v>
       </c>
       <c r="F139" t="s">
-        <v>199</v>
+        <v>271</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3291,39 +3478,39 @@
         <v>2023</v>
       </c>
       <c r="B140" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D140">
-        <v>95</v>
+        <v>813</v>
       </c>
       <c r="E140">
-        <v>16.02023608768971</v>
+        <v>22.17675941080196</v>
       </c>
       <c r="F140" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>2023</v>
-      </c>
-      <c r="B142" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141">
+        <v>2023</v>
+      </c>
+      <c r="B141" t="s">
         <v>41</v>
       </c>
-      <c r="C142" t="s">
-        <v>135</v>
-      </c>
-      <c r="D142">
-        <v>431</v>
-      </c>
-      <c r="E142">
-        <v>36.77474402730375</v>
-      </c>
-      <c r="F142" t="s">
-        <v>199</v>
+      <c r="C141" t="s">
+        <v>159</v>
+      </c>
+      <c r="D141">
+        <v>184</v>
+      </c>
+      <c r="E141">
+        <v>5.019094380796509</v>
+      </c>
+      <c r="F141" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3331,19 +3518,19 @@
         <v>2023</v>
       </c>
       <c r="B143" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C143" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D143">
-        <v>297</v>
+        <v>1334</v>
       </c>
       <c r="E143">
-        <v>25.34129692832764</v>
+        <v>46.38386648122393</v>
       </c>
       <c r="F143" t="s">
-        <v>199</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3351,19 +3538,19 @@
         <v>2023</v>
       </c>
       <c r="B144" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C144" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="D144">
-        <v>285</v>
+        <v>1278</v>
       </c>
       <c r="E144">
-        <v>24.31740614334471</v>
+        <v>44.43671766342142</v>
       </c>
       <c r="F144" t="s">
-        <v>199</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3371,39 +3558,39 @@
         <v>2023</v>
       </c>
       <c r="B145" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C145" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="D145">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="E145">
-        <v>8.191126279863481</v>
+        <v>9.179415855354661</v>
       </c>
       <c r="F145" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>2023</v>
-      </c>
-      <c r="B146" t="s">
-        <v>41</v>
-      </c>
-      <c r="C146" t="s">
-        <v>139</v>
-      </c>
-      <c r="D146">
-        <v>63</v>
-      </c>
-      <c r="E146">
-        <v>5.375426621160409</v>
-      </c>
-      <c r="F146" t="s">
-        <v>199</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147">
+        <v>2023</v>
+      </c>
+      <c r="B147" t="s">
+        <v>43</v>
+      </c>
+      <c r="C147" t="s">
+        <v>143</v>
+      </c>
+      <c r="D147">
+        <v>1466</v>
+      </c>
+      <c r="E147">
+        <v>43.1303324507208</v>
+      </c>
+      <c r="F147" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3411,19 +3598,19 @@
         <v>2023</v>
       </c>
       <c r="B148" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C148" t="s">
         <v>140</v>
       </c>
       <c r="D148">
-        <v>273</v>
+        <v>893</v>
       </c>
       <c r="E148">
-        <v>45.4242928452579</v>
+        <v>26.27243306854957</v>
       </c>
       <c r="F148" t="s">
-        <v>201</v>
+        <v>264</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3431,19 +3618,19 @@
         <v>2023</v>
       </c>
       <c r="B149" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C149" t="s">
         <v>141</v>
       </c>
       <c r="D149">
-        <v>234</v>
+        <v>672</v>
       </c>
       <c r="E149">
-        <v>38.9351081530782</v>
+        <v>19.77052074139453</v>
       </c>
       <c r="F149" t="s">
-        <v>201</v>
+        <v>264</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3451,39 +3638,39 @@
         <v>2023</v>
       </c>
       <c r="B150" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C150" t="s">
         <v>142</v>
       </c>
       <c r="D150">
-        <v>94</v>
+        <v>245</v>
       </c>
       <c r="E150">
-        <v>15.64059900166389</v>
+        <v>7.208002353633422</v>
       </c>
       <c r="F150" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>2023</v>
-      </c>
-      <c r="B152" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151">
+        <v>2023</v>
+      </c>
+      <c r="B151" t="s">
         <v>43</v>
       </c>
-      <c r="C152" t="s">
-        <v>143</v>
-      </c>
-      <c r="D152">
-        <v>124</v>
-      </c>
-      <c r="E152">
-        <v>47.69230769230769</v>
-      </c>
-      <c r="F152" t="s">
-        <v>201</v>
+      <c r="C151" t="s">
+        <v>139</v>
+      </c>
+      <c r="D151">
+        <v>123</v>
+      </c>
+      <c r="E151">
+        <v>3.618711385701677</v>
+      </c>
+      <c r="F151" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3491,19 +3678,19 @@
         <v>2023</v>
       </c>
       <c r="B153" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D153">
-        <v>73</v>
+        <v>1108</v>
       </c>
       <c r="E153">
-        <v>28.07692307692308</v>
+        <v>46.4765100671141</v>
       </c>
       <c r="F153" t="s">
-        <v>201</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3511,19 +3698,39 @@
         <v>2023</v>
       </c>
       <c r="B154" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C154" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D154">
-        <v>63</v>
+        <v>444</v>
       </c>
       <c r="E154">
-        <v>24.23076923076923</v>
+        <v>18.6241610738255</v>
       </c>
       <c r="F154" t="s">
-        <v>201</v>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155">
+        <v>2023</v>
+      </c>
+      <c r="B155" t="s">
+        <v>44</v>
+      </c>
+      <c r="C155" t="s">
+        <v>163</v>
+      </c>
+      <c r="D155">
+        <v>343</v>
+      </c>
+      <c r="E155">
+        <v>14.38758389261745</v>
+      </c>
+      <c r="F155" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3534,16 +3741,16 @@
         <v>44</v>
       </c>
       <c r="C156" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D156">
-        <v>827</v>
+        <v>323</v>
       </c>
       <c r="E156">
-        <v>47.88650839606254</v>
+        <v>13.5486577181208</v>
       </c>
       <c r="F156" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -3554,36 +3761,16 @@
         <v>44</v>
       </c>
       <c r="C157" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D157">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="E157">
-        <v>16.44470179502026</v>
+        <v>6.963087248322148</v>
       </c>
       <c r="F157" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>2023</v>
-      </c>
-      <c r="B158" t="s">
-        <v>44</v>
-      </c>
-      <c r="C158" t="s">
-        <v>148</v>
-      </c>
-      <c r="D158">
-        <v>222</v>
-      </c>
-      <c r="E158">
-        <v>12.85466126230457</v>
-      </c>
-      <c r="F158" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -3591,19 +3778,19 @@
         <v>2023</v>
       </c>
       <c r="B159" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C159" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="D159">
-        <v>211</v>
+        <v>904</v>
       </c>
       <c r="E159">
-        <v>12.21771858714534</v>
+        <v>42.60131950989632</v>
       </c>
       <c r="F159" t="s">
-        <v>204</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -3611,19 +3798,39 @@
         <v>2023</v>
       </c>
       <c r="B160" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C160" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D160">
-        <v>183</v>
+        <v>860</v>
       </c>
       <c r="E160">
-        <v>10.59640995946728</v>
+        <v>40.52780395852969</v>
       </c>
       <c r="F160" t="s">
-        <v>204</v>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161">
+        <v>2023</v>
+      </c>
+      <c r="B161" t="s">
+        <v>45</v>
+      </c>
+      <c r="C161" t="s">
+        <v>166</v>
+      </c>
+      <c r="D161">
+        <v>193</v>
+      </c>
+      <c r="E161">
+        <v>9.095193213949104</v>
+      </c>
+      <c r="F161" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -3634,36 +3841,16 @@
         <v>45</v>
       </c>
       <c r="C162" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D162">
-        <v>605</v>
+        <v>165</v>
       </c>
       <c r="E162">
-        <v>41.10054347826087</v>
+        <v>7.775683317624882</v>
       </c>
       <c r="F162" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163">
-        <v>2023</v>
-      </c>
-      <c r="B163" t="s">
-        <v>45</v>
-      </c>
-      <c r="C163" t="s">
-        <v>152</v>
-      </c>
-      <c r="D163">
-        <v>593</v>
-      </c>
-      <c r="E163">
-        <v>40.28532608695652</v>
-      </c>
-      <c r="F163" t="s">
-        <v>203</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -3671,19 +3858,39 @@
         <v>2023</v>
       </c>
       <c r="B164" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C164" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D164">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="E164">
-        <v>18.61413043478261</v>
+        <v>25.11820330969267</v>
       </c>
       <c r="F164" t="s">
-        <v>203</v>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165">
+        <v>2023</v>
+      </c>
+      <c r="B165" t="s">
+        <v>46</v>
+      </c>
+      <c r="C165" t="s">
+        <v>151</v>
+      </c>
+      <c r="D165">
+        <v>341</v>
+      </c>
+      <c r="E165">
+        <v>20.15366430260048</v>
+      </c>
+      <c r="F165" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -3694,16 +3901,16 @@
         <v>46</v>
       </c>
       <c r="C166" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D166">
-        <v>347</v>
+        <v>279</v>
       </c>
       <c r="E166">
-        <v>49.15014164305949</v>
+        <v>16.48936170212766</v>
       </c>
       <c r="F166" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -3714,16 +3921,16 @@
         <v>46</v>
       </c>
       <c r="C167" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D167">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="E167">
-        <v>23.79603399433428</v>
+        <v>16.07565011820331</v>
       </c>
       <c r="F167" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -3734,16 +3941,16 @@
         <v>46</v>
       </c>
       <c r="C168" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D168">
-        <v>103</v>
+        <v>220</v>
       </c>
       <c r="E168">
-        <v>14.58923512747875</v>
+        <v>13.00236406619385</v>
       </c>
       <c r="F168" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -3754,596 +3961,596 @@
         <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D169">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="E169">
-        <v>12.46458923512748</v>
+        <v>9.160756501182032</v>
       </c>
       <c r="F169" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B171" t="s">
         <v>47</v>
       </c>
       <c r="C171" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D171">
-        <v>147</v>
+        <v>286</v>
       </c>
       <c r="E171">
-        <v>44.68085106382978</v>
+        <v>48.22934232715008</v>
       </c>
       <c r="F171" t="s">
-        <v>10</v>
+        <v>265</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B172" t="s">
         <v>47</v>
       </c>
       <c r="C172" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D172">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="E172">
-        <v>31.00303951367781</v>
+        <v>35.7504215851602</v>
       </c>
       <c r="F172" t="s">
-        <v>10</v>
+        <v>265</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B173" t="s">
         <v>47</v>
       </c>
       <c r="C173" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D173">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E173">
-        <v>24.3161094224924</v>
+        <v>16.02023608768971</v>
       </c>
       <c r="F173" t="s">
-        <v>10</v>
+        <v>265</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B175" t="s">
         <v>48</v>
       </c>
       <c r="C175" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D175">
-        <v>710</v>
+        <v>431</v>
       </c>
       <c r="E175">
-        <v>46.64914586070959</v>
+        <v>36.77474402730375</v>
       </c>
       <c r="F175" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B176" t="s">
         <v>48</v>
       </c>
       <c r="C176" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D176">
-        <v>617</v>
+        <v>297</v>
       </c>
       <c r="E176">
-        <v>40.53876478318003</v>
+        <v>25.34129692832764</v>
       </c>
       <c r="F176" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B177" t="s">
         <v>48</v>
       </c>
       <c r="C177" t="s">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="D177">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="E177">
-        <v>12.81208935611038</v>
+        <v>24.31740614334471</v>
       </c>
       <c r="F177" t="s">
-        <v>199</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178">
+        <v>2023</v>
+      </c>
+      <c r="B178" t="s">
+        <v>48</v>
+      </c>
+      <c r="C178" t="s">
+        <v>175</v>
+      </c>
+      <c r="D178">
+        <v>96</v>
+      </c>
+      <c r="E178">
+        <v>8.191126279863481</v>
+      </c>
+      <c r="F178" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B179" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C179" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D179">
-        <v>241</v>
+        <v>63</v>
       </c>
       <c r="E179">
-        <v>49.79338842975206</v>
+        <v>5.375426621160409</v>
       </c>
       <c r="F179" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180">
-        <v>2025</v>
-      </c>
-      <c r="B180" t="s">
-        <v>49</v>
-      </c>
-      <c r="C180" t="s">
-        <v>164</v>
-      </c>
-      <c r="D180">
-        <v>193</v>
-      </c>
-      <c r="E180">
-        <v>39.87603305785124</v>
-      </c>
-      <c r="F180" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B181" t="s">
         <v>49</v>
       </c>
       <c r="C181" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D181">
+        <v>273</v>
+      </c>
+      <c r="E181">
+        <v>45.4242928452579</v>
+      </c>
+      <c r="F181" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182">
+        <v>2023</v>
+      </c>
+      <c r="B182" t="s">
         <v>49</v>
       </c>
-      <c r="E181">
-        <v>10.12396694214876</v>
-      </c>
-      <c r="F181" t="s">
-        <v>203</v>
+      <c r="C182" t="s">
+        <v>178</v>
+      </c>
+      <c r="D182">
+        <v>234</v>
+      </c>
+      <c r="E182">
+        <v>38.9351081530782</v>
+      </c>
+      <c r="F182" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B183" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C183" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D183">
-        <v>6552</v>
+        <v>94</v>
       </c>
       <c r="E183">
-        <v>47.15704620699582</v>
+        <v>15.64059900166389</v>
       </c>
       <c r="F183" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184">
-        <v>2025</v>
-      </c>
-      <c r="B184" t="s">
-        <v>50</v>
-      </c>
-      <c r="C184" t="s">
-        <v>167</v>
-      </c>
-      <c r="D184">
-        <v>4724</v>
-      </c>
-      <c r="E184">
-        <v>34.00028789405498</v>
-      </c>
-      <c r="F184" t="s">
-        <v>199</v>
+        <v>269</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B185" t="s">
         <v>50</v>
       </c>
       <c r="C185" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D185">
-        <v>2618</v>
+        <v>124</v>
       </c>
       <c r="E185">
-        <v>18.84266589894919</v>
+        <v>47.69230769230769</v>
       </c>
       <c r="F185" t="s">
-        <v>199</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186">
+        <v>2023</v>
+      </c>
+      <c r="B186" t="s">
+        <v>50</v>
+      </c>
+      <c r="C186" t="s">
+        <v>181</v>
+      </c>
+      <c r="D186">
+        <v>73</v>
+      </c>
+      <c r="E186">
+        <v>28.07692307692308</v>
+      </c>
+      <c r="F186" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B187" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C187" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D187">
-        <v>9318</v>
+        <v>63</v>
       </c>
       <c r="E187">
-        <v>41.92764578833693</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="F187" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188">
-        <v>2025</v>
-      </c>
-      <c r="B188" t="s">
-        <v>51</v>
-      </c>
-      <c r="C188" t="s">
-        <v>170</v>
-      </c>
-      <c r="D188">
-        <v>8700</v>
-      </c>
-      <c r="E188">
-        <v>39.14686825053996</v>
-      </c>
-      <c r="F188" t="s">
-        <v>204</v>
+        <v>269</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B189" t="s">
         <v>51</v>
       </c>
       <c r="C189" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D189">
-        <v>4206</v>
+        <v>827</v>
       </c>
       <c r="E189">
-        <v>18.92548596112311</v>
+        <v>47.88650839606254</v>
       </c>
       <c r="F189" t="s">
-        <v>204</v>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190">
+        <v>2023</v>
+      </c>
+      <c r="B190" t="s">
+        <v>51</v>
+      </c>
+      <c r="C190" t="s">
+        <v>184</v>
+      </c>
+      <c r="D190">
+        <v>284</v>
+      </c>
+      <c r="E190">
+        <v>16.44470179502026</v>
+      </c>
+      <c r="F190" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B191" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C191" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D191">
-        <v>1473</v>
+        <v>222</v>
       </c>
       <c r="E191">
-        <v>39.30096051227321</v>
+        <v>12.85466126230457</v>
       </c>
       <c r="F191" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B192" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C192" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D192">
-        <v>1297</v>
+        <v>211</v>
       </c>
       <c r="E192">
-        <v>34.6051227321238</v>
+        <v>12.21771858714534</v>
       </c>
       <c r="F192" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B193" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C193" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D193">
-        <v>516</v>
+        <v>183</v>
       </c>
       <c r="E193">
-        <v>13.76734258271078</v>
+        <v>10.59640995946728</v>
       </c>
       <c r="F193" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194">
-        <v>2025</v>
-      </c>
-      <c r="B194" t="s">
-        <v>52</v>
-      </c>
-      <c r="C194" t="s">
-        <v>175</v>
-      </c>
-      <c r="D194">
-        <v>305</v>
-      </c>
-      <c r="E194">
-        <v>8.137673425827108</v>
-      </c>
-      <c r="F194" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B195" t="s">
         <v>52</v>
       </c>
       <c r="C195" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D195">
-        <v>157</v>
+        <v>605</v>
       </c>
       <c r="E195">
-        <v>4.188900747065102</v>
+        <v>41.10054347826087</v>
       </c>
       <c r="F195" t="s">
-        <v>202</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196">
+        <v>2023</v>
+      </c>
+      <c r="B196" t="s">
+        <v>52</v>
+      </c>
+      <c r="C196" t="s">
+        <v>189</v>
+      </c>
+      <c r="D196">
+        <v>593</v>
+      </c>
+      <c r="E196">
+        <v>40.28532608695652</v>
+      </c>
+      <c r="F196" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B197" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C197" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="D197">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="E197">
-        <v>47.83333333333334</v>
+        <v>18.61413043478261</v>
       </c>
       <c r="F197" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198">
-        <v>2025</v>
-      </c>
-      <c r="B198" t="s">
-        <v>53</v>
-      </c>
-      <c r="C198" t="s">
-        <v>177</v>
-      </c>
-      <c r="D198">
-        <v>175</v>
-      </c>
-      <c r="E198">
-        <v>29.16666666666667</v>
-      </c>
-      <c r="F198" t="s">
-        <v>199</v>
+        <v>271</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B199" t="s">
         <v>53</v>
       </c>
       <c r="C199" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D199">
-        <v>138</v>
+        <v>347</v>
       </c>
       <c r="E199">
-        <v>23</v>
+        <v>49.15014164305949</v>
       </c>
       <c r="F199" t="s">
-        <v>199</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200">
+        <v>2023</v>
+      </c>
+      <c r="B200" t="s">
+        <v>53</v>
+      </c>
+      <c r="C200" t="s">
+        <v>192</v>
+      </c>
+      <c r="D200">
+        <v>168</v>
+      </c>
+      <c r="E200">
+        <v>23.79603399433428</v>
+      </c>
+      <c r="F200" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B201" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C201" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D201">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="E201">
-        <v>38.71733966745843</v>
+        <v>14.58923512747875</v>
       </c>
       <c r="F201" t="s">
-        <v>206</v>
+        <v>271</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B202" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C202" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="D202">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="E202">
-        <v>38.00475059382423</v>
+        <v>12.46458923512748</v>
       </c>
       <c r="F202" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203">
-        <v>2025</v>
-      </c>
-      <c r="B203" t="s">
-        <v>54</v>
-      </c>
-      <c r="C203" t="s">
-        <v>181</v>
-      </c>
-      <c r="D203">
-        <v>75</v>
-      </c>
-      <c r="E203">
-        <v>17.81472684085511</v>
-      </c>
-      <c r="F203" t="s">
-        <v>206</v>
+        <v>271</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B204" t="s">
         <v>54</v>
       </c>
       <c r="C204" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D204">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="E204">
-        <v>5.463182897862233</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="F204" t="s">
-        <v>206</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205">
+        <v>2024</v>
+      </c>
+      <c r="B205" t="s">
+        <v>54</v>
+      </c>
+      <c r="C205" t="s">
+        <v>196</v>
+      </c>
+      <c r="D205">
+        <v>102</v>
+      </c>
+      <c r="E205">
+        <v>31.00303951367781</v>
+      </c>
+      <c r="F205" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B206" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C206" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D206">
-        <v>549</v>
+        <v>80</v>
       </c>
       <c r="E206">
-        <v>42.99138606108065</v>
+        <v>24.3161094224924</v>
       </c>
       <c r="F206" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207">
-        <v>2025</v>
-      </c>
-      <c r="B207" t="s">
-        <v>55</v>
-      </c>
-      <c r="C207" t="s">
-        <v>184</v>
-      </c>
-      <c r="D207">
-        <v>445</v>
-      </c>
-      <c r="E207">
-        <v>34.84729835552075</v>
-      </c>
-      <c r="F207" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4354,16 +4561,36 @@
         <v>55</v>
       </c>
       <c r="C208" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D208">
-        <v>283</v>
+        <v>1224</v>
       </c>
       <c r="E208">
-        <v>22.16131558339859</v>
+        <v>28.77291960507758</v>
       </c>
       <c r="F208" t="s">
-        <v>204</v>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209">
+        <v>2025</v>
+      </c>
+      <c r="B209" t="s">
+        <v>55</v>
+      </c>
+      <c r="C209" t="s">
+        <v>199</v>
+      </c>
+      <c r="D209">
+        <v>1052</v>
+      </c>
+      <c r="E209">
+        <v>24.72966619652092</v>
+      </c>
+      <c r="F209" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -4371,19 +4598,19 @@
         <v>2025</v>
       </c>
       <c r="B210" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C210" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D210">
-        <v>123</v>
+        <v>685</v>
       </c>
       <c r="E210">
-        <v>28.21100917431193</v>
+        <v>16.10249177244946</v>
       </c>
       <c r="F210" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4391,19 +4618,19 @@
         <v>2025</v>
       </c>
       <c r="B211" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C211" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="D211">
-        <v>117</v>
+        <v>656</v>
       </c>
       <c r="E211">
-        <v>26.8348623853211</v>
+        <v>15.420780441937</v>
       </c>
       <c r="F211" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -4411,39 +4638,39 @@
         <v>2025</v>
       </c>
       <c r="B212" t="s">
+        <v>55</v>
+      </c>
+      <c r="C212" t="s">
+        <v>202</v>
+      </c>
+      <c r="D212">
+        <v>637</v>
+      </c>
+      <c r="E212">
+        <v>14.97414198401504</v>
+      </c>
+      <c r="F212" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214">
+        <v>2025</v>
+      </c>
+      <c r="B214" t="s">
         <v>56</v>
       </c>
-      <c r="C212" t="s">
-        <v>188</v>
-      </c>
-      <c r="D212">
-        <v>106</v>
-      </c>
-      <c r="E212">
-        <v>24.31192660550459</v>
-      </c>
-      <c r="F212" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213">
-        <v>2025</v>
-      </c>
-      <c r="B213" t="s">
-        <v>56</v>
-      </c>
-      <c r="C213" t="s">
-        <v>189</v>
-      </c>
-      <c r="D213">
-        <v>90</v>
-      </c>
-      <c r="E213">
-        <v>20.64220183486239</v>
-      </c>
-      <c r="F213" t="s">
-        <v>204</v>
+      <c r="C214" t="s">
+        <v>203</v>
+      </c>
+      <c r="D214">
+        <v>3817</v>
+      </c>
+      <c r="E214">
+        <v>39.10860655737705</v>
+      </c>
+      <c r="F214" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -4451,19 +4678,19 @@
         <v>2025</v>
       </c>
       <c r="B215" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C215" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D215">
-        <v>195</v>
+        <v>3272</v>
       </c>
       <c r="E215">
-        <v>45.03464203233256</v>
+        <v>33.52459016393443</v>
       </c>
       <c r="F215" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -4471,39 +4698,39 @@
         <v>2025</v>
       </c>
       <c r="B216" t="s">
+        <v>56</v>
+      </c>
+      <c r="C216" t="s">
+        <v>205</v>
+      </c>
+      <c r="D216">
+        <v>2671</v>
+      </c>
+      <c r="E216">
+        <v>27.36680327868852</v>
+      </c>
+      <c r="F216" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218">
+        <v>2025</v>
+      </c>
+      <c r="B218" t="s">
         <v>57</v>
       </c>
-      <c r="C216" t="s">
-        <v>191</v>
-      </c>
-      <c r="D216">
-        <v>162</v>
-      </c>
-      <c r="E216">
-        <v>37.41339491916859</v>
-      </c>
-      <c r="F216" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217">
-        <v>2025</v>
-      </c>
-      <c r="B217" t="s">
-        <v>57</v>
-      </c>
-      <c r="C217" t="s">
-        <v>192</v>
-      </c>
-      <c r="D217">
-        <v>76</v>
-      </c>
-      <c r="E217">
-        <v>17.55196304849884</v>
-      </c>
-      <c r="F217" t="s">
-        <v>204</v>
+      <c r="C218" t="s">
+        <v>206</v>
+      </c>
+      <c r="D218">
+        <v>710</v>
+      </c>
+      <c r="E218">
+        <v>46.64914586070959</v>
+      </c>
+      <c r="F218" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -4511,19 +4738,19 @@
         <v>2025</v>
       </c>
       <c r="B219" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C219" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D219">
-        <v>315</v>
+        <v>617</v>
       </c>
       <c r="E219">
-        <v>43.09165526675787</v>
+        <v>40.53876478318003</v>
       </c>
       <c r="F219" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -4531,39 +4758,1119 @@
         <v>2025</v>
       </c>
       <c r="B220" t="s">
+        <v>57</v>
+      </c>
+      <c r="C220" t="s">
+        <v>104</v>
+      </c>
+      <c r="D220">
+        <v>195</v>
+      </c>
+      <c r="E220">
+        <v>12.81208935611038</v>
+      </c>
+      <c r="F220" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222">
+        <v>2025</v>
+      </c>
+      <c r="B222" t="s">
         <v>58</v>
       </c>
-      <c r="C220" t="s">
-        <v>194</v>
-      </c>
-      <c r="D220">
+      <c r="C222" t="s">
+        <v>208</v>
+      </c>
+      <c r="D222">
+        <v>241</v>
+      </c>
+      <c r="E222">
+        <v>49.79338842975206</v>
+      </c>
+      <c r="F222" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223">
+        <v>2025</v>
+      </c>
+      <c r="B223" t="s">
+        <v>58</v>
+      </c>
+      <c r="C223" t="s">
+        <v>209</v>
+      </c>
+      <c r="D223">
+        <v>193</v>
+      </c>
+      <c r="E223">
+        <v>39.87603305785124</v>
+      </c>
+      <c r="F223" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224">
+        <v>2025</v>
+      </c>
+      <c r="B224" t="s">
+        <v>58</v>
+      </c>
+      <c r="C224" t="s">
+        <v>210</v>
+      </c>
+      <c r="D224">
+        <v>49</v>
+      </c>
+      <c r="E224">
+        <v>10.12396694214876</v>
+      </c>
+      <c r="F224" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226">
+        <v>2025</v>
+      </c>
+      <c r="B226" t="s">
+        <v>59</v>
+      </c>
+      <c r="C226" t="s">
+        <v>211</v>
+      </c>
+      <c r="D226">
+        <v>373</v>
+      </c>
+      <c r="E226">
+        <v>36.39024390243902</v>
+      </c>
+      <c r="F226" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227">
+        <v>2025</v>
+      </c>
+      <c r="B227" t="s">
+        <v>59</v>
+      </c>
+      <c r="C227" t="s">
+        <v>212</v>
+      </c>
+      <c r="D227">
+        <v>225</v>
+      </c>
+      <c r="E227">
+        <v>21.95121951219512</v>
+      </c>
+      <c r="F227" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228">
+        <v>2025</v>
+      </c>
+      <c r="B228" t="s">
+        <v>59</v>
+      </c>
+      <c r="C228" t="s">
+        <v>213</v>
+      </c>
+      <c r="D228">
+        <v>206</v>
+      </c>
+      <c r="E228">
+        <v>20.09756097560976</v>
+      </c>
+      <c r="F228" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229">
+        <v>2025</v>
+      </c>
+      <c r="B229" t="s">
+        <v>59</v>
+      </c>
+      <c r="C229" t="s">
+        <v>214</v>
+      </c>
+      <c r="D229">
+        <v>140</v>
+      </c>
+      <c r="E229">
+        <v>13.65853658536586</v>
+      </c>
+      <c r="F229" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230">
+        <v>2025</v>
+      </c>
+      <c r="B230" t="s">
+        <v>59</v>
+      </c>
+      <c r="C230" t="s">
+        <v>215</v>
+      </c>
+      <c r="D230">
+        <v>81</v>
+      </c>
+      <c r="E230">
+        <v>7.902439024390244</v>
+      </c>
+      <c r="F230" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232">
+        <v>2025</v>
+      </c>
+      <c r="B232" t="s">
+        <v>60</v>
+      </c>
+      <c r="C232" t="s">
+        <v>216</v>
+      </c>
+      <c r="D232">
+        <v>6552</v>
+      </c>
+      <c r="E232">
+        <v>47.15704620699582</v>
+      </c>
+      <c r="F232" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233">
+        <v>2025</v>
+      </c>
+      <c r="B233" t="s">
+        <v>60</v>
+      </c>
+      <c r="C233" t="s">
+        <v>217</v>
+      </c>
+      <c r="D233">
+        <v>4724</v>
+      </c>
+      <c r="E233">
+        <v>34.00028789405498</v>
+      </c>
+      <c r="F233" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234">
+        <v>2025</v>
+      </c>
+      <c r="B234" t="s">
+        <v>60</v>
+      </c>
+      <c r="C234" t="s">
+        <v>218</v>
+      </c>
+      <c r="D234">
+        <v>2618</v>
+      </c>
+      <c r="E234">
+        <v>18.84266589894919</v>
+      </c>
+      <c r="F234" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236">
+        <v>2025</v>
+      </c>
+      <c r="B236" t="s">
+        <v>61</v>
+      </c>
+      <c r="C236" t="s">
+        <v>219</v>
+      </c>
+      <c r="D236">
+        <v>5832</v>
+      </c>
+      <c r="E236">
+        <v>37.28423475258919</v>
+      </c>
+      <c r="F236" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237">
+        <v>2025</v>
+      </c>
+      <c r="B237" t="s">
+        <v>61</v>
+      </c>
+      <c r="C237" t="s">
+        <v>220</v>
+      </c>
+      <c r="D237">
+        <v>4950</v>
+      </c>
+      <c r="E237">
+        <v>31.64556962025317</v>
+      </c>
+      <c r="F237" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238">
+        <v>2025</v>
+      </c>
+      <c r="B238" t="s">
+        <v>61</v>
+      </c>
+      <c r="C238" t="s">
+        <v>221</v>
+      </c>
+      <c r="D238">
+        <v>4834</v>
+      </c>
+      <c r="E238">
+        <v>30.90397647359673</v>
+      </c>
+      <c r="F238" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240">
+        <v>2025</v>
+      </c>
+      <c r="B240" t="s">
+        <v>62</v>
+      </c>
+      <c r="C240" t="s">
+        <v>222</v>
+      </c>
+      <c r="D240">
+        <v>9318</v>
+      </c>
+      <c r="E240">
+        <v>41.92764578833693</v>
+      </c>
+      <c r="F240" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241">
+        <v>2025</v>
+      </c>
+      <c r="B241" t="s">
+        <v>62</v>
+      </c>
+      <c r="C241" t="s">
+        <v>223</v>
+      </c>
+      <c r="D241">
+        <v>8700</v>
+      </c>
+      <c r="E241">
+        <v>39.14686825053996</v>
+      </c>
+      <c r="F241" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242">
+        <v>2025</v>
+      </c>
+      <c r="B242" t="s">
+        <v>62</v>
+      </c>
+      <c r="C242" t="s">
+        <v>224</v>
+      </c>
+      <c r="D242">
+        <v>4206</v>
+      </c>
+      <c r="E242">
+        <v>18.92548596112311</v>
+      </c>
+      <c r="F242" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244">
+        <v>2025</v>
+      </c>
+      <c r="B244" t="s">
+        <v>63</v>
+      </c>
+      <c r="C244" t="s">
+        <v>225</v>
+      </c>
+      <c r="D244">
+        <v>1473</v>
+      </c>
+      <c r="E244">
+        <v>39.30096051227321</v>
+      </c>
+      <c r="F244" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245">
+        <v>2025</v>
+      </c>
+      <c r="B245" t="s">
+        <v>63</v>
+      </c>
+      <c r="C245" t="s">
+        <v>226</v>
+      </c>
+      <c r="D245">
+        <v>1297</v>
+      </c>
+      <c r="E245">
+        <v>34.6051227321238</v>
+      </c>
+      <c r="F245" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246">
+        <v>2025</v>
+      </c>
+      <c r="B246" t="s">
+        <v>63</v>
+      </c>
+      <c r="C246" t="s">
+        <v>227</v>
+      </c>
+      <c r="D246">
+        <v>516</v>
+      </c>
+      <c r="E246">
+        <v>13.76734258271078</v>
+      </c>
+      <c r="F246" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247">
+        <v>2025</v>
+      </c>
+      <c r="B247" t="s">
+        <v>63</v>
+      </c>
+      <c r="C247" t="s">
+        <v>228</v>
+      </c>
+      <c r="D247">
+        <v>305</v>
+      </c>
+      <c r="E247">
+        <v>8.137673425827108</v>
+      </c>
+      <c r="F247" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248">
+        <v>2025</v>
+      </c>
+      <c r="B248" t="s">
+        <v>63</v>
+      </c>
+      <c r="C248" t="s">
+        <v>229</v>
+      </c>
+      <c r="D248">
+        <v>157</v>
+      </c>
+      <c r="E248">
+        <v>4.188900747065102</v>
+      </c>
+      <c r="F248" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250">
+        <v>2025</v>
+      </c>
+      <c r="B250" t="s">
+        <v>64</v>
+      </c>
+      <c r="C250" t="s">
+        <v>230</v>
+      </c>
+      <c r="D250">
+        <v>854</v>
+      </c>
+      <c r="E250">
+        <v>47.52365052865888</v>
+      </c>
+      <c r="F250" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251">
+        <v>2025</v>
+      </c>
+      <c r="B251" t="s">
+        <v>64</v>
+      </c>
+      <c r="C251" t="s">
+        <v>231</v>
+      </c>
+      <c r="D251">
+        <v>764</v>
+      </c>
+      <c r="E251">
+        <v>42.51530328324986</v>
+      </c>
+      <c r="F251" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252">
+        <v>2025</v>
+      </c>
+      <c r="B252" t="s">
+        <v>64</v>
+      </c>
+      <c r="C252" t="s">
+        <v>232</v>
+      </c>
+      <c r="D252">
+        <v>175</v>
+      </c>
+      <c r="E252">
+        <v>9.738452977184195</v>
+      </c>
+      <c r="F252" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254">
+        <v>2025</v>
+      </c>
+      <c r="B254" t="s">
+        <v>65</v>
+      </c>
+      <c r="C254" t="s">
+        <v>233</v>
+      </c>
+      <c r="D254">
+        <v>162</v>
+      </c>
+      <c r="E254">
+        <v>45.2513966480447</v>
+      </c>
+      <c r="F254" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255">
+        <v>2025</v>
+      </c>
+      <c r="B255" t="s">
+        <v>65</v>
+      </c>
+      <c r="C255" t="s">
+        <v>234</v>
+      </c>
+      <c r="D255">
+        <v>156</v>
+      </c>
+      <c r="E255">
+        <v>43.5754189944134</v>
+      </c>
+      <c r="F255" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256">
+        <v>2025</v>
+      </c>
+      <c r="B256" t="s">
+        <v>65</v>
+      </c>
+      <c r="C256" t="s">
+        <v>235</v>
+      </c>
+      <c r="D256">
+        <v>40</v>
+      </c>
+      <c r="E256">
+        <v>11.1731843575419</v>
+      </c>
+      <c r="F256" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258">
+        <v>2025</v>
+      </c>
+      <c r="B258" t="s">
+        <v>66</v>
+      </c>
+      <c r="C258" t="s">
+        <v>236</v>
+      </c>
+      <c r="D258">
+        <v>11367</v>
+      </c>
+      <c r="E258">
+        <v>45.69280861840254</v>
+      </c>
+      <c r="F258" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259">
+        <v>2025</v>
+      </c>
+      <c r="B259" t="s">
+        <v>66</v>
+      </c>
+      <c r="C259" t="s">
+        <v>237</v>
+      </c>
+      <c r="D259">
+        <v>8188</v>
+      </c>
+      <c r="E259">
+        <v>32.91393656791413</v>
+      </c>
+      <c r="F259" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260">
+        <v>2025</v>
+      </c>
+      <c r="B260" t="s">
+        <v>66</v>
+      </c>
+      <c r="C260" t="s">
+        <v>238</v>
+      </c>
+      <c r="D260">
+        <v>5322</v>
+      </c>
+      <c r="E260">
+        <v>21.39325481368332</v>
+      </c>
+      <c r="F260" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262">
+        <v>2025</v>
+      </c>
+      <c r="B262" t="s">
+        <v>67</v>
+      </c>
+      <c r="C262" t="s">
+        <v>170</v>
+      </c>
+      <c r="D262">
+        <v>287</v>
+      </c>
+      <c r="E262">
+        <v>47.83333333333334</v>
+      </c>
+      <c r="F262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263">
+        <v>2025</v>
+      </c>
+      <c r="B263" t="s">
+        <v>67</v>
+      </c>
+      <c r="C263" t="s">
+        <v>239</v>
+      </c>
+      <c r="D263">
+        <v>175</v>
+      </c>
+      <c r="E263">
+        <v>29.16666666666667</v>
+      </c>
+      <c r="F263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264">
+        <v>2025</v>
+      </c>
+      <c r="B264" t="s">
+        <v>67</v>
+      </c>
+      <c r="C264" t="s">
+        <v>240</v>
+      </c>
+      <c r="D264">
+        <v>138</v>
+      </c>
+      <c r="E264">
+        <v>23</v>
+      </c>
+      <c r="F264" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266">
+        <v>2025</v>
+      </c>
+      <c r="B266" t="s">
+        <v>68</v>
+      </c>
+      <c r="C266" t="s">
+        <v>241</v>
+      </c>
+      <c r="D266">
+        <v>163</v>
+      </c>
+      <c r="E266">
+        <v>38.71733966745843</v>
+      </c>
+      <c r="F266" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267">
+        <v>2025</v>
+      </c>
+      <c r="B267" t="s">
+        <v>68</v>
+      </c>
+      <c r="C267" t="s">
+        <v>242</v>
+      </c>
+      <c r="D267">
+        <v>160</v>
+      </c>
+      <c r="E267">
+        <v>38.00475059382423</v>
+      </c>
+      <c r="F267" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268">
+        <v>2025</v>
+      </c>
+      <c r="B268" t="s">
+        <v>68</v>
+      </c>
+      <c r="C268" t="s">
+        <v>243</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268">
+        <v>17.81472684085511</v>
+      </c>
+      <c r="F268" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269">
+        <v>2025</v>
+      </c>
+      <c r="B269" t="s">
+        <v>68</v>
+      </c>
+      <c r="C269" t="s">
+        <v>244</v>
+      </c>
+      <c r="D269">
+        <v>23</v>
+      </c>
+      <c r="E269">
+        <v>5.463182897862233</v>
+      </c>
+      <c r="F269" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271">
+        <v>2025</v>
+      </c>
+      <c r="B271" t="s">
+        <v>69</v>
+      </c>
+      <c r="C271" t="s">
+        <v>245</v>
+      </c>
+      <c r="D271">
+        <v>104</v>
+      </c>
+      <c r="E271">
+        <v>35.37414965986395</v>
+      </c>
+      <c r="F271" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272">
+        <v>2025</v>
+      </c>
+      <c r="B272" t="s">
+        <v>69</v>
+      </c>
+      <c r="C272" t="s">
+        <v>246</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272">
+        <v>26.87074829931973</v>
+      </c>
+      <c r="F272" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273">
+        <v>2025</v>
+      </c>
+      <c r="B273" t="s">
+        <v>69</v>
+      </c>
+      <c r="C273" t="s">
         <v>247</v>
       </c>
-      <c r="E220">
+      <c r="D273">
+        <v>78</v>
+      </c>
+      <c r="E273">
+        <v>26.53061224489796</v>
+      </c>
+      <c r="F273" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274">
+        <v>2025</v>
+      </c>
+      <c r="B274" t="s">
+        <v>69</v>
+      </c>
+      <c r="C274" t="s">
+        <v>248</v>
+      </c>
+      <c r="D274">
+        <v>32</v>
+      </c>
+      <c r="E274">
+        <v>10.8843537414966</v>
+      </c>
+      <c r="F274" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276">
+        <v>2025</v>
+      </c>
+      <c r="B276" t="s">
+        <v>70</v>
+      </c>
+      <c r="C276" t="s">
+        <v>249</v>
+      </c>
+      <c r="D276">
+        <v>549</v>
+      </c>
+      <c r="E276">
+        <v>42.99138606108065</v>
+      </c>
+      <c r="F276" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277">
+        <v>2025</v>
+      </c>
+      <c r="B277" t="s">
+        <v>70</v>
+      </c>
+      <c r="C277" t="s">
+        <v>250</v>
+      </c>
+      <c r="D277">
+        <v>445</v>
+      </c>
+      <c r="E277">
+        <v>34.84729835552075</v>
+      </c>
+      <c r="F277" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278">
+        <v>2025</v>
+      </c>
+      <c r="B278" t="s">
+        <v>70</v>
+      </c>
+      <c r="C278" t="s">
+        <v>251</v>
+      </c>
+      <c r="D278">
+        <v>283</v>
+      </c>
+      <c r="E278">
+        <v>22.16131558339859</v>
+      </c>
+      <c r="F278" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280">
+        <v>2025</v>
+      </c>
+      <c r="B280" t="s">
+        <v>71</v>
+      </c>
+      <c r="C280" t="s">
+        <v>252</v>
+      </c>
+      <c r="D280">
+        <v>123</v>
+      </c>
+      <c r="E280">
+        <v>28.21100917431193</v>
+      </c>
+      <c r="F280" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281">
+        <v>2025</v>
+      </c>
+      <c r="B281" t="s">
+        <v>71</v>
+      </c>
+      <c r="C281" t="s">
+        <v>253</v>
+      </c>
+      <c r="D281">
+        <v>117</v>
+      </c>
+      <c r="E281">
+        <v>26.8348623853211</v>
+      </c>
+      <c r="F281" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282">
+        <v>2025</v>
+      </c>
+      <c r="B282" t="s">
+        <v>71</v>
+      </c>
+      <c r="C282" t="s">
+        <v>254</v>
+      </c>
+      <c r="D282">
+        <v>106</v>
+      </c>
+      <c r="E282">
+        <v>24.31192660550459</v>
+      </c>
+      <c r="F282" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283">
+        <v>2025</v>
+      </c>
+      <c r="B283" t="s">
+        <v>71</v>
+      </c>
+      <c r="C283" t="s">
+        <v>255</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283">
+        <v>20.64220183486239</v>
+      </c>
+      <c r="F283" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285">
+        <v>2025</v>
+      </c>
+      <c r="B285" t="s">
+        <v>72</v>
+      </c>
+      <c r="C285" t="s">
+        <v>256</v>
+      </c>
+      <c r="D285">
+        <v>195</v>
+      </c>
+      <c r="E285">
+        <v>45.03464203233256</v>
+      </c>
+      <c r="F285" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286">
+        <v>2025</v>
+      </c>
+      <c r="B286" t="s">
+        <v>72</v>
+      </c>
+      <c r="C286" t="s">
+        <v>257</v>
+      </c>
+      <c r="D286">
+        <v>162</v>
+      </c>
+      <c r="E286">
+        <v>37.41339491916859</v>
+      </c>
+      <c r="F286" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287">
+        <v>2025</v>
+      </c>
+      <c r="B287" t="s">
+        <v>72</v>
+      </c>
+      <c r="C287" t="s">
+        <v>258</v>
+      </c>
+      <c r="D287">
+        <v>76</v>
+      </c>
+      <c r="E287">
+        <v>17.55196304849884</v>
+      </c>
+      <c r="F287" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289">
+        <v>2025</v>
+      </c>
+      <c r="B289" t="s">
+        <v>73</v>
+      </c>
+      <c r="C289" t="s">
+        <v>259</v>
+      </c>
+      <c r="D289">
+        <v>315</v>
+      </c>
+      <c r="E289">
+        <v>43.09165526675787</v>
+      </c>
+      <c r="F289" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290">
+        <v>2025</v>
+      </c>
+      <c r="B290" t="s">
+        <v>73</v>
+      </c>
+      <c r="C290" t="s">
+        <v>260</v>
+      </c>
+      <c r="D290">
+        <v>247</v>
+      </c>
+      <c r="E290">
         <v>33.78932968536252</v>
       </c>
-      <c r="F220" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221">
-        <v>2025</v>
-      </c>
-      <c r="B221" t="s">
-        <v>58</v>
-      </c>
-      <c r="C221" t="s">
-        <v>195</v>
-      </c>
-      <c r="D221">
+      <c r="F290" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291">
+        <v>2025</v>
+      </c>
+      <c r="B291" t="s">
+        <v>73</v>
+      </c>
+      <c r="C291" t="s">
+        <v>261</v>
+      </c>
+      <c r="D291">
         <v>169</v>
       </c>
-      <c r="E221">
+      <c r="E291">
         <v>23.11901504787962</v>
       </c>
-      <c r="F221" t="s">
-        <v>198</v>
+      <c r="F291" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="285">
   <si>
     <t>Year</t>
   </si>
@@ -71,6 +71,12 @@
     <t>DEM Mayor-Swoyersville Borough (4 Year Term)</t>
   </si>
   <si>
+    <t>Magisterial District Judge 38-1-15 Dem</t>
+  </si>
+  <si>
+    <t>New Hanover 2 Inspector of Election Rep</t>
+  </si>
+  <si>
     <t>REP CONSTABLE LIGONIER</t>
   </si>
   <si>
@@ -197,9 +203,6 @@
     <t>REP EAST HUNTINGDON TOWNSHIP Supervisor - 6 Year Term</t>
   </si>
   <si>
-    <t>REP JUDGE OF THE COURT OF COMMON  PLEAS</t>
-  </si>
-  <si>
     <t>REP JUDGE OF THE COURT OF COMMON PLEAS - 6TH JUDICIAL DISTRICT 10 YEAR TERM</t>
   </si>
   <si>
@@ -317,6 +320,27 @@
     <t>ESPY WILLIAMS</t>
   </si>
   <si>
+    <t>DENISE ASHE</t>
+  </si>
+  <si>
+    <t>AARON HOLSTON</t>
+  </si>
+  <si>
+    <t>FRANCIS LAWRENCE JR</t>
+  </si>
+  <si>
+    <t>MONICA MATHEWS REYNOLDS</t>
+  </si>
+  <si>
+    <t>TAMMY WAGNER</t>
+  </si>
+  <si>
+    <t>ANITA KRATZ</t>
+  </si>
+  <si>
+    <t>NICOLE ORENOTSKY</t>
+  </si>
+  <si>
     <t>SHAWN MILLER</t>
   </si>
   <si>
@@ -819,6 +843,9 @@
   </si>
   <si>
     <t>Luzerne County (Wilkes-Barre + boroughs + townships)</t>
+  </si>
+  <si>
+    <t>Montgomery County (Norristown + Philly suburbs)</t>
   </si>
   <si>
     <t>Westmoreland County (city + boroughs + townships)</t>
@@ -1290,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F291"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1321,7 +1348,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2">
         <v>3420</v>
@@ -1330,7 +1357,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1341,7 +1368,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3">
         <v>2391</v>
@@ -1350,7 +1377,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1361,7 +1388,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4">
         <v>2184</v>
@@ -1370,7 +1397,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1381,7 +1408,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>572</v>
@@ -1390,7 +1417,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1401,7 +1428,7 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7">
         <v>380</v>
@@ -1410,7 +1437,7 @@
         <v>31.25</v>
       </c>
       <c r="F7" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1421,7 +1448,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>264</v>
@@ -1430,7 +1457,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1441,7 +1468,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10">
         <v>177</v>
@@ -1450,7 +1477,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F10" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1461,7 +1488,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11">
         <v>141</v>
@@ -1470,7 +1497,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F11" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1481,7 +1508,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12">
         <v>81</v>
@@ -1490,7 +1517,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F12" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1501,7 +1528,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D13">
         <v>44</v>
@@ -1510,7 +1537,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F13" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1521,7 +1548,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15">
         <v>1471</v>
@@ -1530,7 +1557,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F15" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1541,7 +1568,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D16">
         <v>1247</v>
@@ -1550,7 +1577,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F16" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1561,7 +1588,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D17">
         <v>616</v>
@@ -1570,7 +1597,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F17" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1581,7 +1608,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D19">
         <v>1183</v>
@@ -1590,7 +1617,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F19" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1601,7 +1628,7 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D20">
         <v>1177</v>
@@ -1610,7 +1637,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F20" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1621,7 +1648,7 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21">
         <v>373</v>
@@ -1630,7 +1657,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F21" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1641,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D22">
         <v>270</v>
@@ -1650,7 +1677,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F22" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1661,7 +1688,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24">
         <v>2064</v>
@@ -1670,7 +1697,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F24" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1681,7 +1708,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D25">
         <v>1942</v>
@@ -1690,7 +1717,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F25" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1701,7 +1728,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D26">
         <v>1927</v>
@@ -1710,7 +1737,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F26" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1721,7 +1748,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27">
         <v>1817</v>
@@ -1730,7 +1757,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F27" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1741,7 +1768,7 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D29">
         <v>237</v>
@@ -1750,7 +1777,7 @@
         <v>32.20108695652174</v>
       </c>
       <c r="F29" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1761,7 +1788,7 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D30">
         <v>234</v>
@@ -1770,7 +1797,7 @@
         <v>31.79347826086957</v>
       </c>
       <c r="F30" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1781,7 +1808,7 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D31">
         <v>148</v>
@@ -1790,7 +1817,7 @@
         <v>20.10869565217391</v>
       </c>
       <c r="F31" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1801,7 +1828,7 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D32">
         <v>90</v>
@@ -1810,7 +1837,7 @@
         <v>12.22826086956522</v>
       </c>
       <c r="F32" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1821,7 +1848,7 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>27</v>
@@ -1830,7 +1857,7 @@
         <v>3.668478260869565</v>
       </c>
       <c r="F33" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1841,16 +1868,16 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D35">
-        <v>588</v>
+        <v>186</v>
       </c>
       <c r="E35">
-        <v>48.83720930232558</v>
+        <v>40</v>
       </c>
       <c r="F35" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1861,16 +1888,16 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D36">
-        <v>379</v>
+        <v>96</v>
       </c>
       <c r="E36">
-        <v>31.47840531561462</v>
+        <v>20.64516129032258</v>
       </c>
       <c r="F36" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1881,36 +1908,36 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D37">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="E37">
-        <v>19.6843853820598</v>
+        <v>20.43010752688172</v>
       </c>
       <c r="F37" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>2021</v>
-      </c>
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39">
-        <v>522</v>
-      </c>
-      <c r="E39">
-        <v>48.33333333333334</v>
-      </c>
-      <c r="F39" t="s">
-        <v>265</v>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>2021</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38">
+        <v>88</v>
+      </c>
+      <c r="E38">
+        <v>18.9247311827957</v>
+      </c>
+      <c r="F38" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1921,16 +1948,16 @@
         <v>19</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D40">
-        <v>331</v>
+        <v>154</v>
       </c>
       <c r="E40">
-        <v>30.64814814814815</v>
+        <v>39.58868894601542</v>
       </c>
       <c r="F40" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1941,36 +1968,36 @@
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D41">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="E41">
-        <v>21.01851851851852</v>
+        <v>37.01799485861182</v>
       </c>
       <c r="F41" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>2021</v>
-      </c>
-      <c r="B43" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43">
-        <v>4922</v>
-      </c>
-      <c r="E43">
-        <v>41.68713475057169</v>
-      </c>
-      <c r="F43" t="s">
-        <v>262</v>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>2021</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42">
+        <v>91</v>
+      </c>
+      <c r="E42">
+        <v>23.39331619537275</v>
+      </c>
+      <c r="F42" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1981,16 +2008,16 @@
         <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="D44">
-        <v>4820</v>
+        <v>588</v>
       </c>
       <c r="E44">
-        <v>40.82324045058016</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="F44" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2001,36 +2028,36 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="D45">
-        <v>2065</v>
+        <v>379</v>
       </c>
       <c r="E45">
-        <v>17.48962479884814</v>
+        <v>31.47840531561462</v>
       </c>
       <c r="F45" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>2021</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47">
-        <v>1281</v>
-      </c>
-      <c r="E47">
-        <v>43.88489208633094</v>
-      </c>
-      <c r="F47" t="s">
-        <v>268</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>2021</v>
+      </c>
+      <c r="B46" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46">
+        <v>237</v>
+      </c>
+      <c r="E46">
+        <v>19.6843853820598</v>
+      </c>
+      <c r="F46" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2041,16 +2068,16 @@
         <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D48">
-        <v>924</v>
+        <v>522</v>
       </c>
       <c r="E48">
-        <v>31.6546762589928</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="F48" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2061,36 +2088,36 @@
         <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D49">
-        <v>714</v>
+        <v>331</v>
       </c>
       <c r="E49">
-        <v>24.46043165467626</v>
+        <v>30.64814814814815</v>
       </c>
       <c r="F49" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>2021</v>
-      </c>
-      <c r="B51" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" t="s">
-        <v>109</v>
-      </c>
-      <c r="D51">
-        <v>999</v>
-      </c>
-      <c r="E51">
-        <v>49.47994056463596</v>
-      </c>
-      <c r="F51" t="s">
-        <v>268</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>2021</v>
+      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50">
+        <v>227</v>
+      </c>
+      <c r="E50">
+        <v>21.01851851851852</v>
+      </c>
+      <c r="F50" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2101,16 +2128,16 @@
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D52">
-        <v>629</v>
+        <v>4922</v>
       </c>
       <c r="E52">
-        <v>31.15403665180783</v>
+        <v>41.68713475057169</v>
       </c>
       <c r="F52" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2121,36 +2148,36 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D53">
-        <v>391</v>
+        <v>4820</v>
       </c>
       <c r="E53">
-        <v>19.36602278355622</v>
+        <v>40.82324045058016</v>
       </c>
       <c r="F53" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>2021</v>
-      </c>
-      <c r="B55" t="s">
-        <v>23</v>
-      </c>
-      <c r="C55" t="s">
-        <v>77</v>
-      </c>
-      <c r="D55">
-        <v>1779</v>
-      </c>
-      <c r="E55">
-        <v>46.82811266122664</v>
-      </c>
-      <c r="F55" t="s">
-        <v>262</v>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>2021</v>
+      </c>
+      <c r="B54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54">
+        <v>2065</v>
+      </c>
+      <c r="E54">
+        <v>17.48962479884814</v>
+      </c>
+      <c r="F54" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2161,16 +2188,16 @@
         <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="D56">
-        <v>1349</v>
+        <v>1281</v>
       </c>
       <c r="E56">
-        <v>35.50934456435904</v>
+        <v>43.88489208633094</v>
       </c>
       <c r="F56" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2181,36 +2208,36 @@
         <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="D57">
-        <v>671</v>
+        <v>924</v>
       </c>
       <c r="E57">
-        <v>17.66254277441432</v>
+        <v>31.6546762589928</v>
       </c>
       <c r="F57" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>2021</v>
-      </c>
-      <c r="B59" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" t="s">
-        <v>81</v>
-      </c>
-      <c r="D59">
-        <v>253</v>
-      </c>
-      <c r="E59">
-        <v>37.09677419354838</v>
-      </c>
-      <c r="F59" t="s">
-        <v>263</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>2021</v>
+      </c>
+      <c r="B58" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58">
+        <v>714</v>
+      </c>
+      <c r="E58">
+        <v>24.46043165467626</v>
+      </c>
+      <c r="F58" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2221,16 +2248,16 @@
         <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="D60">
-        <v>224</v>
+        <v>999</v>
       </c>
       <c r="E60">
-        <v>32.84457478005865</v>
+        <v>49.47994056463596</v>
       </c>
       <c r="F60" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2241,16 +2268,16 @@
         <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61">
-        <v>122</v>
+        <v>629</v>
       </c>
       <c r="E61">
-        <v>17.88856304985337</v>
+        <v>31.15403665180783</v>
       </c>
       <c r="F61" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2261,36 +2288,36 @@
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="D62">
-        <v>60</v>
+        <v>391</v>
       </c>
       <c r="E62">
-        <v>8.797653958944283</v>
+        <v>19.36602278355622</v>
       </c>
       <c r="F62" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>2021</v>
-      </c>
-      <c r="B63" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" t="s">
-        <v>80</v>
-      </c>
-      <c r="D63">
-        <v>23</v>
-      </c>
-      <c r="E63">
-        <v>3.372434017595308</v>
-      </c>
-      <c r="F63" t="s">
-        <v>263</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>2021</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>78</v>
+      </c>
+      <c r="D64">
+        <v>1779</v>
+      </c>
+      <c r="E64">
+        <v>46.82811266122664</v>
+      </c>
+      <c r="F64" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2301,16 +2328,16 @@
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D65">
-        <v>917</v>
+        <v>1349</v>
       </c>
       <c r="E65">
-        <v>36.31683168316832</v>
+        <v>35.50934456435904</v>
       </c>
       <c r="F65" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2321,36 +2348,16 @@
         <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D66">
-        <v>706</v>
+        <v>671</v>
       </c>
       <c r="E66">
-        <v>27.96039603960396</v>
+        <v>17.66254277441432</v>
       </c>
       <c r="F66" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>2021</v>
-      </c>
-      <c r="B67" t="s">
-        <v>25</v>
-      </c>
-      <c r="C67" t="s">
-        <v>87</v>
-      </c>
-      <c r="D67">
-        <v>578</v>
-      </c>
-      <c r="E67">
-        <v>22.89108910891089</v>
-      </c>
-      <c r="F67" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2358,19 +2365,39 @@
         <v>2021</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D68">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="E68">
-        <v>12.83168316831683</v>
+        <v>37.09677419354838</v>
       </c>
       <c r="F68" t="s">
-        <v>265</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>2021</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69">
+        <v>224</v>
+      </c>
+      <c r="E69">
+        <v>32.84457478005865</v>
+      </c>
+      <c r="F69" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2381,16 +2408,16 @@
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D70">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="E70">
-        <v>41.38888888888889</v>
+        <v>17.88856304985337</v>
       </c>
       <c r="F70" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2401,16 +2428,16 @@
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D71">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="E71">
-        <v>31.38888888888889</v>
+        <v>8.797653958944283</v>
       </c>
       <c r="F71" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2421,36 +2448,36 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D72">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="E72">
-        <v>16.38888888888889</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="F72" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>2021</v>
-      </c>
-      <c r="B73" t="s">
-        <v>26</v>
-      </c>
-      <c r="C73" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73">
-        <v>39</v>
-      </c>
-      <c r="E73">
-        <v>10.83333333333333</v>
-      </c>
-      <c r="F73" t="s">
-        <v>268</v>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>2021</v>
+      </c>
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" t="s">
+        <v>90</v>
+      </c>
+      <c r="D74">
+        <v>917</v>
+      </c>
+      <c r="E74">
+        <v>36.31683168316832</v>
+      </c>
+      <c r="F74" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2461,16 +2488,16 @@
         <v>27</v>
       </c>
       <c r="C75" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="D75">
-        <v>179</v>
+        <v>706</v>
       </c>
       <c r="E75">
-        <v>45.31645569620253</v>
+        <v>27.96039603960396</v>
       </c>
       <c r="F75" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2481,16 +2508,16 @@
         <v>27</v>
       </c>
       <c r="C76" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D76">
-        <v>110</v>
+        <v>578</v>
       </c>
       <c r="E76">
-        <v>27.84810126582278</v>
+        <v>22.89108910891089</v>
       </c>
       <c r="F76" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2501,16 +2528,16 @@
         <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="D77">
-        <v>106</v>
+        <v>324</v>
       </c>
       <c r="E77">
-        <v>26.83544303797468</v>
+        <v>12.83168316831683</v>
       </c>
       <c r="F77" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2521,16 +2548,16 @@
         <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D79">
-        <v>276</v>
+        <v>149</v>
       </c>
       <c r="E79">
-        <v>47.01873935264054</v>
+        <v>41.38888888888889</v>
       </c>
       <c r="F79" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2541,16 +2568,16 @@
         <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D80">
-        <v>226</v>
+        <v>113</v>
       </c>
       <c r="E80">
-        <v>38.50085178875639</v>
+        <v>31.38888888888889</v>
       </c>
       <c r="F80" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2561,36 +2588,36 @@
         <v>28</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D81">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="E81">
-        <v>14.48040885860307</v>
+        <v>16.38888888888889</v>
       </c>
       <c r="F81" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>2021</v>
-      </c>
-      <c r="B83" t="s">
-        <v>29</v>
-      </c>
-      <c r="C83" t="s">
-        <v>123</v>
-      </c>
-      <c r="D83">
-        <v>636</v>
-      </c>
-      <c r="E83">
-        <v>41.24513618677042</v>
-      </c>
-      <c r="F83" t="s">
-        <v>266</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>2021</v>
+      </c>
+      <c r="B82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82">
+        <v>39</v>
+      </c>
+      <c r="E82">
+        <v>10.83333333333333</v>
+      </c>
+      <c r="F82" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2601,16 +2628,16 @@
         <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D84">
-        <v>544</v>
+        <v>179</v>
       </c>
       <c r="E84">
-        <v>35.27885862516213</v>
+        <v>45.31645569620253</v>
       </c>
       <c r="F84" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2621,156 +2648,156 @@
         <v>29</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D85">
-        <v>362</v>
+        <v>110</v>
       </c>
       <c r="E85">
-        <v>23.47600518806744</v>
+        <v>27.84810126582278</v>
       </c>
       <c r="F85" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>2023</v>
-      </c>
-      <c r="B87" t="s">
-        <v>30</v>
-      </c>
-      <c r="C87" t="s">
-        <v>126</v>
-      </c>
-      <c r="D87">
-        <v>104</v>
-      </c>
-      <c r="E87">
-        <v>38.95131086142322</v>
-      </c>
-      <c r="F87" t="s">
-        <v>270</v>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>2021</v>
+      </c>
+      <c r="B86" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" t="s">
+        <v>127</v>
+      </c>
+      <c r="D86">
+        <v>106</v>
+      </c>
+      <c r="E86">
+        <v>26.83544303797468</v>
+      </c>
+      <c r="F86" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B88" t="s">
         <v>30</v>
       </c>
       <c r="C88" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D88">
-        <v>100</v>
+        <v>276</v>
       </c>
       <c r="E88">
-        <v>37.45318352059925</v>
+        <v>47.01873935264054</v>
       </c>
       <c r="F88" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B89" t="s">
         <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D89">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="E89">
-        <v>23.59550561797753</v>
+        <v>38.50085178875639</v>
       </c>
       <c r="F89" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>2023</v>
-      </c>
-      <c r="B91" t="s">
-        <v>31</v>
-      </c>
-      <c r="C91" t="s">
-        <v>129</v>
-      </c>
-      <c r="D91">
-        <v>882</v>
-      </c>
-      <c r="E91">
-        <v>45.60496380558428</v>
-      </c>
-      <c r="F91" t="s">
-        <v>268</v>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>2021</v>
+      </c>
+      <c r="B90" t="s">
+        <v>30</v>
+      </c>
+      <c r="C90" t="s">
+        <v>130</v>
+      </c>
+      <c r="D90">
+        <v>85</v>
+      </c>
+      <c r="E90">
+        <v>14.48040885860307</v>
+      </c>
+      <c r="F90" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B92" t="s">
         <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D92">
-        <v>502</v>
+        <v>636</v>
       </c>
       <c r="E92">
-        <v>25.95656670113754</v>
+        <v>41.24513618677042</v>
       </c>
       <c r="F92" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B93" t="s">
         <v>31</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D93">
-        <v>399</v>
+        <v>544</v>
       </c>
       <c r="E93">
-        <v>20.63081695966908</v>
+        <v>35.27885862516213</v>
       </c>
       <c r="F93" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B94" t="s">
         <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D94">
-        <v>151</v>
+        <v>362</v>
       </c>
       <c r="E94">
-        <v>7.807652533609101</v>
+        <v>23.47600518806744</v>
       </c>
       <c r="F94" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2781,16 +2808,16 @@
         <v>32</v>
       </c>
       <c r="C96" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D96">
-        <v>445</v>
+        <v>104</v>
       </c>
       <c r="E96">
-        <v>43.28793774319066</v>
+        <v>38.95131086142322</v>
       </c>
       <c r="F96" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2801,16 +2828,16 @@
         <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D97">
-        <v>353</v>
+        <v>100</v>
       </c>
       <c r="E97">
-        <v>34.33852140077821</v>
+        <v>37.45318352059925</v>
       </c>
       <c r="F97" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2821,16 +2848,16 @@
         <v>32</v>
       </c>
       <c r="C98" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D98">
-        <v>230</v>
+        <v>63</v>
       </c>
       <c r="E98">
-        <v>22.37354085603113</v>
+        <v>23.59550561797753</v>
       </c>
       <c r="F98" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2841,16 +2868,16 @@
         <v>33</v>
       </c>
       <c r="C100" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D100">
-        <v>684</v>
+        <v>882</v>
       </c>
       <c r="E100">
-        <v>46.94577899794098</v>
+        <v>45.60496380558428</v>
       </c>
       <c r="F100" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -2861,16 +2888,16 @@
         <v>33</v>
       </c>
       <c r="C101" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D101">
-        <v>395</v>
+        <v>502</v>
       </c>
       <c r="E101">
-        <v>27.1105010295127</v>
+        <v>25.95656670113754</v>
       </c>
       <c r="F101" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2881,36 +2908,36 @@
         <v>33</v>
       </c>
       <c r="C102" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D102">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="E102">
-        <v>25.94371997254633</v>
+        <v>20.63081695966908</v>
       </c>
       <c r="F102" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>2023</v>
-      </c>
-      <c r="B104" t="s">
-        <v>34</v>
-      </c>
-      <c r="C104" t="s">
-        <v>139</v>
-      </c>
-      <c r="D104">
-        <v>828</v>
-      </c>
-      <c r="E104">
-        <v>36.71840354767184</v>
-      </c>
-      <c r="F104" t="s">
-        <v>264</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103">
+        <v>2023</v>
+      </c>
+      <c r="B103" t="s">
+        <v>33</v>
+      </c>
+      <c r="C103" t="s">
+        <v>140</v>
+      </c>
+      <c r="D103">
+        <v>151</v>
+      </c>
+      <c r="E103">
+        <v>7.807652533609101</v>
+      </c>
+      <c r="F103" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2921,16 +2948,16 @@
         <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D105">
-        <v>524</v>
+        <v>445</v>
       </c>
       <c r="E105">
-        <v>23.23725055432372</v>
+        <v>43.28793774319066</v>
       </c>
       <c r="F105" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -2941,16 +2968,16 @@
         <v>34</v>
       </c>
       <c r="C106" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D106">
-        <v>485</v>
+        <v>353</v>
       </c>
       <c r="E106">
-        <v>21.50776053215078</v>
+        <v>34.33852140077821</v>
       </c>
       <c r="F106" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -2961,36 +2988,36 @@
         <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D107">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="E107">
-        <v>11.57427937915743</v>
+        <v>22.37354085603113</v>
       </c>
       <c r="F107" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>2023</v>
-      </c>
-      <c r="B108" t="s">
-        <v>34</v>
-      </c>
-      <c r="C108" t="s">
-        <v>143</v>
-      </c>
-      <c r="D108">
-        <v>157</v>
-      </c>
-      <c r="E108">
-        <v>6.962305986696231</v>
-      </c>
-      <c r="F108" t="s">
-        <v>264</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109">
+        <v>2023</v>
+      </c>
+      <c r="B109" t="s">
+        <v>35</v>
+      </c>
+      <c r="C109" t="s">
+        <v>144</v>
+      </c>
+      <c r="D109">
+        <v>684</v>
+      </c>
+      <c r="E109">
+        <v>46.94577899794098</v>
+      </c>
+      <c r="F109" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3001,16 +3028,16 @@
         <v>35</v>
       </c>
       <c r="C110" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D110">
-        <v>584</v>
+        <v>395</v>
       </c>
       <c r="E110">
-        <v>43.90977443609022</v>
+        <v>27.1105010295127</v>
       </c>
       <c r="F110" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3021,35 +3048,35 @@
         <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D111">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="E111">
-        <v>29.17293233082707</v>
+        <v>25.94371997254633</v>
       </c>
       <c r="F111" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>2023</v>
-      </c>
-      <c r="B112" t="s">
-        <v>35</v>
-      </c>
-      <c r="C112" t="s">
-        <v>146</v>
-      </c>
-      <c r="D112">
-        <v>358</v>
-      </c>
-      <c r="E112">
-        <v>26.91729323308271</v>
-      </c>
-      <c r="F112" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113">
+        <v>2023</v>
+      </c>
+      <c r="B113" t="s">
+        <v>36</v>
+      </c>
+      <c r="C113" t="s">
+        <v>147</v>
+      </c>
+      <c r="D113">
+        <v>828</v>
+      </c>
+      <c r="E113">
+        <v>36.71840354767184</v>
+      </c>
+      <c r="F113" t="s">
         <v>272</v>
       </c>
     </row>
@@ -3061,13 +3088,13 @@
         <v>36</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D114">
-        <v>634</v>
+        <v>524</v>
       </c>
       <c r="E114">
-        <v>45.67723342939482</v>
+        <v>23.23725055432372</v>
       </c>
       <c r="F114" t="s">
         <v>272</v>
@@ -3081,13 +3108,13 @@
         <v>36</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D115">
-        <v>298</v>
+        <v>485</v>
       </c>
       <c r="E115">
-        <v>21.46974063400576</v>
+        <v>21.50776053215078</v>
       </c>
       <c r="F115" t="s">
         <v>272</v>
@@ -3101,13 +3128,13 @@
         <v>36</v>
       </c>
       <c r="C116" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D116">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E116">
-        <v>17.72334293948127</v>
+        <v>11.57427937915743</v>
       </c>
       <c r="F116" t="s">
         <v>272</v>
@@ -3121,13 +3148,13 @@
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D117">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="E117">
-        <v>15.12968299711815</v>
+        <v>6.962305986696231</v>
       </c>
       <c r="F117" t="s">
         <v>272</v>
@@ -3141,16 +3168,16 @@
         <v>37</v>
       </c>
       <c r="C119" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D119">
-        <v>294</v>
+        <v>584</v>
       </c>
       <c r="E119">
-        <v>38.33116036505867</v>
+        <v>43.90977443609022</v>
       </c>
       <c r="F119" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3161,16 +3188,16 @@
         <v>37</v>
       </c>
       <c r="C120" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D120">
-        <v>145</v>
+        <v>388</v>
       </c>
       <c r="E120">
-        <v>18.90482398956975</v>
+        <v>29.17293233082707</v>
       </c>
       <c r="F120" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3181,36 +3208,16 @@
         <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D121">
-        <v>136</v>
+        <v>358</v>
       </c>
       <c r="E121">
-        <v>17.73142112125163</v>
+        <v>26.91729323308271</v>
       </c>
       <c r="F121" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>2023</v>
-      </c>
-      <c r="B122" t="s">
-        <v>37</v>
-      </c>
-      <c r="C122" t="s">
-        <v>154</v>
-      </c>
-      <c r="D122">
-        <v>104</v>
-      </c>
-      <c r="E122">
-        <v>13.5593220338983</v>
-      </c>
-      <c r="F122" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3218,19 +3225,39 @@
         <v>2023</v>
       </c>
       <c r="B123" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C123" t="s">
         <v>155</v>
       </c>
       <c r="D123">
-        <v>88</v>
+        <v>634</v>
       </c>
       <c r="E123">
-        <v>11.47327249022164</v>
+        <v>45.67723342939482</v>
       </c>
       <c r="F123" t="s">
-        <v>270</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124">
+        <v>2023</v>
+      </c>
+      <c r="B124" t="s">
+        <v>38</v>
+      </c>
+      <c r="C124" t="s">
+        <v>156</v>
+      </c>
+      <c r="D124">
+        <v>298</v>
+      </c>
+      <c r="E124">
+        <v>21.46974063400576</v>
+      </c>
+      <c r="F124" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3241,16 +3268,16 @@
         <v>38</v>
       </c>
       <c r="C125" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D125">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="E125">
-        <v>46.19565217391305</v>
+        <v>17.72334293948127</v>
       </c>
       <c r="F125" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3261,36 +3288,36 @@
         <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D126">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="E126">
-        <v>45.92391304347826</v>
+        <v>15.12968299711815</v>
       </c>
       <c r="F126" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>2023</v>
-      </c>
-      <c r="B127" t="s">
-        <v>38</v>
-      </c>
-      <c r="C127" t="s">
-        <v>158</v>
-      </c>
-      <c r="D127">
-        <v>29</v>
-      </c>
-      <c r="E127">
-        <v>7.880434782608696</v>
-      </c>
-      <c r="F127" t="s">
-        <v>265</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128">
+        <v>2023</v>
+      </c>
+      <c r="B128" t="s">
+        <v>39</v>
+      </c>
+      <c r="C128" t="s">
+        <v>159</v>
+      </c>
+      <c r="D128">
+        <v>294</v>
+      </c>
+      <c r="E128">
+        <v>38.33116036505867</v>
+      </c>
+      <c r="F128" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3301,16 +3328,16 @@
         <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="D129">
-        <v>1114</v>
+        <v>145</v>
       </c>
       <c r="E129">
-        <v>47.79064779064779</v>
+        <v>18.90482398956975</v>
       </c>
       <c r="F129" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3321,16 +3348,16 @@
         <v>39</v>
       </c>
       <c r="C130" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="D130">
-        <v>647</v>
+        <v>136</v>
       </c>
       <c r="E130">
-        <v>27.75632775632776</v>
+        <v>17.73142112125163</v>
       </c>
       <c r="F130" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3341,16 +3368,16 @@
         <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="D131">
-        <v>369</v>
+        <v>104</v>
       </c>
       <c r="E131">
-        <v>15.83011583011583</v>
+        <v>13.5593220338983</v>
       </c>
       <c r="F131" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3361,16 +3388,16 @@
         <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="D132">
-        <v>201</v>
+        <v>88</v>
       </c>
       <c r="E132">
-        <v>8.622908622908623</v>
+        <v>11.47327249022164</v>
       </c>
       <c r="F132" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3381,16 +3408,16 @@
         <v>40</v>
       </c>
       <c r="C134" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="D134">
-        <v>886</v>
+        <v>170</v>
       </c>
       <c r="E134">
-        <v>48.86927744070601</v>
+        <v>46.19565217391305</v>
       </c>
       <c r="F134" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3401,16 +3428,16 @@
         <v>40</v>
       </c>
       <c r="C135" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D135">
-        <v>699</v>
+        <v>169</v>
       </c>
       <c r="E135">
-        <v>38.55488141202427</v>
+        <v>45.92391304347826</v>
       </c>
       <c r="F135" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3421,16 +3448,16 @@
         <v>40</v>
       </c>
       <c r="C136" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="D136">
-        <v>228</v>
+        <v>29</v>
       </c>
       <c r="E136">
-        <v>12.57584114726972</v>
+        <v>7.880434782608696</v>
       </c>
       <c r="F136" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3441,16 +3468,16 @@
         <v>41</v>
       </c>
       <c r="C138" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D138">
-        <v>1630</v>
+        <v>1114</v>
       </c>
       <c r="E138">
-        <v>44.46262956901255</v>
+        <v>47.79064779064779</v>
       </c>
       <c r="F138" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3461,16 +3488,16 @@
         <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D139">
-        <v>1039</v>
+        <v>647</v>
       </c>
       <c r="E139">
-        <v>28.34151663938898</v>
+        <v>27.75632775632776</v>
       </c>
       <c r="F139" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3481,16 +3508,16 @@
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D140">
-        <v>813</v>
+        <v>369</v>
       </c>
       <c r="E140">
-        <v>22.17675941080196</v>
+        <v>15.83011583011583</v>
       </c>
       <c r="F140" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3501,16 +3528,16 @@
         <v>41</v>
       </c>
       <c r="C141" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D141">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="E141">
-        <v>5.019094380796509</v>
+        <v>8.622908622908623</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3521,16 +3548,16 @@
         <v>42</v>
       </c>
       <c r="C143" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="D143">
-        <v>1334</v>
+        <v>886</v>
       </c>
       <c r="E143">
-        <v>46.38386648122393</v>
+        <v>48.86927744070601</v>
       </c>
       <c r="F143" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3541,16 +3568,16 @@
         <v>42</v>
       </c>
       <c r="C144" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="D144">
-        <v>1278</v>
+        <v>699</v>
       </c>
       <c r="E144">
-        <v>44.43671766342142</v>
+        <v>38.55488141202427</v>
       </c>
       <c r="F144" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3561,16 +3588,16 @@
         <v>42</v>
       </c>
       <c r="C145" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="D145">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="E145">
-        <v>9.179415855354661</v>
+        <v>12.57584114726972</v>
       </c>
       <c r="F145" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -3581,16 +3608,16 @@
         <v>43</v>
       </c>
       <c r="C147" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D147">
-        <v>1466</v>
+        <v>1630</v>
       </c>
       <c r="E147">
-        <v>43.1303324507208</v>
+        <v>44.46262956901255</v>
       </c>
       <c r="F147" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3601,16 +3628,16 @@
         <v>43</v>
       </c>
       <c r="C148" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D148">
-        <v>893</v>
+        <v>1039</v>
       </c>
       <c r="E148">
-        <v>26.27243306854957</v>
+        <v>28.34151663938898</v>
       </c>
       <c r="F148" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3621,16 +3648,16 @@
         <v>43</v>
       </c>
       <c r="C149" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D149">
-        <v>672</v>
+        <v>813</v>
       </c>
       <c r="E149">
-        <v>19.77052074139453</v>
+        <v>22.17675941080196</v>
       </c>
       <c r="F149" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3641,36 +3668,36 @@
         <v>43</v>
       </c>
       <c r="C150" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="D150">
-        <v>245</v>
+        <v>184</v>
       </c>
       <c r="E150">
-        <v>7.208002353633422</v>
+        <v>5.019094380796509</v>
       </c>
       <c r="F150" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>2023</v>
-      </c>
-      <c r="B151" t="s">
-        <v>43</v>
-      </c>
-      <c r="C151" t="s">
-        <v>139</v>
-      </c>
-      <c r="D151">
-        <v>123</v>
-      </c>
-      <c r="E151">
-        <v>3.618711385701677</v>
-      </c>
-      <c r="F151" t="s">
-        <v>264</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152">
+        <v>2023</v>
+      </c>
+      <c r="B152" t="s">
+        <v>44</v>
+      </c>
+      <c r="C152" t="s">
+        <v>168</v>
+      </c>
+      <c r="D152">
+        <v>1334</v>
+      </c>
+      <c r="E152">
+        <v>46.38386648122393</v>
+      </c>
+      <c r="F152" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3681,16 +3708,16 @@
         <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="D153">
-        <v>1108</v>
+        <v>1278</v>
       </c>
       <c r="E153">
-        <v>46.4765100671141</v>
+        <v>44.43671766342142</v>
       </c>
       <c r="F153" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3701,36 +3728,16 @@
         <v>44</v>
       </c>
       <c r="C154" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D154">
-        <v>444</v>
+        <v>264</v>
       </c>
       <c r="E154">
-        <v>18.6241610738255</v>
+        <v>9.179415855354661</v>
       </c>
       <c r="F154" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>2023</v>
-      </c>
-      <c r="B155" t="s">
-        <v>44</v>
-      </c>
-      <c r="C155" t="s">
-        <v>163</v>
-      </c>
-      <c r="D155">
-        <v>343</v>
-      </c>
-      <c r="E155">
-        <v>14.38758389261745</v>
-      </c>
-      <c r="F155" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3738,16 +3745,16 @@
         <v>2023</v>
       </c>
       <c r="B156" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C156" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D156">
-        <v>323</v>
+        <v>1466</v>
       </c>
       <c r="E156">
-        <v>13.5486577181208</v>
+        <v>43.1303324507208</v>
       </c>
       <c r="F156" t="s">
         <v>272</v>
@@ -3758,21 +3765,41 @@
         <v>2023</v>
       </c>
       <c r="B157" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C157" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D157">
-        <v>166</v>
+        <v>893</v>
       </c>
       <c r="E157">
-        <v>6.963087248322148</v>
+        <v>26.27243306854957</v>
       </c>
       <c r="F157" t="s">
         <v>272</v>
       </c>
     </row>
+    <row r="158" spans="1:6">
+      <c r="A158">
+        <v>2023</v>
+      </c>
+      <c r="B158" t="s">
+        <v>45</v>
+      </c>
+      <c r="C158" t="s">
+        <v>149</v>
+      </c>
+      <c r="D158">
+        <v>672</v>
+      </c>
+      <c r="E158">
+        <v>19.77052074139453</v>
+      </c>
+      <c r="F158" t="s">
+        <v>272</v>
+      </c>
+    </row>
     <row r="159" spans="1:6">
       <c r="A159">
         <v>2023</v>
@@ -3781,13 +3808,13 @@
         <v>45</v>
       </c>
       <c r="C159" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D159">
-        <v>904</v>
+        <v>245</v>
       </c>
       <c r="E159">
-        <v>42.60131950989632</v>
+        <v>7.208002353633422</v>
       </c>
       <c r="F159" t="s">
         <v>272</v>
@@ -3801,56 +3828,56 @@
         <v>45</v>
       </c>
       <c r="C160" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D160">
-        <v>860</v>
+        <v>123</v>
       </c>
       <c r="E160">
-        <v>40.52780395852969</v>
+        <v>3.618711385701677</v>
       </c>
       <c r="F160" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>2023</v>
-      </c>
-      <c r="B161" t="s">
-        <v>45</v>
-      </c>
-      <c r="C161" t="s">
-        <v>166</v>
-      </c>
-      <c r="D161">
-        <v>193</v>
-      </c>
-      <c r="E161">
-        <v>9.095193213949104</v>
-      </c>
-      <c r="F161" t="s">
-        <v>272</v>
-      </c>
-    </row>
     <row r="162" spans="1:6">
       <c r="A162">
         <v>2023</v>
       </c>
       <c r="B162" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C162" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D162">
-        <v>165</v>
+        <v>1108</v>
       </c>
       <c r="E162">
-        <v>7.775683317624882</v>
+        <v>46.4765100671141</v>
       </c>
       <c r="F162" t="s">
-        <v>272</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163">
+        <v>2023</v>
+      </c>
+      <c r="B163" t="s">
+        <v>46</v>
+      </c>
+      <c r="C163" t="s">
+        <v>158</v>
+      </c>
+      <c r="D163">
+        <v>444</v>
+      </c>
+      <c r="E163">
+        <v>18.6241610738255</v>
+      </c>
+      <c r="F163" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -3861,16 +3888,16 @@
         <v>46</v>
       </c>
       <c r="C164" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="D164">
-        <v>425</v>
+        <v>343</v>
       </c>
       <c r="E164">
-        <v>25.11820330969267</v>
+        <v>14.38758389261745</v>
       </c>
       <c r="F164" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -3881,16 +3908,16 @@
         <v>46</v>
       </c>
       <c r="C165" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D165">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="E165">
-        <v>20.15366430260048</v>
+        <v>13.5486577181208</v>
       </c>
       <c r="F165" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -3901,36 +3928,16 @@
         <v>46</v>
       </c>
       <c r="C166" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D166">
-        <v>279</v>
+        <v>166</v>
       </c>
       <c r="E166">
-        <v>16.48936170212766</v>
+        <v>6.963087248322148</v>
       </c>
       <c r="F166" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167">
-        <v>2023</v>
-      </c>
-      <c r="B167" t="s">
-        <v>46</v>
-      </c>
-      <c r="C167" t="s">
-        <v>154</v>
-      </c>
-      <c r="D167">
-        <v>272</v>
-      </c>
-      <c r="E167">
-        <v>16.07565011820331</v>
-      </c>
-      <c r="F167" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -3938,19 +3945,19 @@
         <v>2023</v>
       </c>
       <c r="B168" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C168" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D168">
-        <v>220</v>
+        <v>904</v>
       </c>
       <c r="E168">
-        <v>13.00236406619385</v>
+        <v>42.60131950989632</v>
       </c>
       <c r="F168" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -3958,19 +3965,39 @@
         <v>2023</v>
       </c>
       <c r="B169" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C169" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D169">
-        <v>155</v>
+        <v>860</v>
       </c>
       <c r="E169">
-        <v>9.160756501182032</v>
+        <v>40.52780395852969</v>
       </c>
       <c r="F169" t="s">
-        <v>270</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170">
+        <v>2023</v>
+      </c>
+      <c r="B170" t="s">
+        <v>47</v>
+      </c>
+      <c r="C170" t="s">
+        <v>174</v>
+      </c>
+      <c r="D170">
+        <v>193</v>
+      </c>
+      <c r="E170">
+        <v>9.095193213949104</v>
+      </c>
+      <c r="F170" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -3981,36 +4008,16 @@
         <v>47</v>
       </c>
       <c r="C171" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D171">
-        <v>286</v>
+        <v>165</v>
       </c>
       <c r="E171">
-        <v>48.22934232715008</v>
+        <v>7.775683317624882</v>
       </c>
       <c r="F171" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172">
-        <v>2023</v>
-      </c>
-      <c r="B172" t="s">
-        <v>47</v>
-      </c>
-      <c r="C172" t="s">
-        <v>170</v>
-      </c>
-      <c r="D172">
-        <v>212</v>
-      </c>
-      <c r="E172">
-        <v>35.7504215851602</v>
-      </c>
-      <c r="F172" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4018,19 +4025,39 @@
         <v>2023</v>
       </c>
       <c r="B173" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C173" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D173">
-        <v>95</v>
+        <v>425</v>
       </c>
       <c r="E173">
-        <v>16.02023608768971</v>
+        <v>25.11820330969267</v>
       </c>
       <c r="F173" t="s">
-        <v>265</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174">
+        <v>2023</v>
+      </c>
+      <c r="B174" t="s">
+        <v>48</v>
+      </c>
+      <c r="C174" t="s">
+        <v>159</v>
+      </c>
+      <c r="D174">
+        <v>341</v>
+      </c>
+      <c r="E174">
+        <v>20.15366430260048</v>
+      </c>
+      <c r="F174" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4041,16 +4068,16 @@
         <v>48</v>
       </c>
       <c r="C175" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D175">
-        <v>431</v>
+        <v>279</v>
       </c>
       <c r="E175">
-        <v>36.77474402730375</v>
+        <v>16.48936170212766</v>
       </c>
       <c r="F175" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4061,16 +4088,16 @@
         <v>48</v>
       </c>
       <c r="C176" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D176">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="E176">
-        <v>25.34129692832764</v>
+        <v>16.07565011820331</v>
       </c>
       <c r="F176" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -4081,16 +4108,16 @@
         <v>48</v>
       </c>
       <c r="C177" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D177">
-        <v>285</v>
+        <v>220</v>
       </c>
       <c r="E177">
-        <v>24.31740614334471</v>
+        <v>13.00236406619385</v>
       </c>
       <c r="F177" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4101,36 +4128,36 @@
         <v>48</v>
       </c>
       <c r="C178" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D178">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="E178">
-        <v>8.191126279863481</v>
+        <v>9.160756501182032</v>
       </c>
       <c r="F178" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179">
-        <v>2023</v>
-      </c>
-      <c r="B179" t="s">
-        <v>48</v>
-      </c>
-      <c r="C179" t="s">
-        <v>176</v>
-      </c>
-      <c r="D179">
-        <v>63</v>
-      </c>
-      <c r="E179">
-        <v>5.375426621160409</v>
-      </c>
-      <c r="F179" t="s">
-        <v>265</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180">
+        <v>2023</v>
+      </c>
+      <c r="B180" t="s">
+        <v>49</v>
+      </c>
+      <c r="C180" t="s">
+        <v>177</v>
+      </c>
+      <c r="D180">
+        <v>286</v>
+      </c>
+      <c r="E180">
+        <v>48.22934232715008</v>
+      </c>
+      <c r="F180" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -4141,16 +4168,16 @@
         <v>49</v>
       </c>
       <c r="C181" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D181">
+        <v>212</v>
+      </c>
+      <c r="E181">
+        <v>35.7504215851602</v>
+      </c>
+      <c r="F181" t="s">
         <v>273</v>
-      </c>
-      <c r="E181">
-        <v>45.4242928452579</v>
-      </c>
-      <c r="F181" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -4161,36 +4188,36 @@
         <v>49</v>
       </c>
       <c r="C182" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D182">
-        <v>234</v>
+        <v>95</v>
       </c>
       <c r="E182">
-        <v>38.9351081530782</v>
+        <v>16.02023608768971</v>
       </c>
       <c r="F182" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183">
-        <v>2023</v>
-      </c>
-      <c r="B183" t="s">
-        <v>49</v>
-      </c>
-      <c r="C183" t="s">
-        <v>179</v>
-      </c>
-      <c r="D183">
-        <v>94</v>
-      </c>
-      <c r="E183">
-        <v>15.64059900166389</v>
-      </c>
-      <c r="F183" t="s">
-        <v>269</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184">
+        <v>2023</v>
+      </c>
+      <c r="B184" t="s">
+        <v>50</v>
+      </c>
+      <c r="C184" t="s">
+        <v>180</v>
+      </c>
+      <c r="D184">
+        <v>431</v>
+      </c>
+      <c r="E184">
+        <v>36.77474402730375</v>
+      </c>
+      <c r="F184" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4201,16 +4228,16 @@
         <v>50</v>
       </c>
       <c r="C185" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D185">
-        <v>124</v>
+        <v>297</v>
       </c>
       <c r="E185">
-        <v>47.69230769230769</v>
+        <v>25.34129692832764</v>
       </c>
       <c r="F185" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4221,16 +4248,16 @@
         <v>50</v>
       </c>
       <c r="C186" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D186">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="E186">
-        <v>28.07692307692308</v>
+        <v>24.31740614334471</v>
       </c>
       <c r="F186" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4241,36 +4268,36 @@
         <v>50</v>
       </c>
       <c r="C187" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D187">
+        <v>96</v>
+      </c>
+      <c r="E187">
+        <v>8.191126279863481</v>
+      </c>
+      <c r="F187" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188">
+        <v>2023</v>
+      </c>
+      <c r="B188" t="s">
+        <v>50</v>
+      </c>
+      <c r="C188" t="s">
+        <v>184</v>
+      </c>
+      <c r="D188">
         <v>63</v>
       </c>
-      <c r="E187">
-        <v>24.23076923076923</v>
-      </c>
-      <c r="F187" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189">
-        <v>2023</v>
-      </c>
-      <c r="B189" t="s">
-        <v>51</v>
-      </c>
-      <c r="C189" t="s">
-        <v>183</v>
-      </c>
-      <c r="D189">
-        <v>827</v>
-      </c>
-      <c r="E189">
-        <v>47.88650839606254</v>
-      </c>
-      <c r="F189" t="s">
-        <v>272</v>
+      <c r="E188">
+        <v>5.375426621160409</v>
+      </c>
+      <c r="F188" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4281,16 +4308,16 @@
         <v>51</v>
       </c>
       <c r="C190" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D190">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E190">
-        <v>16.44470179502026</v>
+        <v>45.4242928452579</v>
       </c>
       <c r="F190" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4301,16 +4328,16 @@
         <v>51</v>
       </c>
       <c r="C191" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D191">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E191">
-        <v>12.85466126230457</v>
+        <v>38.9351081530782</v>
       </c>
       <c r="F191" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -4321,36 +4348,36 @@
         <v>51</v>
       </c>
       <c r="C192" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D192">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="E192">
-        <v>12.21771858714534</v>
+        <v>15.64059900166389</v>
       </c>
       <c r="F192" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193">
-        <v>2023</v>
-      </c>
-      <c r="B193" t="s">
-        <v>51</v>
-      </c>
-      <c r="C193" t="s">
-        <v>187</v>
-      </c>
-      <c r="D193">
-        <v>183</v>
-      </c>
-      <c r="E193">
-        <v>10.59640995946728</v>
-      </c>
-      <c r="F193" t="s">
-        <v>272</v>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194">
+        <v>2023</v>
+      </c>
+      <c r="B194" t="s">
+        <v>52</v>
+      </c>
+      <c r="C194" t="s">
+        <v>188</v>
+      </c>
+      <c r="D194">
+        <v>124</v>
+      </c>
+      <c r="E194">
+        <v>47.69230769230769</v>
+      </c>
+      <c r="F194" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4361,16 +4388,16 @@
         <v>52</v>
       </c>
       <c r="C195" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D195">
-        <v>605</v>
+        <v>73</v>
       </c>
       <c r="E195">
-        <v>41.10054347826087</v>
+        <v>28.07692307692308</v>
       </c>
       <c r="F195" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -4381,36 +4408,36 @@
         <v>52</v>
       </c>
       <c r="C196" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D196">
-        <v>593</v>
+        <v>63</v>
       </c>
       <c r="E196">
-        <v>40.28532608695652</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="F196" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197">
-        <v>2023</v>
-      </c>
-      <c r="B197" t="s">
-        <v>52</v>
-      </c>
-      <c r="C197" t="s">
-        <v>190</v>
-      </c>
-      <c r="D197">
-        <v>274</v>
-      </c>
-      <c r="E197">
-        <v>18.61413043478261</v>
-      </c>
-      <c r="F197" t="s">
-        <v>271</v>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198">
+        <v>2023</v>
+      </c>
+      <c r="B198" t="s">
+        <v>53</v>
+      </c>
+      <c r="C198" t="s">
+        <v>191</v>
+      </c>
+      <c r="D198">
+        <v>827</v>
+      </c>
+      <c r="E198">
+        <v>47.88650839606254</v>
+      </c>
+      <c r="F198" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4421,16 +4448,16 @@
         <v>53</v>
       </c>
       <c r="C199" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D199">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="E199">
-        <v>49.15014164305949</v>
+        <v>16.44470179502026</v>
       </c>
       <c r="F199" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -4441,16 +4468,16 @@
         <v>53</v>
       </c>
       <c r="C200" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D200">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="E200">
-        <v>23.79603399433428</v>
+        <v>12.85466126230457</v>
       </c>
       <c r="F200" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4461,16 +4488,16 @@
         <v>53</v>
       </c>
       <c r="C201" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D201">
-        <v>103</v>
+        <v>211</v>
       </c>
       <c r="E201">
-        <v>14.58923512747875</v>
+        <v>12.21771858714534</v>
       </c>
       <c r="F201" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4481,236 +4508,236 @@
         <v>53</v>
       </c>
       <c r="C202" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D202">
-        <v>88</v>
+        <v>183</v>
       </c>
       <c r="E202">
-        <v>12.46458923512748</v>
+        <v>10.59640995946728</v>
       </c>
       <c r="F202" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B204" t="s">
         <v>54</v>
       </c>
       <c r="C204" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D204">
-        <v>147</v>
+        <v>605</v>
       </c>
       <c r="E204">
-        <v>44.68085106382978</v>
+        <v>41.10054347826087</v>
       </c>
       <c r="F204" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B205" t="s">
         <v>54</v>
       </c>
       <c r="C205" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D205">
-        <v>102</v>
+        <v>593</v>
       </c>
       <c r="E205">
-        <v>31.00303951367781</v>
+        <v>40.28532608695652</v>
       </c>
       <c r="F205" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B206" t="s">
         <v>54</v>
       </c>
       <c r="C206" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D206">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="E206">
-        <v>24.3161094224924</v>
+        <v>18.61413043478261</v>
       </c>
       <c r="F206" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B208" t="s">
         <v>55</v>
       </c>
       <c r="C208" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D208">
-        <v>1224</v>
+        <v>347</v>
       </c>
       <c r="E208">
-        <v>28.77291960507758</v>
+        <v>49.15014164305949</v>
       </c>
       <c r="F208" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B209" t="s">
         <v>55</v>
       </c>
       <c r="C209" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D209">
-        <v>1052</v>
+        <v>168</v>
       </c>
       <c r="E209">
-        <v>24.72966619652092</v>
+        <v>23.79603399433428</v>
       </c>
       <c r="F209" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B210" t="s">
         <v>55</v>
       </c>
       <c r="C210" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D210">
-        <v>685</v>
+        <v>103</v>
       </c>
       <c r="E210">
-        <v>16.10249177244946</v>
+        <v>14.58923512747875</v>
       </c>
       <c r="F210" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B211" t="s">
         <v>55</v>
       </c>
       <c r="C211" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D211">
-        <v>656</v>
+        <v>88</v>
       </c>
       <c r="E211">
-        <v>15.420780441937</v>
+        <v>12.46458923512748</v>
       </c>
       <c r="F211" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212">
-        <v>2025</v>
-      </c>
-      <c r="B212" t="s">
-        <v>55</v>
-      </c>
-      <c r="C212" t="s">
-        <v>202</v>
-      </c>
-      <c r="D212">
-        <v>637</v>
-      </c>
-      <c r="E212">
-        <v>14.97414198401504</v>
-      </c>
-      <c r="F212" t="s">
-        <v>274</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213">
+        <v>2024</v>
+      </c>
+      <c r="B213" t="s">
+        <v>56</v>
+      </c>
+      <c r="C213" t="s">
+        <v>203</v>
+      </c>
+      <c r="D213">
+        <v>147</v>
+      </c>
+      <c r="E213">
+        <v>44.68085106382978</v>
+      </c>
+      <c r="F213" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B214" t="s">
         <v>56</v>
       </c>
       <c r="C214" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D214">
-        <v>3817</v>
+        <v>102</v>
       </c>
       <c r="E214">
-        <v>39.10860655737705</v>
+        <v>31.00303951367781</v>
       </c>
       <c r="F214" t="s">
-        <v>274</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B215" t="s">
         <v>56</v>
       </c>
       <c r="C215" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D215">
-        <v>3272</v>
+        <v>80</v>
       </c>
       <c r="E215">
-        <v>33.52459016393443</v>
+        <v>24.3161094224924</v>
       </c>
       <c r="F215" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216">
-        <v>2025</v>
-      </c>
-      <c r="B216" t="s">
-        <v>56</v>
-      </c>
-      <c r="C216" t="s">
-        <v>205</v>
-      </c>
-      <c r="D216">
-        <v>2671</v>
-      </c>
-      <c r="E216">
-        <v>27.36680327868852</v>
-      </c>
-      <c r="F216" t="s">
-        <v>274</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217">
+        <v>2025</v>
+      </c>
+      <c r="B217" t="s">
+        <v>57</v>
+      </c>
+      <c r="C217" t="s">
+        <v>206</v>
+      </c>
+      <c r="D217">
+        <v>1224</v>
+      </c>
+      <c r="E217">
+        <v>28.77291960507758</v>
+      </c>
+      <c r="F217" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -4721,16 +4748,16 @@
         <v>57</v>
       </c>
       <c r="C218" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D218">
-        <v>710</v>
+        <v>1052</v>
       </c>
       <c r="E218">
-        <v>46.64914586070959</v>
+        <v>24.72966619652092</v>
       </c>
       <c r="F218" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -4741,16 +4768,16 @@
         <v>57</v>
       </c>
       <c r="C219" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D219">
-        <v>617</v>
+        <v>685</v>
       </c>
       <c r="E219">
-        <v>40.53876478318003</v>
+        <v>16.10249177244946</v>
       </c>
       <c r="F219" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -4761,36 +4788,36 @@
         <v>57</v>
       </c>
       <c r="C220" t="s">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="D220">
-        <v>195</v>
+        <v>656</v>
       </c>
       <c r="E220">
-        <v>12.81208935611038</v>
+        <v>15.420780441937</v>
       </c>
       <c r="F220" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222">
-        <v>2025</v>
-      </c>
-      <c r="B222" t="s">
-        <v>58</v>
-      </c>
-      <c r="C222" t="s">
-        <v>208</v>
-      </c>
-      <c r="D222">
-        <v>241</v>
-      </c>
-      <c r="E222">
-        <v>49.79338842975206</v>
-      </c>
-      <c r="F222" t="s">
-        <v>271</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221">
+        <v>2025</v>
+      </c>
+      <c r="B221" t="s">
+        <v>57</v>
+      </c>
+      <c r="C221" t="s">
+        <v>210</v>
+      </c>
+      <c r="D221">
+        <v>637</v>
+      </c>
+      <c r="E221">
+        <v>14.97414198401504</v>
+      </c>
+      <c r="F221" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -4801,16 +4828,16 @@
         <v>58</v>
       </c>
       <c r="C223" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D223">
-        <v>193</v>
+        <v>3817</v>
       </c>
       <c r="E223">
-        <v>39.87603305785124</v>
+        <v>39.10860655737705</v>
       </c>
       <c r="F223" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -4821,36 +4848,36 @@
         <v>58</v>
       </c>
       <c r="C224" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D224">
-        <v>49</v>
+        <v>3272</v>
       </c>
       <c r="E224">
-        <v>10.12396694214876</v>
+        <v>33.52459016393443</v>
       </c>
       <c r="F224" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
-      <c r="A226">
-        <v>2025</v>
-      </c>
-      <c r="B226" t="s">
-        <v>59</v>
-      </c>
-      <c r="C226" t="s">
-        <v>211</v>
-      </c>
-      <c r="D226">
-        <v>373</v>
-      </c>
-      <c r="E226">
-        <v>36.39024390243902</v>
-      </c>
-      <c r="F226" t="s">
-        <v>268</v>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225">
+        <v>2025</v>
+      </c>
+      <c r="B225" t="s">
+        <v>58</v>
+      </c>
+      <c r="C225" t="s">
+        <v>213</v>
+      </c>
+      <c r="D225">
+        <v>2671</v>
+      </c>
+      <c r="E225">
+        <v>27.36680327868852</v>
+      </c>
+      <c r="F225" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -4861,16 +4888,16 @@
         <v>59</v>
       </c>
       <c r="C227" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D227">
-        <v>225</v>
+        <v>710</v>
       </c>
       <c r="E227">
-        <v>21.95121951219512</v>
+        <v>46.64914586070959</v>
       </c>
       <c r="F227" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -4881,16 +4908,16 @@
         <v>59</v>
       </c>
       <c r="C228" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D228">
-        <v>206</v>
+        <v>617</v>
       </c>
       <c r="E228">
-        <v>20.09756097560976</v>
+        <v>40.53876478318003</v>
       </c>
       <c r="F228" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -4901,36 +4928,36 @@
         <v>59</v>
       </c>
       <c r="C229" t="s">
-        <v>214</v>
+        <v>112</v>
       </c>
       <c r="D229">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="E229">
-        <v>13.65853658536586</v>
+        <v>12.81208935611038</v>
       </c>
       <c r="F229" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6">
-      <c r="A230">
-        <v>2025</v>
-      </c>
-      <c r="B230" t="s">
-        <v>59</v>
-      </c>
-      <c r="C230" t="s">
-        <v>215</v>
-      </c>
-      <c r="D230">
-        <v>81</v>
-      </c>
-      <c r="E230">
-        <v>7.902439024390244</v>
-      </c>
-      <c r="F230" t="s">
-        <v>268</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231">
+        <v>2025</v>
+      </c>
+      <c r="B231" t="s">
+        <v>60</v>
+      </c>
+      <c r="C231" t="s">
+        <v>216</v>
+      </c>
+      <c r="D231">
+        <v>241</v>
+      </c>
+      <c r="E231">
+        <v>49.79338842975206</v>
+      </c>
+      <c r="F231" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -4941,16 +4968,16 @@
         <v>60</v>
       </c>
       <c r="C232" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D232">
-        <v>6552</v>
+        <v>193</v>
       </c>
       <c r="E232">
-        <v>47.15704620699582</v>
+        <v>39.87603305785124</v>
       </c>
       <c r="F232" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -4961,36 +4988,36 @@
         <v>60</v>
       </c>
       <c r="C233" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D233">
-        <v>4724</v>
+        <v>49</v>
       </c>
       <c r="E233">
-        <v>34.00028789405498</v>
+        <v>10.12396694214876</v>
       </c>
       <c r="F233" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
-      <c r="A234">
-        <v>2025</v>
-      </c>
-      <c r="B234" t="s">
-        <v>60</v>
-      </c>
-      <c r="C234" t="s">
-        <v>218</v>
-      </c>
-      <c r="D234">
-        <v>2618</v>
-      </c>
-      <c r="E234">
-        <v>18.84266589894919</v>
-      </c>
-      <c r="F234" t="s">
-        <v>265</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235">
+        <v>2025</v>
+      </c>
+      <c r="B235" t="s">
+        <v>61</v>
+      </c>
+      <c r="C235" t="s">
+        <v>219</v>
+      </c>
+      <c r="D235">
+        <v>373</v>
+      </c>
+      <c r="E235">
+        <v>36.39024390243902</v>
+      </c>
+      <c r="F235" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -5001,16 +5028,16 @@
         <v>61</v>
       </c>
       <c r="C236" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D236">
-        <v>5832</v>
+        <v>225</v>
       </c>
       <c r="E236">
-        <v>37.28423475258919</v>
+        <v>21.95121951219512</v>
       </c>
       <c r="F236" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -5021,16 +5048,16 @@
         <v>61</v>
       </c>
       <c r="C237" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D237">
-        <v>4950</v>
+        <v>206</v>
       </c>
       <c r="E237">
-        <v>31.64556962025317</v>
+        <v>20.09756097560976</v>
       </c>
       <c r="F237" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5041,36 +5068,36 @@
         <v>61</v>
       </c>
       <c r="C238" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D238">
-        <v>4834</v>
+        <v>140</v>
       </c>
       <c r="E238">
-        <v>30.90397647359673</v>
+        <v>13.65853658536586</v>
       </c>
       <c r="F238" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6">
-      <c r="A240">
-        <v>2025</v>
-      </c>
-      <c r="B240" t="s">
-        <v>62</v>
-      </c>
-      <c r="C240" t="s">
-        <v>222</v>
-      </c>
-      <c r="D240">
-        <v>9318</v>
-      </c>
-      <c r="E240">
-        <v>41.92764578833693</v>
-      </c>
-      <c r="F240" t="s">
-        <v>272</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239">
+        <v>2025</v>
+      </c>
+      <c r="B239" t="s">
+        <v>61</v>
+      </c>
+      <c r="C239" t="s">
+        <v>223</v>
+      </c>
+      <c r="D239">
+        <v>81</v>
+      </c>
+      <c r="E239">
+        <v>7.902439024390244</v>
+      </c>
+      <c r="F239" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -5078,19 +5105,19 @@
         <v>2025</v>
       </c>
       <c r="B241" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C241" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D241">
-        <v>8700</v>
+        <v>6552</v>
       </c>
       <c r="E241">
-        <v>39.14686825053996</v>
+        <v>47.15704620699582</v>
       </c>
       <c r="F241" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -5098,39 +5125,39 @@
         <v>2025</v>
       </c>
       <c r="B242" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C242" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D242">
-        <v>4206</v>
+        <v>4724</v>
       </c>
       <c r="E242">
-        <v>18.92548596112311</v>
+        <v>34.00028789405498</v>
       </c>
       <c r="F242" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6">
-      <c r="A244">
-        <v>2025</v>
-      </c>
-      <c r="B244" t="s">
-        <v>63</v>
-      </c>
-      <c r="C244" t="s">
-        <v>225</v>
-      </c>
-      <c r="D244">
-        <v>1473</v>
-      </c>
-      <c r="E244">
-        <v>39.30096051227321</v>
-      </c>
-      <c r="F244" t="s">
-        <v>270</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243">
+        <v>2025</v>
+      </c>
+      <c r="B243" t="s">
+        <v>22</v>
+      </c>
+      <c r="C243" t="s">
+        <v>226</v>
+      </c>
+      <c r="D243">
+        <v>2618</v>
+      </c>
+      <c r="E243">
+        <v>18.84266589894919</v>
+      </c>
+      <c r="F243" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -5138,19 +5165,19 @@
         <v>2025</v>
       </c>
       <c r="B245" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C245" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D245">
-        <v>1297</v>
+        <v>5832</v>
       </c>
       <c r="E245">
-        <v>34.6051227321238</v>
+        <v>37.28423475258919</v>
       </c>
       <c r="F245" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -5158,19 +5185,19 @@
         <v>2025</v>
       </c>
       <c r="B246" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C246" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D246">
-        <v>516</v>
+        <v>4950</v>
       </c>
       <c r="E246">
-        <v>13.76734258271078</v>
+        <v>31.64556962025317</v>
       </c>
       <c r="F246" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -5178,39 +5205,39 @@
         <v>2025</v>
       </c>
       <c r="B247" t="s">
+        <v>62</v>
+      </c>
+      <c r="C247" t="s">
+        <v>229</v>
+      </c>
+      <c r="D247">
+        <v>4834</v>
+      </c>
+      <c r="E247">
+        <v>30.90397647359673</v>
+      </c>
+      <c r="F247" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249">
+        <v>2025</v>
+      </c>
+      <c r="B249" t="s">
         <v>63</v>
       </c>
-      <c r="C247" t="s">
-        <v>228</v>
-      </c>
-      <c r="D247">
-        <v>305</v>
-      </c>
-      <c r="E247">
-        <v>8.137673425827108</v>
-      </c>
-      <c r="F247" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
-      <c r="A248">
-        <v>2025</v>
-      </c>
-      <c r="B248" t="s">
-        <v>63</v>
-      </c>
-      <c r="C248" t="s">
-        <v>229</v>
-      </c>
-      <c r="D248">
-        <v>157</v>
-      </c>
-      <c r="E248">
-        <v>4.188900747065102</v>
-      </c>
-      <c r="F248" t="s">
-        <v>270</v>
+      <c r="C249" t="s">
+        <v>230</v>
+      </c>
+      <c r="D249">
+        <v>9318</v>
+      </c>
+      <c r="E249">
+        <v>41.92764578833693</v>
+      </c>
+      <c r="F249" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -5218,19 +5245,19 @@
         <v>2025</v>
       </c>
       <c r="B250" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C250" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D250">
-        <v>854</v>
+        <v>8700</v>
       </c>
       <c r="E250">
-        <v>47.52365052865888</v>
+        <v>39.14686825053996</v>
       </c>
       <c r="F250" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -5238,39 +5265,39 @@
         <v>2025</v>
       </c>
       <c r="B251" t="s">
+        <v>63</v>
+      </c>
+      <c r="C251" t="s">
+        <v>232</v>
+      </c>
+      <c r="D251">
+        <v>4206</v>
+      </c>
+      <c r="E251">
+        <v>18.92548596112311</v>
+      </c>
+      <c r="F251" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253">
+        <v>2025</v>
+      </c>
+      <c r="B253" t="s">
         <v>64</v>
       </c>
-      <c r="C251" t="s">
-        <v>231</v>
-      </c>
-      <c r="D251">
-        <v>764</v>
-      </c>
-      <c r="E251">
-        <v>42.51530328324986</v>
-      </c>
-      <c r="F251" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
-      <c r="A252">
-        <v>2025</v>
-      </c>
-      <c r="B252" t="s">
-        <v>64</v>
-      </c>
-      <c r="C252" t="s">
-        <v>232</v>
-      </c>
-      <c r="D252">
-        <v>175</v>
-      </c>
-      <c r="E252">
-        <v>9.738452977184195</v>
-      </c>
-      <c r="F252" t="s">
-        <v>267</v>
+      <c r="C253" t="s">
+        <v>233</v>
+      </c>
+      <c r="D253">
+        <v>1473</v>
+      </c>
+      <c r="E253">
+        <v>39.30096051227321</v>
+      </c>
+      <c r="F253" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -5278,19 +5305,19 @@
         <v>2025</v>
       </c>
       <c r="B254" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C254" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D254">
-        <v>162</v>
+        <v>1297</v>
       </c>
       <c r="E254">
-        <v>45.2513966480447</v>
+        <v>34.6051227321238</v>
       </c>
       <c r="F254" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -5298,19 +5325,19 @@
         <v>2025</v>
       </c>
       <c r="B255" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C255" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D255">
-        <v>156</v>
+        <v>516</v>
       </c>
       <c r="E255">
-        <v>43.5754189944134</v>
+        <v>13.76734258271078</v>
       </c>
       <c r="F255" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -5318,39 +5345,39 @@
         <v>2025</v>
       </c>
       <c r="B256" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C256" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D256">
-        <v>40</v>
+        <v>305</v>
       </c>
       <c r="E256">
-        <v>11.1731843575419</v>
+        <v>8.137673425827108</v>
       </c>
       <c r="F256" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
-      <c r="A258">
-        <v>2025</v>
-      </c>
-      <c r="B258" t="s">
-        <v>66</v>
-      </c>
-      <c r="C258" t="s">
-        <v>236</v>
-      </c>
-      <c r="D258">
-        <v>11367</v>
-      </c>
-      <c r="E258">
-        <v>45.69280861840254</v>
-      </c>
-      <c r="F258" t="s">
-        <v>268</v>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257">
+        <v>2025</v>
+      </c>
+      <c r="B257" t="s">
+        <v>64</v>
+      </c>
+      <c r="C257" t="s">
+        <v>237</v>
+      </c>
+      <c r="D257">
+        <v>157</v>
+      </c>
+      <c r="E257">
+        <v>4.188900747065102</v>
+      </c>
+      <c r="F257" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -5358,19 +5385,19 @@
         <v>2025</v>
       </c>
       <c r="B259" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C259" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D259">
-        <v>8188</v>
+        <v>854</v>
       </c>
       <c r="E259">
-        <v>32.91393656791413</v>
+        <v>47.52365052865888</v>
       </c>
       <c r="F259" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -5378,39 +5405,39 @@
         <v>2025</v>
       </c>
       <c r="B260" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C260" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D260">
-        <v>5322</v>
+        <v>764</v>
       </c>
       <c r="E260">
-        <v>21.39325481368332</v>
+        <v>42.51530328324986</v>
       </c>
       <c r="F260" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
-      <c r="A262">
-        <v>2025</v>
-      </c>
-      <c r="B262" t="s">
-        <v>67</v>
-      </c>
-      <c r="C262" t="s">
-        <v>170</v>
-      </c>
-      <c r="D262">
-        <v>287</v>
-      </c>
-      <c r="E262">
-        <v>47.83333333333334</v>
-      </c>
-      <c r="F262" t="s">
-        <v>265</v>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261">
+        <v>2025</v>
+      </c>
+      <c r="B261" t="s">
+        <v>65</v>
+      </c>
+      <c r="C261" t="s">
+        <v>240</v>
+      </c>
+      <c r="D261">
+        <v>175</v>
+      </c>
+      <c r="E261">
+        <v>9.738452977184195</v>
+      </c>
+      <c r="F261" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -5418,19 +5445,19 @@
         <v>2025</v>
       </c>
       <c r="B263" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C263" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D263">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="E263">
-        <v>29.16666666666667</v>
+        <v>45.2513966480447</v>
       </c>
       <c r="F263" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -5438,39 +5465,39 @@
         <v>2025</v>
       </c>
       <c r="B264" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C264" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D264">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="E264">
-        <v>23</v>
+        <v>43.5754189944134</v>
       </c>
       <c r="F264" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
-      <c r="A266">
-        <v>2025</v>
-      </c>
-      <c r="B266" t="s">
-        <v>68</v>
-      </c>
-      <c r="C266" t="s">
-        <v>241</v>
-      </c>
-      <c r="D266">
-        <v>163</v>
-      </c>
-      <c r="E266">
-        <v>38.71733966745843</v>
-      </c>
-      <c r="F266" t="s">
-        <v>275</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265">
+        <v>2025</v>
+      </c>
+      <c r="B265" t="s">
+        <v>66</v>
+      </c>
+      <c r="C265" t="s">
+        <v>243</v>
+      </c>
+      <c r="D265">
+        <v>40</v>
+      </c>
+      <c r="E265">
+        <v>11.1731843575419</v>
+      </c>
+      <c r="F265" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -5478,19 +5505,19 @@
         <v>2025</v>
       </c>
       <c r="B267" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C267" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D267">
-        <v>160</v>
+        <v>11367</v>
       </c>
       <c r="E267">
-        <v>38.00475059382423</v>
+        <v>45.69280861840254</v>
       </c>
       <c r="F267" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -5498,19 +5525,19 @@
         <v>2025</v>
       </c>
       <c r="B268" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C268" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D268">
-        <v>75</v>
+        <v>8188</v>
       </c>
       <c r="E268">
-        <v>17.81472684085511</v>
+        <v>32.91393656791413</v>
       </c>
       <c r="F268" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -5518,19 +5545,19 @@
         <v>2025</v>
       </c>
       <c r="B269" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C269" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D269">
-        <v>23</v>
+        <v>5322</v>
       </c>
       <c r="E269">
-        <v>5.463182897862233</v>
+        <v>21.39325481368332</v>
       </c>
       <c r="F269" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -5538,19 +5565,19 @@
         <v>2025</v>
       </c>
       <c r="B271" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C271" t="s">
-        <v>245</v>
+        <v>178</v>
       </c>
       <c r="D271">
-        <v>104</v>
+        <v>287</v>
       </c>
       <c r="E271">
-        <v>35.37414965986395</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="F271" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -5558,19 +5585,19 @@
         <v>2025</v>
       </c>
       <c r="B272" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C272" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D272">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="E272">
-        <v>26.87074829931973</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="F272" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -5578,39 +5605,39 @@
         <v>2025</v>
       </c>
       <c r="B273" t="s">
+        <v>68</v>
+      </c>
+      <c r="C273" t="s">
+        <v>248</v>
+      </c>
+      <c r="D273">
+        <v>138</v>
+      </c>
+      <c r="E273">
+        <v>23</v>
+      </c>
+      <c r="F273" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275">
+        <v>2025</v>
+      </c>
+      <c r="B275" t="s">
         <v>69</v>
       </c>
-      <c r="C273" t="s">
-        <v>247</v>
-      </c>
-      <c r="D273">
-        <v>78</v>
-      </c>
-      <c r="E273">
-        <v>26.53061224489796</v>
-      </c>
-      <c r="F273" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
-      <c r="A274">
-        <v>2025</v>
-      </c>
-      <c r="B274" t="s">
-        <v>69</v>
-      </c>
-      <c r="C274" t="s">
-        <v>248</v>
-      </c>
-      <c r="D274">
-        <v>32</v>
-      </c>
-      <c r="E274">
-        <v>10.8843537414966</v>
-      </c>
-      <c r="F274" t="s">
-        <v>267</v>
+      <c r="C275" t="s">
+        <v>249</v>
+      </c>
+      <c r="D275">
+        <v>163</v>
+      </c>
+      <c r="E275">
+        <v>38.71733966745843</v>
+      </c>
+      <c r="F275" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -5618,19 +5645,19 @@
         <v>2025</v>
       </c>
       <c r="B276" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C276" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D276">
-        <v>549</v>
+        <v>160</v>
       </c>
       <c r="E276">
-        <v>42.99138606108065</v>
+        <v>38.00475059382423</v>
       </c>
       <c r="F276" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -5638,19 +5665,19 @@
         <v>2025</v>
       </c>
       <c r="B277" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C277" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D277">
-        <v>445</v>
+        <v>75</v>
       </c>
       <c r="E277">
-        <v>34.84729835552075</v>
+        <v>17.81472684085511</v>
       </c>
       <c r="F277" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -5658,19 +5685,19 @@
         <v>2025</v>
       </c>
       <c r="B278" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C278" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D278">
-        <v>283</v>
+        <v>23</v>
       </c>
       <c r="E278">
-        <v>22.16131558339859</v>
+        <v>5.463182897862233</v>
       </c>
       <c r="F278" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -5678,19 +5705,19 @@
         <v>2025</v>
       </c>
       <c r="B280" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C280" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D280">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="E280">
-        <v>28.21100917431193</v>
+        <v>35.37414965986395</v>
       </c>
       <c r="F280" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -5698,19 +5725,19 @@
         <v>2025</v>
       </c>
       <c r="B281" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C281" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D281">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E281">
-        <v>26.8348623853211</v>
+        <v>26.87074829931973</v>
       </c>
       <c r="F281" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -5718,19 +5745,19 @@
         <v>2025</v>
       </c>
       <c r="B282" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C282" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D282">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="E282">
-        <v>24.31192660550459</v>
+        <v>26.53061224489796</v>
       </c>
       <c r="F282" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -5738,19 +5765,19 @@
         <v>2025</v>
       </c>
       <c r="B283" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C283" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D283">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="E283">
-        <v>20.64220183486239</v>
+        <v>10.8843537414966</v>
       </c>
       <c r="F283" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -5758,19 +5785,19 @@
         <v>2025</v>
       </c>
       <c r="B285" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C285" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D285">
-        <v>195</v>
+        <v>549</v>
       </c>
       <c r="E285">
-        <v>45.03464203233256</v>
+        <v>42.99138606108065</v>
       </c>
       <c r="F285" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -5778,19 +5805,19 @@
         <v>2025</v>
       </c>
       <c r="B286" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C286" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D286">
-        <v>162</v>
+        <v>445</v>
       </c>
       <c r="E286">
-        <v>37.41339491916859</v>
+        <v>34.84729835552075</v>
       </c>
       <c r="F286" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -5798,19 +5825,19 @@
         <v>2025</v>
       </c>
       <c r="B287" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C287" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D287">
-        <v>76</v>
+        <v>283</v>
       </c>
       <c r="E287">
-        <v>17.55196304849884</v>
+        <v>22.16131558339859</v>
       </c>
       <c r="F287" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -5818,19 +5845,19 @@
         <v>2025</v>
       </c>
       <c r="B289" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C289" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D289">
-        <v>315</v>
+        <v>123</v>
       </c>
       <c r="E289">
-        <v>43.09165526675787</v>
+        <v>28.21100917431193</v>
       </c>
       <c r="F289" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -5838,19 +5865,19 @@
         <v>2025</v>
       </c>
       <c r="B290" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C290" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D290">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="E290">
-        <v>33.78932968536252</v>
+        <v>26.8348623853211</v>
       </c>
       <c r="F290" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -5858,19 +5885,159 @@
         <v>2025</v>
       </c>
       <c r="B291" t="s">
+        <v>72</v>
+      </c>
+      <c r="C291" t="s">
+        <v>262</v>
+      </c>
+      <c r="D291">
+        <v>106</v>
+      </c>
+      <c r="E291">
+        <v>24.31192660550459</v>
+      </c>
+      <c r="F291" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292">
+        <v>2025</v>
+      </c>
+      <c r="B292" t="s">
+        <v>72</v>
+      </c>
+      <c r="C292" t="s">
+        <v>263</v>
+      </c>
+      <c r="D292">
+        <v>90</v>
+      </c>
+      <c r="E292">
+        <v>20.64220183486239</v>
+      </c>
+      <c r="F292" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294">
+        <v>2025</v>
+      </c>
+      <c r="B294" t="s">
         <v>73</v>
       </c>
-      <c r="C291" t="s">
-        <v>261</v>
-      </c>
-      <c r="D291">
+      <c r="C294" t="s">
+        <v>264</v>
+      </c>
+      <c r="D294">
+        <v>195</v>
+      </c>
+      <c r="E294">
+        <v>45.03464203233256</v>
+      </c>
+      <c r="F294" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295">
+        <v>2025</v>
+      </c>
+      <c r="B295" t="s">
+        <v>73</v>
+      </c>
+      <c r="C295" t="s">
+        <v>265</v>
+      </c>
+      <c r="D295">
+        <v>162</v>
+      </c>
+      <c r="E295">
+        <v>37.41339491916859</v>
+      </c>
+      <c r="F295" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296">
+        <v>2025</v>
+      </c>
+      <c r="B296" t="s">
+        <v>73</v>
+      </c>
+      <c r="C296" t="s">
+        <v>266</v>
+      </c>
+      <c r="D296">
+        <v>76</v>
+      </c>
+      <c r="E296">
+        <v>17.55196304849884</v>
+      </c>
+      <c r="F296" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298">
+        <v>2025</v>
+      </c>
+      <c r="B298" t="s">
+        <v>74</v>
+      </c>
+      <c r="C298" t="s">
+        <v>267</v>
+      </c>
+      <c r="D298">
+        <v>315</v>
+      </c>
+      <c r="E298">
+        <v>43.09165526675787</v>
+      </c>
+      <c r="F298" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299">
+        <v>2025</v>
+      </c>
+      <c r="B299" t="s">
+        <v>74</v>
+      </c>
+      <c r="C299" t="s">
+        <v>268</v>
+      </c>
+      <c r="D299">
+        <v>247</v>
+      </c>
+      <c r="E299">
+        <v>33.78932968536252</v>
+      </c>
+      <c r="F299" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300">
+        <v>2025</v>
+      </c>
+      <c r="B300" t="s">
+        <v>74</v>
+      </c>
+      <c r="C300" t="s">
+        <v>269</v>
+      </c>
+      <c r="D300">
         <v>169</v>
       </c>
-      <c r="E291">
+      <c r="E300">
         <v>23.11901504787962</v>
       </c>
-      <c r="F291" t="s">
-        <v>264</v>
+      <c r="F300" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="325">
   <si>
     <t>Year</t>
   </si>
@@ -50,6 +50,33 @@
     <t>Delaware County (Media + boroughs + townships)</t>
   </si>
   <si>
+    <t>HAZLETON CITY MAYOR</t>
+  </si>
+  <si>
+    <t>MAGISTERIAL DISTRICT JUDGE 10-1-03</t>
+  </si>
+  <si>
+    <t>RECORDER OF DEEDS</t>
+  </si>
+  <si>
+    <t>REGISTER OF WILLS</t>
+  </si>
+  <si>
+    <t>SALEM TOWNSHIP SUPERVISOR</t>
+  </si>
+  <si>
+    <t>SHERIFF</t>
+  </si>
+  <si>
+    <t>V1:T6 TOWNSHIP SUPERVISOR SEWICKLEY</t>
+  </si>
+  <si>
+    <t>V1:T6 TOWNSHIP SUPERVISOR UNITY</t>
+  </si>
+  <si>
+    <t>WILKES-BARRE CITY CONTROLLER</t>
+  </si>
+  <si>
     <t>DEM JUDGE OF THE COURT OF COMMON PLEAS</t>
   </si>
   <si>
@@ -242,6 +269,108 @@
     <t>REP Township Supervisor West Caln Township</t>
   </si>
   <si>
+    <t>JEFF CUSAT</t>
+  </si>
+  <si>
+    <t>ALLISON BARLETTA</t>
+  </si>
+  <si>
+    <t>BOB YEVAK</t>
+  </si>
+  <si>
+    <t>MARIA JACKETTI</t>
+  </si>
+  <si>
+    <t>GRACE CUOZZO</t>
+  </si>
+  <si>
+    <t>WAYNE VLASIC</t>
+  </si>
+  <si>
+    <t>JAMES SMITH</t>
+  </si>
+  <si>
+    <t>ALAN JACK MANDERINO</t>
+  </si>
+  <si>
+    <t>TOM MURPHY</t>
+  </si>
+  <si>
+    <t>FRANK SCHIEFER</t>
+  </si>
+  <si>
+    <t>BRIAN RASEL</t>
+  </si>
+  <si>
+    <t>JON WIAN</t>
+  </si>
+  <si>
+    <t>KATIE PECARCHIK</t>
+  </si>
+  <si>
+    <t>SHERRY MAGRETTI HAMILTON</t>
+  </si>
+  <si>
+    <t>KIMBERLY HORRELL</t>
+  </si>
+  <si>
+    <t>SUSAN VOSEFSKI</t>
+  </si>
+  <si>
+    <t>FREDE FRANSEN</t>
+  </si>
+  <si>
+    <t>ROBERT FISHER</t>
+  </si>
+  <si>
+    <t>KIP MCCABE</t>
+  </si>
+  <si>
+    <t>JAMES ALBERT</t>
+  </si>
+  <si>
+    <t>JONATHAN HELD</t>
+  </si>
+  <si>
+    <t>STEVE FELDER</t>
+  </si>
+  <si>
+    <t>EUGENE ZULISKY</t>
+  </si>
+  <si>
+    <t>SAMUEL PILATO</t>
+  </si>
+  <si>
+    <t>LINDA HARVEY</t>
+  </si>
+  <si>
+    <t>ROBERT MACPHERSON</t>
+  </si>
+  <si>
+    <t>JOSEPH KERBER</t>
+  </si>
+  <si>
+    <t>DOUG MURPHY</t>
+  </si>
+  <si>
+    <t>MIKE OBARTO</t>
+  </si>
+  <si>
+    <t>PAUL MCCOMMONS</t>
+  </si>
+  <si>
+    <t>MARCUS BURRIK</t>
+  </si>
+  <si>
+    <t>DARREN SNYDER</t>
+  </si>
+  <si>
+    <t>CHARLIE TOOT MAJIKES</t>
+  </si>
+  <si>
+    <t>PATRICIA UNVARSKY</t>
+  </si>
+  <si>
     <t>WILLIAM MCCONNELL JR</t>
   </si>
   <si>
@@ -749,15 +878,6 @@
     <t>WILLIAM CUMMINGS</t>
   </si>
   <si>
-    <t>KATIE PECARCHIK</t>
-  </si>
-  <si>
-    <t>JON WIAN</t>
-  </si>
-  <si>
-    <t>KIMBERLY HORRELL</t>
-  </si>
-  <si>
     <t>JONATHAN FRANK ITTERLY</t>
   </si>
   <si>
@@ -827,6 +947,12 @@
     <t>JOE HUTTON</t>
   </si>
   <si>
+    <t>Luzerne County (Wilkes-Barre + boroughs + townships)</t>
+  </si>
+  <si>
+    <t>Westmoreland County (city + boroughs + townships)</t>
+  </si>
+  <si>
     <t>Mercer County (Mercer + Sharon + Hermitage + townships)</t>
   </si>
   <si>
@@ -842,13 +968,7 @@
     <t>Lehigh County (Allentown + boroughs + townships)</t>
   </si>
   <si>
-    <t>Luzerne County (Wilkes-Barre + boroughs + townships)</t>
-  </si>
-  <si>
     <t>Montgomery County (Norristown + Philly suburbs)</t>
-  </si>
-  <si>
-    <t>Westmoreland County (city + boroughs + townships)</t>
   </si>
   <si>
     <t>Northumberland County (Sunbury + Shamokin + boroughs)</t>
@@ -1317,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:F343"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1342,682 +1462,682 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D2">
-        <v>3420</v>
+        <v>799</v>
       </c>
       <c r="E2">
-        <v>42.77673545966229</v>
+        <v>35.94242015294647</v>
       </c>
       <c r="F2" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D3">
-        <v>2391</v>
+        <v>713</v>
       </c>
       <c r="E3">
-        <v>29.90619136960601</v>
+        <v>32.07377417903734</v>
       </c>
       <c r="F3" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D4">
-        <v>2184</v>
+        <v>355</v>
       </c>
       <c r="E4">
-        <v>27.31707317073171</v>
+        <v>15.96941070625281</v>
       </c>
       <c r="F4" t="s">
-        <v>270</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>2019</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5">
+        <v>190</v>
+      </c>
+      <c r="E5">
+        <v>8.547008547008547</v>
+      </c>
+      <c r="F5" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D6">
-        <v>572</v>
+        <v>166</v>
       </c>
       <c r="E6">
-        <v>47.03947368421053</v>
+        <v>7.467386414754835</v>
       </c>
       <c r="F6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>2021</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7">
-        <v>380</v>
-      </c>
-      <c r="E7">
-        <v>31.25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D8">
-        <v>264</v>
+        <v>807</v>
       </c>
       <c r="E8">
-        <v>21.71052631578948</v>
+        <v>42.87991498405951</v>
       </c>
       <c r="F8" t="s">
-        <v>270</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>2019</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9">
+        <v>704</v>
+      </c>
+      <c r="E9">
+        <v>37.40701381509033</v>
+      </c>
+      <c r="F9" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D10">
-        <v>177</v>
+        <v>371</v>
       </c>
       <c r="E10">
-        <v>39.95485327313769</v>
+        <v>19.71307120085016</v>
       </c>
       <c r="F10" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>2021</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11">
-        <v>141</v>
-      </c>
-      <c r="E11">
-        <v>31.82844243792325</v>
-      </c>
-      <c r="F11" t="s">
-        <v>271</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D12">
-        <v>81</v>
+        <v>23009</v>
       </c>
       <c r="E12">
-        <v>18.2844243792325</v>
+        <v>49.36282502359907</v>
       </c>
       <c r="F12" t="s">
-        <v>271</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D13">
-        <v>44</v>
+        <v>10398</v>
       </c>
       <c r="E13">
-        <v>9.932279909706546</v>
+        <v>22.30756028490518</v>
       </c>
       <c r="F13" t="s">
-        <v>271</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>2019</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14">
+        <v>6676</v>
+      </c>
+      <c r="E14">
+        <v>14.32249206212992</v>
+      </c>
+      <c r="F14" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D15">
-        <v>1471</v>
+        <v>6529</v>
       </c>
       <c r="E15">
-        <v>44.12117576484703</v>
+        <v>14.00712262936583</v>
       </c>
       <c r="F15" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>2021</v>
-      </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16">
-        <v>1247</v>
-      </c>
-      <c r="E16">
-        <v>37.40251949610078</v>
-      </c>
-      <c r="F16" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D17">
-        <v>616</v>
+        <v>15761</v>
       </c>
       <c r="E17">
-        <v>18.47630473905219</v>
+        <v>32.71613907628438</v>
       </c>
       <c r="F17" t="s">
-        <v>272</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>2019</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18">
+        <v>12780</v>
+      </c>
+      <c r="E18">
+        <v>26.52828230409964</v>
+      </c>
+      <c r="F18" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D19">
-        <v>1183</v>
+        <v>10691</v>
       </c>
       <c r="E19">
-        <v>39.39393939393939</v>
+        <v>22.19200830306175</v>
       </c>
       <c r="F19" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D20">
-        <v>1177</v>
+        <v>8943</v>
       </c>
       <c r="E20">
-        <v>39.1941391941392</v>
+        <v>18.56357031655423</v>
       </c>
       <c r="F20" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>2021</v>
-      </c>
-      <c r="B21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21">
-        <v>373</v>
-      </c>
-      <c r="E21">
-        <v>12.42091242091242</v>
-      </c>
-      <c r="F21" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D22">
-        <v>270</v>
+        <v>133</v>
       </c>
       <c r="E22">
-        <v>8.991008991008991</v>
+        <v>41.95583596214511</v>
       </c>
       <c r="F22" t="s">
-        <v>273</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>2019</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23">
+        <v>121</v>
+      </c>
+      <c r="E23">
+        <v>38.17034700315457</v>
+      </c>
+      <c r="F23" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D24">
-        <v>2064</v>
+        <v>63</v>
       </c>
       <c r="E24">
-        <v>26.63225806451613</v>
+        <v>19.87381703470032</v>
       </c>
       <c r="F24" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>2021</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25">
-        <v>1942</v>
-      </c>
-      <c r="E25">
-        <v>25.05806451612903</v>
-      </c>
-      <c r="F25" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D26">
-        <v>1927</v>
+        <v>22897</v>
       </c>
       <c r="E26">
-        <v>24.86451612903226</v>
+        <v>47.76078930351891</v>
       </c>
       <c r="F26" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D27">
-        <v>1817</v>
+        <v>8137</v>
       </c>
       <c r="E27">
-        <v>23.44516129032258</v>
+        <v>16.97294591268434</v>
       </c>
       <c r="F27" t="s">
-        <v>274</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>2019</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28">
+        <v>7234</v>
+      </c>
+      <c r="E28">
+        <v>15.08938069710686</v>
+      </c>
+      <c r="F28" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D29">
-        <v>237</v>
+        <v>5373</v>
       </c>
       <c r="E29">
-        <v>32.20108695652174</v>
+        <v>11.20752591727332</v>
       </c>
       <c r="F29" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D30">
-        <v>234</v>
+        <v>4300</v>
       </c>
       <c r="E30">
-        <v>31.79347826086957</v>
+        <v>8.969358169416575</v>
       </c>
       <c r="F30" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>2021</v>
-      </c>
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>98</v>
-      </c>
-      <c r="D31">
-        <v>148</v>
-      </c>
-      <c r="E31">
-        <v>20.10869565217391</v>
-      </c>
-      <c r="F31" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D32">
-        <v>90</v>
+        <v>364</v>
       </c>
       <c r="E32">
-        <v>12.22826086956522</v>
+        <v>39.09774436090225</v>
       </c>
       <c r="F32" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D33">
-        <v>27</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>3.668478260869565</v>
+        <v>36.62728249194414</v>
       </c>
       <c r="F33" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>2021</v>
-      </c>
-      <c r="B35" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35">
-        <v>186</v>
-      </c>
-      <c r="E35">
-        <v>40</v>
-      </c>
-      <c r="F35" t="s">
-        <v>276</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>2019</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34">
+        <v>226</v>
+      </c>
+      <c r="E34">
+        <v>24.2749731471536</v>
+      </c>
+      <c r="F34" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B36" t="s">
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D36">
-        <v>96</v>
+        <v>1283</v>
       </c>
       <c r="E36">
-        <v>20.64516129032258</v>
+        <v>40.52432090966519</v>
       </c>
       <c r="F36" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B37" t="s">
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D37">
-        <v>95</v>
+        <v>954</v>
       </c>
       <c r="E37">
-        <v>20.43010752688172</v>
+        <v>30.13265950726469</v>
       </c>
       <c r="F37" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D38">
-        <v>88</v>
+        <v>746</v>
       </c>
       <c r="E38">
-        <v>18.9247311827957</v>
+        <v>23.56285533796589</v>
       </c>
       <c r="F38" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>2021</v>
-      </c>
-      <c r="B40" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40">
-        <v>154</v>
-      </c>
-      <c r="E40">
-        <v>39.58868894601542</v>
-      </c>
-      <c r="F40" t="s">
-        <v>276</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>2019</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39">
+        <v>183</v>
+      </c>
+      <c r="E39">
+        <v>5.780164245104232</v>
+      </c>
+      <c r="F39" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B41" t="s">
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D41">
-        <v>144</v>
+        <v>1446</v>
       </c>
       <c r="E41">
-        <v>37.01799485861182</v>
+        <v>41.84027777777778</v>
       </c>
       <c r="F41" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B42" t="s">
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D42">
-        <v>91</v>
+        <v>1091</v>
       </c>
       <c r="E42">
-        <v>23.39331619537275</v>
+        <v>31.56828703703703</v>
       </c>
       <c r="F42" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>2021</v>
-      </c>
-      <c r="B44" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" t="s">
-        <v>108</v>
-      </c>
-      <c r="D44">
-        <v>588</v>
-      </c>
-      <c r="E44">
-        <v>48.83720930232558</v>
-      </c>
-      <c r="F44" t="s">
-        <v>277</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>2019</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43">
+        <v>919</v>
+      </c>
+      <c r="E43">
+        <v>26.59143518518519</v>
+      </c>
+      <c r="F43" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2028,16 +2148,16 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D45">
-        <v>379</v>
+        <v>3420</v>
       </c>
       <c r="E45">
-        <v>31.47840531561462</v>
+        <v>42.77673545966229</v>
       </c>
       <c r="F45" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2048,36 +2168,36 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D46">
-        <v>237</v>
+        <v>2391</v>
       </c>
       <c r="E46">
-        <v>19.6843853820598</v>
+        <v>29.90619136960601</v>
       </c>
       <c r="F46" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>2021</v>
-      </c>
-      <c r="B48" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48" t="s">
-        <v>111</v>
-      </c>
-      <c r="D48">
-        <v>522</v>
-      </c>
-      <c r="E48">
-        <v>48.33333333333334</v>
-      </c>
-      <c r="F48" t="s">
-        <v>273</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>2021</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D47">
+        <v>2184</v>
+      </c>
+      <c r="E47">
+        <v>27.31707317073171</v>
+      </c>
+      <c r="F47" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2088,16 +2208,16 @@
         <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D49">
-        <v>331</v>
+        <v>572</v>
       </c>
       <c r="E49">
-        <v>30.64814814814815</v>
+        <v>47.03947368421053</v>
       </c>
       <c r="F49" t="s">
-        <v>273</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2108,36 +2228,36 @@
         <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D50">
-        <v>227</v>
+        <v>380</v>
       </c>
       <c r="E50">
-        <v>21.01851851851852</v>
+        <v>31.25</v>
       </c>
       <c r="F50" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>2021</v>
-      </c>
-      <c r="B52" t="s">
-        <v>22</v>
-      </c>
-      <c r="C52" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52">
-        <v>4922</v>
-      </c>
-      <c r="E52">
-        <v>41.68713475057169</v>
-      </c>
-      <c r="F52" t="s">
-        <v>270</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>2021</v>
+      </c>
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51">
+        <v>264</v>
+      </c>
+      <c r="E51">
+        <v>21.71052631578948</v>
+      </c>
+      <c r="F51" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2148,16 +2268,16 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="D53">
-        <v>4820</v>
+        <v>177</v>
       </c>
       <c r="E53">
-        <v>40.82324045058016</v>
+        <v>39.95485327313769</v>
       </c>
       <c r="F53" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2168,16 +2288,36 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="D54">
-        <v>2065</v>
+        <v>141</v>
       </c>
       <c r="E54">
-        <v>17.48962479884814</v>
+        <v>31.82844243792325</v>
       </c>
       <c r="F54" t="s">
-        <v>270</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>2021</v>
+      </c>
+      <c r="B55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55">
+        <v>81</v>
+      </c>
+      <c r="E55">
+        <v>18.2844243792325</v>
+      </c>
+      <c r="F55" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2185,39 +2325,19 @@
         <v>2021</v>
       </c>
       <c r="B56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D56">
-        <v>1281</v>
+        <v>44</v>
       </c>
       <c r="E56">
-        <v>43.88489208633094</v>
+        <v>9.932279909706546</v>
       </c>
       <c r="F56" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>2021</v>
-      </c>
-      <c r="B57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C57" t="s">
-        <v>115</v>
-      </c>
-      <c r="D57">
-        <v>924</v>
-      </c>
-      <c r="E57">
-        <v>31.6546762589928</v>
-      </c>
-      <c r="F57" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2228,16 +2348,36 @@
         <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D58">
-        <v>714</v>
+        <v>1471</v>
       </c>
       <c r="E58">
-        <v>24.46043165467626</v>
+        <v>44.12117576484703</v>
       </c>
       <c r="F58" t="s">
-        <v>277</v>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>2021</v>
+      </c>
+      <c r="B59" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" t="s">
+        <v>129</v>
+      </c>
+      <c r="D59">
+        <v>1247</v>
+      </c>
+      <c r="E59">
+        <v>37.40251949610078</v>
+      </c>
+      <c r="F59" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2245,39 +2385,19 @@
         <v>2021</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D60">
-        <v>999</v>
+        <v>616</v>
       </c>
       <c r="E60">
-        <v>49.47994056463596</v>
+        <v>18.47630473905219</v>
       </c>
       <c r="F60" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>2021</v>
-      </c>
-      <c r="B61" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61">
-        <v>629</v>
-      </c>
-      <c r="E61">
-        <v>31.15403665180783</v>
-      </c>
-      <c r="F61" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2288,16 +2408,36 @@
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D62">
-        <v>391</v>
+        <v>1183</v>
       </c>
       <c r="E62">
-        <v>19.36602278355622</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="F62" t="s">
-        <v>277</v>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>2021</v>
+      </c>
+      <c r="B63" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" t="s">
+        <v>132</v>
+      </c>
+      <c r="D63">
+        <v>1177</v>
+      </c>
+      <c r="E63">
+        <v>39.1941391941392</v>
+      </c>
+      <c r="F63" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2305,19 +2445,19 @@
         <v>2021</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="D64">
-        <v>1779</v>
+        <v>373</v>
       </c>
       <c r="E64">
-        <v>46.82811266122664</v>
+        <v>12.42091242091242</v>
       </c>
       <c r="F64" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2325,39 +2465,39 @@
         <v>2021</v>
       </c>
       <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D65">
+        <v>270</v>
+      </c>
+      <c r="E65">
+        <v>8.991008991008991</v>
+      </c>
+      <c r="F65" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>2021</v>
+      </c>
+      <c r="B67" t="s">
         <v>25</v>
       </c>
-      <c r="C65" t="s">
-        <v>79</v>
-      </c>
-      <c r="D65">
-        <v>1349</v>
-      </c>
-      <c r="E65">
-        <v>35.50934456435904</v>
-      </c>
-      <c r="F65" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>2021</v>
-      </c>
-      <c r="B66" t="s">
-        <v>25</v>
-      </c>
-      <c r="C66" t="s">
-        <v>80</v>
-      </c>
-      <c r="D66">
-        <v>671</v>
-      </c>
-      <c r="E66">
-        <v>17.66254277441432</v>
-      </c>
-      <c r="F66" t="s">
-        <v>270</v>
+      <c r="C67" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67">
+        <v>2064</v>
+      </c>
+      <c r="E67">
+        <v>26.63225806451613</v>
+      </c>
+      <c r="F67" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2365,19 +2505,19 @@
         <v>2021</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="D68">
-        <v>253</v>
+        <v>1942</v>
       </c>
       <c r="E68">
-        <v>37.09677419354838</v>
+        <v>25.05806451612903</v>
       </c>
       <c r="F68" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2385,19 +2525,19 @@
         <v>2021</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="D69">
-        <v>224</v>
+        <v>1927</v>
       </c>
       <c r="E69">
-        <v>32.84457478005865</v>
+        <v>24.86451612903226</v>
       </c>
       <c r="F69" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2405,39 +2545,19 @@
         <v>2021</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D70">
-        <v>122</v>
+        <v>1817</v>
       </c>
       <c r="E70">
-        <v>17.88856304985337</v>
+        <v>23.44516129032258</v>
       </c>
       <c r="F70" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>2021</v>
-      </c>
-      <c r="B71" t="s">
-        <v>26</v>
-      </c>
-      <c r="C71" t="s">
-        <v>84</v>
-      </c>
-      <c r="D71">
-        <v>60</v>
-      </c>
-      <c r="E71">
-        <v>8.797653958944283</v>
-      </c>
-      <c r="F71" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2448,16 +2568,36 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="D72">
-        <v>23</v>
+        <v>237</v>
       </c>
       <c r="E72">
-        <v>3.372434017595308</v>
+        <v>32.20108695652174</v>
       </c>
       <c r="F72" t="s">
-        <v>271</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>2021</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>140</v>
+      </c>
+      <c r="D73">
+        <v>234</v>
+      </c>
+      <c r="E73">
+        <v>31.79347826086957</v>
+      </c>
+      <c r="F73" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2465,19 +2605,19 @@
         <v>2021</v>
       </c>
       <c r="B74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="D74">
-        <v>917</v>
+        <v>148</v>
       </c>
       <c r="E74">
-        <v>36.31683168316832</v>
+        <v>20.10869565217391</v>
       </c>
       <c r="F74" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2485,19 +2625,19 @@
         <v>2021</v>
       </c>
       <c r="B75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="D75">
-        <v>706</v>
+        <v>90</v>
       </c>
       <c r="E75">
-        <v>27.96039603960396</v>
+        <v>12.22826086956522</v>
       </c>
       <c r="F75" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2505,39 +2645,39 @@
         <v>2021</v>
       </c>
       <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>143</v>
+      </c>
+      <c r="D76">
         <v>27</v>
       </c>
-      <c r="C76" t="s">
-        <v>88</v>
-      </c>
-      <c r="D76">
-        <v>578</v>
-      </c>
       <c r="E76">
-        <v>22.89108910891089</v>
+        <v>3.668478260869565</v>
       </c>
       <c r="F76" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>2021</v>
-      </c>
-      <c r="B77" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>2021</v>
+      </c>
+      <c r="B78" t="s">
         <v>27</v>
       </c>
-      <c r="C77" t="s">
-        <v>91</v>
-      </c>
-      <c r="D77">
-        <v>324</v>
-      </c>
-      <c r="E77">
-        <v>12.83168316831683</v>
-      </c>
-      <c r="F77" t="s">
-        <v>273</v>
+      <c r="C78" t="s">
+        <v>144</v>
+      </c>
+      <c r="D78">
+        <v>186</v>
+      </c>
+      <c r="E78">
+        <v>40</v>
+      </c>
+      <c r="F78" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2545,19 +2685,19 @@
         <v>2021</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D79">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="E79">
-        <v>41.38888888888889</v>
+        <v>20.64516129032258</v>
       </c>
       <c r="F79" t="s">
-        <v>277</v>
+        <v>317</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2565,19 +2705,19 @@
         <v>2021</v>
       </c>
       <c r="B80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D80">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E80">
-        <v>31.38888888888889</v>
+        <v>20.43010752688172</v>
       </c>
       <c r="F80" t="s">
-        <v>277</v>
+        <v>317</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2585,39 +2725,39 @@
         <v>2021</v>
       </c>
       <c r="B81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81" t="s">
+        <v>147</v>
+      </c>
+      <c r="D81">
+        <v>88</v>
+      </c>
+      <c r="E81">
+        <v>18.9247311827957</v>
+      </c>
+      <c r="F81" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>2021</v>
+      </c>
+      <c r="B83" t="s">
         <v>28</v>
       </c>
-      <c r="C81" t="s">
-        <v>123</v>
-      </c>
-      <c r="D81">
-        <v>59</v>
-      </c>
-      <c r="E81">
-        <v>16.38888888888889</v>
-      </c>
-      <c r="F81" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>2021</v>
-      </c>
-      <c r="B82" t="s">
-        <v>28</v>
-      </c>
-      <c r="C82" t="s">
-        <v>124</v>
-      </c>
-      <c r="D82">
-        <v>39</v>
-      </c>
-      <c r="E82">
-        <v>10.83333333333333</v>
-      </c>
-      <c r="F82" t="s">
-        <v>277</v>
+      <c r="C83" t="s">
+        <v>148</v>
+      </c>
+      <c r="D83">
+        <v>154</v>
+      </c>
+      <c r="E83">
+        <v>39.58868894601542</v>
+      </c>
+      <c r="F83" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2625,19 +2765,19 @@
         <v>2021</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="D84">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="E84">
-        <v>45.31645569620253</v>
+        <v>37.01799485861182</v>
       </c>
       <c r="F84" t="s">
-        <v>278</v>
+        <v>317</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2645,39 +2785,39 @@
         <v>2021</v>
       </c>
       <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="s">
+        <v>150</v>
+      </c>
+      <c r="D85">
+        <v>91</v>
+      </c>
+      <c r="E85">
+        <v>23.39331619537275</v>
+      </c>
+      <c r="F85" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>2021</v>
+      </c>
+      <c r="B87" t="s">
         <v>29</v>
       </c>
-      <c r="C85" t="s">
-        <v>126</v>
-      </c>
-      <c r="D85">
-        <v>110</v>
-      </c>
-      <c r="E85">
-        <v>27.84810126582278</v>
-      </c>
-      <c r="F85" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>2021</v>
-      </c>
-      <c r="B86" t="s">
-        <v>29</v>
-      </c>
-      <c r="C86" t="s">
-        <v>127</v>
-      </c>
-      <c r="D86">
-        <v>106</v>
-      </c>
-      <c r="E86">
-        <v>26.83544303797468</v>
-      </c>
-      <c r="F86" t="s">
-        <v>278</v>
+      <c r="C87" t="s">
+        <v>151</v>
+      </c>
+      <c r="D87">
+        <v>588</v>
+      </c>
+      <c r="E87">
+        <v>48.83720930232558</v>
+      </c>
+      <c r="F87" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2685,19 +2825,19 @@
         <v>2021</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D88">
-        <v>276</v>
+        <v>379</v>
       </c>
       <c r="E88">
-        <v>47.01873935264054</v>
+        <v>31.47840531561462</v>
       </c>
       <c r="F88" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2705,39 +2845,39 @@
         <v>2021</v>
       </c>
       <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" t="s">
+        <v>153</v>
+      </c>
+      <c r="D89">
+        <v>237</v>
+      </c>
+      <c r="E89">
+        <v>19.6843853820598</v>
+      </c>
+      <c r="F89" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>2021</v>
+      </c>
+      <c r="B91" t="s">
         <v>30</v>
       </c>
-      <c r="C89" t="s">
-        <v>129</v>
-      </c>
-      <c r="D89">
-        <v>226</v>
-      </c>
-      <c r="E89">
-        <v>38.50085178875639</v>
-      </c>
-      <c r="F89" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>2021</v>
-      </c>
-      <c r="B90" t="s">
-        <v>30</v>
-      </c>
-      <c r="C90" t="s">
-        <v>130</v>
-      </c>
-      <c r="D90">
-        <v>85</v>
-      </c>
-      <c r="E90">
-        <v>14.48040885860307</v>
-      </c>
-      <c r="F90" t="s">
-        <v>274</v>
+      <c r="C91" t="s">
+        <v>154</v>
+      </c>
+      <c r="D91">
+        <v>522</v>
+      </c>
+      <c r="E91">
+        <v>48.33333333333334</v>
+      </c>
+      <c r="F91" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2745,19 +2885,19 @@
         <v>2021</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="D92">
-        <v>636</v>
+        <v>331</v>
       </c>
       <c r="E92">
-        <v>41.24513618677042</v>
+        <v>30.64814814814815</v>
       </c>
       <c r="F92" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2765,719 +2905,699 @@
         <v>2021</v>
       </c>
       <c r="B93" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93" t="s">
+        <v>156</v>
+      </c>
+      <c r="D93">
+        <v>227</v>
+      </c>
+      <c r="E93">
+        <v>21.01851851851852</v>
+      </c>
+      <c r="F93" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>2021</v>
+      </c>
+      <c r="B95" t="s">
         <v>31</v>
       </c>
-      <c r="C93" t="s">
-        <v>132</v>
-      </c>
-      <c r="D93">
-        <v>544</v>
-      </c>
-      <c r="E93">
-        <v>35.27885862516213</v>
-      </c>
-      <c r="F93" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>2021</v>
-      </c>
-      <c r="B94" t="s">
-        <v>31</v>
-      </c>
-      <c r="C94" t="s">
-        <v>133</v>
-      </c>
-      <c r="D94">
-        <v>362</v>
-      </c>
-      <c r="E94">
-        <v>23.47600518806744</v>
-      </c>
-      <c r="F94" t="s">
-        <v>274</v>
+      <c r="C95" t="s">
+        <v>120</v>
+      </c>
+      <c r="D95">
+        <v>4922</v>
+      </c>
+      <c r="E95">
+        <v>41.68713475057169</v>
+      </c>
+      <c r="F95" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C96" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D96">
-        <v>104</v>
+        <v>4820</v>
       </c>
       <c r="E96">
-        <v>38.95131086142322</v>
+        <v>40.82324045058016</v>
       </c>
       <c r="F96" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B97" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" t="s">
+        <v>119</v>
+      </c>
+      <c r="D97">
+        <v>2065</v>
+      </c>
+      <c r="E97">
+        <v>17.48962479884814</v>
+      </c>
+      <c r="F97" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>2021</v>
+      </c>
+      <c r="B99" t="s">
         <v>32</v>
       </c>
-      <c r="C97" t="s">
-        <v>135</v>
-      </c>
-      <c r="D97">
-        <v>100</v>
-      </c>
-      <c r="E97">
-        <v>37.45318352059925</v>
-      </c>
-      <c r="F97" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>2023</v>
-      </c>
-      <c r="B98" t="s">
-        <v>32</v>
-      </c>
-      <c r="C98" t="s">
-        <v>136</v>
-      </c>
-      <c r="D98">
-        <v>63</v>
-      </c>
-      <c r="E98">
-        <v>23.59550561797753</v>
-      </c>
-      <c r="F98" t="s">
-        <v>279</v>
+      <c r="C99" t="s">
+        <v>157</v>
+      </c>
+      <c r="D99">
+        <v>1281</v>
+      </c>
+      <c r="E99">
+        <v>43.88489208633094</v>
+      </c>
+      <c r="F99" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="D100">
-        <v>882</v>
+        <v>924</v>
       </c>
       <c r="E100">
-        <v>45.60496380558428</v>
+        <v>31.6546762589928</v>
       </c>
       <c r="F100" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C101" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="D101">
-        <v>502</v>
+        <v>714</v>
       </c>
       <c r="E101">
-        <v>25.95656670113754</v>
+        <v>24.46043165467626</v>
       </c>
       <c r="F101" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>2023</v>
-      </c>
-      <c r="B102" t="s">
-        <v>33</v>
-      </c>
-      <c r="C102" t="s">
-        <v>139</v>
-      </c>
-      <c r="D102">
-        <v>399</v>
-      </c>
-      <c r="E102">
-        <v>20.63081695966908</v>
-      </c>
-      <c r="F102" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B103" t="s">
         <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D103">
-        <v>151</v>
+        <v>999</v>
       </c>
       <c r="E103">
-        <v>7.807652533609101</v>
+        <v>49.47994056463596</v>
       </c>
       <c r="F103" t="s">
-        <v>277</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104">
+        <v>2021</v>
+      </c>
+      <c r="B104" t="s">
+        <v>33</v>
+      </c>
+      <c r="C104" t="s">
+        <v>161</v>
+      </c>
+      <c r="D104">
+        <v>629</v>
+      </c>
+      <c r="E104">
+        <v>31.15403665180783</v>
+      </c>
+      <c r="F104" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="D105">
-        <v>445</v>
+        <v>391</v>
       </c>
       <c r="E105">
-        <v>43.28793774319066</v>
+        <v>19.36602278355622</v>
       </c>
       <c r="F105" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>2023</v>
-      </c>
-      <c r="B106" t="s">
-        <v>34</v>
-      </c>
-      <c r="C106" t="s">
-        <v>142</v>
-      </c>
-      <c r="D106">
-        <v>353</v>
-      </c>
-      <c r="E106">
-        <v>34.33852140077821</v>
-      </c>
-      <c r="F106" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B107" t="s">
         <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D107">
-        <v>230</v>
+        <v>1779</v>
       </c>
       <c r="E107">
-        <v>22.37354085603113</v>
+        <v>46.82811266122664</v>
       </c>
       <c r="F107" t="s">
-        <v>280</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108">
+        <v>2021</v>
+      </c>
+      <c r="B108" t="s">
+        <v>34</v>
+      </c>
+      <c r="C108" t="s">
+        <v>122</v>
+      </c>
+      <c r="D108">
+        <v>1349</v>
+      </c>
+      <c r="E108">
+        <v>35.50934456435904</v>
+      </c>
+      <c r="F108" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="D109">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="E109">
-        <v>46.94577899794098</v>
+        <v>17.66254277441432</v>
       </c>
       <c r="F109" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>2023</v>
-      </c>
-      <c r="B110" t="s">
-        <v>35</v>
-      </c>
-      <c r="C110" t="s">
-        <v>145</v>
-      </c>
-      <c r="D110">
-        <v>395</v>
-      </c>
-      <c r="E110">
-        <v>27.1105010295127</v>
-      </c>
-      <c r="F110" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B111" t="s">
         <v>35</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D111">
-        <v>378</v>
+        <v>253</v>
       </c>
       <c r="E111">
-        <v>25.94371997254633</v>
+        <v>37.09677419354838</v>
       </c>
       <c r="F111" t="s">
-        <v>280</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112">
+        <v>2021</v>
+      </c>
+      <c r="B112" t="s">
+        <v>35</v>
+      </c>
+      <c r="C112" t="s">
+        <v>126</v>
+      </c>
+      <c r="D112">
+        <v>224</v>
+      </c>
+      <c r="E112">
+        <v>32.84457478005865</v>
+      </c>
+      <c r="F112" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B113" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="D113">
-        <v>828</v>
+        <v>122</v>
       </c>
       <c r="E113">
-        <v>36.71840354767184</v>
+        <v>17.88856304985337</v>
       </c>
       <c r="F113" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B114" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="D114">
-        <v>524</v>
+        <v>60</v>
       </c>
       <c r="E114">
-        <v>23.23725055432372</v>
+        <v>8.797653958944283</v>
       </c>
       <c r="F114" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="D115">
-        <v>485</v>
+        <v>23</v>
       </c>
       <c r="E115">
-        <v>21.50776053215078</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="F115" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>2023</v>
-      </c>
-      <c r="B116" t="s">
-        <v>36</v>
-      </c>
-      <c r="C116" t="s">
-        <v>150</v>
-      </c>
-      <c r="D116">
-        <v>261</v>
-      </c>
-      <c r="E116">
-        <v>11.57427937915743</v>
-      </c>
-      <c r="F116" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B117" t="s">
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="D117">
-        <v>157</v>
+        <v>917</v>
       </c>
       <c r="E117">
-        <v>6.962305986696231</v>
+        <v>36.31683168316832</v>
       </c>
       <c r="F117" t="s">
-        <v>272</v>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118">
+        <v>2021</v>
+      </c>
+      <c r="B118" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" t="s">
+        <v>132</v>
+      </c>
+      <c r="D118">
+        <v>706</v>
+      </c>
+      <c r="E118">
+        <v>27.96039603960396</v>
+      </c>
+      <c r="F118" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C119" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D119">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="E119">
-        <v>43.90977443609022</v>
+        <v>22.89108910891089</v>
       </c>
       <c r="F119" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B120" t="s">
+        <v>36</v>
+      </c>
+      <c r="C120" t="s">
+        <v>134</v>
+      </c>
+      <c r="D120">
+        <v>324</v>
+      </c>
+      <c r="E120">
+        <v>12.83168316831683</v>
+      </c>
+      <c r="F120" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122">
+        <v>2021</v>
+      </c>
+      <c r="B122" t="s">
         <v>37</v>
       </c>
-      <c r="C120" t="s">
-        <v>153</v>
-      </c>
-      <c r="D120">
-        <v>388</v>
-      </c>
-      <c r="E120">
-        <v>29.17293233082707</v>
-      </c>
-      <c r="F120" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>2023</v>
-      </c>
-      <c r="B121" t="s">
-        <v>37</v>
-      </c>
-      <c r="C121" t="s">
-        <v>154</v>
-      </c>
-      <c r="D121">
-        <v>358</v>
-      </c>
-      <c r="E121">
-        <v>26.91729323308271</v>
-      </c>
-      <c r="F121" t="s">
-        <v>281</v>
+      <c r="C122" t="s">
+        <v>164</v>
+      </c>
+      <c r="D122">
+        <v>149</v>
+      </c>
+      <c r="E122">
+        <v>41.38888888888889</v>
+      </c>
+      <c r="F122" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B123" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C123" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D123">
-        <v>634</v>
+        <v>113</v>
       </c>
       <c r="E123">
-        <v>45.67723342939482</v>
+        <v>31.38888888888889</v>
       </c>
       <c r="F123" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C124" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D124">
-        <v>298</v>
+        <v>59</v>
       </c>
       <c r="E124">
-        <v>21.46974063400576</v>
+        <v>16.38888888888889</v>
       </c>
       <c r="F124" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B125" t="s">
+        <v>37</v>
+      </c>
+      <c r="C125" t="s">
+        <v>167</v>
+      </c>
+      <c r="D125">
+        <v>39</v>
+      </c>
+      <c r="E125">
+        <v>10.83333333333333</v>
+      </c>
+      <c r="F125" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127">
+        <v>2021</v>
+      </c>
+      <c r="B127" t="s">
         <v>38</v>
       </c>
-      <c r="C125" t="s">
-        <v>157</v>
-      </c>
-      <c r="D125">
-        <v>246</v>
-      </c>
-      <c r="E125">
-        <v>17.72334293948127</v>
-      </c>
-      <c r="F125" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>2023</v>
-      </c>
-      <c r="B126" t="s">
-        <v>38</v>
-      </c>
-      <c r="C126" t="s">
-        <v>158</v>
-      </c>
-      <c r="D126">
-        <v>210</v>
-      </c>
-      <c r="E126">
-        <v>15.12968299711815</v>
-      </c>
-      <c r="F126" t="s">
-        <v>281</v>
+      <c r="C127" t="s">
+        <v>168</v>
+      </c>
+      <c r="D127">
+        <v>179</v>
+      </c>
+      <c r="E127">
+        <v>45.31645569620253</v>
+      </c>
+      <c r="F127" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B128" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C128" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D128">
-        <v>294</v>
+        <v>110</v>
       </c>
       <c r="E128">
-        <v>38.33116036505867</v>
+        <v>27.84810126582278</v>
       </c>
       <c r="F128" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B129" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C129" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D129">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="E129">
-        <v>18.90482398956975</v>
+        <v>26.83544303797468</v>
       </c>
       <c r="F129" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>2023</v>
-      </c>
-      <c r="B130" t="s">
-        <v>39</v>
-      </c>
-      <c r="C130" t="s">
-        <v>161</v>
-      </c>
-      <c r="D130">
-        <v>136</v>
-      </c>
-      <c r="E130">
-        <v>17.73142112125163</v>
-      </c>
-      <c r="F130" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B131" t="s">
         <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D131">
-        <v>104</v>
+        <v>276</v>
       </c>
       <c r="E131">
-        <v>13.5593220338983</v>
+        <v>47.01873935264054</v>
       </c>
       <c r="F131" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B132" t="s">
         <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D132">
-        <v>88</v>
+        <v>226</v>
       </c>
       <c r="E132">
-        <v>11.47327249022164</v>
+        <v>38.50085178875639</v>
       </c>
       <c r="F132" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>2023</v>
-      </c>
-      <c r="B134" t="s">
-        <v>40</v>
-      </c>
-      <c r="C134" t="s">
-        <v>164</v>
-      </c>
-      <c r="D134">
-        <v>170</v>
-      </c>
-      <c r="E134">
-        <v>46.19565217391305</v>
-      </c>
-      <c r="F134" t="s">
-        <v>273</v>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133">
+        <v>2021</v>
+      </c>
+      <c r="B133" t="s">
+        <v>39</v>
+      </c>
+      <c r="C133" t="s">
+        <v>173</v>
+      </c>
+      <c r="D133">
+        <v>85</v>
+      </c>
+      <c r="E133">
+        <v>14.48040885860307</v>
+      </c>
+      <c r="F133" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B135" t="s">
         <v>40</v>
       </c>
       <c r="C135" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D135">
-        <v>169</v>
+        <v>636</v>
       </c>
       <c r="E135">
-        <v>45.92391304347826</v>
+        <v>41.24513618677042</v>
       </c>
       <c r="F135" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B136" t="s">
         <v>40</v>
       </c>
       <c r="C136" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D136">
-        <v>29</v>
+        <v>544</v>
       </c>
       <c r="E136">
-        <v>7.880434782608696</v>
+        <v>35.27885862516213</v>
       </c>
       <c r="F136" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>2023</v>
-      </c>
-      <c r="B138" t="s">
-        <v>41</v>
-      </c>
-      <c r="C138" t="s">
-        <v>137</v>
-      </c>
-      <c r="D138">
-        <v>1114</v>
-      </c>
-      <c r="E138">
-        <v>47.79064779064779</v>
-      </c>
-      <c r="F138" t="s">
-        <v>277</v>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137">
+        <v>2021</v>
+      </c>
+      <c r="B137" t="s">
+        <v>40</v>
+      </c>
+      <c r="C137" t="s">
+        <v>176</v>
+      </c>
+      <c r="D137">
+        <v>362</v>
+      </c>
+      <c r="E137">
+        <v>23.47600518806744</v>
+      </c>
+      <c r="F137" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3488,16 +3608,16 @@
         <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="D139">
-        <v>647</v>
+        <v>104</v>
       </c>
       <c r="E139">
-        <v>27.75632775632776</v>
+        <v>38.95131086142322</v>
       </c>
       <c r="F139" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3508,16 +3628,16 @@
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="D140">
-        <v>369</v>
+        <v>100</v>
       </c>
       <c r="E140">
-        <v>15.83011583011583</v>
+        <v>37.45318352059925</v>
       </c>
       <c r="F140" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3528,16 +3648,16 @@
         <v>41</v>
       </c>
       <c r="C141" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="D141">
-        <v>201</v>
+        <v>63</v>
       </c>
       <c r="E141">
-        <v>8.622908622908623</v>
+        <v>23.59550561797753</v>
       </c>
       <c r="F141" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3548,16 +3668,16 @@
         <v>42</v>
       </c>
       <c r="C143" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="D143">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="E143">
-        <v>48.86927744070601</v>
+        <v>45.60496380558428</v>
       </c>
       <c r="F143" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3568,16 +3688,16 @@
         <v>42</v>
       </c>
       <c r="C144" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="D144">
-        <v>699</v>
+        <v>502</v>
       </c>
       <c r="E144">
-        <v>38.55488141202427</v>
+        <v>25.95656670113754</v>
       </c>
       <c r="F144" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3588,36 +3708,36 @@
         <v>42</v>
       </c>
       <c r="C145" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="D145">
-        <v>228</v>
+        <v>399</v>
       </c>
       <c r="E145">
-        <v>12.57584114726972</v>
+        <v>20.63081695966908</v>
       </c>
       <c r="F145" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>2023</v>
-      </c>
-      <c r="B147" t="s">
-        <v>43</v>
-      </c>
-      <c r="C147" t="s">
-        <v>144</v>
-      </c>
-      <c r="D147">
-        <v>1630</v>
-      </c>
-      <c r="E147">
-        <v>44.46262956901255</v>
-      </c>
-      <c r="F147" t="s">
-        <v>280</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146">
+        <v>2023</v>
+      </c>
+      <c r="B146" t="s">
+        <v>42</v>
+      </c>
+      <c r="C146" t="s">
+        <v>183</v>
+      </c>
+      <c r="D146">
+        <v>151</v>
+      </c>
+      <c r="E146">
+        <v>7.807652533609101</v>
+      </c>
+      <c r="F146" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3628,16 +3748,16 @@
         <v>43</v>
       </c>
       <c r="C148" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="D148">
-        <v>1039</v>
+        <v>445</v>
       </c>
       <c r="E148">
-        <v>28.34151663938898</v>
+        <v>43.28793774319066</v>
       </c>
       <c r="F148" t="s">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3648,16 +3768,16 @@
         <v>43</v>
       </c>
       <c r="C149" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="D149">
-        <v>813</v>
+        <v>353</v>
       </c>
       <c r="E149">
-        <v>22.17675941080196</v>
+        <v>34.33852140077821</v>
       </c>
       <c r="F149" t="s">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3668,16 +3788,16 @@
         <v>43</v>
       </c>
       <c r="C150" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="D150">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="E150">
-        <v>5.019094380796509</v>
+        <v>22.37354085603113</v>
       </c>
       <c r="F150" t="s">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -3688,16 +3808,16 @@
         <v>44</v>
       </c>
       <c r="C152" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="D152">
-        <v>1334</v>
+        <v>684</v>
       </c>
       <c r="E152">
-        <v>46.38386648122393</v>
+        <v>46.94577899794098</v>
       </c>
       <c r="F152" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3708,16 +3828,16 @@
         <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="D153">
-        <v>1278</v>
+        <v>395</v>
       </c>
       <c r="E153">
-        <v>44.43671766342142</v>
+        <v>27.1105010295127</v>
       </c>
       <c r="F153" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3728,16 +3848,16 @@
         <v>44</v>
       </c>
       <c r="C154" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="D154">
-        <v>264</v>
+        <v>378</v>
       </c>
       <c r="E154">
-        <v>9.179415855354661</v>
+        <v>25.94371997254633</v>
       </c>
       <c r="F154" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3748,16 +3868,16 @@
         <v>45</v>
       </c>
       <c r="C156" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="D156">
-        <v>1466</v>
+        <v>828</v>
       </c>
       <c r="E156">
-        <v>43.1303324507208</v>
+        <v>36.71840354767184</v>
       </c>
       <c r="F156" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -3768,16 +3888,16 @@
         <v>45</v>
       </c>
       <c r="C157" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="D157">
-        <v>893</v>
+        <v>524</v>
       </c>
       <c r="E157">
-        <v>26.27243306854957</v>
+        <v>23.23725055432372</v>
       </c>
       <c r="F157" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -3788,16 +3908,16 @@
         <v>45</v>
       </c>
       <c r="C158" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="D158">
-        <v>672</v>
+        <v>485</v>
       </c>
       <c r="E158">
-        <v>19.77052074139453</v>
+        <v>21.50776053215078</v>
       </c>
       <c r="F158" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -3808,16 +3928,16 @@
         <v>45</v>
       </c>
       <c r="C159" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="D159">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="E159">
-        <v>7.208002353633422</v>
+        <v>11.57427937915743</v>
       </c>
       <c r="F159" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -3828,16 +3948,16 @@
         <v>45</v>
       </c>
       <c r="C160" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="D160">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="E160">
-        <v>3.618711385701677</v>
+        <v>6.962305986696231</v>
       </c>
       <c r="F160" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -3848,16 +3968,16 @@
         <v>46</v>
       </c>
       <c r="C162" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="D162">
-        <v>1108</v>
+        <v>584</v>
       </c>
       <c r="E162">
-        <v>46.4765100671141</v>
+        <v>43.90977443609022</v>
       </c>
       <c r="F162" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -3868,16 +3988,16 @@
         <v>46</v>
       </c>
       <c r="C163" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="D163">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="E163">
-        <v>18.6241610738255</v>
+        <v>29.17293233082707</v>
       </c>
       <c r="F163" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -3888,36 +4008,16 @@
         <v>46</v>
       </c>
       <c r="C164" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="D164">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="E164">
-        <v>14.38758389261745</v>
+        <v>26.91729323308271</v>
       </c>
       <c r="F164" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>2023</v>
-      </c>
-      <c r="B165" t="s">
-        <v>46</v>
-      </c>
-      <c r="C165" t="s">
-        <v>156</v>
-      </c>
-      <c r="D165">
-        <v>323</v>
-      </c>
-      <c r="E165">
-        <v>13.5486577181208</v>
-      </c>
-      <c r="F165" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -3925,19 +4025,39 @@
         <v>2023</v>
       </c>
       <c r="B166" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C166" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="D166">
-        <v>166</v>
+        <v>634</v>
       </c>
       <c r="E166">
-        <v>6.963087248322148</v>
+        <v>45.67723342939482</v>
       </c>
       <c r="F166" t="s">
-        <v>281</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167">
+        <v>2023</v>
+      </c>
+      <c r="B167" t="s">
+        <v>47</v>
+      </c>
+      <c r="C167" t="s">
+        <v>199</v>
+      </c>
+      <c r="D167">
+        <v>298</v>
+      </c>
+      <c r="E167">
+        <v>21.46974063400576</v>
+      </c>
+      <c r="F167" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -3948,16 +4068,16 @@
         <v>47</v>
       </c>
       <c r="C168" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="D168">
-        <v>904</v>
+        <v>246</v>
       </c>
       <c r="E168">
-        <v>42.60131950989632</v>
+        <v>17.72334293948127</v>
       </c>
       <c r="F168" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -3968,36 +4088,16 @@
         <v>47</v>
       </c>
       <c r="C169" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="D169">
-        <v>860</v>
+        <v>210</v>
       </c>
       <c r="E169">
-        <v>40.52780395852969</v>
+        <v>15.12968299711815</v>
       </c>
       <c r="F169" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170">
-        <v>2023</v>
-      </c>
-      <c r="B170" t="s">
-        <v>47</v>
-      </c>
-      <c r="C170" t="s">
-        <v>174</v>
-      </c>
-      <c r="D170">
-        <v>193</v>
-      </c>
-      <c r="E170">
-        <v>9.095193213949104</v>
-      </c>
-      <c r="F170" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -4005,19 +4105,39 @@
         <v>2023</v>
       </c>
       <c r="B171" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C171" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="D171">
-        <v>165</v>
+        <v>294</v>
       </c>
       <c r="E171">
-        <v>7.775683317624882</v>
+        <v>38.33116036505867</v>
       </c>
       <c r="F171" t="s">
-        <v>281</v>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172">
+        <v>2023</v>
+      </c>
+      <c r="B172" t="s">
+        <v>48</v>
+      </c>
+      <c r="C172" t="s">
+        <v>203</v>
+      </c>
+      <c r="D172">
+        <v>145</v>
+      </c>
+      <c r="E172">
+        <v>18.90482398956975</v>
+      </c>
+      <c r="F172" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4028,16 +4148,16 @@
         <v>48</v>
       </c>
       <c r="C173" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="D173">
-        <v>425</v>
+        <v>136</v>
       </c>
       <c r="E173">
-        <v>25.11820330969267</v>
+        <v>17.73142112125163</v>
       </c>
       <c r="F173" t="s">
-        <v>279</v>
+        <v>319</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4048,16 +4168,16 @@
         <v>48</v>
       </c>
       <c r="C174" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="D174">
-        <v>341</v>
+        <v>104</v>
       </c>
       <c r="E174">
-        <v>20.15366430260048</v>
+        <v>13.5593220338983</v>
       </c>
       <c r="F174" t="s">
-        <v>279</v>
+        <v>319</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4068,36 +4188,16 @@
         <v>48</v>
       </c>
       <c r="C175" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="D175">
-        <v>279</v>
+        <v>88</v>
       </c>
       <c r="E175">
-        <v>16.48936170212766</v>
+        <v>11.47327249022164</v>
       </c>
       <c r="F175" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176">
-        <v>2023</v>
-      </c>
-      <c r="B176" t="s">
-        <v>48</v>
-      </c>
-      <c r="C176" t="s">
-        <v>162</v>
-      </c>
-      <c r="D176">
-        <v>272</v>
-      </c>
-      <c r="E176">
-        <v>16.07565011820331</v>
-      </c>
-      <c r="F176" t="s">
-        <v>279</v>
+        <v>319</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -4105,19 +4205,19 @@
         <v>2023</v>
       </c>
       <c r="B177" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C177" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="D177">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="E177">
-        <v>13.00236406619385</v>
+        <v>46.19565217391305</v>
       </c>
       <c r="F177" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4125,39 +4225,39 @@
         <v>2023</v>
       </c>
       <c r="B178" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C178" t="s">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="D178">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E178">
-        <v>9.160756501182032</v>
+        <v>45.92391304347826</v>
       </c>
       <c r="F178" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180">
-        <v>2023</v>
-      </c>
-      <c r="B180" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179">
+        <v>2023</v>
+      </c>
+      <c r="B179" t="s">
         <v>49</v>
       </c>
-      <c r="C180" t="s">
-        <v>177</v>
-      </c>
-      <c r="D180">
-        <v>286</v>
-      </c>
-      <c r="E180">
-        <v>48.22934232715008</v>
-      </c>
-      <c r="F180" t="s">
-        <v>273</v>
+      <c r="C179" t="s">
+        <v>209</v>
+      </c>
+      <c r="D179">
+        <v>29</v>
+      </c>
+      <c r="E179">
+        <v>7.880434782608696</v>
+      </c>
+      <c r="F179" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -4165,19 +4265,19 @@
         <v>2023</v>
       </c>
       <c r="B181" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C181" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D181">
-        <v>212</v>
+        <v>1114</v>
       </c>
       <c r="E181">
-        <v>35.7504215851602</v>
+        <v>47.79064779064779</v>
       </c>
       <c r="F181" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -4185,19 +4285,39 @@
         <v>2023</v>
       </c>
       <c r="B182" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C182" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D182">
-        <v>95</v>
+        <v>647</v>
       </c>
       <c r="E182">
-        <v>16.02023608768971</v>
+        <v>27.75632775632776</v>
       </c>
       <c r="F182" t="s">
-        <v>273</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183">
+        <v>2023</v>
+      </c>
+      <c r="B183" t="s">
+        <v>50</v>
+      </c>
+      <c r="C183" t="s">
+        <v>181</v>
+      </c>
+      <c r="D183">
+        <v>369</v>
+      </c>
+      <c r="E183">
+        <v>15.83011583011583</v>
+      </c>
+      <c r="F183" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4208,36 +4328,16 @@
         <v>50</v>
       </c>
       <c r="C184" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D184">
-        <v>431</v>
+        <v>201</v>
       </c>
       <c r="E184">
-        <v>36.77474402730375</v>
+        <v>8.622908622908623</v>
       </c>
       <c r="F184" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185">
-        <v>2023</v>
-      </c>
-      <c r="B185" t="s">
-        <v>50</v>
-      </c>
-      <c r="C185" t="s">
-        <v>181</v>
-      </c>
-      <c r="D185">
-        <v>297</v>
-      </c>
-      <c r="E185">
-        <v>25.34129692832764</v>
-      </c>
-      <c r="F185" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4245,19 +4345,19 @@
         <v>2023</v>
       </c>
       <c r="B186" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C186" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D186">
-        <v>285</v>
+        <v>886</v>
       </c>
       <c r="E186">
-        <v>24.31740614334471</v>
+        <v>48.86927744070601</v>
       </c>
       <c r="F186" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4265,19 +4365,19 @@
         <v>2023</v>
       </c>
       <c r="B187" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C187" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D187">
-        <v>96</v>
+        <v>699</v>
       </c>
       <c r="E187">
-        <v>8.191126279863481</v>
+        <v>38.55488141202427</v>
       </c>
       <c r="F187" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4285,19 +4385,19 @@
         <v>2023</v>
       </c>
       <c r="B188" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C188" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D188">
-        <v>63</v>
+        <v>228</v>
       </c>
       <c r="E188">
-        <v>5.375426621160409</v>
+        <v>12.57584114726972</v>
       </c>
       <c r="F188" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4305,19 +4405,19 @@
         <v>2023</v>
       </c>
       <c r="B190" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C190" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D190">
-        <v>273</v>
+        <v>1630</v>
       </c>
       <c r="E190">
-        <v>45.4242928452579</v>
+        <v>44.46262956901255</v>
       </c>
       <c r="F190" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4325,19 +4425,19 @@
         <v>2023</v>
       </c>
       <c r="B191" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C191" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D191">
-        <v>234</v>
+        <v>1039</v>
       </c>
       <c r="E191">
-        <v>38.9351081530782</v>
+        <v>28.34151663938898</v>
       </c>
       <c r="F191" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -4345,39 +4445,39 @@
         <v>2023</v>
       </c>
       <c r="B192" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C192" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D192">
-        <v>94</v>
+        <v>813</v>
       </c>
       <c r="E192">
-        <v>15.64059900166389</v>
+        <v>22.17675941080196</v>
       </c>
       <c r="F192" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194">
-        <v>2023</v>
-      </c>
-      <c r="B194" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193">
+        <v>2023</v>
+      </c>
+      <c r="B193" t="s">
         <v>52</v>
       </c>
-      <c r="C194" t="s">
-        <v>188</v>
-      </c>
-      <c r="D194">
-        <v>124</v>
-      </c>
-      <c r="E194">
-        <v>47.69230769230769</v>
-      </c>
-      <c r="F194" t="s">
-        <v>278</v>
+      <c r="C193" t="s">
+        <v>210</v>
+      </c>
+      <c r="D193">
+        <v>184</v>
+      </c>
+      <c r="E193">
+        <v>5.019094380796509</v>
+      </c>
+      <c r="F193" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4385,19 +4485,19 @@
         <v>2023</v>
       </c>
       <c r="B195" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C195" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="D195">
-        <v>73</v>
+        <v>1334</v>
       </c>
       <c r="E195">
-        <v>28.07692307692308</v>
+        <v>46.38386648122393</v>
       </c>
       <c r="F195" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -4405,39 +4505,39 @@
         <v>2023</v>
       </c>
       <c r="B196" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C196" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="D196">
-        <v>63</v>
+        <v>1278</v>
       </c>
       <c r="E196">
-        <v>24.23076923076923</v>
+        <v>44.43671766342142</v>
       </c>
       <c r="F196" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198">
-        <v>2023</v>
-      </c>
-      <c r="B198" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197">
+        <v>2023</v>
+      </c>
+      <c r="B197" t="s">
         <v>53</v>
       </c>
-      <c r="C198" t="s">
-        <v>191</v>
-      </c>
-      <c r="D198">
-        <v>827</v>
-      </c>
-      <c r="E198">
-        <v>47.88650839606254</v>
-      </c>
-      <c r="F198" t="s">
-        <v>281</v>
+      <c r="C197" t="s">
+        <v>213</v>
+      </c>
+      <c r="D197">
+        <v>264</v>
+      </c>
+      <c r="E197">
+        <v>9.179415855354661</v>
+      </c>
+      <c r="F197" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4445,19 +4545,19 @@
         <v>2023</v>
       </c>
       <c r="B199" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C199" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D199">
-        <v>284</v>
+        <v>1466</v>
       </c>
       <c r="E199">
-        <v>16.44470179502026</v>
+        <v>43.1303324507208</v>
       </c>
       <c r="F199" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -4465,19 +4565,19 @@
         <v>2023</v>
       </c>
       <c r="B200" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C200" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D200">
-        <v>222</v>
+        <v>893</v>
       </c>
       <c r="E200">
-        <v>12.85466126230457</v>
+        <v>26.27243306854957</v>
       </c>
       <c r="F200" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4485,19 +4585,19 @@
         <v>2023</v>
       </c>
       <c r="B201" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C201" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D201">
-        <v>211</v>
+        <v>672</v>
       </c>
       <c r="E201">
-        <v>12.21771858714534</v>
+        <v>19.77052074139453</v>
       </c>
       <c r="F201" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4505,39 +4605,39 @@
         <v>2023</v>
       </c>
       <c r="B202" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C202" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D202">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="E202">
-        <v>10.59640995946728</v>
+        <v>7.208002353633422</v>
       </c>
       <c r="F202" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204">
-        <v>2023</v>
-      </c>
-      <c r="B204" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203">
+        <v>2023</v>
+      </c>
+      <c r="B203" t="s">
         <v>54</v>
       </c>
-      <c r="C204" t="s">
-        <v>196</v>
-      </c>
-      <c r="D204">
-        <v>605</v>
-      </c>
-      <c r="E204">
-        <v>41.10054347826087</v>
-      </c>
-      <c r="F204" t="s">
-        <v>280</v>
+      <c r="C203" t="s">
+        <v>190</v>
+      </c>
+      <c r="D203">
+        <v>123</v>
+      </c>
+      <c r="E203">
+        <v>3.618711385701677</v>
+      </c>
+      <c r="F203" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4545,19 +4645,19 @@
         <v>2023</v>
       </c>
       <c r="B205" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C205" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D205">
-        <v>593</v>
+        <v>1108</v>
       </c>
       <c r="E205">
-        <v>40.28532608695652</v>
+        <v>46.4765100671141</v>
       </c>
       <c r="F205" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4565,19 +4665,39 @@
         <v>2023</v>
       </c>
       <c r="B206" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C206" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D206">
-        <v>274</v>
+        <v>444</v>
       </c>
       <c r="E206">
-        <v>18.61413043478261</v>
+        <v>18.6241610738255</v>
       </c>
       <c r="F206" t="s">
-        <v>280</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207">
+        <v>2023</v>
+      </c>
+      <c r="B207" t="s">
+        <v>55</v>
+      </c>
+      <c r="C207" t="s">
+        <v>214</v>
+      </c>
+      <c r="D207">
+        <v>343</v>
+      </c>
+      <c r="E207">
+        <v>14.38758389261745</v>
+      </c>
+      <c r="F207" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4591,13 +4711,13 @@
         <v>199</v>
       </c>
       <c r="D208">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="E208">
-        <v>49.15014164305949</v>
+        <v>13.5486577181208</v>
       </c>
       <c r="F208" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4611,33 +4731,13 @@
         <v>200</v>
       </c>
       <c r="D209">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E209">
-        <v>23.79603399433428</v>
+        <v>6.963087248322148</v>
       </c>
       <c r="F209" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210">
-        <v>2023</v>
-      </c>
-      <c r="B210" t="s">
-        <v>55</v>
-      </c>
-      <c r="C210" t="s">
-        <v>201</v>
-      </c>
-      <c r="D210">
-        <v>103</v>
-      </c>
-      <c r="E210">
-        <v>14.58923512747875</v>
-      </c>
-      <c r="F210" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4645,759 +4745,779 @@
         <v>2023</v>
       </c>
       <c r="B211" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C211" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D211">
-        <v>88</v>
+        <v>904</v>
       </c>
       <c r="E211">
-        <v>12.46458923512748</v>
+        <v>42.60131950989632</v>
       </c>
       <c r="F211" t="s">
-        <v>280</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212">
+        <v>2023</v>
+      </c>
+      <c r="B212" t="s">
+        <v>56</v>
+      </c>
+      <c r="C212" t="s">
+        <v>216</v>
+      </c>
+      <c r="D212">
+        <v>860</v>
+      </c>
+      <c r="E212">
+        <v>40.52780395852969</v>
+      </c>
+      <c r="F212" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B213" t="s">
         <v>56</v>
       </c>
       <c r="C213" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="D213">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="E213">
-        <v>44.68085106382978</v>
+        <v>9.095193213949104</v>
       </c>
       <c r="F213" t="s">
-        <v>10</v>
+        <v>321</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B214" t="s">
         <v>56</v>
       </c>
       <c r="C214" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D214">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="E214">
-        <v>31.00303951367781</v>
+        <v>7.775683317624882</v>
       </c>
       <c r="F214" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215">
-        <v>2024</v>
-      </c>
-      <c r="B215" t="s">
-        <v>56</v>
-      </c>
-      <c r="C215" t="s">
-        <v>205</v>
-      </c>
-      <c r="D215">
-        <v>80</v>
-      </c>
-      <c r="E215">
-        <v>24.3161094224924</v>
-      </c>
-      <c r="F215" t="s">
-        <v>10</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216">
+        <v>2023</v>
+      </c>
+      <c r="B216" t="s">
+        <v>57</v>
+      </c>
+      <c r="C216" t="s">
+        <v>203</v>
+      </c>
+      <c r="D216">
+        <v>425</v>
+      </c>
+      <c r="E216">
+        <v>25.11820330969267</v>
+      </c>
+      <c r="F216" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B217" t="s">
         <v>57</v>
       </c>
       <c r="C217" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D217">
-        <v>1224</v>
+        <v>341</v>
       </c>
       <c r="E217">
-        <v>28.77291960507758</v>
+        <v>20.15366430260048</v>
       </c>
       <c r="F217" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B218" t="s">
         <v>57</v>
       </c>
       <c r="C218" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D218">
-        <v>1052</v>
+        <v>279</v>
       </c>
       <c r="E218">
-        <v>24.72966619652092</v>
+        <v>16.48936170212766</v>
       </c>
       <c r="F218" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B219" t="s">
         <v>57</v>
       </c>
       <c r="C219" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D219">
-        <v>685</v>
+        <v>272</v>
       </c>
       <c r="E219">
-        <v>16.10249177244946</v>
+        <v>16.07565011820331</v>
       </c>
       <c r="F219" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B220" t="s">
         <v>57</v>
       </c>
       <c r="C220" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D220">
-        <v>656</v>
+        <v>220</v>
       </c>
       <c r="E220">
-        <v>15.420780441937</v>
+        <v>13.00236406619385</v>
       </c>
       <c r="F220" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B221" t="s">
         <v>57</v>
       </c>
       <c r="C221" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D221">
-        <v>637</v>
+        <v>155</v>
       </c>
       <c r="E221">
-        <v>14.97414198401504</v>
+        <v>9.160756501182032</v>
       </c>
       <c r="F221" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B223" t="s">
         <v>58</v>
       </c>
       <c r="C223" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D223">
-        <v>3817</v>
+        <v>286</v>
       </c>
       <c r="E223">
-        <v>39.10860655737705</v>
+        <v>48.22934232715008</v>
       </c>
       <c r="F223" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B224" t="s">
         <v>58</v>
       </c>
       <c r="C224" t="s">
+        <v>221</v>
+      </c>
+      <c r="D224">
         <v>212</v>
       </c>
-      <c r="D224">
-        <v>3272</v>
-      </c>
       <c r="E224">
-        <v>33.52459016393443</v>
+        <v>35.7504215851602</v>
       </c>
       <c r="F224" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B225" t="s">
         <v>58</v>
       </c>
       <c r="C225" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D225">
-        <v>2671</v>
+        <v>95</v>
       </c>
       <c r="E225">
-        <v>27.36680327868852</v>
+        <v>16.02023608768971</v>
       </c>
       <c r="F225" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B227" t="s">
         <v>59</v>
       </c>
       <c r="C227" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D227">
-        <v>710</v>
+        <v>431</v>
       </c>
       <c r="E227">
-        <v>46.64914586070959</v>
+        <v>36.77474402730375</v>
       </c>
       <c r="F227" t="s">
-        <v>273</v>
+        <v>315</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B228" t="s">
         <v>59</v>
       </c>
       <c r="C228" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D228">
-        <v>617</v>
+        <v>297</v>
       </c>
       <c r="E228">
-        <v>40.53876478318003</v>
+        <v>25.34129692832764</v>
       </c>
       <c r="F228" t="s">
-        <v>273</v>
+        <v>315</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B229" t="s">
         <v>59</v>
       </c>
       <c r="C229" t="s">
-        <v>112</v>
+        <v>225</v>
       </c>
       <c r="D229">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="E229">
-        <v>12.81208935611038</v>
+        <v>24.31740614334471</v>
       </c>
       <c r="F229" t="s">
-        <v>273</v>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230">
+        <v>2023</v>
+      </c>
+      <c r="B230" t="s">
+        <v>59</v>
+      </c>
+      <c r="C230" t="s">
+        <v>226</v>
+      </c>
+      <c r="D230">
+        <v>96</v>
+      </c>
+      <c r="E230">
+        <v>8.191126279863481</v>
+      </c>
+      <c r="F230" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B231" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C231" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="D231">
-        <v>241</v>
+        <v>63</v>
       </c>
       <c r="E231">
-        <v>49.79338842975206</v>
+        <v>5.375426621160409</v>
       </c>
       <c r="F231" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
-      <c r="A232">
-        <v>2025</v>
-      </c>
-      <c r="B232" t="s">
-        <v>60</v>
-      </c>
-      <c r="C232" t="s">
-        <v>217</v>
-      </c>
-      <c r="D232">
-        <v>193</v>
-      </c>
-      <c r="E232">
-        <v>39.87603305785124</v>
-      </c>
-      <c r="F232" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B233" t="s">
         <v>60</v>
       </c>
       <c r="C233" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D233">
-        <v>49</v>
+        <v>273</v>
       </c>
       <c r="E233">
-        <v>10.12396694214876</v>
+        <v>45.4242928452579</v>
       </c>
       <c r="F233" t="s">
-        <v>280</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234">
+        <v>2023</v>
+      </c>
+      <c r="B234" t="s">
+        <v>60</v>
+      </c>
+      <c r="C234" t="s">
+        <v>229</v>
+      </c>
+      <c r="D234">
+        <v>234</v>
+      </c>
+      <c r="E234">
+        <v>38.9351081530782</v>
+      </c>
+      <c r="F234" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B235" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C235" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D235">
-        <v>373</v>
+        <v>94</v>
       </c>
       <c r="E235">
-        <v>36.39024390243902</v>
+        <v>15.64059900166389</v>
       </c>
       <c r="F235" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
-      <c r="A236">
-        <v>2025</v>
-      </c>
-      <c r="B236" t="s">
-        <v>61</v>
-      </c>
-      <c r="C236" t="s">
-        <v>220</v>
-      </c>
-      <c r="D236">
-        <v>225</v>
-      </c>
-      <c r="E236">
-        <v>21.95121951219512</v>
-      </c>
-      <c r="F236" t="s">
-        <v>277</v>
+        <v>318</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B237" t="s">
         <v>61</v>
       </c>
       <c r="C237" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D237">
-        <v>206</v>
+        <v>124</v>
       </c>
       <c r="E237">
-        <v>20.09756097560976</v>
+        <v>47.69230769230769</v>
       </c>
       <c r="F237" t="s">
-        <v>277</v>
+        <v>318</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B238" t="s">
         <v>61</v>
       </c>
       <c r="C238" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D238">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="E238">
-        <v>13.65853658536586</v>
+        <v>28.07692307692308</v>
       </c>
       <c r="F238" t="s">
-        <v>277</v>
+        <v>318</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B239" t="s">
         <v>61</v>
       </c>
       <c r="C239" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D239">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E239">
-        <v>7.902439024390244</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="F239" t="s">
-        <v>277</v>
+        <v>318</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B241" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C241" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D241">
-        <v>6552</v>
+        <v>827</v>
       </c>
       <c r="E241">
-        <v>47.15704620699582</v>
+        <v>47.88650839606254</v>
       </c>
       <c r="F241" t="s">
-        <v>273</v>
+        <v>321</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B242" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C242" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D242">
-        <v>4724</v>
+        <v>284</v>
       </c>
       <c r="E242">
-        <v>34.00028789405498</v>
+        <v>16.44470179502026</v>
       </c>
       <c r="F242" t="s">
-        <v>273</v>
+        <v>321</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B243" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C243" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D243">
-        <v>2618</v>
+        <v>222</v>
       </c>
       <c r="E243">
-        <v>18.84266589894919</v>
+        <v>12.85466126230457</v>
       </c>
       <c r="F243" t="s">
-        <v>273</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244">
+        <v>2023</v>
+      </c>
+      <c r="B244" t="s">
+        <v>62</v>
+      </c>
+      <c r="C244" t="s">
+        <v>237</v>
+      </c>
+      <c r="D244">
+        <v>211</v>
+      </c>
+      <c r="E244">
+        <v>12.21771858714534</v>
+      </c>
+      <c r="F244" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B245" t="s">
         <v>62</v>
       </c>
       <c r="C245" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D245">
-        <v>5832</v>
+        <v>183</v>
       </c>
       <c r="E245">
-        <v>37.28423475258919</v>
+        <v>10.59640995946728</v>
       </c>
       <c r="F245" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246">
-        <v>2025</v>
-      </c>
-      <c r="B246" t="s">
-        <v>62</v>
-      </c>
-      <c r="C246" t="s">
-        <v>228</v>
-      </c>
-      <c r="D246">
-        <v>4950</v>
-      </c>
-      <c r="E246">
-        <v>31.64556962025317</v>
-      </c>
-      <c r="F246" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B247" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C247" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D247">
-        <v>4834</v>
+        <v>605</v>
       </c>
       <c r="E247">
-        <v>30.90397647359673</v>
+        <v>41.10054347826087</v>
       </c>
       <c r="F247" t="s">
-        <v>283</v>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248">
+        <v>2023</v>
+      </c>
+      <c r="B248" t="s">
+        <v>63</v>
+      </c>
+      <c r="C248" t="s">
+        <v>240</v>
+      </c>
+      <c r="D248">
+        <v>593</v>
+      </c>
+      <c r="E248">
+        <v>40.28532608695652</v>
+      </c>
+      <c r="F248" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B249" t="s">
         <v>63</v>
       </c>
       <c r="C249" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D249">
-        <v>9318</v>
+        <v>274</v>
       </c>
       <c r="E249">
-        <v>41.92764578833693</v>
+        <v>18.61413043478261</v>
       </c>
       <c r="F249" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250">
-        <v>2025</v>
-      </c>
-      <c r="B250" t="s">
-        <v>63</v>
-      </c>
-      <c r="C250" t="s">
-        <v>231</v>
-      </c>
-      <c r="D250">
-        <v>8700</v>
-      </c>
-      <c r="E250">
-        <v>39.14686825053996</v>
-      </c>
-      <c r="F250" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B251" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C251" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D251">
-        <v>4206</v>
+        <v>347</v>
       </c>
       <c r="E251">
-        <v>18.92548596112311</v>
+        <v>49.15014164305949</v>
       </c>
       <c r="F251" t="s">
-        <v>281</v>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252">
+        <v>2023</v>
+      </c>
+      <c r="B252" t="s">
+        <v>64</v>
+      </c>
+      <c r="C252" t="s">
+        <v>243</v>
+      </c>
+      <c r="D252">
+        <v>168</v>
+      </c>
+      <c r="E252">
+        <v>23.79603399433428</v>
+      </c>
+      <c r="F252" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B253" t="s">
         <v>64</v>
       </c>
       <c r="C253" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D253">
-        <v>1473</v>
+        <v>103</v>
       </c>
       <c r="E253">
-        <v>39.30096051227321</v>
+        <v>14.58923512747875</v>
       </c>
       <c r="F253" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B254" t="s">
         <v>64</v>
       </c>
       <c r="C254" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D254">
-        <v>1297</v>
+        <v>88</v>
       </c>
       <c r="E254">
-        <v>34.6051227321238</v>
+        <v>12.46458923512748</v>
       </c>
       <c r="F254" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
-      <c r="A255">
-        <v>2025</v>
-      </c>
-      <c r="B255" t="s">
-        <v>64</v>
-      </c>
-      <c r="C255" t="s">
-        <v>235</v>
-      </c>
-      <c r="D255">
-        <v>516</v>
-      </c>
-      <c r="E255">
-        <v>13.76734258271078</v>
-      </c>
-      <c r="F255" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B256" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C256" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D256">
-        <v>305</v>
+        <v>147</v>
       </c>
       <c r="E256">
-        <v>8.137673425827108</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="F256" t="s">
-        <v>279</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B257" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C257" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D257">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="E257">
-        <v>4.188900747065102</v>
+        <v>31.00303951367781</v>
       </c>
       <c r="F257" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
-      <c r="A259">
-        <v>2025</v>
-      </c>
-      <c r="B259" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258">
+        <v>2024</v>
+      </c>
+      <c r="B258" t="s">
         <v>65</v>
       </c>
-      <c r="C259" t="s">
-        <v>238</v>
-      </c>
-      <c r="D259">
-        <v>854</v>
-      </c>
-      <c r="E259">
-        <v>47.52365052865888</v>
-      </c>
-      <c r="F259" t="s">
-        <v>275</v>
+      <c r="C258" t="s">
+        <v>248</v>
+      </c>
+      <c r="D258">
+        <v>80</v>
+      </c>
+      <c r="E258">
+        <v>24.3161094224924</v>
+      </c>
+      <c r="F258" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -5405,19 +5525,19 @@
         <v>2025</v>
       </c>
       <c r="B260" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C260" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D260">
-        <v>764</v>
+        <v>1224</v>
       </c>
       <c r="E260">
-        <v>42.51530328324986</v>
+        <v>28.77291960507758</v>
       </c>
       <c r="F260" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -5425,19 +5545,39 @@
         <v>2025</v>
       </c>
       <c r="B261" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C261" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D261">
-        <v>175</v>
+        <v>1052</v>
       </c>
       <c r="E261">
-        <v>9.738452977184195</v>
+        <v>24.72966619652092</v>
       </c>
       <c r="F261" t="s">
-        <v>275</v>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262">
+        <v>2025</v>
+      </c>
+      <c r="B262" t="s">
+        <v>66</v>
+      </c>
+      <c r="C262" t="s">
+        <v>251</v>
+      </c>
+      <c r="D262">
+        <v>685</v>
+      </c>
+      <c r="E262">
+        <v>16.10249177244946</v>
+      </c>
+      <c r="F262" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -5448,16 +5588,16 @@
         <v>66</v>
       </c>
       <c r="C263" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D263">
-        <v>162</v>
+        <v>656</v>
       </c>
       <c r="E263">
-        <v>45.2513966480447</v>
+        <v>15.420780441937</v>
       </c>
       <c r="F263" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -5468,36 +5608,36 @@
         <v>66</v>
       </c>
       <c r="C264" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D264">
-        <v>156</v>
+        <v>637</v>
       </c>
       <c r="E264">
-        <v>43.5754189944134</v>
+        <v>14.97414198401504</v>
       </c>
       <c r="F264" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
-      <c r="A265">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266">
         <v>2025</v>
       </c>
-      <c r="B265" t="s">
-        <v>66</v>
-      </c>
-      <c r="C265" t="s">
-        <v>243</v>
-      </c>
-      <c r="D265">
-        <v>40</v>
-      </c>
-      <c r="E265">
-        <v>11.1731843575419</v>
-      </c>
-      <c r="F265" t="s">
-        <v>277</v>
+      <c r="B266" t="s">
+        <v>67</v>
+      </c>
+      <c r="C266" t="s">
+        <v>254</v>
+      </c>
+      <c r="D266">
+        <v>3817</v>
+      </c>
+      <c r="E266">
+        <v>39.10860655737705</v>
+      </c>
+      <c r="F266" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -5508,16 +5648,16 @@
         <v>67</v>
       </c>
       <c r="C267" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D267">
-        <v>11367</v>
+        <v>3272</v>
       </c>
       <c r="E267">
-        <v>45.69280861840254</v>
+        <v>33.52459016393443</v>
       </c>
       <c r="F267" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -5528,36 +5668,36 @@
         <v>67</v>
       </c>
       <c r="C268" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D268">
-        <v>8188</v>
+        <v>2671</v>
       </c>
       <c r="E268">
-        <v>32.91393656791413</v>
+        <v>27.36680327868852</v>
       </c>
       <c r="F268" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
-      <c r="A269">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270">
         <v>2025</v>
       </c>
-      <c r="B269" t="s">
-        <v>67</v>
-      </c>
-      <c r="C269" t="s">
-        <v>246</v>
-      </c>
-      <c r="D269">
-        <v>5322</v>
-      </c>
-      <c r="E269">
-        <v>21.39325481368332</v>
-      </c>
-      <c r="F269" t="s">
-        <v>277</v>
+      <c r="B270" t="s">
+        <v>68</v>
+      </c>
+      <c r="C270" t="s">
+        <v>257</v>
+      </c>
+      <c r="D270">
+        <v>710</v>
+      </c>
+      <c r="E270">
+        <v>46.64914586070959</v>
+      </c>
+      <c r="F270" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -5568,16 +5708,16 @@
         <v>68</v>
       </c>
       <c r="C271" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="D271">
-        <v>287</v>
+        <v>617</v>
       </c>
       <c r="E271">
-        <v>47.83333333333334</v>
+        <v>40.53876478318003</v>
       </c>
       <c r="F271" t="s">
-        <v>273</v>
+        <v>315</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -5588,36 +5728,36 @@
         <v>68</v>
       </c>
       <c r="C272" t="s">
-        <v>247</v>
+        <v>155</v>
       </c>
       <c r="D272">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="E272">
-        <v>29.16666666666667</v>
+        <v>12.81208935611038</v>
       </c>
       <c r="F272" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
-      <c r="A273">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274">
         <v>2025</v>
       </c>
-      <c r="B273" t="s">
-        <v>68</v>
-      </c>
-      <c r="C273" t="s">
-        <v>248</v>
-      </c>
-      <c r="D273">
-        <v>138</v>
-      </c>
-      <c r="E273">
-        <v>23</v>
-      </c>
-      <c r="F273" t="s">
-        <v>273</v>
+      <c r="B274" t="s">
+        <v>69</v>
+      </c>
+      <c r="C274" t="s">
+        <v>259</v>
+      </c>
+      <c r="D274">
+        <v>241</v>
+      </c>
+      <c r="E274">
+        <v>49.79338842975206</v>
+      </c>
+      <c r="F274" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -5628,16 +5768,16 @@
         <v>69</v>
       </c>
       <c r="C275" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D275">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E275">
-        <v>38.71733966745843</v>
+        <v>39.87603305785124</v>
       </c>
       <c r="F275" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -5648,36 +5788,16 @@
         <v>69</v>
       </c>
       <c r="C276" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D276">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="E276">
-        <v>38.00475059382423</v>
+        <v>10.12396694214876</v>
       </c>
       <c r="F276" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
-      <c r="A277">
-        <v>2025</v>
-      </c>
-      <c r="B277" t="s">
-        <v>69</v>
-      </c>
-      <c r="C277" t="s">
-        <v>251</v>
-      </c>
-      <c r="D277">
-        <v>75</v>
-      </c>
-      <c r="E277">
-        <v>17.81472684085511</v>
-      </c>
-      <c r="F277" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -5685,19 +5805,39 @@
         <v>2025</v>
       </c>
       <c r="B278" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C278" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="D278">
-        <v>23</v>
+        <v>373</v>
       </c>
       <c r="E278">
-        <v>5.463182897862233</v>
+        <v>36.39024390243902</v>
       </c>
       <c r="F278" t="s">
-        <v>284</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279">
+        <v>2025</v>
+      </c>
+      <c r="B279" t="s">
+        <v>70</v>
+      </c>
+      <c r="C279" t="s">
+        <v>263</v>
+      </c>
+      <c r="D279">
+        <v>225</v>
+      </c>
+      <c r="E279">
+        <v>21.95121951219512</v>
+      </c>
+      <c r="F279" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -5708,16 +5848,16 @@
         <v>70</v>
       </c>
       <c r="C280" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D280">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="E280">
-        <v>35.37414965986395</v>
+        <v>20.09756097560976</v>
       </c>
       <c r="F280" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -5728,16 +5868,16 @@
         <v>70</v>
       </c>
       <c r="C281" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D281">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="E281">
-        <v>26.87074829931973</v>
+        <v>13.65853658536586</v>
       </c>
       <c r="F281" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -5748,36 +5888,36 @@
         <v>70</v>
       </c>
       <c r="C282" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="D282">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E282">
-        <v>26.53061224489796</v>
+        <v>7.902439024390244</v>
       </c>
       <c r="F282" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
-      <c r="A283">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284">
         <v>2025</v>
       </c>
-      <c r="B283" t="s">
-        <v>70</v>
-      </c>
-      <c r="C283" t="s">
-        <v>256</v>
-      </c>
-      <c r="D283">
-        <v>32</v>
-      </c>
-      <c r="E283">
-        <v>10.8843537414966</v>
-      </c>
-      <c r="F283" t="s">
-        <v>275</v>
+      <c r="B284" t="s">
+        <v>31</v>
+      </c>
+      <c r="C284" t="s">
+        <v>267</v>
+      </c>
+      <c r="D284">
+        <v>6552</v>
+      </c>
+      <c r="E284">
+        <v>47.15704620699582</v>
+      </c>
+      <c r="F284" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -5785,19 +5925,19 @@
         <v>2025</v>
       </c>
       <c r="B285" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="C285" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D285">
-        <v>549</v>
+        <v>4724</v>
       </c>
       <c r="E285">
-        <v>42.99138606108065</v>
+        <v>34.00028789405498</v>
       </c>
       <c r="F285" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -5805,39 +5945,39 @@
         <v>2025</v>
       </c>
       <c r="B286" t="s">
+        <v>31</v>
+      </c>
+      <c r="C286" t="s">
+        <v>269</v>
+      </c>
+      <c r="D286">
+        <v>2618</v>
+      </c>
+      <c r="E286">
+        <v>18.84266589894919</v>
+      </c>
+      <c r="F286" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288">
+        <v>2025</v>
+      </c>
+      <c r="B288" t="s">
         <v>71</v>
       </c>
-      <c r="C286" t="s">
-        <v>258</v>
-      </c>
-      <c r="D286">
-        <v>445</v>
-      </c>
-      <c r="E286">
-        <v>34.84729835552075</v>
-      </c>
-      <c r="F286" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
-      <c r="A287">
-        <v>2025</v>
-      </c>
-      <c r="B287" t="s">
-        <v>71</v>
-      </c>
-      <c r="C287" t="s">
-        <v>259</v>
-      </c>
-      <c r="D287">
-        <v>283</v>
-      </c>
-      <c r="E287">
-        <v>22.16131558339859</v>
-      </c>
-      <c r="F287" t="s">
-        <v>281</v>
+      <c r="C288" t="s">
+        <v>270</v>
+      </c>
+      <c r="D288">
+        <v>5832</v>
+      </c>
+      <c r="E288">
+        <v>37.28423475258919</v>
+      </c>
+      <c r="F288" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -5845,19 +5985,19 @@
         <v>2025</v>
       </c>
       <c r="B289" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C289" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="D289">
-        <v>123</v>
+        <v>4950</v>
       </c>
       <c r="E289">
-        <v>28.21100917431193</v>
+        <v>31.64556962025317</v>
       </c>
       <c r="F289" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -5865,39 +6005,19 @@
         <v>2025</v>
       </c>
       <c r="B290" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C290" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D290">
-        <v>117</v>
+        <v>4834</v>
       </c>
       <c r="E290">
-        <v>26.8348623853211</v>
+        <v>30.90397647359673</v>
       </c>
       <c r="F290" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
-      <c r="A291">
-        <v>2025</v>
-      </c>
-      <c r="B291" t="s">
-        <v>72</v>
-      </c>
-      <c r="C291" t="s">
-        <v>262</v>
-      </c>
-      <c r="D291">
-        <v>106</v>
-      </c>
-      <c r="E291">
-        <v>24.31192660550459</v>
-      </c>
-      <c r="F291" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -5908,16 +6028,36 @@
         <v>72</v>
       </c>
       <c r="C292" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D292">
-        <v>90</v>
+        <v>9318</v>
       </c>
       <c r="E292">
-        <v>20.64220183486239</v>
+        <v>41.92764578833693</v>
       </c>
       <c r="F292" t="s">
-        <v>281</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293">
+        <v>2025</v>
+      </c>
+      <c r="B293" t="s">
+        <v>72</v>
+      </c>
+      <c r="C293" t="s">
+        <v>274</v>
+      </c>
+      <c r="D293">
+        <v>8700</v>
+      </c>
+      <c r="E293">
+        <v>39.14686825053996</v>
+      </c>
+      <c r="F293" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -5925,39 +6065,19 @@
         <v>2025</v>
       </c>
       <c r="B294" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C294" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="D294">
-        <v>195</v>
+        <v>4206</v>
       </c>
       <c r="E294">
-        <v>45.03464203233256</v>
+        <v>18.92548596112311</v>
       </c>
       <c r="F294" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
-      <c r="A295">
-        <v>2025</v>
-      </c>
-      <c r="B295" t="s">
-        <v>73</v>
-      </c>
-      <c r="C295" t="s">
-        <v>265</v>
-      </c>
-      <c r="D295">
-        <v>162</v>
-      </c>
-      <c r="E295">
-        <v>37.41339491916859</v>
-      </c>
-      <c r="F295" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -5968,16 +6088,36 @@
         <v>73</v>
       </c>
       <c r="C296" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D296">
-        <v>76</v>
+        <v>1473</v>
       </c>
       <c r="E296">
-        <v>17.55196304849884</v>
+        <v>39.30096051227321</v>
       </c>
       <c r="F296" t="s">
-        <v>281</v>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297">
+        <v>2025</v>
+      </c>
+      <c r="B297" t="s">
+        <v>73</v>
+      </c>
+      <c r="C297" t="s">
+        <v>277</v>
+      </c>
+      <c r="D297">
+        <v>1297</v>
+      </c>
+      <c r="E297">
+        <v>34.6051227321238</v>
+      </c>
+      <c r="F297" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -5985,19 +6125,19 @@
         <v>2025</v>
       </c>
       <c r="B298" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C298" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D298">
-        <v>315</v>
+        <v>516</v>
       </c>
       <c r="E298">
-        <v>43.09165526675787</v>
+        <v>13.76734258271078</v>
       </c>
       <c r="F298" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -6005,19 +6145,19 @@
         <v>2025</v>
       </c>
       <c r="B299" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C299" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D299">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="E299">
-        <v>33.78932968536252</v>
+        <v>8.137673425827108</v>
       </c>
       <c r="F299" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -6025,19 +6165,679 @@
         <v>2025</v>
       </c>
       <c r="B300" t="s">
+        <v>73</v>
+      </c>
+      <c r="C300" t="s">
+        <v>280</v>
+      </c>
+      <c r="D300">
+        <v>157</v>
+      </c>
+      <c r="E300">
+        <v>4.188900747065102</v>
+      </c>
+      <c r="F300" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302">
+        <v>2025</v>
+      </c>
+      <c r="B302" t="s">
         <v>74</v>
       </c>
-      <c r="C300" t="s">
-        <v>269</v>
-      </c>
-      <c r="D300">
+      <c r="C302" t="s">
+        <v>281</v>
+      </c>
+      <c r="D302">
+        <v>854</v>
+      </c>
+      <c r="E302">
+        <v>47.52365052865888</v>
+      </c>
+      <c r="F302" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303">
+        <v>2025</v>
+      </c>
+      <c r="B303" t="s">
+        <v>74</v>
+      </c>
+      <c r="C303" t="s">
+        <v>282</v>
+      </c>
+      <c r="D303">
+        <v>764</v>
+      </c>
+      <c r="E303">
+        <v>42.51530328324986</v>
+      </c>
+      <c r="F303" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304">
+        <v>2025</v>
+      </c>
+      <c r="B304" t="s">
+        <v>74</v>
+      </c>
+      <c r="C304" t="s">
+        <v>283</v>
+      </c>
+      <c r="D304">
+        <v>175</v>
+      </c>
+      <c r="E304">
+        <v>9.738452977184195</v>
+      </c>
+      <c r="F304" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306">
+        <v>2025</v>
+      </c>
+      <c r="B306" t="s">
+        <v>75</v>
+      </c>
+      <c r="C306" t="s">
+        <v>284</v>
+      </c>
+      <c r="D306">
+        <v>162</v>
+      </c>
+      <c r="E306">
+        <v>45.2513966480447</v>
+      </c>
+      <c r="F306" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307">
+        <v>2025</v>
+      </c>
+      <c r="B307" t="s">
+        <v>75</v>
+      </c>
+      <c r="C307" t="s">
+        <v>285</v>
+      </c>
+      <c r="D307">
+        <v>156</v>
+      </c>
+      <c r="E307">
+        <v>43.5754189944134</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308">
+        <v>2025</v>
+      </c>
+      <c r="B308" t="s">
+        <v>75</v>
+      </c>
+      <c r="C308" t="s">
+        <v>286</v>
+      </c>
+      <c r="D308">
+        <v>40</v>
+      </c>
+      <c r="E308">
+        <v>11.1731843575419</v>
+      </c>
+      <c r="F308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310">
+        <v>2025</v>
+      </c>
+      <c r="B310" t="s">
+        <v>76</v>
+      </c>
+      <c r="C310" t="s">
+        <v>96</v>
+      </c>
+      <c r="D310">
+        <v>11367</v>
+      </c>
+      <c r="E310">
+        <v>45.69280861840254</v>
+      </c>
+      <c r="F310" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311">
+        <v>2025</v>
+      </c>
+      <c r="B311" t="s">
+        <v>76</v>
+      </c>
+      <c r="C311" t="s">
+        <v>95</v>
+      </c>
+      <c r="D311">
+        <v>8188</v>
+      </c>
+      <c r="E311">
+        <v>32.91393656791413</v>
+      </c>
+      <c r="F311" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312">
+        <v>2025</v>
+      </c>
+      <c r="B312" t="s">
+        <v>76</v>
+      </c>
+      <c r="C312" t="s">
+        <v>98</v>
+      </c>
+      <c r="D312">
+        <v>5322</v>
+      </c>
+      <c r="E312">
+        <v>21.39325481368332</v>
+      </c>
+      <c r="F312" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314">
+        <v>2025</v>
+      </c>
+      <c r="B314" t="s">
+        <v>77</v>
+      </c>
+      <c r="C314" t="s">
+        <v>221</v>
+      </c>
+      <c r="D314">
+        <v>287</v>
+      </c>
+      <c r="E314">
+        <v>47.83333333333334</v>
+      </c>
+      <c r="F314" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315">
+        <v>2025</v>
+      </c>
+      <c r="B315" t="s">
+        <v>77</v>
+      </c>
+      <c r="C315" t="s">
+        <v>287</v>
+      </c>
+      <c r="D315">
+        <v>175</v>
+      </c>
+      <c r="E315">
+        <v>29.16666666666667</v>
+      </c>
+      <c r="F315" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316">
+        <v>2025</v>
+      </c>
+      <c r="B316" t="s">
+        <v>77</v>
+      </c>
+      <c r="C316" t="s">
+        <v>288</v>
+      </c>
+      <c r="D316">
+        <v>138</v>
+      </c>
+      <c r="E316">
+        <v>23</v>
+      </c>
+      <c r="F316" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318">
+        <v>2025</v>
+      </c>
+      <c r="B318" t="s">
+        <v>78</v>
+      </c>
+      <c r="C318" t="s">
+        <v>289</v>
+      </c>
+      <c r="D318">
+        <v>163</v>
+      </c>
+      <c r="E318">
+        <v>38.71733966745843</v>
+      </c>
+      <c r="F318" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319">
+        <v>2025</v>
+      </c>
+      <c r="B319" t="s">
+        <v>78</v>
+      </c>
+      <c r="C319" t="s">
+        <v>290</v>
+      </c>
+      <c r="D319">
+        <v>160</v>
+      </c>
+      <c r="E319">
+        <v>38.00475059382423</v>
+      </c>
+      <c r="F319" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320">
+        <v>2025</v>
+      </c>
+      <c r="B320" t="s">
+        <v>78</v>
+      </c>
+      <c r="C320" t="s">
+        <v>291</v>
+      </c>
+      <c r="D320">
+        <v>75</v>
+      </c>
+      <c r="E320">
+        <v>17.81472684085511</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321">
+        <v>2025</v>
+      </c>
+      <c r="B321" t="s">
+        <v>78</v>
+      </c>
+      <c r="C321" t="s">
+        <v>292</v>
+      </c>
+      <c r="D321">
+        <v>23</v>
+      </c>
+      <c r="E321">
+        <v>5.463182897862233</v>
+      </c>
+      <c r="F321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323">
+        <v>2025</v>
+      </c>
+      <c r="B323" t="s">
+        <v>79</v>
+      </c>
+      <c r="C323" t="s">
+        <v>293</v>
+      </c>
+      <c r="D323">
+        <v>104</v>
+      </c>
+      <c r="E323">
+        <v>35.37414965986395</v>
+      </c>
+      <c r="F323" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324">
+        <v>2025</v>
+      </c>
+      <c r="B324" t="s">
+        <v>79</v>
+      </c>
+      <c r="C324" t="s">
+        <v>294</v>
+      </c>
+      <c r="D324">
+        <v>79</v>
+      </c>
+      <c r="E324">
+        <v>26.87074829931973</v>
+      </c>
+      <c r="F324" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325">
+        <v>2025</v>
+      </c>
+      <c r="B325" t="s">
+        <v>79</v>
+      </c>
+      <c r="C325" t="s">
+        <v>295</v>
+      </c>
+      <c r="D325">
+        <v>78</v>
+      </c>
+      <c r="E325">
+        <v>26.53061224489796</v>
+      </c>
+      <c r="F325" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326">
+        <v>2025</v>
+      </c>
+      <c r="B326" t="s">
+        <v>79</v>
+      </c>
+      <c r="C326" t="s">
+        <v>296</v>
+      </c>
+      <c r="D326">
+        <v>32</v>
+      </c>
+      <c r="E326">
+        <v>10.8843537414966</v>
+      </c>
+      <c r="F326" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328">
+        <v>2025</v>
+      </c>
+      <c r="B328" t="s">
+        <v>80</v>
+      </c>
+      <c r="C328" t="s">
+        <v>297</v>
+      </c>
+      <c r="D328">
+        <v>549</v>
+      </c>
+      <c r="E328">
+        <v>42.99138606108065</v>
+      </c>
+      <c r="F328" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329">
+        <v>2025</v>
+      </c>
+      <c r="B329" t="s">
+        <v>80</v>
+      </c>
+      <c r="C329" t="s">
+        <v>298</v>
+      </c>
+      <c r="D329">
+        <v>445</v>
+      </c>
+      <c r="E329">
+        <v>34.84729835552075</v>
+      </c>
+      <c r="F329" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330">
+        <v>2025</v>
+      </c>
+      <c r="B330" t="s">
+        <v>80</v>
+      </c>
+      <c r="C330" t="s">
+        <v>299</v>
+      </c>
+      <c r="D330">
+        <v>283</v>
+      </c>
+      <c r="E330">
+        <v>22.16131558339859</v>
+      </c>
+      <c r="F330" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332">
+        <v>2025</v>
+      </c>
+      <c r="B332" t="s">
+        <v>81</v>
+      </c>
+      <c r="C332" t="s">
+        <v>300</v>
+      </c>
+      <c r="D332">
+        <v>123</v>
+      </c>
+      <c r="E332">
+        <v>28.21100917431193</v>
+      </c>
+      <c r="F332" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333">
+        <v>2025</v>
+      </c>
+      <c r="B333" t="s">
+        <v>81</v>
+      </c>
+      <c r="C333" t="s">
+        <v>301</v>
+      </c>
+      <c r="D333">
+        <v>117</v>
+      </c>
+      <c r="E333">
+        <v>26.8348623853211</v>
+      </c>
+      <c r="F333" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334">
+        <v>2025</v>
+      </c>
+      <c r="B334" t="s">
+        <v>81</v>
+      </c>
+      <c r="C334" t="s">
+        <v>302</v>
+      </c>
+      <c r="D334">
+        <v>106</v>
+      </c>
+      <c r="E334">
+        <v>24.31192660550459</v>
+      </c>
+      <c r="F334" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335">
+        <v>2025</v>
+      </c>
+      <c r="B335" t="s">
+        <v>81</v>
+      </c>
+      <c r="C335" t="s">
+        <v>303</v>
+      </c>
+      <c r="D335">
+        <v>90</v>
+      </c>
+      <c r="E335">
+        <v>20.64220183486239</v>
+      </c>
+      <c r="F335" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337">
+        <v>2025</v>
+      </c>
+      <c r="B337" t="s">
+        <v>82</v>
+      </c>
+      <c r="C337" t="s">
+        <v>304</v>
+      </c>
+      <c r="D337">
+        <v>195</v>
+      </c>
+      <c r="E337">
+        <v>45.03464203233256</v>
+      </c>
+      <c r="F337" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338">
+        <v>2025</v>
+      </c>
+      <c r="B338" t="s">
+        <v>82</v>
+      </c>
+      <c r="C338" t="s">
+        <v>305</v>
+      </c>
+      <c r="D338">
+        <v>162</v>
+      </c>
+      <c r="E338">
+        <v>37.41339491916859</v>
+      </c>
+      <c r="F338" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339">
+        <v>2025</v>
+      </c>
+      <c r="B339" t="s">
+        <v>82</v>
+      </c>
+      <c r="C339" t="s">
+        <v>306</v>
+      </c>
+      <c r="D339">
+        <v>76</v>
+      </c>
+      <c r="E339">
+        <v>17.55196304849884</v>
+      </c>
+      <c r="F339" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341">
+        <v>2025</v>
+      </c>
+      <c r="B341" t="s">
+        <v>83</v>
+      </c>
+      <c r="C341" t="s">
+        <v>307</v>
+      </c>
+      <c r="D341">
+        <v>315</v>
+      </c>
+      <c r="E341">
+        <v>43.09165526675787</v>
+      </c>
+      <c r="F341" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342">
+        <v>2025</v>
+      </c>
+      <c r="B342" t="s">
+        <v>83</v>
+      </c>
+      <c r="C342" t="s">
+        <v>308</v>
+      </c>
+      <c r="D342">
+        <v>247</v>
+      </c>
+      <c r="E342">
+        <v>33.78932968536252</v>
+      </c>
+      <c r="F342" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343">
+        <v>2025</v>
+      </c>
+      <c r="B343" t="s">
+        <v>83</v>
+      </c>
+      <c r="C343" t="s">
+        <v>309</v>
+      </c>
+      <c r="D343">
         <v>169</v>
       </c>
-      <c r="E300">
+      <c r="E343">
         <v>23.11901504787962</v>
       </c>
-      <c r="F300" t="s">
-        <v>272</v>
+      <c r="F343" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="345">
   <si>
     <t>Year</t>
   </si>
@@ -77,6 +77,9 @@
     <t>WILKES-BARRE CITY CONTROLLER</t>
   </si>
   <si>
+    <t>County Executive Dem</t>
+  </si>
+  <si>
     <t>DEM JUDGE OF THE COURT OF COMMON PLEAS</t>
   </si>
   <si>
@@ -98,12 +101,21 @@
     <t>DEM Mayor-Swoyersville Borough (4 Year Term)</t>
   </si>
   <si>
+    <t>Fairview Township 1st District Inspector of Election Rep</t>
+  </si>
+  <si>
+    <t>Girard Borough Mayor Rep</t>
+  </si>
+  <si>
     <t>Magisterial District Judge 38-1-15 Dem</t>
   </si>
   <si>
     <t>New Hanover 2 Inspector of Election Rep</t>
   </si>
   <si>
+    <t>North East Borough Mayor Rep</t>
+  </si>
+  <si>
     <t>REP CONSTABLE LIGONIER</t>
   </si>
   <si>
@@ -164,6 +176,9 @@
     <t>DEM North Schuylkill School District 2yr North Schuylkill Area</t>
   </si>
   <si>
+    <t>JUDGE OF THE COURT OF COMMON PLEAS -REP</t>
+  </si>
+  <si>
     <t>REP Commissioner Bethlehem Twsp 1st Ward</t>
   </si>
   <si>
@@ -371,6 +386,18 @@
     <t>PATRICIA UNVARSKY</t>
   </si>
   <si>
+    <t>TYLER TITUS</t>
+  </si>
+  <si>
+    <t>CARL ANDERSON</t>
+  </si>
+  <si>
+    <t>DYLANNA GRASINGER</t>
+  </si>
+  <si>
+    <t>RITA BISHOP</t>
+  </si>
+  <si>
     <t>WILLIAM MCCONNELL JR</t>
   </si>
   <si>
@@ -449,6 +476,24 @@
     <t>ESPY WILLIAMS</t>
   </si>
   <si>
+    <t>CATHERINE KUZMA</t>
+  </si>
+  <si>
+    <t>JENNIFER ZIESENHEIM</t>
+  </si>
+  <si>
+    <t>ANNA KOSENKO</t>
+  </si>
+  <si>
+    <t>PETER BURTON</t>
+  </si>
+  <si>
+    <t>ROBERT KREMENIK</t>
+  </si>
+  <si>
+    <t>JAMES SIMONELLI</t>
+  </si>
+  <si>
     <t>DENISE ASHE</t>
   </si>
   <si>
@@ -470,6 +515,15 @@
     <t>NICOLE ORENOTSKY</t>
   </si>
   <si>
+    <t>JON TRIANA</t>
+  </si>
+  <si>
+    <t>CALVIN JANES</t>
+  </si>
+  <si>
+    <t>MICHAEL SPELLMAN</t>
+  </si>
+  <si>
     <t>SHAWN MILLER</t>
   </si>
   <si>
@@ -638,6 +692,15 @@
     <t>PHILIP RAPANT JR</t>
   </si>
   <si>
+    <t>ERIC MIKOVCH</t>
+  </si>
+  <si>
+    <t>LEIGH ANN ORTON</t>
+  </si>
+  <si>
+    <t>PETE SALA</t>
+  </si>
+  <si>
     <t>ARTHUR MURPHY</t>
   </si>
   <si>
@@ -830,9 +893,6 @@
     <t>JEREMY LIGHTNER</t>
   </si>
   <si>
-    <t>LEIGH ANN ORTON</t>
-  </si>
-  <si>
     <t>EMILY MOSCO MERSKI</t>
   </si>
   <si>
@@ -953,6 +1013,9 @@
     <t>Westmoreland County (city + boroughs + townships)</t>
   </si>
   <si>
+    <t>Erie County (city + boroughs + townships)</t>
+  </si>
+  <si>
     <t>Mercer County (Mercer + Sharon + Hermitage + townships)</t>
   </si>
   <si>
@@ -984,9 +1047,6 @@
   </si>
   <si>
     <t>Lycoming County (Williamsport + boroughs + townships)</t>
-  </si>
-  <si>
-    <t>Erie County (city + boroughs + townships)</t>
   </si>
   <si>
     <t>Indiana County (Indiana + boroughs + townships)</t>
@@ -1437,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F364"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1468,7 +1528,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D2">
         <v>799</v>
@@ -1477,7 +1537,7 @@
         <v>35.94242015294647</v>
       </c>
       <c r="F2" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1488,7 +1548,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>713</v>
@@ -1497,7 +1557,7 @@
         <v>32.07377417903734</v>
       </c>
       <c r="F3" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1508,7 +1568,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D4">
         <v>355</v>
@@ -1517,7 +1577,7 @@
         <v>15.96941070625281</v>
       </c>
       <c r="F4" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1528,7 +1588,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>190</v>
@@ -1537,7 +1597,7 @@
         <v>8.547008547008547</v>
       </c>
       <c r="F5" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1548,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D6">
         <v>166</v>
@@ -1557,7 +1617,7 @@
         <v>7.467386414754835</v>
       </c>
       <c r="F6" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1568,7 +1628,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D8">
         <v>807</v>
@@ -1577,7 +1637,7 @@
         <v>42.87991498405951</v>
       </c>
       <c r="F8" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1588,7 +1648,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D9">
         <v>704</v>
@@ -1597,7 +1657,7 @@
         <v>37.40701381509033</v>
       </c>
       <c r="F9" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1608,7 +1668,7 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D10">
         <v>371</v>
@@ -1617,7 +1677,7 @@
         <v>19.71307120085016</v>
       </c>
       <c r="F10" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1628,7 +1688,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D12">
         <v>23009</v>
@@ -1637,7 +1697,7 @@
         <v>49.36282502359907</v>
       </c>
       <c r="F12" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1648,7 +1708,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D13">
         <v>10398</v>
@@ -1657,7 +1717,7 @@
         <v>22.30756028490518</v>
       </c>
       <c r="F13" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1668,7 +1728,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D14">
         <v>6676</v>
@@ -1677,7 +1737,7 @@
         <v>14.32249206212992</v>
       </c>
       <c r="F14" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1688,7 +1748,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>6529</v>
@@ -1697,7 +1757,7 @@
         <v>14.00712262936583</v>
       </c>
       <c r="F15" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1708,7 +1768,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D17">
         <v>15761</v>
@@ -1717,7 +1777,7 @@
         <v>32.71613907628438</v>
       </c>
       <c r="F17" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1728,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D18">
         <v>12780</v>
@@ -1737,7 +1797,7 @@
         <v>26.52828230409964</v>
       </c>
       <c r="F18" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1748,7 +1808,7 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D19">
         <v>10691</v>
@@ -1757,7 +1817,7 @@
         <v>22.19200830306175</v>
       </c>
       <c r="F19" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1768,7 +1828,7 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D20">
         <v>8943</v>
@@ -1777,7 +1837,7 @@
         <v>18.56357031655423</v>
       </c>
       <c r="F20" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1788,7 +1848,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D22">
         <v>133</v>
@@ -1797,7 +1857,7 @@
         <v>41.95583596214511</v>
       </c>
       <c r="F22" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1808,7 +1868,7 @@
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D23">
         <v>121</v>
@@ -1817,7 +1877,7 @@
         <v>38.17034700315457</v>
       </c>
       <c r="F23" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1828,7 +1888,7 @@
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D24">
         <v>63</v>
@@ -1837,7 +1897,7 @@
         <v>19.87381703470032</v>
       </c>
       <c r="F24" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1848,7 +1908,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D26">
         <v>22897</v>
@@ -1857,7 +1917,7 @@
         <v>47.76078930351891</v>
       </c>
       <c r="F26" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1868,7 +1928,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D27">
         <v>8137</v>
@@ -1877,7 +1937,7 @@
         <v>16.97294591268434</v>
       </c>
       <c r="F27" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1888,7 +1948,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D28">
         <v>7234</v>
@@ -1897,7 +1957,7 @@
         <v>15.08938069710686</v>
       </c>
       <c r="F28" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1908,7 +1968,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D29">
         <v>5373</v>
@@ -1917,7 +1977,7 @@
         <v>11.20752591727332</v>
       </c>
       <c r="F29" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1928,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D30">
         <v>4300</v>
@@ -1937,7 +1997,7 @@
         <v>8.969358169416575</v>
       </c>
       <c r="F30" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1948,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D32">
         <v>364</v>
@@ -1957,7 +2017,7 @@
         <v>39.09774436090225</v>
       </c>
       <c r="F32" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1968,7 +2028,7 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D33">
         <v>341</v>
@@ -1977,7 +2037,7 @@
         <v>36.62728249194414</v>
       </c>
       <c r="F33" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1988,7 +2048,7 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D34">
         <v>226</v>
@@ -1997,7 +2057,7 @@
         <v>24.2749731471536</v>
       </c>
       <c r="F34" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2008,7 +2068,7 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D36">
         <v>1283</v>
@@ -2017,7 +2077,7 @@
         <v>40.52432090966519</v>
       </c>
       <c r="F36" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2028,7 +2088,7 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D37">
         <v>954</v>
@@ -2037,7 +2097,7 @@
         <v>30.13265950726469</v>
       </c>
       <c r="F37" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2048,7 +2108,7 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D38">
         <v>746</v>
@@ -2057,7 +2117,7 @@
         <v>23.56285533796589</v>
       </c>
       <c r="F38" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2068,7 +2128,7 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D39">
         <v>183</v>
@@ -2077,7 +2137,7 @@
         <v>5.780164245104232</v>
       </c>
       <c r="F39" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2088,7 +2148,7 @@
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D41">
         <v>1446</v>
@@ -2097,7 +2157,7 @@
         <v>41.84027777777778</v>
       </c>
       <c r="F41" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2108,7 +2168,7 @@
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D42">
         <v>1091</v>
@@ -2117,7 +2177,7 @@
         <v>31.56828703703703</v>
       </c>
       <c r="F42" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2128,7 +2188,7 @@
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D43">
         <v>919</v>
@@ -2137,7 +2197,7 @@
         <v>26.59143518518519</v>
       </c>
       <c r="F43" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2148,16 +2208,16 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D45">
-        <v>3420</v>
+        <v>8769</v>
       </c>
       <c r="E45">
-        <v>42.77673545966229</v>
+        <v>32.16683173764719</v>
       </c>
       <c r="F45" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2168,16 +2228,16 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D46">
-        <v>2391</v>
+        <v>8551</v>
       </c>
       <c r="E46">
-        <v>29.90619136960601</v>
+        <v>31.36715454312021</v>
       </c>
       <c r="F46" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2188,36 +2248,36 @@
         <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D47">
-        <v>2184</v>
+        <v>5669</v>
       </c>
       <c r="E47">
-        <v>27.31707317073171</v>
+        <v>20.79527530171307</v>
       </c>
       <c r="F47" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>2021</v>
-      </c>
-      <c r="B49" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" t="s">
-        <v>121</v>
-      </c>
-      <c r="D49">
-        <v>572</v>
-      </c>
-      <c r="E49">
-        <v>47.03947368421053</v>
-      </c>
-      <c r="F49" t="s">
-        <v>312</v>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>2021</v>
+      </c>
+      <c r="B48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48">
+        <v>4272</v>
+      </c>
+      <c r="E48">
+        <v>15.67073841751953</v>
+      </c>
+      <c r="F48" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2228,16 +2288,16 @@
         <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D50">
-        <v>380</v>
+        <v>3420</v>
       </c>
       <c r="E50">
-        <v>31.25</v>
+        <v>42.77673545966229</v>
       </c>
       <c r="F50" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2248,36 +2308,36 @@
         <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D51">
-        <v>264</v>
+        <v>2391</v>
       </c>
       <c r="E51">
-        <v>21.71052631578948</v>
+        <v>29.90619136960601</v>
       </c>
       <c r="F51" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>2021</v>
-      </c>
-      <c r="B53" t="s">
-        <v>22</v>
-      </c>
-      <c r="C53" t="s">
-        <v>124</v>
-      </c>
-      <c r="D53">
-        <v>177</v>
-      </c>
-      <c r="E53">
-        <v>39.95485327313769</v>
-      </c>
-      <c r="F53" t="s">
-        <v>313</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>2021</v>
+      </c>
+      <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52">
+        <v>2184</v>
+      </c>
+      <c r="E52">
+        <v>27.31707317073171</v>
+      </c>
+      <c r="F52" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2288,16 +2348,16 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D54">
-        <v>141</v>
+        <v>572</v>
       </c>
       <c r="E54">
-        <v>31.82844243792325</v>
+        <v>47.03947368421053</v>
       </c>
       <c r="F54" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2308,16 +2368,16 @@
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D55">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="E55">
-        <v>18.2844243792325</v>
+        <v>31.25</v>
       </c>
       <c r="F55" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2328,16 +2388,16 @@
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D56">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="E56">
-        <v>9.932279909706546</v>
+        <v>21.71052631578948</v>
       </c>
       <c r="F56" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2348,16 +2408,16 @@
         <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D58">
-        <v>1471</v>
+        <v>177</v>
       </c>
       <c r="E58">
-        <v>44.12117576484703</v>
+        <v>39.95485327313769</v>
       </c>
       <c r="F58" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2368,16 +2428,16 @@
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D59">
-        <v>1247</v>
+        <v>141</v>
       </c>
       <c r="E59">
-        <v>37.40251949610078</v>
+        <v>31.82844243792325</v>
       </c>
       <c r="F59" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2388,36 +2448,36 @@
         <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D60">
-        <v>616</v>
+        <v>81</v>
       </c>
       <c r="E60">
-        <v>18.47630473905219</v>
+        <v>18.2844243792325</v>
       </c>
       <c r="F60" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>2021</v>
-      </c>
-      <c r="B62" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" t="s">
-        <v>131</v>
-      </c>
-      <c r="D62">
-        <v>1183</v>
-      </c>
-      <c r="E62">
-        <v>39.39393939393939</v>
-      </c>
-      <c r="F62" t="s">
-        <v>315</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>2021</v>
+      </c>
+      <c r="B61" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" t="s">
+        <v>136</v>
+      </c>
+      <c r="D61">
+        <v>44</v>
+      </c>
+      <c r="E61">
+        <v>9.932279909706546</v>
+      </c>
+      <c r="F61" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2428,16 +2488,16 @@
         <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D63">
-        <v>1177</v>
+        <v>1471</v>
       </c>
       <c r="E63">
-        <v>39.1941391941392</v>
+        <v>44.12117576484703</v>
       </c>
       <c r="F63" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2448,16 +2508,16 @@
         <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D64">
-        <v>373</v>
+        <v>1247</v>
       </c>
       <c r="E64">
-        <v>12.42091242091242</v>
+        <v>37.40251949610078</v>
       </c>
       <c r="F64" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2468,16 +2528,16 @@
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D65">
-        <v>270</v>
+        <v>616</v>
       </c>
       <c r="E65">
-        <v>8.991008991008991</v>
+        <v>18.47630473905219</v>
       </c>
       <c r="F65" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2488,16 +2548,16 @@
         <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D67">
-        <v>2064</v>
+        <v>1183</v>
       </c>
       <c r="E67">
-        <v>26.63225806451613</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="F67" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2508,16 +2568,16 @@
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D68">
-        <v>1942</v>
+        <v>1177</v>
       </c>
       <c r="E68">
-        <v>25.05806451612903</v>
+        <v>39.1941391941392</v>
       </c>
       <c r="F68" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2528,16 +2588,16 @@
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D69">
-        <v>1927</v>
+        <v>373</v>
       </c>
       <c r="E69">
-        <v>24.86451612903226</v>
+        <v>12.42091242091242</v>
       </c>
       <c r="F69" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2548,16 +2608,16 @@
         <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D70">
-        <v>1817</v>
+        <v>270</v>
       </c>
       <c r="E70">
-        <v>23.44516129032258</v>
+        <v>8.991008991008991</v>
       </c>
       <c r="F70" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2568,16 +2628,16 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D72">
-        <v>237</v>
+        <v>2064</v>
       </c>
       <c r="E72">
-        <v>32.20108695652174</v>
+        <v>26.63225806451613</v>
       </c>
       <c r="F72" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2588,16 +2648,16 @@
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D73">
-        <v>234</v>
+        <v>1942</v>
       </c>
       <c r="E73">
-        <v>31.79347826086957</v>
+        <v>25.05806451612903</v>
       </c>
       <c r="F73" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2608,16 +2668,16 @@
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D74">
-        <v>148</v>
+        <v>1927</v>
       </c>
       <c r="E74">
-        <v>20.10869565217391</v>
+        <v>24.86451612903226</v>
       </c>
       <c r="F74" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2628,36 +2688,36 @@
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D75">
-        <v>90</v>
+        <v>1817</v>
       </c>
       <c r="E75">
-        <v>12.22826086956522</v>
+        <v>23.44516129032258</v>
       </c>
       <c r="F75" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>2021</v>
-      </c>
-      <c r="B76" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" t="s">
-        <v>143</v>
-      </c>
-      <c r="D76">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>2021</v>
+      </c>
+      <c r="B77" t="s">
         <v>27</v>
       </c>
-      <c r="E76">
-        <v>3.668478260869565</v>
-      </c>
-      <c r="F76" t="s">
-        <v>310</v>
+      <c r="C77" t="s">
+        <v>148</v>
+      </c>
+      <c r="D77">
+        <v>237</v>
+      </c>
+      <c r="E77">
+        <v>32.20108695652174</v>
+      </c>
+      <c r="F77" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2668,16 +2728,16 @@
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D78">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="E78">
-        <v>40</v>
+        <v>31.79347826086957</v>
       </c>
       <c r="F78" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2688,16 +2748,16 @@
         <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D79">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="E79">
-        <v>20.64516129032258</v>
+        <v>20.10869565217391</v>
       </c>
       <c r="F79" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2708,16 +2768,16 @@
         <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D80">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E80">
-        <v>20.43010752688172</v>
+        <v>12.22826086956522</v>
       </c>
       <c r="F80" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2728,16 +2788,16 @@
         <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D81">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="E81">
-        <v>18.9247311827957</v>
+        <v>3.668478260869565</v>
       </c>
       <c r="F81" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2748,16 +2808,16 @@
         <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D83">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E83">
-        <v>39.58868894601542</v>
+        <v>44.61077844311377</v>
       </c>
       <c r="F83" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2768,16 +2828,16 @@
         <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D84">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="E84">
-        <v>37.01799485861182</v>
+        <v>34.4311377245509</v>
       </c>
       <c r="F84" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2788,16 +2848,16 @@
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D85">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E85">
-        <v>23.39331619537275</v>
+        <v>20.95808383233533</v>
       </c>
       <c r="F85" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2808,16 +2868,16 @@
         <v>29</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D87">
-        <v>588</v>
+        <v>138</v>
       </c>
       <c r="E87">
-        <v>48.83720930232558</v>
+        <v>40.70796460176992</v>
       </c>
       <c r="F87" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2828,16 +2888,16 @@
         <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D88">
-        <v>379</v>
+        <v>127</v>
       </c>
       <c r="E88">
-        <v>31.47840531561462</v>
+        <v>37.46312684365782</v>
       </c>
       <c r="F88" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2848,16 +2908,16 @@
         <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D89">
-        <v>237</v>
+        <v>74</v>
       </c>
       <c r="E89">
-        <v>19.6843853820598</v>
+        <v>21.82890855457227</v>
       </c>
       <c r="F89" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2868,16 +2928,16 @@
         <v>30</v>
       </c>
       <c r="C91" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D91">
-        <v>522</v>
+        <v>186</v>
       </c>
       <c r="E91">
-        <v>48.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="F91" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2888,16 +2948,16 @@
         <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D92">
-        <v>331</v>
+        <v>96</v>
       </c>
       <c r="E92">
-        <v>30.64814814814815</v>
+        <v>20.64516129032258</v>
       </c>
       <c r="F92" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2908,36 +2968,36 @@
         <v>30</v>
       </c>
       <c r="C93" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D93">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="E93">
-        <v>21.01851851851852</v>
+        <v>20.43010752688172</v>
       </c>
       <c r="F93" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>2021</v>
-      </c>
-      <c r="B95" t="s">
-        <v>31</v>
-      </c>
-      <c r="C95" t="s">
-        <v>120</v>
-      </c>
-      <c r="D95">
-        <v>4922</v>
-      </c>
-      <c r="E95">
-        <v>41.68713475057169</v>
-      </c>
-      <c r="F95" t="s">
-        <v>312</v>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>2021</v>
+      </c>
+      <c r="B94" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94" t="s">
+        <v>162</v>
+      </c>
+      <c r="D94">
+        <v>88</v>
+      </c>
+      <c r="E94">
+        <v>18.9247311827957</v>
+      </c>
+      <c r="F94" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2948,16 +3008,16 @@
         <v>31</v>
       </c>
       <c r="C96" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D96">
-        <v>4820</v>
+        <v>154</v>
       </c>
       <c r="E96">
-        <v>40.82324045058016</v>
+        <v>39.58868894601542</v>
       </c>
       <c r="F96" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2968,36 +3028,36 @@
         <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="D97">
-        <v>2065</v>
+        <v>144</v>
       </c>
       <c r="E97">
-        <v>17.48962479884814</v>
+        <v>37.01799485861182</v>
       </c>
       <c r="F97" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>2021</v>
-      </c>
-      <c r="B99" t="s">
-        <v>32</v>
-      </c>
-      <c r="C99" t="s">
-        <v>157</v>
-      </c>
-      <c r="D99">
-        <v>1281</v>
-      </c>
-      <c r="E99">
-        <v>43.88489208633094</v>
-      </c>
-      <c r="F99" t="s">
-        <v>311</v>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>2021</v>
+      </c>
+      <c r="B98" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" t="s">
+        <v>165</v>
+      </c>
+      <c r="D98">
+        <v>91</v>
+      </c>
+      <c r="E98">
+        <v>23.39331619537275</v>
+      </c>
+      <c r="F98" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3008,16 +3068,16 @@
         <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D100">
-        <v>924</v>
+        <v>203</v>
       </c>
       <c r="E100">
-        <v>31.6546762589928</v>
+        <v>49.63325183374083</v>
       </c>
       <c r="F100" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3028,36 +3088,36 @@
         <v>32</v>
       </c>
       <c r="C101" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D101">
-        <v>714</v>
+        <v>127</v>
       </c>
       <c r="E101">
-        <v>24.46043165467626</v>
+        <v>31.05134474327628</v>
       </c>
       <c r="F101" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>2021</v>
-      </c>
-      <c r="B103" t="s">
-        <v>33</v>
-      </c>
-      <c r="C103" t="s">
-        <v>160</v>
-      </c>
-      <c r="D103">
-        <v>999</v>
-      </c>
-      <c r="E103">
-        <v>49.47994056463596</v>
-      </c>
-      <c r="F103" t="s">
-        <v>311</v>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>2021</v>
+      </c>
+      <c r="B102" t="s">
+        <v>32</v>
+      </c>
+      <c r="C102" t="s">
+        <v>168</v>
+      </c>
+      <c r="D102">
+        <v>79</v>
+      </c>
+      <c r="E102">
+        <v>19.31540342298289</v>
+      </c>
+      <c r="F102" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3068,16 +3128,16 @@
         <v>33</v>
       </c>
       <c r="C104" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D104">
-        <v>629</v>
+        <v>588</v>
       </c>
       <c r="E104">
-        <v>31.15403665180783</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="F104" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3088,36 +3148,36 @@
         <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D105">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E105">
-        <v>19.36602278355622</v>
+        <v>31.47840531561462</v>
       </c>
       <c r="F105" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>2021</v>
-      </c>
-      <c r="B107" t="s">
-        <v>34</v>
-      </c>
-      <c r="C107" t="s">
-        <v>121</v>
-      </c>
-      <c r="D107">
-        <v>1779</v>
-      </c>
-      <c r="E107">
-        <v>46.82811266122664</v>
-      </c>
-      <c r="F107" t="s">
-        <v>312</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106">
+        <v>2021</v>
+      </c>
+      <c r="B106" t="s">
+        <v>33</v>
+      </c>
+      <c r="C106" t="s">
+        <v>171</v>
+      </c>
+      <c r="D106">
+        <v>237</v>
+      </c>
+      <c r="E106">
+        <v>19.6843853820598</v>
+      </c>
+      <c r="F106" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3128,16 +3188,16 @@
         <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="D108">
-        <v>1349</v>
+        <v>522</v>
       </c>
       <c r="E108">
-        <v>35.50934456435904</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="F108" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3148,36 +3208,36 @@
         <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="D109">
-        <v>671</v>
+        <v>331</v>
       </c>
       <c r="E109">
-        <v>17.66254277441432</v>
+        <v>30.64814814814815</v>
       </c>
       <c r="F109" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>2021</v>
-      </c>
-      <c r="B111" t="s">
-        <v>35</v>
-      </c>
-      <c r="C111" t="s">
-        <v>125</v>
-      </c>
-      <c r="D111">
-        <v>253</v>
-      </c>
-      <c r="E111">
-        <v>37.09677419354838</v>
-      </c>
-      <c r="F111" t="s">
-        <v>313</v>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110">
+        <v>2021</v>
+      </c>
+      <c r="B110" t="s">
+        <v>34</v>
+      </c>
+      <c r="C110" t="s">
+        <v>174</v>
+      </c>
+      <c r="D110">
+        <v>227</v>
+      </c>
+      <c r="E110">
+        <v>21.01851851851852</v>
+      </c>
+      <c r="F110" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3188,16 +3248,16 @@
         <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D112">
-        <v>224</v>
+        <v>4922</v>
       </c>
       <c r="E112">
-        <v>32.84457478005865</v>
+        <v>41.68713475057169</v>
       </c>
       <c r="F112" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3208,16 +3268,16 @@
         <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="D113">
-        <v>122</v>
+        <v>4820</v>
       </c>
       <c r="E113">
-        <v>17.88856304985337</v>
+        <v>40.82324045058016</v>
       </c>
       <c r="F113" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3228,36 +3288,36 @@
         <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D114">
-        <v>60</v>
+        <v>2065</v>
       </c>
       <c r="E114">
-        <v>8.797653958944283</v>
+        <v>17.48962479884814</v>
       </c>
       <c r="F114" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>2021</v>
-      </c>
-      <c r="B115" t="s">
-        <v>35</v>
-      </c>
-      <c r="C115" t="s">
-        <v>124</v>
-      </c>
-      <c r="D115">
-        <v>23</v>
-      </c>
-      <c r="E115">
-        <v>3.372434017595308</v>
-      </c>
-      <c r="F115" t="s">
-        <v>313</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116">
+        <v>2021</v>
+      </c>
+      <c r="B116" t="s">
+        <v>36</v>
+      </c>
+      <c r="C116" t="s">
+        <v>175</v>
+      </c>
+      <c r="D116">
+        <v>1281</v>
+      </c>
+      <c r="E116">
+        <v>43.88489208633094</v>
+      </c>
+      <c r="F116" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3268,16 +3328,16 @@
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="D117">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="E117">
-        <v>36.31683168316832</v>
+        <v>31.6546762589928</v>
       </c>
       <c r="F117" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3288,36 +3348,16 @@
         <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="D118">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="E118">
-        <v>27.96039603960396</v>
+        <v>24.46043165467626</v>
       </c>
       <c r="F118" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>2021</v>
-      </c>
-      <c r="B119" t="s">
-        <v>36</v>
-      </c>
-      <c r="C119" t="s">
-        <v>131</v>
-      </c>
-      <c r="D119">
-        <v>578</v>
-      </c>
-      <c r="E119">
-        <v>22.89108910891089</v>
-      </c>
-      <c r="F119" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3325,19 +3365,39 @@
         <v>2021</v>
       </c>
       <c r="B120" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C120" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="D120">
-        <v>324</v>
+        <v>999</v>
       </c>
       <c r="E120">
-        <v>12.83168316831683</v>
+        <v>49.47994056463596</v>
       </c>
       <c r="F120" t="s">
-        <v>315</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121">
+        <v>2021</v>
+      </c>
+      <c r="B121" t="s">
+        <v>37</v>
+      </c>
+      <c r="C121" t="s">
+        <v>179</v>
+      </c>
+      <c r="D121">
+        <v>629</v>
+      </c>
+      <c r="E121">
+        <v>31.15403665180783</v>
+      </c>
+      <c r="F121" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3348,36 +3408,16 @@
         <v>37</v>
       </c>
       <c r="C122" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D122">
-        <v>149</v>
+        <v>391</v>
       </c>
       <c r="E122">
-        <v>41.38888888888889</v>
+        <v>19.36602278355622</v>
       </c>
       <c r="F122" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>2021</v>
-      </c>
-      <c r="B123" t="s">
-        <v>37</v>
-      </c>
-      <c r="C123" t="s">
-        <v>165</v>
-      </c>
-      <c r="D123">
-        <v>113</v>
-      </c>
-      <c r="E123">
-        <v>31.38888888888889</v>
-      </c>
-      <c r="F123" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3385,19 +3425,19 @@
         <v>2021</v>
       </c>
       <c r="B124" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C124" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="D124">
-        <v>59</v>
+        <v>1779</v>
       </c>
       <c r="E124">
-        <v>16.38888888888889</v>
+        <v>46.82811266122664</v>
       </c>
       <c r="F124" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3405,39 +3445,39 @@
         <v>2021</v>
       </c>
       <c r="B125" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C125" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="D125">
-        <v>39</v>
+        <v>1349</v>
       </c>
       <c r="E125">
-        <v>10.83333333333333</v>
+        <v>35.50934456435904</v>
       </c>
       <c r="F125" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>2021</v>
-      </c>
-      <c r="B127" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126">
+        <v>2021</v>
+      </c>
+      <c r="B126" t="s">
         <v>38</v>
       </c>
-      <c r="C127" t="s">
-        <v>168</v>
-      </c>
-      <c r="D127">
-        <v>179</v>
-      </c>
-      <c r="E127">
-        <v>45.31645569620253</v>
-      </c>
-      <c r="F127" t="s">
-        <v>318</v>
+      <c r="C126" t="s">
+        <v>132</v>
+      </c>
+      <c r="D126">
+        <v>671</v>
+      </c>
+      <c r="E126">
+        <v>17.66254277441432</v>
+      </c>
+      <c r="F126" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3445,19 +3485,19 @@
         <v>2021</v>
       </c>
       <c r="B128" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C128" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="D128">
-        <v>110</v>
+        <v>253</v>
       </c>
       <c r="E128">
-        <v>27.84810126582278</v>
+        <v>37.09677419354838</v>
       </c>
       <c r="F128" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3465,19 +3505,39 @@
         <v>2021</v>
       </c>
       <c r="B129" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="D129">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="E129">
-        <v>26.83544303797468</v>
+        <v>32.84457478005865</v>
       </c>
       <c r="F129" t="s">
-        <v>318</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130">
+        <v>2021</v>
+      </c>
+      <c r="B130" t="s">
+        <v>39</v>
+      </c>
+      <c r="C130" t="s">
+        <v>181</v>
+      </c>
+      <c r="D130">
+        <v>122</v>
+      </c>
+      <c r="E130">
+        <v>17.88856304985337</v>
+      </c>
+      <c r="F130" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3488,16 +3548,16 @@
         <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="D131">
-        <v>276</v>
+        <v>60</v>
       </c>
       <c r="E131">
-        <v>47.01873935264054</v>
+        <v>8.797653958944283</v>
       </c>
       <c r="F131" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3508,36 +3568,36 @@
         <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="D132">
-        <v>226</v>
+        <v>23</v>
       </c>
       <c r="E132">
-        <v>38.50085178875639</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="F132" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>2021</v>
-      </c>
-      <c r="B133" t="s">
-        <v>39</v>
-      </c>
-      <c r="C133" t="s">
-        <v>173</v>
-      </c>
-      <c r="D133">
-        <v>85</v>
-      </c>
-      <c r="E133">
-        <v>14.48040885860307</v>
-      </c>
-      <c r="F133" t="s">
-        <v>316</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134">
+        <v>2021</v>
+      </c>
+      <c r="B134" t="s">
+        <v>40</v>
+      </c>
+      <c r="C134" t="s">
+        <v>142</v>
+      </c>
+      <c r="D134">
+        <v>917</v>
+      </c>
+      <c r="E134">
+        <v>36.31683168316832</v>
+      </c>
+      <c r="F134" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3548,16 +3608,16 @@
         <v>40</v>
       </c>
       <c r="C135" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D135">
-        <v>636</v>
+        <v>706</v>
       </c>
       <c r="E135">
-        <v>41.24513618677042</v>
+        <v>27.96039603960396</v>
       </c>
       <c r="F135" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3568,16 +3628,16 @@
         <v>40</v>
       </c>
       <c r="C136" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="D136">
-        <v>544</v>
+        <v>578</v>
       </c>
       <c r="E136">
-        <v>35.27885862516213</v>
+        <v>22.89108910891089</v>
       </c>
       <c r="F136" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3588,276 +3648,276 @@
         <v>40</v>
       </c>
       <c r="C137" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="D137">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="E137">
-        <v>23.47600518806744</v>
+        <v>12.83168316831683</v>
       </c>
       <c r="F137" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B139" t="s">
         <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D139">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="E139">
-        <v>38.95131086142322</v>
+        <v>41.38888888888889</v>
       </c>
       <c r="F139" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B140" t="s">
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D140">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E140">
-        <v>37.45318352059925</v>
+        <v>31.38888888888889</v>
       </c>
       <c r="F140" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B141" t="s">
         <v>41</v>
       </c>
       <c r="C141" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D141">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E141">
-        <v>23.59550561797753</v>
+        <v>16.38888888888889</v>
       </c>
       <c r="F141" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>2023</v>
-      </c>
-      <c r="B143" t="s">
-        <v>42</v>
-      </c>
-      <c r="C143" t="s">
-        <v>180</v>
-      </c>
-      <c r="D143">
-        <v>882</v>
-      </c>
-      <c r="E143">
-        <v>45.60496380558428</v>
-      </c>
-      <c r="F143" t="s">
-        <v>311</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142">
+        <v>2021</v>
+      </c>
+      <c r="B142" t="s">
+        <v>41</v>
+      </c>
+      <c r="C142" t="s">
+        <v>185</v>
+      </c>
+      <c r="D142">
+        <v>39</v>
+      </c>
+      <c r="E142">
+        <v>10.83333333333333</v>
+      </c>
+      <c r="F142" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B144" t="s">
         <v>42</v>
       </c>
       <c r="C144" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D144">
-        <v>502</v>
+        <v>179</v>
       </c>
       <c r="E144">
-        <v>25.95656670113754</v>
+        <v>45.31645569620253</v>
       </c>
       <c r="F144" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B145" t="s">
         <v>42</v>
       </c>
       <c r="C145" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D145">
-        <v>399</v>
+        <v>110</v>
       </c>
       <c r="E145">
-        <v>20.63081695966908</v>
+        <v>27.84810126582278</v>
       </c>
       <c r="F145" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B146" t="s">
         <v>42</v>
       </c>
       <c r="C146" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D146">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="E146">
-        <v>7.807652533609101</v>
+        <v>26.83544303797468</v>
       </c>
       <c r="F146" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B148" t="s">
         <v>43</v>
       </c>
       <c r="C148" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D148">
-        <v>445</v>
+        <v>276</v>
       </c>
       <c r="E148">
-        <v>43.28793774319066</v>
+        <v>47.01873935264054</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B149" t="s">
         <v>43</v>
       </c>
       <c r="C149" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D149">
-        <v>353</v>
+        <v>226</v>
       </c>
       <c r="E149">
-        <v>34.33852140077821</v>
+        <v>38.50085178875639</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B150" t="s">
         <v>43</v>
       </c>
       <c r="C150" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D150">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="E150">
-        <v>22.37354085603113</v>
+        <v>14.48040885860307</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B152" t="s">
         <v>44</v>
       </c>
       <c r="C152" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D152">
-        <v>684</v>
+        <v>636</v>
       </c>
       <c r="E152">
-        <v>46.94577899794098</v>
+        <v>41.24513618677042</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B153" t="s">
         <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D153">
-        <v>395</v>
+        <v>544</v>
       </c>
       <c r="E153">
-        <v>27.1105010295127</v>
+        <v>35.27885862516213</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B154" t="s">
         <v>44</v>
       </c>
       <c r="C154" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D154">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="E154">
-        <v>25.94371997254633</v>
+        <v>23.47600518806744</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -3868,16 +3928,16 @@
         <v>45</v>
       </c>
       <c r="C156" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D156">
-        <v>828</v>
+        <v>104</v>
       </c>
       <c r="E156">
-        <v>36.71840354767184</v>
+        <v>38.95131086142322</v>
       </c>
       <c r="F156" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -3888,16 +3948,16 @@
         <v>45</v>
       </c>
       <c r="C157" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D157">
-        <v>524</v>
+        <v>100</v>
       </c>
       <c r="E157">
-        <v>23.23725055432372</v>
+        <v>37.45318352059925</v>
       </c>
       <c r="F157" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -3908,36 +3968,16 @@
         <v>45</v>
       </c>
       <c r="C158" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D158">
-        <v>485</v>
+        <v>63</v>
       </c>
       <c r="E158">
-        <v>21.50776053215078</v>
+        <v>23.59550561797753</v>
       </c>
       <c r="F158" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>2023</v>
-      </c>
-      <c r="B159" t="s">
-        <v>45</v>
-      </c>
-      <c r="C159" t="s">
-        <v>193</v>
-      </c>
-      <c r="D159">
-        <v>261</v>
-      </c>
-      <c r="E159">
-        <v>11.57427937915743</v>
-      </c>
-      <c r="F159" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -3945,19 +3985,39 @@
         <v>2023</v>
       </c>
       <c r="B160" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C160" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D160">
-        <v>157</v>
+        <v>882</v>
       </c>
       <c r="E160">
-        <v>6.962305986696231</v>
+        <v>45.60496380558428</v>
       </c>
       <c r="F160" t="s">
-        <v>314</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161">
+        <v>2023</v>
+      </c>
+      <c r="B161" t="s">
+        <v>46</v>
+      </c>
+      <c r="C161" t="s">
+        <v>199</v>
+      </c>
+      <c r="D161">
+        <v>502</v>
+      </c>
+      <c r="E161">
+        <v>25.95656670113754</v>
+      </c>
+      <c r="F161" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -3968,16 +4028,16 @@
         <v>46</v>
       </c>
       <c r="C162" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D162">
-        <v>584</v>
+        <v>399</v>
       </c>
       <c r="E162">
-        <v>43.90977443609022</v>
+        <v>20.63081695966908</v>
       </c>
       <c r="F162" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -3988,36 +4048,36 @@
         <v>46</v>
       </c>
       <c r="C163" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D163">
-        <v>388</v>
+        <v>151</v>
       </c>
       <c r="E163">
-        <v>29.17293233082707</v>
+        <v>7.807652533609101</v>
       </c>
       <c r="F163" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164">
-        <v>2023</v>
-      </c>
-      <c r="B164" t="s">
-        <v>46</v>
-      </c>
-      <c r="C164" t="s">
-        <v>197</v>
-      </c>
-      <c r="D164">
-        <v>358</v>
-      </c>
-      <c r="E164">
-        <v>26.91729323308271</v>
-      </c>
-      <c r="F164" t="s">
-        <v>321</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165">
+        <v>2023</v>
+      </c>
+      <c r="B165" t="s">
+        <v>47</v>
+      </c>
+      <c r="C165" t="s">
+        <v>202</v>
+      </c>
+      <c r="D165">
+        <v>445</v>
+      </c>
+      <c r="E165">
+        <v>43.28793774319066</v>
+      </c>
+      <c r="F165" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -4028,16 +4088,16 @@
         <v>47</v>
       </c>
       <c r="C166" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D166">
-        <v>634</v>
+        <v>353</v>
       </c>
       <c r="E166">
-        <v>45.67723342939482</v>
+        <v>34.33852140077821</v>
       </c>
       <c r="F166" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -4048,36 +4108,16 @@
         <v>47</v>
       </c>
       <c r="C167" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D167">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="E167">
-        <v>21.46974063400576</v>
+        <v>22.37354085603113</v>
       </c>
       <c r="F167" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168">
-        <v>2023</v>
-      </c>
-      <c r="B168" t="s">
-        <v>47</v>
-      </c>
-      <c r="C168" t="s">
-        <v>200</v>
-      </c>
-      <c r="D168">
-        <v>246</v>
-      </c>
-      <c r="E168">
-        <v>17.72334293948127</v>
-      </c>
-      <c r="F168" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -4085,19 +4125,39 @@
         <v>2023</v>
       </c>
       <c r="B169" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C169" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D169">
-        <v>210</v>
+        <v>684</v>
       </c>
       <c r="E169">
-        <v>15.12968299711815</v>
+        <v>46.94577899794098</v>
       </c>
       <c r="F169" t="s">
-        <v>321</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170">
+        <v>2023</v>
+      </c>
+      <c r="B170" t="s">
+        <v>48</v>
+      </c>
+      <c r="C170" t="s">
+        <v>206</v>
+      </c>
+      <c r="D170">
+        <v>395</v>
+      </c>
+      <c r="E170">
+        <v>27.1105010295127</v>
+      </c>
+      <c r="F170" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -4108,36 +4168,16 @@
         <v>48</v>
       </c>
       <c r="C171" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D171">
-        <v>294</v>
+        <v>378</v>
       </c>
       <c r="E171">
-        <v>38.33116036505867</v>
+        <v>25.94371997254633</v>
       </c>
       <c r="F171" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172">
-        <v>2023</v>
-      </c>
-      <c r="B172" t="s">
-        <v>48</v>
-      </c>
-      <c r="C172" t="s">
-        <v>203</v>
-      </c>
-      <c r="D172">
-        <v>145</v>
-      </c>
-      <c r="E172">
-        <v>18.90482398956975</v>
-      </c>
-      <c r="F172" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4145,19 +4185,19 @@
         <v>2023</v>
       </c>
       <c r="B173" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C173" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D173">
-        <v>136</v>
+        <v>828</v>
       </c>
       <c r="E173">
-        <v>17.73142112125163</v>
+        <v>36.71840354767184</v>
       </c>
       <c r="F173" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4165,19 +4205,19 @@
         <v>2023</v>
       </c>
       <c r="B174" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C174" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D174">
-        <v>104</v>
+        <v>524</v>
       </c>
       <c r="E174">
-        <v>13.5593220338983</v>
+        <v>23.23725055432372</v>
       </c>
       <c r="F174" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4185,19 +4225,39 @@
         <v>2023</v>
       </c>
       <c r="B175" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C175" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D175">
-        <v>88</v>
+        <v>485</v>
       </c>
       <c r="E175">
-        <v>11.47327249022164</v>
+        <v>21.50776053215078</v>
       </c>
       <c r="F175" t="s">
-        <v>319</v>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176">
+        <v>2023</v>
+      </c>
+      <c r="B176" t="s">
+        <v>49</v>
+      </c>
+      <c r="C176" t="s">
+        <v>211</v>
+      </c>
+      <c r="D176">
+        <v>261</v>
+      </c>
+      <c r="E176">
+        <v>11.57427937915743</v>
+      </c>
+      <c r="F176" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -4208,36 +4268,16 @@
         <v>49</v>
       </c>
       <c r="C177" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D177">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E177">
-        <v>46.19565217391305</v>
+        <v>6.962305986696231</v>
       </c>
       <c r="F177" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178">
-        <v>2023</v>
-      </c>
-      <c r="B178" t="s">
-        <v>49</v>
-      </c>
-      <c r="C178" t="s">
-        <v>208</v>
-      </c>
-      <c r="D178">
-        <v>169</v>
-      </c>
-      <c r="E178">
-        <v>45.92391304347826</v>
-      </c>
-      <c r="F178" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4245,19 +4285,39 @@
         <v>2023</v>
       </c>
       <c r="B179" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C179" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D179">
-        <v>29</v>
+        <v>584</v>
       </c>
       <c r="E179">
-        <v>7.880434782608696</v>
+        <v>43.90977443609022</v>
       </c>
       <c r="F179" t="s">
-        <v>315</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180">
+        <v>2023</v>
+      </c>
+      <c r="B180" t="s">
+        <v>50</v>
+      </c>
+      <c r="C180" t="s">
+        <v>214</v>
+      </c>
+      <c r="D180">
+        <v>388</v>
+      </c>
+      <c r="E180">
+        <v>29.17293233082707</v>
+      </c>
+      <c r="F180" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -4268,36 +4328,16 @@
         <v>50</v>
       </c>
       <c r="C181" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="D181">
-        <v>1114</v>
+        <v>358</v>
       </c>
       <c r="E181">
-        <v>47.79064779064779</v>
+        <v>26.91729323308271</v>
       </c>
       <c r="F181" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182">
-        <v>2023</v>
-      </c>
-      <c r="B182" t="s">
-        <v>50</v>
-      </c>
-      <c r="C182" t="s">
-        <v>182</v>
-      </c>
-      <c r="D182">
-        <v>647</v>
-      </c>
-      <c r="E182">
-        <v>27.75632775632776</v>
-      </c>
-      <c r="F182" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -4305,19 +4345,19 @@
         <v>2023</v>
       </c>
       <c r="B183" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C183" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="D183">
-        <v>369</v>
+        <v>634</v>
       </c>
       <c r="E183">
-        <v>15.83011583011583</v>
+        <v>45.67723342939482</v>
       </c>
       <c r="F183" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4325,19 +4365,39 @@
         <v>2023</v>
       </c>
       <c r="B184" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C184" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="D184">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="E184">
-        <v>8.622908622908623</v>
+        <v>21.46974063400576</v>
       </c>
       <c r="F184" t="s">
-        <v>311</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185">
+        <v>2023</v>
+      </c>
+      <c r="B185" t="s">
+        <v>51</v>
+      </c>
+      <c r="C185" t="s">
+        <v>218</v>
+      </c>
+      <c r="D185">
+        <v>246</v>
+      </c>
+      <c r="E185">
+        <v>17.72334293948127</v>
+      </c>
+      <c r="F185" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4348,36 +4408,16 @@
         <v>51</v>
       </c>
       <c r="C186" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="D186">
-        <v>886</v>
+        <v>210</v>
       </c>
       <c r="E186">
-        <v>48.86927744070601</v>
+        <v>15.12968299711815</v>
       </c>
       <c r="F186" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187">
-        <v>2023</v>
-      </c>
-      <c r="B187" t="s">
-        <v>51</v>
-      </c>
-      <c r="C187" t="s">
-        <v>185</v>
-      </c>
-      <c r="D187">
-        <v>699</v>
-      </c>
-      <c r="E187">
-        <v>38.55488141202427</v>
-      </c>
-      <c r="F187" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4385,19 +4425,39 @@
         <v>2023</v>
       </c>
       <c r="B188" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C188" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="D188">
-        <v>228</v>
+        <v>294</v>
       </c>
       <c r="E188">
-        <v>12.57584114726972</v>
+        <v>38.33116036505867</v>
       </c>
       <c r="F188" t="s">
-        <v>320</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189">
+        <v>2023</v>
+      </c>
+      <c r="B189" t="s">
+        <v>52</v>
+      </c>
+      <c r="C189" t="s">
+        <v>221</v>
+      </c>
+      <c r="D189">
+        <v>145</v>
+      </c>
+      <c r="E189">
+        <v>18.90482398956975</v>
+      </c>
+      <c r="F189" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4408,16 +4468,16 @@
         <v>52</v>
       </c>
       <c r="C190" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="D190">
-        <v>1630</v>
+        <v>136</v>
       </c>
       <c r="E190">
-        <v>44.46262956901255</v>
+        <v>17.73142112125163</v>
       </c>
       <c r="F190" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4428,16 +4488,16 @@
         <v>52</v>
       </c>
       <c r="C191" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="D191">
-        <v>1039</v>
+        <v>104</v>
       </c>
       <c r="E191">
-        <v>28.34151663938898</v>
+        <v>13.5593220338983</v>
       </c>
       <c r="F191" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -4448,36 +4508,36 @@
         <v>52</v>
       </c>
       <c r="C192" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="D192">
-        <v>813</v>
+        <v>88</v>
       </c>
       <c r="E192">
-        <v>22.17675941080196</v>
+        <v>11.47327249022164</v>
       </c>
       <c r="F192" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193">
-        <v>2023</v>
-      </c>
-      <c r="B193" t="s">
-        <v>52</v>
-      </c>
-      <c r="C193" t="s">
-        <v>210</v>
-      </c>
-      <c r="D193">
-        <v>184</v>
-      </c>
-      <c r="E193">
-        <v>5.019094380796509</v>
-      </c>
-      <c r="F193" t="s">
-        <v>320</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194">
+        <v>2023</v>
+      </c>
+      <c r="B194" t="s">
+        <v>53</v>
+      </c>
+      <c r="C194" t="s">
+        <v>225</v>
+      </c>
+      <c r="D194">
+        <v>5642</v>
+      </c>
+      <c r="E194">
+        <v>34.00638900608764</v>
+      </c>
+      <c r="F194" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4488,16 +4548,16 @@
         <v>53</v>
       </c>
       <c r="C195" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="D195">
-        <v>1334</v>
+        <v>5540</v>
       </c>
       <c r="E195">
-        <v>46.38386648122393</v>
+        <v>33.39159785425833</v>
       </c>
       <c r="F195" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -4508,36 +4568,36 @@
         <v>53</v>
       </c>
       <c r="C196" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="D196">
-        <v>1278</v>
+        <v>5409</v>
       </c>
       <c r="E196">
-        <v>44.43671766342142</v>
+        <v>32.60201313965403</v>
       </c>
       <c r="F196" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197">
-        <v>2023</v>
-      </c>
-      <c r="B197" t="s">
-        <v>53</v>
-      </c>
-      <c r="C197" t="s">
-        <v>213</v>
-      </c>
-      <c r="D197">
-        <v>264</v>
-      </c>
-      <c r="E197">
-        <v>9.179415855354661</v>
-      </c>
-      <c r="F197" t="s">
-        <v>322</v>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198">
+        <v>2023</v>
+      </c>
+      <c r="B198" t="s">
+        <v>54</v>
+      </c>
+      <c r="C198" t="s">
+        <v>228</v>
+      </c>
+      <c r="D198">
+        <v>170</v>
+      </c>
+      <c r="E198">
+        <v>46.19565217391305</v>
+      </c>
+      <c r="F198" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4548,16 +4608,16 @@
         <v>54</v>
       </c>
       <c r="C199" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="D199">
-        <v>1466</v>
+        <v>169</v>
       </c>
       <c r="E199">
-        <v>43.1303324507208</v>
+        <v>45.92391304347826</v>
       </c>
       <c r="F199" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -4568,36 +4628,16 @@
         <v>54</v>
       </c>
       <c r="C200" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="D200">
-        <v>893</v>
+        <v>29</v>
       </c>
       <c r="E200">
-        <v>26.27243306854957</v>
+        <v>7.880434782608696</v>
       </c>
       <c r="F200" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201">
-        <v>2023</v>
-      </c>
-      <c r="B201" t="s">
-        <v>54</v>
-      </c>
-      <c r="C201" t="s">
-        <v>192</v>
-      </c>
-      <c r="D201">
-        <v>672</v>
-      </c>
-      <c r="E201">
-        <v>19.77052074139453</v>
-      </c>
-      <c r="F201" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4605,19 +4645,19 @@
         <v>2023</v>
       </c>
       <c r="B202" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D202">
-        <v>245</v>
+        <v>1114</v>
       </c>
       <c r="E202">
-        <v>7.208002353633422</v>
+        <v>47.79064779064779</v>
       </c>
       <c r="F202" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4625,19 +4665,39 @@
         <v>2023</v>
       </c>
       <c r="B203" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D203">
-        <v>123</v>
+        <v>647</v>
       </c>
       <c r="E203">
-        <v>3.618711385701677</v>
+        <v>27.75632775632776</v>
       </c>
       <c r="F203" t="s">
-        <v>314</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204">
+        <v>2023</v>
+      </c>
+      <c r="B204" t="s">
+        <v>55</v>
+      </c>
+      <c r="C204" t="s">
+        <v>199</v>
+      </c>
+      <c r="D204">
+        <v>369</v>
+      </c>
+      <c r="E204">
+        <v>15.83011583011583</v>
+      </c>
+      <c r="F204" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4648,36 +4708,16 @@
         <v>55</v>
       </c>
       <c r="C205" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D205">
-        <v>1108</v>
+        <v>201</v>
       </c>
       <c r="E205">
-        <v>46.4765100671141</v>
+        <v>8.622908622908623</v>
       </c>
       <c r="F205" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206">
-        <v>2023</v>
-      </c>
-      <c r="B206" t="s">
-        <v>55</v>
-      </c>
-      <c r="C206" t="s">
-        <v>201</v>
-      </c>
-      <c r="D206">
-        <v>444</v>
-      </c>
-      <c r="E206">
-        <v>18.6241610738255</v>
-      </c>
-      <c r="F206" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4685,19 +4725,19 @@
         <v>2023</v>
       </c>
       <c r="B207" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C207" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D207">
-        <v>343</v>
+        <v>886</v>
       </c>
       <c r="E207">
-        <v>14.38758389261745</v>
+        <v>48.86927744070601</v>
       </c>
       <c r="F207" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4705,19 +4745,19 @@
         <v>2023</v>
       </c>
       <c r="B208" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C208" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D208">
-        <v>323</v>
+        <v>699</v>
       </c>
       <c r="E208">
-        <v>13.5486577181208</v>
+        <v>38.55488141202427</v>
       </c>
       <c r="F208" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4725,19 +4765,19 @@
         <v>2023</v>
       </c>
       <c r="B209" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C209" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D209">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="E209">
-        <v>6.963087248322148</v>
+        <v>12.57584114726972</v>
       </c>
       <c r="F209" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4745,19 +4785,19 @@
         <v>2023</v>
       </c>
       <c r="B211" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C211" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D211">
-        <v>904</v>
+        <v>1630</v>
       </c>
       <c r="E211">
-        <v>42.60131950989632</v>
+        <v>44.46262956901255</v>
       </c>
       <c r="F211" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -4765,19 +4805,19 @@
         <v>2023</v>
       </c>
       <c r="B212" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C212" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D212">
-        <v>860</v>
+        <v>1039</v>
       </c>
       <c r="E212">
-        <v>40.52780395852969</v>
+        <v>28.34151663938898</v>
       </c>
       <c r="F212" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -4785,19 +4825,19 @@
         <v>2023</v>
       </c>
       <c r="B213" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C213" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D213">
-        <v>193</v>
+        <v>813</v>
       </c>
       <c r="E213">
-        <v>9.095193213949104</v>
+        <v>22.17675941080196</v>
       </c>
       <c r="F213" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -4805,19 +4845,19 @@
         <v>2023</v>
       </c>
       <c r="B214" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C214" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D214">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E214">
-        <v>7.775683317624882</v>
+        <v>5.019094380796509</v>
       </c>
       <c r="F214" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -4825,19 +4865,19 @@
         <v>2023</v>
       </c>
       <c r="B216" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C216" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="D216">
-        <v>425</v>
+        <v>1334</v>
       </c>
       <c r="E216">
-        <v>25.11820330969267</v>
+        <v>46.38386648122393</v>
       </c>
       <c r="F216" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -4845,19 +4885,19 @@
         <v>2023</v>
       </c>
       <c r="B217" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C217" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="D217">
-        <v>341</v>
+        <v>1278</v>
       </c>
       <c r="E217">
-        <v>20.15366430260048</v>
+        <v>44.43671766342142</v>
       </c>
       <c r="F217" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -4865,39 +4905,19 @@
         <v>2023</v>
       </c>
       <c r="B218" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C218" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D218">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="E218">
-        <v>16.48936170212766</v>
+        <v>9.179415855354661</v>
       </c>
       <c r="F218" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219">
-        <v>2023</v>
-      </c>
-      <c r="B219" t="s">
-        <v>57</v>
-      </c>
-      <c r="C219" t="s">
-        <v>205</v>
-      </c>
-      <c r="D219">
-        <v>272</v>
-      </c>
-      <c r="E219">
-        <v>16.07565011820331</v>
-      </c>
-      <c r="F219" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -4905,19 +4925,19 @@
         <v>2023</v>
       </c>
       <c r="B220" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C220" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D220">
-        <v>220</v>
+        <v>1466</v>
       </c>
       <c r="E220">
-        <v>13.00236406619385</v>
+        <v>43.1303324507208</v>
       </c>
       <c r="F220" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -4925,19 +4945,39 @@
         <v>2023</v>
       </c>
       <c r="B221" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C221" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D221">
-        <v>155</v>
+        <v>893</v>
       </c>
       <c r="E221">
-        <v>9.160756501182032</v>
+        <v>26.27243306854957</v>
       </c>
       <c r="F221" t="s">
-        <v>319</v>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222">
+        <v>2023</v>
+      </c>
+      <c r="B222" t="s">
+        <v>59</v>
+      </c>
+      <c r="C222" t="s">
+        <v>210</v>
+      </c>
+      <c r="D222">
+        <v>672</v>
+      </c>
+      <c r="E222">
+        <v>19.77052074139453</v>
+      </c>
+      <c r="F222" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -4945,19 +4985,19 @@
         <v>2023</v>
       </c>
       <c r="B223" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C223" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D223">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="E223">
-        <v>48.22934232715008</v>
+        <v>7.208002353633422</v>
       </c>
       <c r="F223" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -4965,39 +5005,39 @@
         <v>2023</v>
       </c>
       <c r="B224" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C224" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D224">
-        <v>212</v>
+        <v>123</v>
       </c>
       <c r="E224">
-        <v>35.7504215851602</v>
+        <v>3.618711385701677</v>
       </c>
       <c r="F224" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
-      <c r="A225">
-        <v>2023</v>
-      </c>
-      <c r="B225" t="s">
-        <v>58</v>
-      </c>
-      <c r="C225" t="s">
-        <v>222</v>
-      </c>
-      <c r="D225">
-        <v>95</v>
-      </c>
-      <c r="E225">
-        <v>16.02023608768971</v>
-      </c>
-      <c r="F225" t="s">
-        <v>315</v>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226">
+        <v>2023</v>
+      </c>
+      <c r="B226" t="s">
+        <v>60</v>
+      </c>
+      <c r="C226" t="s">
+        <v>216</v>
+      </c>
+      <c r="D226">
+        <v>1108</v>
+      </c>
+      <c r="E226">
+        <v>46.4765100671141</v>
+      </c>
+      <c r="F226" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -5005,19 +5045,19 @@
         <v>2023</v>
       </c>
       <c r="B227" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C227" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D227">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="E227">
-        <v>36.77474402730375</v>
+        <v>18.6241610738255</v>
       </c>
       <c r="F227" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -5025,19 +5065,19 @@
         <v>2023</v>
       </c>
       <c r="B228" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C228" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="D228">
-        <v>297</v>
+        <v>343</v>
       </c>
       <c r="E228">
-        <v>25.34129692832764</v>
+        <v>14.38758389261745</v>
       </c>
       <c r="F228" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -5045,19 +5085,19 @@
         <v>2023</v>
       </c>
       <c r="B229" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C229" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D229">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="E229">
-        <v>24.31740614334471</v>
+        <v>13.5486577181208</v>
       </c>
       <c r="F229" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5065,39 +5105,39 @@
         <v>2023</v>
       </c>
       <c r="B230" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C230" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D230">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="E230">
-        <v>8.191126279863481</v>
+        <v>6.963087248322148</v>
       </c>
       <c r="F230" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6">
-      <c r="A231">
-        <v>2023</v>
-      </c>
-      <c r="B231" t="s">
-        <v>59</v>
-      </c>
-      <c r="C231" t="s">
-        <v>227</v>
-      </c>
-      <c r="D231">
-        <v>63</v>
-      </c>
-      <c r="E231">
-        <v>5.375426621160409</v>
-      </c>
-      <c r="F231" t="s">
-        <v>315</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232">
+        <v>2023</v>
+      </c>
+      <c r="B232" t="s">
+        <v>61</v>
+      </c>
+      <c r="C232" t="s">
+        <v>236</v>
+      </c>
+      <c r="D232">
+        <v>904</v>
+      </c>
+      <c r="E232">
+        <v>42.60131950989632</v>
+      </c>
+      <c r="F232" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -5105,19 +5145,19 @@
         <v>2023</v>
       </c>
       <c r="B233" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C233" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D233">
-        <v>273</v>
+        <v>860</v>
       </c>
       <c r="E233">
-        <v>45.4242928452579</v>
+        <v>40.52780395852969</v>
       </c>
       <c r="F233" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5125,19 +5165,19 @@
         <v>2023</v>
       </c>
       <c r="B234" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C234" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D234">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="E234">
-        <v>38.9351081530782</v>
+        <v>9.095193213949104</v>
       </c>
       <c r="F234" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5145,19 +5185,19 @@
         <v>2023</v>
       </c>
       <c r="B235" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C235" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D235">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="E235">
-        <v>15.64059900166389</v>
+        <v>7.775683317624882</v>
       </c>
       <c r="F235" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -5165,19 +5205,19 @@
         <v>2023</v>
       </c>
       <c r="B237" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C237" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D237">
-        <v>124</v>
+        <v>425</v>
       </c>
       <c r="E237">
-        <v>47.69230769230769</v>
+        <v>25.11820330969267</v>
       </c>
       <c r="F237" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5185,19 +5225,19 @@
         <v>2023</v>
       </c>
       <c r="B238" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C238" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D238">
-        <v>73</v>
+        <v>341</v>
       </c>
       <c r="E238">
-        <v>28.07692307692308</v>
+        <v>20.15366430260048</v>
       </c>
       <c r="F238" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -5205,19 +5245,39 @@
         <v>2023</v>
       </c>
       <c r="B239" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C239" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D239">
-        <v>63</v>
+        <v>279</v>
       </c>
       <c r="E239">
-        <v>24.23076923076923</v>
+        <v>16.48936170212766</v>
       </c>
       <c r="F239" t="s">
-        <v>318</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240">
+        <v>2023</v>
+      </c>
+      <c r="B240" t="s">
+        <v>62</v>
+      </c>
+      <c r="C240" t="s">
+        <v>223</v>
+      </c>
+      <c r="D240">
+        <v>272</v>
+      </c>
+      <c r="E240">
+        <v>16.07565011820331</v>
+      </c>
+      <c r="F240" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -5228,16 +5288,16 @@
         <v>62</v>
       </c>
       <c r="C241" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D241">
-        <v>827</v>
+        <v>220</v>
       </c>
       <c r="E241">
-        <v>47.88650839606254</v>
+        <v>13.00236406619385</v>
       </c>
       <c r="F241" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -5248,36 +5308,16 @@
         <v>62</v>
       </c>
       <c r="C242" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D242">
-        <v>284</v>
+        <v>155</v>
       </c>
       <c r="E242">
-        <v>16.44470179502026</v>
+        <v>9.160756501182032</v>
       </c>
       <c r="F242" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
-      <c r="A243">
-        <v>2023</v>
-      </c>
-      <c r="B243" t="s">
-        <v>62</v>
-      </c>
-      <c r="C243" t="s">
-        <v>236</v>
-      </c>
-      <c r="D243">
-        <v>222</v>
-      </c>
-      <c r="E243">
-        <v>12.85466126230457</v>
-      </c>
-      <c r="F243" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -5285,19 +5325,19 @@
         <v>2023</v>
       </c>
       <c r="B244" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C244" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D244">
-        <v>211</v>
+        <v>286</v>
       </c>
       <c r="E244">
-        <v>12.21771858714534</v>
+        <v>48.22934232715008</v>
       </c>
       <c r="F244" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -5305,39 +5345,39 @@
         <v>2023</v>
       </c>
       <c r="B245" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C245" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D245">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="E245">
-        <v>10.59640995946728</v>
+        <v>35.7504215851602</v>
       </c>
       <c r="F245" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
-      <c r="A247">
-        <v>2023</v>
-      </c>
-      <c r="B247" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246">
+        <v>2023</v>
+      </c>
+      <c r="B246" t="s">
         <v>63</v>
       </c>
-      <c r="C247" t="s">
-        <v>239</v>
-      </c>
-      <c r="D247">
-        <v>605</v>
-      </c>
-      <c r="E247">
-        <v>41.10054347826087</v>
-      </c>
-      <c r="F247" t="s">
-        <v>320</v>
+      <c r="C246" t="s">
+        <v>243</v>
+      </c>
+      <c r="D246">
+        <v>95</v>
+      </c>
+      <c r="E246">
+        <v>16.02023608768971</v>
+      </c>
+      <c r="F246" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -5345,19 +5385,19 @@
         <v>2023</v>
       </c>
       <c r="B248" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C248" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D248">
-        <v>593</v>
+        <v>431</v>
       </c>
       <c r="E248">
-        <v>40.28532608695652</v>
+        <v>36.77474402730375</v>
       </c>
       <c r="F248" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -5365,19 +5405,39 @@
         <v>2023</v>
       </c>
       <c r="B249" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C249" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D249">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="E249">
-        <v>18.61413043478261</v>
+        <v>25.34129692832764</v>
       </c>
       <c r="F249" t="s">
-        <v>320</v>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250">
+        <v>2023</v>
+      </c>
+      <c r="B250" t="s">
+        <v>64</v>
+      </c>
+      <c r="C250" t="s">
+        <v>246</v>
+      </c>
+      <c r="D250">
+        <v>285</v>
+      </c>
+      <c r="E250">
+        <v>24.31740614334471</v>
+      </c>
+      <c r="F250" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -5388,16 +5448,16 @@
         <v>64</v>
       </c>
       <c r="C251" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D251">
-        <v>347</v>
+        <v>96</v>
       </c>
       <c r="E251">
-        <v>49.15014164305949</v>
+        <v>8.191126279863481</v>
       </c>
       <c r="F251" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -5408,36 +5468,16 @@
         <v>64</v>
       </c>
       <c r="C252" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D252">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="E252">
-        <v>23.79603399433428</v>
+        <v>5.375426621160409</v>
       </c>
       <c r="F252" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
-      <c r="A253">
-        <v>2023</v>
-      </c>
-      <c r="B253" t="s">
-        <v>64</v>
-      </c>
-      <c r="C253" t="s">
-        <v>244</v>
-      </c>
-      <c r="D253">
-        <v>103</v>
-      </c>
-      <c r="E253">
-        <v>14.58923512747875</v>
-      </c>
-      <c r="F253" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -5445,419 +5485,419 @@
         <v>2023</v>
       </c>
       <c r="B254" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C254" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D254">
-        <v>88</v>
+        <v>273</v>
       </c>
       <c r="E254">
-        <v>12.46458923512748</v>
+        <v>45.4242928452579</v>
       </c>
       <c r="F254" t="s">
-        <v>320</v>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255">
+        <v>2023</v>
+      </c>
+      <c r="B255" t="s">
+        <v>65</v>
+      </c>
+      <c r="C255" t="s">
+        <v>250</v>
+      </c>
+      <c r="D255">
+        <v>234</v>
+      </c>
+      <c r="E255">
+        <v>38.9351081530782</v>
+      </c>
+      <c r="F255" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B256" t="s">
         <v>65</v>
       </c>
       <c r="C256" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D256">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="E256">
-        <v>44.68085106382978</v>
+        <v>15.64059900166389</v>
       </c>
       <c r="F256" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
-      <c r="A257">
-        <v>2024</v>
-      </c>
-      <c r="B257" t="s">
-        <v>65</v>
-      </c>
-      <c r="C257" t="s">
-        <v>247</v>
-      </c>
-      <c r="D257">
-        <v>102</v>
-      </c>
-      <c r="E257">
-        <v>31.00303951367781</v>
-      </c>
-      <c r="F257" t="s">
-        <v>10</v>
+        <v>339</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B258" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C258" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D258">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="E258">
-        <v>24.3161094224924</v>
+        <v>47.69230769230769</v>
       </c>
       <c r="F258" t="s">
-        <v>10</v>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259">
+        <v>2023</v>
+      </c>
+      <c r="B259" t="s">
+        <v>66</v>
+      </c>
+      <c r="C259" t="s">
+        <v>253</v>
+      </c>
+      <c r="D259">
+        <v>73</v>
+      </c>
+      <c r="E259">
+        <v>28.07692307692308</v>
+      </c>
+      <c r="F259" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B260" t="s">
         <v>66</v>
       </c>
       <c r="C260" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D260">
-        <v>1224</v>
+        <v>63</v>
       </c>
       <c r="E260">
-        <v>28.77291960507758</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="F260" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
-      <c r="A261">
-        <v>2025</v>
-      </c>
-      <c r="B261" t="s">
-        <v>66</v>
-      </c>
-      <c r="C261" t="s">
-        <v>250</v>
-      </c>
-      <c r="D261">
-        <v>1052</v>
-      </c>
-      <c r="E261">
-        <v>24.72966619652092</v>
-      </c>
-      <c r="F261" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B262" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C262" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D262">
-        <v>685</v>
+        <v>827</v>
       </c>
       <c r="E262">
-        <v>16.10249177244946</v>
+        <v>47.88650839606254</v>
       </c>
       <c r="F262" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B263" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C263" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D263">
-        <v>656</v>
+        <v>284</v>
       </c>
       <c r="E263">
-        <v>15.420780441937</v>
+        <v>16.44470179502026</v>
       </c>
       <c r="F263" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B264" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C264" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D264">
-        <v>637</v>
+        <v>222</v>
       </c>
       <c r="E264">
-        <v>14.97414198401504</v>
+        <v>12.85466126230457</v>
       </c>
       <c r="F264" t="s">
-        <v>323</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265">
+        <v>2023</v>
+      </c>
+      <c r="B265" t="s">
+        <v>67</v>
+      </c>
+      <c r="C265" t="s">
+        <v>258</v>
+      </c>
+      <c r="D265">
+        <v>211</v>
+      </c>
+      <c r="E265">
+        <v>12.21771858714534</v>
+      </c>
+      <c r="F265" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B266" t="s">
         <v>67</v>
       </c>
       <c r="C266" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D266">
-        <v>3817</v>
+        <v>183</v>
       </c>
       <c r="E266">
-        <v>39.10860655737705</v>
+        <v>10.59640995946728</v>
       </c>
       <c r="F266" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="A267">
-        <v>2025</v>
-      </c>
-      <c r="B267" t="s">
-        <v>67</v>
-      </c>
-      <c r="C267" t="s">
-        <v>255</v>
-      </c>
-      <c r="D267">
-        <v>3272</v>
-      </c>
-      <c r="E267">
-        <v>33.52459016393443</v>
-      </c>
-      <c r="F267" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B268" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C268" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D268">
-        <v>2671</v>
+        <v>605</v>
       </c>
       <c r="E268">
-        <v>27.36680327868852</v>
+        <v>41.10054347826087</v>
       </c>
       <c r="F268" t="s">
-        <v>323</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269">
+        <v>2023</v>
+      </c>
+      <c r="B269" t="s">
+        <v>68</v>
+      </c>
+      <c r="C269" t="s">
+        <v>261</v>
+      </c>
+      <c r="D269">
+        <v>593</v>
+      </c>
+      <c r="E269">
+        <v>40.28532608695652</v>
+      </c>
+      <c r="F269" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B270" t="s">
         <v>68</v>
       </c>
       <c r="C270" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D270">
-        <v>710</v>
+        <v>274</v>
       </c>
       <c r="E270">
-        <v>46.64914586070959</v>
+        <v>18.61413043478261</v>
       </c>
       <c r="F270" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
-      <c r="A271">
-        <v>2025</v>
-      </c>
-      <c r="B271" t="s">
-        <v>68</v>
-      </c>
-      <c r="C271" t="s">
-        <v>258</v>
-      </c>
-      <c r="D271">
-        <v>617</v>
-      </c>
-      <c r="E271">
-        <v>40.53876478318003</v>
-      </c>
-      <c r="F271" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B272" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C272" t="s">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="D272">
-        <v>195</v>
+        <v>347</v>
       </c>
       <c r="E272">
-        <v>12.81208935611038</v>
+        <v>49.15014164305949</v>
       </c>
       <c r="F272" t="s">
-        <v>315</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273">
+        <v>2023</v>
+      </c>
+      <c r="B273" t="s">
+        <v>69</v>
+      </c>
+      <c r="C273" t="s">
+        <v>264</v>
+      </c>
+      <c r="D273">
+        <v>168</v>
+      </c>
+      <c r="E273">
+        <v>23.79603399433428</v>
+      </c>
+      <c r="F273" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B274" t="s">
         <v>69</v>
       </c>
       <c r="C274" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D274">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="E274">
-        <v>49.79338842975206</v>
+        <v>14.58923512747875</v>
       </c>
       <c r="F274" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B275" t="s">
         <v>69</v>
       </c>
       <c r="C275" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D275">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="E275">
-        <v>39.87603305785124</v>
+        <v>12.46458923512748</v>
       </c>
       <c r="F275" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
-      <c r="A276">
-        <v>2025</v>
-      </c>
-      <c r="B276" t="s">
-        <v>69</v>
-      </c>
-      <c r="C276" t="s">
-        <v>261</v>
-      </c>
-      <c r="D276">
-        <v>49</v>
-      </c>
-      <c r="E276">
-        <v>10.12396694214876</v>
-      </c>
-      <c r="F276" t="s">
-        <v>320</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277">
+        <v>2024</v>
+      </c>
+      <c r="B277" t="s">
+        <v>70</v>
+      </c>
+      <c r="C277" t="s">
+        <v>267</v>
+      </c>
+      <c r="D277">
+        <v>147</v>
+      </c>
+      <c r="E277">
+        <v>44.68085106382978</v>
+      </c>
+      <c r="F277" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B278" t="s">
         <v>70</v>
       </c>
       <c r="C278" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D278">
-        <v>373</v>
+        <v>102</v>
       </c>
       <c r="E278">
-        <v>36.39024390243902</v>
+        <v>31.00303951367781</v>
       </c>
       <c r="F278" t="s">
-        <v>311</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B279" t="s">
         <v>70</v>
       </c>
       <c r="C279" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D279">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="E279">
-        <v>21.95121951219512</v>
+        <v>24.3161094224924</v>
       </c>
       <c r="F279" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
-      <c r="A280">
-        <v>2025</v>
-      </c>
-      <c r="B280" t="s">
-        <v>70</v>
-      </c>
-      <c r="C280" t="s">
-        <v>264</v>
-      </c>
-      <c r="D280">
-        <v>206</v>
-      </c>
-      <c r="E280">
-        <v>20.09756097560976</v>
-      </c>
-      <c r="F280" t="s">
-        <v>311</v>
+        <v>10</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -5865,19 +5905,19 @@
         <v>2025</v>
       </c>
       <c r="B281" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C281" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D281">
-        <v>140</v>
+        <v>1224</v>
       </c>
       <c r="E281">
-        <v>13.65853658536586</v>
+        <v>28.77291960507758</v>
       </c>
       <c r="F281" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -5885,19 +5925,39 @@
         <v>2025</v>
       </c>
       <c r="B282" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C282" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D282">
-        <v>81</v>
+        <v>1052</v>
       </c>
       <c r="E282">
-        <v>7.902439024390244</v>
+        <v>24.72966619652092</v>
       </c>
       <c r="F282" t="s">
-        <v>311</v>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283">
+        <v>2025</v>
+      </c>
+      <c r="B283" t="s">
+        <v>71</v>
+      </c>
+      <c r="C283" t="s">
+        <v>272</v>
+      </c>
+      <c r="D283">
+        <v>685</v>
+      </c>
+      <c r="E283">
+        <v>16.10249177244946</v>
+      </c>
+      <c r="F283" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -5905,19 +5965,19 @@
         <v>2025</v>
       </c>
       <c r="B284" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C284" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D284">
-        <v>6552</v>
+        <v>656</v>
       </c>
       <c r="E284">
-        <v>47.15704620699582</v>
+        <v>15.420780441937</v>
       </c>
       <c r="F284" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -5925,39 +5985,39 @@
         <v>2025</v>
       </c>
       <c r="B285" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C285" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D285">
-        <v>4724</v>
+        <v>637</v>
       </c>
       <c r="E285">
-        <v>34.00028789405498</v>
+        <v>14.97414198401504</v>
       </c>
       <c r="F285" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
-      <c r="A286">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287">
         <v>2025</v>
       </c>
-      <c r="B286" t="s">
-        <v>31</v>
-      </c>
-      <c r="C286" t="s">
-        <v>269</v>
-      </c>
-      <c r="D286">
-        <v>2618</v>
-      </c>
-      <c r="E286">
-        <v>18.84266589894919</v>
-      </c>
-      <c r="F286" t="s">
-        <v>315</v>
+      <c r="B287" t="s">
+        <v>72</v>
+      </c>
+      <c r="C287" t="s">
+        <v>275</v>
+      </c>
+      <c r="D287">
+        <v>3817</v>
+      </c>
+      <c r="E287">
+        <v>39.10860655737705</v>
+      </c>
+      <c r="F287" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -5965,19 +6025,19 @@
         <v>2025</v>
       </c>
       <c r="B288" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C288" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D288">
-        <v>5832</v>
+        <v>3272</v>
       </c>
       <c r="E288">
-        <v>37.28423475258919</v>
+        <v>33.52459016393443</v>
       </c>
       <c r="F288" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -5985,39 +6045,39 @@
         <v>2025</v>
       </c>
       <c r="B289" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C289" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D289">
-        <v>4950</v>
+        <v>2671</v>
       </c>
       <c r="E289">
-        <v>31.64556962025317</v>
+        <v>27.36680327868852</v>
       </c>
       <c r="F289" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
-      <c r="A290">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291">
         <v>2025</v>
       </c>
-      <c r="B290" t="s">
-        <v>71</v>
-      </c>
-      <c r="C290" t="s">
-        <v>272</v>
-      </c>
-      <c r="D290">
-        <v>4834</v>
-      </c>
-      <c r="E290">
-        <v>30.90397647359673</v>
-      </c>
-      <c r="F290" t="s">
-        <v>323</v>
+      <c r="B291" t="s">
+        <v>73</v>
+      </c>
+      <c r="C291" t="s">
+        <v>278</v>
+      </c>
+      <c r="D291">
+        <v>710</v>
+      </c>
+      <c r="E291">
+        <v>46.64914586070959</v>
+      </c>
+      <c r="F291" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -6025,19 +6085,19 @@
         <v>2025</v>
       </c>
       <c r="B292" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C292" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D292">
-        <v>9318</v>
+        <v>617</v>
       </c>
       <c r="E292">
-        <v>41.92764578833693</v>
+        <v>40.53876478318003</v>
       </c>
       <c r="F292" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -6045,39 +6105,39 @@
         <v>2025</v>
       </c>
       <c r="B293" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C293" t="s">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="D293">
-        <v>8700</v>
+        <v>195</v>
       </c>
       <c r="E293">
-        <v>39.14686825053996</v>
+        <v>12.81208935611038</v>
       </c>
       <c r="F293" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
-      <c r="A294">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295">
         <v>2025</v>
       </c>
-      <c r="B294" t="s">
-        <v>72</v>
-      </c>
-      <c r="C294" t="s">
-        <v>275</v>
-      </c>
-      <c r="D294">
-        <v>4206</v>
-      </c>
-      <c r="E294">
-        <v>18.92548596112311</v>
-      </c>
-      <c r="F294" t="s">
-        <v>321</v>
+      <c r="B295" t="s">
+        <v>74</v>
+      </c>
+      <c r="C295" t="s">
+        <v>280</v>
+      </c>
+      <c r="D295">
+        <v>241</v>
+      </c>
+      <c r="E295">
+        <v>49.79338842975206</v>
+      </c>
+      <c r="F295" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -6085,19 +6145,19 @@
         <v>2025</v>
       </c>
       <c r="B296" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C296" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D296">
-        <v>1473</v>
+        <v>193</v>
       </c>
       <c r="E296">
-        <v>39.30096051227321</v>
+        <v>39.87603305785124</v>
       </c>
       <c r="F296" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -6105,39 +6165,19 @@
         <v>2025</v>
       </c>
       <c r="B297" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C297" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D297">
-        <v>1297</v>
+        <v>49</v>
       </c>
       <c r="E297">
-        <v>34.6051227321238</v>
+        <v>10.12396694214876</v>
       </c>
       <c r="F297" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6">
-      <c r="A298">
-        <v>2025</v>
-      </c>
-      <c r="B298" t="s">
-        <v>73</v>
-      </c>
-      <c r="C298" t="s">
-        <v>278</v>
-      </c>
-      <c r="D298">
-        <v>516</v>
-      </c>
-      <c r="E298">
-        <v>13.76734258271078</v>
-      </c>
-      <c r="F298" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -6145,19 +6185,19 @@
         <v>2025</v>
       </c>
       <c r="B299" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C299" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D299">
-        <v>305</v>
+        <v>373</v>
       </c>
       <c r="E299">
-        <v>8.137673425827108</v>
+        <v>36.39024390243902</v>
       </c>
       <c r="F299" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -6165,19 +6205,39 @@
         <v>2025</v>
       </c>
       <c r="B300" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C300" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D300">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="E300">
-        <v>4.188900747065102</v>
+        <v>21.95121951219512</v>
       </c>
       <c r="F300" t="s">
-        <v>319</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301">
+        <v>2025</v>
+      </c>
+      <c r="B301" t="s">
+        <v>75</v>
+      </c>
+      <c r="C301" t="s">
+        <v>285</v>
+      </c>
+      <c r="D301">
+        <v>206</v>
+      </c>
+      <c r="E301">
+        <v>20.09756097560976</v>
+      </c>
+      <c r="F301" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -6185,19 +6245,19 @@
         <v>2025</v>
       </c>
       <c r="B302" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C302" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D302">
-        <v>854</v>
+        <v>140</v>
       </c>
       <c r="E302">
-        <v>47.52365052865888</v>
+        <v>13.65853658536586</v>
       </c>
       <c r="F302" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -6205,39 +6265,39 @@
         <v>2025</v>
       </c>
       <c r="B303" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C303" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D303">
-        <v>764</v>
+        <v>81</v>
       </c>
       <c r="E303">
-        <v>42.51530328324986</v>
+        <v>7.902439024390244</v>
       </c>
       <c r="F303" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6">
-      <c r="A304">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305">
         <v>2025</v>
       </c>
-      <c r="B304" t="s">
-        <v>74</v>
-      </c>
-      <c r="C304" t="s">
-        <v>283</v>
-      </c>
-      <c r="D304">
-        <v>175</v>
-      </c>
-      <c r="E304">
-        <v>9.738452977184195</v>
-      </c>
-      <c r="F304" t="s">
-        <v>310</v>
+      <c r="B305" t="s">
+        <v>35</v>
+      </c>
+      <c r="C305" t="s">
+        <v>288</v>
+      </c>
+      <c r="D305">
+        <v>6552</v>
+      </c>
+      <c r="E305">
+        <v>47.15704620699582</v>
+      </c>
+      <c r="F305" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -6245,19 +6305,19 @@
         <v>2025</v>
       </c>
       <c r="B306" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="C306" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D306">
-        <v>162</v>
+        <v>4724</v>
       </c>
       <c r="E306">
-        <v>45.2513966480447</v>
+        <v>34.00028789405498</v>
       </c>
       <c r="F306" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -6265,39 +6325,39 @@
         <v>2025</v>
       </c>
       <c r="B307" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="C307" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D307">
-        <v>156</v>
+        <v>2618</v>
       </c>
       <c r="E307">
-        <v>43.5754189944134</v>
+        <v>18.84266589894919</v>
       </c>
       <c r="F307" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6">
-      <c r="A308">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309">
         <v>2025</v>
       </c>
-      <c r="B308" t="s">
-        <v>75</v>
-      </c>
-      <c r="C308" t="s">
-        <v>286</v>
-      </c>
-      <c r="D308">
-        <v>40</v>
-      </c>
-      <c r="E308">
-        <v>11.1731843575419</v>
-      </c>
-      <c r="F308" t="s">
-        <v>311</v>
+      <c r="B309" t="s">
+        <v>76</v>
+      </c>
+      <c r="C309" t="s">
+        <v>291</v>
+      </c>
+      <c r="D309">
+        <v>5832</v>
+      </c>
+      <c r="E309">
+        <v>37.28423475258919</v>
+      </c>
+      <c r="F309" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -6308,16 +6368,16 @@
         <v>76</v>
       </c>
       <c r="C310" t="s">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="D310">
-        <v>11367</v>
+        <v>4950</v>
       </c>
       <c r="E310">
-        <v>45.69280861840254</v>
+        <v>31.64556962025317</v>
       </c>
       <c r="F310" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -6328,36 +6388,36 @@
         <v>76</v>
       </c>
       <c r="C311" t="s">
-        <v>95</v>
+        <v>292</v>
       </c>
       <c r="D311">
-        <v>8188</v>
+        <v>4834</v>
       </c>
       <c r="E311">
-        <v>32.91393656791413</v>
+        <v>30.90397647359673</v>
       </c>
       <c r="F311" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6">
-      <c r="A312">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313">
         <v>2025</v>
       </c>
-      <c r="B312" t="s">
-        <v>76</v>
-      </c>
-      <c r="C312" t="s">
-        <v>98</v>
-      </c>
-      <c r="D312">
-        <v>5322</v>
-      </c>
-      <c r="E312">
-        <v>21.39325481368332</v>
-      </c>
-      <c r="F312" t="s">
-        <v>311</v>
+      <c r="B313" t="s">
+        <v>77</v>
+      </c>
+      <c r="C313" t="s">
+        <v>293</v>
+      </c>
+      <c r="D313">
+        <v>9318</v>
+      </c>
+      <c r="E313">
+        <v>41.92764578833693</v>
+      </c>
+      <c r="F313" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -6368,16 +6428,16 @@
         <v>77</v>
       </c>
       <c r="C314" t="s">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="D314">
-        <v>287</v>
+        <v>8700</v>
       </c>
       <c r="E314">
-        <v>47.83333333333334</v>
+        <v>39.14686825053996</v>
       </c>
       <c r="F314" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -6388,36 +6448,36 @@
         <v>77</v>
       </c>
       <c r="C315" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D315">
-        <v>175</v>
+        <v>4206</v>
       </c>
       <c r="E315">
-        <v>29.16666666666667</v>
+        <v>18.92548596112311</v>
       </c>
       <c r="F315" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6">
-      <c r="A316">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317">
         <v>2025</v>
       </c>
-      <c r="B316" t="s">
-        <v>77</v>
-      </c>
-      <c r="C316" t="s">
-        <v>288</v>
-      </c>
-      <c r="D316">
-        <v>138</v>
-      </c>
-      <c r="E316">
-        <v>23</v>
-      </c>
-      <c r="F316" t="s">
-        <v>315</v>
+      <c r="B317" t="s">
+        <v>78</v>
+      </c>
+      <c r="C317" t="s">
+        <v>296</v>
+      </c>
+      <c r="D317">
+        <v>1473</v>
+      </c>
+      <c r="E317">
+        <v>39.30096051227321</v>
+      </c>
+      <c r="F317" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -6428,16 +6488,16 @@
         <v>78</v>
       </c>
       <c r="C318" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D318">
-        <v>163</v>
+        <v>1297</v>
       </c>
       <c r="E318">
-        <v>38.71733966745843</v>
+        <v>34.6051227321238</v>
       </c>
       <c r="F318" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -6448,16 +6508,16 @@
         <v>78</v>
       </c>
       <c r="C319" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D319">
-        <v>160</v>
+        <v>516</v>
       </c>
       <c r="E319">
-        <v>38.00475059382423</v>
+        <v>13.76734258271078</v>
       </c>
       <c r="F319" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -6468,16 +6528,16 @@
         <v>78</v>
       </c>
       <c r="C320" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D320">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="E320">
-        <v>17.81472684085511</v>
+        <v>8.137673425827108</v>
       </c>
       <c r="F320" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -6488,16 +6548,16 @@
         <v>78</v>
       </c>
       <c r="C321" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D321">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="E321">
-        <v>5.463182897862233</v>
+        <v>4.188900747065102</v>
       </c>
       <c r="F321" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -6508,16 +6568,16 @@
         <v>79</v>
       </c>
       <c r="C323" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D323">
-        <v>104</v>
+        <v>854</v>
       </c>
       <c r="E323">
-        <v>35.37414965986395</v>
+        <v>47.52365052865888</v>
       </c>
       <c r="F323" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -6528,16 +6588,16 @@
         <v>79</v>
       </c>
       <c r="C324" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D324">
-        <v>79</v>
+        <v>764</v>
       </c>
       <c r="E324">
-        <v>26.87074829931973</v>
+        <v>42.51530328324986</v>
       </c>
       <c r="F324" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -6548,36 +6608,36 @@
         <v>79</v>
       </c>
       <c r="C325" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D325">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="E325">
-        <v>26.53061224489796</v>
+        <v>9.738452977184195</v>
       </c>
       <c r="F325" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6">
-      <c r="A326">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327">
         <v>2025</v>
       </c>
-      <c r="B326" t="s">
-        <v>79</v>
-      </c>
-      <c r="C326" t="s">
-        <v>296</v>
-      </c>
-      <c r="D326">
-        <v>32</v>
-      </c>
-      <c r="E326">
-        <v>10.8843537414966</v>
-      </c>
-      <c r="F326" t="s">
-        <v>310</v>
+      <c r="B327" t="s">
+        <v>80</v>
+      </c>
+      <c r="C327" t="s">
+        <v>304</v>
+      </c>
+      <c r="D327">
+        <v>162</v>
+      </c>
+      <c r="E327">
+        <v>45.2513966480447</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -6588,16 +6648,16 @@
         <v>80</v>
       </c>
       <c r="C328" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D328">
-        <v>549</v>
+        <v>156</v>
       </c>
       <c r="E328">
-        <v>42.99138606108065</v>
+        <v>43.5754189944134</v>
       </c>
       <c r="F328" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -6608,36 +6668,36 @@
         <v>80</v>
       </c>
       <c r="C329" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D329">
-        <v>445</v>
+        <v>40</v>
       </c>
       <c r="E329">
-        <v>34.84729835552075</v>
+        <v>11.1731843575419</v>
       </c>
       <c r="F329" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6">
-      <c r="A330">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331">
         <v>2025</v>
       </c>
-      <c r="B330" t="s">
-        <v>80</v>
-      </c>
-      <c r="C330" t="s">
-        <v>299</v>
-      </c>
-      <c r="D330">
-        <v>283</v>
-      </c>
-      <c r="E330">
-        <v>22.16131558339859</v>
-      </c>
-      <c r="F330" t="s">
-        <v>321</v>
+      <c r="B331" t="s">
+        <v>81</v>
+      </c>
+      <c r="C331" t="s">
+        <v>101</v>
+      </c>
+      <c r="D331">
+        <v>11367</v>
+      </c>
+      <c r="E331">
+        <v>45.69280861840254</v>
+      </c>
+      <c r="F331" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -6648,16 +6708,16 @@
         <v>81</v>
       </c>
       <c r="C332" t="s">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D332">
-        <v>123</v>
+        <v>8188</v>
       </c>
       <c r="E332">
-        <v>28.21100917431193</v>
+        <v>32.91393656791413</v>
       </c>
       <c r="F332" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -6668,36 +6728,16 @@
         <v>81</v>
       </c>
       <c r="C333" t="s">
-        <v>301</v>
+        <v>103</v>
       </c>
       <c r="D333">
-        <v>117</v>
+        <v>5322</v>
       </c>
       <c r="E333">
-        <v>26.8348623853211</v>
+        <v>21.39325481368332</v>
       </c>
       <c r="F333" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6">
-      <c r="A334">
-        <v>2025</v>
-      </c>
-      <c r="B334" t="s">
-        <v>81</v>
-      </c>
-      <c r="C334" t="s">
-        <v>302</v>
-      </c>
-      <c r="D334">
-        <v>106</v>
-      </c>
-      <c r="E334">
-        <v>24.31192660550459</v>
-      </c>
-      <c r="F334" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -6705,19 +6745,39 @@
         <v>2025</v>
       </c>
       <c r="B335" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C335" t="s">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="D335">
-        <v>90</v>
+        <v>287</v>
       </c>
       <c r="E335">
-        <v>20.64220183486239</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="F335" t="s">
-        <v>321</v>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336">
+        <v>2025</v>
+      </c>
+      <c r="B336" t="s">
+        <v>82</v>
+      </c>
+      <c r="C336" t="s">
+        <v>307</v>
+      </c>
+      <c r="D336">
+        <v>175</v>
+      </c>
+      <c r="E336">
+        <v>29.16666666666667</v>
+      </c>
+      <c r="F336" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -6728,36 +6788,16 @@
         <v>82</v>
       </c>
       <c r="C337" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D337">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="E337">
-        <v>45.03464203233256</v>
+        <v>23</v>
       </c>
       <c r="F337" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6">
-      <c r="A338">
-        <v>2025</v>
-      </c>
-      <c r="B338" t="s">
-        <v>82</v>
-      </c>
-      <c r="C338" t="s">
-        <v>305</v>
-      </c>
-      <c r="D338">
-        <v>162</v>
-      </c>
-      <c r="E338">
-        <v>37.41339491916859</v>
-      </c>
-      <c r="F338" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -6765,19 +6805,39 @@
         <v>2025</v>
       </c>
       <c r="B339" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C339" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D339">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="E339">
-        <v>17.55196304849884</v>
+        <v>38.71733966745843</v>
       </c>
       <c r="F339" t="s">
-        <v>321</v>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340">
+        <v>2025</v>
+      </c>
+      <c r="B340" t="s">
+        <v>83</v>
+      </c>
+      <c r="C340" t="s">
+        <v>310</v>
+      </c>
+      <c r="D340">
+        <v>160</v>
+      </c>
+      <c r="E340">
+        <v>38.00475059382423</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -6788,16 +6848,16 @@
         <v>83</v>
       </c>
       <c r="C341" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D341">
-        <v>315</v>
+        <v>75</v>
       </c>
       <c r="E341">
-        <v>43.09165526675787</v>
+        <v>17.81472684085511</v>
       </c>
       <c r="F341" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -6808,36 +6868,356 @@
         <v>83</v>
       </c>
       <c r="C342" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D342">
+        <v>23</v>
+      </c>
+      <c r="E342">
+        <v>5.463182897862233</v>
+      </c>
+      <c r="F342" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344">
+        <v>2025</v>
+      </c>
+      <c r="B344" t="s">
+        <v>84</v>
+      </c>
+      <c r="C344" t="s">
+        <v>313</v>
+      </c>
+      <c r="D344">
+        <v>104</v>
+      </c>
+      <c r="E344">
+        <v>35.37414965986395</v>
+      </c>
+      <c r="F344" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345">
+        <v>2025</v>
+      </c>
+      <c r="B345" t="s">
+        <v>84</v>
+      </c>
+      <c r="C345" t="s">
+        <v>314</v>
+      </c>
+      <c r="D345">
+        <v>79</v>
+      </c>
+      <c r="E345">
+        <v>26.87074829931973</v>
+      </c>
+      <c r="F345" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346">
+        <v>2025</v>
+      </c>
+      <c r="B346" t="s">
+        <v>84</v>
+      </c>
+      <c r="C346" t="s">
+        <v>315</v>
+      </c>
+      <c r="D346">
+        <v>78</v>
+      </c>
+      <c r="E346">
+        <v>26.53061224489796</v>
+      </c>
+      <c r="F346" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347">
+        <v>2025</v>
+      </c>
+      <c r="B347" t="s">
+        <v>84</v>
+      </c>
+      <c r="C347" t="s">
+        <v>316</v>
+      </c>
+      <c r="D347">
+        <v>32</v>
+      </c>
+      <c r="E347">
+        <v>10.8843537414966</v>
+      </c>
+      <c r="F347" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349">
+        <v>2025</v>
+      </c>
+      <c r="B349" t="s">
+        <v>85</v>
+      </c>
+      <c r="C349" t="s">
+        <v>317</v>
+      </c>
+      <c r="D349">
+        <v>549</v>
+      </c>
+      <c r="E349">
+        <v>42.99138606108065</v>
+      </c>
+      <c r="F349" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350">
+        <v>2025</v>
+      </c>
+      <c r="B350" t="s">
+        <v>85</v>
+      </c>
+      <c r="C350" t="s">
+        <v>318</v>
+      </c>
+      <c r="D350">
+        <v>445</v>
+      </c>
+      <c r="E350">
+        <v>34.84729835552075</v>
+      </c>
+      <c r="F350" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351">
+        <v>2025</v>
+      </c>
+      <c r="B351" t="s">
+        <v>85</v>
+      </c>
+      <c r="C351" t="s">
+        <v>319</v>
+      </c>
+      <c r="D351">
+        <v>283</v>
+      </c>
+      <c r="E351">
+        <v>22.16131558339859</v>
+      </c>
+      <c r="F351" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353">
+        <v>2025</v>
+      </c>
+      <c r="B353" t="s">
+        <v>86</v>
+      </c>
+      <c r="C353" t="s">
+        <v>320</v>
+      </c>
+      <c r="D353">
+        <v>123</v>
+      </c>
+      <c r="E353">
+        <v>28.21100917431193</v>
+      </c>
+      <c r="F353" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354">
+        <v>2025</v>
+      </c>
+      <c r="B354" t="s">
+        <v>86</v>
+      </c>
+      <c r="C354" t="s">
+        <v>321</v>
+      </c>
+      <c r="D354">
+        <v>117</v>
+      </c>
+      <c r="E354">
+        <v>26.8348623853211</v>
+      </c>
+      <c r="F354" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355">
+        <v>2025</v>
+      </c>
+      <c r="B355" t="s">
+        <v>86</v>
+      </c>
+      <c r="C355" t="s">
+        <v>322</v>
+      </c>
+      <c r="D355">
+        <v>106</v>
+      </c>
+      <c r="E355">
+        <v>24.31192660550459</v>
+      </c>
+      <c r="F355" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356">
+        <v>2025</v>
+      </c>
+      <c r="B356" t="s">
+        <v>86</v>
+      </c>
+      <c r="C356" t="s">
+        <v>323</v>
+      </c>
+      <c r="D356">
+        <v>90</v>
+      </c>
+      <c r="E356">
+        <v>20.64220183486239</v>
+      </c>
+      <c r="F356" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358">
+        <v>2025</v>
+      </c>
+      <c r="B358" t="s">
+        <v>87</v>
+      </c>
+      <c r="C358" t="s">
+        <v>324</v>
+      </c>
+      <c r="D358">
+        <v>195</v>
+      </c>
+      <c r="E358">
+        <v>45.03464203233256</v>
+      </c>
+      <c r="F358" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359">
+        <v>2025</v>
+      </c>
+      <c r="B359" t="s">
+        <v>87</v>
+      </c>
+      <c r="C359" t="s">
+        <v>325</v>
+      </c>
+      <c r="D359">
+        <v>162</v>
+      </c>
+      <c r="E359">
+        <v>37.41339491916859</v>
+      </c>
+      <c r="F359" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360">
+        <v>2025</v>
+      </c>
+      <c r="B360" t="s">
+        <v>87</v>
+      </c>
+      <c r="C360" t="s">
+        <v>326</v>
+      </c>
+      <c r="D360">
+        <v>76</v>
+      </c>
+      <c r="E360">
+        <v>17.55196304849884</v>
+      </c>
+      <c r="F360" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362">
+        <v>2025</v>
+      </c>
+      <c r="B362" t="s">
+        <v>88</v>
+      </c>
+      <c r="C362" t="s">
+        <v>327</v>
+      </c>
+      <c r="D362">
+        <v>315</v>
+      </c>
+      <c r="E362">
+        <v>43.09165526675787</v>
+      </c>
+      <c r="F362" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363">
+        <v>2025</v>
+      </c>
+      <c r="B363" t="s">
+        <v>88</v>
+      </c>
+      <c r="C363" t="s">
+        <v>328</v>
+      </c>
+      <c r="D363">
         <v>247</v>
       </c>
-      <c r="E342">
+      <c r="E363">
         <v>33.78932968536252</v>
       </c>
-      <c r="F342" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6">
-      <c r="A343">
+      <c r="F363" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364">
         <v>2025</v>
       </c>
-      <c r="B343" t="s">
-        <v>83</v>
-      </c>
-      <c r="C343" t="s">
-        <v>309</v>
-      </c>
-      <c r="D343">
+      <c r="B364" t="s">
+        <v>88</v>
+      </c>
+      <c r="C364" t="s">
+        <v>329</v>
+      </c>
+      <c r="D364">
         <v>169</v>
       </c>
-      <c r="E343">
+      <c r="E364">
         <v>23.11901504787962</v>
       </c>
-      <c r="F343" t="s">
-        <v>314</v>
+      <c r="F364" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="418">
   <si>
     <t>Year</t>
   </si>
@@ -101,6 +101,9 @@
     <t>DEM Mayor-Swoyersville Borough (4 Year Term)</t>
   </si>
   <si>
+    <t>DEM SUPERVISOR SMITH</t>
+  </si>
+  <si>
     <t>Fairview Township 1st District Inspector of Election Rep</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
     <t>North East Borough Mayor Rep</t>
   </si>
   <si>
+    <t>REP AUDITOR DONEGAL</t>
+  </si>
+  <si>
     <t>REP CONSTABLE LIGONIER</t>
   </si>
   <si>
@@ -125,6 +131,12 @@
     <t>REP JUDGE OF THE COURT OF COMMON PLEAS</t>
   </si>
   <si>
+    <t>REP MAG DISTRCT JUDGE 27-1-01</t>
+  </si>
+  <si>
+    <t>REP MAG DISTRCT JUDGE 27-3-10</t>
+  </si>
+  <si>
     <t>REP MAGISTERIAL DISTRICT JUDGE 10-2-01</t>
   </si>
   <si>
@@ -155,9 +167,15 @@
     <t>DEM Hazleton Area School District 2yr Hazleton Area School District</t>
   </si>
   <si>
+    <t>DEM MAGISTERIAL DISTRICT JUDGE 07-1-09</t>
+  </si>
+  <si>
     <t>DEM MAGISTERIAL DISTRICT JUDGE 10-2-06</t>
   </si>
   <si>
+    <t>DEM MAGISTERIAL DISTRICT JUDGE 47-3-07 47-3-07</t>
+  </si>
+  <si>
     <t>DEM Magisterial District Judge 19-2-03</t>
   </si>
   <si>
@@ -176,15 +194,24 @@
     <t>DEM North Schuylkill School District 2yr North Schuylkill Area</t>
   </si>
   <si>
+    <t>Dem MAGISTERIAL DISTRICT JUDGE MD 27-3-01</t>
+  </si>
+  <si>
     <t>JUDGE OF THE COURT OF COMMON PLEAS -REP</t>
   </si>
   <si>
     <t>REP Commissioner Bethlehem Twsp 1st Ward</t>
   </si>
   <si>
+    <t>REP MAGISTERIAL DISTRICT JUDGE 07-1-10</t>
+  </si>
+  <si>
     <t>REP MAGISTERIAL DISTRICT JUDGE 10-2-06</t>
   </si>
   <si>
+    <t>REP MAGISTERIAL DISTRICT JUDGE 47-3-07 47-3-07</t>
+  </si>
+  <si>
     <t>REP Magisterial District Judge 19-2-03</t>
   </si>
   <si>
@@ -206,6 +233,9 @@
     <t>REP North Schuylkill School District 2yr North Schuylkill Area</t>
   </si>
   <si>
+    <t>REP SUPERVISOR UPPER YODER TOWNSHIP</t>
+  </si>
+  <si>
     <t>REP Supervisor 2yr Plainfield Twsp</t>
   </si>
   <si>
@@ -227,6 +257,9 @@
     <t>REP Township Supervisor for West Manheim Township</t>
   </si>
   <si>
+    <t>Rep SUPERVISOR - 1 FOR 6 YEARS CHARTIERS</t>
+  </si>
+  <si>
     <t>Committeeman, Aston Township Ward 7</t>
   </si>
   <si>
@@ -251,6 +284,9 @@
     <t>REP Judge of the Court of Common Pleas</t>
   </si>
   <si>
+    <t>REP MAYOR NORTHERN CAMBRIA BOROUGH</t>
+  </si>
+  <si>
     <t>REP Magisterial District Judge 21-3-04</t>
   </si>
   <si>
@@ -266,6 +302,9 @@
     <t>REP SUPERVISOR 6YR Plainfield Twsp</t>
   </si>
   <si>
+    <t>REP SUPERVISOR CAMBRIA TOWNSHIP</t>
+  </si>
+  <si>
     <t>REP TAX COLLECTOR CENTER TOWNSHIP</t>
   </si>
   <si>
@@ -284,6 +323,15 @@
     <t>REP Township Supervisor West Caln Township</t>
   </si>
   <si>
+    <t>Rep COUNTY CONTROLLER</t>
+  </si>
+  <si>
+    <t>Rep SUPERVISOR - 1 FOR 4 YEARS SOMERSET</t>
+  </si>
+  <si>
+    <t>Rep SUPERVISOR SOUTH STRABANE</t>
+  </si>
+  <si>
     <t>JEFF CUSAT</t>
   </si>
   <si>
@@ -476,6 +524,15 @@
     <t>ESPY WILLIAMS</t>
   </si>
   <si>
+    <t>MARIE FERGUSON</t>
+  </si>
+  <si>
+    <t>ANTHONY GIANFRANCESCO</t>
+  </si>
+  <si>
+    <t>THOMAS SCHILINSKI</t>
+  </si>
+  <si>
     <t>CATHERINE KUZMA</t>
   </si>
   <si>
@@ -524,6 +581,18 @@
     <t>MICHAEL SPELLMAN</t>
   </si>
   <si>
+    <t>SHERRI HEWITT-LAIRD</t>
+  </si>
+  <si>
+    <t>KATHERINE PRESCOTT</t>
+  </si>
+  <si>
+    <t>LARRY LEE RODGERS</t>
+  </si>
+  <si>
+    <t>LINDA GERIC</t>
+  </si>
+  <si>
     <t>SHAWN MILLER</t>
   </si>
   <si>
@@ -542,6 +611,27 @@
     <t>JEFFREY KOCHER</t>
   </si>
   <si>
+    <t>PATRICK PUSKARICH</t>
+  </si>
+  <si>
+    <t>KELLY STEWART</t>
+  </si>
+  <si>
+    <t>ROBERT BOB DULANEY</t>
+  </si>
+  <si>
+    <t>JOHN BRUNER</t>
+  </si>
+  <si>
+    <t>DAN STANEK</t>
+  </si>
+  <si>
+    <t>JASON MOORE</t>
+  </si>
+  <si>
+    <t>JOHN SCOTT BERNETT</t>
+  </si>
+  <si>
     <t>SCOTT FANCHALSKY</t>
   </si>
   <si>
@@ -611,6 +701,15 @@
     <t>TAIRA FERRERAS</t>
   </si>
   <si>
+    <t>TODD SAVARESE</t>
+  </si>
+  <si>
+    <t>MARK GREINER</t>
+  </si>
+  <si>
+    <t>CHRIS ONEILL</t>
+  </si>
+  <si>
     <t>JOHN CHRISTNER</t>
   </si>
   <si>
@@ -623,6 +722,21 @@
     <t>MICHAEL STANGROOM</t>
   </si>
   <si>
+    <t>DAVE BEYER</t>
+  </si>
+  <si>
+    <t>ERIN DOMINICK</t>
+  </si>
+  <si>
+    <t>ERIK DILL</t>
+  </si>
+  <si>
+    <t>HOWARD TERNDRUP</t>
+  </si>
+  <si>
+    <t>MONICA PREBISH</t>
+  </si>
+  <si>
     <t>TOBIN ZECH</t>
   </si>
   <si>
@@ -692,6 +806,15 @@
     <t>PHILIP RAPANT JR</t>
   </si>
   <si>
+    <t>CHRISTINA FOX GRASSO</t>
+  </si>
+  <si>
+    <t>DANIEL KETELAAR</t>
+  </si>
+  <si>
+    <t>PHIL MELOGRANE</t>
+  </si>
+  <si>
     <t>ERIC MIKOVCH</t>
   </si>
   <si>
@@ -710,6 +833,15 @@
     <t>RODMAN LAW</t>
   </si>
   <si>
+    <t>JOHN GALLOWAY</t>
+  </si>
+  <si>
+    <t>MILT WARRELL</t>
+  </si>
+  <si>
+    <t>DONALD BERMUDEZ</t>
+  </si>
+  <si>
     <t>MATTHEW RUTH</t>
   </si>
   <si>
@@ -740,6 +872,21 @@
     <t>LORI JALONSKI</t>
   </si>
   <si>
+    <t>SUE KONVOLINKA</t>
+  </si>
+  <si>
+    <t>KYLE SHAFFER</t>
+  </si>
+  <si>
+    <t>BOB VARNER</t>
+  </si>
+  <si>
+    <t>JEFFREY MASTERSON</t>
+  </si>
+  <si>
+    <t>BOB AMISTADI</t>
+  </si>
+  <si>
     <t>KEN FIELD</t>
   </si>
   <si>
@@ -818,6 +965,18 @@
     <t>JUSTIN OCONNOR</t>
   </si>
   <si>
+    <t>HARLAN SHOBER</t>
+  </si>
+  <si>
+    <t>GARY FRIEND</t>
+  </si>
+  <si>
+    <t>JEFFREY ELIAS</t>
+  </si>
+  <si>
+    <t>DARYL HEISER</t>
+  </si>
+  <si>
     <t>MIKE HIGGINS</t>
   </si>
   <si>
@@ -905,6 +1064,15 @@
     <t>ERIC TAYLOR</t>
   </si>
   <si>
+    <t>LISA MAYS</t>
+  </si>
+  <si>
+    <t>DONALD FERGUSON</t>
+  </si>
+  <si>
+    <t>JESSIE LANEY</t>
+  </si>
+  <si>
     <t>CHRISTIAN LENGEL</t>
   </si>
   <si>
@@ -944,6 +1112,15 @@
     <t>KEN FAIRCHILD</t>
   </si>
   <si>
+    <t>GREG VERBOSKY</t>
+  </si>
+  <si>
+    <t>KEVIN LUTE</t>
+  </si>
+  <si>
+    <t>TOM MERRYWEATHER</t>
+  </si>
+  <si>
     <t>BRENDA SMYERS DUFFY</t>
   </si>
   <si>
@@ -1007,6 +1184,39 @@
     <t>JOE HUTTON</t>
   </si>
   <si>
+    <t>PAT PHILLIPS</t>
+  </si>
+  <si>
+    <t>HEATHER SHEATLER</t>
+  </si>
+  <si>
+    <t>BRENDA DAVIS</t>
+  </si>
+  <si>
+    <t>TONY JACOB DELOST</t>
+  </si>
+  <si>
+    <t>PAUL MYERS</t>
+  </si>
+  <si>
+    <t>STEPHEN DAVIS</t>
+  </si>
+  <si>
+    <t>JOSEPH GREG MALISKY</t>
+  </si>
+  <si>
+    <t>ROBERT SCHUERLE</t>
+  </si>
+  <si>
+    <t>ZACK MORGAN</t>
+  </si>
+  <si>
+    <t>GAYLORD PLANTS</t>
+  </si>
+  <si>
+    <t>STEPHANIE HUMENSKY</t>
+  </si>
+  <si>
     <t>Luzerne County (Wilkes-Barre + boroughs + townships)</t>
   </si>
   <si>
@@ -1031,6 +1241,9 @@
     <t>Lehigh County (Allentown + boroughs + townships)</t>
   </si>
   <si>
+    <t>Washington County (Washington + boroughs + townships)</t>
+  </si>
+  <si>
     <t>Montgomery County (Norristown + Philly suburbs)</t>
   </si>
   <si>
@@ -1038,6 +1251,12 @@
   </si>
   <si>
     <t>Schuylkill County (Pottsville + boroughs + townships)</t>
+  </si>
+  <si>
+    <t>Bucks County (Doylestown + Philly suburbs)</t>
+  </si>
+  <si>
+    <t>Cambria County (Johnstown + boroughs + townships)</t>
   </si>
   <si>
     <t>York County (city + boroughs + townships)</t>
@@ -1497,7 +1716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F364"/>
+  <dimension ref="A1:F439"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1528,7 +1747,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D2">
         <v>799</v>
@@ -1537,7 +1756,7 @@
         <v>35.94242015294647</v>
       </c>
       <c r="F2" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1548,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D3">
         <v>713</v>
@@ -1557,7 +1776,7 @@
         <v>32.07377417903734</v>
       </c>
       <c r="F3" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1568,7 +1787,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D4">
         <v>355</v>
@@ -1577,7 +1796,7 @@
         <v>15.96941070625281</v>
       </c>
       <c r="F4" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1588,7 +1807,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D5">
         <v>190</v>
@@ -1597,7 +1816,7 @@
         <v>8.547008547008547</v>
       </c>
       <c r="F5" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1608,7 +1827,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D6">
         <v>166</v>
@@ -1617,7 +1836,7 @@
         <v>7.467386414754835</v>
       </c>
       <c r="F6" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1628,7 +1847,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>807</v>
@@ -1637,7 +1856,7 @@
         <v>42.87991498405951</v>
       </c>
       <c r="F8" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1648,7 +1867,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D9">
         <v>704</v>
@@ -1657,7 +1876,7 @@
         <v>37.40701381509033</v>
       </c>
       <c r="F9" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1668,7 +1887,7 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D10">
         <v>371</v>
@@ -1677,7 +1896,7 @@
         <v>19.71307120085016</v>
       </c>
       <c r="F10" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1688,7 +1907,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D12">
         <v>23009</v>
@@ -1697,7 +1916,7 @@
         <v>49.36282502359907</v>
       </c>
       <c r="F12" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1708,7 +1927,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D13">
         <v>10398</v>
@@ -1717,7 +1936,7 @@
         <v>22.30756028490518</v>
       </c>
       <c r="F13" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1728,7 +1947,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D14">
         <v>6676</v>
@@ -1737,7 +1956,7 @@
         <v>14.32249206212992</v>
       </c>
       <c r="F14" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1748,7 +1967,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D15">
         <v>6529</v>
@@ -1757,7 +1976,7 @@
         <v>14.00712262936583</v>
       </c>
       <c r="F15" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1768,7 +1987,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D17">
         <v>15761</v>
@@ -1777,7 +1996,7 @@
         <v>32.71613907628438</v>
       </c>
       <c r="F17" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1788,7 +2007,7 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D18">
         <v>12780</v>
@@ -1797,7 +2016,7 @@
         <v>26.52828230409964</v>
       </c>
       <c r="F18" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1808,7 +2027,7 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D19">
         <v>10691</v>
@@ -1817,7 +2036,7 @@
         <v>22.19200830306175</v>
       </c>
       <c r="F19" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1828,7 +2047,7 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D20">
         <v>8943</v>
@@ -1837,7 +2056,7 @@
         <v>18.56357031655423</v>
       </c>
       <c r="F20" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1848,7 +2067,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D22">
         <v>133</v>
@@ -1857,7 +2076,7 @@
         <v>41.95583596214511</v>
       </c>
       <c r="F22" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1868,7 +2087,7 @@
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D23">
         <v>121</v>
@@ -1877,7 +2096,7 @@
         <v>38.17034700315457</v>
       </c>
       <c r="F23" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1888,7 +2107,7 @@
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D24">
         <v>63</v>
@@ -1897,7 +2116,7 @@
         <v>19.87381703470032</v>
       </c>
       <c r="F24" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1908,7 +2127,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D26">
         <v>22897</v>
@@ -1917,7 +2136,7 @@
         <v>47.76078930351891</v>
       </c>
       <c r="F26" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1928,7 +2147,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D27">
         <v>8137</v>
@@ -1937,7 +2156,7 @@
         <v>16.97294591268434</v>
       </c>
       <c r="F27" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1948,7 +2167,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D28">
         <v>7234</v>
@@ -1957,7 +2176,7 @@
         <v>15.08938069710686</v>
       </c>
       <c r="F28" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1968,7 +2187,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D29">
         <v>5373</v>
@@ -1977,7 +2196,7 @@
         <v>11.20752591727332</v>
       </c>
       <c r="F29" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1988,7 +2207,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D30">
         <v>4300</v>
@@ -1997,7 +2216,7 @@
         <v>8.969358169416575</v>
       </c>
       <c r="F30" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2008,7 +2227,7 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D32">
         <v>364</v>
@@ -2017,7 +2236,7 @@
         <v>39.09774436090225</v>
       </c>
       <c r="F32" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2028,7 +2247,7 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D33">
         <v>341</v>
@@ -2037,7 +2256,7 @@
         <v>36.62728249194414</v>
       </c>
       <c r="F33" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2048,7 +2267,7 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D34">
         <v>226</v>
@@ -2057,7 +2276,7 @@
         <v>24.2749731471536</v>
       </c>
       <c r="F34" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2068,7 +2287,7 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D36">
         <v>1283</v>
@@ -2077,7 +2296,7 @@
         <v>40.52432090966519</v>
       </c>
       <c r="F36" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2088,7 +2307,7 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="D37">
         <v>954</v>
@@ -2097,7 +2316,7 @@
         <v>30.13265950726469</v>
       </c>
       <c r="F37" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2108,7 +2327,7 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D38">
         <v>746</v>
@@ -2117,7 +2336,7 @@
         <v>23.56285533796589</v>
       </c>
       <c r="F38" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2128,7 +2347,7 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D39">
         <v>183</v>
@@ -2137,7 +2356,7 @@
         <v>5.780164245104232</v>
       </c>
       <c r="F39" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2148,7 +2367,7 @@
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D41">
         <v>1446</v>
@@ -2157,7 +2376,7 @@
         <v>41.84027777777778</v>
       </c>
       <c r="F41" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2168,7 +2387,7 @@
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D42">
         <v>1091</v>
@@ -2177,7 +2396,7 @@
         <v>31.56828703703703</v>
       </c>
       <c r="F42" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2188,7 +2407,7 @@
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D43">
         <v>919</v>
@@ -2197,7 +2416,7 @@
         <v>26.59143518518519</v>
       </c>
       <c r="F43" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2208,7 +2427,7 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D45">
         <v>8769</v>
@@ -2217,7 +2436,7 @@
         <v>32.16683173764719</v>
       </c>
       <c r="F45" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2228,7 +2447,7 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D46">
         <v>8551</v>
@@ -2237,7 +2456,7 @@
         <v>31.36715454312021</v>
       </c>
       <c r="F46" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2248,7 +2467,7 @@
         <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D47">
         <v>5669</v>
@@ -2257,7 +2476,7 @@
         <v>20.79527530171307</v>
       </c>
       <c r="F47" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2268,7 +2487,7 @@
         <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D48">
         <v>4272</v>
@@ -2277,7 +2496,7 @@
         <v>15.67073841751953</v>
       </c>
       <c r="F48" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2288,7 +2507,7 @@
         <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="D50">
         <v>3420</v>
@@ -2297,7 +2516,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F50" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2308,7 +2527,7 @@
         <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="D51">
         <v>2391</v>
@@ -2317,7 +2536,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F51" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2328,7 +2547,7 @@
         <v>21</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="D52">
         <v>2184</v>
@@ -2337,7 +2556,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F52" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2348,7 +2567,7 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D54">
         <v>572</v>
@@ -2357,7 +2576,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F54" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2368,7 +2587,7 @@
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="D55">
         <v>380</v>
@@ -2377,7 +2596,7 @@
         <v>31.25</v>
       </c>
       <c r="F55" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2388,7 +2607,7 @@
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D56">
         <v>264</v>
@@ -2397,7 +2616,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F56" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2408,7 +2627,7 @@
         <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="D58">
         <v>177</v>
@@ -2417,7 +2636,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F58" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2428,7 +2647,7 @@
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="D59">
         <v>141</v>
@@ -2437,7 +2656,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F59" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2448,7 +2667,7 @@
         <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="D60">
         <v>81</v>
@@ -2457,7 +2676,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F60" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2468,7 +2687,7 @@
         <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D61">
         <v>44</v>
@@ -2477,7 +2696,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F61" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2488,7 +2707,7 @@
         <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D63">
         <v>1471</v>
@@ -2497,7 +2716,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F63" t="s">
-        <v>335</v>
+        <v>405</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2508,7 +2727,7 @@
         <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D64">
         <v>1247</v>
@@ -2517,7 +2736,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F64" t="s">
-        <v>335</v>
+        <v>405</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2528,7 +2747,7 @@
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="D65">
         <v>616</v>
@@ -2537,7 +2756,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F65" t="s">
-        <v>335</v>
+        <v>405</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2548,7 +2767,7 @@
         <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D67">
         <v>1183</v>
@@ -2557,7 +2776,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F67" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2568,7 +2787,7 @@
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="D68">
         <v>1177</v>
@@ -2577,7 +2796,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F68" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2588,7 +2807,7 @@
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="D69">
         <v>373</v>
@@ -2597,7 +2816,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F69" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2608,7 +2827,7 @@
         <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D70">
         <v>270</v>
@@ -2617,7 +2836,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F70" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2628,7 +2847,7 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="D72">
         <v>2064</v>
@@ -2637,7 +2856,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F72" t="s">
-        <v>337</v>
+        <v>407</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2648,7 +2867,7 @@
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D73">
         <v>1942</v>
@@ -2657,7 +2876,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F73" t="s">
-        <v>337</v>
+        <v>407</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2668,7 +2887,7 @@
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="D74">
         <v>1927</v>
@@ -2677,7 +2896,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F74" t="s">
-        <v>337</v>
+        <v>407</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2688,7 +2907,7 @@
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="D75">
         <v>1817</v>
@@ -2697,7 +2916,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F75" t="s">
-        <v>337</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2708,7 +2927,7 @@
         <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="D77">
         <v>237</v>
@@ -2717,7 +2936,7 @@
         <v>32.20108695652174</v>
       </c>
       <c r="F77" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2728,7 +2947,7 @@
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D78">
         <v>234</v>
@@ -2737,7 +2956,7 @@
         <v>31.79347826086957</v>
       </c>
       <c r="F78" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2748,7 +2967,7 @@
         <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D79">
         <v>148</v>
@@ -2757,7 +2976,7 @@
         <v>20.10869565217391</v>
       </c>
       <c r="F79" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2768,7 +2987,7 @@
         <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D80">
         <v>90</v>
@@ -2777,7 +2996,7 @@
         <v>12.22826086956522</v>
       </c>
       <c r="F80" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2788,7 +3007,7 @@
         <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="D81">
         <v>27</v>
@@ -2797,7 +3016,7 @@
         <v>3.668478260869565</v>
       </c>
       <c r="F81" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2808,16 +3027,16 @@
         <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D83">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="E83">
-        <v>44.61077844311377</v>
+        <v>40.15151515151515</v>
       </c>
       <c r="F83" t="s">
-        <v>332</v>
+        <v>408</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2828,16 +3047,16 @@
         <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D84">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="E84">
-        <v>34.4311377245509</v>
+        <v>35.22727272727273</v>
       </c>
       <c r="F84" t="s">
-        <v>332</v>
+        <v>408</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2848,16 +3067,16 @@
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="D85">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="E85">
-        <v>20.95808383233533</v>
+        <v>24.62121212121212</v>
       </c>
       <c r="F85" t="s">
-        <v>332</v>
+        <v>408</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2868,16 +3087,16 @@
         <v>29</v>
       </c>
       <c r="C87" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="D87">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="E87">
-        <v>40.70796460176992</v>
+        <v>44.61077844311377</v>
       </c>
       <c r="F87" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2888,16 +3107,16 @@
         <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D88">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E88">
-        <v>37.46312684365782</v>
+        <v>34.4311377245509</v>
       </c>
       <c r="F88" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2908,16 +3127,16 @@
         <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="D89">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E89">
-        <v>21.82890855457227</v>
+        <v>20.95808383233533</v>
       </c>
       <c r="F89" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2928,16 +3147,16 @@
         <v>30</v>
       </c>
       <c r="C91" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D91">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="E91">
-        <v>40</v>
+        <v>40.70796460176992</v>
       </c>
       <c r="F91" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2948,16 +3167,16 @@
         <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D92">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="E92">
-        <v>20.64516129032258</v>
+        <v>37.46312684365782</v>
       </c>
       <c r="F92" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2968,36 +3187,36 @@
         <v>30</v>
       </c>
       <c r="C93" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D93">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E93">
-        <v>20.43010752688172</v>
+        <v>21.82890855457227</v>
       </c>
       <c r="F93" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>2021</v>
-      </c>
-      <c r="B94" t="s">
-        <v>30</v>
-      </c>
-      <c r="C94" t="s">
-        <v>162</v>
-      </c>
-      <c r="D94">
-        <v>88</v>
-      </c>
-      <c r="E94">
-        <v>18.9247311827957</v>
-      </c>
-      <c r="F94" t="s">
-        <v>338</v>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>2021</v>
+      </c>
+      <c r="B95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" t="s">
+        <v>178</v>
+      </c>
+      <c r="D95">
+        <v>186</v>
+      </c>
+      <c r="E95">
+        <v>40</v>
+      </c>
+      <c r="F95" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3008,16 +3227,16 @@
         <v>31</v>
       </c>
       <c r="C96" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="D96">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="E96">
-        <v>39.58868894601542</v>
+        <v>20.64516129032258</v>
       </c>
       <c r="F96" t="s">
-        <v>338</v>
+        <v>409</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3028,16 +3247,16 @@
         <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D97">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="E97">
-        <v>37.01799485861182</v>
+        <v>20.43010752688172</v>
       </c>
       <c r="F97" t="s">
-        <v>338</v>
+        <v>409</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3048,16 +3267,16 @@
         <v>31</v>
       </c>
       <c r="C98" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="D98">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E98">
-        <v>23.39331619537275</v>
+        <v>18.9247311827957</v>
       </c>
       <c r="F98" t="s">
-        <v>338</v>
+        <v>409</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3068,16 +3287,16 @@
         <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D100">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="E100">
-        <v>49.63325183374083</v>
+        <v>39.58868894601542</v>
       </c>
       <c r="F100" t="s">
-        <v>332</v>
+        <v>409</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3088,16 +3307,16 @@
         <v>32</v>
       </c>
       <c r="C101" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="D101">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="E101">
-        <v>31.05134474327628</v>
+        <v>37.01799485861182</v>
       </c>
       <c r="F101" t="s">
-        <v>332</v>
+        <v>409</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3108,16 +3327,16 @@
         <v>32</v>
       </c>
       <c r="C102" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D102">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E102">
-        <v>19.31540342298289</v>
+        <v>23.39331619537275</v>
       </c>
       <c r="F102" t="s">
-        <v>332</v>
+        <v>409</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3128,16 +3347,16 @@
         <v>33</v>
       </c>
       <c r="C104" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="D104">
-        <v>588</v>
+        <v>203</v>
       </c>
       <c r="E104">
-        <v>48.83720930232558</v>
+        <v>49.63325183374083</v>
       </c>
       <c r="F104" t="s">
-        <v>331</v>
+        <v>402</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3148,16 +3367,16 @@
         <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="D105">
-        <v>379</v>
+        <v>127</v>
       </c>
       <c r="E105">
-        <v>31.47840531561462</v>
+        <v>31.05134474327628</v>
       </c>
       <c r="F105" t="s">
-        <v>331</v>
+        <v>402</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3168,16 +3387,16 @@
         <v>33</v>
       </c>
       <c r="C106" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D106">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="E106">
-        <v>19.6843853820598</v>
+        <v>19.31540342298289</v>
       </c>
       <c r="F106" t="s">
-        <v>331</v>
+        <v>402</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3188,16 +3407,16 @@
         <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="D108">
-        <v>522</v>
+        <v>293</v>
       </c>
       <c r="E108">
-        <v>48.33333333333334</v>
+        <v>37.80645161290322</v>
       </c>
       <c r="F108" t="s">
-        <v>336</v>
+        <v>408</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3208,16 +3427,16 @@
         <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="D109">
-        <v>331</v>
+        <v>241</v>
       </c>
       <c r="E109">
-        <v>30.64814814814815</v>
+        <v>31.09677419354839</v>
       </c>
       <c r="F109" t="s">
-        <v>336</v>
+        <v>408</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3228,36 +3447,36 @@
         <v>34</v>
       </c>
       <c r="C110" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D110">
-        <v>227</v>
+        <v>125</v>
       </c>
       <c r="E110">
-        <v>21.01851851851852</v>
+        <v>16.12903225806452</v>
       </c>
       <c r="F110" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>2021</v>
-      </c>
-      <c r="B112" t="s">
-        <v>35</v>
-      </c>
-      <c r="C112" t="s">
-        <v>129</v>
-      </c>
-      <c r="D112">
-        <v>4922</v>
-      </c>
-      <c r="E112">
-        <v>41.68713475057169</v>
-      </c>
-      <c r="F112" t="s">
-        <v>333</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111">
+        <v>2021</v>
+      </c>
+      <c r="B111" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" t="s">
+        <v>191</v>
+      </c>
+      <c r="D111">
+        <v>116</v>
+      </c>
+      <c r="E111">
+        <v>14.96774193548387</v>
+      </c>
+      <c r="F111" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3268,16 +3487,16 @@
         <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="D113">
-        <v>4820</v>
+        <v>588</v>
       </c>
       <c r="E113">
-        <v>40.82324045058016</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="F113" t="s">
-        <v>333</v>
+        <v>401</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3288,36 +3507,36 @@
         <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="D114">
-        <v>2065</v>
+        <v>379</v>
       </c>
       <c r="E114">
-        <v>17.48962479884814</v>
+        <v>31.47840531561462</v>
       </c>
       <c r="F114" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>2021</v>
-      </c>
-      <c r="B116" t="s">
-        <v>36</v>
-      </c>
-      <c r="C116" t="s">
-        <v>175</v>
-      </c>
-      <c r="D116">
-        <v>1281</v>
-      </c>
-      <c r="E116">
-        <v>43.88489208633094</v>
-      </c>
-      <c r="F116" t="s">
-        <v>331</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115">
+        <v>2021</v>
+      </c>
+      <c r="B115" t="s">
+        <v>35</v>
+      </c>
+      <c r="C115" t="s">
+        <v>194</v>
+      </c>
+      <c r="D115">
+        <v>237</v>
+      </c>
+      <c r="E115">
+        <v>19.6843853820598</v>
+      </c>
+      <c r="F115" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3328,16 +3547,16 @@
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D117">
-        <v>924</v>
+        <v>522</v>
       </c>
       <c r="E117">
-        <v>31.6546762589928</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="F117" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3348,36 +3567,36 @@
         <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D118">
-        <v>714</v>
+        <v>331</v>
       </c>
       <c r="E118">
-        <v>24.46043165467626</v>
+        <v>30.64814814814815</v>
       </c>
       <c r="F118" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>2021</v>
-      </c>
-      <c r="B120" t="s">
-        <v>37</v>
-      </c>
-      <c r="C120" t="s">
-        <v>178</v>
-      </c>
-      <c r="D120">
-        <v>999</v>
-      </c>
-      <c r="E120">
-        <v>49.47994056463596</v>
-      </c>
-      <c r="F120" t="s">
-        <v>331</v>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119">
+        <v>2021</v>
+      </c>
+      <c r="B119" t="s">
+        <v>36</v>
+      </c>
+      <c r="C119" t="s">
+        <v>197</v>
+      </c>
+      <c r="D119">
+        <v>227</v>
+      </c>
+      <c r="E119">
+        <v>21.01851851851852</v>
+      </c>
+      <c r="F119" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3388,16 +3607,16 @@
         <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="D121">
-        <v>629</v>
+        <v>4922</v>
       </c>
       <c r="E121">
-        <v>31.15403665180783</v>
+        <v>41.68713475057169</v>
       </c>
       <c r="F121" t="s">
-        <v>331</v>
+        <v>403</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3408,36 +3627,36 @@
         <v>37</v>
       </c>
       <c r="C122" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="D122">
-        <v>391</v>
+        <v>4820</v>
       </c>
       <c r="E122">
-        <v>19.36602278355622</v>
+        <v>40.82324045058016</v>
       </c>
       <c r="F122" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>2021</v>
-      </c>
-      <c r="B124" t="s">
-        <v>38</v>
-      </c>
-      <c r="C124" t="s">
-        <v>130</v>
-      </c>
-      <c r="D124">
-        <v>1779</v>
-      </c>
-      <c r="E124">
-        <v>46.82811266122664</v>
-      </c>
-      <c r="F124" t="s">
-        <v>333</v>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123">
+        <v>2021</v>
+      </c>
+      <c r="B123" t="s">
+        <v>37</v>
+      </c>
+      <c r="C123" t="s">
+        <v>144</v>
+      </c>
+      <c r="D123">
+        <v>2065</v>
+      </c>
+      <c r="E123">
+        <v>17.48962479884814</v>
+      </c>
+      <c r="F123" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3448,16 +3667,16 @@
         <v>38</v>
       </c>
       <c r="C125" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="D125">
-        <v>1349</v>
+        <v>490</v>
       </c>
       <c r="E125">
-        <v>35.50934456435904</v>
+        <v>47.43465634075508</v>
       </c>
       <c r="F125" t="s">
-        <v>333</v>
+        <v>408</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3468,36 +3687,36 @@
         <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="D126">
-        <v>671</v>
+        <v>274</v>
       </c>
       <c r="E126">
-        <v>17.66254277441432</v>
+        <v>26.52468538238141</v>
       </c>
       <c r="F126" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>2021</v>
-      </c>
-      <c r="B128" t="s">
-        <v>39</v>
-      </c>
-      <c r="C128" t="s">
-        <v>134</v>
-      </c>
-      <c r="D128">
-        <v>253</v>
-      </c>
-      <c r="E128">
-        <v>37.09677419354838</v>
-      </c>
-      <c r="F128" t="s">
-        <v>334</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127">
+        <v>2021</v>
+      </c>
+      <c r="B127" t="s">
+        <v>38</v>
+      </c>
+      <c r="C127" t="s">
+        <v>200</v>
+      </c>
+      <c r="D127">
+        <v>269</v>
+      </c>
+      <c r="E127">
+        <v>26.0406582768635</v>
+      </c>
+      <c r="F127" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3508,16 +3727,16 @@
         <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="D129">
-        <v>224</v>
+        <v>1165</v>
       </c>
       <c r="E129">
-        <v>32.84457478005865</v>
+        <v>47.31925264012997</v>
       </c>
       <c r="F129" t="s">
-        <v>334</v>
+        <v>408</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3528,16 +3747,16 @@
         <v>39</v>
       </c>
       <c r="C130" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="D130">
-        <v>122</v>
+        <v>898</v>
       </c>
       <c r="E130">
-        <v>17.88856304985337</v>
+        <v>36.47441104792851</v>
       </c>
       <c r="F130" t="s">
-        <v>334</v>
+        <v>408</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3548,16 +3767,16 @@
         <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="D131">
-        <v>60</v>
+        <v>211</v>
       </c>
       <c r="E131">
-        <v>8.797653958944283</v>
+        <v>8.570268074735987</v>
       </c>
       <c r="F131" t="s">
-        <v>334</v>
+        <v>408</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3568,16 +3787,16 @@
         <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="D132">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="E132">
-        <v>3.372434017595308</v>
+        <v>7.636068237205524</v>
       </c>
       <c r="F132" t="s">
-        <v>334</v>
+        <v>408</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3588,16 +3807,16 @@
         <v>40</v>
       </c>
       <c r="C134" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="D134">
-        <v>917</v>
+        <v>1281</v>
       </c>
       <c r="E134">
-        <v>36.31683168316832</v>
+        <v>43.88489208633094</v>
       </c>
       <c r="F134" t="s">
-        <v>336</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3608,16 +3827,16 @@
         <v>40</v>
       </c>
       <c r="C135" t="s">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="D135">
-        <v>706</v>
+        <v>924</v>
       </c>
       <c r="E135">
-        <v>27.96039603960396</v>
+        <v>31.6546762589928</v>
       </c>
       <c r="F135" t="s">
-        <v>336</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3628,36 +3847,36 @@
         <v>40</v>
       </c>
       <c r="C136" t="s">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="D136">
-        <v>578</v>
+        <v>714</v>
       </c>
       <c r="E136">
-        <v>22.89108910891089</v>
+        <v>24.46043165467626</v>
       </c>
       <c r="F136" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>2021</v>
-      </c>
-      <c r="B137" t="s">
-        <v>40</v>
-      </c>
-      <c r="C137" t="s">
-        <v>143</v>
-      </c>
-      <c r="D137">
-        <v>324</v>
-      </c>
-      <c r="E137">
-        <v>12.83168316831683</v>
-      </c>
-      <c r="F137" t="s">
-        <v>336</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138">
+        <v>2021</v>
+      </c>
+      <c r="B138" t="s">
+        <v>41</v>
+      </c>
+      <c r="C138" t="s">
+        <v>208</v>
+      </c>
+      <c r="D138">
+        <v>999</v>
+      </c>
+      <c r="E138">
+        <v>49.47994056463596</v>
+      </c>
+      <c r="F138" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3668,16 +3887,16 @@
         <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="D139">
-        <v>149</v>
+        <v>629</v>
       </c>
       <c r="E139">
-        <v>41.38888888888889</v>
+        <v>31.15403665180783</v>
       </c>
       <c r="F139" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3688,36 +3907,16 @@
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="D140">
-        <v>113</v>
+        <v>391</v>
       </c>
       <c r="E140">
-        <v>31.38888888888889</v>
+        <v>19.36602278355622</v>
       </c>
       <c r="F140" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>2021</v>
-      </c>
-      <c r="B141" t="s">
-        <v>41</v>
-      </c>
-      <c r="C141" t="s">
-        <v>184</v>
-      </c>
-      <c r="D141">
-        <v>59</v>
-      </c>
-      <c r="E141">
-        <v>16.38888888888889</v>
-      </c>
-      <c r="F141" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3725,19 +3924,39 @@
         <v>2021</v>
       </c>
       <c r="B142" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C142" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="D142">
-        <v>39</v>
+        <v>1779</v>
       </c>
       <c r="E142">
-        <v>10.83333333333333</v>
+        <v>46.82811266122664</v>
       </c>
       <c r="F142" t="s">
-        <v>331</v>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143">
+        <v>2021</v>
+      </c>
+      <c r="B143" t="s">
+        <v>42</v>
+      </c>
+      <c r="C143" t="s">
+        <v>147</v>
+      </c>
+      <c r="D143">
+        <v>1349</v>
+      </c>
+      <c r="E143">
+        <v>35.50934456435904</v>
+      </c>
+      <c r="F143" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3748,36 +3967,16 @@
         <v>42</v>
       </c>
       <c r="C144" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="D144">
-        <v>179</v>
+        <v>671</v>
       </c>
       <c r="E144">
-        <v>45.31645569620253</v>
+        <v>17.66254277441432</v>
       </c>
       <c r="F144" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>2021</v>
-      </c>
-      <c r="B145" t="s">
-        <v>42</v>
-      </c>
-      <c r="C145" t="s">
-        <v>187</v>
-      </c>
-      <c r="D145">
-        <v>110</v>
-      </c>
-      <c r="E145">
-        <v>27.84810126582278</v>
-      </c>
-      <c r="F145" t="s">
-        <v>339</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3785,19 +3984,39 @@
         <v>2021</v>
       </c>
       <c r="B146" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C146" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D146">
-        <v>106</v>
+        <v>253</v>
       </c>
       <c r="E146">
-        <v>26.83544303797468</v>
+        <v>37.09677419354838</v>
       </c>
       <c r="F146" t="s">
-        <v>339</v>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147">
+        <v>2021</v>
+      </c>
+      <c r="B147" t="s">
+        <v>43</v>
+      </c>
+      <c r="C147" t="s">
+        <v>151</v>
+      </c>
+      <c r="D147">
+        <v>224</v>
+      </c>
+      <c r="E147">
+        <v>32.84457478005865</v>
+      </c>
+      <c r="F147" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3808,16 +4027,16 @@
         <v>43</v>
       </c>
       <c r="C148" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="D148">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="E148">
-        <v>47.01873935264054</v>
+        <v>17.88856304985337</v>
       </c>
       <c r="F148" t="s">
-        <v>337</v>
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3828,16 +4047,16 @@
         <v>43</v>
       </c>
       <c r="C149" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="D149">
-        <v>226</v>
+        <v>60</v>
       </c>
       <c r="E149">
-        <v>38.50085178875639</v>
+        <v>8.797653958944283</v>
       </c>
       <c r="F149" t="s">
-        <v>337</v>
+        <v>404</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3848,16 +4067,16 @@
         <v>43</v>
       </c>
       <c r="C150" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="D150">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="E150">
-        <v>14.48040885860307</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="F150" t="s">
-        <v>337</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -3868,16 +4087,16 @@
         <v>44</v>
       </c>
       <c r="C152" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="D152">
-        <v>636</v>
+        <v>917</v>
       </c>
       <c r="E152">
-        <v>41.24513618677042</v>
+        <v>36.31683168316832</v>
       </c>
       <c r="F152" t="s">
-        <v>337</v>
+        <v>406</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3888,16 +4107,16 @@
         <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="D153">
-        <v>544</v>
+        <v>706</v>
       </c>
       <c r="E153">
-        <v>35.27885862516213</v>
+        <v>27.96039603960396</v>
       </c>
       <c r="F153" t="s">
-        <v>337</v>
+        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -3908,296 +4127,296 @@
         <v>44</v>
       </c>
       <c r="C154" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="D154">
-        <v>362</v>
+        <v>578</v>
       </c>
       <c r="E154">
-        <v>23.47600518806744</v>
+        <v>22.89108910891089</v>
       </c>
       <c r="F154" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>2023</v>
-      </c>
-      <c r="B156" t="s">
-        <v>45</v>
-      </c>
-      <c r="C156" t="s">
-        <v>195</v>
-      </c>
-      <c r="D156">
-        <v>104</v>
-      </c>
-      <c r="E156">
-        <v>38.95131086142322</v>
-      </c>
-      <c r="F156" t="s">
-        <v>340</v>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155">
+        <v>2021</v>
+      </c>
+      <c r="B155" t="s">
+        <v>44</v>
+      </c>
+      <c r="C155" t="s">
+        <v>159</v>
+      </c>
+      <c r="D155">
+        <v>324</v>
+      </c>
+      <c r="E155">
+        <v>12.83168316831683</v>
+      </c>
+      <c r="F155" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B157" t="s">
         <v>45</v>
       </c>
       <c r="C157" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="D157">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="E157">
-        <v>37.45318352059925</v>
+        <v>41.38888888888889</v>
       </c>
       <c r="F157" t="s">
-        <v>340</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B158" t="s">
         <v>45</v>
       </c>
       <c r="C158" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="D158">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="E158">
-        <v>23.59550561797753</v>
+        <v>31.38888888888889</v>
       </c>
       <c r="F158" t="s">
-        <v>340</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159">
+        <v>2021</v>
+      </c>
+      <c r="B159" t="s">
+        <v>45</v>
+      </c>
+      <c r="C159" t="s">
+        <v>214</v>
+      </c>
+      <c r="D159">
+        <v>59</v>
+      </c>
+      <c r="E159">
+        <v>16.38888888888889</v>
+      </c>
+      <c r="F159" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B160" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C160" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D160">
-        <v>882</v>
+        <v>39</v>
       </c>
       <c r="E160">
-        <v>45.60496380558428</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="F160" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>2023</v>
-      </c>
-      <c r="B161" t="s">
-        <v>46</v>
-      </c>
-      <c r="C161" t="s">
-        <v>199</v>
-      </c>
-      <c r="D161">
-        <v>502</v>
-      </c>
-      <c r="E161">
-        <v>25.95656670113754</v>
-      </c>
-      <c r="F161" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B162" t="s">
         <v>46</v>
       </c>
       <c r="C162" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="D162">
-        <v>399</v>
+        <v>179</v>
       </c>
       <c r="E162">
-        <v>20.63081695966908</v>
+        <v>45.31645569620253</v>
       </c>
       <c r="F162" t="s">
-        <v>331</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B163" t="s">
         <v>46</v>
       </c>
       <c r="C163" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="D163">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="E163">
-        <v>7.807652533609101</v>
+        <v>27.84810126582278</v>
       </c>
       <c r="F163" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>2023</v>
-      </c>
-      <c r="B165" t="s">
-        <v>47</v>
-      </c>
-      <c r="C165" t="s">
-        <v>202</v>
-      </c>
-      <c r="D165">
-        <v>445</v>
-      </c>
-      <c r="E165">
-        <v>43.28793774319066</v>
-      </c>
-      <c r="F165" t="s">
-        <v>341</v>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164">
+        <v>2021</v>
+      </c>
+      <c r="B164" t="s">
+        <v>46</v>
+      </c>
+      <c r="C164" t="s">
+        <v>218</v>
+      </c>
+      <c r="D164">
+        <v>106</v>
+      </c>
+      <c r="E164">
+        <v>26.83544303797468</v>
+      </c>
+      <c r="F164" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B166" t="s">
         <v>47</v>
       </c>
       <c r="C166" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D166">
-        <v>353</v>
+        <v>276</v>
       </c>
       <c r="E166">
-        <v>34.33852140077821</v>
+        <v>47.01873935264054</v>
       </c>
       <c r="F166" t="s">
-        <v>341</v>
+        <v>407</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B167" t="s">
         <v>47</v>
       </c>
       <c r="C167" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="D167">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E167">
-        <v>22.37354085603113</v>
+        <v>38.50085178875639</v>
       </c>
       <c r="F167" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169">
-        <v>2023</v>
-      </c>
-      <c r="B169" t="s">
-        <v>48</v>
-      </c>
-      <c r="C169" t="s">
-        <v>205</v>
-      </c>
-      <c r="D169">
-        <v>684</v>
-      </c>
-      <c r="E169">
-        <v>46.94577899794098</v>
-      </c>
-      <c r="F169" t="s">
-        <v>341</v>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168">
+        <v>2021</v>
+      </c>
+      <c r="B168" t="s">
+        <v>47</v>
+      </c>
+      <c r="C168" t="s">
+        <v>221</v>
+      </c>
+      <c r="D168">
+        <v>85</v>
+      </c>
+      <c r="E168">
+        <v>14.48040885860307</v>
+      </c>
+      <c r="F168" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B170" t="s">
         <v>48</v>
       </c>
       <c r="C170" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="D170">
-        <v>395</v>
+        <v>636</v>
       </c>
       <c r="E170">
-        <v>27.1105010295127</v>
+        <v>41.24513618677042</v>
       </c>
       <c r="F170" t="s">
-        <v>341</v>
+        <v>407</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B171" t="s">
         <v>48</v>
       </c>
       <c r="C171" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D171">
-        <v>378</v>
+        <v>544</v>
       </c>
       <c r="E171">
-        <v>25.94371997254633</v>
+        <v>35.27885862516213</v>
       </c>
       <c r="F171" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173">
-        <v>2023</v>
-      </c>
-      <c r="B173" t="s">
-        <v>49</v>
-      </c>
-      <c r="C173" t="s">
-        <v>208</v>
-      </c>
-      <c r="D173">
-        <v>828</v>
-      </c>
-      <c r="E173">
-        <v>36.71840354767184</v>
-      </c>
-      <c r="F173" t="s">
-        <v>335</v>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172">
+        <v>2021</v>
+      </c>
+      <c r="B172" t="s">
+        <v>48</v>
+      </c>
+      <c r="C172" t="s">
+        <v>224</v>
+      </c>
+      <c r="D172">
+        <v>362</v>
+      </c>
+      <c r="E172">
+        <v>23.47600518806744</v>
+      </c>
+      <c r="F172" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4208,16 +4427,16 @@
         <v>49</v>
       </c>
       <c r="C174" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="D174">
-        <v>524</v>
+        <v>104</v>
       </c>
       <c r="E174">
-        <v>23.23725055432372</v>
+        <v>38.95131086142322</v>
       </c>
       <c r="F174" t="s">
-        <v>335</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4228,16 +4447,16 @@
         <v>49</v>
       </c>
       <c r="C175" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="D175">
-        <v>485</v>
+        <v>100</v>
       </c>
       <c r="E175">
-        <v>21.50776053215078</v>
+        <v>37.45318352059925</v>
       </c>
       <c r="F175" t="s">
-        <v>335</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4248,36 +4467,36 @@
         <v>49</v>
       </c>
       <c r="C176" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="D176">
-        <v>261</v>
+        <v>63</v>
       </c>
       <c r="E176">
-        <v>11.57427937915743</v>
+        <v>23.59550561797753</v>
       </c>
       <c r="F176" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177">
-        <v>2023</v>
-      </c>
-      <c r="B177" t="s">
-        <v>49</v>
-      </c>
-      <c r="C177" t="s">
-        <v>212</v>
-      </c>
-      <c r="D177">
-        <v>157</v>
-      </c>
-      <c r="E177">
-        <v>6.962305986696231</v>
-      </c>
-      <c r="F177" t="s">
-        <v>335</v>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178">
+        <v>2023</v>
+      </c>
+      <c r="B178" t="s">
+        <v>50</v>
+      </c>
+      <c r="C178" t="s">
+        <v>228</v>
+      </c>
+      <c r="D178">
+        <v>1206</v>
+      </c>
+      <c r="E178">
+        <v>37.08487084870848</v>
+      </c>
+      <c r="F178" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4288,16 +4507,16 @@
         <v>50</v>
       </c>
       <c r="C179" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="D179">
-        <v>584</v>
+        <v>1121</v>
       </c>
       <c r="E179">
-        <v>43.90977443609022</v>
+        <v>34.47109471094711</v>
       </c>
       <c r="F179" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4308,36 +4527,36 @@
         <v>50</v>
       </c>
       <c r="C180" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D180">
-        <v>388</v>
+        <v>925</v>
       </c>
       <c r="E180">
-        <v>29.17293233082707</v>
+        <v>28.4440344403444</v>
       </c>
       <c r="F180" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181">
-        <v>2023</v>
-      </c>
-      <c r="B181" t="s">
-        <v>50</v>
-      </c>
-      <c r="C181" t="s">
-        <v>215</v>
-      </c>
-      <c r="D181">
-        <v>358</v>
-      </c>
-      <c r="E181">
-        <v>26.91729323308271</v>
-      </c>
-      <c r="F181" t="s">
-        <v>342</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182">
+        <v>2023</v>
+      </c>
+      <c r="B182" t="s">
+        <v>51</v>
+      </c>
+      <c r="C182" t="s">
+        <v>231</v>
+      </c>
+      <c r="D182">
+        <v>882</v>
+      </c>
+      <c r="E182">
+        <v>45.60496380558428</v>
+      </c>
+      <c r="F182" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -4348,16 +4567,16 @@
         <v>51</v>
       </c>
       <c r="C183" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="D183">
-        <v>634</v>
+        <v>502</v>
       </c>
       <c r="E183">
-        <v>45.67723342939482</v>
+        <v>25.95656670113754</v>
       </c>
       <c r="F183" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4368,16 +4587,16 @@
         <v>51</v>
       </c>
       <c r="C184" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="D184">
-        <v>298</v>
+        <v>399</v>
       </c>
       <c r="E184">
-        <v>21.46974063400576</v>
+        <v>20.63081695966908</v>
       </c>
       <c r="F184" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4388,36 +4607,36 @@
         <v>51</v>
       </c>
       <c r="C185" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="D185">
-        <v>246</v>
+        <v>151</v>
       </c>
       <c r="E185">
-        <v>17.72334293948127</v>
+        <v>7.807652533609101</v>
       </c>
       <c r="F185" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186">
-        <v>2023</v>
-      </c>
-      <c r="B186" t="s">
-        <v>51</v>
-      </c>
-      <c r="C186" t="s">
-        <v>219</v>
-      </c>
-      <c r="D186">
-        <v>210</v>
-      </c>
-      <c r="E186">
-        <v>15.12968299711815</v>
-      </c>
-      <c r="F186" t="s">
-        <v>342</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187">
+        <v>2023</v>
+      </c>
+      <c r="B187" t="s">
+        <v>52</v>
+      </c>
+      <c r="C187" t="s">
+        <v>235</v>
+      </c>
+      <c r="D187">
+        <v>665</v>
+      </c>
+      <c r="E187">
+        <v>39.98797354179194</v>
+      </c>
+      <c r="F187" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4428,16 +4647,16 @@
         <v>52</v>
       </c>
       <c r="C188" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="D188">
-        <v>294</v>
+        <v>429</v>
       </c>
       <c r="E188">
-        <v>38.33116036505867</v>
+        <v>25.79675285628382</v>
       </c>
       <c r="F188" t="s">
-        <v>340</v>
+        <v>413</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -4448,16 +4667,16 @@
         <v>52</v>
       </c>
       <c r="C189" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="D189">
-        <v>145</v>
+        <v>308</v>
       </c>
       <c r="E189">
-        <v>18.90482398956975</v>
+        <v>18.5207456404089</v>
       </c>
       <c r="F189" t="s">
-        <v>340</v>
+        <v>413</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4468,16 +4687,16 @@
         <v>52</v>
       </c>
       <c r="C190" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D190">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="E190">
-        <v>17.73142112125163</v>
+        <v>9.20024052916416</v>
       </c>
       <c r="F190" t="s">
-        <v>340</v>
+        <v>413</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4488,36 +4707,36 @@
         <v>52</v>
       </c>
       <c r="C191" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="D191">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E191">
-        <v>13.5593220338983</v>
+        <v>6.494287432351173</v>
       </c>
       <c r="F191" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192">
-        <v>2023</v>
-      </c>
-      <c r="B192" t="s">
-        <v>52</v>
-      </c>
-      <c r="C192" t="s">
-        <v>224</v>
-      </c>
-      <c r="D192">
-        <v>88</v>
-      </c>
-      <c r="E192">
-        <v>11.47327249022164</v>
-      </c>
-      <c r="F192" t="s">
-        <v>340</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193">
+        <v>2023</v>
+      </c>
+      <c r="B193" t="s">
+        <v>53</v>
+      </c>
+      <c r="C193" t="s">
+        <v>240</v>
+      </c>
+      <c r="D193">
+        <v>445</v>
+      </c>
+      <c r="E193">
+        <v>43.28793774319066</v>
+      </c>
+      <c r="F193" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4528,16 +4747,16 @@
         <v>53</v>
       </c>
       <c r="C194" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="D194">
-        <v>5642</v>
+        <v>353</v>
       </c>
       <c r="E194">
-        <v>34.00638900608764</v>
+        <v>34.33852140077821</v>
       </c>
       <c r="F194" t="s">
-        <v>332</v>
+        <v>414</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4548,36 +4767,36 @@
         <v>53</v>
       </c>
       <c r="C195" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="D195">
-        <v>5540</v>
+        <v>230</v>
       </c>
       <c r="E195">
-        <v>33.39159785425833</v>
+        <v>22.37354085603113</v>
       </c>
       <c r="F195" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196">
-        <v>2023</v>
-      </c>
-      <c r="B196" t="s">
-        <v>53</v>
-      </c>
-      <c r="C196" t="s">
-        <v>227</v>
-      </c>
-      <c r="D196">
-        <v>5409</v>
-      </c>
-      <c r="E196">
-        <v>32.60201313965403</v>
-      </c>
-      <c r="F196" t="s">
-        <v>332</v>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197">
+        <v>2023</v>
+      </c>
+      <c r="B197" t="s">
+        <v>54</v>
+      </c>
+      <c r="C197" t="s">
+        <v>243</v>
+      </c>
+      <c r="D197">
+        <v>684</v>
+      </c>
+      <c r="E197">
+        <v>46.94577899794098</v>
+      </c>
+      <c r="F197" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4588,16 +4807,16 @@
         <v>54</v>
       </c>
       <c r="C198" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="D198">
-        <v>170</v>
+        <v>395</v>
       </c>
       <c r="E198">
-        <v>46.19565217391305</v>
+        <v>27.1105010295127</v>
       </c>
       <c r="F198" t="s">
-        <v>336</v>
+        <v>414</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4608,36 +4827,36 @@
         <v>54</v>
       </c>
       <c r="C199" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="D199">
-        <v>169</v>
+        <v>378</v>
       </c>
       <c r="E199">
-        <v>45.92391304347826</v>
+        <v>25.94371997254633</v>
       </c>
       <c r="F199" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200">
-        <v>2023</v>
-      </c>
-      <c r="B200" t="s">
-        <v>54</v>
-      </c>
-      <c r="C200" t="s">
-        <v>230</v>
-      </c>
-      <c r="D200">
-        <v>29</v>
-      </c>
-      <c r="E200">
-        <v>7.880434782608696</v>
-      </c>
-      <c r="F200" t="s">
-        <v>336</v>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201">
+        <v>2023</v>
+      </c>
+      <c r="B201" t="s">
+        <v>55</v>
+      </c>
+      <c r="C201" t="s">
+        <v>246</v>
+      </c>
+      <c r="D201">
+        <v>828</v>
+      </c>
+      <c r="E201">
+        <v>36.71840354767184</v>
+      </c>
+      <c r="F201" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4648,16 +4867,16 @@
         <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="D202">
-        <v>1114</v>
+        <v>524</v>
       </c>
       <c r="E202">
-        <v>47.79064779064779</v>
+        <v>23.23725055432372</v>
       </c>
       <c r="F202" t="s">
-        <v>331</v>
+        <v>405</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4668,16 +4887,16 @@
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="D203">
-        <v>647</v>
+        <v>485</v>
       </c>
       <c r="E203">
-        <v>27.75632775632776</v>
+        <v>21.50776053215078</v>
       </c>
       <c r="F203" t="s">
-        <v>331</v>
+        <v>405</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4688,16 +4907,16 @@
         <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="D204">
-        <v>369</v>
+        <v>261</v>
       </c>
       <c r="E204">
-        <v>15.83011583011583</v>
+        <v>11.57427937915743</v>
       </c>
       <c r="F204" t="s">
-        <v>331</v>
+        <v>405</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4708,16 +4927,16 @@
         <v>55</v>
       </c>
       <c r="C205" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D205">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="E205">
-        <v>8.622908622908623</v>
+        <v>6.962305986696231</v>
       </c>
       <c r="F205" t="s">
-        <v>331</v>
+        <v>405</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4728,16 +4947,16 @@
         <v>56</v>
       </c>
       <c r="C207" t="s">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="D207">
-        <v>886</v>
+        <v>584</v>
       </c>
       <c r="E207">
-        <v>48.86927744070601</v>
+        <v>43.90977443609022</v>
       </c>
       <c r="F207" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4748,16 +4967,16 @@
         <v>56</v>
       </c>
       <c r="C208" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="D208">
-        <v>699</v>
+        <v>388</v>
       </c>
       <c r="E208">
-        <v>38.55488141202427</v>
+        <v>29.17293233082707</v>
       </c>
       <c r="F208" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4768,16 +4987,16 @@
         <v>56</v>
       </c>
       <c r="C209" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="D209">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E209">
-        <v>12.57584114726972</v>
+        <v>26.91729323308271</v>
       </c>
       <c r="F209" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4788,16 +5007,16 @@
         <v>57</v>
       </c>
       <c r="C211" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="D211">
-        <v>1630</v>
+        <v>634</v>
       </c>
       <c r="E211">
-        <v>44.46262956901255</v>
+        <v>45.67723342939482</v>
       </c>
       <c r="F211" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -4808,16 +5027,16 @@
         <v>57</v>
       </c>
       <c r="C212" t="s">
-        <v>207</v>
+        <v>255</v>
       </c>
       <c r="D212">
-        <v>1039</v>
+        <v>298</v>
       </c>
       <c r="E212">
-        <v>28.34151663938898</v>
+        <v>21.46974063400576</v>
       </c>
       <c r="F212" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -4828,16 +5047,16 @@
         <v>57</v>
       </c>
       <c r="C213" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="D213">
-        <v>813</v>
+        <v>246</v>
       </c>
       <c r="E213">
-        <v>22.17675941080196</v>
+        <v>17.72334293948127</v>
       </c>
       <c r="F213" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -4848,16 +5067,16 @@
         <v>57</v>
       </c>
       <c r="C214" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="D214">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="E214">
-        <v>5.019094380796509</v>
+        <v>15.12968299711815</v>
       </c>
       <c r="F214" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -4868,16 +5087,16 @@
         <v>58</v>
       </c>
       <c r="C216" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="D216">
-        <v>1334</v>
+        <v>294</v>
       </c>
       <c r="E216">
-        <v>46.38386648122393</v>
+        <v>38.33116036505867</v>
       </c>
       <c r="F216" t="s">
-        <v>343</v>
+        <v>411</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -4888,16 +5107,16 @@
         <v>58</v>
       </c>
       <c r="C217" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="D217">
-        <v>1278</v>
+        <v>145</v>
       </c>
       <c r="E217">
-        <v>44.43671766342142</v>
+        <v>18.90482398956975</v>
       </c>
       <c r="F217" t="s">
-        <v>343</v>
+        <v>411</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -4908,16 +5127,36 @@
         <v>58</v>
       </c>
       <c r="C218" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="D218">
-        <v>264</v>
+        <v>136</v>
       </c>
       <c r="E218">
-        <v>9.179415855354661</v>
+        <v>17.73142112125163</v>
       </c>
       <c r="F218" t="s">
-        <v>343</v>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219">
+        <v>2023</v>
+      </c>
+      <c r="B219" t="s">
+        <v>58</v>
+      </c>
+      <c r="C219" t="s">
+        <v>261</v>
+      </c>
+      <c r="D219">
+        <v>104</v>
+      </c>
+      <c r="E219">
+        <v>13.5593220338983</v>
+      </c>
+      <c r="F219" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -4925,39 +5164,19 @@
         <v>2023</v>
       </c>
       <c r="B220" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C220" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="D220">
-        <v>1466</v>
+        <v>88</v>
       </c>
       <c r="E220">
-        <v>43.1303324507208</v>
+        <v>11.47327249022164</v>
       </c>
       <c r="F220" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221">
-        <v>2023</v>
-      </c>
-      <c r="B221" t="s">
-        <v>59</v>
-      </c>
-      <c r="C221" t="s">
-        <v>209</v>
-      </c>
-      <c r="D221">
-        <v>893</v>
-      </c>
-      <c r="E221">
-        <v>26.27243306854957</v>
-      </c>
-      <c r="F221" t="s">
-        <v>335</v>
+        <v>411</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -4968,16 +5187,16 @@
         <v>59</v>
       </c>
       <c r="C222" t="s">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="D222">
-        <v>672</v>
+        <v>957</v>
       </c>
       <c r="E222">
-        <v>19.77052074139453</v>
+        <v>36.62456946039035</v>
       </c>
       <c r="F222" t="s">
-        <v>335</v>
+        <v>408</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -4988,16 +5207,16 @@
         <v>59</v>
       </c>
       <c r="C223" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="D223">
-        <v>245</v>
+        <v>917</v>
       </c>
       <c r="E223">
-        <v>7.208002353633422</v>
+        <v>35.0937619594336</v>
       </c>
       <c r="F223" t="s">
-        <v>335</v>
+        <v>408</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -5008,16 +5227,16 @@
         <v>59</v>
       </c>
       <c r="C224" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="D224">
-        <v>123</v>
+        <v>739</v>
       </c>
       <c r="E224">
-        <v>3.618711385701677</v>
+        <v>28.28166858017605</v>
       </c>
       <c r="F224" t="s">
-        <v>335</v>
+        <v>408</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -5028,16 +5247,16 @@
         <v>60</v>
       </c>
       <c r="C226" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="D226">
-        <v>1108</v>
+        <v>5642</v>
       </c>
       <c r="E226">
-        <v>46.4765100671141</v>
+        <v>34.00638900608764</v>
       </c>
       <c r="F226" t="s">
-        <v>342</v>
+        <v>402</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -5048,16 +5267,16 @@
         <v>60</v>
       </c>
       <c r="C227" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="D227">
-        <v>444</v>
+        <v>5540</v>
       </c>
       <c r="E227">
-        <v>18.6241610738255</v>
+        <v>33.39159785425833</v>
       </c>
       <c r="F227" t="s">
-        <v>342</v>
+        <v>402</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -5068,36 +5287,16 @@
         <v>60</v>
       </c>
       <c r="C228" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="D228">
-        <v>343</v>
+        <v>5409</v>
       </c>
       <c r="E228">
-        <v>14.38758389261745</v>
+        <v>32.60201313965403</v>
       </c>
       <c r="F228" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6">
-      <c r="A229">
-        <v>2023</v>
-      </c>
-      <c r="B229" t="s">
-        <v>60</v>
-      </c>
-      <c r="C229" t="s">
-        <v>217</v>
-      </c>
-      <c r="D229">
-        <v>323</v>
-      </c>
-      <c r="E229">
-        <v>13.5486577181208</v>
-      </c>
-      <c r="F229" t="s">
-        <v>342</v>
+        <v>402</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5105,19 +5304,39 @@
         <v>2023</v>
       </c>
       <c r="B230" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C230" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="D230">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E230">
-        <v>6.963087248322148</v>
+        <v>46.19565217391305</v>
       </c>
       <c r="F230" t="s">
-        <v>342</v>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231">
+        <v>2023</v>
+      </c>
+      <c r="B231" t="s">
+        <v>61</v>
+      </c>
+      <c r="C231" t="s">
+        <v>270</v>
+      </c>
+      <c r="D231">
+        <v>169</v>
+      </c>
+      <c r="E231">
+        <v>45.92391304347826</v>
+      </c>
+      <c r="F231" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -5128,36 +5347,16 @@
         <v>61</v>
       </c>
       <c r="C232" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="D232">
-        <v>904</v>
+        <v>29</v>
       </c>
       <c r="E232">
-        <v>42.60131950989632</v>
+        <v>7.880434782608696</v>
       </c>
       <c r="F232" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
-      <c r="A233">
-        <v>2023</v>
-      </c>
-      <c r="B233" t="s">
-        <v>61</v>
-      </c>
-      <c r="C233" t="s">
-        <v>237</v>
-      </c>
-      <c r="D233">
-        <v>860</v>
-      </c>
-      <c r="E233">
-        <v>40.52780395852969</v>
-      </c>
-      <c r="F233" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5165,19 +5364,19 @@
         <v>2023</v>
       </c>
       <c r="B234" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C234" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="D234">
-        <v>193</v>
+        <v>616</v>
       </c>
       <c r="E234">
-        <v>9.095193213949104</v>
+        <v>48.85011895321173</v>
       </c>
       <c r="F234" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5185,39 +5384,39 @@
         <v>2023</v>
       </c>
       <c r="B235" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C235" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="D235">
-        <v>165</v>
+        <v>534</v>
       </c>
       <c r="E235">
-        <v>7.775683317624882</v>
+        <v>42.34734337827121</v>
       </c>
       <c r="F235" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
-      <c r="A237">
-        <v>2023</v>
-      </c>
-      <c r="B237" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236">
+        <v>2023</v>
+      </c>
+      <c r="B236" t="s">
         <v>62</v>
       </c>
-      <c r="C237" t="s">
-        <v>221</v>
-      </c>
-      <c r="D237">
-        <v>425</v>
-      </c>
-      <c r="E237">
-        <v>25.11820330969267</v>
-      </c>
-      <c r="F237" t="s">
-        <v>340</v>
+      <c r="C236" t="s">
+        <v>274</v>
+      </c>
+      <c r="D236">
+        <v>111</v>
+      </c>
+      <c r="E236">
+        <v>8.802537668517051</v>
+      </c>
+      <c r="F236" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5225,19 +5424,19 @@
         <v>2023</v>
       </c>
       <c r="B238" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C238" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D238">
-        <v>341</v>
+        <v>1114</v>
       </c>
       <c r="E238">
-        <v>20.15366430260048</v>
+        <v>47.79064779064779</v>
       </c>
       <c r="F238" t="s">
-        <v>340</v>
+        <v>401</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -5245,19 +5444,19 @@
         <v>2023</v>
       </c>
       <c r="B239" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C239" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D239">
-        <v>279</v>
+        <v>647</v>
       </c>
       <c r="E239">
-        <v>16.48936170212766</v>
+        <v>27.75632775632776</v>
       </c>
       <c r="F239" t="s">
-        <v>340</v>
+        <v>401</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -5265,19 +5464,19 @@
         <v>2023</v>
       </c>
       <c r="B240" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C240" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D240">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="E240">
-        <v>16.07565011820331</v>
+        <v>15.83011583011583</v>
       </c>
       <c r="F240" t="s">
-        <v>340</v>
+        <v>401</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -5285,39 +5484,39 @@
         <v>2023</v>
       </c>
       <c r="B241" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C241" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D241">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="E241">
-        <v>13.00236406619385</v>
+        <v>8.622908622908623</v>
       </c>
       <c r="F241" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
-      <c r="A242">
-        <v>2023</v>
-      </c>
-      <c r="B242" t="s">
-        <v>62</v>
-      </c>
-      <c r="C242" t="s">
-        <v>224</v>
-      </c>
-      <c r="D242">
-        <v>155</v>
-      </c>
-      <c r="E242">
-        <v>9.160756501182032</v>
-      </c>
-      <c r="F242" t="s">
-        <v>340</v>
+        <v>401</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243">
+        <v>2023</v>
+      </c>
+      <c r="B243" t="s">
+        <v>64</v>
+      </c>
+      <c r="C243" t="s">
+        <v>235</v>
+      </c>
+      <c r="D243">
+        <v>592</v>
+      </c>
+      <c r="E243">
+        <v>32.52747252747253</v>
+      </c>
+      <c r="F243" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -5325,19 +5524,19 @@
         <v>2023</v>
       </c>
       <c r="B244" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C244" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D244">
-        <v>286</v>
+        <v>571</v>
       </c>
       <c r="E244">
-        <v>48.22934232715008</v>
+        <v>31.37362637362637</v>
       </c>
       <c r="F244" t="s">
-        <v>336</v>
+        <v>413</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -5345,19 +5544,19 @@
         <v>2023</v>
       </c>
       <c r="B245" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C245" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D245">
-        <v>212</v>
+        <v>324</v>
       </c>
       <c r="E245">
-        <v>35.7504215851602</v>
+        <v>17.8021978021978</v>
       </c>
       <c r="F245" t="s">
-        <v>336</v>
+        <v>413</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -5365,39 +5564,39 @@
         <v>2023</v>
       </c>
       <c r="B246" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C246" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D246">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="E246">
-        <v>16.02023608768971</v>
+        <v>16.20879120879121</v>
       </c>
       <c r="F246" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
-      <c r="A248">
-        <v>2023</v>
-      </c>
-      <c r="B248" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247">
+        <v>2023</v>
+      </c>
+      <c r="B247" t="s">
         <v>64</v>
       </c>
-      <c r="C248" t="s">
-        <v>244</v>
-      </c>
-      <c r="D248">
-        <v>431</v>
-      </c>
-      <c r="E248">
-        <v>36.77474402730375</v>
-      </c>
-      <c r="F248" t="s">
-        <v>336</v>
+      <c r="C247" t="s">
+        <v>239</v>
+      </c>
+      <c r="D247">
+        <v>38</v>
+      </c>
+      <c r="E247">
+        <v>2.087912087912088</v>
+      </c>
+      <c r="F247" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -5405,19 +5604,19 @@
         <v>2023</v>
       </c>
       <c r="B249" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C249" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D249">
-        <v>297</v>
+        <v>886</v>
       </c>
       <c r="E249">
-        <v>25.34129692832764</v>
+        <v>48.86927744070601</v>
       </c>
       <c r="F249" t="s">
-        <v>336</v>
+        <v>414</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -5425,19 +5624,19 @@
         <v>2023</v>
       </c>
       <c r="B250" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C250" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D250">
-        <v>285</v>
+        <v>699</v>
       </c>
       <c r="E250">
-        <v>24.31740614334471</v>
+        <v>38.55488141202427</v>
       </c>
       <c r="F250" t="s">
-        <v>336</v>
+        <v>414</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -5445,39 +5644,39 @@
         <v>2023</v>
       </c>
       <c r="B251" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C251" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D251">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="E251">
-        <v>8.191126279863481</v>
+        <v>12.57584114726972</v>
       </c>
       <c r="F251" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
-      <c r="A252">
-        <v>2023</v>
-      </c>
-      <c r="B252" t="s">
-        <v>64</v>
-      </c>
-      <c r="C252" t="s">
-        <v>248</v>
-      </c>
-      <c r="D252">
-        <v>63</v>
-      </c>
-      <c r="E252">
-        <v>5.375426621160409</v>
-      </c>
-      <c r="F252" t="s">
-        <v>336</v>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253">
+        <v>2023</v>
+      </c>
+      <c r="B253" t="s">
+        <v>66</v>
+      </c>
+      <c r="C253" t="s">
+        <v>243</v>
+      </c>
+      <c r="D253">
+        <v>1630</v>
+      </c>
+      <c r="E253">
+        <v>44.46262956901255</v>
+      </c>
+      <c r="F253" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -5485,19 +5684,19 @@
         <v>2023</v>
       </c>
       <c r="B254" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C254" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D254">
-        <v>273</v>
+        <v>1039</v>
       </c>
       <c r="E254">
-        <v>45.4242928452579</v>
+        <v>28.34151663938898</v>
       </c>
       <c r="F254" t="s">
-        <v>339</v>
+        <v>414</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -5505,19 +5704,19 @@
         <v>2023</v>
       </c>
       <c r="B255" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C255" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D255">
-        <v>234</v>
+        <v>813</v>
       </c>
       <c r="E255">
-        <v>38.9351081530782</v>
+        <v>22.17675941080196</v>
       </c>
       <c r="F255" t="s">
-        <v>339</v>
+        <v>414</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -5525,19 +5724,19 @@
         <v>2023</v>
       </c>
       <c r="B256" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C256" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="D256">
-        <v>94</v>
+        <v>184</v>
       </c>
       <c r="E256">
-        <v>15.64059900166389</v>
+        <v>5.019094380796509</v>
       </c>
       <c r="F256" t="s">
-        <v>339</v>
+        <v>414</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -5545,19 +5744,19 @@
         <v>2023</v>
       </c>
       <c r="B258" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C258" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="D258">
-        <v>124</v>
+        <v>1334</v>
       </c>
       <c r="E258">
-        <v>47.69230769230769</v>
+        <v>46.38386648122393</v>
       </c>
       <c r="F258" t="s">
-        <v>339</v>
+        <v>416</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -5565,19 +5764,19 @@
         <v>2023</v>
       </c>
       <c r="B259" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C259" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="D259">
-        <v>73</v>
+        <v>1278</v>
       </c>
       <c r="E259">
-        <v>28.07692307692308</v>
+        <v>44.43671766342142</v>
       </c>
       <c r="F259" t="s">
-        <v>339</v>
+        <v>416</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -5585,19 +5784,19 @@
         <v>2023</v>
       </c>
       <c r="B260" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C260" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="D260">
-        <v>63</v>
+        <v>264</v>
       </c>
       <c r="E260">
-        <v>24.23076923076923</v>
+        <v>9.179415855354661</v>
       </c>
       <c r="F260" t="s">
-        <v>339</v>
+        <v>416</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -5605,19 +5804,19 @@
         <v>2023</v>
       </c>
       <c r="B262" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C262" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D262">
-        <v>827</v>
+        <v>1466</v>
       </c>
       <c r="E262">
-        <v>47.88650839606254</v>
+        <v>43.1303324507208</v>
       </c>
       <c r="F262" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -5625,19 +5824,19 @@
         <v>2023</v>
       </c>
       <c r="B263" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C263" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="D263">
-        <v>284</v>
+        <v>893</v>
       </c>
       <c r="E263">
-        <v>16.44470179502026</v>
+        <v>26.27243306854957</v>
       </c>
       <c r="F263" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -5645,19 +5844,19 @@
         <v>2023</v>
       </c>
       <c r="B264" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C264" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D264">
-        <v>222</v>
+        <v>672</v>
       </c>
       <c r="E264">
-        <v>12.85466126230457</v>
+        <v>19.77052074139453</v>
       </c>
       <c r="F264" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -5665,19 +5864,19 @@
         <v>2023</v>
       </c>
       <c r="B265" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C265" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="D265">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="E265">
-        <v>12.21771858714534</v>
+        <v>7.208002353633422</v>
       </c>
       <c r="F265" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -5685,19 +5884,19 @@
         <v>2023</v>
       </c>
       <c r="B266" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C266" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="D266">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="E266">
-        <v>10.59640995946728</v>
+        <v>3.618711385701677</v>
       </c>
       <c r="F266" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -5705,19 +5904,19 @@
         <v>2023</v>
       </c>
       <c r="B268" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C268" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D268">
-        <v>605</v>
+        <v>1108</v>
       </c>
       <c r="E268">
-        <v>41.10054347826087</v>
+        <v>46.4765100671141</v>
       </c>
       <c r="F268" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -5725,19 +5924,19 @@
         <v>2023</v>
       </c>
       <c r="B269" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C269" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D269">
-        <v>593</v>
+        <v>444</v>
       </c>
       <c r="E269">
-        <v>40.28532608695652</v>
+        <v>18.6241610738255</v>
       </c>
       <c r="F269" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -5745,19 +5944,39 @@
         <v>2023</v>
       </c>
       <c r="B270" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C270" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="D270">
-        <v>274</v>
+        <v>343</v>
       </c>
       <c r="E270">
-        <v>18.61413043478261</v>
+        <v>14.38758389261745</v>
       </c>
       <c r="F270" t="s">
-        <v>341</v>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271">
+        <v>2023</v>
+      </c>
+      <c r="B271" t="s">
+        <v>69</v>
+      </c>
+      <c r="C271" t="s">
+        <v>255</v>
+      </c>
+      <c r="D271">
+        <v>323</v>
+      </c>
+      <c r="E271">
+        <v>13.5486577181208</v>
+      </c>
+      <c r="F271" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -5768,36 +5987,16 @@
         <v>69</v>
       </c>
       <c r="C272" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D272">
-        <v>347</v>
+        <v>166</v>
       </c>
       <c r="E272">
-        <v>49.15014164305949</v>
+        <v>6.963087248322148</v>
       </c>
       <c r="F272" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
-      <c r="A273">
-        <v>2023</v>
-      </c>
-      <c r="B273" t="s">
-        <v>69</v>
-      </c>
-      <c r="C273" t="s">
-        <v>264</v>
-      </c>
-      <c r="D273">
-        <v>168</v>
-      </c>
-      <c r="E273">
-        <v>23.79603399433428</v>
-      </c>
-      <c r="F273" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -5805,19 +6004,19 @@
         <v>2023</v>
       </c>
       <c r="B274" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C274" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D274">
-        <v>103</v>
+        <v>904</v>
       </c>
       <c r="E274">
-        <v>14.58923512747875</v>
+        <v>42.60131950989632</v>
       </c>
       <c r="F274" t="s">
-        <v>341</v>
+        <v>415</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -5825,919 +6024,959 @@
         <v>2023</v>
       </c>
       <c r="B275" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C275" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="D275">
-        <v>88</v>
+        <v>860</v>
       </c>
       <c r="E275">
-        <v>12.46458923512748</v>
+        <v>40.52780395852969</v>
       </c>
       <c r="F275" t="s">
-        <v>341</v>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276">
+        <v>2023</v>
+      </c>
+      <c r="B276" t="s">
+        <v>70</v>
+      </c>
+      <c r="C276" t="s">
+        <v>282</v>
+      </c>
+      <c r="D276">
+        <v>193</v>
+      </c>
+      <c r="E276">
+        <v>9.095193213949104</v>
+      </c>
+      <c r="F276" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B277" t="s">
         <v>70</v>
       </c>
       <c r="C277" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="D277">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E277">
-        <v>44.68085106382978</v>
+        <v>7.775683317624882</v>
       </c>
       <c r="F277" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
-      <c r="A278">
-        <v>2024</v>
-      </c>
-      <c r="B278" t="s">
-        <v>70</v>
-      </c>
-      <c r="C278" t="s">
-        <v>268</v>
-      </c>
-      <c r="D278">
-        <v>102</v>
-      </c>
-      <c r="E278">
-        <v>31.00303951367781</v>
-      </c>
-      <c r="F278" t="s">
-        <v>10</v>
+        <v>415</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B279" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C279" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D279">
-        <v>80</v>
+        <v>425</v>
       </c>
       <c r="E279">
-        <v>24.3161094224924</v>
+        <v>25.11820330969267</v>
       </c>
       <c r="F279" t="s">
-        <v>10</v>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280">
+        <v>2023</v>
+      </c>
+      <c r="B280" t="s">
+        <v>71</v>
+      </c>
+      <c r="C280" t="s">
+        <v>258</v>
+      </c>
+      <c r="D280">
+        <v>341</v>
+      </c>
+      <c r="E280">
+        <v>20.15366430260048</v>
+      </c>
+      <c r="F280" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B281" t="s">
         <v>71</v>
       </c>
       <c r="C281" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D281">
-        <v>1224</v>
+        <v>279</v>
       </c>
       <c r="E281">
-        <v>28.77291960507758</v>
+        <v>16.48936170212766</v>
       </c>
       <c r="F281" t="s">
-        <v>332</v>
+        <v>411</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B282" t="s">
         <v>71</v>
       </c>
       <c r="C282" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D282">
-        <v>1052</v>
+        <v>272</v>
       </c>
       <c r="E282">
-        <v>24.72966619652092</v>
+        <v>16.07565011820331</v>
       </c>
       <c r="F282" t="s">
-        <v>332</v>
+        <v>411</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B283" t="s">
         <v>71</v>
       </c>
       <c r="C283" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="D283">
-        <v>685</v>
+        <v>220</v>
       </c>
       <c r="E283">
-        <v>16.10249177244946</v>
+        <v>13.00236406619385</v>
       </c>
       <c r="F283" t="s">
-        <v>332</v>
+        <v>411</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B284" t="s">
         <v>71</v>
       </c>
       <c r="C284" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="D284">
-        <v>656</v>
+        <v>155</v>
       </c>
       <c r="E284">
-        <v>15.420780441937</v>
+        <v>9.160756501182032</v>
       </c>
       <c r="F284" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
-      <c r="A285">
-        <v>2025</v>
-      </c>
-      <c r="B285" t="s">
-        <v>71</v>
-      </c>
-      <c r="C285" t="s">
-        <v>274</v>
-      </c>
-      <c r="D285">
-        <v>637</v>
-      </c>
-      <c r="E285">
-        <v>14.97414198401504</v>
-      </c>
-      <c r="F285" t="s">
-        <v>332</v>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286">
+        <v>2023</v>
+      </c>
+      <c r="B286" t="s">
+        <v>72</v>
+      </c>
+      <c r="C286" t="s">
+        <v>285</v>
+      </c>
+      <c r="D286">
+        <v>272</v>
+      </c>
+      <c r="E286">
+        <v>44.01294498381877</v>
+      </c>
+      <c r="F286" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B287" t="s">
         <v>72</v>
       </c>
       <c r="C287" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D287">
-        <v>3817</v>
+        <v>145</v>
       </c>
       <c r="E287">
-        <v>39.10860655737705</v>
+        <v>23.46278317152104</v>
       </c>
       <c r="F287" t="s">
-        <v>332</v>
+        <v>413</v>
       </c>
     </row>
     <row r="288" spans="1:6">
       <c r="A288">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B288" t="s">
         <v>72</v>
       </c>
       <c r="C288" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D288">
-        <v>3272</v>
+        <v>108</v>
       </c>
       <c r="E288">
-        <v>33.52459016393443</v>
+        <v>17.47572815533981</v>
       </c>
       <c r="F288" t="s">
-        <v>332</v>
+        <v>413</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B289" t="s">
         <v>72</v>
       </c>
       <c r="C289" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="D289">
-        <v>2671</v>
+        <v>50</v>
       </c>
       <c r="E289">
-        <v>27.36680327868852</v>
+        <v>8.090614886731391</v>
       </c>
       <c r="F289" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
-      <c r="A291">
-        <v>2025</v>
-      </c>
-      <c r="B291" t="s">
-        <v>73</v>
-      </c>
-      <c r="C291" t="s">
-        <v>278</v>
-      </c>
-      <c r="D291">
-        <v>710</v>
-      </c>
-      <c r="E291">
-        <v>46.64914586070959</v>
-      </c>
-      <c r="F291" t="s">
-        <v>336</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290">
+        <v>2023</v>
+      </c>
+      <c r="B290" t="s">
+        <v>72</v>
+      </c>
+      <c r="C290" t="s">
+        <v>289</v>
+      </c>
+      <c r="D290">
+        <v>43</v>
+      </c>
+      <c r="E290">
+        <v>6.957928802588997</v>
+      </c>
+      <c r="F290" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B292" t="s">
         <v>73</v>
       </c>
       <c r="C292" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="D292">
-        <v>617</v>
+        <v>286</v>
       </c>
       <c r="E292">
-        <v>40.53876478318003</v>
+        <v>48.22934232715008</v>
       </c>
       <c r="F292" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B293" t="s">
         <v>73</v>
       </c>
       <c r="C293" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="D293">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="E293">
-        <v>12.81208935611038</v>
+        <v>35.7504215851602</v>
       </c>
       <c r="F293" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
-      <c r="A295">
-        <v>2025</v>
-      </c>
-      <c r="B295" t="s">
-        <v>74</v>
-      </c>
-      <c r="C295" t="s">
-        <v>280</v>
-      </c>
-      <c r="D295">
-        <v>241</v>
-      </c>
-      <c r="E295">
-        <v>49.79338842975206</v>
-      </c>
-      <c r="F295" t="s">
-        <v>341</v>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294">
+        <v>2023</v>
+      </c>
+      <c r="B294" t="s">
+        <v>73</v>
+      </c>
+      <c r="C294" t="s">
+        <v>292</v>
+      </c>
+      <c r="D294">
+        <v>95</v>
+      </c>
+      <c r="E294">
+        <v>16.02023608768971</v>
+      </c>
+      <c r="F294" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B296" t="s">
         <v>74</v>
       </c>
       <c r="C296" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D296">
-        <v>193</v>
+        <v>431</v>
       </c>
       <c r="E296">
-        <v>39.87603305785124</v>
+        <v>36.77474402730375</v>
       </c>
       <c r="F296" t="s">
-        <v>341</v>
+        <v>406</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B297" t="s">
         <v>74</v>
       </c>
       <c r="C297" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D297">
-        <v>49</v>
+        <v>297</v>
       </c>
       <c r="E297">
-        <v>10.12396694214876</v>
+        <v>25.34129692832764</v>
       </c>
       <c r="F297" t="s">
-        <v>341</v>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298">
+        <v>2023</v>
+      </c>
+      <c r="B298" t="s">
+        <v>74</v>
+      </c>
+      <c r="C298" t="s">
+        <v>295</v>
+      </c>
+      <c r="D298">
+        <v>285</v>
+      </c>
+      <c r="E298">
+        <v>24.31740614334471</v>
+      </c>
+      <c r="F298" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B299" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C299" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D299">
-        <v>373</v>
+        <v>96</v>
       </c>
       <c r="E299">
-        <v>36.39024390243902</v>
+        <v>8.191126279863481</v>
       </c>
       <c r="F299" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B300" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C300" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="D300">
-        <v>225</v>
+        <v>63</v>
       </c>
       <c r="E300">
-        <v>21.95121951219512</v>
+        <v>5.375426621160409</v>
       </c>
       <c r="F300" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6">
-      <c r="A301">
-        <v>2025</v>
-      </c>
-      <c r="B301" t="s">
-        <v>75</v>
-      </c>
-      <c r="C301" t="s">
-        <v>285</v>
-      </c>
-      <c r="D301">
-        <v>206</v>
-      </c>
-      <c r="E301">
-        <v>20.09756097560976</v>
-      </c>
-      <c r="F301" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B302" t="s">
         <v>75</v>
       </c>
       <c r="C302" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D302">
-        <v>140</v>
+        <v>273</v>
       </c>
       <c r="E302">
-        <v>13.65853658536586</v>
+        <v>45.4242928452579</v>
       </c>
       <c r="F302" t="s">
-        <v>331</v>
+        <v>410</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B303" t="s">
         <v>75</v>
       </c>
       <c r="C303" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D303">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="E303">
-        <v>7.902439024390244</v>
+        <v>38.9351081530782</v>
       </c>
       <c r="F303" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6">
-      <c r="A305">
-        <v>2025</v>
-      </c>
-      <c r="B305" t="s">
-        <v>35</v>
-      </c>
-      <c r="C305" t="s">
-        <v>288</v>
-      </c>
-      <c r="D305">
-        <v>6552</v>
-      </c>
-      <c r="E305">
-        <v>47.15704620699582</v>
-      </c>
-      <c r="F305" t="s">
-        <v>336</v>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304">
+        <v>2023</v>
+      </c>
+      <c r="B304" t="s">
+        <v>75</v>
+      </c>
+      <c r="C304" t="s">
+        <v>300</v>
+      </c>
+      <c r="D304">
+        <v>94</v>
+      </c>
+      <c r="E304">
+        <v>15.64059900166389</v>
+      </c>
+      <c r="F304" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="306" spans="1:6">
       <c r="A306">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B306" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C306" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="D306">
-        <v>4724</v>
+        <v>124</v>
       </c>
       <c r="E306">
-        <v>34.00028789405498</v>
+        <v>47.69230769230769</v>
       </c>
       <c r="F306" t="s">
-        <v>336</v>
+        <v>410</v>
       </c>
     </row>
     <row r="307" spans="1:6">
       <c r="A307">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B307" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C307" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D307">
-        <v>2618</v>
+        <v>73</v>
       </c>
       <c r="E307">
-        <v>18.84266589894919</v>
+        <v>28.07692307692308</v>
       </c>
       <c r="F307" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6">
-      <c r="A309">
-        <v>2025</v>
-      </c>
-      <c r="B309" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308">
+        <v>2023</v>
+      </c>
+      <c r="B308" t="s">
         <v>76</v>
       </c>
-      <c r="C309" t="s">
-        <v>291</v>
-      </c>
-      <c r="D309">
-        <v>5832</v>
-      </c>
-      <c r="E309">
-        <v>37.28423475258919</v>
-      </c>
-      <c r="F309" t="s">
-        <v>332</v>
+      <c r="C308" t="s">
+        <v>303</v>
+      </c>
+      <c r="D308">
+        <v>63</v>
+      </c>
+      <c r="E308">
+        <v>24.23076923076923</v>
+      </c>
+      <c r="F308" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B310" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C310" t="s">
-        <v>226</v>
+        <v>304</v>
       </c>
       <c r="D310">
-        <v>4950</v>
+        <v>827</v>
       </c>
       <c r="E310">
-        <v>31.64556962025317</v>
+        <v>47.88650839606254</v>
       </c>
       <c r="F310" t="s">
-        <v>332</v>
+        <v>415</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B311" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C311" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="D311">
-        <v>4834</v>
+        <v>284</v>
       </c>
       <c r="E311">
-        <v>30.90397647359673</v>
+        <v>16.44470179502026</v>
       </c>
       <c r="F311" t="s">
-        <v>332</v>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312">
+        <v>2023</v>
+      </c>
+      <c r="B312" t="s">
+        <v>77</v>
+      </c>
+      <c r="C312" t="s">
+        <v>306</v>
+      </c>
+      <c r="D312">
+        <v>222</v>
+      </c>
+      <c r="E312">
+        <v>12.85466126230457</v>
+      </c>
+      <c r="F312" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="313" spans="1:6">
       <c r="A313">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B313" t="s">
         <v>77</v>
       </c>
       <c r="C313" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="D313">
-        <v>9318</v>
+        <v>211</v>
       </c>
       <c r="E313">
-        <v>41.92764578833693</v>
+        <v>12.21771858714534</v>
       </c>
       <c r="F313" t="s">
-        <v>342</v>
+        <v>415</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B314" t="s">
         <v>77</v>
       </c>
       <c r="C314" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="D314">
-        <v>8700</v>
+        <v>183</v>
       </c>
       <c r="E314">
-        <v>39.14686825053996</v>
+        <v>10.59640995946728</v>
       </c>
       <c r="F314" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6">
-      <c r="A315">
-        <v>2025</v>
-      </c>
-      <c r="B315" t="s">
-        <v>77</v>
-      </c>
-      <c r="C315" t="s">
-        <v>295</v>
-      </c>
-      <c r="D315">
-        <v>4206</v>
-      </c>
-      <c r="E315">
-        <v>18.92548596112311</v>
-      </c>
-      <c r="F315" t="s">
-        <v>342</v>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316">
+        <v>2023</v>
+      </c>
+      <c r="B316" t="s">
+        <v>78</v>
+      </c>
+      <c r="C316" t="s">
+        <v>309</v>
+      </c>
+      <c r="D316">
+        <v>605</v>
+      </c>
+      <c r="E316">
+        <v>41.10054347826087</v>
+      </c>
+      <c r="F316" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B317" t="s">
         <v>78</v>
       </c>
       <c r="C317" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D317">
-        <v>1473</v>
+        <v>593</v>
       </c>
       <c r="E317">
-        <v>39.30096051227321</v>
+        <v>40.28532608695652</v>
       </c>
       <c r="F317" t="s">
-        <v>340</v>
+        <v>414</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B318" t="s">
         <v>78</v>
       </c>
       <c r="C318" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="D318">
-        <v>1297</v>
+        <v>274</v>
       </c>
       <c r="E318">
-        <v>34.6051227321238</v>
+        <v>18.61413043478261</v>
       </c>
       <c r="F318" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6">
-      <c r="A319">
-        <v>2025</v>
-      </c>
-      <c r="B319" t="s">
-        <v>78</v>
-      </c>
-      <c r="C319" t="s">
-        <v>298</v>
-      </c>
-      <c r="D319">
-        <v>516</v>
-      </c>
-      <c r="E319">
-        <v>13.76734258271078</v>
-      </c>
-      <c r="F319" t="s">
-        <v>340</v>
+        <v>414</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B320" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C320" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D320">
-        <v>305</v>
+        <v>347</v>
       </c>
       <c r="E320">
-        <v>8.137673425827108</v>
+        <v>49.15014164305949</v>
       </c>
       <c r="F320" t="s">
-        <v>340</v>
+        <v>414</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B321" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C321" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D321">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E321">
-        <v>4.188900747065102</v>
+        <v>23.79603399433428</v>
       </c>
       <c r="F321" t="s">
-        <v>340</v>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322">
+        <v>2023</v>
+      </c>
+      <c r="B322" t="s">
+        <v>79</v>
+      </c>
+      <c r="C322" t="s">
+        <v>314</v>
+      </c>
+      <c r="D322">
+        <v>103</v>
+      </c>
+      <c r="E322">
+        <v>14.58923512747875</v>
+      </c>
+      <c r="F322" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B323" t="s">
         <v>79</v>
       </c>
       <c r="C323" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D323">
-        <v>854</v>
+        <v>88</v>
       </c>
       <c r="E323">
-        <v>47.52365052865888</v>
+        <v>12.46458923512748</v>
       </c>
       <c r="F323" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6">
-      <c r="A324">
-        <v>2025</v>
-      </c>
-      <c r="B324" t="s">
-        <v>79</v>
-      </c>
-      <c r="C324" t="s">
-        <v>302</v>
-      </c>
-      <c r="D324">
-        <v>764</v>
-      </c>
-      <c r="E324">
-        <v>42.51530328324986</v>
-      </c>
-      <c r="F324" t="s">
-        <v>330</v>
+        <v>414</v>
       </c>
     </row>
     <row r="325" spans="1:6">
       <c r="A325">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B325" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C325" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D325">
-        <v>175</v>
+        <v>372</v>
       </c>
       <c r="E325">
-        <v>9.738452977184195</v>
+        <v>42.36902050113896</v>
       </c>
       <c r="F325" t="s">
-        <v>330</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326">
+        <v>2023</v>
+      </c>
+      <c r="B326" t="s">
+        <v>80</v>
+      </c>
+      <c r="C326" t="s">
+        <v>317</v>
+      </c>
+      <c r="D326">
+        <v>195</v>
+      </c>
+      <c r="E326">
+        <v>22.20956719817768</v>
+      </c>
+      <c r="F326" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B327" t="s">
         <v>80</v>
       </c>
       <c r="C327" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D327">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="E327">
-        <v>45.2513966480447</v>
+        <v>21.98177676537586</v>
       </c>
       <c r="F327" t="s">
-        <v>331</v>
+        <v>408</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B328" t="s">
         <v>80</v>
       </c>
       <c r="C328" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D328">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="E328">
-        <v>43.5754189944134</v>
+        <v>13.43963553530752</v>
       </c>
       <c r="F328" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6">
-      <c r="A329">
-        <v>2025</v>
-      </c>
-      <c r="B329" t="s">
-        <v>80</v>
-      </c>
-      <c r="C329" t="s">
-        <v>306</v>
-      </c>
-      <c r="D329">
-        <v>40</v>
-      </c>
-      <c r="E329">
-        <v>11.1731843575419</v>
-      </c>
-      <c r="F329" t="s">
-        <v>331</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330">
+        <v>2024</v>
+      </c>
+      <c r="B330" t="s">
+        <v>81</v>
+      </c>
+      <c r="C330" t="s">
+        <v>320</v>
+      </c>
+      <c r="D330">
+        <v>147</v>
+      </c>
+      <c r="E330">
+        <v>44.68085106382978</v>
+      </c>
+      <c r="F330" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B331" t="s">
         <v>81</v>
       </c>
       <c r="C331" t="s">
-        <v>101</v>
+        <v>321</v>
       </c>
       <c r="D331">
-        <v>11367</v>
+        <v>102</v>
       </c>
       <c r="E331">
-        <v>45.69280861840254</v>
+        <v>31.00303951367781</v>
       </c>
       <c r="F331" t="s">
-        <v>331</v>
+        <v>10</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B332" t="s">
         <v>81</v>
       </c>
       <c r="C332" t="s">
-        <v>100</v>
+        <v>322</v>
       </c>
       <c r="D332">
-        <v>8188</v>
+        <v>80</v>
       </c>
       <c r="E332">
-        <v>32.91393656791413</v>
+        <v>24.3161094224924</v>
       </c>
       <c r="F332" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6">
-      <c r="A333">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334">
         <v>2025</v>
       </c>
-      <c r="B333" t="s">
-        <v>81</v>
-      </c>
-      <c r="C333" t="s">
-        <v>103</v>
-      </c>
-      <c r="D333">
-        <v>5322</v>
-      </c>
-      <c r="E333">
-        <v>21.39325481368332</v>
-      </c>
-      <c r="F333" t="s">
-        <v>331</v>
+      <c r="B334" t="s">
+        <v>82</v>
+      </c>
+      <c r="C334" t="s">
+        <v>323</v>
+      </c>
+      <c r="D334">
+        <v>1224</v>
+      </c>
+      <c r="E334">
+        <v>28.77291960507758</v>
+      </c>
+      <c r="F334" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -6748,16 +6987,16 @@
         <v>82</v>
       </c>
       <c r="C335" t="s">
-        <v>242</v>
+        <v>324</v>
       </c>
       <c r="D335">
-        <v>287</v>
+        <v>1052</v>
       </c>
       <c r="E335">
-        <v>47.83333333333334</v>
+        <v>24.72966619652092</v>
       </c>
       <c r="F335" t="s">
-        <v>336</v>
+        <v>402</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -6768,16 +7007,16 @@
         <v>82</v>
       </c>
       <c r="C336" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="D336">
-        <v>175</v>
+        <v>685</v>
       </c>
       <c r="E336">
-        <v>29.16666666666667</v>
+        <v>16.10249177244946</v>
       </c>
       <c r="F336" t="s">
-        <v>336</v>
+        <v>402</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -6788,36 +7027,36 @@
         <v>82</v>
       </c>
       <c r="C337" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D337">
-        <v>138</v>
+        <v>656</v>
       </c>
       <c r="E337">
-        <v>23</v>
+        <v>15.420780441937</v>
       </c>
       <c r="F337" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6">
-      <c r="A339">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338">
         <v>2025</v>
       </c>
-      <c r="B339" t="s">
-        <v>83</v>
-      </c>
-      <c r="C339" t="s">
-        <v>309</v>
-      </c>
-      <c r="D339">
-        <v>163</v>
-      </c>
-      <c r="E339">
-        <v>38.71733966745843</v>
-      </c>
-      <c r="F339" t="s">
-        <v>344</v>
+      <c r="B338" t="s">
+        <v>82</v>
+      </c>
+      <c r="C338" t="s">
+        <v>327</v>
+      </c>
+      <c r="D338">
+        <v>637</v>
+      </c>
+      <c r="E338">
+        <v>14.97414198401504</v>
+      </c>
+      <c r="F338" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -6828,16 +7067,16 @@
         <v>83</v>
       </c>
       <c r="C340" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="D340">
-        <v>160</v>
+        <v>3817</v>
       </c>
       <c r="E340">
-        <v>38.00475059382423</v>
+        <v>39.10860655737705</v>
       </c>
       <c r="F340" t="s">
-        <v>344</v>
+        <v>402</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -6848,16 +7087,16 @@
         <v>83</v>
       </c>
       <c r="C341" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="D341">
-        <v>75</v>
+        <v>3272</v>
       </c>
       <c r="E341">
-        <v>17.81472684085511</v>
+        <v>33.52459016393443</v>
       </c>
       <c r="F341" t="s">
-        <v>344</v>
+        <v>402</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -6868,16 +7107,16 @@
         <v>83</v>
       </c>
       <c r="C342" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D342">
-        <v>23</v>
+        <v>2671</v>
       </c>
       <c r="E342">
-        <v>5.463182897862233</v>
+        <v>27.36680327868852</v>
       </c>
       <c r="F342" t="s">
-        <v>344</v>
+        <v>402</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -6888,16 +7127,16 @@
         <v>84</v>
       </c>
       <c r="C344" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D344">
-        <v>104</v>
+        <v>710</v>
       </c>
       <c r="E344">
-        <v>35.37414965986395</v>
+        <v>46.64914586070959</v>
       </c>
       <c r="F344" t="s">
-        <v>330</v>
+        <v>406</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -6908,16 +7147,16 @@
         <v>84</v>
       </c>
       <c r="C345" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D345">
-        <v>79</v>
+        <v>617</v>
       </c>
       <c r="E345">
-        <v>26.87074829931973</v>
+        <v>40.53876478318003</v>
       </c>
       <c r="F345" t="s">
-        <v>330</v>
+        <v>406</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -6928,36 +7167,36 @@
         <v>84</v>
       </c>
       <c r="C346" t="s">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="D346">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="E346">
-        <v>26.53061224489796</v>
+        <v>12.81208935611038</v>
       </c>
       <c r="F346" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6">
-      <c r="A347">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348">
         <v>2025</v>
       </c>
-      <c r="B347" t="s">
-        <v>84</v>
-      </c>
-      <c r="C347" t="s">
-        <v>316</v>
-      </c>
-      <c r="D347">
-        <v>32</v>
-      </c>
-      <c r="E347">
-        <v>10.8843537414966</v>
-      </c>
-      <c r="F347" t="s">
-        <v>330</v>
+      <c r="B348" t="s">
+        <v>85</v>
+      </c>
+      <c r="C348" t="s">
+        <v>333</v>
+      </c>
+      <c r="D348">
+        <v>241</v>
+      </c>
+      <c r="E348">
+        <v>49.79338842975206</v>
+      </c>
+      <c r="F348" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -6968,16 +7207,16 @@
         <v>85</v>
       </c>
       <c r="C349" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="D349">
-        <v>549</v>
+        <v>193</v>
       </c>
       <c r="E349">
-        <v>42.99138606108065</v>
+        <v>39.87603305785124</v>
       </c>
       <c r="F349" t="s">
-        <v>342</v>
+        <v>414</v>
       </c>
     </row>
     <row r="350" spans="1:6">
@@ -6988,36 +7227,36 @@
         <v>85</v>
       </c>
       <c r="C350" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="D350">
-        <v>445</v>
+        <v>49</v>
       </c>
       <c r="E350">
-        <v>34.84729835552075</v>
+        <v>10.12396694214876</v>
       </c>
       <c r="F350" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6">
-      <c r="A351">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352">
         <v>2025</v>
       </c>
-      <c r="B351" t="s">
-        <v>85</v>
-      </c>
-      <c r="C351" t="s">
-        <v>319</v>
-      </c>
-      <c r="D351">
-        <v>283</v>
-      </c>
-      <c r="E351">
-        <v>22.16131558339859</v>
-      </c>
-      <c r="F351" t="s">
-        <v>342</v>
+      <c r="B352" t="s">
+        <v>86</v>
+      </c>
+      <c r="C352" t="s">
+        <v>336</v>
+      </c>
+      <c r="D352">
+        <v>373</v>
+      </c>
+      <c r="E352">
+        <v>36.39024390243902</v>
+      </c>
+      <c r="F352" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -7028,16 +7267,16 @@
         <v>86</v>
       </c>
       <c r="C353" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D353">
-        <v>123</v>
+        <v>225</v>
       </c>
       <c r="E353">
-        <v>28.21100917431193</v>
+        <v>21.95121951219512</v>
       </c>
       <c r="F353" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="354" spans="1:6">
@@ -7048,16 +7287,16 @@
         <v>86</v>
       </c>
       <c r="C354" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="D354">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="E354">
-        <v>26.8348623853211</v>
+        <v>20.09756097560976</v>
       </c>
       <c r="F354" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="355" spans="1:6">
@@ -7068,16 +7307,16 @@
         <v>86</v>
       </c>
       <c r="C355" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="D355">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="E355">
-        <v>24.31192660550459</v>
+        <v>13.65853658536586</v>
       </c>
       <c r="F355" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -7088,16 +7327,16 @@
         <v>86</v>
       </c>
       <c r="C356" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D356">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E356">
-        <v>20.64220183486239</v>
+        <v>7.902439024390244</v>
       </c>
       <c r="F356" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -7105,19 +7344,19 @@
         <v>2025</v>
       </c>
       <c r="B358" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C358" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="D358">
-        <v>195</v>
+        <v>6552</v>
       </c>
       <c r="E358">
-        <v>45.03464203233256</v>
+        <v>47.15704620699582</v>
       </c>
       <c r="F358" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
     </row>
     <row r="359" spans="1:6">
@@ -7125,19 +7364,19 @@
         <v>2025</v>
       </c>
       <c r="B359" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C359" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="D359">
-        <v>162</v>
+        <v>4724</v>
       </c>
       <c r="E359">
-        <v>37.41339491916859</v>
+        <v>34.00028789405498</v>
       </c>
       <c r="F359" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -7145,19 +7384,19 @@
         <v>2025</v>
       </c>
       <c r="B360" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C360" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="D360">
-        <v>76</v>
+        <v>2618</v>
       </c>
       <c r="E360">
-        <v>17.55196304849884</v>
+        <v>18.84266589894919</v>
       </c>
       <c r="F360" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -7165,19 +7404,19 @@
         <v>2025</v>
       </c>
       <c r="B362" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C362" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D362">
-        <v>315</v>
+        <v>5832</v>
       </c>
       <c r="E362">
-        <v>43.09165526675787</v>
+        <v>37.28423475258919</v>
       </c>
       <c r="F362" t="s">
-        <v>335</v>
+        <v>402</v>
       </c>
     </row>
     <row r="363" spans="1:6">
@@ -7185,19 +7424,19 @@
         <v>2025</v>
       </c>
       <c r="B363" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C363" t="s">
-        <v>328</v>
+        <v>267</v>
       </c>
       <c r="D363">
-        <v>247</v>
+        <v>4950</v>
       </c>
       <c r="E363">
-        <v>33.78932968536252</v>
+        <v>31.64556962025317</v>
       </c>
       <c r="F363" t="s">
-        <v>335</v>
+        <v>402</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -7205,19 +7444,1179 @@
         <v>2025</v>
       </c>
       <c r="B364" t="s">
+        <v>87</v>
+      </c>
+      <c r="C364" t="s">
+        <v>345</v>
+      </c>
+      <c r="D364">
+        <v>4834</v>
+      </c>
+      <c r="E364">
+        <v>30.90397647359673</v>
+      </c>
+      <c r="F364" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366">
+        <v>2025</v>
+      </c>
+      <c r="B366" t="s">
         <v>88</v>
       </c>
-      <c r="C364" t="s">
-        <v>329</v>
-      </c>
-      <c r="D364">
+      <c r="C366" t="s">
+        <v>346</v>
+      </c>
+      <c r="D366">
+        <v>9318</v>
+      </c>
+      <c r="E366">
+        <v>41.92764578833693</v>
+      </c>
+      <c r="F366" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367">
+        <v>2025</v>
+      </c>
+      <c r="B367" t="s">
+        <v>88</v>
+      </c>
+      <c r="C367" t="s">
+        <v>347</v>
+      </c>
+      <c r="D367">
+        <v>8700</v>
+      </c>
+      <c r="E367">
+        <v>39.14686825053996</v>
+      </c>
+      <c r="F367" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368">
+        <v>2025</v>
+      </c>
+      <c r="B368" t="s">
+        <v>88</v>
+      </c>
+      <c r="C368" t="s">
+        <v>348</v>
+      </c>
+      <c r="D368">
+        <v>4206</v>
+      </c>
+      <c r="E368">
+        <v>18.92548596112311</v>
+      </c>
+      <c r="F368" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370">
+        <v>2025</v>
+      </c>
+      <c r="B370" t="s">
+        <v>89</v>
+      </c>
+      <c r="C370" t="s">
+        <v>349</v>
+      </c>
+      <c r="D370">
+        <v>193</v>
+      </c>
+      <c r="E370">
+        <v>44.36781609195402</v>
+      </c>
+      <c r="F370" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371">
+        <v>2025</v>
+      </c>
+      <c r="B371" t="s">
+        <v>89</v>
+      </c>
+      <c r="C371" t="s">
+        <v>350</v>
+      </c>
+      <c r="D371">
+        <v>161</v>
+      </c>
+      <c r="E371">
+        <v>37.01149425287356</v>
+      </c>
+      <c r="F371" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372">
+        <v>2025</v>
+      </c>
+      <c r="B372" t="s">
+        <v>89</v>
+      </c>
+      <c r="C372" t="s">
+        <v>351</v>
+      </c>
+      <c r="D372">
+        <v>81</v>
+      </c>
+      <c r="E372">
+        <v>18.62068965517242</v>
+      </c>
+      <c r="F372" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374">
+        <v>2025</v>
+      </c>
+      <c r="B374" t="s">
+        <v>90</v>
+      </c>
+      <c r="C374" t="s">
+        <v>352</v>
+      </c>
+      <c r="D374">
+        <v>1473</v>
+      </c>
+      <c r="E374">
+        <v>39.30096051227321</v>
+      </c>
+      <c r="F374" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375">
+        <v>2025</v>
+      </c>
+      <c r="B375" t="s">
+        <v>90</v>
+      </c>
+      <c r="C375" t="s">
+        <v>353</v>
+      </c>
+      <c r="D375">
+        <v>1297</v>
+      </c>
+      <c r="E375">
+        <v>34.6051227321238</v>
+      </c>
+      <c r="F375" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376">
+        <v>2025</v>
+      </c>
+      <c r="B376" t="s">
+        <v>90</v>
+      </c>
+      <c r="C376" t="s">
+        <v>354</v>
+      </c>
+      <c r="D376">
+        <v>516</v>
+      </c>
+      <c r="E376">
+        <v>13.76734258271078</v>
+      </c>
+      <c r="F376" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377">
+        <v>2025</v>
+      </c>
+      <c r="B377" t="s">
+        <v>90</v>
+      </c>
+      <c r="C377" t="s">
+        <v>355</v>
+      </c>
+      <c r="D377">
+        <v>305</v>
+      </c>
+      <c r="E377">
+        <v>8.137673425827108</v>
+      </c>
+      <c r="F377" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378">
+        <v>2025</v>
+      </c>
+      <c r="B378" t="s">
+        <v>90</v>
+      </c>
+      <c r="C378" t="s">
+        <v>356</v>
+      </c>
+      <c r="D378">
+        <v>157</v>
+      </c>
+      <c r="E378">
+        <v>4.188900747065102</v>
+      </c>
+      <c r="F378" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380">
+        <v>2025</v>
+      </c>
+      <c r="B380" t="s">
+        <v>91</v>
+      </c>
+      <c r="C380" t="s">
+        <v>357</v>
+      </c>
+      <c r="D380">
+        <v>854</v>
+      </c>
+      <c r="E380">
+        <v>47.52365052865888</v>
+      </c>
+      <c r="F380" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381">
+        <v>2025</v>
+      </c>
+      <c r="B381" t="s">
+        <v>91</v>
+      </c>
+      <c r="C381" t="s">
+        <v>358</v>
+      </c>
+      <c r="D381">
+        <v>764</v>
+      </c>
+      <c r="E381">
+        <v>42.51530328324986</v>
+      </c>
+      <c r="F381" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382">
+        <v>2025</v>
+      </c>
+      <c r="B382" t="s">
+        <v>91</v>
+      </c>
+      <c r="C382" t="s">
+        <v>359</v>
+      </c>
+      <c r="D382">
+        <v>175</v>
+      </c>
+      <c r="E382">
+        <v>9.738452977184195</v>
+      </c>
+      <c r="F382" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384">
+        <v>2025</v>
+      </c>
+      <c r="B384" t="s">
+        <v>92</v>
+      </c>
+      <c r="C384" t="s">
+        <v>360</v>
+      </c>
+      <c r="D384">
+        <v>162</v>
+      </c>
+      <c r="E384">
+        <v>45.2513966480447</v>
+      </c>
+      <c r="F384" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385">
+        <v>2025</v>
+      </c>
+      <c r="B385" t="s">
+        <v>92</v>
+      </c>
+      <c r="C385" t="s">
+        <v>361</v>
+      </c>
+      <c r="D385">
+        <v>156</v>
+      </c>
+      <c r="E385">
+        <v>43.5754189944134</v>
+      </c>
+      <c r="F385" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
+      <c r="A386">
+        <v>2025</v>
+      </c>
+      <c r="B386" t="s">
+        <v>92</v>
+      </c>
+      <c r="C386" t="s">
+        <v>362</v>
+      </c>
+      <c r="D386">
+        <v>40</v>
+      </c>
+      <c r="E386">
+        <v>11.1731843575419</v>
+      </c>
+      <c r="F386" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6">
+      <c r="A388">
+        <v>2025</v>
+      </c>
+      <c r="B388" t="s">
+        <v>93</v>
+      </c>
+      <c r="C388" t="s">
+        <v>117</v>
+      </c>
+      <c r="D388">
+        <v>11367</v>
+      </c>
+      <c r="E388">
+        <v>45.69280861840254</v>
+      </c>
+      <c r="F388" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
+      <c r="A389">
+        <v>2025</v>
+      </c>
+      <c r="B389" t="s">
+        <v>93</v>
+      </c>
+      <c r="C389" t="s">
+        <v>116</v>
+      </c>
+      <c r="D389">
+        <v>8188</v>
+      </c>
+      <c r="E389">
+        <v>32.91393656791413</v>
+      </c>
+      <c r="F389" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
+      <c r="A390">
+        <v>2025</v>
+      </c>
+      <c r="B390" t="s">
+        <v>93</v>
+      </c>
+      <c r="C390" t="s">
+        <v>119</v>
+      </c>
+      <c r="D390">
+        <v>5322</v>
+      </c>
+      <c r="E390">
+        <v>21.39325481368332</v>
+      </c>
+      <c r="F390" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6">
+      <c r="A392">
+        <v>2025</v>
+      </c>
+      <c r="B392" t="s">
+        <v>94</v>
+      </c>
+      <c r="C392" t="s">
+        <v>291</v>
+      </c>
+      <c r="D392">
+        <v>287</v>
+      </c>
+      <c r="E392">
+        <v>47.83333333333334</v>
+      </c>
+      <c r="F392" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6">
+      <c r="A393">
+        <v>2025</v>
+      </c>
+      <c r="B393" t="s">
+        <v>94</v>
+      </c>
+      <c r="C393" t="s">
+        <v>363</v>
+      </c>
+      <c r="D393">
+        <v>175</v>
+      </c>
+      <c r="E393">
+        <v>29.16666666666667</v>
+      </c>
+      <c r="F393" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6">
+      <c r="A394">
+        <v>2025</v>
+      </c>
+      <c r="B394" t="s">
+        <v>94</v>
+      </c>
+      <c r="C394" t="s">
+        <v>364</v>
+      </c>
+      <c r="D394">
+        <v>138</v>
+      </c>
+      <c r="E394">
+        <v>23</v>
+      </c>
+      <c r="F394" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6">
+      <c r="A396">
+        <v>2025</v>
+      </c>
+      <c r="B396" t="s">
+        <v>95</v>
+      </c>
+      <c r="C396" t="s">
+        <v>365</v>
+      </c>
+      <c r="D396">
+        <v>253</v>
+      </c>
+      <c r="E396">
+        <v>45.50359712230216</v>
+      </c>
+      <c r="F396" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6">
+      <c r="A397">
+        <v>2025</v>
+      </c>
+      <c r="B397" t="s">
+        <v>95</v>
+      </c>
+      <c r="C397" t="s">
+        <v>366</v>
+      </c>
+      <c r="D397">
+        <v>154</v>
+      </c>
+      <c r="E397">
+        <v>27.69784172661871</v>
+      </c>
+      <c r="F397" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6">
+      <c r="A398">
+        <v>2025</v>
+      </c>
+      <c r="B398" t="s">
+        <v>95</v>
+      </c>
+      <c r="C398" t="s">
+        <v>367</v>
+      </c>
+      <c r="D398">
+        <v>149</v>
+      </c>
+      <c r="E398">
+        <v>26.79856115107914</v>
+      </c>
+      <c r="F398" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6">
+      <c r="A400">
+        <v>2025</v>
+      </c>
+      <c r="B400" t="s">
+        <v>96</v>
+      </c>
+      <c r="C400" t="s">
+        <v>368</v>
+      </c>
+      <c r="D400">
+        <v>163</v>
+      </c>
+      <c r="E400">
+        <v>38.71733966745843</v>
+      </c>
+      <c r="F400" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6">
+      <c r="A401">
+        <v>2025</v>
+      </c>
+      <c r="B401" t="s">
+        <v>96</v>
+      </c>
+      <c r="C401" t="s">
+        <v>369</v>
+      </c>
+      <c r="D401">
+        <v>160</v>
+      </c>
+      <c r="E401">
+        <v>38.00475059382423</v>
+      </c>
+      <c r="F401" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6">
+      <c r="A402">
+        <v>2025</v>
+      </c>
+      <c r="B402" t="s">
+        <v>96</v>
+      </c>
+      <c r="C402" t="s">
+        <v>370</v>
+      </c>
+      <c r="D402">
+        <v>75</v>
+      </c>
+      <c r="E402">
+        <v>17.81472684085511</v>
+      </c>
+      <c r="F402" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6">
+      <c r="A403">
+        <v>2025</v>
+      </c>
+      <c r="B403" t="s">
+        <v>96</v>
+      </c>
+      <c r="C403" t="s">
+        <v>371</v>
+      </c>
+      <c r="D403">
+        <v>23</v>
+      </c>
+      <c r="E403">
+        <v>5.463182897862233</v>
+      </c>
+      <c r="F403" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6">
+      <c r="A405">
+        <v>2025</v>
+      </c>
+      <c r="B405" t="s">
+        <v>97</v>
+      </c>
+      <c r="C405" t="s">
+        <v>372</v>
+      </c>
+      <c r="D405">
+        <v>104</v>
+      </c>
+      <c r="E405">
+        <v>35.37414965986395</v>
+      </c>
+      <c r="F405" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6">
+      <c r="A406">
+        <v>2025</v>
+      </c>
+      <c r="B406" t="s">
+        <v>97</v>
+      </c>
+      <c r="C406" t="s">
+        <v>373</v>
+      </c>
+      <c r="D406">
+        <v>79</v>
+      </c>
+      <c r="E406">
+        <v>26.87074829931973</v>
+      </c>
+      <c r="F406" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6">
+      <c r="A407">
+        <v>2025</v>
+      </c>
+      <c r="B407" t="s">
+        <v>97</v>
+      </c>
+      <c r="C407" t="s">
+        <v>374</v>
+      </c>
+      <c r="D407">
+        <v>78</v>
+      </c>
+      <c r="E407">
+        <v>26.53061224489796</v>
+      </c>
+      <c r="F407" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6">
+      <c r="A408">
+        <v>2025</v>
+      </c>
+      <c r="B408" t="s">
+        <v>97</v>
+      </c>
+      <c r="C408" t="s">
+        <v>375</v>
+      </c>
+      <c r="D408">
+        <v>32</v>
+      </c>
+      <c r="E408">
+        <v>10.8843537414966</v>
+      </c>
+      <c r="F408" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6">
+      <c r="A410">
+        <v>2025</v>
+      </c>
+      <c r="B410" t="s">
+        <v>98</v>
+      </c>
+      <c r="C410" t="s">
+        <v>376</v>
+      </c>
+      <c r="D410">
+        <v>549</v>
+      </c>
+      <c r="E410">
+        <v>42.99138606108065</v>
+      </c>
+      <c r="F410" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6">
+      <c r="A411">
+        <v>2025</v>
+      </c>
+      <c r="B411" t="s">
+        <v>98</v>
+      </c>
+      <c r="C411" t="s">
+        <v>377</v>
+      </c>
+      <c r="D411">
+        <v>445</v>
+      </c>
+      <c r="E411">
+        <v>34.84729835552075</v>
+      </c>
+      <c r="F411" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6">
+      <c r="A412">
+        <v>2025</v>
+      </c>
+      <c r="B412" t="s">
+        <v>98</v>
+      </c>
+      <c r="C412" t="s">
+        <v>378</v>
+      </c>
+      <c r="D412">
+        <v>283</v>
+      </c>
+      <c r="E412">
+        <v>22.16131558339859</v>
+      </c>
+      <c r="F412" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6">
+      <c r="A414">
+        <v>2025</v>
+      </c>
+      <c r="B414" t="s">
+        <v>99</v>
+      </c>
+      <c r="C414" t="s">
+        <v>379</v>
+      </c>
+      <c r="D414">
+        <v>123</v>
+      </c>
+      <c r="E414">
+        <v>28.21100917431193</v>
+      </c>
+      <c r="F414" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6">
+      <c r="A415">
+        <v>2025</v>
+      </c>
+      <c r="B415" t="s">
+        <v>99</v>
+      </c>
+      <c r="C415" t="s">
+        <v>380</v>
+      </c>
+      <c r="D415">
+        <v>117</v>
+      </c>
+      <c r="E415">
+        <v>26.8348623853211</v>
+      </c>
+      <c r="F415" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6">
+      <c r="A416">
+        <v>2025</v>
+      </c>
+      <c r="B416" t="s">
+        <v>99</v>
+      </c>
+      <c r="C416" t="s">
+        <v>381</v>
+      </c>
+      <c r="D416">
+        <v>106</v>
+      </c>
+      <c r="E416">
+        <v>24.31192660550459</v>
+      </c>
+      <c r="F416" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6">
+      <c r="A417">
+        <v>2025</v>
+      </c>
+      <c r="B417" t="s">
+        <v>99</v>
+      </c>
+      <c r="C417" t="s">
+        <v>382</v>
+      </c>
+      <c r="D417">
+        <v>90</v>
+      </c>
+      <c r="E417">
+        <v>20.64220183486239</v>
+      </c>
+      <c r="F417" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6">
+      <c r="A419">
+        <v>2025</v>
+      </c>
+      <c r="B419" t="s">
+        <v>100</v>
+      </c>
+      <c r="C419" t="s">
+        <v>383</v>
+      </c>
+      <c r="D419">
+        <v>195</v>
+      </c>
+      <c r="E419">
+        <v>45.03464203233256</v>
+      </c>
+      <c r="F419" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6">
+      <c r="A420">
+        <v>2025</v>
+      </c>
+      <c r="B420" t="s">
+        <v>100</v>
+      </c>
+      <c r="C420" t="s">
+        <v>384</v>
+      </c>
+      <c r="D420">
+        <v>162</v>
+      </c>
+      <c r="E420">
+        <v>37.41339491916859</v>
+      </c>
+      <c r="F420" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
+      <c r="A421">
+        <v>2025</v>
+      </c>
+      <c r="B421" t="s">
+        <v>100</v>
+      </c>
+      <c r="C421" t="s">
+        <v>385</v>
+      </c>
+      <c r="D421">
+        <v>76</v>
+      </c>
+      <c r="E421">
+        <v>17.55196304849884</v>
+      </c>
+      <c r="F421" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6">
+      <c r="A423">
+        <v>2025</v>
+      </c>
+      <c r="B423" t="s">
+        <v>101</v>
+      </c>
+      <c r="C423" t="s">
+        <v>386</v>
+      </c>
+      <c r="D423">
+        <v>315</v>
+      </c>
+      <c r="E423">
+        <v>43.09165526675787</v>
+      </c>
+      <c r="F423" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6">
+      <c r="A424">
+        <v>2025</v>
+      </c>
+      <c r="B424" t="s">
+        <v>101</v>
+      </c>
+      <c r="C424" t="s">
+        <v>387</v>
+      </c>
+      <c r="D424">
+        <v>247</v>
+      </c>
+      <c r="E424">
+        <v>33.78932968536252</v>
+      </c>
+      <c r="F424" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6">
+      <c r="A425">
+        <v>2025</v>
+      </c>
+      <c r="B425" t="s">
+        <v>101</v>
+      </c>
+      <c r="C425" t="s">
+        <v>388</v>
+      </c>
+      <c r="D425">
         <v>169</v>
       </c>
-      <c r="E364">
+      <c r="E425">
         <v>23.11901504787962</v>
       </c>
-      <c r="F364" t="s">
-        <v>335</v>
+      <c r="F425" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6">
+      <c r="A427">
+        <v>2025</v>
+      </c>
+      <c r="B427" t="s">
+        <v>102</v>
+      </c>
+      <c r="C427" t="s">
+        <v>389</v>
+      </c>
+      <c r="D427">
+        <v>3982</v>
+      </c>
+      <c r="E427">
+        <v>29.84112709832134</v>
+      </c>
+      <c r="F427" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6">
+      <c r="A428">
+        <v>2025</v>
+      </c>
+      <c r="B428" t="s">
+        <v>102</v>
+      </c>
+      <c r="C428" t="s">
+        <v>390</v>
+      </c>
+      <c r="D428">
+        <v>3532</v>
+      </c>
+      <c r="E428">
+        <v>26.46882494004796</v>
+      </c>
+      <c r="F428" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6">
+      <c r="A429">
+        <v>2025</v>
+      </c>
+      <c r="B429" t="s">
+        <v>102</v>
+      </c>
+      <c r="C429" t="s">
+        <v>391</v>
+      </c>
+      <c r="D429">
+        <v>2933</v>
+      </c>
+      <c r="E429">
+        <v>21.97991606714628</v>
+      </c>
+      <c r="F429" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
+      <c r="A430">
+        <v>2025</v>
+      </c>
+      <c r="B430" t="s">
+        <v>102</v>
+      </c>
+      <c r="C430" t="s">
+        <v>392</v>
+      </c>
+      <c r="D430">
+        <v>2897</v>
+      </c>
+      <c r="E430">
+        <v>21.71013189448441</v>
+      </c>
+      <c r="F430" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6">
+      <c r="A432">
+        <v>2025</v>
+      </c>
+      <c r="B432" t="s">
+        <v>103</v>
+      </c>
+      <c r="C432" t="s">
+        <v>393</v>
+      </c>
+      <c r="D432">
+        <v>155</v>
+      </c>
+      <c r="E432">
+        <v>39.84575835475578</v>
+      </c>
+      <c r="F432" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6">
+      <c r="A433">
+        <v>2025</v>
+      </c>
+      <c r="B433" t="s">
+        <v>103</v>
+      </c>
+      <c r="C433" t="s">
+        <v>394</v>
+      </c>
+      <c r="D433">
+        <v>149</v>
+      </c>
+      <c r="E433">
+        <v>38.30334190231363</v>
+      </c>
+      <c r="F433" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6">
+      <c r="A434">
+        <v>2025</v>
+      </c>
+      <c r="B434" t="s">
+        <v>103</v>
+      </c>
+      <c r="C434" t="s">
+        <v>395</v>
+      </c>
+      <c r="D434">
+        <v>85</v>
+      </c>
+      <c r="E434">
+        <v>21.85089974293059</v>
+      </c>
+      <c r="F434" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6">
+      <c r="A436">
+        <v>2025</v>
+      </c>
+      <c r="B436" t="s">
+        <v>104</v>
+      </c>
+      <c r="C436" t="s">
+        <v>396</v>
+      </c>
+      <c r="D436">
+        <v>328</v>
+      </c>
+      <c r="E436">
+        <v>37.27272727272727</v>
+      </c>
+      <c r="F436" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6">
+      <c r="A437">
+        <v>2025</v>
+      </c>
+      <c r="B437" t="s">
+        <v>104</v>
+      </c>
+      <c r="C437" t="s">
+        <v>397</v>
+      </c>
+      <c r="D437">
+        <v>310</v>
+      </c>
+      <c r="E437">
+        <v>35.22727272727273</v>
+      </c>
+      <c r="F437" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6">
+      <c r="A438">
+        <v>2025</v>
+      </c>
+      <c r="B438" t="s">
+        <v>104</v>
+      </c>
+      <c r="C438" t="s">
+        <v>398</v>
+      </c>
+      <c r="D438">
+        <v>127</v>
+      </c>
+      <c r="E438">
+        <v>14.43181818181818</v>
+      </c>
+      <c r="F438" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6">
+      <c r="A439">
+        <v>2025</v>
+      </c>
+      <c r="B439" t="s">
+        <v>104</v>
+      </c>
+      <c r="C439" t="s">
+        <v>399</v>
+      </c>
+      <c r="D439">
+        <v>115</v>
+      </c>
+      <c r="E439">
+        <v>13.06818181818182</v>
+      </c>
+      <c r="F439" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="431">
   <si>
     <t>Year</t>
   </si>
@@ -251,6 +251,9 @@
     <t>REP Supervisor Robeson Twp</t>
   </si>
   <si>
+    <t>REP Township Supervisor FRANKLIN TOWNSHIP</t>
+  </si>
+  <si>
     <t>REP Township Supervisor for Newberry Township</t>
   </si>
   <si>
@@ -272,6 +275,9 @@
     <t>DEM MAGISTERIAL DISTRICT JUDGE 03-3-02</t>
   </si>
   <si>
+    <t>REP COUNTY CORONER</t>
+  </si>
+  <si>
     <t>REP Codorus Township Supervisor-REP</t>
   </si>
   <si>
@@ -308,6 +314,9 @@
     <t>REP TAX COLLECTOR CENTER TOWNSHIP</t>
   </si>
   <si>
+    <t>REP TAX COLLECTOR OAKLAND TWP</t>
+  </si>
+  <si>
     <t>REP Township Supervisor (6 Year Term) Foster Twp</t>
   </si>
   <si>
@@ -944,6 +953,15 @@
     <t>GALEN BROWN</t>
   </si>
   <si>
+    <t>JOE SCHUBERT</t>
+  </si>
+  <si>
+    <t>MARK THOMAS</t>
+  </si>
+  <si>
+    <t>ROBERT THOMPSON</t>
+  </si>
+  <si>
     <t>AARON SCHWARTZ</t>
   </si>
   <si>
@@ -1016,6 +1034,15 @@
     <t>ROBERT KEMMERER</t>
   </si>
   <si>
+    <t>KORYNNE YOUNG</t>
+  </si>
+  <si>
+    <t>JOHN HANOVICK</t>
+  </si>
+  <si>
+    <t>BRADEN FOX</t>
+  </si>
+  <si>
     <t>JASON GROSS</t>
   </si>
   <si>
@@ -1133,6 +1160,15 @@
     <t>JENNIFER SHAFFOR</t>
   </si>
   <si>
+    <t>MARY ELLEN SANKO</t>
+  </si>
+  <si>
+    <t>SARAH FILGES</t>
+  </si>
+  <si>
+    <t>KATHLEEN BAUER</t>
+  </si>
+  <si>
     <t>JOHN PAVUK</t>
   </si>
   <si>
@@ -1266,6 +1302,9 @@
   </si>
   <si>
     <t>Lycoming County (Williamsport + boroughs + townships)</t>
+  </si>
+  <si>
+    <t>Butler County (Butler City + boroughs + townships)</t>
   </si>
   <si>
     <t>Indiana County (Indiana + boroughs + townships)</t>
@@ -1716,7 +1755,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F439"/>
+  <dimension ref="A1:F451"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1747,7 +1786,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D2">
         <v>799</v>
@@ -1756,7 +1795,7 @@
         <v>35.94242015294647</v>
       </c>
       <c r="F2" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1767,7 +1806,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D3">
         <v>713</v>
@@ -1776,7 +1815,7 @@
         <v>32.07377417903734</v>
       </c>
       <c r="F3" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1787,7 +1826,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>355</v>
@@ -1796,7 +1835,7 @@
         <v>15.96941070625281</v>
       </c>
       <c r="F4" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1807,7 +1846,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D5">
         <v>190</v>
@@ -1816,7 +1855,7 @@
         <v>8.547008547008547</v>
       </c>
       <c r="F5" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1827,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D6">
         <v>166</v>
@@ -1836,7 +1875,7 @@
         <v>7.467386414754835</v>
       </c>
       <c r="F6" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1847,7 +1886,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D8">
         <v>807</v>
@@ -1856,7 +1895,7 @@
         <v>42.87991498405951</v>
       </c>
       <c r="F8" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1867,7 +1906,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D9">
         <v>704</v>
@@ -1876,7 +1915,7 @@
         <v>37.40701381509033</v>
       </c>
       <c r="F9" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1887,7 +1926,7 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D10">
         <v>371</v>
@@ -1896,7 +1935,7 @@
         <v>19.71307120085016</v>
       </c>
       <c r="F10" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1907,7 +1946,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12">
         <v>23009</v>
@@ -1916,7 +1955,7 @@
         <v>49.36282502359907</v>
       </c>
       <c r="F12" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1927,7 +1966,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D13">
         <v>10398</v>
@@ -1936,7 +1975,7 @@
         <v>22.30756028490518</v>
       </c>
       <c r="F13" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1947,7 +1986,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D14">
         <v>6676</v>
@@ -1956,7 +1995,7 @@
         <v>14.32249206212992</v>
       </c>
       <c r="F14" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1967,7 +2006,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D15">
         <v>6529</v>
@@ -1976,7 +2015,7 @@
         <v>14.00712262936583</v>
       </c>
       <c r="F15" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1987,7 +2026,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D17">
         <v>15761</v>
@@ -1996,7 +2035,7 @@
         <v>32.71613907628438</v>
       </c>
       <c r="F17" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2007,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D18">
         <v>12780</v>
@@ -2016,7 +2055,7 @@
         <v>26.52828230409964</v>
       </c>
       <c r="F18" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2027,7 +2066,7 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D19">
         <v>10691</v>
@@ -2036,7 +2075,7 @@
         <v>22.19200830306175</v>
       </c>
       <c r="F19" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2047,7 +2086,7 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D20">
         <v>8943</v>
@@ -2056,7 +2095,7 @@
         <v>18.56357031655423</v>
       </c>
       <c r="F20" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2067,7 +2106,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D22">
         <v>133</v>
@@ -2076,7 +2115,7 @@
         <v>41.95583596214511</v>
       </c>
       <c r="F22" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2087,7 +2126,7 @@
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D23">
         <v>121</v>
@@ -2096,7 +2135,7 @@
         <v>38.17034700315457</v>
       </c>
       <c r="F23" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2107,7 +2146,7 @@
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D24">
         <v>63</v>
@@ -2116,7 +2155,7 @@
         <v>19.87381703470032</v>
       </c>
       <c r="F24" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2127,7 +2166,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D26">
         <v>22897</v>
@@ -2136,7 +2175,7 @@
         <v>47.76078930351891</v>
       </c>
       <c r="F26" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2147,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D27">
         <v>8137</v>
@@ -2156,7 +2195,7 @@
         <v>16.97294591268434</v>
       </c>
       <c r="F27" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2167,7 +2206,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D28">
         <v>7234</v>
@@ -2176,7 +2215,7 @@
         <v>15.08938069710686</v>
       </c>
       <c r="F28" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2187,7 +2226,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D29">
         <v>5373</v>
@@ -2196,7 +2235,7 @@
         <v>11.20752591727332</v>
       </c>
       <c r="F29" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2207,7 +2246,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D30">
         <v>4300</v>
@@ -2216,7 +2255,7 @@
         <v>8.969358169416575</v>
       </c>
       <c r="F30" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2227,7 +2266,7 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D32">
         <v>364</v>
@@ -2236,7 +2275,7 @@
         <v>39.09774436090225</v>
       </c>
       <c r="F32" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2247,7 +2286,7 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D33">
         <v>341</v>
@@ -2256,7 +2295,7 @@
         <v>36.62728249194414</v>
       </c>
       <c r="F33" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2267,7 +2306,7 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D34">
         <v>226</v>
@@ -2276,7 +2315,7 @@
         <v>24.2749731471536</v>
       </c>
       <c r="F34" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2287,7 +2326,7 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D36">
         <v>1283</v>
@@ -2296,7 +2335,7 @@
         <v>40.52432090966519</v>
       </c>
       <c r="F36" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2307,7 +2346,7 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D37">
         <v>954</v>
@@ -2316,7 +2355,7 @@
         <v>30.13265950726469</v>
       </c>
       <c r="F37" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2327,7 +2366,7 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D38">
         <v>746</v>
@@ -2336,7 +2375,7 @@
         <v>23.56285533796589</v>
       </c>
       <c r="F38" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2347,7 +2386,7 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D39">
         <v>183</v>
@@ -2356,7 +2395,7 @@
         <v>5.780164245104232</v>
       </c>
       <c r="F39" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2367,7 +2406,7 @@
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D41">
         <v>1446</v>
@@ -2376,7 +2415,7 @@
         <v>41.84027777777778</v>
       </c>
       <c r="F41" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2387,7 +2426,7 @@
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D42">
         <v>1091</v>
@@ -2396,7 +2435,7 @@
         <v>31.56828703703703</v>
       </c>
       <c r="F42" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2407,7 +2446,7 @@
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D43">
         <v>919</v>
@@ -2416,7 +2455,7 @@
         <v>26.59143518518519</v>
       </c>
       <c r="F43" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2427,7 +2466,7 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D45">
         <v>8769</v>
@@ -2436,7 +2475,7 @@
         <v>32.16683173764719</v>
       </c>
       <c r="F45" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2447,7 +2486,7 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D46">
         <v>8551</v>
@@ -2456,7 +2495,7 @@
         <v>31.36715454312021</v>
       </c>
       <c r="F46" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2467,7 +2506,7 @@
         <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D47">
         <v>5669</v>
@@ -2476,7 +2515,7 @@
         <v>20.79527530171307</v>
       </c>
       <c r="F47" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2487,7 +2526,7 @@
         <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D48">
         <v>4272</v>
@@ -2496,7 +2535,7 @@
         <v>15.67073841751953</v>
       </c>
       <c r="F48" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2507,7 +2546,7 @@
         <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D50">
         <v>3420</v>
@@ -2516,7 +2555,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F50" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2527,7 +2566,7 @@
         <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D51">
         <v>2391</v>
@@ -2536,7 +2575,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F51" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2547,7 +2586,7 @@
         <v>21</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D52">
         <v>2184</v>
@@ -2556,7 +2595,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F52" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2567,7 +2606,7 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D54">
         <v>572</v>
@@ -2576,7 +2615,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F54" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2587,7 +2626,7 @@
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D55">
         <v>380</v>
@@ -2596,7 +2635,7 @@
         <v>31.25</v>
       </c>
       <c r="F55" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2607,7 +2646,7 @@
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D56">
         <v>264</v>
@@ -2616,7 +2655,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F56" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2627,7 +2666,7 @@
         <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D58">
         <v>177</v>
@@ -2636,7 +2675,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F58" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2647,7 +2686,7 @@
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D59">
         <v>141</v>
@@ -2656,7 +2695,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F59" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2667,7 +2706,7 @@
         <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D60">
         <v>81</v>
@@ -2676,7 +2715,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F60" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2687,7 +2726,7 @@
         <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D61">
         <v>44</v>
@@ -2696,7 +2735,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F61" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2707,7 +2746,7 @@
         <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D63">
         <v>1471</v>
@@ -2716,7 +2755,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F63" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2727,7 +2766,7 @@
         <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D64">
         <v>1247</v>
@@ -2736,7 +2775,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F64" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2747,7 +2786,7 @@
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D65">
         <v>616</v>
@@ -2756,7 +2795,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F65" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2767,7 +2806,7 @@
         <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D67">
         <v>1183</v>
@@ -2776,7 +2815,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F67" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2787,7 +2826,7 @@
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D68">
         <v>1177</v>
@@ -2796,7 +2835,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F68" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2807,7 +2846,7 @@
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D69">
         <v>373</v>
@@ -2816,7 +2855,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F69" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2827,7 +2866,7 @@
         <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D70">
         <v>270</v>
@@ -2836,7 +2875,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F70" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2847,7 +2886,7 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D72">
         <v>2064</v>
@@ -2856,7 +2895,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F72" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2867,7 +2906,7 @@
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D73">
         <v>1942</v>
@@ -2876,7 +2915,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F73" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2887,7 +2926,7 @@
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D74">
         <v>1927</v>
@@ -2896,7 +2935,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F74" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2907,7 +2946,7 @@
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D75">
         <v>1817</v>
@@ -2916,7 +2955,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F75" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2927,7 +2966,7 @@
         <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D77">
         <v>237</v>
@@ -2936,7 +2975,7 @@
         <v>32.20108695652174</v>
       </c>
       <c r="F77" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2947,7 +2986,7 @@
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D78">
         <v>234</v>
@@ -2956,7 +2995,7 @@
         <v>31.79347826086957</v>
       </c>
       <c r="F78" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2967,7 +3006,7 @@
         <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D79">
         <v>148</v>
@@ -2976,7 +3015,7 @@
         <v>20.10869565217391</v>
       </c>
       <c r="F79" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2987,7 +3026,7 @@
         <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D80">
         <v>90</v>
@@ -2996,7 +3035,7 @@
         <v>12.22826086956522</v>
       </c>
       <c r="F80" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3007,7 +3046,7 @@
         <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D81">
         <v>27</v>
@@ -3016,7 +3055,7 @@
         <v>3.668478260869565</v>
       </c>
       <c r="F81" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3027,7 +3066,7 @@
         <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D83">
         <v>212</v>
@@ -3036,7 +3075,7 @@
         <v>40.15151515151515</v>
       </c>
       <c r="F83" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3047,7 +3086,7 @@
         <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D84">
         <v>186</v>
@@ -3056,7 +3095,7 @@
         <v>35.22727272727273</v>
       </c>
       <c r="F84" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3067,7 +3106,7 @@
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D85">
         <v>130</v>
@@ -3076,7 +3115,7 @@
         <v>24.62121212121212</v>
       </c>
       <c r="F85" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3087,7 +3126,7 @@
         <v>29</v>
       </c>
       <c r="C87" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D87">
         <v>149</v>
@@ -3096,7 +3135,7 @@
         <v>44.61077844311377</v>
       </c>
       <c r="F87" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3107,7 +3146,7 @@
         <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D88">
         <v>115</v>
@@ -3116,7 +3155,7 @@
         <v>34.4311377245509</v>
       </c>
       <c r="F88" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3127,7 +3166,7 @@
         <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D89">
         <v>70</v>
@@ -3136,7 +3175,7 @@
         <v>20.95808383233533</v>
       </c>
       <c r="F89" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3147,7 +3186,7 @@
         <v>30</v>
       </c>
       <c r="C91" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D91">
         <v>138</v>
@@ -3156,7 +3195,7 @@
         <v>40.70796460176992</v>
       </c>
       <c r="F91" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3167,7 +3206,7 @@
         <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D92">
         <v>127</v>
@@ -3176,7 +3215,7 @@
         <v>37.46312684365782</v>
       </c>
       <c r="F92" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3187,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="C93" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D93">
         <v>74</v>
@@ -3196,7 +3235,7 @@
         <v>21.82890855457227</v>
       </c>
       <c r="F93" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3207,7 +3246,7 @@
         <v>31</v>
       </c>
       <c r="C95" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D95">
         <v>186</v>
@@ -3216,7 +3255,7 @@
         <v>40</v>
       </c>
       <c r="F95" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3227,7 +3266,7 @@
         <v>31</v>
       </c>
       <c r="C96" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D96">
         <v>96</v>
@@ -3236,7 +3275,7 @@
         <v>20.64516129032258</v>
       </c>
       <c r="F96" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3247,7 +3286,7 @@
         <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D97">
         <v>95</v>
@@ -3256,7 +3295,7 @@
         <v>20.43010752688172</v>
       </c>
       <c r="F97" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3267,7 +3306,7 @@
         <v>31</v>
       </c>
       <c r="C98" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D98">
         <v>88</v>
@@ -3276,7 +3315,7 @@
         <v>18.9247311827957</v>
       </c>
       <c r="F98" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3287,7 +3326,7 @@
         <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D100">
         <v>154</v>
@@ -3296,7 +3335,7 @@
         <v>39.58868894601542</v>
       </c>
       <c r="F100" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3307,7 +3346,7 @@
         <v>32</v>
       </c>
       <c r="C101" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D101">
         <v>144</v>
@@ -3316,7 +3355,7 @@
         <v>37.01799485861182</v>
       </c>
       <c r="F101" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3327,7 +3366,7 @@
         <v>32</v>
       </c>
       <c r="C102" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D102">
         <v>91</v>
@@ -3336,7 +3375,7 @@
         <v>23.39331619537275</v>
       </c>
       <c r="F102" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3347,7 +3386,7 @@
         <v>33</v>
       </c>
       <c r="C104" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D104">
         <v>203</v>
@@ -3356,7 +3395,7 @@
         <v>49.63325183374083</v>
       </c>
       <c r="F104" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3367,7 +3406,7 @@
         <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D105">
         <v>127</v>
@@ -3376,7 +3415,7 @@
         <v>31.05134474327628</v>
       </c>
       <c r="F105" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3387,7 +3426,7 @@
         <v>33</v>
       </c>
       <c r="C106" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D106">
         <v>79</v>
@@ -3396,7 +3435,7 @@
         <v>19.31540342298289</v>
       </c>
       <c r="F106" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3407,7 +3446,7 @@
         <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D108">
         <v>293</v>
@@ -3416,7 +3455,7 @@
         <v>37.80645161290322</v>
       </c>
       <c r="F108" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3427,7 +3466,7 @@
         <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D109">
         <v>241</v>
@@ -3436,7 +3475,7 @@
         <v>31.09677419354839</v>
       </c>
       <c r="F109" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3447,7 +3486,7 @@
         <v>34</v>
       </c>
       <c r="C110" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D110">
         <v>125</v>
@@ -3456,7 +3495,7 @@
         <v>16.12903225806452</v>
       </c>
       <c r="F110" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3467,7 +3506,7 @@
         <v>34</v>
       </c>
       <c r="C111" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D111">
         <v>116</v>
@@ -3476,7 +3515,7 @@
         <v>14.96774193548387</v>
       </c>
       <c r="F111" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3487,7 +3526,7 @@
         <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D113">
         <v>588</v>
@@ -3496,7 +3535,7 @@
         <v>48.83720930232558</v>
       </c>
       <c r="F113" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3507,7 +3546,7 @@
         <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D114">
         <v>379</v>
@@ -3516,7 +3555,7 @@
         <v>31.47840531561462</v>
       </c>
       <c r="F114" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3527,7 +3566,7 @@
         <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D115">
         <v>237</v>
@@ -3536,7 +3575,7 @@
         <v>19.6843853820598</v>
       </c>
       <c r="F115" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3547,7 +3586,7 @@
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D117">
         <v>522</v>
@@ -3556,7 +3595,7 @@
         <v>48.33333333333334</v>
       </c>
       <c r="F117" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3567,7 +3606,7 @@
         <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D118">
         <v>331</v>
@@ -3576,7 +3615,7 @@
         <v>30.64814814814815</v>
       </c>
       <c r="F118" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3587,7 +3626,7 @@
         <v>36</v>
       </c>
       <c r="C119" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D119">
         <v>227</v>
@@ -3596,7 +3635,7 @@
         <v>21.01851851851852</v>
       </c>
       <c r="F119" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3607,7 +3646,7 @@
         <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D121">
         <v>4922</v>
@@ -3616,7 +3655,7 @@
         <v>41.68713475057169</v>
       </c>
       <c r="F121" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3627,7 +3666,7 @@
         <v>37</v>
       </c>
       <c r="C122" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D122">
         <v>4820</v>
@@ -3636,7 +3675,7 @@
         <v>40.82324045058016</v>
       </c>
       <c r="F122" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3647,7 +3686,7 @@
         <v>37</v>
       </c>
       <c r="C123" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D123">
         <v>2065</v>
@@ -3656,7 +3695,7 @@
         <v>17.48962479884814</v>
       </c>
       <c r="F123" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3667,7 +3706,7 @@
         <v>38</v>
       </c>
       <c r="C125" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D125">
         <v>490</v>
@@ -3676,7 +3715,7 @@
         <v>47.43465634075508</v>
       </c>
       <c r="F125" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3687,7 +3726,7 @@
         <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D126">
         <v>274</v>
@@ -3696,7 +3735,7 @@
         <v>26.52468538238141</v>
       </c>
       <c r="F126" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3707,7 +3746,7 @@
         <v>38</v>
       </c>
       <c r="C127" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D127">
         <v>269</v>
@@ -3716,7 +3755,7 @@
         <v>26.0406582768635</v>
       </c>
       <c r="F127" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3727,7 +3766,7 @@
         <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D129">
         <v>1165</v>
@@ -3736,7 +3775,7 @@
         <v>47.31925264012997</v>
       </c>
       <c r="F129" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3747,7 +3786,7 @@
         <v>39</v>
       </c>
       <c r="C130" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D130">
         <v>898</v>
@@ -3756,7 +3795,7 @@
         <v>36.47441104792851</v>
       </c>
       <c r="F130" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3767,7 +3806,7 @@
         <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D131">
         <v>211</v>
@@ -3776,7 +3815,7 @@
         <v>8.570268074735987</v>
       </c>
       <c r="F131" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3787,7 +3826,7 @@
         <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D132">
         <v>188</v>
@@ -3796,7 +3835,7 @@
         <v>7.636068237205524</v>
       </c>
       <c r="F132" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3807,7 +3846,7 @@
         <v>40</v>
       </c>
       <c r="C134" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D134">
         <v>1281</v>
@@ -3816,7 +3855,7 @@
         <v>43.88489208633094</v>
       </c>
       <c r="F134" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3827,7 +3866,7 @@
         <v>40</v>
       </c>
       <c r="C135" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D135">
         <v>924</v>
@@ -3836,7 +3875,7 @@
         <v>31.6546762589928</v>
       </c>
       <c r="F135" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3847,7 +3886,7 @@
         <v>40</v>
       </c>
       <c r="C136" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D136">
         <v>714</v>
@@ -3856,7 +3895,7 @@
         <v>24.46043165467626</v>
       </c>
       <c r="F136" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3867,7 +3906,7 @@
         <v>41</v>
       </c>
       <c r="C138" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D138">
         <v>999</v>
@@ -3876,7 +3915,7 @@
         <v>49.47994056463596</v>
       </c>
       <c r="F138" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3887,7 +3926,7 @@
         <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D139">
         <v>629</v>
@@ -3896,7 +3935,7 @@
         <v>31.15403665180783</v>
       </c>
       <c r="F139" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3907,7 +3946,7 @@
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D140">
         <v>391</v>
@@ -3916,7 +3955,7 @@
         <v>19.36602278355622</v>
       </c>
       <c r="F140" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3927,7 +3966,7 @@
         <v>42</v>
       </c>
       <c r="C142" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D142">
         <v>1779</v>
@@ -3936,7 +3975,7 @@
         <v>46.82811266122664</v>
       </c>
       <c r="F142" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3947,7 +3986,7 @@
         <v>42</v>
       </c>
       <c r="C143" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D143">
         <v>1349</v>
@@ -3956,7 +3995,7 @@
         <v>35.50934456435904</v>
       </c>
       <c r="F143" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3967,7 +4006,7 @@
         <v>42</v>
       </c>
       <c r="C144" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D144">
         <v>671</v>
@@ -3976,7 +4015,7 @@
         <v>17.66254277441432</v>
       </c>
       <c r="F144" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3987,7 +4026,7 @@
         <v>43</v>
       </c>
       <c r="C146" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D146">
         <v>253</v>
@@ -3996,7 +4035,7 @@
         <v>37.09677419354838</v>
       </c>
       <c r="F146" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4007,7 +4046,7 @@
         <v>43</v>
       </c>
       <c r="C147" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D147">
         <v>224</v>
@@ -4016,7 +4055,7 @@
         <v>32.84457478005865</v>
       </c>
       <c r="F147" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4027,7 +4066,7 @@
         <v>43</v>
       </c>
       <c r="C148" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D148">
         <v>122</v>
@@ -4036,7 +4075,7 @@
         <v>17.88856304985337</v>
       </c>
       <c r="F148" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4047,7 +4086,7 @@
         <v>43</v>
       </c>
       <c r="C149" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D149">
         <v>60</v>
@@ -4056,7 +4095,7 @@
         <v>8.797653958944283</v>
       </c>
       <c r="F149" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4067,7 +4106,7 @@
         <v>43</v>
       </c>
       <c r="C150" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D150">
         <v>23</v>
@@ -4076,7 +4115,7 @@
         <v>3.372434017595308</v>
       </c>
       <c r="F150" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4087,7 +4126,7 @@
         <v>44</v>
       </c>
       <c r="C152" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D152">
         <v>917</v>
@@ -4096,7 +4135,7 @@
         <v>36.31683168316832</v>
       </c>
       <c r="F152" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4107,7 +4146,7 @@
         <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D153">
         <v>706</v>
@@ -4116,7 +4155,7 @@
         <v>27.96039603960396</v>
       </c>
       <c r="F153" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4127,7 +4166,7 @@
         <v>44</v>
       </c>
       <c r="C154" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D154">
         <v>578</v>
@@ -4136,7 +4175,7 @@
         <v>22.89108910891089</v>
       </c>
       <c r="F154" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4147,7 +4186,7 @@
         <v>44</v>
       </c>
       <c r="C155" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D155">
         <v>324</v>
@@ -4156,7 +4195,7 @@
         <v>12.83168316831683</v>
       </c>
       <c r="F155" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4167,7 +4206,7 @@
         <v>45</v>
       </c>
       <c r="C157" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D157">
         <v>149</v>
@@ -4176,7 +4215,7 @@
         <v>41.38888888888889</v>
       </c>
       <c r="F157" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4187,7 +4226,7 @@
         <v>45</v>
       </c>
       <c r="C158" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D158">
         <v>113</v>
@@ -4196,7 +4235,7 @@
         <v>31.38888888888889</v>
       </c>
       <c r="F158" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4207,7 +4246,7 @@
         <v>45</v>
       </c>
       <c r="C159" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D159">
         <v>59</v>
@@ -4216,7 +4255,7 @@
         <v>16.38888888888889</v>
       </c>
       <c r="F159" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4227,7 +4266,7 @@
         <v>45</v>
       </c>
       <c r="C160" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D160">
         <v>39</v>
@@ -4236,7 +4275,7 @@
         <v>10.83333333333333</v>
       </c>
       <c r="F160" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4247,7 +4286,7 @@
         <v>46</v>
       </c>
       <c r="C162" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D162">
         <v>179</v>
@@ -4256,7 +4295,7 @@
         <v>45.31645569620253</v>
       </c>
       <c r="F162" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4267,7 +4306,7 @@
         <v>46</v>
       </c>
       <c r="C163" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D163">
         <v>110</v>
@@ -4276,7 +4315,7 @@
         <v>27.84810126582278</v>
       </c>
       <c r="F163" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4287,7 +4326,7 @@
         <v>46</v>
       </c>
       <c r="C164" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D164">
         <v>106</v>
@@ -4296,7 +4335,7 @@
         <v>26.83544303797468</v>
       </c>
       <c r="F164" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -4307,7 +4346,7 @@
         <v>47</v>
       </c>
       <c r="C166" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D166">
         <v>276</v>
@@ -4316,7 +4355,7 @@
         <v>47.01873935264054</v>
       </c>
       <c r="F166" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -4327,7 +4366,7 @@
         <v>47</v>
       </c>
       <c r="C167" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D167">
         <v>226</v>
@@ -4336,7 +4375,7 @@
         <v>38.50085178875639</v>
       </c>
       <c r="F167" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -4347,7 +4386,7 @@
         <v>47</v>
       </c>
       <c r="C168" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D168">
         <v>85</v>
@@ -4356,7 +4395,7 @@
         <v>14.48040885860307</v>
       </c>
       <c r="F168" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -4367,7 +4406,7 @@
         <v>48</v>
       </c>
       <c r="C170" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D170">
         <v>636</v>
@@ -4376,7 +4415,7 @@
         <v>41.24513618677042</v>
       </c>
       <c r="F170" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -4387,7 +4426,7 @@
         <v>48</v>
       </c>
       <c r="C171" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D171">
         <v>544</v>
@@ -4396,7 +4435,7 @@
         <v>35.27885862516213</v>
       </c>
       <c r="F171" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -4407,7 +4446,7 @@
         <v>48</v>
       </c>
       <c r="C172" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D172">
         <v>362</v>
@@ -4416,7 +4455,7 @@
         <v>23.47600518806744</v>
       </c>
       <c r="F172" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4427,7 +4466,7 @@
         <v>49</v>
       </c>
       <c r="C174" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D174">
         <v>104</v>
@@ -4436,7 +4475,7 @@
         <v>38.95131086142322</v>
       </c>
       <c r="F174" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4447,7 +4486,7 @@
         <v>49</v>
       </c>
       <c r="C175" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D175">
         <v>100</v>
@@ -4456,7 +4495,7 @@
         <v>37.45318352059925</v>
       </c>
       <c r="F175" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4467,7 +4506,7 @@
         <v>49</v>
       </c>
       <c r="C176" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D176">
         <v>63</v>
@@ -4476,7 +4515,7 @@
         <v>23.59550561797753</v>
       </c>
       <c r="F176" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4487,7 +4526,7 @@
         <v>50</v>
       </c>
       <c r="C178" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D178">
         <v>1206</v>
@@ -4496,7 +4535,7 @@
         <v>37.08487084870848</v>
       </c>
       <c r="F178" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4507,7 +4546,7 @@
         <v>50</v>
       </c>
       <c r="C179" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D179">
         <v>1121</v>
@@ -4516,7 +4555,7 @@
         <v>34.47109471094711</v>
       </c>
       <c r="F179" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4527,7 +4566,7 @@
         <v>50</v>
       </c>
       <c r="C180" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D180">
         <v>925</v>
@@ -4536,7 +4575,7 @@
         <v>28.4440344403444</v>
       </c>
       <c r="F180" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -4547,7 +4586,7 @@
         <v>51</v>
       </c>
       <c r="C182" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D182">
         <v>882</v>
@@ -4556,7 +4595,7 @@
         <v>45.60496380558428</v>
       </c>
       <c r="F182" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -4567,7 +4606,7 @@
         <v>51</v>
       </c>
       <c r="C183" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D183">
         <v>502</v>
@@ -4576,7 +4615,7 @@
         <v>25.95656670113754</v>
       </c>
       <c r="F183" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4587,7 +4626,7 @@
         <v>51</v>
       </c>
       <c r="C184" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D184">
         <v>399</v>
@@ -4596,7 +4635,7 @@
         <v>20.63081695966908</v>
       </c>
       <c r="F184" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4607,7 +4646,7 @@
         <v>51</v>
       </c>
       <c r="C185" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D185">
         <v>151</v>
@@ -4616,7 +4655,7 @@
         <v>7.807652533609101</v>
       </c>
       <c r="F185" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4627,7 +4666,7 @@
         <v>52</v>
       </c>
       <c r="C187" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D187">
         <v>665</v>
@@ -4636,7 +4675,7 @@
         <v>39.98797354179194</v>
       </c>
       <c r="F187" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4647,7 +4686,7 @@
         <v>52</v>
       </c>
       <c r="C188" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D188">
         <v>429</v>
@@ -4656,7 +4695,7 @@
         <v>25.79675285628382</v>
       </c>
       <c r="F188" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -4667,7 +4706,7 @@
         <v>52</v>
       </c>
       <c r="C189" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D189">
         <v>308</v>
@@ -4676,7 +4715,7 @@
         <v>18.5207456404089</v>
       </c>
       <c r="F189" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4687,7 +4726,7 @@
         <v>52</v>
       </c>
       <c r="C190" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D190">
         <v>153</v>
@@ -4696,7 +4735,7 @@
         <v>9.20024052916416</v>
       </c>
       <c r="F190" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4707,7 +4746,7 @@
         <v>52</v>
       </c>
       <c r="C191" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D191">
         <v>108</v>
@@ -4716,7 +4755,7 @@
         <v>6.494287432351173</v>
       </c>
       <c r="F191" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4727,7 +4766,7 @@
         <v>53</v>
       </c>
       <c r="C193" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D193">
         <v>445</v>
@@ -4736,7 +4775,7 @@
         <v>43.28793774319066</v>
       </c>
       <c r="F193" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4747,7 +4786,7 @@
         <v>53</v>
       </c>
       <c r="C194" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D194">
         <v>353</v>
@@ -4756,7 +4795,7 @@
         <v>34.33852140077821</v>
       </c>
       <c r="F194" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4767,7 +4806,7 @@
         <v>53</v>
       </c>
       <c r="C195" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D195">
         <v>230</v>
@@ -4776,7 +4815,7 @@
         <v>22.37354085603113</v>
       </c>
       <c r="F195" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4787,7 +4826,7 @@
         <v>54</v>
       </c>
       <c r="C197" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D197">
         <v>684</v>
@@ -4796,7 +4835,7 @@
         <v>46.94577899794098</v>
       </c>
       <c r="F197" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4807,7 +4846,7 @@
         <v>54</v>
       </c>
       <c r="C198" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D198">
         <v>395</v>
@@ -4816,7 +4855,7 @@
         <v>27.1105010295127</v>
       </c>
       <c r="F198" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4827,7 +4866,7 @@
         <v>54</v>
       </c>
       <c r="C199" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D199">
         <v>378</v>
@@ -4836,7 +4875,7 @@
         <v>25.94371997254633</v>
       </c>
       <c r="F199" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4847,7 +4886,7 @@
         <v>55</v>
       </c>
       <c r="C201" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D201">
         <v>828</v>
@@ -4856,7 +4895,7 @@
         <v>36.71840354767184</v>
       </c>
       <c r="F201" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4867,7 +4906,7 @@
         <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D202">
         <v>524</v>
@@ -4876,7 +4915,7 @@
         <v>23.23725055432372</v>
       </c>
       <c r="F202" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4887,7 +4926,7 @@
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D203">
         <v>485</v>
@@ -4896,7 +4935,7 @@
         <v>21.50776053215078</v>
       </c>
       <c r="F203" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4907,7 +4946,7 @@
         <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D204">
         <v>261</v>
@@ -4916,7 +4955,7 @@
         <v>11.57427937915743</v>
       </c>
       <c r="F204" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4927,7 +4966,7 @@
         <v>55</v>
       </c>
       <c r="C205" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D205">
         <v>157</v>
@@ -4936,7 +4975,7 @@
         <v>6.962305986696231</v>
       </c>
       <c r="F205" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4947,7 +4986,7 @@
         <v>56</v>
       </c>
       <c r="C207" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D207">
         <v>584</v>
@@ -4956,7 +4995,7 @@
         <v>43.90977443609022</v>
       </c>
       <c r="F207" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4967,7 +5006,7 @@
         <v>56</v>
       </c>
       <c r="C208" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D208">
         <v>388</v>
@@ -4976,7 +5015,7 @@
         <v>29.17293233082707</v>
       </c>
       <c r="F208" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4987,7 +5026,7 @@
         <v>56</v>
       </c>
       <c r="C209" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D209">
         <v>358</v>
@@ -4996,7 +5035,7 @@
         <v>26.91729323308271</v>
       </c>
       <c r="F209" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -5007,7 +5046,7 @@
         <v>57</v>
       </c>
       <c r="C211" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D211">
         <v>634</v>
@@ -5016,7 +5055,7 @@
         <v>45.67723342939482</v>
       </c>
       <c r="F211" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -5027,7 +5066,7 @@
         <v>57</v>
       </c>
       <c r="C212" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D212">
         <v>298</v>
@@ -5036,7 +5075,7 @@
         <v>21.46974063400576</v>
       </c>
       <c r="F212" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -5047,7 +5086,7 @@
         <v>57</v>
       </c>
       <c r="C213" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D213">
         <v>246</v>
@@ -5056,7 +5095,7 @@
         <v>17.72334293948127</v>
       </c>
       <c r="F213" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -5067,7 +5106,7 @@
         <v>57</v>
       </c>
       <c r="C214" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D214">
         <v>210</v>
@@ -5076,7 +5115,7 @@
         <v>15.12968299711815</v>
       </c>
       <c r="F214" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -5087,7 +5126,7 @@
         <v>58</v>
       </c>
       <c r="C216" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D216">
         <v>294</v>
@@ -5096,7 +5135,7 @@
         <v>38.33116036505867</v>
       </c>
       <c r="F216" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -5107,7 +5146,7 @@
         <v>58</v>
       </c>
       <c r="C217" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D217">
         <v>145</v>
@@ -5116,7 +5155,7 @@
         <v>18.90482398956975</v>
       </c>
       <c r="F217" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -5127,7 +5166,7 @@
         <v>58</v>
       </c>
       <c r="C218" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D218">
         <v>136</v>
@@ -5136,7 +5175,7 @@
         <v>17.73142112125163</v>
       </c>
       <c r="F218" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -5147,7 +5186,7 @@
         <v>58</v>
       </c>
       <c r="C219" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D219">
         <v>104</v>
@@ -5156,7 +5195,7 @@
         <v>13.5593220338983</v>
       </c>
       <c r="F219" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -5167,7 +5206,7 @@
         <v>58</v>
       </c>
       <c r="C220" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D220">
         <v>88</v>
@@ -5176,7 +5215,7 @@
         <v>11.47327249022164</v>
       </c>
       <c r="F220" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -5187,7 +5226,7 @@
         <v>59</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D222">
         <v>957</v>
@@ -5196,7 +5235,7 @@
         <v>36.62456946039035</v>
       </c>
       <c r="F222" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -5207,7 +5246,7 @@
         <v>59</v>
       </c>
       <c r="C223" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D223">
         <v>917</v>
@@ -5216,7 +5255,7 @@
         <v>35.0937619594336</v>
       </c>
       <c r="F223" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -5227,7 +5266,7 @@
         <v>59</v>
       </c>
       <c r="C224" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D224">
         <v>739</v>
@@ -5236,7 +5275,7 @@
         <v>28.28166858017605</v>
       </c>
       <c r="F224" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -5247,7 +5286,7 @@
         <v>60</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D226">
         <v>5642</v>
@@ -5256,7 +5295,7 @@
         <v>34.00638900608764</v>
       </c>
       <c r="F226" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -5267,7 +5306,7 @@
         <v>60</v>
       </c>
       <c r="C227" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D227">
         <v>5540</v>
@@ -5276,7 +5315,7 @@
         <v>33.39159785425833</v>
       </c>
       <c r="F227" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -5287,7 +5326,7 @@
         <v>60</v>
       </c>
       <c r="C228" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D228">
         <v>5409</v>
@@ -5296,7 +5335,7 @@
         <v>32.60201313965403</v>
       </c>
       <c r="F228" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5307,7 +5346,7 @@
         <v>61</v>
       </c>
       <c r="C230" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D230">
         <v>170</v>
@@ -5316,7 +5355,7 @@
         <v>46.19565217391305</v>
       </c>
       <c r="F230" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -5327,7 +5366,7 @@
         <v>61</v>
       </c>
       <c r="C231" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D231">
         <v>169</v>
@@ -5336,7 +5375,7 @@
         <v>45.92391304347826</v>
       </c>
       <c r="F231" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -5347,7 +5386,7 @@
         <v>61</v>
       </c>
       <c r="C232" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D232">
         <v>29</v>
@@ -5356,7 +5395,7 @@
         <v>7.880434782608696</v>
       </c>
       <c r="F232" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5367,7 +5406,7 @@
         <v>62</v>
       </c>
       <c r="C234" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D234">
         <v>616</v>
@@ -5376,7 +5415,7 @@
         <v>48.85011895321173</v>
       </c>
       <c r="F234" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5387,7 +5426,7 @@
         <v>62</v>
       </c>
       <c r="C235" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D235">
         <v>534</v>
@@ -5396,7 +5435,7 @@
         <v>42.34734337827121</v>
       </c>
       <c r="F235" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -5407,7 +5446,7 @@
         <v>62</v>
       </c>
       <c r="C236" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D236">
         <v>111</v>
@@ -5416,7 +5455,7 @@
         <v>8.802537668517051</v>
       </c>
       <c r="F236" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5427,7 +5466,7 @@
         <v>63</v>
       </c>
       <c r="C238" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D238">
         <v>1114</v>
@@ -5436,7 +5475,7 @@
         <v>47.79064779064779</v>
       </c>
       <c r="F238" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -5447,7 +5486,7 @@
         <v>63</v>
       </c>
       <c r="C239" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D239">
         <v>647</v>
@@ -5456,7 +5495,7 @@
         <v>27.75632775632776</v>
       </c>
       <c r="F239" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -5467,7 +5506,7 @@
         <v>63</v>
       </c>
       <c r="C240" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D240">
         <v>369</v>
@@ -5476,7 +5515,7 @@
         <v>15.83011583011583</v>
       </c>
       <c r="F240" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -5487,7 +5526,7 @@
         <v>63</v>
       </c>
       <c r="C241" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D241">
         <v>201</v>
@@ -5496,7 +5535,7 @@
         <v>8.622908622908623</v>
       </c>
       <c r="F241" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -5507,7 +5546,7 @@
         <v>64</v>
       </c>
       <c r="C243" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D243">
         <v>592</v>
@@ -5516,7 +5555,7 @@
         <v>32.52747252747253</v>
       </c>
       <c r="F243" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -5527,7 +5566,7 @@
         <v>64</v>
       </c>
       <c r="C244" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D244">
         <v>571</v>
@@ -5536,7 +5575,7 @@
         <v>31.37362637362637</v>
       </c>
       <c r="F244" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -5547,7 +5586,7 @@
         <v>64</v>
       </c>
       <c r="C245" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D245">
         <v>324</v>
@@ -5556,7 +5595,7 @@
         <v>17.8021978021978</v>
       </c>
       <c r="F245" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -5567,7 +5606,7 @@
         <v>64</v>
       </c>
       <c r="C246" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D246">
         <v>295</v>
@@ -5576,7 +5615,7 @@
         <v>16.20879120879121</v>
       </c>
       <c r="F246" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -5587,7 +5626,7 @@
         <v>64</v>
       </c>
       <c r="C247" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D247">
         <v>38</v>
@@ -5596,7 +5635,7 @@
         <v>2.087912087912088</v>
       </c>
       <c r="F247" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -5607,7 +5646,7 @@
         <v>65</v>
       </c>
       <c r="C249" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D249">
         <v>886</v>
@@ -5616,7 +5655,7 @@
         <v>48.86927744070601</v>
       </c>
       <c r="F249" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -5627,7 +5666,7 @@
         <v>65</v>
       </c>
       <c r="C250" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D250">
         <v>699</v>
@@ -5636,7 +5675,7 @@
         <v>38.55488141202427</v>
       </c>
       <c r="F250" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -5647,7 +5686,7 @@
         <v>65</v>
       </c>
       <c r="C251" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D251">
         <v>228</v>
@@ -5656,7 +5695,7 @@
         <v>12.57584114726972</v>
       </c>
       <c r="F251" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -5667,7 +5706,7 @@
         <v>66</v>
       </c>
       <c r="C253" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D253">
         <v>1630</v>
@@ -5676,7 +5715,7 @@
         <v>44.46262956901255</v>
       </c>
       <c r="F253" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -5687,7 +5726,7 @@
         <v>66</v>
       </c>
       <c r="C254" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D254">
         <v>1039</v>
@@ -5696,7 +5735,7 @@
         <v>28.34151663938898</v>
       </c>
       <c r="F254" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -5707,7 +5746,7 @@
         <v>66</v>
       </c>
       <c r="C255" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D255">
         <v>813</v>
@@ -5716,7 +5755,7 @@
         <v>22.17675941080196</v>
       </c>
       <c r="F255" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -5727,7 +5766,7 @@
         <v>66</v>
       </c>
       <c r="C256" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D256">
         <v>184</v>
@@ -5736,7 +5775,7 @@
         <v>5.019094380796509</v>
       </c>
       <c r="F256" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -5747,7 +5786,7 @@
         <v>67</v>
       </c>
       <c r="C258" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D258">
         <v>1334</v>
@@ -5756,7 +5795,7 @@
         <v>46.38386648122393</v>
       </c>
       <c r="F258" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -5767,7 +5806,7 @@
         <v>67</v>
       </c>
       <c r="C259" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D259">
         <v>1278</v>
@@ -5776,7 +5815,7 @@
         <v>44.43671766342142</v>
       </c>
       <c r="F259" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -5787,7 +5826,7 @@
         <v>67</v>
       </c>
       <c r="C260" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D260">
         <v>264</v>
@@ -5796,7 +5835,7 @@
         <v>9.179415855354661</v>
       </c>
       <c r="F260" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -5807,7 +5846,7 @@
         <v>68</v>
       </c>
       <c r="C262" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D262">
         <v>1466</v>
@@ -5816,7 +5855,7 @@
         <v>43.1303324507208</v>
       </c>
       <c r="F262" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -5827,7 +5866,7 @@
         <v>68</v>
       </c>
       <c r="C263" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D263">
         <v>893</v>
@@ -5836,7 +5875,7 @@
         <v>26.27243306854957</v>
       </c>
       <c r="F263" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -5847,7 +5886,7 @@
         <v>68</v>
       </c>
       <c r="C264" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D264">
         <v>672</v>
@@ -5856,7 +5895,7 @@
         <v>19.77052074139453</v>
       </c>
       <c r="F264" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -5867,7 +5906,7 @@
         <v>68</v>
       </c>
       <c r="C265" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D265">
         <v>245</v>
@@ -5876,7 +5915,7 @@
         <v>7.208002353633422</v>
       </c>
       <c r="F265" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -5887,7 +5926,7 @@
         <v>68</v>
       </c>
       <c r="C266" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D266">
         <v>123</v>
@@ -5896,7 +5935,7 @@
         <v>3.618711385701677</v>
       </c>
       <c r="F266" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -5907,7 +5946,7 @@
         <v>69</v>
       </c>
       <c r="C268" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D268">
         <v>1108</v>
@@ -5916,7 +5955,7 @@
         <v>46.4765100671141</v>
       </c>
       <c r="F268" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -5927,7 +5966,7 @@
         <v>69</v>
       </c>
       <c r="C269" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D269">
         <v>444</v>
@@ -5936,7 +5975,7 @@
         <v>18.6241610738255</v>
       </c>
       <c r="F269" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -5947,7 +5986,7 @@
         <v>69</v>
       </c>
       <c r="C270" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D270">
         <v>343</v>
@@ -5956,7 +5995,7 @@
         <v>14.38758389261745</v>
       </c>
       <c r="F270" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -5967,7 +6006,7 @@
         <v>69</v>
       </c>
       <c r="C271" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D271">
         <v>323</v>
@@ -5976,7 +6015,7 @@
         <v>13.5486577181208</v>
       </c>
       <c r="F271" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -5987,7 +6026,7 @@
         <v>69</v>
       </c>
       <c r="C272" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D272">
         <v>166</v>
@@ -5996,7 +6035,7 @@
         <v>6.963087248322148</v>
       </c>
       <c r="F272" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -6007,7 +6046,7 @@
         <v>70</v>
       </c>
       <c r="C274" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D274">
         <v>904</v>
@@ -6016,7 +6055,7 @@
         <v>42.60131950989632</v>
       </c>
       <c r="F274" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -6027,7 +6066,7 @@
         <v>70</v>
       </c>
       <c r="C275" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D275">
         <v>860</v>
@@ -6036,7 +6075,7 @@
         <v>40.52780395852969</v>
       </c>
       <c r="F275" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -6047,7 +6086,7 @@
         <v>70</v>
       </c>
       <c r="C276" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D276">
         <v>193</v>
@@ -6056,7 +6095,7 @@
         <v>9.095193213949104</v>
       </c>
       <c r="F276" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -6067,7 +6106,7 @@
         <v>70</v>
       </c>
       <c r="C277" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D277">
         <v>165</v>
@@ -6076,7 +6115,7 @@
         <v>7.775683317624882</v>
       </c>
       <c r="F277" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -6087,7 +6126,7 @@
         <v>71</v>
       </c>
       <c r="C279" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D279">
         <v>425</v>
@@ -6096,7 +6135,7 @@
         <v>25.11820330969267</v>
       </c>
       <c r="F279" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -6107,7 +6146,7 @@
         <v>71</v>
       </c>
       <c r="C280" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D280">
         <v>341</v>
@@ -6116,7 +6155,7 @@
         <v>20.15366430260048</v>
       </c>
       <c r="F280" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -6127,7 +6166,7 @@
         <v>71</v>
       </c>
       <c r="C281" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D281">
         <v>279</v>
@@ -6136,7 +6175,7 @@
         <v>16.48936170212766</v>
       </c>
       <c r="F281" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -6147,7 +6186,7 @@
         <v>71</v>
       </c>
       <c r="C282" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D282">
         <v>272</v>
@@ -6156,7 +6195,7 @@
         <v>16.07565011820331</v>
       </c>
       <c r="F282" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -6167,7 +6206,7 @@
         <v>71</v>
       </c>
       <c r="C283" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D283">
         <v>220</v>
@@ -6176,7 +6215,7 @@
         <v>13.00236406619385</v>
       </c>
       <c r="F283" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -6187,7 +6226,7 @@
         <v>71</v>
       </c>
       <c r="C284" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D284">
         <v>155</v>
@@ -6196,7 +6235,7 @@
         <v>9.160756501182032</v>
       </c>
       <c r="F284" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -6207,7 +6246,7 @@
         <v>72</v>
       </c>
       <c r="C286" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D286">
         <v>272</v>
@@ -6216,7 +6255,7 @@
         <v>44.01294498381877</v>
       </c>
       <c r="F286" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -6227,7 +6266,7 @@
         <v>72</v>
       </c>
       <c r="C287" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D287">
         <v>145</v>
@@ -6236,7 +6275,7 @@
         <v>23.46278317152104</v>
       </c>
       <c r="F287" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -6247,7 +6286,7 @@
         <v>72</v>
       </c>
       <c r="C288" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D288">
         <v>108</v>
@@ -6256,7 +6295,7 @@
         <v>17.47572815533981</v>
       </c>
       <c r="F288" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -6267,7 +6306,7 @@
         <v>72</v>
       </c>
       <c r="C289" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D289">
         <v>50</v>
@@ -6276,7 +6315,7 @@
         <v>8.090614886731391</v>
       </c>
       <c r="F289" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -6287,7 +6326,7 @@
         <v>72</v>
       </c>
       <c r="C290" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D290">
         <v>43</v>
@@ -6296,7 +6335,7 @@
         <v>6.957928802588997</v>
       </c>
       <c r="F290" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -6307,7 +6346,7 @@
         <v>73</v>
       </c>
       <c r="C292" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D292">
         <v>286</v>
@@ -6316,7 +6355,7 @@
         <v>48.22934232715008</v>
       </c>
       <c r="F292" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -6327,7 +6366,7 @@
         <v>73</v>
       </c>
       <c r="C293" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D293">
         <v>212</v>
@@ -6336,7 +6375,7 @@
         <v>35.7504215851602</v>
       </c>
       <c r="F293" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -6347,7 +6386,7 @@
         <v>73</v>
       </c>
       <c r="C294" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D294">
         <v>95</v>
@@ -6356,7 +6395,7 @@
         <v>16.02023608768971</v>
       </c>
       <c r="F294" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -6367,7 +6406,7 @@
         <v>74</v>
       </c>
       <c r="C296" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D296">
         <v>431</v>
@@ -6376,7 +6415,7 @@
         <v>36.77474402730375</v>
       </c>
       <c r="F296" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -6387,7 +6426,7 @@
         <v>74</v>
       </c>
       <c r="C297" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D297">
         <v>297</v>
@@ -6396,7 +6435,7 @@
         <v>25.34129692832764</v>
       </c>
       <c r="F297" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -6407,7 +6446,7 @@
         <v>74</v>
       </c>
       <c r="C298" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D298">
         <v>285</v>
@@ -6416,7 +6455,7 @@
         <v>24.31740614334471</v>
       </c>
       <c r="F298" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -6427,7 +6466,7 @@
         <v>74</v>
       </c>
       <c r="C299" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D299">
         <v>96</v>
@@ -6436,7 +6475,7 @@
         <v>8.191126279863481</v>
       </c>
       <c r="F299" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -6447,7 +6486,7 @@
         <v>74</v>
       </c>
       <c r="C300" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D300">
         <v>63</v>
@@ -6456,7 +6495,7 @@
         <v>5.375426621160409</v>
       </c>
       <c r="F300" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -6467,7 +6506,7 @@
         <v>75</v>
       </c>
       <c r="C302" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D302">
         <v>273</v>
@@ -6476,7 +6515,7 @@
         <v>45.4242928452579</v>
       </c>
       <c r="F302" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -6487,7 +6526,7 @@
         <v>75</v>
       </c>
       <c r="C303" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D303">
         <v>234</v>
@@ -6496,7 +6535,7 @@
         <v>38.9351081530782</v>
       </c>
       <c r="F303" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -6507,7 +6546,7 @@
         <v>75</v>
       </c>
       <c r="C304" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D304">
         <v>94</v>
@@ -6516,7 +6555,7 @@
         <v>15.64059900166389</v>
       </c>
       <c r="F304" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -6527,7 +6566,7 @@
         <v>76</v>
       </c>
       <c r="C306" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D306">
         <v>124</v>
@@ -6536,7 +6575,7 @@
         <v>47.69230769230769</v>
       </c>
       <c r="F306" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -6547,7 +6586,7 @@
         <v>76</v>
       </c>
       <c r="C307" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D307">
         <v>73</v>
@@ -6556,7 +6595,7 @@
         <v>28.07692307692308</v>
       </c>
       <c r="F307" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -6567,7 +6606,7 @@
         <v>76</v>
       </c>
       <c r="C308" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D308">
         <v>63</v>
@@ -6576,7 +6615,7 @@
         <v>24.23076923076923</v>
       </c>
       <c r="F308" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -6587,7 +6626,7 @@
         <v>77</v>
       </c>
       <c r="C310" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D310">
         <v>827</v>
@@ -6596,7 +6635,7 @@
         <v>47.88650839606254</v>
       </c>
       <c r="F310" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -6607,7 +6646,7 @@
         <v>77</v>
       </c>
       <c r="C311" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D311">
         <v>284</v>
@@ -6616,7 +6655,7 @@
         <v>16.44470179502026</v>
       </c>
       <c r="F311" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -6627,7 +6666,7 @@
         <v>77</v>
       </c>
       <c r="C312" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D312">
         <v>222</v>
@@ -6636,7 +6675,7 @@
         <v>12.85466126230457</v>
       </c>
       <c r="F312" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -6647,7 +6686,7 @@
         <v>77</v>
       </c>
       <c r="C313" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D313">
         <v>211</v>
@@ -6656,7 +6695,7 @@
         <v>12.21771858714534</v>
       </c>
       <c r="F313" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -6667,7 +6706,7 @@
         <v>77</v>
       </c>
       <c r="C314" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D314">
         <v>183</v>
@@ -6676,7 +6715,7 @@
         <v>10.59640995946728</v>
       </c>
       <c r="F314" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -6687,16 +6726,16 @@
         <v>78</v>
       </c>
       <c r="C316" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D316">
-        <v>605</v>
+        <v>186</v>
       </c>
       <c r="E316">
-        <v>41.10054347826087</v>
+        <v>42.46575342465754</v>
       </c>
       <c r="F316" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -6707,16 +6746,16 @@
         <v>78</v>
       </c>
       <c r="C317" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D317">
-        <v>593</v>
+        <v>144</v>
       </c>
       <c r="E317">
-        <v>40.28532608695652</v>
+        <v>32.87671232876712</v>
       </c>
       <c r="F317" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -6727,16 +6766,16 @@
         <v>78</v>
       </c>
       <c r="C318" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D318">
-        <v>274</v>
+        <v>108</v>
       </c>
       <c r="E318">
-        <v>18.61413043478261</v>
+        <v>24.65753424657534</v>
       </c>
       <c r="F318" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -6747,16 +6786,16 @@
         <v>79</v>
       </c>
       <c r="C320" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D320">
-        <v>347</v>
+        <v>605</v>
       </c>
       <c r="E320">
-        <v>49.15014164305949</v>
+        <v>41.10054347826087</v>
       </c>
       <c r="F320" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -6767,16 +6806,16 @@
         <v>79</v>
       </c>
       <c r="C321" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D321">
-        <v>168</v>
+        <v>593</v>
       </c>
       <c r="E321">
-        <v>23.79603399433428</v>
+        <v>40.28532608695652</v>
       </c>
       <c r="F321" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -6787,36 +6826,36 @@
         <v>79</v>
       </c>
       <c r="C322" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D322">
-        <v>103</v>
+        <v>274</v>
       </c>
       <c r="E322">
-        <v>14.58923512747875</v>
+        <v>18.61413043478261</v>
       </c>
       <c r="F322" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6">
-      <c r="A323">
-        <v>2023</v>
-      </c>
-      <c r="B323" t="s">
-        <v>79</v>
-      </c>
-      <c r="C323" t="s">
-        <v>315</v>
-      </c>
-      <c r="D323">
-        <v>88</v>
-      </c>
-      <c r="E323">
-        <v>12.46458923512748</v>
-      </c>
-      <c r="F323" t="s">
-        <v>414</v>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324">
+        <v>2023</v>
+      </c>
+      <c r="B324" t="s">
+        <v>80</v>
+      </c>
+      <c r="C324" t="s">
+        <v>318</v>
+      </c>
+      <c r="D324">
+        <v>347</v>
+      </c>
+      <c r="E324">
+        <v>49.15014164305949</v>
+      </c>
+      <c r="F324" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -6827,16 +6866,16 @@
         <v>80</v>
       </c>
       <c r="C325" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D325">
-        <v>372</v>
+        <v>168</v>
       </c>
       <c r="E325">
-        <v>42.36902050113896</v>
+        <v>23.79603399433428</v>
       </c>
       <c r="F325" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -6847,16 +6886,16 @@
         <v>80</v>
       </c>
       <c r="C326" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D326">
-        <v>195</v>
+        <v>103</v>
       </c>
       <c r="E326">
-        <v>22.20956719817768</v>
+        <v>14.58923512747875</v>
       </c>
       <c r="F326" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -6867,176 +6906,156 @@
         <v>80</v>
       </c>
       <c r="C327" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D327">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="E327">
-        <v>21.98177676537586</v>
+        <v>12.46458923512748</v>
       </c>
       <c r="F327" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6">
-      <c r="A328">
-        <v>2023</v>
-      </c>
-      <c r="B328" t="s">
-        <v>80</v>
-      </c>
-      <c r="C328" t="s">
-        <v>319</v>
-      </c>
-      <c r="D328">
-        <v>118</v>
-      </c>
-      <c r="E328">
-        <v>13.43963553530752</v>
-      </c>
-      <c r="F328" t="s">
-        <v>408</v>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329">
+        <v>2023</v>
+      </c>
+      <c r="B329" t="s">
+        <v>81</v>
+      </c>
+      <c r="C329" t="s">
+        <v>322</v>
+      </c>
+      <c r="D329">
+        <v>372</v>
+      </c>
+      <c r="E329">
+        <v>42.36902050113896</v>
+      </c>
+      <c r="F329" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="330" spans="1:6">
       <c r="A330">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B330" t="s">
         <v>81</v>
       </c>
       <c r="C330" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D330">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="E330">
-        <v>44.68085106382978</v>
+        <v>22.20956719817768</v>
       </c>
       <c r="F330" t="s">
-        <v>10</v>
+        <v>420</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B331" t="s">
         <v>81</v>
       </c>
       <c r="C331" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D331">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="E331">
-        <v>31.00303951367781</v>
+        <v>21.98177676537586</v>
       </c>
       <c r="F331" t="s">
-        <v>10</v>
+        <v>420</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B332" t="s">
         <v>81</v>
       </c>
       <c r="C332" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D332">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="E332">
-        <v>24.3161094224924</v>
+        <v>13.43963553530752</v>
       </c>
       <c r="F332" t="s">
-        <v>10</v>
+        <v>420</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B334" t="s">
         <v>82</v>
       </c>
       <c r="C334" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D334">
-        <v>1224</v>
+        <v>147</v>
       </c>
       <c r="E334">
-        <v>28.77291960507758</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="F334" t="s">
-        <v>402</v>
+        <v>10</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B335" t="s">
         <v>82</v>
       </c>
       <c r="C335" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D335">
-        <v>1052</v>
+        <v>102</v>
       </c>
       <c r="E335">
-        <v>24.72966619652092</v>
+        <v>31.00303951367781</v>
       </c>
       <c r="F335" t="s">
-        <v>402</v>
+        <v>10</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B336" t="s">
         <v>82</v>
       </c>
       <c r="C336" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D336">
-        <v>685</v>
+        <v>80</v>
       </c>
       <c r="E336">
-        <v>16.10249177244946</v>
+        <v>24.3161094224924</v>
       </c>
       <c r="F336" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6">
-      <c r="A337">
-        <v>2025</v>
-      </c>
-      <c r="B337" t="s">
-        <v>82</v>
-      </c>
-      <c r="C337" t="s">
-        <v>326</v>
-      </c>
-      <c r="D337">
-        <v>656</v>
-      </c>
-      <c r="E337">
-        <v>15.420780441937</v>
-      </c>
-      <c r="F337" t="s">
-        <v>402</v>
+        <v>10</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -7044,19 +7063,39 @@
         <v>2025</v>
       </c>
       <c r="B338" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C338" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D338">
-        <v>637</v>
+        <v>1224</v>
       </c>
       <c r="E338">
-        <v>14.97414198401504</v>
+        <v>28.77291960507758</v>
       </c>
       <c r="F338" t="s">
-        <v>402</v>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339">
+        <v>2025</v>
+      </c>
+      <c r="B339" t="s">
+        <v>83</v>
+      </c>
+      <c r="C339" t="s">
+        <v>330</v>
+      </c>
+      <c r="D339">
+        <v>1052</v>
+      </c>
+      <c r="E339">
+        <v>24.72966619652092</v>
+      </c>
+      <c r="F339" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -7067,16 +7106,16 @@
         <v>83</v>
       </c>
       <c r="C340" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D340">
-        <v>3817</v>
+        <v>685</v>
       </c>
       <c r="E340">
-        <v>39.10860655737705</v>
+        <v>16.10249177244946</v>
       </c>
       <c r="F340" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -7087,16 +7126,16 @@
         <v>83</v>
       </c>
       <c r="C341" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D341">
-        <v>3272</v>
+        <v>656</v>
       </c>
       <c r="E341">
-        <v>33.52459016393443</v>
+        <v>15.420780441937</v>
       </c>
       <c r="F341" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -7107,16 +7146,16 @@
         <v>83</v>
       </c>
       <c r="C342" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D342">
-        <v>2671</v>
+        <v>637</v>
       </c>
       <c r="E342">
-        <v>27.36680327868852</v>
+        <v>14.97414198401504</v>
       </c>
       <c r="F342" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -7127,16 +7166,16 @@
         <v>84</v>
       </c>
       <c r="C344" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D344">
-        <v>710</v>
+        <v>3817</v>
       </c>
       <c r="E344">
-        <v>46.64914586070959</v>
+        <v>39.10860655737705</v>
       </c>
       <c r="F344" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -7147,16 +7186,16 @@
         <v>84</v>
       </c>
       <c r="C345" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D345">
-        <v>617</v>
+        <v>3272</v>
       </c>
       <c r="E345">
-        <v>40.53876478318003</v>
+        <v>33.52459016393443</v>
       </c>
       <c r="F345" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -7167,16 +7206,16 @@
         <v>84</v>
       </c>
       <c r="C346" t="s">
-        <v>196</v>
+        <v>336</v>
       </c>
       <c r="D346">
-        <v>195</v>
+        <v>2671</v>
       </c>
       <c r="E346">
-        <v>12.81208935611038</v>
+        <v>27.36680327868852</v>
       </c>
       <c r="F346" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -7187,16 +7226,16 @@
         <v>85</v>
       </c>
       <c r="C348" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D348">
-        <v>241</v>
+        <v>710</v>
       </c>
       <c r="E348">
-        <v>49.79338842975206</v>
+        <v>46.64914586070959</v>
       </c>
       <c r="F348" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -7207,16 +7246,16 @@
         <v>85</v>
       </c>
       <c r="C349" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D349">
-        <v>193</v>
+        <v>617</v>
       </c>
       <c r="E349">
-        <v>39.87603305785124</v>
+        <v>40.53876478318003</v>
       </c>
       <c r="F349" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="350" spans="1:6">
@@ -7227,16 +7266,16 @@
         <v>85</v>
       </c>
       <c r="C350" t="s">
-        <v>335</v>
+        <v>199</v>
       </c>
       <c r="D350">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="E350">
-        <v>10.12396694214876</v>
+        <v>12.81208935611038</v>
       </c>
       <c r="F350" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="352" spans="1:6">
@@ -7247,16 +7286,16 @@
         <v>86</v>
       </c>
       <c r="C352" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D352">
-        <v>373</v>
+        <v>7014</v>
       </c>
       <c r="E352">
-        <v>36.39024390243902</v>
+        <v>38.28393646635008</v>
       </c>
       <c r="F352" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -7267,16 +7306,16 @@
         <v>86</v>
       </c>
       <c r="C353" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D353">
-        <v>225</v>
+        <v>6543</v>
       </c>
       <c r="E353">
-        <v>21.95121951219512</v>
+        <v>35.71311609628295</v>
       </c>
       <c r="F353" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
     </row>
     <row r="354" spans="1:6">
@@ -7287,36 +7326,16 @@
         <v>86</v>
       </c>
       <c r="C354" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D354">
-        <v>206</v>
+        <v>4764</v>
       </c>
       <c r="E354">
-        <v>20.09756097560976</v>
+        <v>26.00294743736696</v>
       </c>
       <c r="F354" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6">
-      <c r="A355">
-        <v>2025</v>
-      </c>
-      <c r="B355" t="s">
-        <v>86</v>
-      </c>
-      <c r="C355" t="s">
-        <v>339</v>
-      </c>
-      <c r="D355">
-        <v>140</v>
-      </c>
-      <c r="E355">
-        <v>13.65853658536586</v>
-      </c>
-      <c r="F355" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -7324,19 +7343,39 @@
         <v>2025</v>
       </c>
       <c r="B356" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C356" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D356">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="E356">
-        <v>7.902439024390244</v>
+        <v>49.79338842975206</v>
       </c>
       <c r="F356" t="s">
-        <v>401</v>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357">
+        <v>2025</v>
+      </c>
+      <c r="B357" t="s">
+        <v>87</v>
+      </c>
+      <c r="C357" t="s">
+        <v>343</v>
+      </c>
+      <c r="D357">
+        <v>193</v>
+      </c>
+      <c r="E357">
+        <v>39.87603305785124</v>
+      </c>
+      <c r="F357" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -7344,39 +7383,19 @@
         <v>2025</v>
       </c>
       <c r="B358" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="C358" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D358">
-        <v>6552</v>
+        <v>49</v>
       </c>
       <c r="E358">
-        <v>47.15704620699582</v>
+        <v>10.12396694214876</v>
       </c>
       <c r="F358" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="359" spans="1:6">
-      <c r="A359">
-        <v>2025</v>
-      </c>
-      <c r="B359" t="s">
-        <v>37</v>
-      </c>
-      <c r="C359" t="s">
-        <v>342</v>
-      </c>
-      <c r="D359">
-        <v>4724</v>
-      </c>
-      <c r="E359">
-        <v>34.00028789405498</v>
-      </c>
-      <c r="F359" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -7384,19 +7403,39 @@
         <v>2025</v>
       </c>
       <c r="B360" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C360" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D360">
-        <v>2618</v>
+        <v>373</v>
       </c>
       <c r="E360">
-        <v>18.84266589894919</v>
+        <v>36.39024390243902</v>
       </c>
       <c r="F360" t="s">
-        <v>406</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361">
+        <v>2025</v>
+      </c>
+      <c r="B361" t="s">
+        <v>88</v>
+      </c>
+      <c r="C361" t="s">
+        <v>346</v>
+      </c>
+      <c r="D361">
+        <v>225</v>
+      </c>
+      <c r="E361">
+        <v>21.95121951219512</v>
+      </c>
+      <c r="F361" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -7404,19 +7443,19 @@
         <v>2025</v>
       </c>
       <c r="B362" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C362" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D362">
-        <v>5832</v>
+        <v>206</v>
       </c>
       <c r="E362">
-        <v>37.28423475258919</v>
+        <v>20.09756097560976</v>
       </c>
       <c r="F362" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="363" spans="1:6">
@@ -7424,19 +7463,19 @@
         <v>2025</v>
       </c>
       <c r="B363" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C363" t="s">
-        <v>267</v>
+        <v>348</v>
       </c>
       <c r="D363">
-        <v>4950</v>
+        <v>140</v>
       </c>
       <c r="E363">
-        <v>31.64556962025317</v>
+        <v>13.65853658536586</v>
       </c>
       <c r="F363" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -7444,19 +7483,19 @@
         <v>2025</v>
       </c>
       <c r="B364" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C364" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D364">
-        <v>4834</v>
+        <v>81</v>
       </c>
       <c r="E364">
-        <v>30.90397647359673</v>
+        <v>7.902439024390244</v>
       </c>
       <c r="F364" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -7464,19 +7503,19 @@
         <v>2025</v>
       </c>
       <c r="B366" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="C366" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D366">
-        <v>9318</v>
+        <v>6552</v>
       </c>
       <c r="E366">
-        <v>41.92764578833693</v>
+        <v>47.15704620699582</v>
       </c>
       <c r="F366" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="367" spans="1:6">
@@ -7484,19 +7523,19 @@
         <v>2025</v>
       </c>
       <c r="B367" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="C367" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D367">
-        <v>8700</v>
+        <v>4724</v>
       </c>
       <c r="E367">
-        <v>39.14686825053996</v>
+        <v>34.00028789405498</v>
       </c>
       <c r="F367" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -7504,19 +7543,19 @@
         <v>2025</v>
       </c>
       <c r="B368" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="C368" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D368">
-        <v>4206</v>
+        <v>2618</v>
       </c>
       <c r="E368">
-        <v>18.92548596112311</v>
+        <v>18.84266589894919</v>
       </c>
       <c r="F368" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -7527,16 +7566,16 @@
         <v>89</v>
       </c>
       <c r="C370" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D370">
-        <v>193</v>
+        <v>5832</v>
       </c>
       <c r="E370">
-        <v>44.36781609195402</v>
+        <v>37.28423475258919</v>
       </c>
       <c r="F370" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -7547,16 +7586,16 @@
         <v>89</v>
       </c>
       <c r="C371" t="s">
-        <v>350</v>
+        <v>270</v>
       </c>
       <c r="D371">
-        <v>161</v>
+        <v>4950</v>
       </c>
       <c r="E371">
-        <v>37.01149425287356</v>
+        <v>31.64556962025317</v>
       </c>
       <c r="F371" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -7567,16 +7606,16 @@
         <v>89</v>
       </c>
       <c r="C372" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D372">
-        <v>81</v>
+        <v>4834</v>
       </c>
       <c r="E372">
-        <v>18.62068965517242</v>
+        <v>30.90397647359673</v>
       </c>
       <c r="F372" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="374" spans="1:6">
@@ -7587,16 +7626,16 @@
         <v>90</v>
       </c>
       <c r="C374" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D374">
-        <v>1473</v>
+        <v>9318</v>
       </c>
       <c r="E374">
-        <v>39.30096051227321</v>
+        <v>41.92764578833693</v>
       </c>
       <c r="F374" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -7607,16 +7646,16 @@
         <v>90</v>
       </c>
       <c r="C375" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D375">
-        <v>1297</v>
+        <v>8700</v>
       </c>
       <c r="E375">
-        <v>34.6051227321238</v>
+        <v>39.14686825053996</v>
       </c>
       <c r="F375" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
     </row>
     <row r="376" spans="1:6">
@@ -7627,36 +7666,16 @@
         <v>90</v>
       </c>
       <c r="C376" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D376">
-        <v>516</v>
+        <v>4206</v>
       </c>
       <c r="E376">
-        <v>13.76734258271078</v>
+        <v>18.92548596112311</v>
       </c>
       <c r="F376" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="377" spans="1:6">
-      <c r="A377">
-        <v>2025</v>
-      </c>
-      <c r="B377" t="s">
-        <v>90</v>
-      </c>
-      <c r="C377" t="s">
-        <v>355</v>
-      </c>
-      <c r="D377">
-        <v>305</v>
-      </c>
-      <c r="E377">
-        <v>8.137673425827108</v>
-      </c>
-      <c r="F377" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -7664,19 +7683,39 @@
         <v>2025</v>
       </c>
       <c r="B378" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C378" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D378">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="E378">
-        <v>4.188900747065102</v>
+        <v>44.36781609195402</v>
       </c>
       <c r="F378" t="s">
-        <v>411</v>
+        <v>425</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379">
+        <v>2025</v>
+      </c>
+      <c r="B379" t="s">
+        <v>91</v>
+      </c>
+      <c r="C379" t="s">
+        <v>359</v>
+      </c>
+      <c r="D379">
+        <v>161</v>
+      </c>
+      <c r="E379">
+        <v>37.01149425287356</v>
+      </c>
+      <c r="F379" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="380" spans="1:6">
@@ -7687,36 +7726,16 @@
         <v>91</v>
       </c>
       <c r="C380" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D380">
-        <v>854</v>
+        <v>81</v>
       </c>
       <c r="E380">
-        <v>47.52365052865888</v>
+        <v>18.62068965517242</v>
       </c>
       <c r="F380" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6">
-      <c r="A381">
-        <v>2025</v>
-      </c>
-      <c r="B381" t="s">
-        <v>91</v>
-      </c>
-      <c r="C381" t="s">
-        <v>358</v>
-      </c>
-      <c r="D381">
-        <v>764</v>
-      </c>
-      <c r="E381">
-        <v>42.51530328324986</v>
-      </c>
-      <c r="F381" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
     </row>
     <row r="382" spans="1:6">
@@ -7724,19 +7743,39 @@
         <v>2025</v>
       </c>
       <c r="B382" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C382" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D382">
-        <v>175</v>
+        <v>1473</v>
       </c>
       <c r="E382">
-        <v>9.738452977184195</v>
+        <v>39.30096051227321</v>
       </c>
       <c r="F382" t="s">
-        <v>400</v>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383">
+        <v>2025</v>
+      </c>
+      <c r="B383" t="s">
+        <v>92</v>
+      </c>
+      <c r="C383" t="s">
+        <v>362</v>
+      </c>
+      <c r="D383">
+        <v>1297</v>
+      </c>
+      <c r="E383">
+        <v>34.6051227321238</v>
+      </c>
+      <c r="F383" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -7747,16 +7786,16 @@
         <v>92</v>
       </c>
       <c r="C384" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D384">
-        <v>162</v>
+        <v>516</v>
       </c>
       <c r="E384">
-        <v>45.2513966480447</v>
+        <v>13.76734258271078</v>
       </c>
       <c r="F384" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -7767,16 +7806,16 @@
         <v>92</v>
       </c>
       <c r="C385" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D385">
-        <v>156</v>
+        <v>305</v>
       </c>
       <c r="E385">
-        <v>43.5754189944134</v>
+        <v>8.137673425827108</v>
       </c>
       <c r="F385" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
     </row>
     <row r="386" spans="1:6">
@@ -7787,16 +7826,16 @@
         <v>92</v>
       </c>
       <c r="C386" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D386">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="E386">
-        <v>11.1731843575419</v>
+        <v>4.188900747065102</v>
       </c>
       <c r="F386" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -7807,16 +7846,16 @@
         <v>93</v>
       </c>
       <c r="C388" t="s">
-        <v>117</v>
+        <v>366</v>
       </c>
       <c r="D388">
-        <v>11367</v>
+        <v>854</v>
       </c>
       <c r="E388">
-        <v>45.69280861840254</v>
+        <v>47.52365052865888</v>
       </c>
       <c r="F388" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -7827,16 +7866,16 @@
         <v>93</v>
       </c>
       <c r="C389" t="s">
-        <v>116</v>
+        <v>367</v>
       </c>
       <c r="D389">
-        <v>8188</v>
+        <v>764</v>
       </c>
       <c r="E389">
-        <v>32.91393656791413</v>
+        <v>42.51530328324986</v>
       </c>
       <c r="F389" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -7847,16 +7886,16 @@
         <v>93</v>
       </c>
       <c r="C390" t="s">
-        <v>119</v>
+        <v>368</v>
       </c>
       <c r="D390">
-        <v>5322</v>
+        <v>175</v>
       </c>
       <c r="E390">
-        <v>21.39325481368332</v>
+        <v>9.738452977184195</v>
       </c>
       <c r="F390" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
     </row>
     <row r="392" spans="1:6">
@@ -7867,16 +7906,16 @@
         <v>94</v>
       </c>
       <c r="C392" t="s">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="D392">
-        <v>287</v>
+        <v>162</v>
       </c>
       <c r="E392">
-        <v>47.83333333333334</v>
+        <v>45.2513966480447</v>
       </c>
       <c r="F392" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="393" spans="1:6">
@@ -7887,16 +7926,16 @@
         <v>94</v>
       </c>
       <c r="C393" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D393">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="E393">
-        <v>29.16666666666667</v>
+        <v>43.5754189944134</v>
       </c>
       <c r="F393" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -7907,16 +7946,16 @@
         <v>94</v>
       </c>
       <c r="C394" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D394">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="E394">
-        <v>23</v>
+        <v>11.1731843575419</v>
       </c>
       <c r="F394" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -7927,13 +7966,13 @@
         <v>95</v>
       </c>
       <c r="C396" t="s">
-        <v>365</v>
+        <v>120</v>
       </c>
       <c r="D396">
-        <v>253</v>
+        <v>11367</v>
       </c>
       <c r="E396">
-        <v>45.50359712230216</v>
+        <v>45.69280861840254</v>
       </c>
       <c r="F396" t="s">
         <v>413</v>
@@ -7947,13 +7986,13 @@
         <v>95</v>
       </c>
       <c r="C397" t="s">
-        <v>366</v>
+        <v>119</v>
       </c>
       <c r="D397">
-        <v>154</v>
+        <v>8188</v>
       </c>
       <c r="E397">
-        <v>27.69784172661871</v>
+        <v>32.91393656791413</v>
       </c>
       <c r="F397" t="s">
         <v>413</v>
@@ -7967,13 +8006,13 @@
         <v>95</v>
       </c>
       <c r="C398" t="s">
-        <v>367</v>
+        <v>122</v>
       </c>
       <c r="D398">
-        <v>149</v>
+        <v>5322</v>
       </c>
       <c r="E398">
-        <v>26.79856115107914</v>
+        <v>21.39325481368332</v>
       </c>
       <c r="F398" t="s">
         <v>413</v>
@@ -7987,16 +8026,16 @@
         <v>96</v>
       </c>
       <c r="C400" t="s">
-        <v>368</v>
+        <v>294</v>
       </c>
       <c r="D400">
-        <v>163</v>
+        <v>287</v>
       </c>
       <c r="E400">
-        <v>38.71733966745843</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="F400" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -8007,16 +8046,16 @@
         <v>96</v>
       </c>
       <c r="C401" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D401">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E401">
-        <v>38.00475059382423</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="F401" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="402" spans="1:6">
@@ -8027,36 +8066,36 @@
         <v>96</v>
       </c>
       <c r="C402" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D402">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="E402">
-        <v>17.81472684085511</v>
+        <v>23</v>
       </c>
       <c r="F402" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6">
-      <c r="A403">
-        <v>2025</v>
-      </c>
-      <c r="B403" t="s">
-        <v>96</v>
-      </c>
-      <c r="C403" t="s">
-        <v>371</v>
-      </c>
-      <c r="D403">
-        <v>23</v>
-      </c>
-      <c r="E403">
-        <v>5.463182897862233</v>
-      </c>
-      <c r="F403" t="s">
-        <v>417</v>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6">
+      <c r="A404">
+        <v>2025</v>
+      </c>
+      <c r="B404" t="s">
+        <v>97</v>
+      </c>
+      <c r="C404" t="s">
+        <v>374</v>
+      </c>
+      <c r="D404">
+        <v>253</v>
+      </c>
+      <c r="E404">
+        <v>45.50359712230216</v>
+      </c>
+      <c r="F404" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -8067,16 +8106,16 @@
         <v>97</v>
       </c>
       <c r="C405" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D405">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="E405">
-        <v>35.37414965986395</v>
+        <v>27.69784172661871</v>
       </c>
       <c r="F405" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
     </row>
     <row r="406" spans="1:6">
@@ -8087,36 +8126,16 @@
         <v>97</v>
       </c>
       <c r="C406" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D406">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="E406">
-        <v>26.87074829931973</v>
+        <v>26.79856115107914</v>
       </c>
       <c r="F406" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="407" spans="1:6">
-      <c r="A407">
-        <v>2025</v>
-      </c>
-      <c r="B407" t="s">
-        <v>97</v>
-      </c>
-      <c r="C407" t="s">
-        <v>374</v>
-      </c>
-      <c r="D407">
-        <v>78</v>
-      </c>
-      <c r="E407">
-        <v>26.53061224489796</v>
-      </c>
-      <c r="F407" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -8124,19 +8143,39 @@
         <v>2025</v>
       </c>
       <c r="B408" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C408" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D408">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="E408">
-        <v>10.8843537414966</v>
+        <v>38.71733966745843</v>
       </c>
       <c r="F408" t="s">
-        <v>400</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6">
+      <c r="A409">
+        <v>2025</v>
+      </c>
+      <c r="B409" t="s">
+        <v>98</v>
+      </c>
+      <c r="C409" t="s">
+        <v>378</v>
+      </c>
+      <c r="D409">
+        <v>160</v>
+      </c>
+      <c r="E409">
+        <v>38.00475059382423</v>
+      </c>
+      <c r="F409" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -8147,16 +8186,16 @@
         <v>98</v>
       </c>
       <c r="C410" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D410">
-        <v>549</v>
+        <v>75</v>
       </c>
       <c r="E410">
-        <v>42.99138606108065</v>
+        <v>17.81472684085511</v>
       </c>
       <c r="F410" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -8167,36 +8206,36 @@
         <v>98</v>
       </c>
       <c r="C411" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D411">
-        <v>445</v>
+        <v>23</v>
       </c>
       <c r="E411">
-        <v>34.84729835552075</v>
+        <v>5.463182897862233</v>
       </c>
       <c r="F411" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="412" spans="1:6">
-      <c r="A412">
-        <v>2025</v>
-      </c>
-      <c r="B412" t="s">
-        <v>98</v>
-      </c>
-      <c r="C412" t="s">
-        <v>378</v>
-      </c>
-      <c r="D412">
-        <v>283</v>
-      </c>
-      <c r="E412">
-        <v>22.16131558339859</v>
-      </c>
-      <c r="F412" t="s">
-        <v>415</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6">
+      <c r="A413">
+        <v>2025</v>
+      </c>
+      <c r="B413" t="s">
+        <v>99</v>
+      </c>
+      <c r="C413" t="s">
+        <v>381</v>
+      </c>
+      <c r="D413">
+        <v>156</v>
+      </c>
+      <c r="E413">
+        <v>48</v>
+      </c>
+      <c r="F413" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -8207,16 +8246,16 @@
         <v>99</v>
       </c>
       <c r="C414" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D414">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E414">
-        <v>28.21100917431193</v>
+        <v>40.61538461538461</v>
       </c>
       <c r="F414" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -8227,36 +8266,16 @@
         <v>99</v>
       </c>
       <c r="C415" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D415">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="E415">
-        <v>26.8348623853211</v>
+        <v>11.38461538461539</v>
       </c>
       <c r="F415" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="416" spans="1:6">
-      <c r="A416">
-        <v>2025</v>
-      </c>
-      <c r="B416" t="s">
-        <v>99</v>
-      </c>
-      <c r="C416" t="s">
-        <v>381</v>
-      </c>
-      <c r="D416">
-        <v>106</v>
-      </c>
-      <c r="E416">
-        <v>24.31192660550459</v>
-      </c>
-      <c r="F416" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -8264,19 +8283,39 @@
         <v>2025</v>
       </c>
       <c r="B417" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C417" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D417">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E417">
-        <v>20.64220183486239</v>
+        <v>35.37414965986395</v>
       </c>
       <c r="F417" t="s">
-        <v>415</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6">
+      <c r="A418">
+        <v>2025</v>
+      </c>
+      <c r="B418" t="s">
+        <v>100</v>
+      </c>
+      <c r="C418" t="s">
+        <v>385</v>
+      </c>
+      <c r="D418">
+        <v>79</v>
+      </c>
+      <c r="E418">
+        <v>26.87074829931973</v>
+      </c>
+      <c r="F418" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -8287,16 +8326,16 @@
         <v>100</v>
       </c>
       <c r="C419" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D419">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="E419">
-        <v>45.03464203233256</v>
+        <v>26.53061224489796</v>
       </c>
       <c r="F419" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="420" spans="1:6">
@@ -8307,36 +8346,36 @@
         <v>100</v>
       </c>
       <c r="C420" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D420">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="E420">
-        <v>37.41339491916859</v>
+        <v>10.8843537414966</v>
       </c>
       <c r="F420" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="421" spans="1:6">
-      <c r="A421">
-        <v>2025</v>
-      </c>
-      <c r="B421" t="s">
-        <v>100</v>
-      </c>
-      <c r="C421" t="s">
-        <v>385</v>
-      </c>
-      <c r="D421">
-        <v>76</v>
-      </c>
-      <c r="E421">
-        <v>17.55196304849884</v>
-      </c>
-      <c r="F421" t="s">
-        <v>415</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6">
+      <c r="A422">
+        <v>2025</v>
+      </c>
+      <c r="B422" t="s">
+        <v>101</v>
+      </c>
+      <c r="C422" t="s">
+        <v>388</v>
+      </c>
+      <c r="D422">
+        <v>549</v>
+      </c>
+      <c r="E422">
+        <v>42.99138606108065</v>
+      </c>
+      <c r="F422" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -8347,16 +8386,16 @@
         <v>101</v>
       </c>
       <c r="C423" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D423">
-        <v>315</v>
+        <v>445</v>
       </c>
       <c r="E423">
-        <v>43.09165526675787</v>
+        <v>34.84729835552075</v>
       </c>
       <c r="F423" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
     </row>
     <row r="424" spans="1:6">
@@ -8367,36 +8406,36 @@
         <v>101</v>
       </c>
       <c r="C424" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D424">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="E424">
-        <v>33.78932968536252</v>
+        <v>22.16131558339859</v>
       </c>
       <c r="F424" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="425" spans="1:6">
-      <c r="A425">
-        <v>2025</v>
-      </c>
-      <c r="B425" t="s">
-        <v>101</v>
-      </c>
-      <c r="C425" t="s">
-        <v>388</v>
-      </c>
-      <c r="D425">
-        <v>169</v>
-      </c>
-      <c r="E425">
-        <v>23.11901504787962</v>
-      </c>
-      <c r="F425" t="s">
-        <v>405</v>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6">
+      <c r="A426">
+        <v>2025</v>
+      </c>
+      <c r="B426" t="s">
+        <v>102</v>
+      </c>
+      <c r="C426" t="s">
+        <v>391</v>
+      </c>
+      <c r="D426">
+        <v>123</v>
+      </c>
+      <c r="E426">
+        <v>28.21100917431193</v>
+      </c>
+      <c r="F426" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -8407,16 +8446,16 @@
         <v>102</v>
       </c>
       <c r="C427" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D427">
-        <v>3982</v>
+        <v>117</v>
       </c>
       <c r="E427">
-        <v>29.84112709832134</v>
+        <v>26.8348623853211</v>
       </c>
       <c r="F427" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -8427,16 +8466,16 @@
         <v>102</v>
       </c>
       <c r="C428" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D428">
-        <v>3532</v>
+        <v>106</v>
       </c>
       <c r="E428">
-        <v>26.46882494004796</v>
+        <v>24.31192660550459</v>
       </c>
       <c r="F428" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -8447,36 +8486,36 @@
         <v>102</v>
       </c>
       <c r="C429" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D429">
-        <v>2933</v>
+        <v>90</v>
       </c>
       <c r="E429">
-        <v>21.97991606714628</v>
+        <v>20.64220183486239</v>
       </c>
       <c r="F429" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="430" spans="1:6">
-      <c r="A430">
-        <v>2025</v>
-      </c>
-      <c r="B430" t="s">
-        <v>102</v>
-      </c>
-      <c r="C430" t="s">
-        <v>392</v>
-      </c>
-      <c r="D430">
-        <v>2897</v>
-      </c>
-      <c r="E430">
-        <v>21.71013189448441</v>
-      </c>
-      <c r="F430" t="s">
-        <v>408</v>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6">
+      <c r="A431">
+        <v>2025</v>
+      </c>
+      <c r="B431" t="s">
+        <v>103</v>
+      </c>
+      <c r="C431" t="s">
+        <v>395</v>
+      </c>
+      <c r="D431">
+        <v>195</v>
+      </c>
+      <c r="E431">
+        <v>45.03464203233256</v>
+      </c>
+      <c r="F431" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="432" spans="1:6">
@@ -8487,16 +8526,16 @@
         <v>103</v>
       </c>
       <c r="C432" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D432">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E432">
-        <v>39.84575835475578</v>
+        <v>37.41339491916859</v>
       </c>
       <c r="F432" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -8507,36 +8546,36 @@
         <v>103</v>
       </c>
       <c r="C433" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D433">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="E433">
-        <v>38.30334190231363</v>
+        <v>17.55196304849884</v>
       </c>
       <c r="F433" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="434" spans="1:6">
-      <c r="A434">
-        <v>2025</v>
-      </c>
-      <c r="B434" t="s">
-        <v>103</v>
-      </c>
-      <c r="C434" t="s">
-        <v>395</v>
-      </c>
-      <c r="D434">
-        <v>85</v>
-      </c>
-      <c r="E434">
-        <v>21.85089974293059</v>
-      </c>
-      <c r="F434" t="s">
-        <v>408</v>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6">
+      <c r="A435">
+        <v>2025</v>
+      </c>
+      <c r="B435" t="s">
+        <v>104</v>
+      </c>
+      <c r="C435" t="s">
+        <v>398</v>
+      </c>
+      <c r="D435">
+        <v>315</v>
+      </c>
+      <c r="E435">
+        <v>43.09165526675787</v>
+      </c>
+      <c r="F435" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="436" spans="1:6">
@@ -8547,16 +8586,16 @@
         <v>104</v>
       </c>
       <c r="C436" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D436">
-        <v>328</v>
+        <v>247</v>
       </c>
       <c r="E436">
-        <v>37.27272727272727</v>
+        <v>33.78932968536252</v>
       </c>
       <c r="F436" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -8567,36 +8606,16 @@
         <v>104</v>
       </c>
       <c r="C437" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D437">
-        <v>310</v>
+        <v>169</v>
       </c>
       <c r="E437">
-        <v>35.22727272727273</v>
+        <v>23.11901504787962</v>
       </c>
       <c r="F437" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="438" spans="1:6">
-      <c r="A438">
-        <v>2025</v>
-      </c>
-      <c r="B438" t="s">
-        <v>104</v>
-      </c>
-      <c r="C438" t="s">
-        <v>398</v>
-      </c>
-      <c r="D438">
-        <v>127</v>
-      </c>
-      <c r="E438">
-        <v>14.43181818181818</v>
-      </c>
-      <c r="F438" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -8604,19 +8623,219 @@
         <v>2025</v>
       </c>
       <c r="B439" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C439" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D439">
+        <v>3982</v>
+      </c>
+      <c r="E439">
+        <v>29.84112709832134</v>
+      </c>
+      <c r="F439" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6">
+      <c r="A440">
+        <v>2025</v>
+      </c>
+      <c r="B440" t="s">
+        <v>105</v>
+      </c>
+      <c r="C440" t="s">
+        <v>402</v>
+      </c>
+      <c r="D440">
+        <v>3532</v>
+      </c>
+      <c r="E440">
+        <v>26.46882494004796</v>
+      </c>
+      <c r="F440" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6">
+      <c r="A441">
+        <v>2025</v>
+      </c>
+      <c r="B441" t="s">
+        <v>105</v>
+      </c>
+      <c r="C441" t="s">
+        <v>403</v>
+      </c>
+      <c r="D441">
+        <v>2933</v>
+      </c>
+      <c r="E441">
+        <v>21.97991606714628</v>
+      </c>
+      <c r="F441" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
+      <c r="A442">
+        <v>2025</v>
+      </c>
+      <c r="B442" t="s">
+        <v>105</v>
+      </c>
+      <c r="C442" t="s">
+        <v>404</v>
+      </c>
+      <c r="D442">
+        <v>2897</v>
+      </c>
+      <c r="E442">
+        <v>21.71013189448441</v>
+      </c>
+      <c r="F442" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6">
+      <c r="A444">
+        <v>2025</v>
+      </c>
+      <c r="B444" t="s">
+        <v>106</v>
+      </c>
+      <c r="C444" t="s">
+        <v>405</v>
+      </c>
+      <c r="D444">
+        <v>155</v>
+      </c>
+      <c r="E444">
+        <v>39.84575835475578</v>
+      </c>
+      <c r="F444" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6">
+      <c r="A445">
+        <v>2025</v>
+      </c>
+      <c r="B445" t="s">
+        <v>106</v>
+      </c>
+      <c r="C445" t="s">
+        <v>406</v>
+      </c>
+      <c r="D445">
+        <v>149</v>
+      </c>
+      <c r="E445">
+        <v>38.30334190231363</v>
+      </c>
+      <c r="F445" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6">
+      <c r="A446">
+        <v>2025</v>
+      </c>
+      <c r="B446" t="s">
+        <v>106</v>
+      </c>
+      <c r="C446" t="s">
+        <v>407</v>
+      </c>
+      <c r="D446">
+        <v>85</v>
+      </c>
+      <c r="E446">
+        <v>21.85089974293059</v>
+      </c>
+      <c r="F446" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6">
+      <c r="A448">
+        <v>2025</v>
+      </c>
+      <c r="B448" t="s">
+        <v>107</v>
+      </c>
+      <c r="C448" t="s">
+        <v>408</v>
+      </c>
+      <c r="D448">
+        <v>328</v>
+      </c>
+      <c r="E448">
+        <v>37.27272727272727</v>
+      </c>
+      <c r="F448" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6">
+      <c r="A449">
+        <v>2025</v>
+      </c>
+      <c r="B449" t="s">
+        <v>107</v>
+      </c>
+      <c r="C449" t="s">
+        <v>409</v>
+      </c>
+      <c r="D449">
+        <v>310</v>
+      </c>
+      <c r="E449">
+        <v>35.22727272727273</v>
+      </c>
+      <c r="F449" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
+      <c r="A450">
+        <v>2025</v>
+      </c>
+      <c r="B450" t="s">
+        <v>107</v>
+      </c>
+      <c r="C450" t="s">
+        <v>410</v>
+      </c>
+      <c r="D450">
+        <v>127</v>
+      </c>
+      <c r="E450">
+        <v>14.43181818181818</v>
+      </c>
+      <c r="F450" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
+      <c r="A451">
+        <v>2025</v>
+      </c>
+      <c r="B451" t="s">
+        <v>107</v>
+      </c>
+      <c r="C451" t="s">
+        <v>411</v>
+      </c>
+      <c r="D451">
         <v>115</v>
       </c>
-      <c r="E439">
+      <c r="E451">
         <v>13.06818181818182</v>
       </c>
-      <c r="F439" t="s">
-        <v>408</v>
+      <c r="F451" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="436">
   <si>
     <t>Year</t>
   </si>
@@ -203,6 +203,9 @@
     <t>REP Commissioner Bethlehem Twsp 1st Ward</t>
   </si>
   <si>
+    <t>REP MAGISTERIAL DISTRICT JUDGE 02-3-04</t>
+  </si>
+  <si>
     <t>REP MAGISTERIAL DISTRICT JUDGE 07-1-10</t>
   </si>
   <si>
@@ -842,6 +845,15 @@
     <t>RODMAN LAW</t>
   </si>
   <si>
+    <t>BILL MANKIN II</t>
+  </si>
+  <si>
+    <t>RICHARD ALLEN BUCK</t>
+  </si>
+  <si>
+    <t>MELISSA ANDERSON</t>
+  </si>
+  <si>
     <t>JOHN GALLOWAY</t>
   </si>
   <si>
@@ -1299,6 +1311,9 @@
   </si>
   <si>
     <t>Berks County (Reading + boroughs + townships)</t>
+  </si>
+  <si>
+    <t>Lancaster County (Lancaster City + boroughs + townships)</t>
   </si>
   <si>
     <t>Lycoming County (Williamsport + boroughs + townships)</t>
@@ -1755,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F451"/>
+  <dimension ref="A1:F455"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1786,7 +1801,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2">
         <v>799</v>
@@ -1795,7 +1810,7 @@
         <v>35.94242015294647</v>
       </c>
       <c r="F2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1806,7 +1821,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D3">
         <v>713</v>
@@ -1815,7 +1830,7 @@
         <v>32.07377417903734</v>
       </c>
       <c r="F3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1826,7 +1841,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D4">
         <v>355</v>
@@ -1835,7 +1850,7 @@
         <v>15.96941070625281</v>
       </c>
       <c r="F4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1846,7 +1861,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>190</v>
@@ -1855,7 +1870,7 @@
         <v>8.547008547008547</v>
       </c>
       <c r="F5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1866,7 +1881,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D6">
         <v>166</v>
@@ -1875,7 +1890,7 @@
         <v>7.467386414754835</v>
       </c>
       <c r="F6" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1886,7 +1901,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>807</v>
@@ -1895,7 +1910,7 @@
         <v>42.87991498405951</v>
       </c>
       <c r="F8" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1906,7 +1921,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D9">
         <v>704</v>
@@ -1915,7 +1930,7 @@
         <v>37.40701381509033</v>
       </c>
       <c r="F9" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1926,7 +1941,7 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D10">
         <v>371</v>
@@ -1935,7 +1950,7 @@
         <v>19.71307120085016</v>
       </c>
       <c r="F10" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1946,7 +1961,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12">
         <v>23009</v>
@@ -1955,7 +1970,7 @@
         <v>49.36282502359907</v>
       </c>
       <c r="F12" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1966,7 +1981,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <v>10398</v>
@@ -1975,7 +1990,7 @@
         <v>22.30756028490518</v>
       </c>
       <c r="F13" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1986,7 +2001,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D14">
         <v>6676</v>
@@ -1995,7 +2010,7 @@
         <v>14.32249206212992</v>
       </c>
       <c r="F14" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2006,7 +2021,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D15">
         <v>6529</v>
@@ -2015,7 +2030,7 @@
         <v>14.00712262936583</v>
       </c>
       <c r="F15" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2026,7 +2041,7 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17">
         <v>15761</v>
@@ -2035,7 +2050,7 @@
         <v>32.71613907628438</v>
       </c>
       <c r="F17" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2046,7 +2061,7 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18">
         <v>12780</v>
@@ -2055,7 +2070,7 @@
         <v>26.52828230409964</v>
       </c>
       <c r="F18" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2066,7 +2081,7 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D19">
         <v>10691</v>
@@ -2075,7 +2090,7 @@
         <v>22.19200830306175</v>
       </c>
       <c r="F19" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2086,7 +2101,7 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D20">
         <v>8943</v>
@@ -2095,7 +2110,7 @@
         <v>18.56357031655423</v>
       </c>
       <c r="F20" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2106,7 +2121,7 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D22">
         <v>133</v>
@@ -2115,7 +2130,7 @@
         <v>41.95583596214511</v>
       </c>
       <c r="F22" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2126,7 +2141,7 @@
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D23">
         <v>121</v>
@@ -2135,7 +2150,7 @@
         <v>38.17034700315457</v>
       </c>
       <c r="F23" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2146,7 +2161,7 @@
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D24">
         <v>63</v>
@@ -2155,7 +2170,7 @@
         <v>19.87381703470032</v>
       </c>
       <c r="F24" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2166,7 +2181,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D26">
         <v>22897</v>
@@ -2175,7 +2190,7 @@
         <v>47.76078930351891</v>
       </c>
       <c r="F26" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2186,7 +2201,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D27">
         <v>8137</v>
@@ -2195,7 +2210,7 @@
         <v>16.97294591268434</v>
       </c>
       <c r="F27" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2206,7 +2221,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D28">
         <v>7234</v>
@@ -2215,7 +2230,7 @@
         <v>15.08938069710686</v>
       </c>
       <c r="F28" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2226,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D29">
         <v>5373</v>
@@ -2235,7 +2250,7 @@
         <v>11.20752591727332</v>
       </c>
       <c r="F29" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2246,7 +2261,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D30">
         <v>4300</v>
@@ -2255,7 +2270,7 @@
         <v>8.969358169416575</v>
       </c>
       <c r="F30" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2266,7 +2281,7 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D32">
         <v>364</v>
@@ -2275,7 +2290,7 @@
         <v>39.09774436090225</v>
       </c>
       <c r="F32" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2286,7 +2301,7 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D33">
         <v>341</v>
@@ -2295,7 +2310,7 @@
         <v>36.62728249194414</v>
       </c>
       <c r="F33" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2306,7 +2321,7 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D34">
         <v>226</v>
@@ -2315,7 +2330,7 @@
         <v>24.2749731471536</v>
       </c>
       <c r="F34" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2326,7 +2341,7 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D36">
         <v>1283</v>
@@ -2335,7 +2350,7 @@
         <v>40.52432090966519</v>
       </c>
       <c r="F36" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2346,7 +2361,7 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D37">
         <v>954</v>
@@ -2355,7 +2370,7 @@
         <v>30.13265950726469</v>
       </c>
       <c r="F37" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2366,7 +2381,7 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D38">
         <v>746</v>
@@ -2375,7 +2390,7 @@
         <v>23.56285533796589</v>
       </c>
       <c r="F38" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2386,7 +2401,7 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D39">
         <v>183</v>
@@ -2395,7 +2410,7 @@
         <v>5.780164245104232</v>
       </c>
       <c r="F39" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2406,7 +2421,7 @@
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D41">
         <v>1446</v>
@@ -2415,7 +2430,7 @@
         <v>41.84027777777778</v>
       </c>
       <c r="F41" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2426,7 +2441,7 @@
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D42">
         <v>1091</v>
@@ -2435,7 +2450,7 @@
         <v>31.56828703703703</v>
       </c>
       <c r="F42" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2446,7 +2461,7 @@
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D43">
         <v>919</v>
@@ -2455,7 +2470,7 @@
         <v>26.59143518518519</v>
       </c>
       <c r="F43" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2466,7 +2481,7 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D45">
         <v>8769</v>
@@ -2475,7 +2490,7 @@
         <v>32.16683173764719</v>
       </c>
       <c r="F45" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2486,7 +2501,7 @@
         <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D46">
         <v>8551</v>
@@ -2495,7 +2510,7 @@
         <v>31.36715454312021</v>
       </c>
       <c r="F46" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2506,7 +2521,7 @@
         <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D47">
         <v>5669</v>
@@ -2515,7 +2530,7 @@
         <v>20.79527530171307</v>
       </c>
       <c r="F47" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2526,7 +2541,7 @@
         <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D48">
         <v>4272</v>
@@ -2535,7 +2550,7 @@
         <v>15.67073841751953</v>
       </c>
       <c r="F48" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2546,7 +2561,7 @@
         <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D50">
         <v>3420</v>
@@ -2555,7 +2570,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F50" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2566,7 +2581,7 @@
         <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D51">
         <v>2391</v>
@@ -2575,7 +2590,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F51" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2586,7 +2601,7 @@
         <v>21</v>
       </c>
       <c r="C52" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D52">
         <v>2184</v>
@@ -2595,7 +2610,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F52" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2606,7 +2621,7 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D54">
         <v>572</v>
@@ -2615,7 +2630,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F54" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2626,7 +2641,7 @@
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D55">
         <v>380</v>
@@ -2635,7 +2650,7 @@
         <v>31.25</v>
       </c>
       <c r="F55" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2646,7 +2661,7 @@
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D56">
         <v>264</v>
@@ -2655,7 +2670,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F56" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2666,7 +2681,7 @@
         <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D58">
         <v>177</v>
@@ -2675,7 +2690,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F58" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2686,7 +2701,7 @@
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D59">
         <v>141</v>
@@ -2695,7 +2710,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F59" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2706,7 +2721,7 @@
         <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D60">
         <v>81</v>
@@ -2715,7 +2730,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F60" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2726,7 +2741,7 @@
         <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D61">
         <v>44</v>
@@ -2735,7 +2750,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F61" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2746,7 +2761,7 @@
         <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D63">
         <v>1471</v>
@@ -2755,7 +2770,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F63" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2766,7 +2781,7 @@
         <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D64">
         <v>1247</v>
@@ -2775,7 +2790,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F64" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2786,7 +2801,7 @@
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D65">
         <v>616</v>
@@ -2795,7 +2810,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F65" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2806,7 +2821,7 @@
         <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D67">
         <v>1183</v>
@@ -2815,7 +2830,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F67" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2826,7 +2841,7 @@
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D68">
         <v>1177</v>
@@ -2835,7 +2850,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F68" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2846,7 +2861,7 @@
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D69">
         <v>373</v>
@@ -2855,7 +2870,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F69" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2866,7 +2881,7 @@
         <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D70">
         <v>270</v>
@@ -2875,7 +2890,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F70" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2886,7 +2901,7 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D72">
         <v>2064</v>
@@ -2895,7 +2910,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F72" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2906,7 +2921,7 @@
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D73">
         <v>1942</v>
@@ -2915,7 +2930,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F73" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2926,7 +2941,7 @@
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D74">
         <v>1927</v>
@@ -2935,7 +2950,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F74" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2946,7 +2961,7 @@
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D75">
         <v>1817</v>
@@ -2955,7 +2970,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F75" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2966,7 +2981,7 @@
         <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D77">
         <v>237</v>
@@ -2975,7 +2990,7 @@
         <v>32.20108695652174</v>
       </c>
       <c r="F77" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2986,7 +3001,7 @@
         <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D78">
         <v>234</v>
@@ -2995,7 +3010,7 @@
         <v>31.79347826086957</v>
       </c>
       <c r="F78" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3006,7 +3021,7 @@
         <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D79">
         <v>148</v>
@@ -3015,7 +3030,7 @@
         <v>20.10869565217391</v>
       </c>
       <c r="F79" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3026,7 +3041,7 @@
         <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D80">
         <v>90</v>
@@ -3035,7 +3050,7 @@
         <v>12.22826086956522</v>
       </c>
       <c r="F80" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3046,7 +3061,7 @@
         <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D81">
         <v>27</v>
@@ -3055,7 +3070,7 @@
         <v>3.668478260869565</v>
       </c>
       <c r="F81" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3066,7 +3081,7 @@
         <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D83">
         <v>212</v>
@@ -3075,7 +3090,7 @@
         <v>40.15151515151515</v>
       </c>
       <c r="F83" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3086,7 +3101,7 @@
         <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D84">
         <v>186</v>
@@ -3095,7 +3110,7 @@
         <v>35.22727272727273</v>
       </c>
       <c r="F84" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3106,7 +3121,7 @@
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D85">
         <v>130</v>
@@ -3115,7 +3130,7 @@
         <v>24.62121212121212</v>
       </c>
       <c r="F85" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3126,7 +3141,7 @@
         <v>29</v>
       </c>
       <c r="C87" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D87">
         <v>149</v>
@@ -3135,7 +3150,7 @@
         <v>44.61077844311377</v>
       </c>
       <c r="F87" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3146,7 +3161,7 @@
         <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D88">
         <v>115</v>
@@ -3155,7 +3170,7 @@
         <v>34.4311377245509</v>
       </c>
       <c r="F88" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3166,7 +3181,7 @@
         <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D89">
         <v>70</v>
@@ -3175,7 +3190,7 @@
         <v>20.95808383233533</v>
       </c>
       <c r="F89" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3186,7 +3201,7 @@
         <v>30</v>
       </c>
       <c r="C91" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D91">
         <v>138</v>
@@ -3195,7 +3210,7 @@
         <v>40.70796460176992</v>
       </c>
       <c r="F91" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3206,7 +3221,7 @@
         <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D92">
         <v>127</v>
@@ -3215,7 +3230,7 @@
         <v>37.46312684365782</v>
       </c>
       <c r="F92" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3226,7 +3241,7 @@
         <v>30</v>
       </c>
       <c r="C93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D93">
         <v>74</v>
@@ -3235,7 +3250,7 @@
         <v>21.82890855457227</v>
       </c>
       <c r="F93" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3246,7 +3261,7 @@
         <v>31</v>
       </c>
       <c r="C95" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D95">
         <v>186</v>
@@ -3255,7 +3270,7 @@
         <v>40</v>
       </c>
       <c r="F95" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3266,7 +3281,7 @@
         <v>31</v>
       </c>
       <c r="C96" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D96">
         <v>96</v>
@@ -3275,7 +3290,7 @@
         <v>20.64516129032258</v>
       </c>
       <c r="F96" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3286,7 +3301,7 @@
         <v>31</v>
       </c>
       <c r="C97" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D97">
         <v>95</v>
@@ -3295,7 +3310,7 @@
         <v>20.43010752688172</v>
       </c>
       <c r="F97" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3306,7 +3321,7 @@
         <v>31</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D98">
         <v>88</v>
@@ -3315,7 +3330,7 @@
         <v>18.9247311827957</v>
       </c>
       <c r="F98" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3326,7 +3341,7 @@
         <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D100">
         <v>154</v>
@@ -3335,7 +3350,7 @@
         <v>39.58868894601542</v>
       </c>
       <c r="F100" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3346,7 +3361,7 @@
         <v>32</v>
       </c>
       <c r="C101" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D101">
         <v>144</v>
@@ -3355,7 +3370,7 @@
         <v>37.01799485861182</v>
       </c>
       <c r="F101" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3366,7 +3381,7 @@
         <v>32</v>
       </c>
       <c r="C102" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D102">
         <v>91</v>
@@ -3375,7 +3390,7 @@
         <v>23.39331619537275</v>
       </c>
       <c r="F102" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3386,7 +3401,7 @@
         <v>33</v>
       </c>
       <c r="C104" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D104">
         <v>203</v>
@@ -3395,7 +3410,7 @@
         <v>49.63325183374083</v>
       </c>
       <c r="F104" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3406,7 +3421,7 @@
         <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D105">
         <v>127</v>
@@ -3415,7 +3430,7 @@
         <v>31.05134474327628</v>
       </c>
       <c r="F105" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3426,7 +3441,7 @@
         <v>33</v>
       </c>
       <c r="C106" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D106">
         <v>79</v>
@@ -3435,7 +3450,7 @@
         <v>19.31540342298289</v>
       </c>
       <c r="F106" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3446,7 +3461,7 @@
         <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D108">
         <v>293</v>
@@ -3455,7 +3470,7 @@
         <v>37.80645161290322</v>
       </c>
       <c r="F108" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3466,7 +3481,7 @@
         <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D109">
         <v>241</v>
@@ -3475,7 +3490,7 @@
         <v>31.09677419354839</v>
       </c>
       <c r="F109" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3486,7 +3501,7 @@
         <v>34</v>
       </c>
       <c r="C110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D110">
         <v>125</v>
@@ -3495,7 +3510,7 @@
         <v>16.12903225806452</v>
       </c>
       <c r="F110" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3506,7 +3521,7 @@
         <v>34</v>
       </c>
       <c r="C111" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D111">
         <v>116</v>
@@ -3515,7 +3530,7 @@
         <v>14.96774193548387</v>
       </c>
       <c r="F111" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3526,7 +3541,7 @@
         <v>35</v>
       </c>
       <c r="C113" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D113">
         <v>588</v>
@@ -3535,7 +3550,7 @@
         <v>48.83720930232558</v>
       </c>
       <c r="F113" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3546,7 +3561,7 @@
         <v>35</v>
       </c>
       <c r="C114" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D114">
         <v>379</v>
@@ -3555,7 +3570,7 @@
         <v>31.47840531561462</v>
       </c>
       <c r="F114" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3566,7 +3581,7 @@
         <v>35</v>
       </c>
       <c r="C115" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D115">
         <v>237</v>
@@ -3575,7 +3590,7 @@
         <v>19.6843853820598</v>
       </c>
       <c r="F115" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3586,7 +3601,7 @@
         <v>36</v>
       </c>
       <c r="C117" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D117">
         <v>522</v>
@@ -3595,7 +3610,7 @@
         <v>48.33333333333334</v>
       </c>
       <c r="F117" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3606,7 +3621,7 @@
         <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D118">
         <v>331</v>
@@ -3615,7 +3630,7 @@
         <v>30.64814814814815</v>
       </c>
       <c r="F118" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3626,7 +3641,7 @@
         <v>36</v>
       </c>
       <c r="C119" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D119">
         <v>227</v>
@@ -3635,7 +3650,7 @@
         <v>21.01851851851852</v>
       </c>
       <c r="F119" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3646,7 +3661,7 @@
         <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D121">
         <v>4922</v>
@@ -3655,7 +3670,7 @@
         <v>41.68713475057169</v>
       </c>
       <c r="F121" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3666,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="C122" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D122">
         <v>4820</v>
@@ -3675,7 +3690,7 @@
         <v>40.82324045058016</v>
       </c>
       <c r="F122" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3686,7 +3701,7 @@
         <v>37</v>
       </c>
       <c r="C123" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D123">
         <v>2065</v>
@@ -3695,7 +3710,7 @@
         <v>17.48962479884814</v>
       </c>
       <c r="F123" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3706,7 +3721,7 @@
         <v>38</v>
       </c>
       <c r="C125" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D125">
         <v>490</v>
@@ -3715,7 +3730,7 @@
         <v>47.43465634075508</v>
       </c>
       <c r="F125" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3726,7 +3741,7 @@
         <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D126">
         <v>274</v>
@@ -3735,7 +3750,7 @@
         <v>26.52468538238141</v>
       </c>
       <c r="F126" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3746,7 +3761,7 @@
         <v>38</v>
       </c>
       <c r="C127" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D127">
         <v>269</v>
@@ -3755,7 +3770,7 @@
         <v>26.0406582768635</v>
       </c>
       <c r="F127" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3766,7 +3781,7 @@
         <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D129">
         <v>1165</v>
@@ -3775,7 +3790,7 @@
         <v>47.31925264012997</v>
       </c>
       <c r="F129" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3786,7 +3801,7 @@
         <v>39</v>
       </c>
       <c r="C130" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D130">
         <v>898</v>
@@ -3795,7 +3810,7 @@
         <v>36.47441104792851</v>
       </c>
       <c r="F130" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3806,7 +3821,7 @@
         <v>39</v>
       </c>
       <c r="C131" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D131">
         <v>211</v>
@@ -3815,7 +3830,7 @@
         <v>8.570268074735987</v>
       </c>
       <c r="F131" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3826,7 +3841,7 @@
         <v>39</v>
       </c>
       <c r="C132" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D132">
         <v>188</v>
@@ -3835,7 +3850,7 @@
         <v>7.636068237205524</v>
       </c>
       <c r="F132" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3846,7 +3861,7 @@
         <v>40</v>
       </c>
       <c r="C134" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D134">
         <v>1281</v>
@@ -3855,7 +3870,7 @@
         <v>43.88489208633094</v>
       </c>
       <c r="F134" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3866,7 +3881,7 @@
         <v>40</v>
       </c>
       <c r="C135" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D135">
         <v>924</v>
@@ -3875,7 +3890,7 @@
         <v>31.6546762589928</v>
       </c>
       <c r="F135" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3886,7 +3901,7 @@
         <v>40</v>
       </c>
       <c r="C136" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D136">
         <v>714</v>
@@ -3895,7 +3910,7 @@
         <v>24.46043165467626</v>
       </c>
       <c r="F136" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3906,7 +3921,7 @@
         <v>41</v>
       </c>
       <c r="C138" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D138">
         <v>999</v>
@@ -3915,7 +3930,7 @@
         <v>49.47994056463596</v>
       </c>
       <c r="F138" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3926,7 +3941,7 @@
         <v>41</v>
       </c>
       <c r="C139" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D139">
         <v>629</v>
@@ -3935,7 +3950,7 @@
         <v>31.15403665180783</v>
       </c>
       <c r="F139" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3946,7 +3961,7 @@
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D140">
         <v>391</v>
@@ -3955,7 +3970,7 @@
         <v>19.36602278355622</v>
       </c>
       <c r="F140" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3966,7 +3981,7 @@
         <v>42</v>
       </c>
       <c r="C142" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D142">
         <v>1779</v>
@@ -3975,7 +3990,7 @@
         <v>46.82811266122664</v>
       </c>
       <c r="F142" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3986,7 +4001,7 @@
         <v>42</v>
       </c>
       <c r="C143" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D143">
         <v>1349</v>
@@ -3995,7 +4010,7 @@
         <v>35.50934456435904</v>
       </c>
       <c r="F143" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4006,7 +4021,7 @@
         <v>42</v>
       </c>
       <c r="C144" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D144">
         <v>671</v>
@@ -4015,7 +4030,7 @@
         <v>17.66254277441432</v>
       </c>
       <c r="F144" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4026,7 +4041,7 @@
         <v>43</v>
       </c>
       <c r="C146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D146">
         <v>253</v>
@@ -4035,7 +4050,7 @@
         <v>37.09677419354838</v>
       </c>
       <c r="F146" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4046,7 +4061,7 @@
         <v>43</v>
       </c>
       <c r="C147" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D147">
         <v>224</v>
@@ -4055,7 +4070,7 @@
         <v>32.84457478005865</v>
       </c>
       <c r="F147" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4066,7 +4081,7 @@
         <v>43</v>
       </c>
       <c r="C148" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D148">
         <v>122</v>
@@ -4075,7 +4090,7 @@
         <v>17.88856304985337</v>
       </c>
       <c r="F148" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4086,7 +4101,7 @@
         <v>43</v>
       </c>
       <c r="C149" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D149">
         <v>60</v>
@@ -4095,7 +4110,7 @@
         <v>8.797653958944283</v>
       </c>
       <c r="F149" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4106,7 +4121,7 @@
         <v>43</v>
       </c>
       <c r="C150" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D150">
         <v>23</v>
@@ -4115,7 +4130,7 @@
         <v>3.372434017595308</v>
       </c>
       <c r="F150" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4126,7 +4141,7 @@
         <v>44</v>
       </c>
       <c r="C152" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D152">
         <v>917</v>
@@ -4135,7 +4150,7 @@
         <v>36.31683168316832</v>
       </c>
       <c r="F152" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4146,7 +4161,7 @@
         <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D153">
         <v>706</v>
@@ -4155,7 +4170,7 @@
         <v>27.96039603960396</v>
       </c>
       <c r="F153" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4166,7 +4181,7 @@
         <v>44</v>
       </c>
       <c r="C154" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D154">
         <v>578</v>
@@ -4175,7 +4190,7 @@
         <v>22.89108910891089</v>
       </c>
       <c r="F154" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4186,7 +4201,7 @@
         <v>44</v>
       </c>
       <c r="C155" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D155">
         <v>324</v>
@@ -4195,7 +4210,7 @@
         <v>12.83168316831683</v>
       </c>
       <c r="F155" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4206,7 +4221,7 @@
         <v>45</v>
       </c>
       <c r="C157" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D157">
         <v>149</v>
@@ -4215,7 +4230,7 @@
         <v>41.38888888888889</v>
       </c>
       <c r="F157" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4226,7 +4241,7 @@
         <v>45</v>
       </c>
       <c r="C158" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D158">
         <v>113</v>
@@ -4235,7 +4250,7 @@
         <v>31.38888888888889</v>
       </c>
       <c r="F158" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4246,7 +4261,7 @@
         <v>45</v>
       </c>
       <c r="C159" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D159">
         <v>59</v>
@@ -4255,7 +4270,7 @@
         <v>16.38888888888889</v>
       </c>
       <c r="F159" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4266,7 +4281,7 @@
         <v>45</v>
       </c>
       <c r="C160" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D160">
         <v>39</v>
@@ -4275,7 +4290,7 @@
         <v>10.83333333333333</v>
       </c>
       <c r="F160" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4286,7 +4301,7 @@
         <v>46</v>
       </c>
       <c r="C162" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D162">
         <v>179</v>
@@ -4295,7 +4310,7 @@
         <v>45.31645569620253</v>
       </c>
       <c r="F162" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4306,7 +4321,7 @@
         <v>46</v>
       </c>
       <c r="C163" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D163">
         <v>110</v>
@@ -4315,7 +4330,7 @@
         <v>27.84810126582278</v>
       </c>
       <c r="F163" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4326,7 +4341,7 @@
         <v>46</v>
       </c>
       <c r="C164" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D164">
         <v>106</v>
@@ -4335,7 +4350,7 @@
         <v>26.83544303797468</v>
       </c>
       <c r="F164" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -4346,7 +4361,7 @@
         <v>47</v>
       </c>
       <c r="C166" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D166">
         <v>276</v>
@@ -4355,7 +4370,7 @@
         <v>47.01873935264054</v>
       </c>
       <c r="F166" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -4366,7 +4381,7 @@
         <v>47</v>
       </c>
       <c r="C167" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D167">
         <v>226</v>
@@ -4375,7 +4390,7 @@
         <v>38.50085178875639</v>
       </c>
       <c r="F167" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -4386,7 +4401,7 @@
         <v>47</v>
       </c>
       <c r="C168" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D168">
         <v>85</v>
@@ -4395,7 +4410,7 @@
         <v>14.48040885860307</v>
       </c>
       <c r="F168" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -4406,7 +4421,7 @@
         <v>48</v>
       </c>
       <c r="C170" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D170">
         <v>636</v>
@@ -4415,7 +4430,7 @@
         <v>41.24513618677042</v>
       </c>
       <c r="F170" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -4426,7 +4441,7 @@
         <v>48</v>
       </c>
       <c r="C171" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D171">
         <v>544</v>
@@ -4435,7 +4450,7 @@
         <v>35.27885862516213</v>
       </c>
       <c r="F171" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -4446,7 +4461,7 @@
         <v>48</v>
       </c>
       <c r="C172" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D172">
         <v>362</v>
@@ -4455,7 +4470,7 @@
         <v>23.47600518806744</v>
       </c>
       <c r="F172" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4466,7 +4481,7 @@
         <v>49</v>
       </c>
       <c r="C174" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D174">
         <v>104</v>
@@ -4475,7 +4490,7 @@
         <v>38.95131086142322</v>
       </c>
       <c r="F174" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4486,7 +4501,7 @@
         <v>49</v>
       </c>
       <c r="C175" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D175">
         <v>100</v>
@@ -4495,7 +4510,7 @@
         <v>37.45318352059925</v>
       </c>
       <c r="F175" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4506,7 +4521,7 @@
         <v>49</v>
       </c>
       <c r="C176" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D176">
         <v>63</v>
@@ -4515,7 +4530,7 @@
         <v>23.59550561797753</v>
       </c>
       <c r="F176" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4526,7 +4541,7 @@
         <v>50</v>
       </c>
       <c r="C178" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D178">
         <v>1206</v>
@@ -4535,7 +4550,7 @@
         <v>37.08487084870848</v>
       </c>
       <c r="F178" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4546,7 +4561,7 @@
         <v>50</v>
       </c>
       <c r="C179" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D179">
         <v>1121</v>
@@ -4555,7 +4570,7 @@
         <v>34.47109471094711</v>
       </c>
       <c r="F179" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4566,7 +4581,7 @@
         <v>50</v>
       </c>
       <c r="C180" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D180">
         <v>925</v>
@@ -4575,7 +4590,7 @@
         <v>28.4440344403444</v>
       </c>
       <c r="F180" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -4586,7 +4601,7 @@
         <v>51</v>
       </c>
       <c r="C182" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D182">
         <v>882</v>
@@ -4595,7 +4610,7 @@
         <v>45.60496380558428</v>
       </c>
       <c r="F182" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -4606,7 +4621,7 @@
         <v>51</v>
       </c>
       <c r="C183" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D183">
         <v>502</v>
@@ -4615,7 +4630,7 @@
         <v>25.95656670113754</v>
       </c>
       <c r="F183" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4626,7 +4641,7 @@
         <v>51</v>
       </c>
       <c r="C184" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D184">
         <v>399</v>
@@ -4635,7 +4650,7 @@
         <v>20.63081695966908</v>
       </c>
       <c r="F184" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4646,7 +4661,7 @@
         <v>51</v>
       </c>
       <c r="C185" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D185">
         <v>151</v>
@@ -4655,7 +4670,7 @@
         <v>7.807652533609101</v>
       </c>
       <c r="F185" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4666,7 +4681,7 @@
         <v>52</v>
       </c>
       <c r="C187" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D187">
         <v>665</v>
@@ -4675,7 +4690,7 @@
         <v>39.98797354179194</v>
       </c>
       <c r="F187" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4686,7 +4701,7 @@
         <v>52</v>
       </c>
       <c r="C188" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D188">
         <v>429</v>
@@ -4695,7 +4710,7 @@
         <v>25.79675285628382</v>
       </c>
       <c r="F188" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -4706,7 +4721,7 @@
         <v>52</v>
       </c>
       <c r="C189" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D189">
         <v>308</v>
@@ -4715,7 +4730,7 @@
         <v>18.5207456404089</v>
       </c>
       <c r="F189" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4726,7 +4741,7 @@
         <v>52</v>
       </c>
       <c r="C190" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D190">
         <v>153</v>
@@ -4735,7 +4750,7 @@
         <v>9.20024052916416</v>
       </c>
       <c r="F190" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4746,7 +4761,7 @@
         <v>52</v>
       </c>
       <c r="C191" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D191">
         <v>108</v>
@@ -4755,7 +4770,7 @@
         <v>6.494287432351173</v>
       </c>
       <c r="F191" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4766,7 +4781,7 @@
         <v>53</v>
       </c>
       <c r="C193" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D193">
         <v>445</v>
@@ -4775,7 +4790,7 @@
         <v>43.28793774319066</v>
       </c>
       <c r="F193" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4786,7 +4801,7 @@
         <v>53</v>
       </c>
       <c r="C194" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D194">
         <v>353</v>
@@ -4795,7 +4810,7 @@
         <v>34.33852140077821</v>
       </c>
       <c r="F194" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4806,7 +4821,7 @@
         <v>53</v>
       </c>
       <c r="C195" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D195">
         <v>230</v>
@@ -4815,7 +4830,7 @@
         <v>22.37354085603113</v>
       </c>
       <c r="F195" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4826,7 +4841,7 @@
         <v>54</v>
       </c>
       <c r="C197" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D197">
         <v>684</v>
@@ -4835,7 +4850,7 @@
         <v>46.94577899794098</v>
       </c>
       <c r="F197" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4846,7 +4861,7 @@
         <v>54</v>
       </c>
       <c r="C198" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D198">
         <v>395</v>
@@ -4855,7 +4870,7 @@
         <v>27.1105010295127</v>
       </c>
       <c r="F198" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4866,7 +4881,7 @@
         <v>54</v>
       </c>
       <c r="C199" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D199">
         <v>378</v>
@@ -4875,7 +4890,7 @@
         <v>25.94371997254633</v>
       </c>
       <c r="F199" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4886,7 +4901,7 @@
         <v>55</v>
       </c>
       <c r="C201" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D201">
         <v>828</v>
@@ -4895,7 +4910,7 @@
         <v>36.71840354767184</v>
       </c>
       <c r="F201" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4906,7 +4921,7 @@
         <v>55</v>
       </c>
       <c r="C202" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D202">
         <v>524</v>
@@ -4915,7 +4930,7 @@
         <v>23.23725055432372</v>
       </c>
       <c r="F202" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4926,7 +4941,7 @@
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D203">
         <v>485</v>
@@ -4935,7 +4950,7 @@
         <v>21.50776053215078</v>
       </c>
       <c r="F203" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4946,7 +4961,7 @@
         <v>55</v>
       </c>
       <c r="C204" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D204">
         <v>261</v>
@@ -4955,7 +4970,7 @@
         <v>11.57427937915743</v>
       </c>
       <c r="F204" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4966,7 +4981,7 @@
         <v>55</v>
       </c>
       <c r="C205" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D205">
         <v>157</v>
@@ -4975,7 +4990,7 @@
         <v>6.962305986696231</v>
       </c>
       <c r="F205" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4986,7 +5001,7 @@
         <v>56</v>
       </c>
       <c r="C207" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D207">
         <v>584</v>
@@ -4995,7 +5010,7 @@
         <v>43.90977443609022</v>
       </c>
       <c r="F207" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -5006,7 +5021,7 @@
         <v>56</v>
       </c>
       <c r="C208" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D208">
         <v>388</v>
@@ -5015,7 +5030,7 @@
         <v>29.17293233082707</v>
       </c>
       <c r="F208" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -5026,7 +5041,7 @@
         <v>56</v>
       </c>
       <c r="C209" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D209">
         <v>358</v>
@@ -5035,7 +5050,7 @@
         <v>26.91729323308271</v>
       </c>
       <c r="F209" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -5046,7 +5061,7 @@
         <v>57</v>
       </c>
       <c r="C211" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D211">
         <v>634</v>
@@ -5055,7 +5070,7 @@
         <v>45.67723342939482</v>
       </c>
       <c r="F211" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -5066,7 +5081,7 @@
         <v>57</v>
       </c>
       <c r="C212" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D212">
         <v>298</v>
@@ -5075,7 +5090,7 @@
         <v>21.46974063400576</v>
       </c>
       <c r="F212" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -5086,7 +5101,7 @@
         <v>57</v>
       </c>
       <c r="C213" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D213">
         <v>246</v>
@@ -5095,7 +5110,7 @@
         <v>17.72334293948127</v>
       </c>
       <c r="F213" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -5106,7 +5121,7 @@
         <v>57</v>
       </c>
       <c r="C214" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D214">
         <v>210</v>
@@ -5115,7 +5130,7 @@
         <v>15.12968299711815</v>
       </c>
       <c r="F214" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -5126,7 +5141,7 @@
         <v>58</v>
       </c>
       <c r="C216" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D216">
         <v>294</v>
@@ -5135,7 +5150,7 @@
         <v>38.33116036505867</v>
       </c>
       <c r="F216" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -5146,7 +5161,7 @@
         <v>58</v>
       </c>
       <c r="C217" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D217">
         <v>145</v>
@@ -5155,7 +5170,7 @@
         <v>18.90482398956975</v>
       </c>
       <c r="F217" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -5166,7 +5181,7 @@
         <v>58</v>
       </c>
       <c r="C218" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D218">
         <v>136</v>
@@ -5175,7 +5190,7 @@
         <v>17.73142112125163</v>
       </c>
       <c r="F218" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -5186,7 +5201,7 @@
         <v>58</v>
       </c>
       <c r="C219" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D219">
         <v>104</v>
@@ -5195,7 +5210,7 @@
         <v>13.5593220338983</v>
       </c>
       <c r="F219" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -5206,7 +5221,7 @@
         <v>58</v>
       </c>
       <c r="C220" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D220">
         <v>88</v>
@@ -5215,7 +5230,7 @@
         <v>11.47327249022164</v>
       </c>
       <c r="F220" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -5226,7 +5241,7 @@
         <v>59</v>
       </c>
       <c r="C222" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D222">
         <v>957</v>
@@ -5235,7 +5250,7 @@
         <v>36.62456946039035</v>
       </c>
       <c r="F222" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -5246,7 +5261,7 @@
         <v>59</v>
       </c>
       <c r="C223" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D223">
         <v>917</v>
@@ -5255,7 +5270,7 @@
         <v>35.0937619594336</v>
       </c>
       <c r="F223" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -5266,7 +5281,7 @@
         <v>59</v>
       </c>
       <c r="C224" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D224">
         <v>739</v>
@@ -5275,7 +5290,7 @@
         <v>28.28166858017605</v>
       </c>
       <c r="F224" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -5286,7 +5301,7 @@
         <v>60</v>
       </c>
       <c r="C226" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D226">
         <v>5642</v>
@@ -5295,7 +5310,7 @@
         <v>34.00638900608764</v>
       </c>
       <c r="F226" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -5306,7 +5321,7 @@
         <v>60</v>
       </c>
       <c r="C227" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D227">
         <v>5540</v>
@@ -5315,7 +5330,7 @@
         <v>33.39159785425833</v>
       </c>
       <c r="F227" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -5326,7 +5341,7 @@
         <v>60</v>
       </c>
       <c r="C228" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D228">
         <v>5409</v>
@@ -5335,7 +5350,7 @@
         <v>32.60201313965403</v>
       </c>
       <c r="F228" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5346,7 +5361,7 @@
         <v>61</v>
       </c>
       <c r="C230" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D230">
         <v>170</v>
@@ -5355,7 +5370,7 @@
         <v>46.19565217391305</v>
       </c>
       <c r="F230" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -5366,7 +5381,7 @@
         <v>61</v>
       </c>
       <c r="C231" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D231">
         <v>169</v>
@@ -5375,7 +5390,7 @@
         <v>45.92391304347826</v>
       </c>
       <c r="F231" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -5386,7 +5401,7 @@
         <v>61</v>
       </c>
       <c r="C232" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D232">
         <v>29</v>
@@ -5395,7 +5410,7 @@
         <v>7.880434782608696</v>
       </c>
       <c r="F232" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5406,16 +5421,16 @@
         <v>62</v>
       </c>
       <c r="C234" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D234">
-        <v>616</v>
+        <v>1471</v>
       </c>
       <c r="E234">
-        <v>48.85011895321173</v>
+        <v>47.82184655396619</v>
       </c>
       <c r="F234" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5426,16 +5441,16 @@
         <v>62</v>
       </c>
       <c r="C235" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D235">
-        <v>534</v>
+        <v>857</v>
       </c>
       <c r="E235">
-        <v>42.34734337827121</v>
+        <v>27.86085825747724</v>
       </c>
       <c r="F235" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -5446,16 +5461,16 @@
         <v>62</v>
       </c>
       <c r="C236" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D236">
-        <v>111</v>
+        <v>748</v>
       </c>
       <c r="E236">
-        <v>8.802537668517051</v>
+        <v>24.31729518855657</v>
       </c>
       <c r="F236" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5466,16 +5481,16 @@
         <v>63</v>
       </c>
       <c r="C238" t="s">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="D238">
-        <v>1114</v>
+        <v>616</v>
       </c>
       <c r="E238">
-        <v>47.79064779064779</v>
+        <v>48.85011895321173</v>
       </c>
       <c r="F238" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -5486,16 +5501,16 @@
         <v>63</v>
       </c>
       <c r="C239" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="D239">
-        <v>647</v>
+        <v>534</v>
       </c>
       <c r="E239">
-        <v>27.75632775632776</v>
+        <v>42.34734337827121</v>
       </c>
       <c r="F239" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -5506,36 +5521,36 @@
         <v>63</v>
       </c>
       <c r="C240" t="s">
+        <v>281</v>
+      </c>
+      <c r="D240">
+        <v>111</v>
+      </c>
+      <c r="E240">
+        <v>8.802537668517051</v>
+      </c>
+      <c r="F240" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242">
+        <v>2023</v>
+      </c>
+      <c r="B242" t="s">
+        <v>64</v>
+      </c>
+      <c r="C242" t="s">
         <v>235</v>
       </c>
-      <c r="D240">
-        <v>369</v>
-      </c>
-      <c r="E240">
-        <v>15.83011583011583</v>
-      </c>
-      <c r="F240" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
-      <c r="A241">
-        <v>2023</v>
-      </c>
-      <c r="B241" t="s">
-        <v>63</v>
-      </c>
-      <c r="C241" t="s">
-        <v>237</v>
-      </c>
-      <c r="D241">
-        <v>201</v>
-      </c>
-      <c r="E241">
-        <v>8.622908622908623</v>
-      </c>
-      <c r="F241" t="s">
-        <v>413</v>
+      <c r="D242">
+        <v>1114</v>
+      </c>
+      <c r="E242">
+        <v>47.79064779064779</v>
+      </c>
+      <c r="F242" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -5546,16 +5561,16 @@
         <v>64</v>
       </c>
       <c r="C243" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D243">
-        <v>592</v>
+        <v>647</v>
       </c>
       <c r="E243">
-        <v>32.52747252747253</v>
+        <v>27.75632775632776</v>
       </c>
       <c r="F243" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -5566,16 +5581,16 @@
         <v>64</v>
       </c>
       <c r="C244" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D244">
-        <v>571</v>
+        <v>369</v>
       </c>
       <c r="E244">
-        <v>31.37362637362637</v>
+        <v>15.83011583011583</v>
       </c>
       <c r="F244" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -5586,36 +5601,16 @@
         <v>64</v>
       </c>
       <c r="C245" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D245">
-        <v>324</v>
+        <v>201</v>
       </c>
       <c r="E245">
-        <v>17.8021978021978</v>
+        <v>8.622908622908623</v>
       </c>
       <c r="F245" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246">
-        <v>2023</v>
-      </c>
-      <c r="B246" t="s">
-        <v>64</v>
-      </c>
-      <c r="C246" t="s">
-        <v>240</v>
-      </c>
-      <c r="D246">
-        <v>295</v>
-      </c>
-      <c r="E246">
-        <v>16.20879120879121</v>
-      </c>
-      <c r="F246" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -5623,19 +5618,39 @@
         <v>2023</v>
       </c>
       <c r="B247" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C247" t="s">
+        <v>239</v>
+      </c>
+      <c r="D247">
+        <v>592</v>
+      </c>
+      <c r="E247">
+        <v>32.52747252747253</v>
+      </c>
+      <c r="F247" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248">
+        <v>2023</v>
+      </c>
+      <c r="B248" t="s">
+        <v>65</v>
+      </c>
+      <c r="C248" t="s">
         <v>242</v>
       </c>
-      <c r="D247">
-        <v>38</v>
-      </c>
-      <c r="E247">
-        <v>2.087912087912088</v>
-      </c>
-      <c r="F247" t="s">
-        <v>425</v>
+      <c r="D248">
+        <v>571</v>
+      </c>
+      <c r="E248">
+        <v>31.37362637362637</v>
+      </c>
+      <c r="F248" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -5646,16 +5661,16 @@
         <v>65</v>
       </c>
       <c r="C249" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D249">
-        <v>886</v>
+        <v>324</v>
       </c>
       <c r="E249">
-        <v>48.86927744070601</v>
+        <v>17.8021978021978</v>
       </c>
       <c r="F249" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -5666,16 +5681,16 @@
         <v>65</v>
       </c>
       <c r="C250" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D250">
-        <v>699</v>
+        <v>295</v>
       </c>
       <c r="E250">
-        <v>38.55488141202427</v>
+        <v>16.20879120879121</v>
       </c>
       <c r="F250" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -5686,16 +5701,16 @@
         <v>65</v>
       </c>
       <c r="C251" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D251">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="E251">
-        <v>12.57584114726972</v>
+        <v>2.087912087912088</v>
       </c>
       <c r="F251" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -5706,16 +5721,16 @@
         <v>66</v>
       </c>
       <c r="C253" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D253">
-        <v>1630</v>
+        <v>886</v>
       </c>
       <c r="E253">
-        <v>44.46262956901255</v>
+        <v>48.86927744070601</v>
       </c>
       <c r="F253" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -5726,16 +5741,16 @@
         <v>66</v>
       </c>
       <c r="C254" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D254">
-        <v>1039</v>
+        <v>699</v>
       </c>
       <c r="E254">
-        <v>28.34151663938898</v>
+        <v>38.55488141202427</v>
       </c>
       <c r="F254" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -5746,36 +5761,36 @@
         <v>66</v>
       </c>
       <c r="C255" t="s">
+        <v>246</v>
+      </c>
+      <c r="D255">
+        <v>228</v>
+      </c>
+      <c r="E255">
+        <v>12.57584114726972</v>
+      </c>
+      <c r="F255" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257">
+        <v>2023</v>
+      </c>
+      <c r="B257" t="s">
+        <v>67</v>
+      </c>
+      <c r="C257" t="s">
         <v>247</v>
       </c>
-      <c r="D255">
-        <v>813</v>
-      </c>
-      <c r="E255">
-        <v>22.17675941080196</v>
-      </c>
-      <c r="F255" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
-      <c r="A256">
-        <v>2023</v>
-      </c>
-      <c r="B256" t="s">
-        <v>66</v>
-      </c>
-      <c r="C256" t="s">
-        <v>278</v>
-      </c>
-      <c r="D256">
-        <v>184</v>
-      </c>
-      <c r="E256">
-        <v>5.019094380796509</v>
-      </c>
-      <c r="F256" t="s">
-        <v>426</v>
+      <c r="D257">
+        <v>1630</v>
+      </c>
+      <c r="E257">
+        <v>44.46262956901255</v>
+      </c>
+      <c r="F257" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -5786,16 +5801,16 @@
         <v>67</v>
       </c>
       <c r="C258" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="D258">
-        <v>1334</v>
+        <v>1039</v>
       </c>
       <c r="E258">
-        <v>46.38386648122393</v>
+        <v>28.34151663938898</v>
       </c>
       <c r="F258" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -5806,16 +5821,16 @@
         <v>67</v>
       </c>
       <c r="C259" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="D259">
-        <v>1278</v>
+        <v>813</v>
       </c>
       <c r="E259">
-        <v>44.43671766342142</v>
+        <v>22.17675941080196</v>
       </c>
       <c r="F259" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -5826,16 +5841,16 @@
         <v>67</v>
       </c>
       <c r="C260" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D260">
-        <v>264</v>
+        <v>184</v>
       </c>
       <c r="E260">
-        <v>9.179415855354661</v>
+        <v>5.019094380796509</v>
       </c>
       <c r="F260" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -5846,16 +5861,16 @@
         <v>68</v>
       </c>
       <c r="C262" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="D262">
-        <v>1466</v>
+        <v>1334</v>
       </c>
       <c r="E262">
-        <v>43.1303324507208</v>
+        <v>46.38386648122393</v>
       </c>
       <c r="F262" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -5866,16 +5881,16 @@
         <v>68</v>
       </c>
       <c r="C263" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D263">
-        <v>893</v>
+        <v>1278</v>
       </c>
       <c r="E263">
-        <v>26.27243306854957</v>
+        <v>44.43671766342142</v>
       </c>
       <c r="F263" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -5886,36 +5901,16 @@
         <v>68</v>
       </c>
       <c r="C264" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="D264">
-        <v>672</v>
+        <v>264</v>
       </c>
       <c r="E264">
-        <v>19.77052074139453</v>
+        <v>9.179415855354661</v>
       </c>
       <c r="F264" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
-      <c r="A265">
-        <v>2023</v>
-      </c>
-      <c r="B265" t="s">
-        <v>68</v>
-      </c>
-      <c r="C265" t="s">
-        <v>252</v>
-      </c>
-      <c r="D265">
-        <v>245</v>
-      </c>
-      <c r="E265">
-        <v>7.208002353633422</v>
-      </c>
-      <c r="F265" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -5923,19 +5918,39 @@
         <v>2023</v>
       </c>
       <c r="B266" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C266" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D266">
-        <v>123</v>
+        <v>1466</v>
       </c>
       <c r="E266">
-        <v>3.618711385701677</v>
+        <v>43.1303324507208</v>
       </c>
       <c r="F266" t="s">
-        <v>417</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267">
+        <v>2023</v>
+      </c>
+      <c r="B267" t="s">
+        <v>69</v>
+      </c>
+      <c r="C267" t="s">
+        <v>251</v>
+      </c>
+      <c r="D267">
+        <v>893</v>
+      </c>
+      <c r="E267">
+        <v>26.27243306854957</v>
+      </c>
+      <c r="F267" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -5946,16 +5961,16 @@
         <v>69</v>
       </c>
       <c r="C268" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D268">
-        <v>1108</v>
+        <v>672</v>
       </c>
       <c r="E268">
-        <v>46.4765100671141</v>
+        <v>19.77052074139453</v>
       </c>
       <c r="F268" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -5966,16 +5981,16 @@
         <v>69</v>
       </c>
       <c r="C269" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D269">
-        <v>444</v>
+        <v>245</v>
       </c>
       <c r="E269">
-        <v>18.6241610738255</v>
+        <v>7.208002353633422</v>
       </c>
       <c r="F269" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -5986,36 +6001,16 @@
         <v>69</v>
       </c>
       <c r="C270" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="D270">
-        <v>343</v>
+        <v>123</v>
       </c>
       <c r="E270">
-        <v>14.38758389261745</v>
+        <v>3.618711385701677</v>
       </c>
       <c r="F270" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
-      <c r="A271">
-        <v>2023</v>
-      </c>
-      <c r="B271" t="s">
-        <v>69</v>
-      </c>
-      <c r="C271" t="s">
-        <v>258</v>
-      </c>
-      <c r="D271">
-        <v>323</v>
-      </c>
-      <c r="E271">
-        <v>13.5486577181208</v>
-      </c>
-      <c r="F271" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -6023,19 +6018,39 @@
         <v>2023</v>
       </c>
       <c r="B272" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C272" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D272">
-        <v>166</v>
+        <v>1108</v>
       </c>
       <c r="E272">
-        <v>6.963087248322148</v>
+        <v>46.4765100671141</v>
       </c>
       <c r="F272" t="s">
-        <v>427</v>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273">
+        <v>2023</v>
+      </c>
+      <c r="B273" t="s">
+        <v>70</v>
+      </c>
+      <c r="C273" t="s">
+        <v>261</v>
+      </c>
+      <c r="D273">
+        <v>444</v>
+      </c>
+      <c r="E273">
+        <v>18.6241610738255</v>
+      </c>
+      <c r="F273" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -6046,16 +6061,16 @@
         <v>70</v>
       </c>
       <c r="C274" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D274">
-        <v>904</v>
+        <v>343</v>
       </c>
       <c r="E274">
-        <v>42.60131950989632</v>
+        <v>14.38758389261745</v>
       </c>
       <c r="F274" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -6066,16 +6081,16 @@
         <v>70</v>
       </c>
       <c r="C275" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="D275">
-        <v>860</v>
+        <v>323</v>
       </c>
       <c r="E275">
-        <v>40.52780395852969</v>
+        <v>13.5486577181208</v>
       </c>
       <c r="F275" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -6086,36 +6101,36 @@
         <v>70</v>
       </c>
       <c r="C276" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="D276">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="E276">
-        <v>9.095193213949104</v>
+        <v>6.963087248322148</v>
       </c>
       <c r="F276" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
-      <c r="A277">
-        <v>2023</v>
-      </c>
-      <c r="B277" t="s">
-        <v>70</v>
-      </c>
-      <c r="C277" t="s">
-        <v>286</v>
-      </c>
-      <c r="D277">
-        <v>165</v>
-      </c>
-      <c r="E277">
-        <v>7.775683317624882</v>
-      </c>
-      <c r="F277" t="s">
-        <v>427</v>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278">
+        <v>2023</v>
+      </c>
+      <c r="B278" t="s">
+        <v>71</v>
+      </c>
+      <c r="C278" t="s">
+        <v>287</v>
+      </c>
+      <c r="D278">
+        <v>904</v>
+      </c>
+      <c r="E278">
+        <v>42.60131950989632</v>
+      </c>
+      <c r="F278" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -6126,16 +6141,16 @@
         <v>71</v>
       </c>
       <c r="C279" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="D279">
-        <v>425</v>
+        <v>860</v>
       </c>
       <c r="E279">
-        <v>25.11820330969267</v>
+        <v>40.52780395852969</v>
       </c>
       <c r="F279" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -6146,16 +6161,16 @@
         <v>71</v>
       </c>
       <c r="C280" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="D280">
-        <v>341</v>
+        <v>193</v>
       </c>
       <c r="E280">
-        <v>20.15366430260048</v>
+        <v>9.095193213949104</v>
       </c>
       <c r="F280" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -6166,36 +6181,16 @@
         <v>71</v>
       </c>
       <c r="C281" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="D281">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="E281">
-        <v>16.48936170212766</v>
+        <v>7.775683317624882</v>
       </c>
       <c r="F281" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
-      <c r="A282">
-        <v>2023</v>
-      </c>
-      <c r="B282" t="s">
-        <v>71</v>
-      </c>
-      <c r="C282" t="s">
-        <v>264</v>
-      </c>
-      <c r="D282">
-        <v>272</v>
-      </c>
-      <c r="E282">
-        <v>16.07565011820331</v>
-      </c>
-      <c r="F282" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -6203,19 +6198,19 @@
         <v>2023</v>
       </c>
       <c r="B283" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C283" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="D283">
-        <v>220</v>
+        <v>425</v>
       </c>
       <c r="E283">
-        <v>13.00236406619385</v>
+        <v>25.11820330969267</v>
       </c>
       <c r="F283" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -6223,19 +6218,39 @@
         <v>2023</v>
       </c>
       <c r="B284" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C284" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D284">
-        <v>155</v>
+        <v>341</v>
       </c>
       <c r="E284">
-        <v>9.160756501182032</v>
+        <v>20.15366430260048</v>
       </c>
       <c r="F284" t="s">
-        <v>423</v>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285">
+        <v>2023</v>
+      </c>
+      <c r="B285" t="s">
+        <v>72</v>
+      </c>
+      <c r="C285" t="s">
+        <v>264</v>
+      </c>
+      <c r="D285">
+        <v>279</v>
+      </c>
+      <c r="E285">
+        <v>16.48936170212766</v>
+      </c>
+      <c r="F285" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -6246,16 +6261,16 @@
         <v>72</v>
       </c>
       <c r="C286" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="D286">
         <v>272</v>
       </c>
       <c r="E286">
-        <v>44.01294498381877</v>
+        <v>16.07565011820331</v>
       </c>
       <c r="F286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -6266,16 +6281,16 @@
         <v>72</v>
       </c>
       <c r="C287" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D287">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="E287">
-        <v>23.46278317152104</v>
+        <v>13.00236406619385</v>
       </c>
       <c r="F287" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -6286,36 +6301,16 @@
         <v>72</v>
       </c>
       <c r="C288" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="D288">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E288">
-        <v>17.47572815533981</v>
+        <v>9.160756501182032</v>
       </c>
       <c r="F288" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6">
-      <c r="A289">
-        <v>2023</v>
-      </c>
-      <c r="B289" t="s">
-        <v>72</v>
-      </c>
-      <c r="C289" t="s">
-        <v>291</v>
-      </c>
-      <c r="D289">
-        <v>50</v>
-      </c>
-      <c r="E289">
-        <v>8.090614886731391</v>
-      </c>
-      <c r="F289" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -6323,19 +6318,39 @@
         <v>2023</v>
       </c>
       <c r="B290" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C290" t="s">
         <v>292</v>
       </c>
       <c r="D290">
-        <v>43</v>
+        <v>272</v>
       </c>
       <c r="E290">
-        <v>6.957928802588997</v>
+        <v>44.01294498381877</v>
       </c>
       <c r="F290" t="s">
-        <v>425</v>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291">
+        <v>2023</v>
+      </c>
+      <c r="B291" t="s">
+        <v>73</v>
+      </c>
+      <c r="C291" t="s">
+        <v>293</v>
+      </c>
+      <c r="D291">
+        <v>145</v>
+      </c>
+      <c r="E291">
+        <v>23.46278317152104</v>
+      </c>
+      <c r="F291" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -6346,16 +6361,16 @@
         <v>73</v>
       </c>
       <c r="C292" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D292">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="E292">
-        <v>48.22934232715008</v>
+        <v>17.47572815533981</v>
       </c>
       <c r="F292" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -6366,16 +6381,16 @@
         <v>73</v>
       </c>
       <c r="C293" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D293">
-        <v>212</v>
+        <v>50</v>
       </c>
       <c r="E293">
-        <v>35.7504215851602</v>
+        <v>8.090614886731391</v>
       </c>
       <c r="F293" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -6386,16 +6401,16 @@
         <v>73</v>
       </c>
       <c r="C294" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D294">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E294">
-        <v>16.02023608768971</v>
+        <v>6.957928802588997</v>
       </c>
       <c r="F294" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -6406,16 +6421,16 @@
         <v>74</v>
       </c>
       <c r="C296" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D296">
-        <v>431</v>
+        <v>286</v>
       </c>
       <c r="E296">
-        <v>36.77474402730375</v>
+        <v>48.22934232715008</v>
       </c>
       <c r="F296" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -6426,16 +6441,16 @@
         <v>74</v>
       </c>
       <c r="C297" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D297">
-        <v>297</v>
+        <v>212</v>
       </c>
       <c r="E297">
-        <v>25.34129692832764</v>
+        <v>35.7504215851602</v>
       </c>
       <c r="F297" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -6446,36 +6461,16 @@
         <v>74</v>
       </c>
       <c r="C298" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D298">
-        <v>285</v>
+        <v>95</v>
       </c>
       <c r="E298">
-        <v>24.31740614334471</v>
+        <v>16.02023608768971</v>
       </c>
       <c r="F298" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6">
-      <c r="A299">
-        <v>2023</v>
-      </c>
-      <c r="B299" t="s">
-        <v>74</v>
-      </c>
-      <c r="C299" t="s">
-        <v>299</v>
-      </c>
-      <c r="D299">
-        <v>96</v>
-      </c>
-      <c r="E299">
-        <v>8.191126279863481</v>
-      </c>
-      <c r="F299" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -6483,19 +6478,39 @@
         <v>2023</v>
       </c>
       <c r="B300" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C300" t="s">
         <v>300</v>
       </c>
       <c r="D300">
-        <v>63</v>
+        <v>431</v>
       </c>
       <c r="E300">
-        <v>5.375426621160409</v>
+        <v>36.77474402730375</v>
       </c>
       <c r="F300" t="s">
-        <v>418</v>
+        <v>422</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301">
+        <v>2023</v>
+      </c>
+      <c r="B301" t="s">
+        <v>75</v>
+      </c>
+      <c r="C301" t="s">
+        <v>301</v>
+      </c>
+      <c r="D301">
+        <v>297</v>
+      </c>
+      <c r="E301">
+        <v>25.34129692832764</v>
+      </c>
+      <c r="F301" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -6506,13 +6521,13 @@
         <v>75</v>
       </c>
       <c r="C302" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D302">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="E302">
-        <v>45.4242928452579</v>
+        <v>24.31740614334471</v>
       </c>
       <c r="F302" t="s">
         <v>422</v>
@@ -6526,13 +6541,13 @@
         <v>75</v>
       </c>
       <c r="C303" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D303">
-        <v>234</v>
+        <v>96</v>
       </c>
       <c r="E303">
-        <v>38.9351081530782</v>
+        <v>8.191126279863481</v>
       </c>
       <c r="F303" t="s">
         <v>422</v>
@@ -6546,13 +6561,13 @@
         <v>75</v>
       </c>
       <c r="C304" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D304">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="E304">
-        <v>15.64059900166389</v>
+        <v>5.375426621160409</v>
       </c>
       <c r="F304" t="s">
         <v>422</v>
@@ -6566,16 +6581,16 @@
         <v>76</v>
       </c>
       <c r="C306" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D306">
-        <v>124</v>
+        <v>273</v>
       </c>
       <c r="E306">
-        <v>47.69230769230769</v>
+        <v>45.4242928452579</v>
       </c>
       <c r="F306" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -6586,16 +6601,16 @@
         <v>76</v>
       </c>
       <c r="C307" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D307">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="E307">
-        <v>28.07692307692308</v>
+        <v>38.9351081530782</v>
       </c>
       <c r="F307" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -6606,16 +6621,16 @@
         <v>76</v>
       </c>
       <c r="C308" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D308">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="E308">
-        <v>24.23076923076923</v>
+        <v>15.64059900166389</v>
       </c>
       <c r="F308" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -6626,16 +6641,16 @@
         <v>77</v>
       </c>
       <c r="C310" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D310">
-        <v>827</v>
+        <v>124</v>
       </c>
       <c r="E310">
-        <v>47.88650839606254</v>
+        <v>47.69230769230769</v>
       </c>
       <c r="F310" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -6646,16 +6661,16 @@
         <v>77</v>
       </c>
       <c r="C311" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D311">
-        <v>284</v>
+        <v>73</v>
       </c>
       <c r="E311">
-        <v>16.44470179502026</v>
+        <v>28.07692307692308</v>
       </c>
       <c r="F311" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -6666,36 +6681,16 @@
         <v>77</v>
       </c>
       <c r="C312" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D312">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="E312">
-        <v>12.85466126230457</v>
+        <v>24.23076923076923</v>
       </c>
       <c r="F312" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6">
-      <c r="A313">
-        <v>2023</v>
-      </c>
-      <c r="B313" t="s">
-        <v>77</v>
-      </c>
-      <c r="C313" t="s">
-        <v>310</v>
-      </c>
-      <c r="D313">
-        <v>211</v>
-      </c>
-      <c r="E313">
-        <v>12.21771858714534</v>
-      </c>
-      <c r="F313" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -6703,19 +6698,39 @@
         <v>2023</v>
       </c>
       <c r="B314" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C314" t="s">
         <v>311</v>
       </c>
       <c r="D314">
-        <v>183</v>
+        <v>827</v>
       </c>
       <c r="E314">
-        <v>10.59640995946728</v>
+        <v>47.88650839606254</v>
       </c>
       <c r="F314" t="s">
-        <v>427</v>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315">
+        <v>2023</v>
+      </c>
+      <c r="B315" t="s">
+        <v>78</v>
+      </c>
+      <c r="C315" t="s">
+        <v>312</v>
+      </c>
+      <c r="D315">
+        <v>284</v>
+      </c>
+      <c r="E315">
+        <v>16.44470179502026</v>
+      </c>
+      <c r="F315" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -6726,16 +6741,16 @@
         <v>78</v>
       </c>
       <c r="C316" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D316">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="E316">
-        <v>42.46575342465754</v>
+        <v>12.85466126230457</v>
       </c>
       <c r="F316" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -6746,16 +6761,16 @@
         <v>78</v>
       </c>
       <c r="C317" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D317">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="E317">
-        <v>32.87671232876712</v>
+        <v>12.21771858714534</v>
       </c>
       <c r="F317" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -6766,16 +6781,16 @@
         <v>78</v>
       </c>
       <c r="C318" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D318">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="E318">
-        <v>24.65753424657534</v>
+        <v>10.59640995946728</v>
       </c>
       <c r="F318" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -6786,16 +6801,16 @@
         <v>79</v>
       </c>
       <c r="C320" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D320">
-        <v>605</v>
+        <v>186</v>
       </c>
       <c r="E320">
-        <v>41.10054347826087</v>
+        <v>42.46575342465754</v>
       </c>
       <c r="F320" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -6806,16 +6821,16 @@
         <v>79</v>
       </c>
       <c r="C321" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D321">
-        <v>593</v>
+        <v>144</v>
       </c>
       <c r="E321">
-        <v>40.28532608695652</v>
+        <v>32.87671232876712</v>
       </c>
       <c r="F321" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -6826,16 +6841,16 @@
         <v>79</v>
       </c>
       <c r="C322" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D322">
-        <v>274</v>
+        <v>108</v>
       </c>
       <c r="E322">
-        <v>18.61413043478261</v>
+        <v>24.65753424657534</v>
       </c>
       <c r="F322" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -6846,16 +6861,16 @@
         <v>80</v>
       </c>
       <c r="C324" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D324">
-        <v>347</v>
+        <v>605</v>
       </c>
       <c r="E324">
-        <v>49.15014164305949</v>
+        <v>41.10054347826087</v>
       </c>
       <c r="F324" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -6866,16 +6881,16 @@
         <v>80</v>
       </c>
       <c r="C325" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D325">
-        <v>168</v>
+        <v>593</v>
       </c>
       <c r="E325">
-        <v>23.79603399433428</v>
+        <v>40.28532608695652</v>
       </c>
       <c r="F325" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -6886,36 +6901,36 @@
         <v>80</v>
       </c>
       <c r="C326" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D326">
-        <v>103</v>
+        <v>274</v>
       </c>
       <c r="E326">
-        <v>14.58923512747875</v>
+        <v>18.61413043478261</v>
       </c>
       <c r="F326" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6">
-      <c r="A327">
-        <v>2023</v>
-      </c>
-      <c r="B327" t="s">
-        <v>80</v>
-      </c>
-      <c r="C327" t="s">
-        <v>321</v>
-      </c>
-      <c r="D327">
-        <v>88</v>
-      </c>
-      <c r="E327">
-        <v>12.46458923512748</v>
-      </c>
-      <c r="F327" t="s">
-        <v>426</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328">
+        <v>2023</v>
+      </c>
+      <c r="B328" t="s">
+        <v>81</v>
+      </c>
+      <c r="C328" t="s">
+        <v>322</v>
+      </c>
+      <c r="D328">
+        <v>347</v>
+      </c>
+      <c r="E328">
+        <v>49.15014164305949</v>
+      </c>
+      <c r="F328" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -6926,16 +6941,16 @@
         <v>81</v>
       </c>
       <c r="C329" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D329">
-        <v>372</v>
+        <v>168</v>
       </c>
       <c r="E329">
-        <v>42.36902050113896</v>
+        <v>23.79603399433428</v>
       </c>
       <c r="F329" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -6946,16 +6961,16 @@
         <v>81</v>
       </c>
       <c r="C330" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D330">
-        <v>195</v>
+        <v>103</v>
       </c>
       <c r="E330">
-        <v>22.20956719817768</v>
+        <v>14.58923512747875</v>
       </c>
       <c r="F330" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -6966,176 +6981,156 @@
         <v>81</v>
       </c>
       <c r="C331" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D331">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="E331">
-        <v>21.98177676537586</v>
+        <v>12.46458923512748</v>
       </c>
       <c r="F331" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6">
-      <c r="A332">
-        <v>2023</v>
-      </c>
-      <c r="B332" t="s">
-        <v>81</v>
-      </c>
-      <c r="C332" t="s">
-        <v>325</v>
-      </c>
-      <c r="D332">
-        <v>118</v>
-      </c>
-      <c r="E332">
-        <v>13.43963553530752</v>
-      </c>
-      <c r="F332" t="s">
-        <v>420</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333">
+        <v>2023</v>
+      </c>
+      <c r="B333" t="s">
+        <v>82</v>
+      </c>
+      <c r="C333" t="s">
+        <v>326</v>
+      </c>
+      <c r="D333">
+        <v>372</v>
+      </c>
+      <c r="E333">
+        <v>42.36902050113896</v>
+      </c>
+      <c r="F333" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B334" t="s">
         <v>82</v>
       </c>
       <c r="C334" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D334">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="E334">
-        <v>44.68085106382978</v>
+        <v>22.20956719817768</v>
       </c>
       <c r="F334" t="s">
-        <v>10</v>
+        <v>424</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B335" t="s">
         <v>82</v>
       </c>
       <c r="C335" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D335">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="E335">
-        <v>31.00303951367781</v>
+        <v>21.98177676537586</v>
       </c>
       <c r="F335" t="s">
-        <v>10</v>
+        <v>424</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B336" t="s">
         <v>82</v>
       </c>
       <c r="C336" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D336">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="E336">
-        <v>24.3161094224924</v>
+        <v>13.43963553530752</v>
       </c>
       <c r="F336" t="s">
-        <v>10</v>
+        <v>424</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B338" t="s">
         <v>83</v>
       </c>
       <c r="C338" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D338">
-        <v>1224</v>
+        <v>147</v>
       </c>
       <c r="E338">
-        <v>28.77291960507758</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="F338" t="s">
-        <v>414</v>
+        <v>10</v>
       </c>
     </row>
     <row r="339" spans="1:6">
       <c r="A339">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B339" t="s">
         <v>83</v>
       </c>
       <c r="C339" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D339">
-        <v>1052</v>
+        <v>102</v>
       </c>
       <c r="E339">
-        <v>24.72966619652092</v>
+        <v>31.00303951367781</v>
       </c>
       <c r="F339" t="s">
-        <v>414</v>
+        <v>10</v>
       </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B340" t="s">
         <v>83</v>
       </c>
       <c r="C340" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D340">
-        <v>685</v>
+        <v>80</v>
       </c>
       <c r="E340">
-        <v>16.10249177244946</v>
+        <v>24.3161094224924</v>
       </c>
       <c r="F340" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6">
-      <c r="A341">
-        <v>2025</v>
-      </c>
-      <c r="B341" t="s">
-        <v>83</v>
-      </c>
-      <c r="C341" t="s">
-        <v>332</v>
-      </c>
-      <c r="D341">
-        <v>656</v>
-      </c>
-      <c r="E341">
-        <v>15.420780441937</v>
-      </c>
-      <c r="F341" t="s">
-        <v>414</v>
+        <v>10</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -7143,19 +7138,39 @@
         <v>2025</v>
       </c>
       <c r="B342" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C342" t="s">
         <v>333</v>
       </c>
       <c r="D342">
-        <v>637</v>
+        <v>1224</v>
       </c>
       <c r="E342">
-        <v>14.97414198401504</v>
+        <v>28.77291960507758</v>
       </c>
       <c r="F342" t="s">
-        <v>414</v>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343">
+        <v>2025</v>
+      </c>
+      <c r="B343" t="s">
+        <v>84</v>
+      </c>
+      <c r="C343" t="s">
+        <v>334</v>
+      </c>
+      <c r="D343">
+        <v>1052</v>
+      </c>
+      <c r="E343">
+        <v>24.72966619652092</v>
+      </c>
+      <c r="F343" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -7166,16 +7181,16 @@
         <v>84</v>
       </c>
       <c r="C344" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D344">
-        <v>3817</v>
+        <v>685</v>
       </c>
       <c r="E344">
-        <v>39.10860655737705</v>
+        <v>16.10249177244946</v>
       </c>
       <c r="F344" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -7186,16 +7201,16 @@
         <v>84</v>
       </c>
       <c r="C345" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D345">
-        <v>3272</v>
+        <v>656</v>
       </c>
       <c r="E345">
-        <v>33.52459016393443</v>
+        <v>15.420780441937</v>
       </c>
       <c r="F345" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -7206,16 +7221,16 @@
         <v>84</v>
       </c>
       <c r="C346" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D346">
-        <v>2671</v>
+        <v>637</v>
       </c>
       <c r="E346">
-        <v>27.36680327868852</v>
+        <v>14.97414198401504</v>
       </c>
       <c r="F346" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -7226,13 +7241,13 @@
         <v>85</v>
       </c>
       <c r="C348" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D348">
-        <v>710</v>
+        <v>3817</v>
       </c>
       <c r="E348">
-        <v>46.64914586070959</v>
+        <v>39.10860655737705</v>
       </c>
       <c r="F348" t="s">
         <v>418</v>
@@ -7246,13 +7261,13 @@
         <v>85</v>
       </c>
       <c r="C349" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D349">
-        <v>617</v>
+        <v>3272</v>
       </c>
       <c r="E349">
-        <v>40.53876478318003</v>
+        <v>33.52459016393443</v>
       </c>
       <c r="F349" t="s">
         <v>418</v>
@@ -7266,13 +7281,13 @@
         <v>85</v>
       </c>
       <c r="C350" t="s">
-        <v>199</v>
+        <v>340</v>
       </c>
       <c r="D350">
-        <v>195</v>
+        <v>2671</v>
       </c>
       <c r="E350">
-        <v>12.81208935611038</v>
+        <v>27.36680327868852</v>
       </c>
       <c r="F350" t="s">
         <v>418</v>
@@ -7286,16 +7301,16 @@
         <v>86</v>
       </c>
       <c r="C352" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D352">
-        <v>7014</v>
+        <v>710</v>
       </c>
       <c r="E352">
-        <v>38.28393646635008</v>
+        <v>46.64914586070959</v>
       </c>
       <c r="F352" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -7306,16 +7321,16 @@
         <v>86</v>
       </c>
       <c r="C353" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D353">
-        <v>6543</v>
+        <v>617</v>
       </c>
       <c r="E353">
-        <v>35.71311609628295</v>
+        <v>40.53876478318003</v>
       </c>
       <c r="F353" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="354" spans="1:6">
@@ -7326,16 +7341,16 @@
         <v>86</v>
       </c>
       <c r="C354" t="s">
-        <v>341</v>
+        <v>200</v>
       </c>
       <c r="D354">
-        <v>4764</v>
+        <v>195</v>
       </c>
       <c r="E354">
-        <v>26.00294743736696</v>
+        <v>12.81208935611038</v>
       </c>
       <c r="F354" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -7346,16 +7361,16 @@
         <v>87</v>
       </c>
       <c r="C356" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D356">
-        <v>241</v>
+        <v>7014</v>
       </c>
       <c r="E356">
-        <v>49.79338842975206</v>
+        <v>38.28393646635008</v>
       </c>
       <c r="F356" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -7366,16 +7381,16 @@
         <v>87</v>
       </c>
       <c r="C357" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D357">
-        <v>193</v>
+        <v>6543</v>
       </c>
       <c r="E357">
-        <v>39.87603305785124</v>
+        <v>35.71311609628295</v>
       </c>
       <c r="F357" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -7386,16 +7401,16 @@
         <v>87</v>
       </c>
       <c r="C358" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D358">
-        <v>49</v>
+        <v>4764</v>
       </c>
       <c r="E358">
-        <v>10.12396694214876</v>
+        <v>26.00294743736696</v>
       </c>
       <c r="F358" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -7406,16 +7421,16 @@
         <v>88</v>
       </c>
       <c r="C360" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D360">
-        <v>373</v>
+        <v>241</v>
       </c>
       <c r="E360">
-        <v>36.39024390243902</v>
+        <v>49.79338842975206</v>
       </c>
       <c r="F360" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
     </row>
     <row r="361" spans="1:6">
@@ -7426,16 +7441,16 @@
         <v>88</v>
       </c>
       <c r="C361" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D361">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="E361">
-        <v>21.95121951219512</v>
+        <v>39.87603305785124</v>
       </c>
       <c r="F361" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -7446,36 +7461,16 @@
         <v>88</v>
       </c>
       <c r="C362" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D362">
-        <v>206</v>
+        <v>49</v>
       </c>
       <c r="E362">
-        <v>20.09756097560976</v>
+        <v>10.12396694214876</v>
       </c>
       <c r="F362" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6">
-      <c r="A363">
-        <v>2025</v>
-      </c>
-      <c r="B363" t="s">
-        <v>88</v>
-      </c>
-      <c r="C363" t="s">
-        <v>348</v>
-      </c>
-      <c r="D363">
-        <v>140</v>
-      </c>
-      <c r="E363">
-        <v>13.65853658536586</v>
-      </c>
-      <c r="F363" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -7483,19 +7478,39 @@
         <v>2025</v>
       </c>
       <c r="B364" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C364" t="s">
         <v>349</v>
       </c>
       <c r="D364">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="E364">
-        <v>7.902439024390244</v>
+        <v>36.39024390243902</v>
       </c>
       <c r="F364" t="s">
-        <v>413</v>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365">
+        <v>2025</v>
+      </c>
+      <c r="B365" t="s">
+        <v>89</v>
+      </c>
+      <c r="C365" t="s">
+        <v>350</v>
+      </c>
+      <c r="D365">
+        <v>225</v>
+      </c>
+      <c r="E365">
+        <v>21.95121951219512</v>
+      </c>
+      <c r="F365" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -7503,19 +7518,19 @@
         <v>2025</v>
       </c>
       <c r="B366" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="C366" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D366">
-        <v>6552</v>
+        <v>206</v>
       </c>
       <c r="E366">
-        <v>47.15704620699582</v>
+        <v>20.09756097560976</v>
       </c>
       <c r="F366" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="367" spans="1:6">
@@ -7523,19 +7538,19 @@
         <v>2025</v>
       </c>
       <c r="B367" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="C367" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D367">
-        <v>4724</v>
+        <v>140</v>
       </c>
       <c r="E367">
-        <v>34.00028789405498</v>
+        <v>13.65853658536586</v>
       </c>
       <c r="F367" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -7543,19 +7558,19 @@
         <v>2025</v>
       </c>
       <c r="B368" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="C368" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D368">
-        <v>2618</v>
+        <v>81</v>
       </c>
       <c r="E368">
-        <v>18.84266589894919</v>
+        <v>7.902439024390244</v>
       </c>
       <c r="F368" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -7563,19 +7578,19 @@
         <v>2025</v>
       </c>
       <c r="B370" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="C370" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D370">
-        <v>5832</v>
+        <v>6552</v>
       </c>
       <c r="E370">
-        <v>37.28423475258919</v>
+        <v>47.15704620699582</v>
       </c>
       <c r="F370" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -7583,19 +7598,19 @@
         <v>2025</v>
       </c>
       <c r="B371" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="C371" t="s">
-        <v>270</v>
+        <v>355</v>
       </c>
       <c r="D371">
-        <v>4950</v>
+        <v>4724</v>
       </c>
       <c r="E371">
-        <v>31.64556962025317</v>
+        <v>34.00028789405498</v>
       </c>
       <c r="F371" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -7603,19 +7618,19 @@
         <v>2025</v>
       </c>
       <c r="B372" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="C372" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D372">
-        <v>4834</v>
+        <v>2618</v>
       </c>
       <c r="E372">
-        <v>30.90397647359673</v>
+        <v>18.84266589894919</v>
       </c>
       <c r="F372" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="374" spans="1:6">
@@ -7626,16 +7641,16 @@
         <v>90</v>
       </c>
       <c r="C374" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D374">
-        <v>9318</v>
+        <v>5832</v>
       </c>
       <c r="E374">
-        <v>41.92764578833693</v>
+        <v>37.28423475258919</v>
       </c>
       <c r="F374" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -7646,16 +7661,16 @@
         <v>90</v>
       </c>
       <c r="C375" t="s">
-        <v>356</v>
+        <v>271</v>
       </c>
       <c r="D375">
-        <v>8700</v>
+        <v>4950</v>
       </c>
       <c r="E375">
-        <v>39.14686825053996</v>
+        <v>31.64556962025317</v>
       </c>
       <c r="F375" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="376" spans="1:6">
@@ -7666,16 +7681,16 @@
         <v>90</v>
       </c>
       <c r="C376" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D376">
-        <v>4206</v>
+        <v>4834</v>
       </c>
       <c r="E376">
-        <v>18.92548596112311</v>
+        <v>30.90397647359673</v>
       </c>
       <c r="F376" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -7686,16 +7701,16 @@
         <v>91</v>
       </c>
       <c r="C378" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D378">
-        <v>193</v>
+        <v>9318</v>
       </c>
       <c r="E378">
-        <v>44.36781609195402</v>
+        <v>41.92764578833693</v>
       </c>
       <c r="F378" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="379" spans="1:6">
@@ -7706,16 +7721,16 @@
         <v>91</v>
       </c>
       <c r="C379" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D379">
-        <v>161</v>
+        <v>8700</v>
       </c>
       <c r="E379">
-        <v>37.01149425287356</v>
+        <v>39.14686825053996</v>
       </c>
       <c r="F379" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="380" spans="1:6">
@@ -7726,16 +7741,16 @@
         <v>91</v>
       </c>
       <c r="C380" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D380">
-        <v>81</v>
+        <v>4206</v>
       </c>
       <c r="E380">
-        <v>18.62068965517242</v>
+        <v>18.92548596112311</v>
       </c>
       <c r="F380" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="382" spans="1:6">
@@ -7746,16 +7761,16 @@
         <v>92</v>
       </c>
       <c r="C382" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D382">
-        <v>1473</v>
+        <v>193</v>
       </c>
       <c r="E382">
-        <v>39.30096051227321</v>
+        <v>44.36781609195402</v>
       </c>
       <c r="F382" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="383" spans="1:6">
@@ -7766,16 +7781,16 @@
         <v>92</v>
       </c>
       <c r="C383" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D383">
-        <v>1297</v>
+        <v>161</v>
       </c>
       <c r="E383">
-        <v>34.6051227321238</v>
+        <v>37.01149425287356</v>
       </c>
       <c r="F383" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -7786,36 +7801,16 @@
         <v>92</v>
       </c>
       <c r="C384" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D384">
-        <v>516</v>
+        <v>81</v>
       </c>
       <c r="E384">
-        <v>13.76734258271078</v>
+        <v>18.62068965517242</v>
       </c>
       <c r="F384" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6">
-      <c r="A385">
-        <v>2025</v>
-      </c>
-      <c r="B385" t="s">
-        <v>92</v>
-      </c>
-      <c r="C385" t="s">
-        <v>364</v>
-      </c>
-      <c r="D385">
-        <v>305</v>
-      </c>
-      <c r="E385">
-        <v>8.137673425827108</v>
-      </c>
-      <c r="F385" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="386" spans="1:6">
@@ -7823,19 +7818,39 @@
         <v>2025</v>
       </c>
       <c r="B386" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C386" t="s">
         <v>365</v>
       </c>
       <c r="D386">
-        <v>157</v>
+        <v>1473</v>
       </c>
       <c r="E386">
-        <v>4.188900747065102</v>
+        <v>39.30096051227321</v>
       </c>
       <c r="F386" t="s">
-        <v>423</v>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
+      <c r="A387">
+        <v>2025</v>
+      </c>
+      <c r="B387" t="s">
+        <v>93</v>
+      </c>
+      <c r="C387" t="s">
+        <v>366</v>
+      </c>
+      <c r="D387">
+        <v>1297</v>
+      </c>
+      <c r="E387">
+        <v>34.6051227321238</v>
+      </c>
+      <c r="F387" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -7846,16 +7861,16 @@
         <v>93</v>
       </c>
       <c r="C388" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D388">
-        <v>854</v>
+        <v>516</v>
       </c>
       <c r="E388">
-        <v>47.52365052865888</v>
+        <v>13.76734258271078</v>
       </c>
       <c r="F388" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -7866,16 +7881,16 @@
         <v>93</v>
       </c>
       <c r="C389" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D389">
-        <v>764</v>
+        <v>305</v>
       </c>
       <c r="E389">
-        <v>42.51530328324986</v>
+        <v>8.137673425827108</v>
       </c>
       <c r="F389" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -7886,16 +7901,16 @@
         <v>93</v>
       </c>
       <c r="C390" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D390">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E390">
-        <v>9.738452977184195</v>
+        <v>4.188900747065102</v>
       </c>
       <c r="F390" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
     </row>
     <row r="392" spans="1:6">
@@ -7906,16 +7921,16 @@
         <v>94</v>
       </c>
       <c r="C392" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D392">
-        <v>162</v>
+        <v>854</v>
       </c>
       <c r="E392">
-        <v>45.2513966480447</v>
+        <v>47.52365052865888</v>
       </c>
       <c r="F392" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="393" spans="1:6">
@@ -7926,16 +7941,16 @@
         <v>94</v>
       </c>
       <c r="C393" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D393">
-        <v>156</v>
+        <v>764</v>
       </c>
       <c r="E393">
-        <v>43.5754189944134</v>
+        <v>42.51530328324986</v>
       </c>
       <c r="F393" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -7946,16 +7961,16 @@
         <v>94</v>
       </c>
       <c r="C394" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D394">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="E394">
-        <v>11.1731843575419</v>
+        <v>9.738452977184195</v>
       </c>
       <c r="F394" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -7966,16 +7981,16 @@
         <v>95</v>
       </c>
       <c r="C396" t="s">
-        <v>120</v>
+        <v>373</v>
       </c>
       <c r="D396">
-        <v>11367</v>
+        <v>162</v>
       </c>
       <c r="E396">
-        <v>45.69280861840254</v>
+        <v>45.2513966480447</v>
       </c>
       <c r="F396" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="397" spans="1:6">
@@ -7986,16 +8001,16 @@
         <v>95</v>
       </c>
       <c r="C397" t="s">
-        <v>119</v>
+        <v>374</v>
       </c>
       <c r="D397">
-        <v>8188</v>
+        <v>156</v>
       </c>
       <c r="E397">
-        <v>32.91393656791413</v>
+        <v>43.5754189944134</v>
       </c>
       <c r="F397" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="398" spans="1:6">
@@ -8006,16 +8021,16 @@
         <v>95</v>
       </c>
       <c r="C398" t="s">
-        <v>122</v>
+        <v>375</v>
       </c>
       <c r="D398">
-        <v>5322</v>
+        <v>40</v>
       </c>
       <c r="E398">
-        <v>21.39325481368332</v>
+        <v>11.1731843575419</v>
       </c>
       <c r="F398" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="400" spans="1:6">
@@ -8026,16 +8041,16 @@
         <v>96</v>
       </c>
       <c r="C400" t="s">
-        <v>294</v>
+        <v>121</v>
       </c>
       <c r="D400">
-        <v>287</v>
+        <v>11367</v>
       </c>
       <c r="E400">
-        <v>47.83333333333334</v>
+        <v>45.69280861840254</v>
       </c>
       <c r="F400" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -8046,16 +8061,16 @@
         <v>96</v>
       </c>
       <c r="C401" t="s">
-        <v>372</v>
+        <v>120</v>
       </c>
       <c r="D401">
-        <v>175</v>
+        <v>8188</v>
       </c>
       <c r="E401">
-        <v>29.16666666666667</v>
+        <v>32.91393656791413</v>
       </c>
       <c r="F401" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="402" spans="1:6">
@@ -8066,16 +8081,16 @@
         <v>96</v>
       </c>
       <c r="C402" t="s">
-        <v>373</v>
+        <v>123</v>
       </c>
       <c r="D402">
-        <v>138</v>
+        <v>5322</v>
       </c>
       <c r="E402">
-        <v>23</v>
+        <v>21.39325481368332</v>
       </c>
       <c r="F402" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="404" spans="1:6">
@@ -8086,16 +8101,16 @@
         <v>97</v>
       </c>
       <c r="C404" t="s">
-        <v>374</v>
+        <v>298</v>
       </c>
       <c r="D404">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="E404">
-        <v>45.50359712230216</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="F404" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -8106,16 +8121,16 @@
         <v>97</v>
       </c>
       <c r="C405" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D405">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="E405">
-        <v>27.69784172661871</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="F405" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="406" spans="1:6">
@@ -8126,16 +8141,16 @@
         <v>97</v>
       </c>
       <c r="C406" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D406">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E406">
-        <v>26.79856115107914</v>
+        <v>23</v>
       </c>
       <c r="F406" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -8146,16 +8161,16 @@
         <v>98</v>
       </c>
       <c r="C408" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D408">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="E408">
-        <v>38.71733966745843</v>
+        <v>45.50359712230216</v>
       </c>
       <c r="F408" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="409" spans="1:6">
@@ -8166,16 +8181,16 @@
         <v>98</v>
       </c>
       <c r="C409" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D409">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E409">
-        <v>38.00475059382423</v>
+        <v>27.69784172661871</v>
       </c>
       <c r="F409" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -8186,36 +8201,36 @@
         <v>98</v>
       </c>
       <c r="C410" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D410">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E410">
-        <v>17.81472684085511</v>
+        <v>26.79856115107914</v>
       </c>
       <c r="F410" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="411" spans="1:6">
-      <c r="A411">
-        <v>2025</v>
-      </c>
-      <c r="B411" t="s">
-        <v>98</v>
-      </c>
-      <c r="C411" t="s">
-        <v>380</v>
-      </c>
-      <c r="D411">
-        <v>23</v>
-      </c>
-      <c r="E411">
-        <v>5.463182897862233</v>
-      </c>
-      <c r="F411" t="s">
-        <v>430</v>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6">
+      <c r="A412">
+        <v>2025</v>
+      </c>
+      <c r="B412" t="s">
+        <v>99</v>
+      </c>
+      <c r="C412" t="s">
+        <v>381</v>
+      </c>
+      <c r="D412">
+        <v>163</v>
+      </c>
+      <c r="E412">
+        <v>38.71733966745843</v>
+      </c>
+      <c r="F412" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -8226,16 +8241,16 @@
         <v>99</v>
       </c>
       <c r="C413" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D413">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E413">
-        <v>48</v>
+        <v>38.00475059382423</v>
       </c>
       <c r="F413" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -8246,16 +8261,16 @@
         <v>99</v>
       </c>
       <c r="C414" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D414">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="E414">
-        <v>40.61538461538461</v>
+        <v>17.81472684085511</v>
       </c>
       <c r="F414" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -8266,16 +8281,16 @@
         <v>99</v>
       </c>
       <c r="C415" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D415">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E415">
-        <v>11.38461538461539</v>
+        <v>5.463182897862233</v>
       </c>
       <c r="F415" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -8286,16 +8301,16 @@
         <v>100</v>
       </c>
       <c r="C417" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D417">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="E417">
-        <v>35.37414965986395</v>
+        <v>48</v>
       </c>
       <c r="F417" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
     </row>
     <row r="418" spans="1:6">
@@ -8306,16 +8321,16 @@
         <v>100</v>
       </c>
       <c r="C418" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D418">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="E418">
-        <v>26.87074829931973</v>
+        <v>40.61538461538461</v>
       </c>
       <c r="F418" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -8326,36 +8341,36 @@
         <v>100</v>
       </c>
       <c r="C419" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D419">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E419">
-        <v>26.53061224489796</v>
+        <v>11.38461538461539</v>
       </c>
       <c r="F419" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="420" spans="1:6">
-      <c r="A420">
-        <v>2025</v>
-      </c>
-      <c r="B420" t="s">
-        <v>100</v>
-      </c>
-      <c r="C420" t="s">
-        <v>387</v>
-      </c>
-      <c r="D420">
-        <v>32</v>
-      </c>
-      <c r="E420">
-        <v>10.8843537414966</v>
-      </c>
-      <c r="F420" t="s">
-        <v>412</v>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
+      <c r="A421">
+        <v>2025</v>
+      </c>
+      <c r="B421" t="s">
+        <v>101</v>
+      </c>
+      <c r="C421" t="s">
+        <v>388</v>
+      </c>
+      <c r="D421">
+        <v>104</v>
+      </c>
+      <c r="E421">
+        <v>35.37414965986395</v>
+      </c>
+      <c r="F421" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="422" spans="1:6">
@@ -8366,16 +8381,16 @@
         <v>101</v>
       </c>
       <c r="C422" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D422">
-        <v>549</v>
+        <v>79</v>
       </c>
       <c r="E422">
-        <v>42.99138606108065</v>
+        <v>26.87074829931973</v>
       </c>
       <c r="F422" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -8386,16 +8401,16 @@
         <v>101</v>
       </c>
       <c r="C423" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D423">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="E423">
-        <v>34.84729835552075</v>
+        <v>26.53061224489796</v>
       </c>
       <c r="F423" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
     </row>
     <row r="424" spans="1:6">
@@ -8406,16 +8421,16 @@
         <v>101</v>
       </c>
       <c r="C424" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D424">
-        <v>283</v>
+        <v>32</v>
       </c>
       <c r="E424">
-        <v>22.16131558339859</v>
+        <v>10.8843537414966</v>
       </c>
       <c r="F424" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
     </row>
     <row r="426" spans="1:6">
@@ -8426,16 +8441,16 @@
         <v>102</v>
       </c>
       <c r="C426" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D426">
-        <v>123</v>
+        <v>549</v>
       </c>
       <c r="E426">
-        <v>28.21100917431193</v>
+        <v>42.99138606108065</v>
       </c>
       <c r="F426" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -8446,16 +8461,16 @@
         <v>102</v>
       </c>
       <c r="C427" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D427">
-        <v>117</v>
+        <v>445</v>
       </c>
       <c r="E427">
-        <v>26.8348623853211</v>
+        <v>34.84729835552075</v>
       </c>
       <c r="F427" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -8466,36 +8481,36 @@
         <v>102</v>
       </c>
       <c r="C428" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D428">
-        <v>106</v>
+        <v>283</v>
       </c>
       <c r="E428">
-        <v>24.31192660550459</v>
+        <v>22.16131558339859</v>
       </c>
       <c r="F428" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="429" spans="1:6">
-      <c r="A429">
-        <v>2025</v>
-      </c>
-      <c r="B429" t="s">
-        <v>102</v>
-      </c>
-      <c r="C429" t="s">
-        <v>394</v>
-      </c>
-      <c r="D429">
-        <v>90</v>
-      </c>
-      <c r="E429">
-        <v>20.64220183486239</v>
-      </c>
-      <c r="F429" t="s">
-        <v>427</v>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
+      <c r="A430">
+        <v>2025</v>
+      </c>
+      <c r="B430" t="s">
+        <v>103</v>
+      </c>
+      <c r="C430" t="s">
+        <v>395</v>
+      </c>
+      <c r="D430">
+        <v>123</v>
+      </c>
+      <c r="E430">
+        <v>28.21100917431193</v>
+      </c>
+      <c r="F430" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -8506,16 +8521,16 @@
         <v>103</v>
       </c>
       <c r="C431" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D431">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="E431">
-        <v>45.03464203233256</v>
+        <v>26.8348623853211</v>
       </c>
       <c r="F431" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="432" spans="1:6">
@@ -8526,16 +8541,16 @@
         <v>103</v>
       </c>
       <c r="C432" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D432">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="E432">
-        <v>37.41339491916859</v>
+        <v>24.31192660550459</v>
       </c>
       <c r="F432" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -8546,16 +8561,16 @@
         <v>103</v>
       </c>
       <c r="C433" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D433">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E433">
-        <v>17.55196304849884</v>
+        <v>20.64220183486239</v>
       </c>
       <c r="F433" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="435" spans="1:6">
@@ -8566,16 +8581,16 @@
         <v>104</v>
       </c>
       <c r="C435" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D435">
-        <v>315</v>
+        <v>195</v>
       </c>
       <c r="E435">
-        <v>43.09165526675787</v>
+        <v>45.03464203233256</v>
       </c>
       <c r="F435" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
     </row>
     <row r="436" spans="1:6">
@@ -8586,16 +8601,16 @@
         <v>104</v>
       </c>
       <c r="C436" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D436">
-        <v>247</v>
+        <v>162</v>
       </c>
       <c r="E436">
-        <v>33.78932968536252</v>
+        <v>37.41339491916859</v>
       </c>
       <c r="F436" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -8606,16 +8621,16 @@
         <v>104</v>
       </c>
       <c r="C437" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D437">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="E437">
-        <v>23.11901504787962</v>
+        <v>17.55196304849884</v>
       </c>
       <c r="F437" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -8626,16 +8641,16 @@
         <v>105</v>
       </c>
       <c r="C439" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D439">
-        <v>3982</v>
+        <v>315</v>
       </c>
       <c r="E439">
-        <v>29.84112709832134</v>
+        <v>43.09165526675787</v>
       </c>
       <c r="F439" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="440" spans="1:6">
@@ -8646,16 +8661,16 @@
         <v>105</v>
       </c>
       <c r="C440" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D440">
-        <v>3532</v>
+        <v>247</v>
       </c>
       <c r="E440">
-        <v>26.46882494004796</v>
+        <v>33.78932968536252</v>
       </c>
       <c r="F440" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -8666,36 +8681,36 @@
         <v>105</v>
       </c>
       <c r="C441" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D441">
-        <v>2933</v>
+        <v>169</v>
       </c>
       <c r="E441">
-        <v>21.97991606714628</v>
+        <v>23.11901504787962</v>
       </c>
       <c r="F441" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="442" spans="1:6">
-      <c r="A442">
-        <v>2025</v>
-      </c>
-      <c r="B442" t="s">
-        <v>105</v>
-      </c>
-      <c r="C442" t="s">
-        <v>404</v>
-      </c>
-      <c r="D442">
-        <v>2897</v>
-      </c>
-      <c r="E442">
-        <v>21.71013189448441</v>
-      </c>
-      <c r="F442" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6">
+      <c r="A443">
+        <v>2025</v>
+      </c>
+      <c r="B443" t="s">
+        <v>106</v>
+      </c>
+      <c r="C443" t="s">
+        <v>405</v>
+      </c>
+      <c r="D443">
+        <v>3982</v>
+      </c>
+      <c r="E443">
+        <v>29.84112709832134</v>
+      </c>
+      <c r="F443" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="444" spans="1:6">
@@ -8706,16 +8721,16 @@
         <v>106</v>
       </c>
       <c r="C444" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D444">
-        <v>155</v>
+        <v>3532</v>
       </c>
       <c r="E444">
-        <v>39.84575835475578</v>
+        <v>26.46882494004796</v>
       </c>
       <c r="F444" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -8726,16 +8741,16 @@
         <v>106</v>
       </c>
       <c r="C445" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D445">
-        <v>149</v>
+        <v>2933</v>
       </c>
       <c r="E445">
-        <v>38.30334190231363</v>
+        <v>21.97991606714628</v>
       </c>
       <c r="F445" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="446" spans="1:6">
@@ -8746,16 +8761,16 @@
         <v>106</v>
       </c>
       <c r="C446" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D446">
-        <v>85</v>
+        <v>2897</v>
       </c>
       <c r="E446">
-        <v>21.85089974293059</v>
+        <v>21.71013189448441</v>
       </c>
       <c r="F446" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="448" spans="1:6">
@@ -8766,16 +8781,16 @@
         <v>107</v>
       </c>
       <c r="C448" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D448">
-        <v>328</v>
+        <v>155</v>
       </c>
       <c r="E448">
-        <v>37.27272727272727</v>
+        <v>39.84575835475578</v>
       </c>
       <c r="F448" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="449" spans="1:6">
@@ -8786,16 +8801,16 @@
         <v>107</v>
       </c>
       <c r="C449" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D449">
-        <v>310</v>
+        <v>149</v>
       </c>
       <c r="E449">
-        <v>35.22727272727273</v>
+        <v>38.30334190231363</v>
       </c>
       <c r="F449" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="450" spans="1:6">
@@ -8806,36 +8821,96 @@
         <v>107</v>
       </c>
       <c r="C450" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D450">
+        <v>85</v>
+      </c>
+      <c r="E450">
+        <v>21.85089974293059</v>
+      </c>
+      <c r="F450" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
+      <c r="A452">
+        <v>2025</v>
+      </c>
+      <c r="B452" t="s">
+        <v>108</v>
+      </c>
+      <c r="C452" t="s">
+        <v>412</v>
+      </c>
+      <c r="D452">
+        <v>328</v>
+      </c>
+      <c r="E452">
+        <v>37.27272727272727</v>
+      </c>
+      <c r="F452" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6">
+      <c r="A453">
+        <v>2025</v>
+      </c>
+      <c r="B453" t="s">
+        <v>108</v>
+      </c>
+      <c r="C453" t="s">
+        <v>413</v>
+      </c>
+      <c r="D453">
+        <v>310</v>
+      </c>
+      <c r="E453">
+        <v>35.22727272727273</v>
+      </c>
+      <c r="F453" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6">
+      <c r="A454">
+        <v>2025</v>
+      </c>
+      <c r="B454" t="s">
+        <v>108</v>
+      </c>
+      <c r="C454" t="s">
+        <v>414</v>
+      </c>
+      <c r="D454">
         <v>127</v>
       </c>
-      <c r="E450">
+      <c r="E454">
         <v>14.43181818181818</v>
       </c>
-      <c r="F450" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="451" spans="1:6">
-      <c r="A451">
-        <v>2025</v>
-      </c>
-      <c r="B451" t="s">
-        <v>107</v>
-      </c>
-      <c r="C451" t="s">
-        <v>411</v>
-      </c>
-      <c r="D451">
+      <c r="F454" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
+      <c r="A455">
+        <v>2025</v>
+      </c>
+      <c r="B455" t="s">
+        <v>108</v>
+      </c>
+      <c r="C455" t="s">
+        <v>415</v>
+      </c>
+      <c r="D455">
         <v>115</v>
       </c>
-      <c r="E451">
+      <c r="E455">
         <v>13.06818181818182</v>
       </c>
-      <c r="F451" t="s">
-        <v>420</v>
+      <c r="F455" t="s">
+        <v>424</v>
       </c>
     </row>
   </sheetData>

--- a/Pennsylvania_NonMajority_MidCounties.xlsx
+++ b/Pennsylvania_NonMajority_MidCounties.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="440">
   <si>
     <t>Year</t>
   </si>
@@ -35,9 +35,21 @@
     <t>Coverage</t>
   </si>
   <si>
+    <t>SUPERVISOR LIGONIER TOWNSHIP</t>
+  </si>
+  <si>
     <t>Chester Twp Auditor</t>
   </si>
   <si>
+    <t>REP ERIK ROSS</t>
+  </si>
+  <si>
+    <t>REP DANIEL RESENIC</t>
+  </si>
+  <si>
+    <t>DEM ROXANNE SHADRON</t>
+  </si>
+  <si>
     <t>TYRE MACON</t>
   </si>
   <si>
@@ -47,6 +59,9 @@
     <t>AKESHA GAINER</t>
   </si>
   <si>
+    <t>Westmoreland County (city + boroughs + townships)</t>
+  </si>
+  <si>
     <t>Delaware County (Media + boroughs + townships)</t>
   </si>
   <si>
@@ -1266,9 +1281,6 @@
   </si>
   <si>
     <t>Luzerne County (Wilkes-Barre + boroughs + townships)</t>
-  </si>
-  <si>
-    <t>Westmoreland County (city + boroughs + townships)</t>
   </si>
   <si>
     <t>Erie County (city + boroughs + townships)</t>
@@ -1680,7 +1692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1705,62 +1717,122 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>773</v>
+        <v>1433</v>
       </c>
       <c r="E2">
-        <v>33.97802197802198</v>
+        <v>43.93010423053342</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>757</v>
+        <v>1153</v>
       </c>
       <c r="E3">
-        <v>33.27472527472528</v>
+        <v>35.34641324340895</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4">
+        <v>676</v>
+      </c>
+      <c r="E4">
+        <v>20.72348252605763</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>773</v>
+      </c>
+      <c r="E6">
+        <v>33.97802197802198</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>2025</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>757</v>
+      </c>
+      <c r="E7">
+        <v>33.27472527472528</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
         <v>745</v>
       </c>
-      <c r="E4">
+      <c r="E8">
         <v>32.74725274725274</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
+      <c r="F8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1798,10 +1870,10 @@
         <v>2019</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D2">
         <v>799</v>
@@ -1810,7 +1882,7 @@
         <v>35.94242015294647</v>
       </c>
       <c r="F2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1818,10 +1890,10 @@
         <v>2019</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D3">
         <v>713</v>
@@ -1830,7 +1902,7 @@
         <v>32.07377417903734</v>
       </c>
       <c r="F3" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1838,10 +1910,10 @@
         <v>2019</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D4">
         <v>355</v>
@@ -1850,7 +1922,7 @@
         <v>15.96941070625281</v>
       </c>
       <c r="F4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1858,10 +1930,10 @@
         <v>2019</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D5">
         <v>190</v>
@@ -1870,7 +1942,7 @@
         <v>8.547008547008547</v>
       </c>
       <c r="F5" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1878,10 +1950,10 @@
         <v>2019</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D6">
         <v>166</v>
@@ -1890,7 +1962,7 @@
         <v>7.467386414754835</v>
       </c>
       <c r="F6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1898,10 +1970,10 @@
         <v>2019</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D8">
         <v>807</v>
@@ -1910,7 +1982,7 @@
         <v>42.87991498405951</v>
       </c>
       <c r="F8" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1918,10 +1990,10 @@
         <v>2019</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D9">
         <v>704</v>
@@ -1930,7 +2002,7 @@
         <v>37.40701381509033</v>
       </c>
       <c r="F9" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1938,10 +2010,10 @@
         <v>2019</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D10">
         <v>371</v>
@@ -1950,7 +2022,7 @@
         <v>19.71307120085016</v>
       </c>
       <c r="F10" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1958,10 +2030,10 @@
         <v>2019</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D12">
         <v>23009</v>
@@ -1970,7 +2042,7 @@
         <v>49.36282502359907</v>
       </c>
       <c r="F12" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1978,10 +2050,10 @@
         <v>2019</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D13">
         <v>10398</v>
@@ -1990,7 +2062,7 @@
         <v>22.30756028490518</v>
       </c>
       <c r="F13" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1998,10 +2070,10 @@
         <v>2019</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D14">
         <v>6676</v>
@@ -2010,7 +2082,7 @@
         <v>14.32249206212992</v>
       </c>
       <c r="F14" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2018,10 +2090,10 @@
         <v>2019</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D15">
         <v>6529</v>
@@ -2030,7 +2102,7 @@
         <v>14.00712262936583</v>
       </c>
       <c r="F15" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2038,10 +2110,10 @@
         <v>2019</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D17">
         <v>15761</v>
@@ -2050,7 +2122,7 @@
         <v>32.71613907628438</v>
       </c>
       <c r="F17" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2058,10 +2130,10 @@
         <v>2019</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D18">
         <v>12780</v>
@@ -2070,7 +2142,7 @@
         <v>26.52828230409964</v>
       </c>
       <c r="F18" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2078,10 +2150,10 @@
         <v>2019</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D19">
         <v>10691</v>
@@ -2090,7 +2162,7 @@
         <v>22.19200830306175</v>
       </c>
       <c r="F19" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2098,10 +2170,10 @@
         <v>2019</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D20">
         <v>8943</v>
@@ -2110,7 +2182,7 @@
         <v>18.56357031655423</v>
       </c>
       <c r="F20" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2118,10 +2190,10 @@
         <v>2019</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D22">
         <v>133</v>
@@ -2130,7 +2202,7 @@
         <v>41.95583596214511</v>
       </c>
       <c r="F22" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2138,10 +2210,10 @@
         <v>2019</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D23">
         <v>121</v>
@@ -2150,7 +2222,7 @@
         <v>38.17034700315457</v>
       </c>
       <c r="F23" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2158,10 +2230,10 @@
         <v>2019</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D24">
         <v>63</v>
@@ -2170,7 +2242,7 @@
         <v>19.87381703470032</v>
       </c>
       <c r="F24" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2178,10 +2250,10 @@
         <v>2019</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D26">
         <v>22897</v>
@@ -2190,7 +2262,7 @@
         <v>47.76078930351891</v>
       </c>
       <c r="F26" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2198,10 +2270,10 @@
         <v>2019</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D27">
         <v>8137</v>
@@ -2210,7 +2282,7 @@
         <v>16.97294591268434</v>
       </c>
       <c r="F27" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2218,10 +2290,10 @@
         <v>2019</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D28">
         <v>7234</v>
@@ -2230,7 +2302,7 @@
         <v>15.08938069710686</v>
       </c>
       <c r="F28" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2238,10 +2310,10 @@
         <v>2019</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D29">
         <v>5373</v>
@@ -2250,7 +2322,7 @@
         <v>11.20752591727332</v>
       </c>
       <c r="F29" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2258,10 +2330,10 @@
         <v>2019</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D30">
         <v>4300</v>
@@ -2270,7 +2342,7 @@
         <v>8.969358169416575</v>
       </c>
       <c r="F30" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2278,10 +2350,10 @@
         <v>2019</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D32">
         <v>364</v>
@@ -2290,7 +2362,7 @@
         <v>39.09774436090225</v>
       </c>
       <c r="F32" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2298,10 +2370,10 @@
         <v>2019</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D33">
         <v>341</v>
@@ -2310,7 +2382,7 @@
         <v>36.62728249194414</v>
       </c>
       <c r="F33" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2318,10 +2390,10 @@
         <v>2019</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D34">
         <v>226</v>
@@ -2330,7 +2402,7 @@
         <v>24.2749731471536</v>
       </c>
       <c r="F34" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2338,10 +2410,10 @@
         <v>2019</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D36">
         <v>1283</v>
@@ -2350,7 +2422,7 @@
         <v>40.52432090966519</v>
       </c>
       <c r="F36" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2358,10 +2430,10 @@
         <v>2019</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D37">
         <v>954</v>
@@ -2370,7 +2442,7 @@
         <v>30.13265950726469</v>
       </c>
       <c r="F37" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2378,10 +2450,10 @@
         <v>2019</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D38">
         <v>746</v>
@@ -2390,7 +2462,7 @@
         <v>23.56285533796589</v>
       </c>
       <c r="F38" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2398,10 +2470,10 @@
         <v>2019</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D39">
         <v>183</v>
@@ -2410,7 +2482,7 @@
         <v>5.780164245104232</v>
       </c>
       <c r="F39" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2418,10 +2490,10 @@
         <v>2019</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D41">
         <v>1446</v>
@@ -2430,7 +2502,7 @@
         <v>41.84027777777778</v>
       </c>
       <c r="F41" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2438,10 +2510,10 @@
         <v>2019</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D42">
         <v>1091</v>
@@ -2450,7 +2522,7 @@
         <v>31.56828703703703</v>
       </c>
       <c r="F42" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2458,10 +2530,10 @@
         <v>2019</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D43">
         <v>919</v>
@@ -2470,7 +2542,7 @@
         <v>26.59143518518519</v>
       </c>
       <c r="F43" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2478,10 +2550,10 @@
         <v>2021</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D45">
         <v>8769</v>
@@ -2490,7 +2562,7 @@
         <v>32.16683173764719</v>
       </c>
       <c r="F45" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2498,10 +2570,10 @@
         <v>2021</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D46">
         <v>8551</v>
@@ -2510,7 +2582,7 @@
         <v>31.36715454312021</v>
       </c>
       <c r="F46" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2518,10 +2590,10 @@
         <v>2021</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D47">
         <v>5669</v>
@@ -2530,7 +2602,7 @@
         <v>20.79527530171307</v>
       </c>
       <c r="F47" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2538,10 +2610,10 @@
         <v>2021</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D48">
         <v>4272</v>
@@ -2550,7 +2622,7 @@
         <v>15.67073841751953</v>
       </c>
       <c r="F48" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2558,10 +2630,10 @@
         <v>2021</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D50">
         <v>3420</v>
@@ -2570,7 +2642,7 @@
         <v>42.77673545966229</v>
       </c>
       <c r="F50" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2578,10 +2650,10 @@
         <v>2021</v>
       </c>
       <c r="B51" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D51">
         <v>2391</v>
@@ -2590,7 +2662,7 @@
         <v>29.90619136960601</v>
       </c>
       <c r="F51" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2598,10 +2670,10 @@
         <v>2021</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D52">
         <v>2184</v>
@@ -2610,7 +2682,7 @@
         <v>27.31707317073171</v>
       </c>
       <c r="F52" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2618,10 +2690,10 @@
         <v>2021</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D54">
         <v>572</v>
@@ -2630,7 +2702,7 @@
         <v>47.03947368421053</v>
       </c>
       <c r="F54" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2638,10 +2710,10 @@
         <v>2021</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D55">
         <v>380</v>
@@ -2650,7 +2722,7 @@
         <v>31.25</v>
       </c>
       <c r="F55" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2658,10 +2730,10 @@
         <v>2021</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D56">
         <v>264</v>
@@ -2670,7 +2742,7 @@
         <v>21.71052631578948</v>
       </c>
       <c r="F56" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2678,10 +2750,10 @@
         <v>2021</v>
       </c>
       <c r="B58" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D58">
         <v>177</v>
@@ -2690,7 +2762,7 @@
         <v>39.95485327313769</v>
       </c>
       <c r="F58" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2698,10 +2770,10 @@
         <v>2021</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D59">
         <v>141</v>
@@ -2710,7 +2782,7 @@
         <v>31.82844243792325</v>
       </c>
       <c r="F59" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2718,10 +2790,10 @@
         <v>2021</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D60">
         <v>81</v>
@@ -2730,7 +2802,7 @@
         <v>18.2844243792325</v>
       </c>
       <c r="F60" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2738,10 +2810,10 @@
         <v>2021</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D61">
         <v>44</v>
@@ -2750,7 +2822,7 @@
         <v>9.932279909706546</v>
       </c>
       <c r="F61" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2758,10 +2830,10 @@
         <v>2021</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D63">
         <v>1471</v>
@@ -2770,7 +2842,7 @@
         <v>44.12117576484703</v>
       </c>
       <c r="F63" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2778,10 +2850,10 @@
         <v>2021</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D64">
         <v>1247</v>
@@ -2790,7 +2862,7 @@
         <v>37.40251949610078</v>
       </c>
       <c r="F64" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2798,10 +2870,10 @@
         <v>2021</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D65">
         <v>616</v>
@@ -2810,7 +2882,7 @@
         <v>18.47630473905219</v>
       </c>
       <c r="F65" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2818,10 +2890,10 @@
         <v>2021</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C67" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D67">
         <v>1183</v>
@@ -2830,7 +2902,7 @@
         <v>39.39393939393939</v>
       </c>
       <c r="F67" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2838,10 +2910,10 @@
         <v>2021</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C68" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D68">
         <v>1177</v>
@@ -2850,7 +2922,7 @@
         <v>39.1941391941392</v>
       </c>
       <c r="F68" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2858,10 +2930,10 @@
         <v>2021</v>
       </c>
       <c r="B69" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D69">
         <v>373</v>
@@ -2870,7 +2942,7 @@
         <v>12.42091242091242</v>
       </c>
       <c r="F69" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2878,10 +2950,10 @@
         <v>2021</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C70" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D70">
         <v>270</v>
@@ -2890,7 +2962,7 @@
         <v>8.991008991008991</v>
       </c>
       <c r="F70" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2898,10 +2970,10 @@
         <v>2021</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D72">
         <v>2064</v>
@@ -2910,7 +2982,7 @@
         <v>26.63225806451613</v>
       </c>
       <c r="F72" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2918,10 +2990,10 @@
         <v>2021</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D73">
         <v>1942</v>
@@ -2930,7 +3002,7 @@
         <v>25.05806451612903</v>
       </c>
       <c r="F73" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2938,10 +3010,10 @@
         <v>2021</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C74" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D74">
         <v>1927</v>
@@ -2950,7 +3022,7 @@
         <v>24.86451612903226</v>
       </c>
       <c r="F74" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2958,10 +3030,10 @@
         <v>2021</v>
       </c>
       <c r="B75" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D75">
         <v>1817</v>
@@ -2970,7 +3042,7 @@
         <v>23.44516129032258</v>
       </c>
       <c r="F75" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2978,10 +3050,10 @@
         <v>2021</v>
       </c>
       <c r="B77" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D77">
         <v>237</v>
@@ -2990,7 +3062,7 @@
         <v>32.20108695652174</v>
       </c>
       <c r="F77" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2998,10 +3070,10 @@
         <v>2021</v>
       </c>
       <c r="B78" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C78" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D78">
         <v>234</v>
@@ -3010,7 +3082,7 @@
         <v>31.79347826086957</v>
       </c>
       <c r="F78" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3018,10 +3090,10 @@
         <v>2021</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D79">
         <v>148</v>
@@ -3030,7 +3102,7 @@
         <v>20.10869565217391</v>
       </c>
       <c r="F79" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3038,10 +3110,10 @@
         <v>2021</v>
       </c>
       <c r="B80" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C80" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D80">
         <v>90</v>
@@ -3050,7 +3122,7 @@
         <v>12.22826086956522</v>
       </c>
       <c r="F80" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3058,10 +3130,10 @@
         <v>2021</v>
       </c>
       <c r="B81" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C81" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D81">
         <v>27</v>
@@ -3070,7 +3142,7 @@
         <v>3.668478260869565</v>
       </c>
       <c r="F81" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3078,10 +3150,10 @@
         <v>2021</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C83" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D83">
         <v>212</v>
@@ -3090,7 +3162,7 @@
         <v>40.15151515151515</v>
       </c>
       <c r="F83" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3098,10 +3170,10 @@
         <v>2021</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C84" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D84">
         <v>186</v>
@@ -3110,7 +3182,7 @@
         <v>35.22727272727273</v>
       </c>
       <c r="F84" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3118,10 +3190,10 @@
         <v>2021</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C85" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D85">
         <v>130</v>
@@ -3130,7 +3202,7 @@
         <v>24.62121212121212</v>
       </c>
       <c r="F85" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3138,10 +3210,10 @@
         <v>2021</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C87" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D87">
         <v>149</v>
@@ -3150,7 +3222,7 @@
         <v>44.61077844311377</v>
       </c>
       <c r="F87" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3158,10 +3230,10 @@
         <v>2021</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D88">
         <v>115</v>
@@ -3170,7 +3242,7 @@
         <v>34.4311377245509</v>
       </c>
       <c r="F88" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3178,10 +3250,10 @@
         <v>2021</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D89">
         <v>70</v>
@@ -3190,7 +3262,7 @@
         <v>20.95808383233533</v>
       </c>
       <c r="F89" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3198,10 +3270,10 @@
         <v>2021</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C91" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D91">
         <v>138</v>
@@ -3210,7 +3282,7 @@
         <v>40.70796460176992</v>
       </c>
       <c r="F91" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3218,10 +3290,10 @@
         <v>2021</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C92" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D92">
         <v>127</v>
@@ -3230,7 +3302,7 @@
         <v>37.46312684365782</v>
       </c>
       <c r="F92" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3238,10 +3310,10 @@
         <v>2021</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D93">
         <v>74</v>
@@ -3250,7 +3322,7 @@
         <v>21.82890855457227</v>
       </c>
       <c r="F93" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3258,10 +3330,10 @@
         <v>2021</v>
       </c>
       <c r="B95" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C95" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D95">
         <v>186</v>
@@ -3270,7 +3342,7 @@
         <v>40</v>
       </c>
       <c r="F95" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3278,10 +3350,10 @@
         <v>2021</v>
       </c>
       <c r="B96" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C96" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D96">
         <v>96</v>
@@ -3290,7 +3362,7 @@
         <v>20.64516129032258</v>
       </c>
       <c r="F96" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3298,10 +3370,10 @@
         <v>2021</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C97" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D97">
         <v>95</v>
@@ -3310,7 +3382,7 @@
         <v>20.43010752688172</v>
       </c>
       <c r="F97" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3318,10 +3390,10 @@
         <v>2021</v>
       </c>
       <c r="B98" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C98" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D98">
         <v>88</v>
@@ -3330,7 +3402,7 @@
         <v>18.9247311827957</v>
       </c>
       <c r="F98" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3338,10 +3410,10 @@
         <v>2021</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C100" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D100">
         <v>154</v>
@@ -3350,7 +3422,7 @@
         <v>39.58868894601542</v>
       </c>
       <c r="F100" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3358,10 +3430,10 @@
         <v>2021</v>
       </c>
       <c r="B101" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C101" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D101">
         <v>144</v>
@@ -3370,7 +3442,7 @@
         <v>37.01799485861182</v>
       </c>
       <c r="F101" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3378,10 +3450,10 @@
         <v>2021</v>
       </c>
       <c r="B102" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C102" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D102">
         <v>91</v>
@@ -3390,7 +3462,7 @@
         <v>23.39331619537275</v>
       </c>
       <c r="F102" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3398,10 +3470,10 @@
         <v>2021</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C104" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D104">
         <v>203</v>
@@ -3410,7 +3482,7 @@
         <v>49.63325183374083</v>
       </c>
       <c r="F104" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3418,10 +3490,10 @@
         <v>2021</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C105" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D105">
         <v>127</v>
@@ -3430,7 +3502,7 @@
         <v>31.05134474327628</v>
       </c>
       <c r="F105" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3438,10 +3510,10 @@
         <v>2021</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C106" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D106">
         <v>79</v>
@@ -3450,7 +3522,7 @@
         <v>19.31540342298289</v>
       </c>
       <c r="F106" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3458,10 +3530,10 @@
         <v>2021</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C108" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D108">
         <v>293</v>
@@ -3470,7 +3542,7 @@
         <v>37.80645161290322</v>
       </c>
       <c r="F108" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3478,10 +3550,10 @@
         <v>2021</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C109" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D109">
         <v>241</v>
@@ -3490,7 +3562,7 @@
         <v>31.09677419354839</v>
       </c>
       <c r="F109" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3498,10 +3570,10 @@
         <v>2021</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C110" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D110">
         <v>125</v>
@@ -3510,7 +3582,7 @@
         <v>16.12903225806452</v>
       </c>
       <c r="F110" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3518,10 +3590,10 @@
         <v>2021</v>
       </c>
       <c r="B111" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C111" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D111">
         <v>116</v>
@@ -3530,7 +3602,7 @@
         <v>14.96774193548387</v>
       </c>
       <c r="F111" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3538,10 +3610,10 @@
         <v>2021</v>
       </c>
       <c r="B113" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C113" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D113">
         <v>588</v>
@@ -3550,7 +3622,7 @@
         <v>48.83720930232558</v>
       </c>
       <c r="F113" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3558,10 +3630,10 @@
         <v>2021</v>
       </c>
       <c r="B114" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C114" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D114">
         <v>379</v>
@@ -3570,7 +3642,7 @@
         <v>31.47840531561462</v>
       </c>
       <c r="F114" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3578,10 +3650,10 @@
         <v>2021</v>
       </c>
       <c r="B115" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C115" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D115">
         <v>237</v>
@@ -3590,7 +3662,7 @@
         <v>19.6843853820598</v>
       </c>
       <c r="F115" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3598,10 +3670,10 @@
         <v>2021</v>
       </c>
       <c r="B117" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C117" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D117">
         <v>522</v>
@@ -3610,7 +3682,7 @@
         <v>48.33333333333334</v>
       </c>
       <c r="F117" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3618,10 +3690,10 @@
         <v>2021</v>
       </c>
       <c r="B118" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C118" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D118">
         <v>331</v>
@@ -3630,7 +3702,7 @@
         <v>30.64814814814815</v>
       </c>
       <c r="F118" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3638,10 +3710,10 @@
         <v>2021</v>
       </c>
       <c r="B119" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C119" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D119">
         <v>227</v>
@@ -3650,7 +3722,7 @@
         <v>21.01851851851852</v>
       </c>
       <c r="F119" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3658,10 +3730,10 @@
         <v>2021</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C121" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D121">
         <v>4922</v>
@@ -3670,7 +3742,7 @@
         <v>41.68713475057169</v>
       </c>
       <c r="F121" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3678,10 +3750,10 @@
         <v>2021</v>
       </c>
       <c r="B122" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C122" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D122">
         <v>4820</v>
@@ -3690,7 +3762,7 @@
         <v>40.82324045058016</v>
       </c>
       <c r="F122" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3698,10 +3770,10 @@
         <v>2021</v>
       </c>
       <c r="B123" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C123" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D123">
         <v>2065</v>
@@ -3710,7 +3782,7 @@
         <v>17.48962479884814</v>
       </c>
       <c r="F123" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3718,10 +3790,10 @@
         <v>2021</v>
       </c>
       <c r="B125" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C125" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D125">
         <v>490</v>
@@ -3730,7 +3802,7 @@
         <v>47.43465634075508</v>
       </c>
       <c r="F125" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3738,10 +3810,10 @@
         <v>2021</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C126" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D126">
         <v>274</v>
@@ -3750,7 +3822,7 @@
         <v>26.52468538238141</v>
       </c>
       <c r="F126" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3758,10 +3830,10 @@
         <v>2021</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C127" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D127">
         <v>269</v>
@@ -3770,7 +3842,7 @@
         <v>26.0406582768635</v>
       </c>
       <c r="F127" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3778,10 +3850,10 @@
         <v>2021</v>
       </c>
       <c r="B129" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C129" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D129">
         <v>1165</v>
@@ -3790,7 +3862,7 @@
         <v>47.31925264012997</v>
       </c>
       <c r="F129" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3798,10 +3870,10 @@
         <v>2021</v>
       </c>
       <c r="B130" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C130" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D130">
         <v>898</v>
@@ -3810,7 +3882,7 @@
         <v>36.47441104792851</v>
       </c>
       <c r="F130" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3818,10 +3890,10 @@
         <v>2021</v>
       </c>
       <c r="B131" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C131" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D131">
         <v>211</v>
@@ -3830,7 +3902,7 @@
         <v>8.570268074735987</v>
       </c>
       <c r="F131" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3838,10 +3910,10 @@
         <v>2021</v>
       </c>
       <c r="B132" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C132" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D132">
         <v>188</v>
@@ -3850,7 +3922,7 @@
         <v>7.636068237205524</v>
       </c>
       <c r="F132" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3858,10 +3930,10 @@
         <v>2021</v>
       </c>
       <c r="B134" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C134" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D134">
         <v>1281</v>
@@ -3870,7 +3942,7 @@
         <v>43.88489208633094</v>
       </c>
       <c r="F134" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3878,10 +3950,10 @@
         <v>2021</v>
       </c>
       <c r="B135" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C135" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D135">
         <v>924</v>
@@ -3890,7 +3962,7 @@
         <v>31.6546762589928</v>
       </c>
       <c r="F135" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3898,10 +3970,10 @@
         <v>2021</v>
       </c>
       <c r="B136" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C136" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D136">
         <v>714</v>
@@ -3910,7 +3982,7 @@
         <v>24.46043165467626</v>
       </c>
       <c r="F136" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3918,10 +3990,10 @@
         <v>2021</v>
       </c>
       <c r="B138" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C138" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D138">
         <v>999</v>
@@ -3930,7 +4002,7 @@
         <v>49.47994056463596</v>
       </c>
       <c r="F138" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3938,10 +4010,10 @@
         <v>2021</v>
       </c>
       <c r="B139" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C139" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D139">
         <v>629</v>
@@ -3950,7 +4022,7 @@
         <v>31.15403665180783</v>
       </c>
       <c r="F139" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3958,10 +4030,10 @@
         <v>2021</v>
       </c>
       <c r="B140" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C140" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D140">
         <v>391</v>
@@ -3970,7 +4042,7 @@
         <v>19.36602278355622</v>
       </c>
       <c r="F140" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3978,10 +4050,10 @@
         <v>2021</v>
       </c>
       <c r="B142" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C142" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D142">
         <v>1779</v>
@@ -3990,7 +4062,7 @@
         <v>46.82811266122664</v>
       </c>
       <c r="F142" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3998,10 +4070,10 @@
         <v>2021</v>
       </c>
       <c r="B143" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C143" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D143">
         <v>1349</v>
@@ -4010,7 +4082,7 @@
         <v>35.50934456435904</v>
       </c>
       <c r="F143" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4018,10 +4090,10 @@
         <v>2021</v>
       </c>
       <c r="B144" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C144" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D144">
         <v>671</v>
@@ -4030,7 +4102,7 @@
         <v>17.66254277441432</v>
       </c>
       <c r="F144" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4038,10 +4110,10 @@
         <v>2021</v>
       </c>
       <c r="B146" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C146" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D146">
         <v>253</v>
@@ -4050,7 +4122,7 @@
         <v>37.09677419354838</v>
       </c>
       <c r="F146" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4058,10 +4130,10 @@
         <v>2021</v>
       </c>
       <c r="B147" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C147" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D147">
         <v>224</v>
@@ -4070,7 +4142,7 @@
         <v>32.84457478005865</v>
       </c>
       <c r="F147" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4078,10 +4150,10 @@
         <v>2021</v>
       </c>
       <c r="B148" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C148" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D148">
         <v>122</v>
@@ -4090,7 +4162,7 @@
         <v>17.88856304985337</v>
       </c>
       <c r="F148" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4098,10 +4170,10 @@
         <v>2021</v>
       </c>
       <c r="B149" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C149" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D149">
         <v>60</v>
@@ -4110,7 +4182,7 @@
         <v>8.797653958944283</v>
       </c>
       <c r="F149" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4118,10 +4190,10 @@
         <v>2021</v>
       </c>
       <c r="B150" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C150" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D150">
         <v>23</v>
@@ -4130,7 +4202,7 @@
         <v>3.372434017595308</v>
       </c>
       <c r="F150" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4138,10 +4210,10 @@
         <v>2021</v>
       </c>
       <c r="B152" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C152" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D152">
         <v>917</v>
@@ -4150,7 +4222,7 @@
         <v>36.31683168316832</v>
       </c>
       <c r="F152" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4158,10 +4230,10 @@
         <v>2021</v>
       </c>
       <c r="B153" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C153" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D153">
         <v>706</v>
@@ -4170,7 +4242,7 @@
         <v>27.96039603960396</v>
       </c>
       <c r="F153" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4178,10 +4250,10 @@
         <v>2021</v>
       </c>
       <c r="B154" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C154" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D154">
         <v>578</v>
@@ -4190,7 +4262,7 @@
         <v>22.89108910891089</v>
       </c>
       <c r="F154" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4198,10 +4270,10 @@
         <v>2021</v>
       </c>
       <c r="B155" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D155">
         <v>324</v>
@@ -4210,7 +4282,7 @@
         <v>12.83168316831683</v>
       </c>
       <c r="F155" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4218,10 +4290,10 @@
         <v>2021</v>
       </c>
       <c r="B157" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C157" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D157">
         <v>149</v>
@@ -4230,7 +4302,7 @@
         <v>41.38888888888889</v>
       </c>
       <c r="F157" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4238,10 +4310,10 @@
         <v>2021</v>
       </c>
       <c r="B158" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C158" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D158">
         <v>113</v>
@@ -4250,7 +4322,7 @@
         <v>31.38888888888889</v>
       </c>
       <c r="F158" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4258,10 +4330,10 @@
         <v>2021</v>
       </c>
       <c r="B159" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C159" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D159">
         <v>59</v>
@@ -4270,7 +4342,7 @@
         <v>16.38888888888889</v>
       </c>
       <c r="F159" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4278,10 +4350,10 @@
         <v>2021</v>
       </c>
       <c r="B160" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C160" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D160">
         <v>39</v>
@@ -4290,7 +4362,7 @@
         <v>10.83333333333333</v>
       </c>
       <c r="F160" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4298,10 +4370,10 @@
         <v>2021</v>
       </c>
       <c r="B162" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C162" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D162">
         <v>179</v>
@@ -4310,7 +4382,7 @@
         <v>45.31645569620253</v>
       </c>
       <c r="F162" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4318,10 +4390,10 @@
         <v>2021</v>
       </c>
       <c r="B163" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C163" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D163">
         <v>110</v>
@@ -4330,7 +4402,7 @@
         <v>27.84810126582278</v>
       </c>
       <c r="F163" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4338,10 +4410,10 @@
         <v>2021</v>
       </c>
       <c r="B164" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C164" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D164">
         <v>106</v>
@@ -4350,7 +4422,7 @@
         <v>26.83544303797468</v>
       </c>
       <c r="F164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -4358,10 +4430,10 @@
         <v>2021</v>
       </c>
       <c r="B166" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C166" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D166">
         <v>276</v>
@@ -4370,7 +4442,7 @@
         <v>47.01873935264054</v>
       </c>
       <c r="F166" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -4378,10 +4450,10 @@
         <v>2021</v>
       </c>
       <c r="B167" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C167" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D167">
         <v>226</v>
@@ -4390,7 +4462,7 @@
         <v>38.50085178875639</v>
       </c>
       <c r="F167" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -4398,10 +4470,10 @@
         <v>2021</v>
       </c>
       <c r="B168" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C168" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D168">
         <v>85</v>
@@ -4410,7 +4482,7 @@
         <v>14.48040885860307</v>
       </c>
       <c r="F168" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -4418,10 +4490,10 @@
         <v>2021</v>
       </c>
       <c r="B170" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C170" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D170">
         <v>636</v>
@@ -4430,7 +4502,7 @@
         <v>41.24513618677042</v>
       </c>
       <c r="F170" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -4438,10 +4510,10 @@
         <v>2021</v>
       </c>
       <c r="B171" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C171" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D171">
         <v>544</v>
@@ -4450,7 +4522,7 @@
         <v>35.27885862516213</v>
       </c>
       <c r="F171" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -4458,10 +4530,10 @@
         <v>2021</v>
       </c>
       <c r="B172" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C172" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D172">
         <v>362</v>
@@ -4470,7 +4542,7 @@
         <v>23.47600518806744</v>
       </c>
       <c r="F172" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4478,10 +4550,10 @@
         <v>2023</v>
       </c>
       <c r="B174" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C174" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D174">
         <v>104</v>
@@ -4490,7 +4562,7 @@
         <v>38.95131086142322</v>
       </c>
       <c r="F174" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4498,10 +4570,10 @@
         <v>2023</v>
       </c>
       <c r="B175" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C175" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D175">
         <v>100</v>
@@ -4510,7 +4582,7 @@
         <v>37.45318352059925</v>
       </c>
       <c r="F175" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4518,10 +4590,10 @@
         <v>2023</v>
       </c>
       <c r="B176" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C176" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D176">
         <v>63</v>
@@ -4530,7 +4602,7 @@
         <v>23.59550561797753</v>
       </c>
       <c r="F176" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4538,10 +4610,10 @@
         <v>2023</v>
       </c>
       <c r="B178" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C178" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D178">
         <v>1206</v>
@@ -4550,7 +4622,7 @@
         <v>37.08487084870848</v>
       </c>
       <c r="F178" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4558,10 +4630,10 @@
         <v>2023</v>
       </c>
       <c r="B179" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C179" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D179">
         <v>1121</v>
@@ -4570,7 +4642,7 @@
         <v>34.47109471094711</v>
       </c>
       <c r="F179" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4578,10 +4650,10 @@
         <v>2023</v>
       </c>
       <c r="B180" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C180" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D180">
         <v>925</v>
@@ -4590,7 +4662,7 @@
         <v>28.4440344403444</v>
       </c>
       <c r="F180" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -4598,10 +4670,10 @@
         <v>2023</v>
       </c>
       <c r="B182" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C182" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D182">
         <v>882</v>
@@ -4610,7 +4682,7 @@
         <v>45.60496380558428</v>
       </c>
       <c r="F182" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -4618,10 +4690,10 @@
         <v>2023</v>
       </c>
       <c r="B183" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C183" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D183">
         <v>502</v>
@@ -4630,7 +4702,7 @@
         <v>25.95656670113754</v>
       </c>
       <c r="F183" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4638,10 +4710,10 @@
         <v>2023</v>
       </c>
       <c r="B184" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C184" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D184">
         <v>399</v>
@@ -4650,7 +4722,7 @@
         <v>20.63081695966908</v>
       </c>
       <c r="F184" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4658,10 +4730,10 @@
         <v>2023</v>
       </c>
       <c r="B185" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C185" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D185">
         <v>151</v>
@@ -4670,7 +4742,7 @@
         <v>7.807652533609101</v>
       </c>
       <c r="F185" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4678,10 +4750,10 @@
         <v>2023</v>
       </c>
       <c r="B187" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C187" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D187">
         <v>665</v>
@@ -4690,7 +4762,7 @@
         <v>39.98797354179194</v>
       </c>
       <c r="F187" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4698,10 +4770,10 @@
         <v>2023</v>
       </c>
       <c r="B188" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C188" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D188">
         <v>429</v>
@@ -4710,7 +4782,7 @@
         <v>25.79675285628382</v>
       </c>
       <c r="F188" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -4718,10 +4790,10 @@
         <v>2023</v>
       </c>
       <c r="B189" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C189" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D189">
         <v>308</v>
@@ -4730,7 +4802,7 @@
         <v>18.5207456404089</v>
       </c>
       <c r="F189" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4738,10 +4810,10 @@
         <v>2023</v>
       </c>
       <c r="B190" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C190" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D190">
         <v>153</v>
@@ -4750,7 +4822,7 @@
         <v>9.20024052916416</v>
       </c>
       <c r="F190" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4758,10 +4830,10 @@
         <v>2023</v>
       </c>
       <c r="B191" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C191" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D191">
         <v>108</v>
@@ -4770,7 +4842,7 @@
         <v>6.494287432351173</v>
       </c>
       <c r="F191" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4778,10 +4850,10 @@
         <v>2023</v>
       </c>
       <c r="B193" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C193" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D193">
         <v>445</v>
@@ -4790,7 +4862,7 @@
         <v>43.28793774319066</v>
       </c>
       <c r="F193" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4798,10 +4870,10 @@
         <v>2023</v>
       </c>
       <c r="B194" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C194" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D194">
         <v>353</v>
@@ -4810,7 +4882,7 @@
         <v>34.33852140077821</v>
       </c>
       <c r="F194" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4818,10 +4890,10 @@
         <v>2023</v>
       </c>
       <c r="B195" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C195" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D195">
         <v>230</v>
@@ -4830,7 +4902,7 @@
         <v>22.37354085603113</v>
       </c>
       <c r="F195" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4838,10 +4910,10 @@
         <v>2023</v>
       </c>
       <c r="B197" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C197" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D197">
         <v>684</v>
@@ -4850,7 +4922,7 @@
         <v>46.94577899794098</v>
       </c>
       <c r="F197" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4858,10 +4930,10 @@
         <v>2023</v>
       </c>
       <c r="B198" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C198" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D198">
         <v>395</v>
@@ -4870,7 +4942,7 @@
         <v>27.1105010295127</v>
       </c>
       <c r="F198" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4878,10 +4950,10 @@
         <v>2023</v>
       </c>
       <c r="B199" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C199" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D199">
         <v>378</v>
@@ -4890,7 +4962,7 @@
         <v>25.94371997254633</v>
       </c>
       <c r="F199" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4898,10 +4970,10 @@
         <v>2023</v>
       </c>
       <c r="B201" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C201" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D201">
         <v>828</v>
@@ -4910,7 +4982,7 @@
         <v>36.71840354767184</v>
       </c>
       <c r="F201" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4918,10 +4990,10 @@
         <v>2023</v>
       </c>
       <c r="B202" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C202" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D202">
         <v>524</v>
@@ -4930,7 +5002,7 @@
         <v>23.23725055432372</v>
       </c>
       <c r="F202" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4938,10 +5010,10 @@
         <v>2023</v>
       </c>
       <c r="B203" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C203" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D203">
         <v>485</v>
@@ -4950,7 +5022,7 @@
         <v>21.50776053215078</v>
       </c>
       <c r="F203" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4958,10 +5030,10 @@
         <v>2023</v>
       </c>
       <c r="B204" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C204" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D204">
         <v>261</v>
@@ -4970,7 +5042,7 @@
         <v>11.57427937915743</v>
       </c>
       <c r="F204" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4978,10 +5050,10 @@
         <v>2023</v>
       </c>
       <c r="B205" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C205" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D205">
         <v>157</v>
@@ -4990,7 +5062,7 @@
         <v>6.962305986696231</v>
       </c>
       <c r="F205" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4998,10 +5070,10 @@
         <v>2023</v>
       </c>
       <c r="B207" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C207" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D207">
         <v>584</v>
@@ -5010,7 +5082,7 @@
         <v>43.90977443609022</v>
       </c>
       <c r="F207" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -5018,10 +5090,10 @@
         <v>2023</v>
       </c>
       <c r="B208" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C208" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D208">
         <v>388</v>
@@ -5030,7 +5102,7 @@
         <v>29.17293233082707</v>
       </c>
       <c r="F208" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -5038,10 +5110,10 @@
         <v>2023</v>
       </c>
       <c r="B209" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C209" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D209">
         <v>358</v>
@@ -5050,7 +5122,7 @@
         <v>26.91729323308271</v>
       </c>
       <c r="F209" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -5058,10 +5130,10 @@
         <v>2023</v>
       </c>
       <c r="B211" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C211" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D211">
         <v>634</v>
@@ -5070,7 +5142,7 @@
         <v>45.67723342939482</v>
       </c>
       <c r="F211" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -5078,10 +5150,10 @@
         <v>2023</v>
       </c>
       <c r="B212" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D212">
         <v>298</v>
@@ -5090,7 +5162,7 @@
         <v>21.46974063400576</v>
       </c>
       <c r="F212" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -5098,10 +5170,10 @@
         <v>2023</v>
       </c>
       <c r="B213" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C213" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D213">
         <v>246</v>
@@ -5110,7 +5182,7 @@
         <v>17.72334293948127</v>
       </c>
       <c r="F213" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -5118,10 +5190,10 @@
         <v>2023</v>
       </c>
       <c r="B214" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C214" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D214">
         <v>210</v>
@@ -5130,7 +5202,7 @@
         <v>15.12968299711815</v>
       </c>
       <c r="F214" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -5138,10 +5210,10 @@
         <v>2023</v>
       </c>
       <c r="B216" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C216" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D216">
         <v>294</v>
@@ -5150,7 +5222,7 @@
         <v>38.33116036505867</v>
       </c>
       <c r="F216" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -5158,10 +5230,10 @@
         <v>2023</v>
       </c>
       <c r="B217" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C217" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D217">
         <v>145</v>
@@ -5170,7 +5242,7 @@
         <v>18.90482398956975</v>
       </c>
       <c r="F217" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -5178,10 +5250,10 @@
         <v>2023</v>
       </c>
       <c r="B218" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C218" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D218">
         <v>136</v>
@@ -5190,7 +5262,7 @@
         <v>17.73142112125163</v>
       </c>
       <c r="F218" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -5198,10 +5270,10 @@
         <v>2023</v>
       </c>
       <c r="B219" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C219" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D219">
         <v>104</v>
@@ -5210,7 +5282,7 @@
         <v>13.5593220338983</v>
       </c>
       <c r="F219" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -5218,10 +5290,10 @@
         <v>2023</v>
       </c>
       <c r="B220" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C220" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D220">
         <v>88</v>
@@ -5230,7 +5302,7 @@
         <v>11.47327249022164</v>
       </c>
       <c r="F220" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -5238,10 +5310,10 @@
         <v>2023</v>
       </c>
       <c r="B222" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C222" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D222">
         <v>957</v>
@@ -5250,7 +5322,7 @@
         <v>36.62456946039035</v>
       </c>
       <c r="F222" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -5258,10 +5330,10 @@
         <v>2023</v>
       </c>
       <c r="B223" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C223" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D223">
         <v>917</v>
@@ -5270,7 +5342,7 @@
         <v>35.0937619594336</v>
       </c>
       <c r="F223" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -5278,10 +5350,10 @@
         <v>2023</v>
       </c>
       <c r="B224" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C224" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D224">
         <v>739</v>
@@ -5290,7 +5362,7 @@
         <v>28.28166858017605</v>
       </c>
       <c r="F224" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -5298,10 +5370,10 @@
         <v>2023</v>
       </c>
       <c r="B226" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C226" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D226">
         <v>5642</v>
@@ -5310,7 +5382,7 @@
         <v>34.00638900608764</v>
       </c>
       <c r="F226" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -5318,10 +5390,10 @@
         <v>2023</v>
       </c>
       <c r="B227" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C227" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D227">
         <v>5540</v>
@@ -5330,7 +5402,7 @@
         <v>33.39159785425833</v>
       </c>
       <c r="F227" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -5338,10 +5410,10 @@
         <v>2023</v>
       </c>
       <c r="B228" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C228" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D228">
         <v>5409</v>
@@ -5350,7 +5422,7 @@
         <v>32.60201313965403</v>
       </c>
       <c r="F228" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5358,10 +5430,10 @@
         <v>2023</v>
       </c>
       <c r="B230" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C230" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D230">
         <v>170</v>
@@ -5370,7 +5442,7 @@
         <v>46.19565217391305</v>
       </c>
       <c r="F230" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -5378,10 +5450,10 @@
         <v>2023</v>
       </c>
       <c r="B231" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C231" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D231">
         <v>169</v>
@@ -5390,7 +5462,7 @@
         <v>45.92391304347826</v>
       </c>
       <c r="F231" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -5398,10 +5470,10 @@
         <v>2023</v>
       </c>
       <c r="B232" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C232" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D232">
         <v>29</v>
@@ -5410,7 +5482,7 @@
         <v>7.880434782608696</v>
       </c>
       <c r="F232" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5418,10 +5490,10 @@
         <v>2023</v>
       </c>
       <c r="B234" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C234" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D234">
         <v>1471</v>
@@ -5430,7 +5502,7 @@
         <v>47.82184655396619</v>
       </c>
       <c r="F234" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -5438,10 +5510,10 @@
         <v>2023</v>
       </c>
       <c r="B235" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C235" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D235">
         <v>857</v>
@@ -5450,7 +5522,7 @@
         <v>27.86085825747724</v>
       </c>
       <c r="F235" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -5458,10 +5530,10 @@
         <v>2023</v>
       </c>
       <c r="B236" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C236" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D236">
         <v>748</v>
@@ -5470,7 +5542,7 @@
         <v>24.31729518855657</v>
       </c>
       <c r="F236" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -5478,10 +5550,10 @@
         <v>2023</v>
       </c>
       <c r="B238" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C238" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D238">
         <v>616</v>
@@ -5490,7 +5562,7 @@
         <v>48.85011895321173</v>
       </c>
       <c r="F238" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -5498,10 +5570,10 @@
         <v>2023</v>
       </c>
       <c r="B239" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C239" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D239">
         <v>534</v>
@@ -5510,7 +5582,7 @@
         <v>42.34734337827121</v>
       </c>
       <c r="F239" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -5518,10 +5590,10 @@
         <v>2023</v>
       </c>
       <c r="B240" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C240" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D240">
         <v>111</v>
@@ -5530,7 +5602,7 @@
         <v>8.802537668517051</v>
       </c>
       <c r="F240" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -5538,10 +5610,10 @@
         <v>2023</v>
       </c>
       <c r="B242" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C242" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D242">
         <v>1114</v>
@@ -5550,7 +5622,7 @@
         <v>47.79064779064779</v>
       </c>
       <c r="F242" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -5558,10 +5630,10 @@
         <v>2023</v>
       </c>
       <c r="B243" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C243" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D243">
         <v>647</v>
@@ -5570,7 +5642,7 @@
         <v>27.75632775632776</v>
       </c>
       <c r="F243" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -5578,10 +5650,10 @@
         <v>2023</v>
       </c>
       <c r="B244" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C244" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D244">
         <v>369</v>
@@ -5590,7 +5662,7 @@
         <v>15.83011583011583</v>
       </c>
       <c r="F244" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -5598,10 +5670,10 @@
         <v>2023</v>
       </c>
       <c r="B245" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C245" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D245">
         <v>201</v>
@@ -5610,7 +5682,7 @@
         <v>8.622908622908623</v>
       </c>
       <c r="F245" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -5618,10 +5690,10 @@
         <v>2023</v>
       </c>
       <c r="B247" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C247" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D247">
         <v>592</v>
@@ -5630,7 +5702,7 @@
         <v>32.52747252747253</v>
       </c>
       <c r="F247" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -5638,10 +5710,10 @@
         <v>2023</v>
       </c>
       <c r="B248" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C248" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D248">
         <v>571</v>
@@ -5650,7 +5722,7 @@
         <v>31.37362637362637</v>
       </c>
       <c r="F248" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -5658,10 +5730,10 @@
         <v>2023</v>
       </c>
       <c r="B249" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C249" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D249">
         <v>324</v>
@@ -5670,7 +5742,7 @@
         <v>17.8021978021978</v>
       </c>
       <c r="F249" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -5678,10 +5750,10 @@
         <v>2023</v>
       </c>
       <c r="B250" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C250" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D250">
         <v>295</v>
@@ -5690,7 +5762,7 @@
         <v>16.20879120879121</v>
       </c>
       <c r="F250" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -5698,10 +5770,10 @@
         <v>2023</v>
       </c>
       <c r="B251" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C251" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D251">
         <v>38</v>
@@ -5710,7 +5782,7 @@
         <v>2.087912087912088</v>
       </c>
       <c r="F251" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -5718,10 +5790,10 @@
         <v>2023</v>
       </c>
       <c r="B253" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C253" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D253">
         <v>886</v>
@@ -5730,7 +5802,7 @@
         <v>48.86927744070601</v>
       </c>
       <c r="F253" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -5738,10 +5810,10 @@
         <v>2023</v>
       </c>
       <c r="B254" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C254" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D254">
         <v>699</v>
@@ -5750,7 +5822,7 @@
         <v>38.55488141202427</v>
       </c>
       <c r="F254" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -5758,10 +5830,10 @@
         <v>2023</v>
       </c>
       <c r="B255" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C255" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D255">
         <v>228</v>
@@ -5770,7 +5842,7 @@
         <v>12.57584114726972</v>
       </c>
       <c r="F255" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -5778,10 +5850,10 @@
         <v>2023</v>
       </c>
       <c r="B257" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C257" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D257">
         <v>1630</v>
@@ -5790,7 +5862,7 @@
         <v>44.46262956901255</v>
       </c>
       <c r="F257" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -5798,10 +5870,10 @@
         <v>2023</v>
       </c>
       <c r="B258" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C258" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D258">
         <v>1039</v>
@@ -5810,7 +5882,7 @@
         <v>28.34151663938898</v>
       </c>
       <c r="F258" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -5818,10 +5890,10 @@
         <v>2023</v>
       </c>
       <c r="B259" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C259" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D259">
         <v>813</v>
@@ -5830,7 +5902,7 @@
         <v>22.17675941080196</v>
       </c>
       <c r="F259" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -5838,10 +5910,10 @@
         <v>2023</v>
       </c>
       <c r="B260" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C260" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D260">
         <v>184</v>
@@ -5850,7 +5922,7 @@
         <v>5.019094380796509</v>
       </c>
       <c r="F260" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -5858,10 +5930,10 @@
         <v>2023</v>
       </c>
       <c r="B262" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C262" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D262">
         <v>1334</v>
@@ -5870,7 +5942,7 @@
         <v>46.38386648122393</v>
       </c>
       <c r="F262" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -5878,10 +5950,10 @@
         <v>2023</v>
       </c>
       <c r="B263" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C263" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D263">
         <v>1278</v>
@@ -5890,7 +5962,7 @@
         <v>44.43671766342142</v>
       </c>
       <c r="F263" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -5898,10 +5970,10 @@
         <v>2023</v>
       </c>
       <c r="B264" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C264" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D264">
         <v>264</v>
@@ -5910,7 +5982,7 @@
         <v>9.179415855354661</v>
       </c>
       <c r="F264" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -5918,10 +5990,10 @@
         <v>2023</v>
       </c>
       <c r="B266" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C266" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D266">
         <v>1466</v>
@@ -5930,7 +6002,7 @@
         <v>43.1303324507208</v>
       </c>
       <c r="F266" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -5938,10 +6010,10 @@
         <v>2023</v>
       </c>
       <c r="B267" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C267" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D267">
         <v>893</v>
@@ -5950,7 +6022,7 @@
         <v>26.27243306854957</v>
       </c>
       <c r="F267" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -5958,10 +6030,10 @@
         <v>2023</v>
       </c>
       <c r="B268" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C268" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D268">
         <v>672</v>
@@ -5970,7 +6042,7 @@
         <v>19.77052074139453</v>
       </c>
       <c r="F268" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -5978,10 +6050,10 @@
         <v>2023</v>
       </c>
       <c r="B269" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C269" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D269">
         <v>245</v>
@@ -5990,7 +6062,7 @@
         <v>7.208002353633422</v>
       </c>
       <c r="F269" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -5998,10 +6070,10 @@
         <v>2023</v>
       </c>
       <c r="B270" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C270" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D270">
         <v>123</v>
@@ -6010,7 +6082,7 @@
         <v>3.618711385701677</v>
       </c>
       <c r="F270" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -6018,10 +6090,10 @@
         <v>2023</v>
       </c>
       <c r="B272" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C272" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D272">
         <v>1108</v>
@@ -6030,7 +6102,7 @@
         <v>46.4765100671141</v>
       </c>
       <c r="F272" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -6038,10 +6110,10 @@
         <v>2023</v>
       </c>
       <c r="B273" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C273" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D273">
         <v>444</v>
@@ -6050,7 +6122,7 @@
         <v>18.6241610738255</v>
       </c>
       <c r="F273" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -6058,10 +6130,10 @@
         <v>2023</v>
       </c>
       <c r="B274" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C274" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D274">
         <v>343</v>
@@ -6070,7 +6142,7 @@
         <v>14.38758389261745</v>
       </c>
       <c r="F274" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -6078,10 +6150,10 @@
         <v>2023</v>
       </c>
       <c r="B275" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C275" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D275">
         <v>323</v>
@@ -6090,7 +6162,7 @@
         <v>13.5486577181208</v>
       </c>
       <c r="F275" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -6098,10 +6170,10 @@
         <v>2023</v>
       </c>
       <c r="B276" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C276" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D276">
         <v>166</v>
@@ -6110,7 +6182,7 @@
         <v>6.963087248322148</v>
       </c>
       <c r="F276" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -6118,10 +6190,10 @@
         <v>2023</v>
       </c>
       <c r="B278" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C278" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D278">
         <v>904</v>
@@ -6130,7 +6202,7 @@
         <v>42.60131950989632</v>
       </c>
       <c r="F278" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -6138,10 +6210,10 @@
         <v>2023</v>
       </c>
       <c r="B279" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C279" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D279">
         <v>860</v>
@@ -6150,7 +6222,7 @@
         <v>40.52780395852969</v>
       </c>
       <c r="F279" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -6158,10 +6230,10 @@
         <v>2023</v>
       </c>
       <c r="B280" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C280" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D280">
         <v>193</v>
@@ -6170,7 +6242,7 @@
         <v>9.095193213949104</v>
       </c>
       <c r="F280" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -6178,10 +6250,10 @@
         <v>2023</v>
       </c>
       <c r="B281" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C281" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D281">
         <v>165</v>
@@ -6190,7 +6262,7 @@
         <v>7.775683317624882</v>
       </c>
       <c r="F281" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -6198,10 +6270,10 @@
         <v>2023</v>
       </c>
       <c r="B283" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C283" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D283">
         <v>425</v>
@@ -6210,7 +6282,7 @@
         <v>25.11820330969267</v>
       </c>
       <c r="F283" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -6218,10 +6290,10 @@
         <v>2023</v>
       </c>
       <c r="B284" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C284" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D284">
         <v>341</v>
@@ -6230,7 +6302,7 @@
         <v>20.15366430260048</v>
       </c>
       <c r="F284" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -6238,10 +6310,10 @@
         <v>2023</v>
       </c>
       <c r="B285" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C285" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D285">
         <v>279</v>
@@ -6250,7 +6322,7 @@
         <v>16.48936170212766</v>
       </c>
       <c r="F285" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -6258,10 +6330,10 @@
         <v>2023</v>
       </c>
       <c r="B286" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C286" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D286">
         <v>272</v>
@@ -6270,7 +6342,7 @@
         <v>16.07565011820331</v>
       </c>
       <c r="F286" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -6278,10 +6350,10 @@
         <v>2023</v>
       </c>
       <c r="B287" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C287" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D287">
         <v>220</v>
@@ -6290,7 +6362,7 @@
         <v>13.00236406619385</v>
       </c>
       <c r="F287" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -6298,10 +6370,10 @@
         <v>2023</v>
       </c>
       <c r="B288" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C288" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D288">
         <v>155</v>
@@ -6310,7 +6382,7 @@
         <v>9.160756501182032</v>
       </c>
       <c r="F288" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -6318,10 +6390,10 @@
         <v>2023</v>
       </c>
       <c r="B290" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C290" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D290">
         <v>272</v>
@@ -6330,7 +6402,7 @@
         <v>44.01294498381877</v>
       </c>
       <c r="F290" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -6338,10 +6410,10 @@
         <v>2023</v>
       </c>
       <c r="B291" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C291" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D291">
         <v>145</v>
@@ -6350,7 +6422,7 @@
         <v>23.46278317152104</v>
       </c>
       <c r="F291" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -6358,10 +6430,10 @@
         <v>2023</v>
       </c>
       <c r="B292" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C292" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D292">
         <v>108</v>
@@ -6370,7 +6442,7 @@
         <v>17.47572815533981</v>
       </c>
       <c r="F292" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -6378,10 +6450,10 @@
         <v>2023</v>
       </c>
       <c r="B293" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C293" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D293">
         <v>50</v>
@@ -6390,7 +6462,7 @@
         <v>8.090614886731391</v>
       </c>
       <c r="F293" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -6398,10 +6470,10 @@
         <v>2023</v>
       </c>
       <c r="B294" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C294" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D294">
         <v>43</v>
@@ -6410,7 +6482,7 @@
         <v>6.957928802588997</v>
       </c>
       <c r="F294" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -6418,10 +6490,10 @@
         <v>2023</v>
       </c>
       <c r="B296" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C296" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D296">
         <v>286</v>
@@ -6430,7 +6502,7 @@
         <v>48.22934232715008</v>
       </c>
       <c r="F296" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -6438,10 +6510,10 @@
         <v>2023</v>
       </c>
       <c r="B297" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C297" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D297">
         <v>212</v>
@@ -6450,7 +6522,7 @@
         <v>35.7504215851602</v>
       </c>
       <c r="F297" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -6458,10 +6530,10 @@
         <v>2023</v>
       </c>
       <c r="B298" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C298" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D298">
         <v>95</v>
@@ -6470,7 +6542,7 @@
         <v>16.02023608768971</v>
       </c>
       <c r="F298" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -6478,10 +6550,10 @@
         <v>2023</v>
       </c>
       <c r="B300" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C300" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D300">
         <v>431</v>
@@ -6490,7 +6562,7 @@
         <v>36.77474402730375</v>
       </c>
       <c r="F300" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -6498,10 +6570,10 @@
         <v>2023</v>
       </c>
       <c r="B301" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C301" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D301">
         <v>297</v>
@@ -6510,7 +6582,7 @@
         <v>25.34129692832764</v>
       </c>
       <c r="F301" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -6518,10 +6590,10 @@
         <v>2023</v>
       </c>
       <c r="B302" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C302" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D302">
         <v>285</v>
@@ -6530,7 +6602,7 @@
         <v>24.31740614334471</v>
       </c>
       <c r="F302" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -6538,10 +6610,10 @@
         <v>2023</v>
       </c>
       <c r="B303" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C303" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D303">
         <v>96</v>
@@ -6550,7 +6622,7 @@
         <v>8.191126279863481</v>
       </c>
       <c r="F303" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -6558,10 +6630,10 @@
         <v>2023</v>
       </c>
       <c r="B304" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C304" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D304">
         <v>63</v>
@@ -6570,7 +6642,7 @@
         <v>5.375426621160409</v>
       </c>
       <c r="F304" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -6578,10 +6650,10 @@
         <v>2023</v>
       </c>
       <c r="B306" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C306" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D306">
         <v>273</v>
@@ -6590,7 +6662,7 @@
         <v>45.4242928452579</v>
       </c>
       <c r="F306" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -6598,10 +6670,10 @@
         <v>2023</v>
       </c>
       <c r="B307" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C307" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D307">
         <v>234</v>
@@ -6610,7 +6682,7 @@
         <v>38.9351081530782</v>
       </c>
       <c r="F307" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -6618,10 +6690,10 @@
         <v>2023</v>
       </c>
       <c r="B308" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C308" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D308">
         <v>94</v>
@@ -6630,7 +6702,7 @@
         <v>15.64059900166389</v>
       </c>
       <c r="F308" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -6638,10 +6710,10 @@
         <v>2023</v>
       </c>
       <c r="B310" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C310" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D310">
         <v>124</v>
@@ -6650,7 +6722,7 @@
         <v>47.69230769230769</v>
       </c>
       <c r="F310" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -6658,10 +6730,10 @@
         <v>2023</v>
       </c>
       <c r="B311" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C311" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D311">
         <v>73</v>
@@ -6670,7 +6742,7 @@
         <v>28.07692307692308</v>
       </c>
       <c r="F311" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -6678,10 +6750,10 @@
         <v>2023</v>
       </c>
       <c r="B312" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C312" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D312">
         <v>63</v>
@@ -6690,7 +6762,7 @@
         <v>24.23076923076923</v>
       </c>
       <c r="F312" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -6698,10 +6770,10 @@
         <v>2023</v>
       </c>
       <c r="B314" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C314" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D314">
         <v>827</v>
@@ -6710,7 +6782,7 @@
         <v>47.88650839606254</v>
       </c>
       <c r="F314" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -6718,10 +6790,10 @@
         <v>2023</v>
       </c>
       <c r="B315" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C315" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D315">
         <v>284</v>
@@ -6730,7 +6802,7 @@
         <v>16.44470179502026</v>
       </c>
       <c r="F315" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -6738,10 +6810,10 @@
         <v>2023</v>
       </c>
       <c r="B316" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C316" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D316">
         <v>222</v>
@@ -6750,7 +6822,7 @@
         <v>12.85466126230457</v>
       </c>
       <c r="F316" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -6758,10 +6830,10 @@
         <v>2023</v>
       </c>
       <c r="B317" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C317" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D317">
         <v>211</v>
@@ -6770,7 +6842,7 @@
         <v>12.21771858714534</v>
       </c>
       <c r="F317" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -6778,10 +6850,10 @@
         <v>2023</v>
       </c>
       <c r="B318" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C318" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D318">
         <v>183</v>
@@ -6790,7 +6862,7 @@
         <v>10.59640995946728</v>
       </c>
       <c r="F318" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -6798,10 +6870,10 @@
         <v>2023</v>
       </c>
       <c r="B320" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C320" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D320">
         <v>186</v>
@@ -6810,7 +6882,7 @@
         <v>42.46575342465754</v>
       </c>
       <c r="F320" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -6818,10 +6890,10 @@
         <v>2023</v>
       </c>
       <c r="B321" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C321" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D321">
         <v>144</v>
@@ -6830,7 +6902,7 @@
         <v>32.87671232876712</v>
       </c>
       <c r="F321" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -6838,10 +6910,10 @@
         <v>2023</v>
       </c>
       <c r="B322" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C322" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D322">
         <v>108</v>
@@ -6850,7 +6922,7 @@
         <v>24.65753424657534</v>
       </c>
       <c r="F322" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -6858,10 +6930,10 @@
         <v>2023</v>
       </c>
       <c r="B324" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C324" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D324">
         <v>605</v>
@@ -6870,7 +6942,7 @@
         <v>41.10054347826087</v>
       </c>
       <c r="F324" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -6878,10 +6950,10 @@
         <v>2023</v>
       </c>
       <c r="B325" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C325" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D325">
         <v>593</v>
@@ -6890,7 +6962,7 @@
         <v>40.28532608695652</v>
       </c>
       <c r="F325" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -6898,10 +6970,10 @@
         <v>2023</v>
       </c>
       <c r="B326" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C326" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D326">
         <v>274</v>
@@ -6910,7 +6982,7 @@
         <v>18.61413043478261</v>
       </c>
       <c r="F326" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -6918,10 +6990,10 @@
         <v>2023</v>
       </c>
       <c r="B328" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C328" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D328">
         <v>347</v>
@@ -6930,7 +7002,7 @@
         <v>49.15014164305949</v>
       </c>
       <c r="F328" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -6938,10 +7010,10 @@
         <v>2023</v>
       </c>
       <c r="B329" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C329" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D329">
         <v>168</v>
@@ -6950,7 +7022,7 @@
         <v>23.79603399433428</v>
       </c>
       <c r="F329" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -6958,10 +7030,10 @@
         <v>2023</v>
       </c>
       <c r="B330" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C330" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="D330">
         <v>103</v>
@@ -6970,7 +7042,7 @@
         <v>14.58923512747875</v>
       </c>
       <c r="F330" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -6978,10 +7050,10 @@
         <v>2023</v>
       </c>
       <c r="B331" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C331" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D331">
         <v>88</v>
@@ -6990,7 +7062,7 @@
         <v>12.46458923512748</v>
       </c>
       <c r="F331" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -6998,10 +7070,10 @@
         <v>2023</v>
       </c>
       <c r="B333" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C333" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D333">
         <v>372</v>
@@ -7010,7 +7082,7 @@
         <v>42.36902050113896</v>
       </c>
       <c r="F333" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -7018,10 +7090,10 @@
         <v>2023</v>
       </c>
       <c r="B334" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C334" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D334">
         <v>195</v>
@@ -7030,7 +7102,7 @@
         <v>22.20956719817768</v>
       </c>
       <c r="F334" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -7038,10 +7110,10 @@
         <v>2023</v>
       </c>
       <c r="B335" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C335" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D335">
         <v>193</v>
@@ -7050,7 +7122,7 @@
         <v>21.98177676537586</v>
       </c>
       <c r="F335" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -7058,10 +7130,10 @@
         <v>2023</v>
       </c>
       <c r="B336" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C336" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D336">
         <v>118</v>
@@ -7070,7 +7142,7 @@
         <v>13.43963553530752</v>
       </c>
       <c r="F336" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -7078,10 +7150,10 @@
         <v>2024</v>
       </c>
       <c r="B338" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C338" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D338">
         <v>147</v>
@@ -7090,7 +7162,7 @@
         <v>44.68085106382978</v>
       </c>
       <c r="F338" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -7098,10 +7170,10 @@
         <v>2024</v>
       </c>
       <c r="B339" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C339" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D339">
         <v>102</v>
@@ -7110,7 +7182,7 @@
         <v>31.00303951367781</v>
       </c>
       <c r="F339" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -7118,10 +7190,10 @@
         <v>2024</v>
       </c>
       <c r="B340" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C340" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D340">
         <v>80</v>
@@ -7130,7 +7202,7 @@
         <v>24.3161094224924</v>
       </c>
       <c r="F340" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -7138,10 +7210,10 @@
         <v>2025</v>
       </c>
       <c r="B342" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C342" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D342">
         <v>1224</v>
@@ -7150,7 +7222,7 @@
         <v>28.77291960507758</v>
       </c>
       <c r="F342" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="343" spans="1:6">
@@ -7158,10 +7230,10 @@
         <v>2025</v>
       </c>
       <c r="B343" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C343" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D343">
         <v>1052</v>
@@ -7170,7 +7242,7 @@
         <v>24.72966619652092</v>
       </c>
       <c r="F343" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -7178,10 +7250,10 @@
         <v>2025</v>
       </c>
       <c r="B344" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C344" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D344">
         <v>685</v>
@@ -7190,7 +7262,7 @@
         <v>16.10249177244946</v>
       </c>
       <c r="F344" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -7198,10 +7270,10 @@
         <v>2025</v>
       </c>
       <c r="B345" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C345" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D345">
         <v>656</v>
@@ -7210,7 +7282,7 @@
         <v>15.420780441937</v>
       </c>
       <c r="F345" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -7218,10 +7290,10 @@
         <v>2025</v>
       </c>
       <c r="B346" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C346" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D346">
         <v>637</v>
@@ -7230,7 +7302,7 @@
         <v>14.97414198401504</v>
       </c>
       <c r="F346" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -7238,10 +7310,10 @@
         <v>2025</v>
       </c>
       <c r="B348" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C348" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D348">
         <v>3817</v>
@@ -7250,7 +7322,7 @@
         <v>39.10860655737705</v>
       </c>
       <c r="F348" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -7258,10 +7330,10 @@
         <v>2025</v>
       </c>
       <c r="B349" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C349" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D349">
         <v>3272</v>
@@ -7270,7 +7342,7 @@
         <v>33.52459016393443</v>
       </c>
       <c r="F349" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="350" spans="1:6">
@@ -7278,10 +7350,10 @@
         <v>2025</v>
       </c>
       <c r="B350" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C350" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D350">
         <v>2671</v>
@@ -7290,7 +7362,7 @@
         <v>27.36680327868852</v>
       </c>
       <c r="F350" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="352" spans="1:6">
@@ -7298,10 +7370,10 @@
         <v>2025</v>
       </c>
       <c r="B352" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C352" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D352">
         <v>710</v>
@@ -7310,7 +7382,7 @@
         <v>46.64914586070959</v>
       </c>
       <c r="F352" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -7318,10 +7390,10 @@
         <v>2025</v>
       </c>
       <c r="B353" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C353" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D353">
         <v>617</v>
@@ -7330,7 +7402,7 @@
         <v>40.53876478318003</v>
       </c>
       <c r="F353" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="354" spans="1:6">
@@ -7338,10 +7410,10 @@
         <v>2025</v>
       </c>
       <c r="B354" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C354" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D354">
         <v>195</v>
@@ -7350,7 +7422,7 @@
         <v>12.81208935611038</v>
       </c>
       <c r="F354" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -7358,10 +7430,10 @@
         <v>2025</v>
       </c>
       <c r="B356" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C356" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="D356">
         <v>7014</v>
@@ -7370,7 +7442,7 @@
         <v>38.28393646635008</v>
       </c>
       <c r="F356" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -7378,10 +7450,10 @@
         <v>2025</v>
       </c>
       <c r="B357" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C357" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D357">
         <v>6543</v>
@@ -7390,7 +7462,7 @@
         <v>35.71311609628295</v>
       </c>
       <c r="F357" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -7398,10 +7470,10 @@
         <v>2025</v>
       </c>
       <c r="B358" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C358" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D358">
         <v>4764</v>
@@ -7410,7 +7482,7 @@
         <v>26.00294743736696</v>
       </c>
       <c r="F358" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -7418,10 +7490,10 @@
         <v>2025</v>
       </c>
       <c r="B360" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C360" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D360">
         <v>241</v>
@@ -7430,7 +7502,7 @@
         <v>49.79338842975206</v>
       </c>
       <c r="F360" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="361" spans="1:6">
@@ -7438,10 +7510,10 @@
         <v>2025</v>
       </c>
       <c r="B361" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C361" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D361">
         <v>193</v>
@@ -7450,7 +7522,7 @@
         <v>39.87603305785124</v>
       </c>
       <c r="F361" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -7458,10 +7530,10 @@
         <v>2025</v>
       </c>
       <c r="B362" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C362" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D362">
         <v>49</v>
@@ -7470,7 +7542,7 @@
         <v>10.12396694214876</v>
       </c>
       <c r="F362" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -7478,10 +7550,10 @@
         <v>2025</v>
       </c>
       <c r="B364" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C364" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D364">
         <v>373</v>
@@ -7490,7 +7562,7 @@
         <v>36.39024390243902</v>
       </c>
       <c r="F364" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="365" spans="1:6">
@@ -7498,10 +7570,10 @@
         <v>2025</v>
       </c>
       <c r="B365" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C365" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D365">
         <v>225</v>
@@ -7510,7 +7582,7 @@
         <v>21.95121951219512</v>
       </c>
       <c r="F365" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -7518,10 +7590,10 @@
         <v>2025</v>
       </c>
       <c r="B366" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C366" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D366">
         <v>206</v>
@@ -7530,7 +7602,7 @@
         <v>20.09756097560976</v>
       </c>
       <c r="F366" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="367" spans="1:6">
@@ -7538,10 +7610,10 @@
         <v>2025</v>
       </c>
       <c r="B367" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C367" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D367">
         <v>140</v>
@@ -7550,7 +7622,7 @@
         <v>13.65853658536586</v>
       </c>
       <c r="F367" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -7558,10 +7630,10 @@
         <v>2025</v>
       </c>
       <c r="B368" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C368" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D368">
         <v>81</v>
@@ -7570,7 +7642,7 @@
         <v>7.902439024390244</v>
       </c>
       <c r="F368" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -7578,10 +7650,10 @@
         <v>2025</v>
       </c>
       <c r="B370" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C370" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D370">
         <v>6552</v>
@@ -7590,7 +7662,7 @@
         <v>47.15704620699582</v>
       </c>
       <c r="F370" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -7598,10 +7670,10 @@
         <v>2025</v>
       </c>
       <c r="B371" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C371" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D371">
         <v>4724</v>
@@ -7610,7 +7682,7 @@
         <v>34.00028789405498</v>
       </c>
       <c r="F371" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -7618,10 +7690,10 @@
         <v>2025</v>
       </c>
       <c r="B372" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C372" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D372">
         <v>2618</v>
@@ -7630,7 +7702,7 @@
         <v>18.84266589894919</v>
       </c>
       <c r="F372" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="374" spans="1:6">
@@ -7638,10 +7710,10 @@
         <v>2025</v>
       </c>
       <c r="B374" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C374" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D374">
         <v>5832</v>
@@ -7650,7 +7722,7 @@
         <v>37.28423475258919</v>
       </c>
       <c r="F374" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -7658,10 +7730,10 @@
         <v>2025</v>
       </c>
       <c r="B375" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C375" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D375">
         <v>4950</v>
@@ -7670,7 +7742,7 @@
         <v>31.64556962025317</v>
       </c>
       <c r="F375" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="376" spans="1:6">
@@ -7678,10 +7750,10 @@
         <v>2025</v>
       </c>
       <c r="B376" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C376" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D376">
         <v>4834</v>
@@ -7690,7 +7762,7 @@
         <v>30.90397647359673</v>
       </c>
       <c r="F376" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -7698,10 +7770,10 @@
         <v>2025</v>
       </c>
       <c r="B378" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C378" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D378">
         <v>9318</v>
@@ -7710,7 +7782,7 @@
         <v>41.92764578833693</v>
       </c>
       <c r="F378" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="379" spans="1:6">
@@ -7718,10 +7790,10 @@
         <v>2025</v>
       </c>
       <c r="B379" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C379" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D379">
         <v>8700</v>
@@ -7730,7 +7802,7 @@
         <v>39.14686825053996</v>
       </c>
       <c r="F379" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="380" spans="1:6">
@@ -7738,10 +7810,10 @@
         <v>2025</v>
       </c>
       <c r="B380" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C380" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D380">
         <v>4206</v>
@@ -7750,7 +7822,7 @@
         <v>18.92548596112311</v>
       </c>
       <c r="F380" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="382" spans="1:6">
@@ -7758,10 +7830,10 @@
         <v>2025</v>
       </c>
       <c r="B382" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C382" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D382">
         <v>193</v>
@@ -7770,7 +7842,7 @@
         <v>44.36781609195402</v>
       </c>
       <c r="F382" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="383" spans="1:6">
@@ -7778,10 +7850,10 @@
         <v>2025</v>
       </c>
       <c r="B383" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C383" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D383">
         <v>161</v>
@@ -7790,7 +7862,7 @@
         <v>37.01149425287356</v>
       </c>
       <c r="F383" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -7798,10 +7870,10 @@
         <v>2025</v>
       </c>
       <c r="B384" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C384" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D384">
         <v>81</v>
@@ -7810,7 +7882,7 @@
         <v>18.62068965517242</v>
       </c>
       <c r="F384" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="386" spans="1:6">
@@ -7818,10 +7890,10 @@
         <v>2025</v>
       </c>
       <c r="B386" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C386" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D386">
         <v>1473</v>
@@ -7830,7 +7902,7 @@
         <v>39.30096051227321</v>
       </c>
       <c r="F386" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -7838,10 +7910,10 @@
         <v>2025</v>
       </c>
       <c r="B387" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C387" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D387">
         <v>1297</v>
@@ -7850,7 +7922,7 @@
         <v>34.6051227321238</v>
       </c>
       <c r="F387" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -7858,10 +7930,10 @@
         <v>2025</v>
       </c>
       <c r="B388" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C388" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D388">
         <v>516</v>
@@ -7870,7 +7942,7 @@
         <v>13.76734258271078</v>
       </c>
       <c r="F388" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -7878,10 +7950,10 @@
         <v>2025</v>
       </c>
       <c r="B389" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C389" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D389">
         <v>305</v>
@@ -7890,7 +7962,7 @@
         <v>8.137673425827108</v>
       </c>
       <c r="F389" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -7898,10 +7970,10 @@
         <v>2025</v>
       </c>
       <c r="B390" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C390" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D390">
         <v>157</v>
@@ -7910,7 +7982,7 @@
         <v>4.188900747065102</v>
       </c>
       <c r="F390" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="392" spans="1:6">
@@ -7918,10 +7990,10 @@
         <v>2025</v>
       </c>
       <c r="B392" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C392" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D392">
         <v>854</v>
@@ -7930,7 +8002,7 @@
         <v>47.52365052865888</v>
       </c>
       <c r="F392" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="393" spans="1:6">
@@ -7938,10 +8010,10 @@
         <v>2025</v>
       </c>
       <c r="B393" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C393" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D393">
         <v>764</v>
@@ -7950,7 +8022,7 @@
         <v>42.51530328324986</v>
       </c>
       <c r="F393" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -7958,10 +8030,10 @@
         <v>2025</v>
       </c>
       <c r="B394" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C394" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D394">
         <v>175</v>
@@ -7970,7 +8042,7 @@
         <v>9.738452977184195</v>
       </c>
       <c r="F394" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -7978,10 +8050,10 @@
         <v>2025</v>
       </c>
       <c r="B396" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C396" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D396">
         <v>162</v>
@@ -7990,7 +8062,7 @@
         <v>45.2513966480447</v>
       </c>
       <c r="F396" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="397" spans="1:6">
@@ -7998,10 +8070,10 @@
         <v>2025</v>
       </c>
       <c r="B397" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C397" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D397">
         <v>156</v>
@@ -8010,7 +8082,7 @@
         <v>43.5754189944134</v>
       </c>
       <c r="F397" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="398" spans="1:6">
@@ -8018,10 +8090,10 @@
         <v>2025</v>
       </c>
       <c r="B398" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C398" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D398">
         <v>40</v>
@@ -8030,7 +8102,7 @@
         <v>11.1731843575419</v>
       </c>
       <c r="F398" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="400" spans="1:6">
@@ -8038,10 +8110,10 @@
         <v>2025</v>
       </c>
       <c r="B400" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C400" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D400">
         <v>11367</v>
@@ -8050,7 +8122,7 @@
         <v>45.69280861840254</v>
       </c>
       <c r="F400" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -8058,10 +8130,10 @@
         <v>2025</v>
       </c>
       <c r="B401" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C401" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D401">
         <v>8188</v>
@@ -8070,7 +8142,7 @@
         <v>32.91393656791413</v>
       </c>
       <c r="F401" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="402" spans="1:6">
@@ -8078,10 +8150,10 @@
         <v>2025</v>
       </c>
       <c r="B402" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C402" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D402">
         <v>5322</v>
@@ -8090,7 +8162,7 @@
         <v>21.39325481368332</v>
       </c>
       <c r="F402" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="404" spans="1:6">
@@ -8098,10 +8170,10 @@
         <v>2025</v>
       </c>
       <c r="B404" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C404" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D404">
         <v>287</v>
@@ -8110,7 +8182,7 @@
         <v>47.83333333333334</v>
       </c>
       <c r="F404" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -8118,10 +8190,10 @@
         <v>2025</v>
       </c>
       <c r="B405" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C405" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D405">
         <v>175</v>
@@ -8130,7 +8202,7 @@
         <v>29.16666666666667</v>
       </c>
       <c r="F405" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="406" spans="1:6">
@@ -8138,10 +8210,10 @@
         <v>2025</v>
       </c>
       <c r="B406" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C406" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D406">
         <v>138</v>
@@ -8150,7 +8222,7 @@
         <v>23</v>
       </c>
       <c r="F406" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -8158,10 +8230,10 @@
         <v>2025</v>
       </c>
       <c r="B408" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C408" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D408">
         <v>253</v>
@@ -8170,7 +8242,7 @@
         <v>45.50359712230216</v>
       </c>
       <c r="F408" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="409" spans="1:6">
@@ -8178,10 +8250,10 @@
         <v>2025</v>
       </c>
       <c r="B409" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C409" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D409">
         <v>154</v>
@@ -8190,7 +8262,7 @@
         <v>27.69784172661871</v>
       </c>
       <c r="F409" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -8198,10 +8270,10 @@
         <v>2025</v>
       </c>
       <c r="B410" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C410" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D410">
         <v>149</v>
@@ -8210,7 +8282,7 @@
         <v>26.79856115107914</v>
       </c>
       <c r="F410" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -8218,10 +8290,10 @@
         <v>2025</v>
       </c>
       <c r="B412" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C412" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D412">
         <v>163</v>
@@ -8230,7 +8302,7 @@
         <v>38.71733966745843</v>
       </c>
       <c r="F412" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -8238,10 +8310,10 @@
         <v>2025</v>
       </c>
       <c r="B413" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C413" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D413">
         <v>160</v>
@@ -8250,7 +8322,7 @@
         <v>38.00475059382423</v>
       </c>
       <c r="F413" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -8258,10 +8330,10 @@
         <v>2025</v>
       </c>
       <c r="B414" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C414" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="D414">
         <v>75</v>
@@ -8270,7 +8342,7 @@
         <v>17.81472684085511</v>
       </c>
       <c r="F414" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -8278,10 +8350,10 @@
         <v>2025</v>
       </c>
       <c r="B415" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C415" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D415">
         <v>23</v>
@@ -8290,7 +8362,7 @@
         <v>5.463182897862233</v>
       </c>
       <c r="F415" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -8298,10 +8370,10 @@
         <v>2025</v>
       </c>
       <c r="B417" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C417" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="D417">
         <v>156</v>
@@ -8310,7 +8382,7 @@
         <v>48</v>
       </c>
       <c r="F417" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="418" spans="1:6">
@@ -8318,10 +8390,10 @@
         <v>2025</v>
       </c>
       <c r="B418" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C418" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D418">
         <v>132</v>
@@ -8330,7 +8402,7 @@
         <v>40.61538461538461</v>
       </c>
       <c r="F418" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -8338,10 +8410,10 @@
         <v>2025</v>
       </c>
       <c r="B419" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C419" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D419">
         <v>37</v>
@@ -8350,7 +8422,7 @@
         <v>11.38461538461539</v>
       </c>
       <c r="F419" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -8358,10 +8430,10 @@
         <v>2025</v>
       </c>
       <c r="B421" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C421" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D421">
         <v>104</v>
@@ -8370,7 +8442,7 @@
         <v>35.37414965986395</v>
       </c>
       <c r="F421" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="422" spans="1:6">
@@ -8378,10 +8450,10 @@
         <v>2025</v>
       </c>
       <c r="B422" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C422" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D422">
         <v>79</v>
@@ -8390,7 +8462,7 @@
         <v>26.87074829931973</v>
       </c>
       <c r="F422" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -8398,10 +8470,10 @@
         <v>2025</v>
       </c>
       <c r="B423" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C423" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D423">
         <v>78</v>
@@ -8410,7 +8482,7 @@
         <v>26.53061224489796</v>
       </c>
       <c r="F423" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="424" spans="1:6">
@@ -8418,10 +8490,10 @@
         <v>2025</v>
       </c>
       <c r="B424" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C424" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D424">
         <v>32</v>
@@ -8430,7 +8502,7 @@
         <v>10.8843537414966</v>
       </c>
       <c r="F424" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="426" spans="1:6">
@@ -8438,10 +8510,10 @@
         <v>2025</v>
       </c>
       <c r="B426" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C426" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D426">
         <v>549</v>
@@ -8450,7 +8522,7 @@
         <v>42.99138606108065</v>
       </c>
       <c r="F426" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -8458,10 +8530,10 @@
         <v>2025</v>
       </c>
       <c r="B427" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C427" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D427">
         <v>445</v>
@@ -8470,7 +8542,7 @@
         <v>34.84729835552075</v>
       </c>
       <c r="F427" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -8478,10 +8550,10 @@
         <v>2025</v>
       </c>
       <c r="B428" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C428" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D428">
         <v>283</v>
@@ -8490,7 +8562,7 @@
         <v>22.16131558339859</v>
       </c>
       <c r="F428" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -8498,10 +8570,10 @@
         <v>2025</v>
       </c>
       <c r="B430" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C430" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D430">
         <v>123</v>
@@ -8510,7 +8582,7 @@
         <v>28.21100917431193</v>
       </c>
       <c r="F430" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -8518,10 +8590,10 @@
         <v>2025</v>
       </c>
       <c r="B431" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C431" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D431">
         <v>117</v>
@@ -8530,7 +8602,7 @@
         <v>26.8348623853211</v>
       </c>
       <c r="F431" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="432" spans="1:6">
@@ -8538,10 +8610,10 @@
         <v>2025</v>
       </c>
       <c r="B432" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C432" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D432">
         <v>106</v>
@@ -8550,7 +8622,7 @@
         <v>24.31192660550459</v>
       </c>
       <c r="F432" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -8558,10 +8630,10 @@
         <v>2025</v>
       </c>
       <c r="B433" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C433" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D433">
         <v>90</v>
@@ -8570,7 +8642,7 @@
         <v>20.64220183486239</v>
       </c>
       <c r="F433" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="435" spans="1:6">
@@ -8578,10 +8650,10 @@
         <v>2025</v>
       </c>
       <c r="B435" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C435" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D435">
         <v>195</v>
@@ -8590,7 +8662,7 @@
         <v>45.03464203233256</v>
       </c>
       <c r="F435" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="436" spans="1:6">
@@ -8598,10 +8670,10 @@
         <v>2025</v>
       </c>
       <c r="B436" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C436" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D436">
         <v>162</v>
@@ -8610,7 +8682,7 @@
         <v>37.41339491916859</v>
       </c>
       <c r="F436" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -8618,10 +8690,10 @@
         <v>2025</v>
       </c>
       <c r="B437" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C437" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D437">
         <v>76</v>
@@ -8630,7 +8702,7 @@
         <v>17.55196304849884</v>
       </c>
       <c r="F437" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -8638,10 +8710,10 @@
         <v>2025</v>
       </c>
       <c r="B439" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C439" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D439">
         <v>315</v>
@@ -8650,7 +8722,7 @@
         <v>43.09165526675787</v>
       </c>
       <c r="F439" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="440" spans="1:6">
@@ -8658,10 +8730,10 @@
         <v>2025</v>
       </c>
       <c r="B440" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C440" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D440">
         <v>247</v>
@@ -8670,7 +8742,7 @@
         <v>33.78932968536252</v>
       </c>
       <c r="F440" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -8678,10 +8750,10 @@
         <v>2025</v>
       </c>
       <c r="B441" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C441" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D441">
         <v>169</v>
@@ -8690,7 +8762,7 @@
         <v>23.11901504787962</v>
       </c>
       <c r="F441" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -8698,10 +8770,10 @@
         <v>2025</v>
       </c>
       <c r="B443" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C443" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D443">
         <v>3982</v>
@@ -8710,7 +8782,7 @@
         <v>29.84112709832134</v>
       </c>
       <c r="F443" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="444" spans="1:6">
@@ -8718,10 +8790,10 @@
         <v>2025</v>
       </c>
       <c r="B444" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C444" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D444">
         <v>3532</v>
@@ -8730,7 +8802,7 @@
         <v>26.46882494004796</v>
       </c>
       <c r="F444" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -8738,10 +8810,10 @@
         <v>2025</v>
       </c>
       <c r="B445" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C445" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D445">
         <v>2933</v>
@@ -8750,7 +8822,7 @@
         <v>21.97991606714628</v>
       </c>
       <c r="F445" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="446" spans="1:6">
@@ -8758,10 +8830,10 @@
         <v>2025</v>
       </c>
       <c r="B446" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C446" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D446">
         <v>2897</v>
@@ -8770,7 +8842,7 @@
         <v>21.71013189448441</v>
       </c>
       <c r="F446" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="448" spans="1:6">
@@ -8778,10 +8850,10 @@
         <v>2025</v>
       </c>
       <c r="B448" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C448" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D448">
         <v>155</v>
@@ -8790,7 +8862,7 @@
         <v>39.84575835475578</v>
       </c>
       <c r="F448" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="449" spans="1:6">
@@ -8798,10 +8870,10 @@
         <v>2025</v>
       </c>
       <c r="B449" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C449" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D449">
         <v>149</v>
@@ -8810,7 +8882,7 @@
         <v>38.30334190231363</v>
       </c>
       <c r="F449" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="450" spans="1:6">
@@ -8818,10 +8890,10 @@
         <v>2025</v>
       </c>
       <c r="B450" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C450" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D450">
         <v>85</v>
@@ -8830,7 +8902,7 @@
         <v>21.85089974293059</v>
       </c>
       <c r="F450" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="452" spans="1:6">
@@ -8838,10 +8910,10 @@
         <v>2025</v>
       </c>
       <c r="B452" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C452" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D452">
         <v>328</v>
@@ -8850,7 +8922,7 @@
         <v>37.27272727272727</v>
       </c>
       <c r="F452" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="453" spans="1:6">
@@ -8858,10 +8930,10 @@
         <v>2025</v>
       </c>
       <c r="B453" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C453" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D453">
         <v>310</v>
@@ -8870,7 +8942,7 @@
         <v>35.22727272727273</v>
       </c>
       <c r="F453" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="454" spans="1:6">
@@ -8878,10 +8950,10 @@
         <v>2025</v>
       </c>
       <c r="B454" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C454" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D454">
         <v>127</v>
@@ -8890,7 +8962,7 @@
         <v>14.43181818181818</v>
       </c>
       <c r="F454" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="455" spans="1:6">
@@ -8898,10 +8970,10 @@
         <v>2025</v>
       </c>
       <c r="B455" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C455" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D455">
         <v>115</v>
@@ -8910,7 +8982,7 @@
         <v>13.06818181818182</v>
       </c>
       <c r="F455" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
